--- a/KSTOCK.xlsx
+++ b/KSTOCK.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c2e6f8dd72a68295/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="45" documentId="11_C9E6DE52C4094E9AB632FCC5BEAB4EC433025488" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FADF219C-6775-4104-BF65-8B7E174EB021}"/>
+  <xr:revisionPtr revIDLastSave="50" documentId="11_C936DE5EC4094E9AB632FCC5BE045EC4273C7029" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B22D174-DD1B-4D40-A4EF-78A71FEAB2E3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$233</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$244</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="479">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="476">
   <si>
     <t>ROSUSEP-20</t>
   </si>
@@ -139,6 +139,9 @@
     <t>25S3GTA657</t>
   </si>
   <si>
+    <t>ACECLOPHARM-SP FORTE</t>
+  </si>
+  <si>
     <t>CHYMOACTIVE-FORTE</t>
   </si>
   <si>
@@ -217,9 +220,6 @@
     <t>SITAFREE-MET 500 IR</t>
   </si>
   <si>
-    <t>25S3GTA265</t>
-  </si>
-  <si>
     <t>25S3GTA916</t>
   </si>
   <si>
@@ -262,6 +262,9 @@
     <t>25S1GTA562</t>
   </si>
   <si>
+    <t>BETA COBAL-G</t>
+  </si>
+  <si>
     <t>ATROLIA-40</t>
   </si>
   <si>
@@ -316,15 +319,15 @@
     <t>AZIPACE-250</t>
   </si>
   <si>
+    <t>25S2GTA330</t>
+  </si>
+  <si>
+    <t>20X6</t>
+  </si>
+  <si>
     <t>25S2GTB662</t>
   </si>
   <si>
-    <t>20X6</t>
-  </si>
-  <si>
-    <t>25S2GTA330</t>
-  </si>
-  <si>
     <t>DAPAPHARM-M</t>
   </si>
   <si>
@@ -349,12 +352,12 @@
     <t>ROSUSEP- GOLD 10</t>
   </si>
   <si>
+    <t>25S3GCA050</t>
+  </si>
+  <si>
     <t>25S3GCA094</t>
   </si>
   <si>
-    <t>25S3GCA050</t>
-  </si>
-  <si>
     <t>ROSUSEP- GOLD 20</t>
   </si>
   <si>
@@ -364,12 +367,15 @@
     <t>ROSUSEP-ASP 10</t>
   </si>
   <si>
-    <t>25S3GCA104</t>
-  </si>
-  <si>
     <t>25S3GCA125</t>
   </si>
   <si>
+    <t>UDISWIFT 300</t>
+  </si>
+  <si>
+    <t>10X15</t>
+  </si>
+  <si>
     <t>ITRAZOLLIN 100</t>
   </si>
   <si>
@@ -388,9 +394,6 @@
     <t>LEZIOD 600</t>
   </si>
   <si>
-    <t>25S2GTC412</t>
-  </si>
-  <si>
     <t>PREGAWALK NT 50/10</t>
   </si>
   <si>
@@ -406,12 +409,12 @@
     <t>TICASHIELD-90</t>
   </si>
   <si>
+    <t>10X1X14</t>
+  </si>
+  <si>
     <t>25S2GTC854</t>
   </si>
   <si>
-    <t>10X1X14</t>
-  </si>
-  <si>
     <t>PREGAWALK NT 75/10</t>
   </si>
   <si>
@@ -436,9 +439,6 @@
     <t>25S2GTB434</t>
   </si>
   <si>
-    <t>25S2GTA696</t>
-  </si>
-  <si>
     <t>SITAFREE-50</t>
   </si>
   <si>
@@ -463,21 +463,21 @@
     <t>GABAKAT NT-400</t>
   </si>
   <si>
+    <t>25S3GTA585</t>
+  </si>
+  <si>
     <t>25S3GTA850</t>
   </si>
   <si>
-    <t>25S3GTA585</t>
-  </si>
-  <si>
     <t>VILDAPHARM-OD 100</t>
   </si>
   <si>
+    <t>25S1GTA780</t>
+  </si>
+  <si>
     <t>25S1GTA463</t>
   </si>
   <si>
-    <t>25S1GTA780</t>
-  </si>
-  <si>
     <t>REBEHIT-LS</t>
   </si>
   <si>
@@ -502,15 +502,12 @@
     <t>ATROLIA GOLD 20/75</t>
   </si>
   <si>
+    <t>25S3GCA129</t>
+  </si>
+  <si>
     <t>25S3GCA113</t>
   </si>
   <si>
-    <t>25S3GCA129</t>
-  </si>
-  <si>
-    <t>25S3GCA078</t>
-  </si>
-  <si>
     <t>Atrolia-ASP 75</t>
   </si>
   <si>
@@ -526,12 +523,12 @@
     <t>ROSUSEP-CV 10</t>
   </si>
   <si>
+    <t>25S3GCA099</t>
+  </si>
+  <si>
     <t>25S3GCA046</t>
   </si>
   <si>
-    <t>25S3GCA099</t>
-  </si>
-  <si>
     <t>ROSUSEP-CV 20</t>
   </si>
   <si>
@@ -574,6 +571,12 @@
     <t>10X5X1ML</t>
   </si>
   <si>
+    <t>BAKUMIDE 1ML INJECTION</t>
+  </si>
+  <si>
+    <t>10X1ML</t>
+  </si>
+  <si>
     <t>CALWINIT D3 INJ</t>
   </si>
   <si>
@@ -604,15 +607,15 @@
     <t>DECAHIT INJECTION</t>
   </si>
   <si>
+    <t>NL2722504</t>
+  </si>
+  <si>
+    <t>96X2ML</t>
+  </si>
+  <si>
     <t>NL2722503</t>
   </si>
   <si>
-    <t>96X2ML</t>
-  </si>
-  <si>
-    <t>NL2722504</t>
-  </si>
-  <si>
     <t>GENTAHIT INJ</t>
   </si>
   <si>
@@ -769,12 +772,6 @@
     <t>NL2702506</t>
   </si>
   <si>
-    <t>ACECLOPHARM P TABLET</t>
-  </si>
-  <si>
-    <t>MT2602050</t>
-  </si>
-  <si>
     <t>ACECLOPHARM-MR TABLET</t>
   </si>
   <si>
@@ -784,24 +781,33 @@
     <t>MT2507317A</t>
   </si>
   <si>
+    <t>ACECLOPHARM-PLUS TABLET</t>
+  </si>
+  <si>
     <t>AMLINA-5 TABLET</t>
   </si>
   <si>
+    <t>T50499A</t>
+  </si>
+  <si>
+    <t>20X30</t>
+  </si>
+  <si>
     <t>T60096A</t>
   </si>
   <si>
-    <t>20X30</t>
-  </si>
-  <si>
-    <t>T50499A</t>
-  </si>
-  <si>
     <t>AMLINA-AT TABLET</t>
   </si>
   <si>
     <t>DRQ02ADA</t>
   </si>
   <si>
+    <t>CEFIXLIA - 200 TABLET</t>
+  </si>
+  <si>
+    <t>CLAVMYCIN 625 DUO TABLET</t>
+  </si>
+  <si>
     <t>DICLODARD-MR TABLET</t>
   </si>
   <si>
@@ -853,9 +859,6 @@
     <t>DRQ01ACA</t>
   </si>
   <si>
-    <t>10X15</t>
-  </si>
-  <si>
     <t>NIMUDARD-P GOLD TABLET</t>
   </si>
   <si>
@@ -880,30 +883,21 @@
     <t>T50625B</t>
   </si>
   <si>
-    <t>OMNISYN-D CAPSULE</t>
-  </si>
-  <si>
-    <t>MC2508085</t>
+    <t>OMNISYN 20 CAPSULE</t>
   </si>
   <si>
     <t>20X20</t>
   </si>
   <si>
-    <t>ONMOTRON MD TABLET</t>
-  </si>
-  <si>
-    <t>T50762D</t>
-  </si>
-  <si>
     <t>PANTAHIT 40 TABLET 15S</t>
   </si>
   <si>
+    <t>GF985056B</t>
+  </si>
+  <si>
     <t>GF986003C</t>
   </si>
   <si>
-    <t>GF985056B</t>
-  </si>
-  <si>
     <t>PANTAHIT-D TABLET</t>
   </si>
   <si>
@@ -1003,6 +997,12 @@
     <t>L60050A</t>
   </si>
   <si>
+    <t>POVIALL OINTMENT 15 GM</t>
+  </si>
+  <si>
+    <t>1X15GM</t>
+  </si>
+  <si>
     <t>POVIALL OINTMENT 250 GM</t>
   </si>
   <si>
@@ -1039,12 +1039,12 @@
     <t>OFFSYN 200 TABLET (Blister)</t>
   </si>
   <si>
+    <t>T50628A</t>
+  </si>
+  <si>
     <t>T60106A</t>
   </si>
   <si>
-    <t>T50628A</t>
-  </si>
-  <si>
     <t>ENOXAEASE 60 INJ</t>
   </si>
   <si>
@@ -1063,6 +1063,12 @@
     <t>75 GM</t>
   </si>
   <si>
+    <t>EPODOX-CV TABLET</t>
+  </si>
+  <si>
+    <t>KEMROXIM 500 TABLET</t>
+  </si>
+  <si>
     <t>CALWINIT CT</t>
   </si>
   <si>
@@ -1078,12 +1084,12 @@
     <t>CALWINIT-D3 SOFTGEL CAPSULE</t>
   </si>
   <si>
+    <t>20X1X4</t>
+  </si>
+  <si>
     <t>3D260094D</t>
   </si>
   <si>
-    <t>20X1X4</t>
-  </si>
-  <si>
     <t>VOLOPAIN MAXX 35GM</t>
   </si>
   <si>
@@ -1159,9 +1165,6 @@
     <t>12X5X10</t>
   </si>
   <si>
-    <t>T250967</t>
-  </si>
-  <si>
     <t>Tempfree 650 Tablet</t>
   </si>
   <si>
@@ -1171,6 +1174,9 @@
     <t>30X15</t>
   </si>
   <si>
+    <t>CLAVMYCIN 375 DUO TABLET</t>
+  </si>
+  <si>
     <t>Cefixlia DS 100</t>
   </si>
   <si>
@@ -1264,18 +1270,12 @@
     <t>DANSOFT SHAMPOO 7.5ML SACHET</t>
   </si>
   <si>
+    <t>7.5ML</t>
+  </si>
+  <si>
     <t>N13250001</t>
   </si>
   <si>
-    <t>7.5ML</t>
-  </si>
-  <si>
-    <t>DICLODARD-SP TABLET</t>
-  </si>
-  <si>
-    <t>MT2602055</t>
-  </si>
-  <si>
     <t>POVIALL 7.5% SCRUB  500ML</t>
   </si>
   <si>
@@ -1285,15 +1285,15 @@
     <t>POVIALL OINTMENT 125GM</t>
   </si>
   <si>
+    <t>GLN26004</t>
+  </si>
+  <si>
+    <t>125GM</t>
+  </si>
+  <si>
     <t>GLN26007</t>
   </si>
   <si>
-    <t>125GM</t>
-  </si>
-  <si>
-    <t>GLN26004</t>
-  </si>
-  <si>
     <t>FAROPHARM 300 ER TABLET</t>
   </si>
   <si>
@@ -1303,12 +1303,12 @@
     <t>CEFIXLIA-O 200 TABLET</t>
   </si>
   <si>
+    <t>CT26007G</t>
+  </si>
+  <si>
     <t>CT25488B</t>
   </si>
   <si>
-    <t>CT26007G</t>
-  </si>
-  <si>
     <t>MONTALIA-LC 60ML SYRUP</t>
   </si>
   <si>
@@ -1330,39 +1330,30 @@
     <t>MC2510116</t>
   </si>
   <si>
-    <t>MC2510117</t>
-  </si>
-  <si>
     <t>PANTAHIT DSR CAPSULE (20x10)</t>
   </si>
   <si>
-    <t>MC2601003A</t>
-  </si>
-  <si>
     <t>CLAVMYCIN 625 DUO TABLET (20x1x10)</t>
   </si>
   <si>
+    <t>50045258</t>
+  </si>
+  <si>
     <t>50046010</t>
   </si>
   <si>
-    <t>50045258</t>
-  </si>
-  <si>
-    <t>KEMROXIM 500 TABLET</t>
-  </si>
-  <si>
     <t>CT25512H</t>
   </si>
   <si>
     <t>CEFIXLIA - 200 DT TABLET</t>
   </si>
   <si>
+    <t>CT26039A</t>
+  </si>
+  <si>
     <t>CT25427</t>
   </si>
   <si>
-    <t>CT26039A</t>
-  </si>
-  <si>
     <t>FERRIFINE XT TABLET</t>
   </si>
   <si>
@@ -1393,15 +1384,15 @@
     <t>VOLOPAIN AQ INJECTION</t>
   </si>
   <si>
+    <t>NL3062501</t>
+  </si>
+  <si>
+    <t>20 X 5 X 1ML</t>
+  </si>
+  <si>
     <t>NL3062502</t>
   </si>
   <si>
-    <t>20 X 5 X 1ML</t>
-  </si>
-  <si>
-    <t>NL3062501</t>
-  </si>
-  <si>
     <t>MONTALIA-LC 30ML SYRUP</t>
   </si>
   <si>
@@ -1444,6 +1435,9 @@
     <t>Item Name</t>
   </si>
   <si>
+    <t>Unrestricted Qty</t>
+  </si>
+  <si>
     <t>PACK STYLE</t>
   </si>
   <si>
@@ -1456,20 +1450,14 @@
     <t xml:space="preserve"> Batch No.</t>
   </si>
   <si>
-    <t xml:space="preserve"> Unrestricted Qty</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Blocked Qty</t>
+    <t xml:space="preserve"> Transit Qty</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.000"/>
-  </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1480,15 +1468,8 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1497,7 +1478,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1529,7 +1516,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -1540,9 +1527,6 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1557,37 +1541,23 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1917,82 +1887,80 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H233"/>
+  <dimension ref="A1:H244"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="37.21875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11.77734375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.88671875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.5546875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="12.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="12.77734375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30.109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.77734375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="20" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.88671875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="11.33203125" style="1" customWidth="1"/>
     <col min="9" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>469</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>474</v>
+      </c>
+      <c r="E1" s="6" t="s">
         <v>471</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>472</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="G1" s="7" t="s">
+        <v>470</v>
+      </c>
+      <c r="H1" s="7" t="s">
         <v>475</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>476</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>473</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>474</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>477</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>478</v>
-      </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="9">
-        <v>6010000117</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>281</v>
-      </c>
-      <c r="C2" s="12">
-        <v>46711</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>282</v>
-      </c>
-      <c r="E2" s="10" t="s">
+      <c r="A2" s="8">
+        <v>6010000095</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="C2" s="10"/>
+      <c r="D2" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="13"/>
+      <c r="F2" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="11"/>
       <c r="H2" s="11">
-        <v>6520</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
-        <v>6010000094</v>
+        <v>6010000095</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="C3" s="5">
-        <v>46753</v>
+        <v>249</v>
+      </c>
+      <c r="C3" s="4">
+        <v>46568</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>23</v>
@@ -2000,20 +1968,20 @@
       <c r="F3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="6">
-        <v>2400</v>
-      </c>
-      <c r="H3" s="4"/>
+      <c r="G3" s="5">
+        <v>5460</v>
+      </c>
+      <c r="H3" s="5"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>6010000095</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="C4" s="5">
-        <v>46568</v>
+        <v>249</v>
+      </c>
+      <c r="C4" s="4">
+        <v>46559</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>251</v>
@@ -2024,130 +1992,126 @@
       <c r="F4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="6">
-        <v>5460</v>
-      </c>
-      <c r="H4" s="4"/>
+      <c r="G4" s="5">
+        <v>2820</v>
+      </c>
+      <c r="H4" s="5"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
-        <v>6010000095</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="C5" s="5">
-        <v>46559</v>
-      </c>
-      <c r="D5" s="3" t="s">
+      <c r="A5" s="8">
+        <v>6010000096</v>
+      </c>
+      <c r="B5" s="9" t="s">
         <v>252</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="C5" s="10"/>
+      <c r="D5" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G5" s="6">
-        <v>4120</v>
-      </c>
-      <c r="H5" s="4"/>
+      <c r="F5" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11">
+        <v>1200</v>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
-        <v>6010000138</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="C6" s="5">
-        <v>46746</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G6" s="6">
-        <v>683</v>
-      </c>
-      <c r="H6" s="4"/>
+      <c r="A6" s="8">
+        <v>4010013388</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="10"/>
+      <c r="D6" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11">
+        <v>1280</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>4010015107</v>
+        <v>6010000138</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C7" s="5">
-        <v>46752</v>
+        <v>316</v>
+      </c>
+      <c r="C7" s="4">
+        <v>46746</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>179</v>
+        <v>317</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>133</v>
+        <v>318</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G7" s="6">
-        <v>1440</v>
-      </c>
-      <c r="H7" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G7" s="5">
+        <v>653</v>
+      </c>
+      <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>4010013476</v>
+        <v>4010015107</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C8" s="5">
-        <v>46548</v>
+        <v>177</v>
+      </c>
+      <c r="C8" s="4">
+        <v>46752</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>62</v>
+        <v>178</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>30</v>
+        <v>134</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G8" s="6">
-        <v>320</v>
-      </c>
-      <c r="H8" s="4"/>
+      <c r="G8" s="5">
+        <v>1440</v>
+      </c>
+      <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>6010000097</v>
+        <v>4010013476</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="C9" s="5">
-        <v>46751</v>
+        <v>62</v>
+      </c>
+      <c r="C9" s="4">
+        <v>46548</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>254</v>
+        <v>63</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>255</v>
+        <v>30</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G9" s="6">
-        <v>160</v>
-      </c>
-      <c r="H9" s="4"/>
+      <c r="G9" s="5">
+        <v>270</v>
+      </c>
+      <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
@@ -2156,11 +2120,11 @@
       <c r="B10" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="4">
         <v>46556</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>255</v>
@@ -2168,106 +2132,106 @@
       <c r="F10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="5">
         <v>600</v>
       </c>
-      <c r="H10" s="4"/>
+      <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
-        <v>6010000098</v>
+        <v>6010000097</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="C11" s="5">
-        <v>46539</v>
+        <v>253</v>
+      </c>
+      <c r="C11" s="4">
+        <v>46751</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>91</v>
+        <v>255</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G11" s="6">
-        <v>1740</v>
-      </c>
-      <c r="H11" s="4"/>
+      <c r="G11" s="5">
+        <v>160</v>
+      </c>
+      <c r="H11" s="5"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
-        <v>6010000195</v>
+        <v>6010000098</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="C12" s="5">
-        <v>46549</v>
+        <v>257</v>
+      </c>
+      <c r="C12" s="4">
+        <v>46539</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>394</v>
+        <v>258</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>23</v>
+        <v>92</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G12" s="6">
-        <v>520</v>
-      </c>
-      <c r="H12" s="4"/>
+      <c r="G12" s="5">
+        <v>1540</v>
+      </c>
+      <c r="H12" s="5"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
-        <v>4010013259</v>
+        <v>6010000195</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="5">
-        <v>46568</v>
+        <v>395</v>
+      </c>
+      <c r="C13" s="4">
+        <v>46549</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>7</v>
+        <v>396</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G13" s="6">
-        <v>780</v>
-      </c>
-      <c r="H13" s="4"/>
+      <c r="G13" s="5">
+        <v>500</v>
+      </c>
+      <c r="H13" s="5"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <v>4010013260</v>
+        <v>4010013259</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="5">
-        <v>46589</v>
+        <v>6</v>
+      </c>
+      <c r="C14" s="4">
+        <v>46568</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G14" s="6">
-        <v>1200</v>
-      </c>
-      <c r="H14" s="4"/>
+      <c r="G14" s="5">
+        <v>680</v>
+      </c>
+      <c r="H14" s="5"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
@@ -2276,11 +2240,11 @@
       <c r="B15" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="5">
-        <v>46568</v>
+      <c r="C15" s="4">
+        <v>46589</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>11</v>
@@ -2288,47 +2252,47 @@
       <c r="F15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G15" s="6">
-        <v>780</v>
-      </c>
-      <c r="H15" s="4"/>
+      <c r="G15" s="5">
+        <v>1200</v>
+      </c>
+      <c r="H15" s="5"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
-        <v>4010013692</v>
+        <v>4010013260</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="C16" s="5">
-        <v>46549</v>
+        <v>9</v>
+      </c>
+      <c r="C16" s="4">
+        <v>46568</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>157</v>
+        <v>12</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G16" s="6">
-        <v>1100</v>
-      </c>
-      <c r="H16" s="4"/>
+      <c r="G16" s="5">
+        <v>630</v>
+      </c>
+      <c r="H16" s="5"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
-        <v>4010013693</v>
+        <v>4010013692</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C17" s="5">
+        <v>156</v>
+      </c>
+      <c r="C17" s="4">
         <v>46549</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>8</v>
@@ -2336,10 +2300,10 @@
       <c r="F17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G17" s="6">
-        <v>680</v>
-      </c>
-      <c r="H17" s="4"/>
+      <c r="G17" s="5">
+        <v>1000</v>
+      </c>
+      <c r="H17" s="5"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
@@ -2348,11 +2312,11 @@
       <c r="B18" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="C18" s="5">
+      <c r="C18" s="4">
         <v>46587</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>8</v>
@@ -2360,10 +2324,10 @@
       <c r="F18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G18" s="6">
+      <c r="G18" s="5">
         <v>420</v>
       </c>
-      <c r="H18" s="4"/>
+      <c r="H18" s="5"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
@@ -2372,11 +2336,11 @@
       <c r="B19" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="C19" s="5">
-        <v>46495</v>
+      <c r="C19" s="4">
+        <v>46549</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>8</v>
@@ -2384,23 +2348,23 @@
       <c r="F19" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G19" s="6">
-        <v>100</v>
-      </c>
-      <c r="H19" s="4"/>
+      <c r="G19" s="5">
+        <v>480</v>
+      </c>
+      <c r="H19" s="5"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>4010013578</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C20" s="5">
+        <v>88</v>
+      </c>
+      <c r="C20" s="4">
         <v>46640</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>23</v>
@@ -2408,47 +2372,47 @@
       <c r="F20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G20" s="6">
-        <v>490</v>
-      </c>
-      <c r="H20" s="4"/>
+      <c r="G20" s="5">
+        <v>290</v>
+      </c>
+      <c r="H20" s="5"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>4010013580</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C21" s="5">
+        <v>90</v>
+      </c>
+      <c r="C21" s="4">
         <v>46666</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G21" s="6">
-        <v>720</v>
-      </c>
-      <c r="H21" s="4"/>
+      <c r="G21" s="5">
+        <v>520</v>
+      </c>
+      <c r="H21" s="5"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>4010013551</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C22" s="5">
+        <v>80</v>
+      </c>
+      <c r="C22" s="4">
         <v>46598</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>23</v>
@@ -2456,10 +2420,10 @@
       <c r="F22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G22" s="6">
-        <v>1560</v>
-      </c>
-      <c r="H22" s="4"/>
+      <c r="G22" s="5">
+        <v>1360</v>
+      </c>
+      <c r="H22" s="5"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
@@ -2468,7 +2432,7 @@
       <c r="B23" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="C23" s="5">
+      <c r="C23" s="4">
         <v>46518</v>
       </c>
       <c r="D23" s="3" t="s">
@@ -2480,23 +2444,23 @@
       <c r="F23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G23" s="6">
+      <c r="G23" s="5">
         <v>380</v>
       </c>
-      <c r="H23" s="4"/>
+      <c r="H23" s="5"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>4010013694</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C24" s="4">
+        <v>46536</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>162</v>
-      </c>
-      <c r="C24" s="5">
-        <v>46536</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>163</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>8</v>
@@ -2504,1381 +2468,1363 @@
       <c r="F24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G24" s="6">
-        <v>930</v>
-      </c>
-      <c r="H24" s="4"/>
+      <c r="G24" s="5">
+        <v>670</v>
+      </c>
+      <c r="H24" s="5"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>6010000065</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C25" s="4">
+        <v>46447</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="C25" s="5">
-        <v>46447</v>
-      </c>
-      <c r="D25" s="3" t="s">
+      <c r="E25" s="3" t="s">
         <v>181</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>182</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G25" s="6">
+      <c r="G25" s="5">
         <v>2200</v>
       </c>
-      <c r="H25" s="4"/>
+      <c r="H25" s="5"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>4010013582</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C26" s="5">
-        <v>46541</v>
+        <v>97</v>
+      </c>
+      <c r="C26" s="4">
+        <v>46392</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G26" s="6">
-        <v>320</v>
-      </c>
-      <c r="H26" s="4"/>
+      <c r="G26" s="5">
+        <v>500</v>
+      </c>
+      <c r="H26" s="5"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>4010013582</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C27" s="5">
-        <v>46392</v>
+        <v>97</v>
+      </c>
+      <c r="C27" s="4">
+        <v>46541</v>
       </c>
       <c r="D27" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E27" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="E27" s="3" t="s">
-        <v>98</v>
-      </c>
       <c r="F27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G27" s="6">
-        <v>540</v>
-      </c>
-      <c r="H27" s="4"/>
+      <c r="G27" s="5">
+        <v>320</v>
+      </c>
+      <c r="H27" s="5"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>4010013581</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C28" s="5">
+        <v>93</v>
+      </c>
+      <c r="C28" s="4">
         <v>46412</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G28" s="6">
-        <v>400</v>
-      </c>
-      <c r="H28" s="4"/>
+      <c r="G28" s="5">
+        <v>360</v>
+      </c>
+      <c r="H28" s="5"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>4010013581</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C29" s="5">
+        <v>93</v>
+      </c>
+      <c r="C29" s="4">
         <v>46541</v>
       </c>
       <c r="D29" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E29" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="E29" s="3" t="s">
-        <v>94</v>
-      </c>
       <c r="F29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G29" s="6">
+      <c r="G29" s="5">
         <v>4880</v>
       </c>
-      <c r="H29" s="4"/>
+      <c r="H29" s="5"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
-        <v>7050000018</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="C30" s="5"/>
-      <c r="D30" s="3" t="s">
+      <c r="A30" s="8">
+        <v>6010000066</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="C30" s="10"/>
+      <c r="D30" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E30" s="3" t="s">
-        <v>464</v>
-      </c>
-      <c r="F30" s="3" t="s">
+      <c r="E30" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="F30" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="G30" s="6">
-        <v>100</v>
-      </c>
-      <c r="H30" s="4"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11">
+        <v>900</v>
+      </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
-        <v>7050000016</v>
+        <v>7050000018</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>466</v>
-      </c>
-      <c r="C31" s="5"/>
+        <v>465</v>
+      </c>
+      <c r="C31" s="4"/>
       <c r="D31" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G31" s="6">
+      <c r="G31" s="5">
         <v>100</v>
       </c>
-      <c r="H31" s="4"/>
+      <c r="H31" s="5"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
-        <v>7050000015</v>
+        <v>7050000016</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>465</v>
-      </c>
-      <c r="C32" s="5"/>
+        <v>463</v>
+      </c>
+      <c r="C32" s="4"/>
       <c r="D32" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G32" s="6">
+      <c r="G32" s="5">
         <v>100</v>
       </c>
-      <c r="H32" s="4"/>
+      <c r="H32" s="5"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
-        <v>7050000014</v>
+        <v>7050000015</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>463</v>
-      </c>
-      <c r="C33" s="5"/>
+        <v>462</v>
+      </c>
+      <c r="C33" s="4"/>
       <c r="D33" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G33" s="6">
+      <c r="G33" s="5">
         <v>100</v>
       </c>
-      <c r="H33" s="4"/>
+      <c r="H33" s="5"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
-        <v>7050000017</v>
+        <v>7050000014</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="C34" s="5"/>
+        <v>460</v>
+      </c>
+      <c r="C34" s="4"/>
       <c r="D34" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G34" s="6">
+      <c r="G34" s="5">
         <v>100</v>
       </c>
-      <c r="H34" s="4"/>
+      <c r="H34" s="5"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
-        <v>4010013478</v>
+        <v>7050000017</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C35" s="5">
-        <v>46551</v>
-      </c>
+        <v>464</v>
+      </c>
+      <c r="C35" s="4"/>
       <c r="D35" s="3" t="s">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="E35" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G35" s="5">
+        <v>100</v>
+      </c>
+      <c r="H35" s="5"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="8">
+        <v>4010013550</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C36" s="10"/>
+      <c r="D36" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E36" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="F35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G35" s="6">
-        <v>240</v>
-      </c>
-      <c r="H35" s="4"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="2">
-        <v>6010000154</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="C36" s="5">
-        <v>47007</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G36" s="6">
-        <v>729</v>
-      </c>
-      <c r="H36" s="4"/>
+      <c r="F36" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11">
+        <v>1800</v>
+      </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
-        <v>6010000158</v>
+        <v>4010013478</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="C37" s="5">
-        <v>46752</v>
+        <v>66</v>
+      </c>
+      <c r="C37" s="4">
+        <v>46551</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>347</v>
+        <v>67</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G37" s="6">
-        <v>800</v>
-      </c>
-      <c r="H37" s="4"/>
+      <c r="G37" s="5">
+        <v>240</v>
+      </c>
+      <c r="H37" s="5"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
-        <v>6010000068</v>
+        <v>6010000154</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="C38" s="5">
-        <v>46495</v>
+        <v>343</v>
+      </c>
+      <c r="C38" s="4">
+        <v>47007</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>184</v>
+        <v>344</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>185</v>
+        <v>345</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G38" s="6">
-        <v>1690</v>
-      </c>
-      <c r="H38" s="4"/>
+      <c r="G38" s="5">
+        <v>639</v>
+      </c>
+      <c r="H38" s="5"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
-        <v>6010000159</v>
+        <v>6010000158</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="C39" s="5">
-        <v>46780</v>
+      <c r="C39" s="4">
+        <v>46752</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>349</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G39" s="6">
-        <v>260</v>
-      </c>
-      <c r="H39" s="4"/>
+      <c r="G39" s="5">
+        <v>600</v>
+      </c>
+      <c r="H39" s="5"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
-        <v>6010000160</v>
+        <v>6010000068</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="C40" s="5">
-        <v>46780</v>
+        <v>184</v>
+      </c>
+      <c r="C40" s="4">
+        <v>46495</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>351</v>
+        <v>185</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>352</v>
+        <v>186</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G40" s="6">
-        <v>660</v>
-      </c>
-      <c r="H40" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G40" s="5">
+        <v>1390</v>
+      </c>
+      <c r="H40" s="5"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="2">
-        <v>6010000234</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>443</v>
-      </c>
-      <c r="C41" s="5">
-        <v>46661</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>444</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G41" s="6">
-        <v>1340</v>
-      </c>
-      <c r="H41" s="4"/>
+      <c r="A41" s="8">
+        <v>6010000068</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="C41" s="10"/>
+      <c r="D41" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E41" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="G41" s="11"/>
+      <c r="H41" s="11">
+        <v>1500</v>
+      </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
-        <v>6010000234</v>
+        <v>6010000159</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>443</v>
-      </c>
-      <c r="C42" s="5">
-        <v>46726</v>
+        <v>350</v>
+      </c>
+      <c r="C42" s="4">
+        <v>46780</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>445</v>
+        <v>351</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G42" s="6">
-        <v>7920</v>
-      </c>
-      <c r="H42" s="4"/>
+      <c r="G42" s="5">
+        <v>160</v>
+      </c>
+      <c r="H42" s="5"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="2">
-        <v>6010000191</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="C43" s="5">
-        <v>46568</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G43" s="6">
-        <v>324</v>
-      </c>
-      <c r="H43" s="4"/>
+      <c r="A43" s="8">
+        <v>6010000160</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>352</v>
+      </c>
+      <c r="C43" s="10"/>
+      <c r="D43" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E43" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G43" s="11"/>
+      <c r="H43" s="11">
+        <v>960</v>
+      </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
-        <v>6010000239</v>
+        <v>6010000160</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="C44" s="5">
-        <v>46507</v>
+        <v>352</v>
+      </c>
+      <c r="C44" s="4">
+        <v>46780</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>449</v>
+        <v>354</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>384</v>
+        <v>353</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G44" s="6">
-        <v>1247</v>
-      </c>
-      <c r="H44" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="G44" s="5">
+        <v>560</v>
+      </c>
+      <c r="H44" s="5"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="2">
-        <v>6010000217</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="C45" s="5">
-        <v>46721</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G45" s="6">
-        <v>760</v>
-      </c>
-      <c r="H45" s="4"/>
+      <c r="A45" s="8">
+        <v>6010000100</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="C45" s="10"/>
+      <c r="D45" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G45" s="11"/>
+      <c r="H45" s="11">
+        <v>2520</v>
+      </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
-        <v>6010000217</v>
+        <v>6010000234</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="C46" s="5">
-        <v>46751</v>
+        <v>440</v>
+      </c>
+      <c r="C46" s="4">
+        <v>46726</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>427</v>
+        <v>441</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G46" s="6">
-        <v>10</v>
-      </c>
-      <c r="H46" s="4"/>
+      <c r="G46" s="5">
+        <v>7920</v>
+      </c>
+      <c r="H46" s="5"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
-        <v>6010000071</v>
+        <v>6010000234</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="C47" s="5">
-        <v>46797</v>
+        <v>440</v>
+      </c>
+      <c r="C47" s="4">
+        <v>46661</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>187</v>
+        <v>442</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>188</v>
+        <v>23</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G47" s="6">
-        <v>9200</v>
-      </c>
-      <c r="H47" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="G47" s="5">
+        <v>340</v>
+      </c>
+      <c r="H47" s="5"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
-        <v>4010013389</v>
+        <v>6010000191</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C48" s="5">
-        <v>46621</v>
+        <v>384</v>
+      </c>
+      <c r="C48" s="4">
+        <v>46568</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>39</v>
+        <v>385</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>40</v>
+        <v>386</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G48" s="6">
-        <v>1040</v>
-      </c>
-      <c r="H48" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G48" s="5">
+        <v>324</v>
+      </c>
+      <c r="H48" s="5"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
-        <v>4010013389</v>
+        <v>6010000239</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C49" s="5">
-        <v>46681</v>
+        <v>445</v>
+      </c>
+      <c r="C49" s="4">
+        <v>46507</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>41</v>
+        <v>446</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>40</v>
+        <v>386</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G49" s="6">
-        <v>1120</v>
-      </c>
-      <c r="H49" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G49" s="5">
+        <v>1247</v>
+      </c>
+      <c r="H49" s="5"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
-        <v>4010013266</v>
+        <v>6010000217</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C50" s="5">
-        <v>46575</v>
+        <v>425</v>
+      </c>
+      <c r="C50" s="4">
+        <v>46751</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>18</v>
+        <v>426</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G50" s="6">
-        <v>560</v>
-      </c>
-      <c r="H50" s="4"/>
+      <c r="G50" s="5">
+        <v>10</v>
+      </c>
+      <c r="H50" s="5"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
-        <v>4010013267</v>
+        <v>6010000217</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C51" s="5">
-        <v>46598</v>
+        <v>425</v>
+      </c>
+      <c r="C51" s="4">
+        <v>46721</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>20</v>
+        <v>427</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G51" s="6">
-        <v>640</v>
-      </c>
-      <c r="H51" s="4"/>
+      <c r="G51" s="5">
+        <v>710</v>
+      </c>
+      <c r="H51" s="5"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
-        <v>4010013553</v>
+        <v>6010000071</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C52" s="5">
-        <v>46575</v>
+        <v>187</v>
+      </c>
+      <c r="C52" s="4">
+        <v>46797</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>82</v>
+        <v>188</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>8</v>
+        <v>189</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G52" s="6">
-        <v>880</v>
-      </c>
-      <c r="H52" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G52" s="5">
+        <v>9000</v>
+      </c>
+      <c r="H52" s="5"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
-        <v>4010013397</v>
+        <v>4010013389</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C53" s="5">
-        <v>46545</v>
+        <v>39</v>
+      </c>
+      <c r="C53" s="4">
+        <v>46621</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G53" s="6">
-        <v>1080</v>
-      </c>
-      <c r="H53" s="4"/>
+      <c r="G53" s="5">
+        <v>710</v>
+      </c>
+      <c r="H53" s="5"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
-        <v>6010000224</v>
+        <v>4010013389</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>431</v>
-      </c>
-      <c r="C54" s="5">
-        <v>46711</v>
+        <v>39</v>
+      </c>
+      <c r="C54" s="4">
+        <v>46681</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>432</v>
+        <v>42</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G54" s="6">
-        <v>520</v>
-      </c>
-      <c r="H54" s="4"/>
+      <c r="G54" s="5">
+        <v>1120</v>
+      </c>
+      <c r="H54" s="5"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
-        <v>6010000232</v>
+        <v>4010013266</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>438</v>
-      </c>
-      <c r="C55" s="5">
-        <v>46726</v>
+        <v>17</v>
+      </c>
+      <c r="C55" s="4">
+        <v>46575</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>439</v>
+        <v>18</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G55" s="6">
-        <v>14400</v>
-      </c>
-      <c r="H55" s="4"/>
+      <c r="G55" s="5">
+        <v>560</v>
+      </c>
+      <c r="H55" s="5"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
-        <v>6010000232</v>
+        <v>4010013267</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>438</v>
-      </c>
-      <c r="C56" s="5">
-        <v>46692</v>
+        <v>19</v>
+      </c>
+      <c r="C56" s="4">
+        <v>46598</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>440</v>
+        <v>20</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G56" s="6">
-        <v>3160</v>
-      </c>
-      <c r="H56" s="4"/>
+      <c r="G56" s="5">
+        <v>640</v>
+      </c>
+      <c r="H56" s="5"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
-        <v>6010000240</v>
+        <v>4010013553</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="C57" s="5">
-        <v>46527</v>
+        <v>82</v>
+      </c>
+      <c r="C57" s="4">
+        <v>46575</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>451</v>
+        <v>83</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>452</v>
+        <v>8</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G57" s="6">
-        <v>102</v>
-      </c>
-      <c r="H57" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="G57" s="5">
+        <v>880</v>
+      </c>
+      <c r="H57" s="5"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
-        <v>6010000073</v>
+        <v>4010013397</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="C58" s="5">
-        <v>46511</v>
+        <v>43</v>
+      </c>
+      <c r="C58" s="4">
+        <v>46545</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>190</v>
+        <v>44</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>191</v>
+        <v>8</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G58" s="6">
-        <v>2080</v>
-      </c>
-      <c r="H58" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="G58" s="5">
+        <v>1080</v>
+      </c>
+      <c r="H58" s="5"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="2">
-        <v>6010000169</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="C59" s="5">
-        <v>46751</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G59" s="6">
-        <v>2110</v>
-      </c>
-      <c r="H59" s="4"/>
+      <c r="A59" s="8">
+        <v>6010000189</v>
+      </c>
+      <c r="B59" s="9" t="s">
+        <v>383</v>
+      </c>
+      <c r="C59" s="10"/>
+      <c r="D59" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E59" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G59" s="11"/>
+      <c r="H59" s="11">
+        <v>160</v>
+      </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
-        <v>6010000170</v>
+        <v>6010000224</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="C60" s="5">
-        <v>46721</v>
+        <v>431</v>
+      </c>
+      <c r="C60" s="4">
+        <v>46711</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>362</v>
+        <v>432</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>276</v>
+        <v>15</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G60" s="6">
-        <v>2590</v>
-      </c>
-      <c r="H60" s="4"/>
+      <c r="G60" s="5">
+        <v>520</v>
+      </c>
+      <c r="H60" s="5"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="2">
-        <v>6010000139</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="C61" s="5">
-        <v>46711</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G61" s="6">
-        <v>888</v>
-      </c>
-      <c r="H61" s="4"/>
+      <c r="A61" s="8">
+        <v>6010000101</v>
+      </c>
+      <c r="B61" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="C61" s="10"/>
+      <c r="D61" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E61" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G61" s="11"/>
+      <c r="H61" s="11">
+        <v>620</v>
+      </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
-        <v>6010000141</v>
+        <v>6010000232</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="C62" s="5">
-        <v>46746</v>
+        <v>436</v>
+      </c>
+      <c r="C62" s="4">
+        <v>46692</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>325</v>
+        <v>437</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>323</v>
+        <v>15</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G62" s="6">
-        <v>2665</v>
-      </c>
-      <c r="H62" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="G62" s="5">
+        <v>3160</v>
+      </c>
+      <c r="H62" s="5"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
-        <v>6010000205</v>
+        <v>6010000232</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="C63" s="5">
-        <v>46692</v>
+        <v>436</v>
+      </c>
+      <c r="C63" s="4">
+        <v>46726</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>413</v>
+        <v>438</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>414</v>
+        <v>15</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G63" s="6">
-        <v>6900</v>
-      </c>
-      <c r="H63" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="G63" s="5">
+        <v>14400</v>
+      </c>
+      <c r="H63" s="5"/>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
-        <v>4010013583</v>
+        <v>6010000240</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C64" s="5">
-        <v>46504</v>
+        <v>447</v>
+      </c>
+      <c r="C64" s="4">
+        <v>46527</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>101</v>
+        <v>448</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>76</v>
+        <v>449</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G64" s="6">
-        <v>820</v>
-      </c>
-      <c r="H64" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G64" s="5">
+        <v>102</v>
+      </c>
+      <c r="H64" s="5"/>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
-        <v>6010000074</v>
+        <v>6010000073</v>
       </c>
       <c r="B65" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C65" s="4">
+        <v>46511</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="E65" s="3" t="s">
         <v>192</v>
-      </c>
-      <c r="C65" s="5">
-        <v>46721</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="E65" s="3" t="s">
-        <v>194</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G65" s="6">
-        <v>4992</v>
-      </c>
-      <c r="H65" s="4"/>
+      <c r="G65" s="5">
+        <v>1870</v>
+      </c>
+      <c r="H65" s="5"/>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
-        <v>6010000074</v>
+        <v>6010000169</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="C66" s="5">
-        <v>46721</v>
+        <v>361</v>
+      </c>
+      <c r="C66" s="4">
+        <v>46751</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>195</v>
+        <v>362</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>194</v>
+        <v>116</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G66" s="6">
-        <v>5760</v>
-      </c>
-      <c r="H66" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="G66" s="5">
+        <v>2110</v>
+      </c>
+      <c r="H66" s="5"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
-        <v>4010013472</v>
+        <v>6010000170</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C67" s="5">
-        <v>46648</v>
+        <v>363</v>
+      </c>
+      <c r="C67" s="4">
+        <v>46721</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>53</v>
+        <v>364</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>15</v>
+        <v>116</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G67" s="6">
-        <v>1000</v>
-      </c>
-      <c r="H67" s="4"/>
+      <c r="G67" s="5">
+        <v>2590</v>
+      </c>
+      <c r="H67" s="5"/>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
-        <v>6010000102</v>
+        <v>6010000139</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="C68" s="5">
-        <v>46631</v>
+        <v>319</v>
+      </c>
+      <c r="C68" s="4">
+        <v>46711</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>260</v>
+        <v>320</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>23</v>
+        <v>321</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G68" s="6">
-        <v>3460</v>
-      </c>
-      <c r="H68" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G68" s="5">
+        <v>888</v>
+      </c>
+      <c r="H68" s="5"/>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="2">
-        <v>6010000102</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="C69" s="5">
-        <v>46780</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="E69" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G69" s="6">
-        <v>3200</v>
-      </c>
-      <c r="H69" s="4"/>
+      <c r="A69" s="8">
+        <v>6010000139</v>
+      </c>
+      <c r="B69" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="C69" s="10"/>
+      <c r="D69" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E69" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="F69" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="G69" s="11"/>
+      <c r="H69" s="11">
+        <v>600</v>
+      </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
-        <v>6010000103</v>
+        <v>6010000141</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="C70" s="5">
-        <v>46645</v>
+        <v>322</v>
+      </c>
+      <c r="C70" s="4">
+        <v>46746</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>263</v>
+        <v>323</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>23</v>
+        <v>321</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G70" s="6">
-        <v>3320</v>
-      </c>
-      <c r="H70" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G70" s="5">
+        <v>2665</v>
+      </c>
+      <c r="H70" s="5"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="2">
-        <v>6010000196</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="C71" s="5">
-        <v>46606</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="E71" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="F71" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G71" s="6">
-        <v>1840</v>
-      </c>
-      <c r="H71" s="4"/>
+      <c r="A71" s="8">
+        <v>6010000205</v>
+      </c>
+      <c r="B71" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="C71" s="10"/>
+      <c r="D71" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E71" s="9" t="s">
+        <v>415</v>
+      </c>
+      <c r="F71" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="G71" s="11"/>
+      <c r="H71" s="11">
+        <v>12000</v>
+      </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
-        <v>6010000212</v>
+        <v>6010000205</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="C72" s="5">
-        <v>46753</v>
+        <v>414</v>
+      </c>
+      <c r="C72" s="4">
+        <v>46692</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>416</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>23</v>
+        <v>415</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G72" s="6">
-        <v>440</v>
-      </c>
-      <c r="H72" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G72" s="5">
+        <v>6900</v>
+      </c>
+      <c r="H72" s="5"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
-        <v>6010000104</v>
+        <v>4010013583</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="C73" s="5">
-        <v>46429</v>
+        <v>101</v>
+      </c>
+      <c r="C73" s="4">
+        <v>46504</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>265</v>
+        <v>102</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>23</v>
+        <v>76</v>
       </c>
       <c r="F73" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G73" s="6">
-        <v>100</v>
-      </c>
-      <c r="H73" s="4"/>
+      <c r="G73" s="5">
+        <v>620</v>
+      </c>
+      <c r="H73" s="5"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
-        <v>4010013473</v>
+        <v>6010000074</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C74" s="5">
-        <v>46524</v>
+        <v>193</v>
+      </c>
+      <c r="C74" s="4">
+        <v>46721</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>55</v>
+        <v>194</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>30</v>
+        <v>195</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G74" s="6">
-        <v>480</v>
-      </c>
-      <c r="H74" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G74" s="5">
+        <v>3456</v>
+      </c>
+      <c r="H74" s="5"/>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
-        <v>6010000151</v>
+        <v>6010000074</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="C75" s="5">
-        <v>46692</v>
+        <v>193</v>
+      </c>
+      <c r="C75" s="4">
+        <v>46721</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>341</v>
+        <v>196</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>342</v>
+        <v>195</v>
       </c>
       <c r="F75" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G75" s="6">
-        <v>1112</v>
-      </c>
-      <c r="H75" s="4"/>
+      <c r="G75" s="5">
+        <v>3072</v>
+      </c>
+      <c r="H75" s="5"/>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
-        <v>6010000241</v>
+        <v>4010013472</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>453</v>
-      </c>
-      <c r="C76" s="5">
-        <v>46596</v>
+        <v>53</v>
+      </c>
+      <c r="C76" s="4">
+        <v>46648</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>454</v>
+        <v>54</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>452</v>
+        <v>15</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G76" s="6">
-        <v>162</v>
-      </c>
-      <c r="H76" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="G76" s="5">
+        <v>800</v>
+      </c>
+      <c r="H76" s="5"/>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
-        <v>6010000194</v>
+        <v>6010000102</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="C77" s="5">
-        <v>46803</v>
+        <v>261</v>
+      </c>
+      <c r="C77" s="4">
+        <v>46631</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>391</v>
+        <v>262</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F77" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G77" s="6">
-        <v>1470</v>
-      </c>
-      <c r="H77" s="4"/>
+      <c r="G77" s="5">
+        <v>3160</v>
+      </c>
+      <c r="H77" s="5"/>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
-        <v>6010000194</v>
+        <v>6010000102</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="C78" s="5">
-        <v>46721</v>
+        <v>261</v>
+      </c>
+      <c r="C78" s="4">
+        <v>46780</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>392</v>
+        <v>263</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G78" s="6">
-        <v>5460</v>
-      </c>
-      <c r="H78" s="4"/>
+      <c r="G78" s="5">
+        <v>3200</v>
+      </c>
+      <c r="H78" s="5"/>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
-        <v>6010000192</v>
+        <v>6010000103</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="C79" s="5">
-        <v>46367</v>
+        <v>264</v>
+      </c>
+      <c r="C79" s="4">
+        <v>46645</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>386</v>
+        <v>265</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>384</v>
+        <v>23</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G79" s="6">
-        <v>383</v>
-      </c>
-      <c r="H79" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="G79" s="5">
+        <v>3320</v>
+      </c>
+      <c r="H79" s="5"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
-        <v>6010000108</v>
+        <v>6010000196</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="C80" s="5">
-        <v>46574</v>
+        <v>397</v>
+      </c>
+      <c r="C80" s="4">
+        <v>46606</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>267</v>
+        <v>398</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>15</v>
+        <v>399</v>
       </c>
       <c r="F80" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G80" s="6">
-        <v>180</v>
-      </c>
-      <c r="H80" s="4"/>
+      <c r="G80" s="5">
+        <v>1840</v>
+      </c>
+      <c r="H80" s="5"/>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
-        <v>6010000193</v>
+        <v>6010000104</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="C81" s="5">
-        <v>46711</v>
+        <v>266</v>
+      </c>
+      <c r="C81" s="4">
+        <v>46429</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>388</v>
+        <v>267</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G81" s="6">
-        <v>320</v>
-      </c>
-      <c r="H81" s="4"/>
+      <c r="G81" s="5">
+        <v>100</v>
+      </c>
+      <c r="H81" s="5"/>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
-        <v>6010000193</v>
+        <v>4010013473</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="C82" s="5">
-        <v>46726</v>
+        <v>55</v>
+      </c>
+      <c r="C82" s="4">
+        <v>46524</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>389</v>
+        <v>56</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>30</v>
@@ -3886,71 +3832,71 @@
       <c r="F82" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G82" s="6">
-        <v>80</v>
-      </c>
-      <c r="H82" s="4"/>
+      <c r="G82" s="5">
+        <v>430</v>
+      </c>
+      <c r="H82" s="5"/>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
-        <v>6010000216</v>
+        <v>6010000151</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="C83" s="5">
-        <v>46690</v>
+        <v>340</v>
+      </c>
+      <c r="C83" s="4">
+        <v>46692</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>424</v>
+        <v>341</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>30</v>
+        <v>342</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G83" s="6">
-        <v>220</v>
-      </c>
-      <c r="H83" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G83" s="5">
+        <v>1112</v>
+      </c>
+      <c r="H83" s="5"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
-        <v>6010000235</v>
+        <v>6010000241</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>446</v>
-      </c>
-      <c r="C84" s="5">
-        <v>46808</v>
+        <v>450</v>
+      </c>
+      <c r="C84" s="4">
+        <v>46596</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>15</v>
+        <v>449</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G84" s="6">
-        <v>4080</v>
-      </c>
-      <c r="H84" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G84" s="5">
+        <v>162</v>
+      </c>
+      <c r="H84" s="5"/>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
-        <v>4010013662</v>
+        <v>6010000194</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C85" s="5">
-        <v>46546</v>
+        <v>392</v>
+      </c>
+      <c r="C85" s="4">
+        <v>46803</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>146</v>
+        <v>393</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>30</v>
@@ -3958,23 +3904,23 @@
       <c r="F85" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G85" s="6">
-        <v>420</v>
-      </c>
-      <c r="H85" s="4"/>
+      <c r="G85" s="5">
+        <v>1470</v>
+      </c>
+      <c r="H85" s="5"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
-        <v>4010013662</v>
+        <v>6010000194</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C86" s="5">
-        <v>46537</v>
+        <v>392</v>
+      </c>
+      <c r="C86" s="4">
+        <v>46721</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>147</v>
+        <v>394</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>30</v>
@@ -3982,551 +3928,547 @@
       <c r="F86" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G86" s="6">
-        <v>430</v>
-      </c>
-      <c r="H86" s="4"/>
+      <c r="G86" s="5">
+        <v>5360</v>
+      </c>
+      <c r="H86" s="5"/>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
-        <v>6010000076</v>
+        <v>6010000192</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="C87" s="5">
-        <v>46415</v>
+        <v>387</v>
+      </c>
+      <c r="C87" s="4">
+        <v>46367</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>197</v>
+        <v>388</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>194</v>
+        <v>386</v>
       </c>
       <c r="F87" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G87" s="6">
-        <v>1152</v>
-      </c>
-      <c r="H87" s="4"/>
+      <c r="G87" s="5">
+        <v>365</v>
+      </c>
+      <c r="H87" s="5"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="2">
-        <v>6010000076</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="C88" s="5">
-        <v>46483</v>
-      </c>
-      <c r="D88" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E88" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="F88" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G88" s="6">
-        <v>3556</v>
-      </c>
-      <c r="H88" s="4"/>
+      <c r="A88" s="8">
+        <v>6010000155</v>
+      </c>
+      <c r="B88" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="C88" s="10"/>
+      <c r="D88" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E88" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F88" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G88" s="11"/>
+      <c r="H88" s="11">
+        <v>400</v>
+      </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
-        <v>6010000110</v>
+        <v>6010000108</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="C89" s="5">
-        <v>46640</v>
+      <c r="C89" s="4">
+        <v>46574</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>269</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G89" s="6">
-        <v>1100</v>
-      </c>
-      <c r="H89" s="4"/>
+      <c r="G89" s="5">
+        <v>180</v>
+      </c>
+      <c r="H89" s="5"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90" s="2">
-        <v>6010000111</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="C90" s="5">
-        <v>46640</v>
-      </c>
-      <c r="D90" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="E90" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F90" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G90" s="6">
-        <v>2840</v>
-      </c>
-      <c r="H90" s="4"/>
+      <c r="A90" s="8">
+        <v>6010000108</v>
+      </c>
+      <c r="B90" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="C90" s="10"/>
+      <c r="D90" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E90" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F90" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G90" s="11"/>
+      <c r="H90" s="11">
+        <v>480</v>
+      </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
-        <v>4010013584</v>
+        <v>6010000193</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C91" s="5">
-        <v>46532</v>
+        <v>389</v>
+      </c>
+      <c r="C91" s="4">
+        <v>46711</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>103</v>
+        <v>390</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>91</v>
+        <v>30</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G91" s="6">
-        <v>900</v>
-      </c>
-      <c r="H91" s="4"/>
+      <c r="G91" s="5">
+        <v>270</v>
+      </c>
+      <c r="H91" s="5"/>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
-        <v>4010013584</v>
+        <v>6010000193</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C92" s="5">
-        <v>46537</v>
+        <v>389</v>
+      </c>
+      <c r="C92" s="4">
+        <v>46726</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>104</v>
+        <v>391</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>91</v>
+        <v>30</v>
       </c>
       <c r="F92" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G92" s="6">
-        <v>380</v>
-      </c>
-      <c r="H92" s="4"/>
+      <c r="G92" s="5">
+        <v>80</v>
+      </c>
+      <c r="H92" s="5"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
-        <v>6010000171</v>
+        <v>6010000216</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="C93" s="5">
-        <v>46579</v>
+        <v>423</v>
+      </c>
+      <c r="C93" s="4">
+        <v>46690</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>364</v>
+        <v>424</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>91</v>
+        <v>30</v>
       </c>
       <c r="F93" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G93" s="6">
-        <v>1500</v>
-      </c>
-      <c r="H93" s="4"/>
+      <c r="G93" s="5">
+        <v>170</v>
+      </c>
+      <c r="H93" s="5"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
-        <v>4010013585</v>
+        <v>6010000235</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C94" s="5">
-        <v>46568</v>
+        <v>443</v>
+      </c>
+      <c r="C94" s="4">
+        <v>46808</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>106</v>
+        <v>444</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>91</v>
+        <v>15</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G94" s="6">
-        <v>1700</v>
-      </c>
-      <c r="H94" s="4"/>
+      <c r="G94" s="5">
+        <v>3800</v>
+      </c>
+      <c r="H94" s="5"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
-        <v>6010000172</v>
+        <v>4010013662</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="C95" s="5">
-        <v>46579</v>
+        <v>145</v>
+      </c>
+      <c r="C95" s="4">
+        <v>46537</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>366</v>
+        <v>146</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>91</v>
+        <v>30</v>
       </c>
       <c r="F95" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G95" s="6">
-        <v>1700</v>
-      </c>
-      <c r="H95" s="4"/>
+      <c r="G95" s="5">
+        <v>430</v>
+      </c>
+      <c r="H95" s="5"/>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
-        <v>6010000077</v>
+        <v>4010013662</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="C96" s="5">
-        <v>46471</v>
+        <v>145</v>
+      </c>
+      <c r="C96" s="4">
+        <v>46546</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>200</v>
+        <v>147</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>201</v>
+        <v>30</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G96" s="6">
-        <v>6680</v>
-      </c>
-      <c r="H96" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="G96" s="5">
+        <v>420</v>
+      </c>
+      <c r="H96" s="5"/>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
-        <v>6010000078</v>
+        <v>6010000076</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="C97" s="5">
-        <v>46780</v>
+        <v>197</v>
+      </c>
+      <c r="C97" s="4">
+        <v>46415</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="F97" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G97" s="6">
-        <v>13350</v>
-      </c>
-      <c r="H97" s="4"/>
+      <c r="G97" s="5">
+        <v>1152</v>
+      </c>
+      <c r="H97" s="5"/>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
-        <v>6010000079</v>
+        <v>6010000076</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="C98" s="5">
-        <v>46512</v>
+        <v>197</v>
+      </c>
+      <c r="C98" s="4">
+        <v>46483</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="F98" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G98" s="6">
-        <v>890</v>
-      </c>
-      <c r="H98" s="4"/>
+      <c r="G98" s="5">
+        <v>3556</v>
+      </c>
+      <c r="H98" s="5"/>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
-        <v>4010013593</v>
+        <v>6010000110</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C99" s="5">
-        <v>46758</v>
+        <v>270</v>
+      </c>
+      <c r="C99" s="4">
+        <v>46640</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>116</v>
+        <v>271</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F99" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G99" s="6">
-        <v>560</v>
-      </c>
-      <c r="H99" s="4"/>
+      <c r="G99" s="5">
+        <v>1100</v>
+      </c>
+      <c r="H99" s="5"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
-        <v>4010013593</v>
+        <v>6010000111</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C100" s="5">
-        <v>46526</v>
+        <v>272</v>
+      </c>
+      <c r="C100" s="4">
+        <v>46640</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>117</v>
+        <v>273</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G100" s="6">
-        <v>310</v>
-      </c>
-      <c r="H100" s="4"/>
+      <c r="G100" s="5">
+        <v>2640</v>
+      </c>
+      <c r="H100" s="5"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
-        <v>4010014329</v>
+        <v>4010013584</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C101" s="5">
-        <v>46641</v>
+        <v>103</v>
+      </c>
+      <c r="C101" s="4">
+        <v>46532</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>172</v>
+        <v>104</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>30</v>
+        <v>92</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G101" s="6">
-        <v>230</v>
-      </c>
-      <c r="H101" s="4"/>
+      <c r="G101" s="5">
+        <v>700</v>
+      </c>
+      <c r="H101" s="5"/>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
-        <v>4010013594</v>
+        <v>4010013584</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C102" s="5">
-        <v>46573</v>
+        <v>103</v>
+      </c>
+      <c r="C102" s="4">
+        <v>46537</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>30</v>
+        <v>92</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G102" s="6">
-        <v>1550</v>
-      </c>
-      <c r="H102" s="4"/>
+      <c r="G102" s="5">
+        <v>380</v>
+      </c>
+      <c r="H102" s="5"/>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
-        <v>4010014330</v>
+        <v>6010000171</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C103" s="5">
-        <v>46610</v>
+        <v>365</v>
+      </c>
+      <c r="C103" s="4">
+        <v>46579</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>174</v>
+        <v>366</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>30</v>
+        <v>92</v>
       </c>
       <c r="F103" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G103" s="6">
-        <v>280</v>
-      </c>
-      <c r="H103" s="4"/>
+      <c r="G103" s="5">
+        <v>1500</v>
+      </c>
+      <c r="H103" s="5"/>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
-        <v>6010000233</v>
+        <v>4010013585</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>441</v>
-      </c>
-      <c r="C104" s="5">
-        <v>46721</v>
+        <v>106</v>
+      </c>
+      <c r="C104" s="4">
+        <v>46568</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>442</v>
+        <v>107</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>30</v>
+        <v>92</v>
       </c>
       <c r="F104" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G104" s="6">
-        <v>970</v>
-      </c>
-      <c r="H104" s="4"/>
+      <c r="G104" s="5">
+        <v>1500</v>
+      </c>
+      <c r="H104" s="5"/>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
-        <v>6010000080</v>
+        <v>6010000172</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="C105" s="5">
-        <v>46423</v>
+        <v>367</v>
+      </c>
+      <c r="C105" s="4">
+        <v>46579</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>209</v>
+        <v>368</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>210</v>
+        <v>92</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G105" s="6">
-        <v>500</v>
-      </c>
-      <c r="H105" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="G105" s="5">
+        <v>1700</v>
+      </c>
+      <c r="H105" s="5"/>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
-        <v>6010000113</v>
+        <v>6010000077</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="C106" s="5">
-        <v>46598</v>
+        <v>200</v>
+      </c>
+      <c r="C106" s="4">
+        <v>46471</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>273</v>
+        <v>201</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>23</v>
+        <v>202</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G106" s="6">
-        <v>10640</v>
-      </c>
-      <c r="H106" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G106" s="5">
+        <v>6180</v>
+      </c>
+      <c r="H106" s="5"/>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
-        <v>4010013656</v>
+        <v>6010000078</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="C107" s="5">
-        <v>46423</v>
+        <v>203</v>
+      </c>
+      <c r="C107" s="4">
+        <v>46780</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>132</v>
+        <v>204</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>133</v>
+        <v>205</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G107" s="6">
-        <v>260</v>
-      </c>
-      <c r="H107" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G107" s="5">
+        <v>12850</v>
+      </c>
+      <c r="H107" s="5"/>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
-        <v>4010013656</v>
+        <v>6010000079</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="C108" s="5">
-        <v>46510</v>
+        <v>206</v>
+      </c>
+      <c r="C108" s="4">
+        <v>46512</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>134</v>
+        <v>207</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>133</v>
+        <v>208</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G108" s="6">
-        <v>2380</v>
-      </c>
-      <c r="H108" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G108" s="5">
+        <v>760</v>
+      </c>
+      <c r="H108" s="5"/>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
-        <v>4010013595</v>
+        <v>4010013593</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="C109" s="5">
-        <v>46623</v>
+        <v>117</v>
+      </c>
+      <c r="C109" s="4">
+        <v>46758</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E109" s="3" t="s">
         <v>30</v>
@@ -4534,741 +4476,739 @@
       <c r="F109" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G109" s="6">
-        <v>200</v>
-      </c>
-      <c r="H109" s="4"/>
+      <c r="G109" s="5">
+        <v>560</v>
+      </c>
+      <c r="H109" s="5"/>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
-        <v>6010000174</v>
+        <v>4010013593</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="C110" s="5">
-        <v>46586</v>
+        <v>117</v>
+      </c>
+      <c r="C110" s="4">
+        <v>46526</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>368</v>
+        <v>119</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>369</v>
+        <v>30</v>
       </c>
       <c r="F110" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G110" s="6">
-        <v>1160</v>
-      </c>
-      <c r="H110" s="4"/>
+      <c r="G110" s="5">
+        <v>260</v>
+      </c>
+      <c r="H110" s="5"/>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
-        <v>6010000114</v>
+        <v>4010014329</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="C111" s="5">
-        <v>46488</v>
+        <v>170</v>
+      </c>
+      <c r="C111" s="4">
+        <v>46641</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>275</v>
+        <v>171</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>276</v>
+        <v>30</v>
       </c>
       <c r="F111" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G111" s="6">
-        <v>2000</v>
-      </c>
-      <c r="H111" s="4"/>
+      <c r="G111" s="5">
+        <v>230</v>
+      </c>
+      <c r="H111" s="5"/>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
-        <v>6010000081</v>
+        <v>4010013594</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="C112" s="5">
-        <v>46660</v>
+        <v>120</v>
+      </c>
+      <c r="C112" s="4">
+        <v>46573</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>212</v>
+        <v>121</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G112" s="6">
-        <v>770</v>
-      </c>
-      <c r="H112" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="G112" s="5">
+        <v>1550</v>
+      </c>
+      <c r="H112" s="5"/>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="2">
-        <v>6010000082</v>
+        <v>4010014330</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="C113" s="5">
-        <v>46505</v>
+        <v>172</v>
+      </c>
+      <c r="C113" s="4">
+        <v>46610</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>214</v>
+        <v>173</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>215</v>
+        <v>30</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G113" s="6">
-        <v>13800</v>
-      </c>
-      <c r="H113" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="G113" s="5">
+        <v>280</v>
+      </c>
+      <c r="H113" s="5"/>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A114" s="2">
-        <v>6010000175</v>
-      </c>
-      <c r="B114" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="C114" s="5">
-        <v>46556</v>
-      </c>
-      <c r="D114" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="E114" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="F114" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G114" s="6">
-        <v>1900</v>
-      </c>
-      <c r="H114" s="4"/>
+      <c r="A114" s="8">
+        <v>6010000156</v>
+      </c>
+      <c r="B114" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="C114" s="10"/>
+      <c r="D114" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E114" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F114" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G114" s="11"/>
+      <c r="H114" s="11">
+        <v>300</v>
+      </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
-        <v>6010000176</v>
+        <v>6010000233</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="C115" s="5">
-        <v>46586</v>
+        <v>347</v>
+      </c>
+      <c r="C115" s="4">
+        <v>46721</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>374</v>
+        <v>439</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>372</v>
+        <v>30</v>
       </c>
       <c r="F115" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G115" s="6">
-        <v>1980</v>
-      </c>
-      <c r="H115" s="4"/>
+      <c r="G115" s="5">
+        <v>920</v>
+      </c>
+      <c r="H115" s="5"/>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
-        <v>6010000201</v>
+        <v>6010000080</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="C116" s="5">
-        <v>46624</v>
+        <v>209</v>
+      </c>
+      <c r="C116" s="4">
+        <v>46423</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>406</v>
+        <v>210</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>407</v>
+        <v>211</v>
       </c>
       <c r="F116" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G116" s="6">
-        <v>910</v>
-      </c>
-      <c r="H116" s="4"/>
+      <c r="G116" s="5">
+        <v>500</v>
+      </c>
+      <c r="H116" s="5"/>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
-        <v>6010000202</v>
+        <v>6010000113</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="C117" s="5">
-        <v>46685</v>
+        <v>274</v>
+      </c>
+      <c r="C117" s="4">
+        <v>46598</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>409</v>
+        <v>275</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>407</v>
+        <v>23</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G117" s="6">
-        <v>830</v>
-      </c>
-      <c r="H117" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="G117" s="5">
+        <v>9740</v>
+      </c>
+      <c r="H117" s="5"/>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
-        <v>4010013262</v>
+        <v>4010013656</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C118" s="5">
-        <v>46549</v>
+        <v>132</v>
+      </c>
+      <c r="C118" s="4">
+        <v>46423</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>14</v>
+        <v>133</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>15</v>
+        <v>134</v>
       </c>
       <c r="F118" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G118" s="6">
-        <v>520</v>
-      </c>
-      <c r="H118" s="4"/>
+      <c r="G118" s="5">
+        <v>240</v>
+      </c>
+      <c r="H118" s="5"/>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
-        <v>4010013262</v>
+        <v>4010013656</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C119" s="5">
-        <v>46475</v>
+        <v>132</v>
+      </c>
+      <c r="C119" s="4">
+        <v>46510</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>16</v>
+        <v>135</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>15</v>
+        <v>134</v>
       </c>
       <c r="F119" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G119" s="6">
-        <v>20</v>
-      </c>
-      <c r="H119" s="4"/>
+      <c r="G119" s="5">
+        <v>2380</v>
+      </c>
+      <c r="H119" s="5"/>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A120" s="2">
-        <v>4010013465</v>
-      </c>
-      <c r="B120" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C120" s="5">
-        <v>46637</v>
-      </c>
-      <c r="D120" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E120" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F120" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G120" s="6">
-        <v>3020</v>
-      </c>
-      <c r="H120" s="4"/>
+      <c r="A120" s="8">
+        <v>4010013595</v>
+      </c>
+      <c r="B120" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="C120" s="10"/>
+      <c r="D120" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E120" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F120" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G120" s="11"/>
+      <c r="H120" s="11">
+        <v>300</v>
+      </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
-        <v>4010013466</v>
+        <v>6010000174</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C121" s="5">
-        <v>46388</v>
+        <v>369</v>
+      </c>
+      <c r="C121" s="4">
+        <v>46586</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>49</v>
+        <v>370</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>50</v>
+        <v>371</v>
       </c>
       <c r="F121" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G121" s="6">
-        <v>200</v>
-      </c>
-      <c r="H121" s="4"/>
+      <c r="G121" s="5">
+        <v>1160</v>
+      </c>
+      <c r="H121" s="5"/>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
-        <v>4010013466</v>
+        <v>6010000114</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C122" s="5">
-        <v>46704</v>
+        <v>276</v>
+      </c>
+      <c r="C122" s="4">
+        <v>46488</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>51</v>
+        <v>277</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>50</v>
+        <v>116</v>
       </c>
       <c r="F122" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G122" s="6">
-        <v>120</v>
-      </c>
-      <c r="H122" s="4"/>
+      <c r="G122" s="5">
+        <v>2000</v>
+      </c>
+      <c r="H122" s="5"/>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
-        <v>4010013671</v>
+        <v>6010000081</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="C123" s="5">
-        <v>46566</v>
+        <v>212</v>
+      </c>
+      <c r="C123" s="4">
+        <v>46660</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>155</v>
+        <v>213</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G123" s="6">
-        <v>1840</v>
-      </c>
-      <c r="H123" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G123" s="5">
+        <v>750</v>
+      </c>
+      <c r="H123" s="5"/>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" s="2">
-        <v>6010000252</v>
+        <v>6010000082</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>459</v>
-      </c>
-      <c r="C124" s="5">
-        <v>46780</v>
+        <v>214</v>
+      </c>
+      <c r="C124" s="4">
+        <v>46505</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>460</v>
+        <v>215</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>461</v>
+        <v>216</v>
       </c>
       <c r="F124" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G124" s="6">
-        <v>1500</v>
-      </c>
-      <c r="H124" s="4"/>
+      <c r="G124" s="5">
+        <v>13800</v>
+      </c>
+      <c r="H124" s="5"/>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" s="2">
-        <v>6010000252</v>
+        <v>6010000175</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>459</v>
-      </c>
-      <c r="C125" s="5">
-        <v>46661</v>
+        <v>372</v>
+      </c>
+      <c r="C125" s="4">
+        <v>46556</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>462</v>
+        <v>373</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>461</v>
+        <v>374</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G125" s="6">
-        <v>890</v>
-      </c>
-      <c r="H125" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="G125" s="5">
+        <v>1900</v>
+      </c>
+      <c r="H125" s="5"/>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" s="2">
-        <v>6010000218</v>
+        <v>6010000176</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>428</v>
-      </c>
-      <c r="C126" s="5">
-        <v>46780</v>
+        <v>375</v>
+      </c>
+      <c r="C126" s="4">
+        <v>46586</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>429</v>
+        <v>376</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>430</v>
+        <v>374</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G126" s="6">
-        <v>2050</v>
-      </c>
-      <c r="H126" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="G126" s="5">
+        <v>1980</v>
+      </c>
+      <c r="H126" s="5"/>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" s="2">
-        <v>6010000083</v>
+        <v>6010000201</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="C127" s="5">
-        <v>46537</v>
+        <v>407</v>
+      </c>
+      <c r="C127" s="4">
+        <v>46624</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>217</v>
+        <v>408</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>218</v>
+        <v>409</v>
       </c>
       <c r="F127" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G127" s="6">
-        <v>1430</v>
-      </c>
-      <c r="H127" s="4"/>
+      <c r="G127" s="5">
+        <v>910</v>
+      </c>
+      <c r="H127" s="5"/>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" s="2">
-        <v>6010000084</v>
+        <v>6010000202</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="C128" s="5">
-        <v>46711</v>
+        <v>410</v>
+      </c>
+      <c r="C128" s="4">
+        <v>46685</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>220</v>
+        <v>411</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>221</v>
+        <v>409</v>
       </c>
       <c r="F128" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G128" s="6">
-        <v>6380</v>
-      </c>
-      <c r="H128" s="4"/>
+      <c r="G128" s="5">
+        <v>830</v>
+      </c>
+      <c r="H128" s="5"/>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
-        <v>6010000115</v>
+        <v>4010013262</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="C129" s="5">
-        <v>46971</v>
+        <v>13</v>
+      </c>
+      <c r="C129" s="4">
+        <v>46549</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>278</v>
+        <v>14</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F129" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G129" s="6">
-        <v>2400</v>
-      </c>
-      <c r="H129" s="4"/>
+      <c r="G129" s="5">
+        <v>520</v>
+      </c>
+      <c r="H129" s="5"/>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
-        <v>6010000116</v>
+        <v>4010013262</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="C130" s="5">
-        <v>46971</v>
+        <v>13</v>
+      </c>
+      <c r="C130" s="4">
+        <v>46475</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F130" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G130" s="6">
-        <v>4480</v>
-      </c>
-      <c r="H130" s="4"/>
+      <c r="G130" s="5">
+        <v>20</v>
+      </c>
+      <c r="H130" s="5"/>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" s="2">
-        <v>7050000019</v>
+        <v>4010013465</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="C131" s="5"/>
+        <v>47</v>
+      </c>
+      <c r="C131" s="4">
+        <v>46637</v>
+      </c>
       <c r="D131" s="3" t="s">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G131" s="6">
-        <v>530</v>
-      </c>
-      <c r="H131" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="G131" s="5">
+        <v>3020</v>
+      </c>
+      <c r="H131" s="5"/>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" s="2">
-        <v>6010000118</v>
+        <v>4010013466</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="C132" s="5">
-        <v>46574</v>
+        <v>49</v>
+      </c>
+      <c r="C132" s="4">
+        <v>46388</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>284</v>
+        <v>50</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="F132" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G132" s="6">
-        <v>10640</v>
-      </c>
-      <c r="H132" s="4"/>
+      <c r="G132" s="5">
+        <v>200</v>
+      </c>
+      <c r="H132" s="5"/>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" s="2">
-        <v>6010000148</v>
+        <v>4010013466</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="C133" s="5">
-        <v>46751</v>
+        <v>49</v>
+      </c>
+      <c r="C133" s="4">
+        <v>46704</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>338</v>
+        <v>52</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="F133" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G133" s="6">
-        <v>2520</v>
-      </c>
-      <c r="H133" s="4"/>
+      <c r="G133" s="5">
+        <v>120</v>
+      </c>
+      <c r="H133" s="5"/>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
-        <v>6010000148</v>
+        <v>4010013671</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="C134" s="5">
-        <v>46574</v>
+        <v>154</v>
+      </c>
+      <c r="C134" s="4">
+        <v>46566</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>339</v>
+        <v>155</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F134" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G134" s="6">
-        <v>780</v>
-      </c>
-      <c r="H134" s="4"/>
+      <c r="G134" s="5">
+        <v>1640</v>
+      </c>
+      <c r="H134" s="5"/>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" s="2">
-        <v>6010000120</v>
+        <v>6010000252</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="C135" s="5">
-        <v>46598</v>
+        <v>456</v>
+      </c>
+      <c r="C135" s="4">
+        <v>46780</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>286</v>
+        <v>457</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>287</v>
+        <v>458</v>
       </c>
       <c r="F135" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G135" s="6">
-        <v>160</v>
-      </c>
-      <c r="H135" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G135" s="5">
+        <v>1500</v>
+      </c>
+      <c r="H135" s="5"/>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" s="2">
-        <v>6010000085</v>
+        <v>6010000252</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="C136" s="5">
-        <v>46388</v>
+        <v>456</v>
+      </c>
+      <c r="C136" s="4">
+        <v>46661</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>223</v>
+        <v>459</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>224</v>
+        <v>458</v>
       </c>
       <c r="F136" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G136" s="6">
-        <v>35500</v>
-      </c>
-      <c r="H136" s="4"/>
+      <c r="G136" s="5">
+        <v>890</v>
+      </c>
+      <c r="H136" s="5"/>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" s="2">
-        <v>6010000121</v>
+        <v>6010000218</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="C137" s="5">
-        <v>46631</v>
+        <v>428</v>
+      </c>
+      <c r="C137" s="4">
+        <v>46780</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>289</v>
+        <v>429</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>23</v>
+        <v>430</v>
       </c>
       <c r="F137" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G137" s="6">
-        <v>160</v>
-      </c>
-      <c r="H137" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G137" s="5">
+        <v>2000</v>
+      </c>
+      <c r="H137" s="5"/>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" s="2">
-        <v>6010000123</v>
+        <v>6010000083</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="C138" s="5">
-        <v>46752</v>
+        <v>217</v>
+      </c>
+      <c r="C138" s="4">
+        <v>46537</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>291</v>
+        <v>218</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>91</v>
+        <v>219</v>
       </c>
       <c r="F138" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G138" s="6">
-        <v>5080</v>
-      </c>
-      <c r="H138" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G138" s="5">
+        <v>1100</v>
+      </c>
+      <c r="H138" s="5"/>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" s="2">
-        <v>6010000123</v>
+        <v>6010000084</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="C139" s="5">
-        <v>46692</v>
+        <v>220</v>
+      </c>
+      <c r="C139" s="4">
+        <v>46711</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>292</v>
+        <v>221</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>91</v>
+        <v>222</v>
       </c>
       <c r="F139" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G139" s="6">
-        <v>680</v>
-      </c>
-      <c r="H139" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G139" s="5">
+        <v>6220</v>
+      </c>
+      <c r="H139" s="5"/>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" s="2">
-        <v>6010000230</v>
+        <v>6010000115</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="C140" s="5">
-        <v>46752</v>
+        <v>278</v>
+      </c>
+      <c r="C140" s="4">
+        <v>46971</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>437</v>
+        <v>279</v>
       </c>
       <c r="E140" s="3" t="s">
         <v>23</v>
@@ -5276,503 +5216,495 @@
       <c r="F140" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G140" s="6">
-        <v>590</v>
-      </c>
-      <c r="H140" s="4"/>
+      <c r="G140" s="5">
+        <v>2400</v>
+      </c>
+      <c r="H140" s="5"/>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" s="2">
-        <v>6010000086</v>
+        <v>6010000116</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="C141" s="5">
-        <v>46641</v>
+        <v>280</v>
+      </c>
+      <c r="C141" s="4">
+        <v>46971</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>226</v>
+        <v>281</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>227</v>
+        <v>4</v>
       </c>
       <c r="F141" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G141" s="6">
-        <v>9800</v>
-      </c>
-      <c r="H141" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="G141" s="5">
+        <v>4480</v>
+      </c>
+      <c r="H141" s="5"/>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" s="2">
-        <v>6010000125</v>
+        <v>7050000019</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="C142" s="5">
-        <v>46574</v>
-      </c>
+        <v>466</v>
+      </c>
+      <c r="C142" s="4"/>
       <c r="D142" s="3" t="s">
-        <v>294</v>
+        <v>2</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="F142" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G142" s="6">
-        <v>960</v>
-      </c>
-      <c r="H142" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G142" s="5">
+        <v>530</v>
+      </c>
+      <c r="H142" s="5"/>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" s="2">
-        <v>6010000144</v>
+        <v>6010000117</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="C143" s="5">
-        <v>46605</v>
+        <v>282</v>
+      </c>
+      <c r="C143" s="4">
+        <v>46711</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>330</v>
+        <v>283</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>323</v>
+        <v>23</v>
       </c>
       <c r="F143" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G143" s="6">
-        <v>1320</v>
-      </c>
-      <c r="H143" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="G143" s="5">
+        <v>6100</v>
+      </c>
+      <c r="H143" s="5"/>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" s="2">
-        <v>6010000214</v>
+        <v>6010000118</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="C144" s="5">
-        <v>46692</v>
+        <v>284</v>
+      </c>
+      <c r="C144" s="4">
+        <v>46574</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>418</v>
+        <v>285</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>333</v>
+        <v>23</v>
       </c>
       <c r="F144" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G144" s="6">
-        <v>400</v>
-      </c>
-      <c r="H144" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="G144" s="5">
+        <v>10640</v>
+      </c>
+      <c r="H144" s="5"/>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" s="2">
-        <v>6010000215</v>
+        <v>6010000148</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>419</v>
-      </c>
-      <c r="C145" s="5">
-        <v>46726</v>
+        <v>337</v>
+      </c>
+      <c r="C145" s="4">
+        <v>46574</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>420</v>
+        <v>338</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>421</v>
+        <v>23</v>
       </c>
       <c r="F145" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G145" s="6">
-        <v>17</v>
-      </c>
-      <c r="H145" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="G145" s="5">
+        <v>780</v>
+      </c>
+      <c r="H145" s="5"/>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" s="2">
-        <v>6010000215</v>
+        <v>6010000148</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>419</v>
-      </c>
-      <c r="C146" s="5">
-        <v>46726</v>
+        <v>337</v>
+      </c>
+      <c r="C146" s="4">
+        <v>46751</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>422</v>
+        <v>339</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>421</v>
+        <v>23</v>
       </c>
       <c r="F146" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G146" s="6">
-        <v>1278</v>
-      </c>
-      <c r="H146" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="G146" s="5">
+        <v>2520</v>
+      </c>
+      <c r="H146" s="5"/>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A147" s="2">
-        <v>6010000143</v>
-      </c>
-      <c r="B147" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="C147" s="5">
-        <v>46425</v>
-      </c>
-      <c r="D147" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="E147" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="F147" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G147" s="6">
-        <v>120</v>
-      </c>
-      <c r="H147" s="4"/>
+      <c r="A147" s="8">
+        <v>6010000119</v>
+      </c>
+      <c r="B147" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="C147" s="10"/>
+      <c r="D147" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E147" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="F147" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G147" s="11"/>
+      <c r="H147" s="11">
+        <v>300</v>
+      </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" s="2">
-        <v>6010000145</v>
+        <v>6010000085</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="C148" s="5">
-        <v>46556</v>
+        <v>223</v>
+      </c>
+      <c r="C148" s="4">
+        <v>46388</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>332</v>
+        <v>224</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>333</v>
+        <v>225</v>
       </c>
       <c r="F148" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G148" s="6">
-        <v>289</v>
-      </c>
-      <c r="H148" s="4"/>
+      <c r="G148" s="5">
+        <v>31700</v>
+      </c>
+      <c r="H148" s="5"/>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" s="2">
-        <v>4010013596</v>
+        <v>6010000123</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C149" s="5">
-        <v>46446</v>
+        <v>288</v>
+      </c>
+      <c r="C149" s="4">
+        <v>46692</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>123</v>
+        <v>289</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>30</v>
+        <v>92</v>
       </c>
       <c r="F149" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G149" s="6">
-        <v>520</v>
-      </c>
-      <c r="H149" s="4"/>
+      <c r="G149" s="5">
+        <v>620</v>
+      </c>
+      <c r="H149" s="5"/>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" s="2">
-        <v>4010013655</v>
+        <v>6010000123</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="C150" s="5">
-        <v>46550</v>
+        <v>288</v>
+      </c>
+      <c r="C150" s="4">
+        <v>46752</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>130</v>
+        <v>290</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>30</v>
+        <v>92</v>
       </c>
       <c r="F150" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G150" s="6">
-        <v>1000</v>
-      </c>
-      <c r="H150" s="4"/>
+      <c r="G150" s="5">
+        <v>5080</v>
+      </c>
+      <c r="H150" s="5"/>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A151" s="2">
-        <v>4010013474</v>
-      </c>
-      <c r="B151" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C151" s="5">
-        <v>46511</v>
-      </c>
-      <c r="D151" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E151" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F151" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G151" s="6">
-        <v>290</v>
-      </c>
-      <c r="H151" s="4"/>
+      <c r="A151" s="8">
+        <v>6010000230</v>
+      </c>
+      <c r="B151" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="C151" s="10"/>
+      <c r="D151" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E151" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F151" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G151" s="11"/>
+      <c r="H151" s="11">
+        <v>3600</v>
+      </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" s="2">
-        <v>4010013474</v>
+        <v>6010000086</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C152" s="5">
-        <v>46579</v>
+        <v>226</v>
+      </c>
+      <c r="C152" s="4">
+        <v>46641</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>58</v>
+        <v>227</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>30</v>
+        <v>228</v>
       </c>
       <c r="F152" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G152" s="6">
-        <v>590</v>
-      </c>
-      <c r="H152" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G152" s="5">
+        <v>9400</v>
+      </c>
+      <c r="H152" s="5"/>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" s="2">
-        <v>4010013475</v>
+        <v>6010000125</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C153" s="5">
-        <v>46525</v>
+        <v>291</v>
+      </c>
+      <c r="C153" s="4">
+        <v>46574</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>60</v>
+        <v>292</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F153" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G153" s="6">
-        <v>1330</v>
-      </c>
-      <c r="H153" s="4"/>
+      <c r="G153" s="5">
+        <v>660</v>
+      </c>
+      <c r="H153" s="5"/>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" s="2">
-        <v>6010000087</v>
+        <v>6010000144</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="C154" s="5">
-        <v>46388</v>
+        <v>329</v>
+      </c>
+      <c r="C154" s="4">
+        <v>46605</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>229</v>
+        <v>330</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>215</v>
+        <v>321</v>
       </c>
       <c r="F154" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G154" s="6">
-        <v>18100</v>
-      </c>
-      <c r="H154" s="4"/>
+      <c r="G154" s="5">
+        <v>1250</v>
+      </c>
+      <c r="H154" s="5"/>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" s="2">
-        <v>6010000126</v>
+        <v>6010000214</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="C155" s="5">
-        <v>46780</v>
+        <v>417</v>
+      </c>
+      <c r="C155" s="4">
+        <v>46692</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>296</v>
+        <v>418</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>23</v>
+        <v>333</v>
       </c>
       <c r="F155" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G155" s="6">
-        <v>8400</v>
-      </c>
-      <c r="H155" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G155" s="5">
+        <v>360</v>
+      </c>
+      <c r="H155" s="5"/>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" s="2">
-        <v>6010000227</v>
+        <v>6010000215</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>433</v>
-      </c>
-      <c r="C156" s="5">
-        <v>46645</v>
+        <v>419</v>
+      </c>
+      <c r="C156" s="4">
+        <v>46726</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>434</v>
+        <v>420</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>23</v>
+        <v>421</v>
       </c>
       <c r="F156" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G156" s="6">
-        <v>3300</v>
-      </c>
-      <c r="H156" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G156" s="5">
+        <v>1278</v>
+      </c>
+      <c r="H156" s="5"/>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" s="2">
-        <v>6010000227</v>
+        <v>6010000215</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>433</v>
-      </c>
-      <c r="C157" s="5">
-        <v>46631</v>
+        <v>419</v>
+      </c>
+      <c r="C157" s="4">
+        <v>46726</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>435</v>
+        <v>422</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>23</v>
+        <v>421</v>
       </c>
       <c r="F157" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G157" s="6">
-        <v>840</v>
-      </c>
-      <c r="H157" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G157" s="5">
+        <v>12</v>
+      </c>
+      <c r="H157" s="5"/>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A158" s="2">
-        <v>6010000088</v>
-      </c>
-      <c r="B158" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="C158" s="5">
-        <v>46661</v>
-      </c>
-      <c r="D158" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="E158" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="F158" s="3" t="s">
+      <c r="A158" s="8">
+        <v>6010000142</v>
+      </c>
+      <c r="B158" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="C158" s="10"/>
+      <c r="D158" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E158" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="F158" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="G158" s="6">
-        <v>2660</v>
-      </c>
-      <c r="H158" s="4"/>
+      <c r="G158" s="11"/>
+      <c r="H158" s="11">
+        <v>250</v>
+      </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" s="2">
-        <v>4010013666</v>
+        <v>6010000143</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="C159" s="5">
-        <v>46625</v>
+        <v>326</v>
+      </c>
+      <c r="C159" s="4">
+        <v>46425</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>152</v>
+        <v>327</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>30</v>
+        <v>328</v>
       </c>
       <c r="F159" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G159" s="6">
-        <v>100</v>
-      </c>
-      <c r="H159" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G159" s="5">
+        <v>110</v>
+      </c>
+      <c r="H159" s="5"/>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" s="2">
-        <v>4010013666</v>
+        <v>6010000145</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="C160" s="5">
-        <v>46593</v>
+        <v>331</v>
+      </c>
+      <c r="C160" s="4">
+        <v>46556</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>153</v>
+        <v>332</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>30</v>
+        <v>333</v>
       </c>
       <c r="F160" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G160" s="6">
-        <v>200</v>
-      </c>
-      <c r="H160" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G160" s="5">
+        <v>259</v>
+      </c>
+      <c r="H160" s="5"/>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" s="2">
-        <v>6010000128</v>
+        <v>4010013596</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="C161" s="5">
-        <v>46721</v>
+        <v>123</v>
+      </c>
+      <c r="C161" s="4">
+        <v>46446</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>298</v>
+        <v>124</v>
       </c>
       <c r="E161" s="3" t="s">
         <v>30</v>
@@ -5780,71 +5712,71 @@
       <c r="F161" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G161" s="6">
-        <v>900</v>
-      </c>
-      <c r="H161" s="4"/>
+      <c r="G161" s="5">
+        <v>420</v>
+      </c>
+      <c r="H161" s="5"/>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" s="2">
-        <v>6010000129</v>
+        <v>4010013655</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="C162" s="5">
-        <v>46569</v>
+        <v>130</v>
+      </c>
+      <c r="C162" s="4">
+        <v>46550</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>300</v>
+        <v>131</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F162" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G162" s="6">
-        <v>450</v>
-      </c>
-      <c r="H162" s="4"/>
+      <c r="G162" s="5">
+        <v>1000</v>
+      </c>
+      <c r="H162" s="5"/>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" s="2">
-        <v>6010000129</v>
+        <v>4010013474</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="C163" s="5">
-        <v>46758</v>
+        <v>57</v>
+      </c>
+      <c r="C163" s="4">
+        <v>46511</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>301</v>
+        <v>58</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F163" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G163" s="6">
-        <v>700</v>
-      </c>
-      <c r="H163" s="4"/>
+      <c r="G163" s="5">
+        <v>290</v>
+      </c>
+      <c r="H163" s="5"/>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" s="2">
-        <v>6010000130</v>
+        <v>4010013474</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="C164" s="5">
-        <v>46569</v>
+        <v>57</v>
+      </c>
+      <c r="C164" s="4">
+        <v>46579</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>303</v>
+        <v>59</v>
       </c>
       <c r="E164" s="3" t="s">
         <v>30</v>
@@ -5852,23 +5784,23 @@
       <c r="F164" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G164" s="6">
-        <v>430</v>
-      </c>
-      <c r="H164" s="4"/>
+      <c r="G164" s="5">
+        <v>590</v>
+      </c>
+      <c r="H164" s="5"/>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" s="2">
-        <v>6010000130</v>
+        <v>4010013475</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="C165" s="5">
-        <v>46753</v>
+        <v>60</v>
+      </c>
+      <c r="C165" s="4">
+        <v>46525</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>304</v>
+        <v>61</v>
       </c>
       <c r="E165" s="3" t="s">
         <v>30</v>
@@ -5876,383 +5808,381 @@
       <c r="F165" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G165" s="6">
-        <v>630</v>
-      </c>
-      <c r="H165" s="4"/>
+      <c r="G165" s="5">
+        <v>1330</v>
+      </c>
+      <c r="H165" s="5"/>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" s="2">
-        <v>6010000198</v>
+        <v>6010000087</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="C166" s="5">
-        <v>46568</v>
+        <v>229</v>
+      </c>
+      <c r="C166" s="4">
+        <v>46388</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>399</v>
+        <v>230</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>8</v>
+        <v>216</v>
       </c>
       <c r="F166" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G166" s="6">
-        <v>640</v>
-      </c>
-      <c r="H166" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G166" s="5">
+        <v>18100</v>
+      </c>
+      <c r="H166" s="5"/>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" s="2">
-        <v>4010013586</v>
+        <v>6010000126</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C167" s="5">
-        <v>46537</v>
+        <v>293</v>
+      </c>
+      <c r="C167" s="4">
+        <v>46780</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>108</v>
+        <v>294</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F167" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G167" s="6">
-        <v>1440</v>
-      </c>
-      <c r="H167" s="4"/>
+      <c r="G167" s="5">
+        <v>6400</v>
+      </c>
+      <c r="H167" s="5"/>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" s="2">
-        <v>4010013586</v>
+        <v>6010000227</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C168" s="5">
-        <v>46439</v>
+        <v>433</v>
+      </c>
+      <c r="C168" s="4">
+        <v>46645</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>109</v>
+        <v>434</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F168" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G168" s="6">
-        <v>120</v>
-      </c>
-      <c r="H168" s="4"/>
+      <c r="G168" s="5">
+        <v>2540</v>
+      </c>
+      <c r="H168" s="5"/>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" s="2">
-        <v>4010013587</v>
+        <v>6010000088</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C169" s="5">
-        <v>46537</v>
+        <v>231</v>
+      </c>
+      <c r="C169" s="4">
+        <v>46661</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>111</v>
+        <v>232</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>4</v>
+        <v>233</v>
       </c>
       <c r="F169" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G169" s="6">
-        <v>360</v>
-      </c>
-      <c r="H169" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G169" s="5">
+        <v>2660</v>
+      </c>
+      <c r="H169" s="5"/>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" s="2">
-        <v>4010013549</v>
+        <v>4010013666</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C170" s="5">
-        <v>46525</v>
+        <v>151</v>
+      </c>
+      <c r="C170" s="4">
+        <v>46625</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>78</v>
+        <v>152</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F170" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G170" s="6">
-        <v>1180</v>
-      </c>
-      <c r="H170" s="4"/>
+      <c r="G170" s="5">
+        <v>100</v>
+      </c>
+      <c r="H170" s="5"/>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" s="2">
-        <v>4010013249</v>
+        <v>4010013666</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C171" s="5">
-        <v>46442</v>
+        <v>151</v>
+      </c>
+      <c r="C171" s="4">
+        <v>46593</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>1</v>
+        <v>153</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F171" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G171" s="6">
-        <v>860</v>
-      </c>
-      <c r="H171" s="4"/>
+      <c r="G171" s="5">
+        <v>200</v>
+      </c>
+      <c r="H171" s="5"/>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" s="2">
-        <v>4010013573</v>
+        <v>6010000128</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C172" s="5">
-        <v>46423</v>
+        <v>295</v>
+      </c>
+      <c r="C172" s="4">
+        <v>46721</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>84</v>
+        <v>296</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F172" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G172" s="6">
-        <v>800</v>
-      </c>
-      <c r="H172" s="4"/>
+      <c r="G172" s="5">
+        <v>750</v>
+      </c>
+      <c r="H172" s="5"/>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" s="2">
-        <v>4010013574</v>
+        <v>6010000129</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C173" s="5">
-        <v>46545</v>
+        <v>297</v>
+      </c>
+      <c r="C173" s="4">
+        <v>46569</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>86</v>
+        <v>298</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F173" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G173" s="6">
-        <v>660</v>
-      </c>
-      <c r="H173" s="4"/>
+      <c r="G173" s="5">
+        <v>450</v>
+      </c>
+      <c r="H173" s="5"/>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" s="2">
-        <v>4010013588</v>
+        <v>6010000129</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="C174" s="5">
-        <v>46536</v>
+        <v>297</v>
+      </c>
+      <c r="C174" s="4">
+        <v>46758</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>113</v>
+        <v>299</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F174" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G174" s="6">
-        <v>320</v>
-      </c>
-      <c r="H174" s="4"/>
+      <c r="G174" s="5">
+        <v>700</v>
+      </c>
+      <c r="H174" s="5"/>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" s="2">
-        <v>4010013588</v>
+        <v>6010000130</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="C175" s="5">
-        <v>46582</v>
+        <v>300</v>
+      </c>
+      <c r="C175" s="4">
+        <v>46569</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>114</v>
+        <v>301</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F175" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G175" s="6">
-        <v>3620</v>
-      </c>
-      <c r="H175" s="4"/>
+      <c r="G175" s="5">
+        <v>430</v>
+      </c>
+      <c r="H175" s="5"/>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" s="2">
-        <v>4010013479</v>
+        <v>6010000130</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C176" s="5">
-        <v>46536</v>
+        <v>300</v>
+      </c>
+      <c r="C176" s="4">
+        <v>46753</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>69</v>
+        <v>302</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F176" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G176" s="6">
-        <v>320</v>
-      </c>
-      <c r="H176" s="4"/>
+      <c r="G176" s="5">
+        <v>630</v>
+      </c>
+      <c r="H176" s="5"/>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" s="2">
-        <v>4010013479</v>
+        <v>6010000198</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C177" s="5">
-        <v>46419</v>
+        <v>400</v>
+      </c>
+      <c r="C177" s="4">
+        <v>46568</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>70</v>
+        <v>401</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F177" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G177" s="6">
-        <v>240</v>
-      </c>
-      <c r="H177" s="4"/>
+      <c r="G177" s="5">
+        <v>640</v>
+      </c>
+      <c r="H177" s="5"/>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" s="2">
-        <v>4010013479</v>
+        <v>4010013586</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C178" s="5">
-        <v>46594</v>
+        <v>108</v>
+      </c>
+      <c r="C178" s="4">
+        <v>46439</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>71</v>
+        <v>109</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F178" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G178" s="6">
-        <v>400</v>
-      </c>
-      <c r="H178" s="4"/>
+      <c r="G178" s="5">
+        <v>120</v>
+      </c>
+      <c r="H178" s="5"/>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A179" s="2">
-        <v>4010013700</v>
-      </c>
-      <c r="B179" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="C179" s="5">
-        <v>46446</v>
-      </c>
-      <c r="D179" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="E179" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F179" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G179" s="6">
-        <v>600</v>
-      </c>
-      <c r="H179" s="4"/>
+      <c r="A179" s="8">
+        <v>4010013586</v>
+      </c>
+      <c r="B179" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="C179" s="10"/>
+      <c r="D179" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E179" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F179" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G179" s="11"/>
+      <c r="H179" s="11">
+        <v>20</v>
+      </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" s="2">
-        <v>4010013700</v>
+        <v>4010013586</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="C180" s="5">
-        <v>46533</v>
+        <v>108</v>
+      </c>
+      <c r="C180" s="4">
+        <v>46537</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>168</v>
+        <v>110</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F180" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G180" s="6">
-        <v>300</v>
-      </c>
-      <c r="H180" s="4"/>
+      <c r="G180" s="5">
+        <v>1440</v>
+      </c>
+      <c r="H180" s="5"/>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" s="2">
-        <v>4010013701</v>
+        <v>4010013587</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="C181" s="5">
-        <v>46589</v>
+        <v>111</v>
+      </c>
+      <c r="C181" s="4">
+        <v>46537</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>170</v>
+        <v>112</v>
       </c>
       <c r="E181" s="3" t="s">
         <v>4</v>
@@ -6260,23 +6190,23 @@
       <c r="F181" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G181" s="6">
-        <v>1200</v>
-      </c>
-      <c r="H181" s="4"/>
+      <c r="G181" s="5">
+        <v>360</v>
+      </c>
+      <c r="H181" s="5"/>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" s="2">
-        <v>4010013657</v>
+        <v>4010013549</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C182" s="5">
-        <v>46513</v>
+        <v>77</v>
+      </c>
+      <c r="C182" s="4">
+        <v>46525</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="E182" s="3" t="s">
         <v>8</v>
@@ -6284,71 +6214,71 @@
       <c r="F182" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G182" s="6">
-        <v>1060</v>
-      </c>
-      <c r="H182" s="4"/>
+      <c r="G182" s="5">
+        <v>1180</v>
+      </c>
+      <c r="H182" s="5"/>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" s="2">
-        <v>4010013657</v>
+        <v>4010013249</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C183" s="5">
-        <v>46444</v>
+        <v>0</v>
+      </c>
+      <c r="C183" s="4">
+        <v>46442</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>137</v>
+        <v>1</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F183" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G183" s="6">
-        <v>220</v>
-      </c>
-      <c r="H183" s="4"/>
+      <c r="G183" s="5">
+        <v>860</v>
+      </c>
+      <c r="H183" s="5"/>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" s="2">
-        <v>4010013658</v>
+        <v>4010013573</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="C184" s="5">
-        <v>46563</v>
+        <v>84</v>
+      </c>
+      <c r="C184" s="4">
+        <v>46423</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>139</v>
+        <v>85</v>
       </c>
       <c r="E184" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F184" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G184" s="6">
-        <v>110</v>
-      </c>
-      <c r="H184" s="4"/>
+      <c r="G184" s="5">
+        <v>600</v>
+      </c>
+      <c r="H184" s="5"/>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" s="2">
-        <v>4010013658</v>
+        <v>4010013574</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="C185" s="5">
-        <v>46587</v>
+        <v>86</v>
+      </c>
+      <c r="C185" s="4">
+        <v>46545</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>140</v>
+        <v>87</v>
       </c>
       <c r="E185" s="3" t="s">
         <v>8</v>
@@ -6356,1163 +6286,1421 @@
       <c r="F185" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G185" s="6">
-        <v>1200</v>
-      </c>
-      <c r="H185" s="4"/>
+      <c r="G185" s="5">
+        <v>660</v>
+      </c>
+      <c r="H185" s="5"/>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" s="2">
-        <v>4010013548</v>
+        <v>4010013588</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C186" s="5">
-        <v>46469</v>
+        <v>113</v>
+      </c>
+      <c r="C186" s="4">
+        <v>46582</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="E186" s="3" t="s">
-        <v>76</v>
+        <v>4</v>
       </c>
       <c r="F186" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G186" s="6">
-        <v>830</v>
-      </c>
-      <c r="H186" s="4"/>
+      <c r="G186" s="5">
+        <v>3540</v>
+      </c>
+      <c r="H186" s="5"/>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187" s="2">
-        <v>4010013480</v>
+        <v>4010013479</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C187" s="5">
-        <v>46408</v>
+        <v>68</v>
+      </c>
+      <c r="C187" s="4">
+        <v>46536</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F187" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G187" s="6">
-        <v>1230</v>
-      </c>
-      <c r="H187" s="4"/>
+      <c r="G187" s="5">
+        <v>320</v>
+      </c>
+      <c r="H187" s="5"/>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" s="2">
-        <v>4010013477</v>
+        <v>4010013479</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C188" s="5">
-        <v>46443</v>
+        <v>68</v>
+      </c>
+      <c r="C188" s="4">
+        <v>46419</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="E188" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F188" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G188" s="6">
-        <v>60</v>
-      </c>
-      <c r="H188" s="4"/>
+      <c r="G188" s="5">
+        <v>240</v>
+      </c>
+      <c r="H188" s="5"/>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" s="2">
-        <v>4010013477</v>
+        <v>4010013479</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C189" s="5">
-        <v>46574</v>
+        <v>68</v>
+      </c>
+      <c r="C189" s="4">
+        <v>46594</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="E189" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F189" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G189" s="6">
-        <v>1360</v>
-      </c>
-      <c r="H189" s="4"/>
+      <c r="G189" s="5">
+        <v>400</v>
+      </c>
+      <c r="H189" s="5"/>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190" s="2">
-        <v>6010000131</v>
+        <v>4010013700</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="C190" s="5">
-        <v>46784</v>
+        <v>165</v>
+      </c>
+      <c r="C190" s="4">
+        <v>46533</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>306</v>
+        <v>166</v>
       </c>
       <c r="E190" s="3" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F190" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G190" s="6">
-        <v>2340</v>
-      </c>
-      <c r="H190" s="4"/>
+      <c r="G190" s="5">
+        <v>300</v>
+      </c>
+      <c r="H190" s="5"/>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" s="2">
-        <v>4010013699</v>
+        <v>4010013700</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="C191" s="5">
-        <v>46438</v>
+        <v>165</v>
+      </c>
+      <c r="C191" s="4">
+        <v>46446</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E191" s="3" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F191" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G191" s="6">
-        <v>380</v>
-      </c>
-      <c r="H191" s="4"/>
+      <c r="G191" s="5">
+        <v>600</v>
+      </c>
+      <c r="H191" s="5"/>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192" s="2">
-        <v>6010000089</v>
+        <v>4010013701</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="C192" s="5">
-        <v>46424</v>
+        <v>168</v>
+      </c>
+      <c r="C192" s="4">
+        <v>46589</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>234</v>
+        <v>169</v>
       </c>
       <c r="E192" s="3" t="s">
-        <v>235</v>
+        <v>4</v>
       </c>
       <c r="F192" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G192" s="6">
-        <v>2440</v>
-      </c>
-      <c r="H192" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="G192" s="5">
+        <v>1200</v>
+      </c>
+      <c r="H192" s="5"/>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" s="2">
-        <v>6010000089</v>
+        <v>4010013657</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="C193" s="5">
-        <v>46871</v>
+        <v>136</v>
+      </c>
+      <c r="C193" s="4">
+        <v>46513</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>236</v>
+        <v>137</v>
       </c>
       <c r="E193" s="3" t="s">
-        <v>235</v>
+        <v>8</v>
       </c>
       <c r="F193" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G193" s="6">
-        <v>2300</v>
-      </c>
-      <c r="H193" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="G193" s="5">
+        <v>1060</v>
+      </c>
+      <c r="H193" s="5"/>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" s="2">
-        <v>6010000132</v>
+        <v>4010013658</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="C194" s="5">
-        <v>46614</v>
+        <v>138</v>
+      </c>
+      <c r="C194" s="4">
+        <v>46563</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>2</v>
+        <v>139</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F194" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G194" s="6">
-        <v>3600</v>
-      </c>
-      <c r="H194" s="4"/>
+      <c r="G194" s="5">
+        <v>90</v>
+      </c>
+      <c r="H194" s="5"/>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" s="2">
-        <v>6010000146</v>
+        <v>4010013658</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="C195" s="5">
-        <v>46746</v>
+        <v>138</v>
+      </c>
+      <c r="C195" s="4">
+        <v>46587</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>335</v>
+        <v>140</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>336</v>
+        <v>8</v>
       </c>
       <c r="F195" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G195" s="6">
-        <v>640</v>
-      </c>
-      <c r="H195" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="G195" s="5">
+        <v>1200</v>
+      </c>
+      <c r="H195" s="5"/>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" s="2">
-        <v>6010000090</v>
+        <v>4010013548</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="C196" s="5">
-        <v>46482</v>
+        <v>74</v>
+      </c>
+      <c r="C196" s="4">
+        <v>46469</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>238</v>
+        <v>75</v>
       </c>
       <c r="E196" s="3" t="s">
-        <v>239</v>
+        <v>76</v>
       </c>
       <c r="F196" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G196" s="6">
-        <v>4800</v>
-      </c>
-      <c r="H196" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="G196" s="5">
+        <v>830</v>
+      </c>
+      <c r="H196" s="5"/>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" s="2">
-        <v>6010000200</v>
+        <v>4010013480</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="C197" s="5">
-        <v>46593</v>
+        <v>72</v>
+      </c>
+      <c r="C197" s="4">
+        <v>46408</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>403</v>
+        <v>73</v>
       </c>
       <c r="E197" s="3" t="s">
-        <v>404</v>
+        <v>8</v>
       </c>
       <c r="F197" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G197" s="6">
-        <v>450</v>
-      </c>
-      <c r="H197" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="G197" s="5">
+        <v>1230</v>
+      </c>
+      <c r="H197" s="5"/>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" s="2">
-        <v>6010000199</v>
+        <v>4010013477</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="C198" s="5">
-        <v>46556</v>
+        <v>64</v>
+      </c>
+      <c r="C198" s="4">
+        <v>46574</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>401</v>
+        <v>65</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="F198" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G198" s="6">
-        <v>1740</v>
-      </c>
-      <c r="H198" s="4"/>
+      <c r="G198" s="5">
+        <v>900</v>
+      </c>
+      <c r="H198" s="5"/>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" s="2">
-        <v>6010000133</v>
+        <v>6010000131</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="C199" s="5">
-        <v>46388</v>
+        <v>303</v>
+      </c>
+      <c r="C199" s="4">
+        <v>46784</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="E199" s="3" t="s">
-        <v>91</v>
+        <v>23</v>
       </c>
       <c r="F199" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G199" s="6">
-        <v>1420</v>
-      </c>
-      <c r="H199" s="4"/>
+      <c r="G199" s="5">
+        <v>2340</v>
+      </c>
+      <c r="H199" s="5"/>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A200" s="2">
-        <v>6010000134</v>
-      </c>
-      <c r="B200" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="C200" s="5">
-        <v>46488</v>
-      </c>
-      <c r="D200" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="E200" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="F200" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G200" s="6">
-        <v>1860</v>
-      </c>
-      <c r="H200" s="4"/>
+      <c r="A200" s="8">
+        <v>6010000131</v>
+      </c>
+      <c r="B200" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="C200" s="10"/>
+      <c r="D200" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E200" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F200" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G200" s="11"/>
+      <c r="H200" s="11">
+        <v>560</v>
+      </c>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" s="2">
-        <v>6010000135</v>
+        <v>4010013699</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="C201" s="5">
-        <v>46388</v>
+        <v>163</v>
+      </c>
+      <c r="C201" s="4">
+        <v>46438</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>313</v>
+        <v>164</v>
       </c>
       <c r="E201" s="3" t="s">
-        <v>91</v>
+        <v>30</v>
       </c>
       <c r="F201" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G201" s="6">
-        <v>1560</v>
-      </c>
-      <c r="H201" s="4"/>
+      <c r="G201" s="5">
+        <v>380</v>
+      </c>
+      <c r="H201" s="5"/>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202" s="2">
-        <v>6010000136</v>
+        <v>6010000089</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="C202" s="5">
-        <v>46496</v>
+        <v>234</v>
+      </c>
+      <c r="C202" s="4">
+        <v>46424</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>315</v>
+        <v>235</v>
       </c>
       <c r="E202" s="3" t="s">
-        <v>30</v>
+        <v>236</v>
       </c>
       <c r="F202" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G202" s="6">
-        <v>630</v>
-      </c>
-      <c r="H202" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G202" s="5">
+        <v>2360</v>
+      </c>
+      <c r="H202" s="5"/>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203" s="2">
-        <v>6010000137</v>
+        <v>6010000089</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="C203" s="5">
-        <v>46496</v>
+        <v>234</v>
+      </c>
+      <c r="C203" s="4">
+        <v>46871</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>317</v>
+        <v>237</v>
       </c>
       <c r="E203" s="3" t="s">
-        <v>30</v>
+        <v>236</v>
       </c>
       <c r="F203" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G203" s="6">
-        <v>950</v>
-      </c>
-      <c r="H203" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G203" s="5">
+        <v>2300</v>
+      </c>
+      <c r="H203" s="5"/>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204" s="2">
-        <v>4010013269</v>
+        <v>6010000132</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C204" s="5">
-        <v>46558</v>
+        <v>305</v>
+      </c>
+      <c r="C204" s="4">
+        <v>46614</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="E204" s="3" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F204" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G204" s="6">
-        <v>1040</v>
-      </c>
-      <c r="H204" s="4"/>
+      <c r="G204" s="5">
+        <v>3600</v>
+      </c>
+      <c r="H204" s="5"/>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205" s="2">
-        <v>6010000177</v>
+        <v>6010000146</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="C205" s="5">
-        <v>46971</v>
+        <v>334</v>
+      </c>
+      <c r="C205" s="4">
+        <v>46746</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>376</v>
+        <v>335</v>
       </c>
       <c r="E205" s="3" t="s">
-        <v>377</v>
+        <v>336</v>
       </c>
       <c r="F205" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G205" s="6">
-        <v>3180</v>
-      </c>
-      <c r="H205" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G205" s="5">
+        <v>600</v>
+      </c>
+      <c r="H205" s="5"/>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A206" s="2">
-        <v>6010000177</v>
+        <v>6010000090</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="C206" s="5">
-        <v>46941</v>
+        <v>238</v>
+      </c>
+      <c r="C206" s="4">
+        <v>46482</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>378</v>
+        <v>239</v>
       </c>
       <c r="E206" s="3" t="s">
-        <v>377</v>
+        <v>240</v>
       </c>
       <c r="F206" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G206" s="6">
-        <v>200</v>
-      </c>
-      <c r="H206" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G206" s="5">
+        <v>4650</v>
+      </c>
+      <c r="H206" s="5"/>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A207" s="2">
-        <v>6010000178</v>
+        <v>6010000200</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="C207" s="5">
-        <v>47087</v>
+        <v>404</v>
+      </c>
+      <c r="C207" s="4">
+        <v>46593</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>380</v>
+        <v>405</v>
       </c>
       <c r="E207" s="3" t="s">
-        <v>381</v>
+        <v>406</v>
       </c>
       <c r="F207" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G207" s="6">
-        <v>1860</v>
-      </c>
-      <c r="H207" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G207" s="5">
+        <v>420</v>
+      </c>
+      <c r="H207" s="5"/>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208" s="2">
-        <v>4010013597</v>
+        <v>6010000199</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="C208" s="5">
-        <v>46525</v>
+        <v>402</v>
+      </c>
+      <c r="C208" s="4">
+        <v>46556</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>125</v>
+        <v>403</v>
       </c>
       <c r="E208" s="3" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F208" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G208" s="6">
-        <v>620</v>
-      </c>
-      <c r="H208" s="4"/>
+      <c r="G208" s="5">
+        <v>1740</v>
+      </c>
+      <c r="H208" s="5"/>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" s="2">
-        <v>4010013368</v>
+        <v>6010000133</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C209" s="5">
-        <v>46457</v>
+        <v>306</v>
+      </c>
+      <c r="C209" s="4">
+        <v>46388</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>33</v>
+        <v>307</v>
       </c>
       <c r="E209" s="3" t="s">
-        <v>4</v>
+        <v>92</v>
       </c>
       <c r="F209" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G209" s="6">
-        <v>100</v>
-      </c>
-      <c r="H209" s="4"/>
+      <c r="G209" s="5">
+        <v>1420</v>
+      </c>
+      <c r="H209" s="5"/>
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210" s="2">
-        <v>4010013368</v>
+        <v>6010000134</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C210" s="5">
-        <v>46533</v>
+        <v>308</v>
+      </c>
+      <c r="C210" s="4">
+        <v>46488</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>34</v>
+        <v>309</v>
       </c>
       <c r="E210" s="3" t="s">
-        <v>4</v>
+        <v>92</v>
       </c>
       <c r="F210" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G210" s="6">
-        <v>160</v>
-      </c>
-      <c r="H210" s="4"/>
+      <c r="G210" s="5">
+        <v>1860</v>
+      </c>
+      <c r="H210" s="5"/>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211" s="2">
-        <v>4010013369</v>
+        <v>6010000135</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C211" s="5">
-        <v>46429</v>
+        <v>310</v>
+      </c>
+      <c r="C211" s="4">
+        <v>46388</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>36</v>
+        <v>311</v>
       </c>
       <c r="E211" s="3" t="s">
-        <v>4</v>
+        <v>92</v>
       </c>
       <c r="F211" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G211" s="6">
-        <v>440</v>
-      </c>
-      <c r="H211" s="4"/>
+      <c r="G211" s="5">
+        <v>1560</v>
+      </c>
+      <c r="H211" s="5"/>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212" s="2">
-        <v>4010013369</v>
+        <v>6010000136</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C212" s="5">
-        <v>46533</v>
+        <v>312</v>
+      </c>
+      <c r="C212" s="4">
+        <v>46496</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>37</v>
+        <v>313</v>
       </c>
       <c r="E212" s="3" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F212" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G212" s="6">
-        <v>80</v>
-      </c>
-      <c r="H212" s="4"/>
+      <c r="G212" s="5">
+        <v>630</v>
+      </c>
+      <c r="H212" s="5"/>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213" s="2">
-        <v>4010013598</v>
+        <v>6010000137</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C213" s="5">
-        <v>47043</v>
+        <v>314</v>
+      </c>
+      <c r="C213" s="4">
+        <v>46496</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>127</v>
+        <v>315</v>
       </c>
       <c r="E213" s="3" t="s">
-        <v>128</v>
+        <v>30</v>
       </c>
       <c r="F213" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G213" s="6">
-        <v>340</v>
-      </c>
-      <c r="H213" s="4"/>
+      <c r="G213" s="5">
+        <v>850</v>
+      </c>
+      <c r="H213" s="5"/>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214" s="2">
-        <v>6010000091</v>
+        <v>4010013269</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="C214" s="5">
-        <v>46721</v>
+        <v>21</v>
+      </c>
+      <c r="C214" s="4">
+        <v>46558</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>241</v>
+        <v>22</v>
       </c>
       <c r="E214" s="3" t="s">
-        <v>242</v>
+        <v>23</v>
       </c>
       <c r="F214" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G214" s="6">
-        <v>450</v>
-      </c>
-      <c r="H214" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="G214" s="5">
+        <v>1040</v>
+      </c>
+      <c r="H214" s="5"/>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A215" s="2">
-        <v>6010000091</v>
+        <v>6010000177</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="C215" s="5">
-        <v>46392</v>
+        <v>377</v>
+      </c>
+      <c r="C215" s="4">
+        <v>46971</v>
       </c>
       <c r="D215" s="3" t="s">
-        <v>243</v>
+        <v>378</v>
       </c>
       <c r="E215" s="3" t="s">
-        <v>242</v>
+        <v>379</v>
       </c>
       <c r="F215" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G215" s="6">
-        <v>420</v>
-      </c>
-      <c r="H215" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="G215" s="5">
+        <v>2980</v>
+      </c>
+      <c r="H215" s="5"/>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A216" s="2">
-        <v>4010013399</v>
+        <v>6010000178</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C216" s="5">
-        <v>46532</v>
+        <v>380</v>
+      </c>
+      <c r="C216" s="4">
+        <v>47087</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>45</v>
+        <v>381</v>
       </c>
       <c r="E216" s="3" t="s">
-        <v>23</v>
+        <v>382</v>
       </c>
       <c r="F216" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G216" s="6">
-        <v>570</v>
-      </c>
-      <c r="H216" s="4"/>
+      <c r="G216" s="5">
+        <v>1260</v>
+      </c>
+      <c r="H216" s="5"/>
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A217" s="2">
-        <v>6010000203</v>
+        <v>4010013597</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="C217" s="5">
-        <v>46606</v>
+        <v>125</v>
+      </c>
+      <c r="C217" s="4">
+        <v>46525</v>
       </c>
       <c r="D217" s="3" t="s">
-        <v>411</v>
+        <v>126</v>
       </c>
       <c r="E217" s="3" t="s">
-        <v>407</v>
+        <v>11</v>
       </c>
       <c r="F217" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G217" s="6">
-        <v>510</v>
-      </c>
-      <c r="H217" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="G217" s="5">
+        <v>620</v>
+      </c>
+      <c r="H217" s="5"/>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218" s="2">
-        <v>4010014926</v>
+        <v>4010013368</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="C218" s="5">
-        <v>46768</v>
+        <v>32</v>
+      </c>
+      <c r="C218" s="4">
+        <v>46457</v>
       </c>
       <c r="D218" s="3" t="s">
-        <v>176</v>
+        <v>33</v>
       </c>
       <c r="E218" s="3" t="s">
-        <v>177</v>
+        <v>4</v>
       </c>
       <c r="F218" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G218" s="6">
-        <v>830</v>
-      </c>
-      <c r="H218" s="4"/>
+      <c r="G218" s="5">
+        <v>100</v>
+      </c>
+      <c r="H218" s="5"/>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" s="2">
-        <v>7050000020</v>
+        <v>4010013368</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="C219" s="5"/>
+        <v>32</v>
+      </c>
+      <c r="C219" s="4">
+        <v>46533</v>
+      </c>
       <c r="D219" s="3" t="s">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="E219" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F219" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G219" s="6">
-        <v>30</v>
-      </c>
-      <c r="H219" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="G219" s="5">
+        <v>160</v>
+      </c>
+      <c r="H219" s="5"/>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A220" s="2">
-        <v>7050000020</v>
+        <v>4010013369</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="C220" s="5"/>
+        <v>35</v>
+      </c>
+      <c r="C220" s="4">
+        <v>46429</v>
+      </c>
       <c r="D220" s="3" t="s">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="E220" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F220" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G220" s="6">
-        <v>70</v>
-      </c>
-      <c r="H220" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="G220" s="5">
+        <v>440</v>
+      </c>
+      <c r="H220" s="5"/>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221" s="2">
-        <v>4010013659</v>
+        <v>4010013369</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="C221" s="5">
-        <v>46526</v>
+        <v>35</v>
+      </c>
+      <c r="C221" s="4">
+        <v>46533</v>
       </c>
       <c r="D221" s="3" t="s">
-        <v>142</v>
+        <v>37</v>
       </c>
       <c r="E221" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F221" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G221" s="6">
-        <v>1370</v>
-      </c>
-      <c r="H221" s="4"/>
+      <c r="G221" s="5">
+        <v>80</v>
+      </c>
+      <c r="H221" s="5"/>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A222" s="2">
-        <v>4010013273</v>
-      </c>
-      <c r="B222" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C222" s="5">
-        <v>46444</v>
-      </c>
-      <c r="D222" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E222" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F222" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G222" s="6">
-        <v>80</v>
-      </c>
-      <c r="H222" s="4"/>
+      <c r="A222" s="8">
+        <v>4010013598</v>
+      </c>
+      <c r="B222" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C222" s="10"/>
+      <c r="D222" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E222" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="F222" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G222" s="11"/>
+      <c r="H222" s="11">
+        <v>150</v>
+      </c>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A223" s="2">
-        <v>4010013273</v>
+        <v>4010013598</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C223" s="5">
-        <v>46444</v>
+        <v>127</v>
+      </c>
+      <c r="C223" s="4">
+        <v>47043</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>31</v>
+        <v>129</v>
       </c>
       <c r="E223" s="3" t="s">
-        <v>30</v>
+        <v>128</v>
       </c>
       <c r="F223" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G223" s="6">
-        <v>710</v>
-      </c>
-      <c r="H223" s="4"/>
+      <c r="G223" s="5">
+        <v>270</v>
+      </c>
+      <c r="H223" s="5"/>
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A224" s="2">
-        <v>4010013271</v>
+        <v>6010000091</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C224" s="5">
-        <v>46402</v>
+        <v>241</v>
+      </c>
+      <c r="C224" s="4">
+        <v>46721</v>
       </c>
       <c r="D224" s="3" t="s">
-        <v>25</v>
+        <v>242</v>
       </c>
       <c r="E224" s="3" t="s">
-        <v>8</v>
+        <v>243</v>
       </c>
       <c r="F224" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G224" s="6">
-        <v>320</v>
-      </c>
-      <c r="H224" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G224" s="5">
+        <v>450</v>
+      </c>
+      <c r="H224" s="5"/>
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A225" s="2">
-        <v>4010013272</v>
+        <v>6010000091</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C225" s="5">
-        <v>46523</v>
+        <v>241</v>
+      </c>
+      <c r="C225" s="4">
+        <v>46392</v>
       </c>
       <c r="D225" s="3" t="s">
-        <v>27</v>
+        <v>244</v>
       </c>
       <c r="E225" s="3" t="s">
-        <v>8</v>
+        <v>243</v>
       </c>
       <c r="F225" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G225" s="6">
-        <v>1920</v>
-      </c>
-      <c r="H225" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G225" s="5">
+        <v>420</v>
+      </c>
+      <c r="H225" s="5"/>
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226" s="2">
-        <v>4010013663</v>
+        <v>4010013399</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="C226" s="5">
-        <v>46514</v>
+        <v>45</v>
+      </c>
+      <c r="C226" s="4">
+        <v>46532</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>149</v>
+        <v>46</v>
       </c>
       <c r="E226" s="3" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F226" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G226" s="6">
-        <v>200</v>
-      </c>
-      <c r="H226" s="4"/>
+      <c r="G226" s="5">
+        <v>570</v>
+      </c>
+      <c r="H226" s="5"/>
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A227" s="2">
-        <v>4010013663</v>
+        <v>6010000203</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="C227" s="5">
-        <v>46612</v>
+        <v>412</v>
+      </c>
+      <c r="C227" s="4">
+        <v>46606</v>
       </c>
       <c r="D227" s="3" t="s">
-        <v>150</v>
+        <v>413</v>
       </c>
       <c r="E227" s="3" t="s">
-        <v>8</v>
+        <v>409</v>
       </c>
       <c r="F227" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G227" s="6">
-        <v>1200</v>
-      </c>
-      <c r="H227" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G227" s="5">
+        <v>510</v>
+      </c>
+      <c r="H227" s="5"/>
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A228" s="2">
-        <v>6010000245</v>
-      </c>
-      <c r="B228" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="C228" s="5">
-        <v>46629</v>
-      </c>
-      <c r="D228" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="E228" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="F228" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G228" s="6">
-        <v>500</v>
-      </c>
-      <c r="H228" s="4"/>
+      <c r="A228" s="8">
+        <v>4010013592</v>
+      </c>
+      <c r="B228" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C228" s="10"/>
+      <c r="D228" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E228" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="F228" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G228" s="11"/>
+      <c r="H228" s="11">
+        <v>250</v>
+      </c>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A229" s="2">
-        <v>6010000245</v>
+        <v>4010014926</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="C229" s="5">
-        <v>46574</v>
+        <v>174</v>
+      </c>
+      <c r="C229" s="4">
+        <v>46768</v>
       </c>
       <c r="D229" s="3" t="s">
-        <v>458</v>
+        <v>175</v>
       </c>
       <c r="E229" s="3" t="s">
-        <v>457</v>
+        <v>176</v>
       </c>
       <c r="F229" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G229" s="6">
-        <v>9000</v>
-      </c>
-      <c r="H229" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="G229" s="5">
+        <v>780</v>
+      </c>
+      <c r="H229" s="5"/>
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A230" s="2">
-        <v>6010000093</v>
+        <v>7050000020</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="C230" s="5">
-        <v>46504</v>
-      </c>
+        <v>467</v>
+      </c>
+      <c r="C230" s="4"/>
       <c r="D230" s="3" t="s">
-        <v>245</v>
+        <v>2</v>
       </c>
       <c r="E230" s="3" t="s">
-        <v>246</v>
+        <v>2</v>
       </c>
       <c r="F230" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G230" s="6">
-        <v>600</v>
-      </c>
-      <c r="H230" s="4"/>
+      <c r="G230" s="5">
+        <v>30</v>
+      </c>
+      <c r="H230" s="5"/>
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A231" s="2">
-        <v>6010000093</v>
+        <v>7050000020</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="C231" s="5">
-        <v>46504</v>
-      </c>
+        <v>467</v>
+      </c>
+      <c r="C231" s="4"/>
       <c r="D231" s="3" t="s">
-        <v>247</v>
+        <v>2</v>
       </c>
       <c r="E231" s="3" t="s">
-        <v>246</v>
+        <v>2</v>
       </c>
       <c r="F231" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G231" s="6">
-        <v>18000</v>
-      </c>
-      <c r="H231" s="4"/>
+      <c r="G231" s="5">
+        <v>70</v>
+      </c>
+      <c r="H231" s="5"/>
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A232" s="2">
-        <v>6010000161</v>
+        <v>4010013659</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="C232" s="5">
-        <v>47087</v>
+        <v>141</v>
+      </c>
+      <c r="C232" s="4">
+        <v>46526</v>
       </c>
       <c r="D232" s="3" t="s">
-        <v>354</v>
+        <v>142</v>
       </c>
       <c r="E232" s="3" t="s">
-        <v>355</v>
+        <v>8</v>
       </c>
       <c r="F232" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G232" s="6">
-        <v>966</v>
-      </c>
-      <c r="H232" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="G232" s="5">
+        <v>870</v>
+      </c>
+      <c r="H232" s="5"/>
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A233" s="2">
+        <v>4010013273</v>
+      </c>
+      <c r="B233" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C233" s="4">
+        <v>46444</v>
+      </c>
+      <c r="D233" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E233" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F233" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G233" s="5">
+        <v>80</v>
+      </c>
+      <c r="H233" s="5"/>
+    </row>
+    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A234" s="2">
+        <v>4010013273</v>
+      </c>
+      <c r="B234" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C234" s="4">
+        <v>46444</v>
+      </c>
+      <c r="D234" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E234" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F234" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G234" s="5">
+        <v>710</v>
+      </c>
+      <c r="H234" s="5"/>
+    </row>
+    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A235" s="2">
+        <v>4010013271</v>
+      </c>
+      <c r="B235" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C235" s="4">
+        <v>46402</v>
+      </c>
+      <c r="D235" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E235" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F235" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G235" s="5">
+        <v>320</v>
+      </c>
+      <c r="H235" s="5"/>
+    </row>
+    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A236" s="2">
+        <v>4010013272</v>
+      </c>
+      <c r="B236" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C236" s="4">
+        <v>46523</v>
+      </c>
+      <c r="D236" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E236" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F236" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G236" s="5">
+        <v>1320</v>
+      </c>
+      <c r="H236" s="5"/>
+    </row>
+    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A237" s="2">
+        <v>4010013663</v>
+      </c>
+      <c r="B237" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C237" s="4">
+        <v>46612</v>
+      </c>
+      <c r="D237" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E237" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F237" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G237" s="5">
+        <v>1200</v>
+      </c>
+      <c r="H237" s="5"/>
+    </row>
+    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A238" s="2">
+        <v>4010013663</v>
+      </c>
+      <c r="B238" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C238" s="4">
+        <v>46514</v>
+      </c>
+      <c r="D238" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="E238" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F238" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G238" s="5">
+        <v>200</v>
+      </c>
+      <c r="H238" s="5"/>
+    </row>
+    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A239" s="2">
+        <v>6010000245</v>
+      </c>
+      <c r="B239" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="C239" s="4">
+        <v>46574</v>
+      </c>
+      <c r="D239" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="E239" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="F239" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G239" s="5">
+        <v>8700</v>
+      </c>
+      <c r="H239" s="5"/>
+    </row>
+    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A240" s="2">
+        <v>6010000245</v>
+      </c>
+      <c r="B240" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="C240" s="4">
+        <v>46629</v>
+      </c>
+      <c r="D240" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="E240" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="F240" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G240" s="5">
+        <v>500</v>
+      </c>
+      <c r="H240" s="5"/>
+    </row>
+    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A241" s="2">
+        <v>6010000093</v>
+      </c>
+      <c r="B241" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C241" s="4">
+        <v>46504</v>
+      </c>
+      <c r="D241" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="E241" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="F241" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G241" s="5">
+        <v>600</v>
+      </c>
+      <c r="H241" s="5"/>
+    </row>
+    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A242" s="2">
+        <v>6010000093</v>
+      </c>
+      <c r="B242" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C242" s="4">
+        <v>46504</v>
+      </c>
+      <c r="D242" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="E242" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="F242" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G242" s="5">
+        <v>18000</v>
+      </c>
+      <c r="H242" s="5"/>
+    </row>
+    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A243" s="2">
+        <v>6010000161</v>
+      </c>
+      <c r="B243" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C243" s="4">
+        <v>47087</v>
+      </c>
+      <c r="D243" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="E243" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="F243" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G243" s="5">
+        <v>936</v>
+      </c>
+      <c r="H243" s="5"/>
+    </row>
+    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A244" s="2">
         <v>6010000162</v>
       </c>
-      <c r="B233" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="C233" s="5">
+      <c r="B244" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="C244" s="4">
         <v>47087</v>
       </c>
-      <c r="D233" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="E233" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="F233" s="3" t="s">
+      <c r="D244" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="E244" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="F244" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G233" s="6">
-        <v>1374</v>
-      </c>
-      <c r="H233" s="4"/>
+      <c r="G244" s="5">
+        <v>1344</v>
+      </c>
+      <c r="H244" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H233" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H233">
-      <sortCondition sortBy="fontColor" ref="B1:B233" dxfId="1"/>
+  <autoFilter ref="A1:H244" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H244">
+      <sortCondition ref="B1:B244"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="0" type="noConversion"/>

--- a/KSTOCK.xlsx
+++ b/KSTOCK.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$240</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$234</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1174" uniqueCount="480">
   <si>
     <t>7003</t>
   </si>
@@ -70,9 +70,6 @@
     <t>20X1X10</t>
   </si>
   <si>
-    <t>25S3GTA407</t>
-  </si>
-  <si>
     <t>CILNIEASE-10</t>
   </si>
   <si>
@@ -109,15 +106,15 @@
     <t>VILDAPHARM-DP</t>
   </si>
   <si>
+    <t>25S3GTA308</t>
+  </si>
+  <si>
+    <t>10X1X10</t>
+  </si>
+  <si>
     <t>25S3GTA311</t>
   </si>
   <si>
-    <t>10X1X10</t>
-  </si>
-  <si>
-    <t>25S3GTA308</t>
-  </si>
-  <si>
     <t>TENEJEET-M 1000</t>
   </si>
   <si>
@@ -172,15 +169,15 @@
     <t>MONTALIA LC TABLET 15s</t>
   </si>
   <si>
+    <t>25S3GTB480</t>
+  </si>
+  <si>
+    <t>20X1X15</t>
+  </si>
+  <si>
     <t>25S3GTA271</t>
   </si>
   <si>
-    <t>20X1X15</t>
-  </si>
-  <si>
-    <t>25S3GTB480</t>
-  </si>
-  <si>
     <t>DYDROSMILE 10</t>
   </si>
   <si>
@@ -223,15 +220,15 @@
     <t>ROSUSEP-ASP 20</t>
   </si>
   <si>
+    <t>25S3GCA138</t>
+  </si>
+  <si>
+    <t>25S3GCA105</t>
+  </si>
+  <si>
     <t>25S3GCA034</t>
   </si>
   <si>
-    <t>25S3GCA138</t>
-  </si>
-  <si>
-    <t>25S3GCA105</t>
-  </si>
-  <si>
     <t>SITAFREE-MET 1000 IR</t>
   </si>
   <si>
@@ -334,12 +331,12 @@
     <t>GLIMKAT-MET 1 (PR)</t>
   </si>
   <si>
+    <t>25S3GTA626</t>
+  </si>
+  <si>
     <t>25S3GTA625</t>
   </si>
   <si>
-    <t>25S3GTA626</t>
-  </si>
-  <si>
     <t>GLIMKAT-MET 2 (PR)</t>
   </si>
   <si>
@@ -352,9 +349,6 @@
     <t>25S3GCA094</t>
   </si>
   <si>
-    <t>25S3GCA050</t>
-  </si>
-  <si>
     <t>ROSUSEP- GOLD 20</t>
   </si>
   <si>
@@ -424,15 +418,15 @@
     <t>LEVELISH 500</t>
   </si>
   <si>
+    <t>25S2GTA561</t>
+  </si>
+  <si>
+    <t>10X10</t>
+  </si>
+  <si>
     <t>25S2GTB370</t>
   </si>
   <si>
-    <t>10X10</t>
-  </si>
-  <si>
-    <t>25S2GTA561</t>
-  </si>
-  <si>
     <t>SITAFREE-100</t>
   </si>
   <si>
@@ -472,12 +466,12 @@
     <t>VILDAPHARM-OD 100</t>
   </si>
   <si>
+    <t>25S1GTA780</t>
+  </si>
+  <si>
     <t>25S1GTA463</t>
   </si>
   <si>
-    <t>25S1GTA780</t>
-  </si>
-  <si>
     <t>REBEHIT-LS</t>
   </si>
   <si>
@@ -502,12 +496,12 @@
     <t>ATROLIA GOLD 20/75</t>
   </si>
   <si>
+    <t>25S3GCA129</t>
+  </si>
+  <si>
     <t>25S3GCA113</t>
   </si>
   <si>
-    <t>25S3GCA129</t>
-  </si>
-  <si>
     <t>Atrolia-ASP 75</t>
   </si>
   <si>
@@ -580,12 +574,12 @@
     <t>CALWINIT D3 INJ</t>
   </si>
   <si>
+    <t>NL2922501</t>
+  </si>
+  <si>
     <t>10X6X1ML</t>
   </si>
   <si>
-    <t>NL2922501</t>
-  </si>
-  <si>
     <t>CEFTAPACE-1G</t>
   </si>
   <si>
@@ -607,15 +601,15 @@
     <t>DECAHIT INJECTION</t>
   </si>
   <si>
+    <t>NL2722503</t>
+  </si>
+  <si>
+    <t>96X2ML</t>
+  </si>
+  <si>
     <t>NL2722504</t>
   </si>
   <si>
-    <t>96X2ML</t>
-  </si>
-  <si>
-    <t>NL2722503</t>
-  </si>
-  <si>
     <t>GENTAHIT INJ</t>
   </si>
   <si>
@@ -730,15 +724,15 @@
     <t>SYNACORT</t>
   </si>
   <si>
+    <t>NL2682501</t>
+  </si>
+  <si>
+    <t>10X8X1ML</t>
+  </si>
+  <si>
     <t>NL2682502</t>
   </si>
   <si>
-    <t>10X8X1ML</t>
-  </si>
-  <si>
-    <t>NL2682501</t>
-  </si>
-  <si>
     <t>TAZCILLIN-P 4.5 INJ</t>
   </si>
   <si>
@@ -751,15 +745,15 @@
     <t>TNEMIC INJ</t>
   </si>
   <si>
+    <t>NL2852505</t>
+  </si>
+  <si>
+    <t>6X5X5ML</t>
+  </si>
+  <si>
     <t>NL2852502</t>
   </si>
   <si>
-    <t>6X5X5ML</t>
-  </si>
-  <si>
-    <t>NL2852505</t>
-  </si>
-  <si>
     <t>VOLOPAIN INJ</t>
   </si>
   <si>
@@ -811,9 +805,6 @@
     <t>41215071</t>
   </si>
   <si>
-    <t>41215066</t>
-  </si>
-  <si>
     <t>CLAVMYCIN 625 DUO TABLET</t>
   </si>
   <si>
@@ -907,12 +898,12 @@
     <t>PANTAHIT 40 TABLET 15S</t>
   </si>
   <si>
+    <t>GF985056B</t>
+  </si>
+  <si>
     <t>GF986003C</t>
   </si>
   <si>
-    <t>GF985056B</t>
-  </si>
-  <si>
     <t>PANTAHIT-D TABLET</t>
   </si>
   <si>
@@ -943,12 +934,12 @@
     <t>RIFIXIEM 550 TABLET</t>
   </si>
   <si>
+    <t>GE545020</t>
+  </si>
+  <si>
     <t>GE545002B</t>
   </si>
   <si>
-    <t>GE545020</t>
-  </si>
-  <si>
     <t>SPASMOSAFE-MF TABLET</t>
   </si>
   <si>
@@ -1057,9 +1048,6 @@
     <t>T60106A</t>
   </si>
   <si>
-    <t>T50628A</t>
-  </si>
-  <si>
     <t>ENOXAEASE 60 INJ</t>
   </si>
   <si>
@@ -1096,12 +1084,6 @@
     <t>2D260006G</t>
   </si>
   <si>
-    <t>CALWINIT K2-7 SOFTGEL CAPSULE 10S</t>
-  </si>
-  <si>
-    <t>36D260126B</t>
-  </si>
-  <si>
     <t>CALWINIT-D3 SOFTGEL CAPSULE</t>
   </si>
   <si>
@@ -1309,15 +1291,12 @@
     <t>POVIALL OINTMENT 125GM</t>
   </si>
   <si>
-    <t>GLN26007</t>
+    <t>GLN26004</t>
   </si>
   <si>
     <t>125GM</t>
   </si>
   <si>
-    <t>GLN26004</t>
-  </si>
-  <si>
     <t>FAROPHARM 300 ER TABLET</t>
   </si>
   <si>
@@ -1360,24 +1339,24 @@
     <t>CLAVMYCIN 625 DUO TABLET (20x1x10)</t>
   </si>
   <si>
+    <t>50045258</t>
+  </si>
+  <si>
     <t>50046010</t>
   </si>
   <si>
-    <t>50045258</t>
-  </si>
-  <si>
     <t>CT25512H</t>
   </si>
   <si>
     <t>CEFIXLIA - 200 DT TABLET</t>
   </si>
   <si>
+    <t>CT26039A</t>
+  </si>
+  <si>
     <t>CT25427</t>
   </si>
   <si>
-    <t>CT26039A</t>
-  </si>
-  <si>
     <t>FERRIFINE XT TABLET</t>
   </si>
   <si>
@@ -1408,15 +1387,15 @@
     <t>VOLOPAIN AQ INJECTION</t>
   </si>
   <si>
+    <t>NL3062501</t>
+  </si>
+  <si>
+    <t>20 X 5 X 1ML</t>
+  </si>
+  <si>
     <t>NL3062502</t>
   </si>
   <si>
-    <t>20 X 5 X 1ML</t>
-  </si>
-  <si>
-    <t>NL3062501</t>
-  </si>
-  <si>
     <t>MONTALIA-LC 30ML SYRUP</t>
   </si>
   <si>
@@ -1468,9 +1447,6 @@
     <t>Sales Unit</t>
   </si>
   <si>
-    <t>Sales Transit Qty</t>
-  </si>
-  <si>
     <t>Expiry</t>
   </si>
   <si>
@@ -1478,12 +1454,18 @@
   </si>
   <si>
     <t xml:space="preserve"> Unrestricted Qty</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Transit Qty</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -1517,7 +1499,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1562,7 +1544,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -1573,6 +1555,9 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1594,6 +1579,9 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1939,74 +1927,76 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I240"/>
+  <dimension ref="A1:I234"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" style="1" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="13.109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="31.109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.5546875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.88671875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.21875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="13.44140625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="14.21875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="36.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.21875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.21875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="14.109375" style="1" customWidth="1"/>
     <col min="10" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:9" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>471</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>472</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>473</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>476</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>477</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>474</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>475</v>
+      </c>
+      <c r="H1" s="15" t="s">
         <v>478</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="I1" s="14" t="s">
         <v>479</v>
-      </c>
-      <c r="C1" s="12" t="s">
-        <v>480</v>
-      </c>
-      <c r="D1" s="12" t="s">
-        <v>484</v>
-      </c>
-      <c r="E1" s="12" t="s">
-        <v>485</v>
-      </c>
-      <c r="F1" s="12" t="s">
-        <v>481</v>
-      </c>
-      <c r="G1" s="12" t="s">
-        <v>482</v>
-      </c>
-      <c r="H1" s="13" t="s">
-        <v>486</v>
-      </c>
-      <c r="I1" s="13" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="3">
         <v>6010000095</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="D2" s="10"/>
-      <c r="E2" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11">
-        <v>1200</v>
-      </c>
+      <c r="C2" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="D2" s="5">
+        <v>46559</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="6">
+        <v>1420</v>
+      </c>
+      <c r="I2" s="4"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -2016,51 +2006,49 @@
         <v>6010000095</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="D3" s="5">
+        <v>46568</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="D3" s="4">
-        <v>46559</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>252</v>
-      </c>
       <c r="F3" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="5">
-        <v>2820</v>
-      </c>
-      <c r="I3" s="5"/>
+      <c r="H3" s="6">
+        <v>5460</v>
+      </c>
+      <c r="I3" s="4"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="9">
         <v>6010000095</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="D4" s="4">
-        <v>46568</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H4" s="5">
-        <v>5460</v>
-      </c>
-      <c r="I4" s="5"/>
+      <c r="C4" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="D4" s="11"/>
+      <c r="E4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="H4" s="12"/>
+      <c r="I4" s="13">
+        <v>1200</v>
+      </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -2070,47 +2058,47 @@
         <v>6010000096</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="D5" s="4">
+        <v>252</v>
+      </c>
+      <c r="D5" s="5">
         <v>46559</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="6">
         <v>1200</v>
       </c>
-      <c r="I5" s="5"/>
+      <c r="I5" s="4"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="9">
         <v>4010013388</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="9" t="s">
+      <c r="C6" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="11"/>
+      <c r="E6" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="F6" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11">
+      <c r="F6" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="H6" s="12"/>
+      <c r="I6" s="13">
         <v>1280</v>
       </c>
     </row>
@@ -2122,24 +2110,24 @@
         <v>6010000138</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="D7" s="4">
+        <v>320</v>
+      </c>
+      <c r="D7" s="5">
         <v>46746</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="6">
         <v>653</v>
       </c>
-      <c r="I7" s="5"/>
+      <c r="I7" s="4"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
@@ -2149,24 +2137,24 @@
         <v>4010015107</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D8" s="4">
+        <v>177</v>
+      </c>
+      <c r="D8" s="5">
         <v>46752</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H8" s="5">
-        <v>1440</v>
-      </c>
-      <c r="I8" s="5"/>
+      <c r="H8" s="6">
+        <v>1040</v>
+      </c>
+      <c r="I8" s="4"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
@@ -2176,24 +2164,24 @@
         <v>4010013476</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D9" s="5">
+        <v>46548</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D9" s="4">
-        <v>46548</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>62</v>
-      </c>
       <c r="F9" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H9" s="5">
-        <v>270</v>
-      </c>
-      <c r="I9" s="5"/>
+      <c r="H9" s="6">
+        <v>230</v>
+      </c>
+      <c r="I9" s="4"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
@@ -2203,24 +2191,24 @@
         <v>6010000097</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="D10" s="5">
+        <v>46751</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="D10" s="4">
-        <v>46751</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>258</v>
-      </c>
       <c r="G10" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10" s="6">
         <v>160</v>
       </c>
-      <c r="I10" s="5"/>
+      <c r="I10" s="4"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
@@ -2230,24 +2218,24 @@
         <v>6010000097</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="D11" s="5">
+        <v>46556</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="D11" s="4">
-        <v>46556</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>258</v>
-      </c>
       <c r="G11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H11" s="5">
-        <v>600</v>
-      </c>
-      <c r="I11" s="5"/>
+      <c r="H11" s="6">
+        <v>400</v>
+      </c>
+      <c r="I11" s="4"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
@@ -2257,24 +2245,24 @@
         <v>6010000098</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="D12" s="4">
+        <v>258</v>
+      </c>
+      <c r="D12" s="5">
         <v>46539</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H12" s="6">
         <v>1540</v>
       </c>
-      <c r="I12" s="5"/>
+      <c r="I12" s="4"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
@@ -2284,24 +2272,24 @@
         <v>6010000195</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="D13" s="4">
+        <v>399</v>
+      </c>
+      <c r="D13" s="5">
         <v>46549</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H13" s="5">
-        <v>500</v>
-      </c>
-      <c r="I13" s="5"/>
+      <c r="H13" s="6">
+        <v>440</v>
+      </c>
+      <c r="I13" s="4"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
@@ -2313,7 +2301,7 @@
       <c r="C14" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="5">
         <v>46568</v>
       </c>
       <c r="E14" s="2" t="s">
@@ -2325,10 +2313,10 @@
       <c r="G14" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H14" s="5">
-        <v>680</v>
-      </c>
-      <c r="I14" s="5"/>
+      <c r="H14" s="6">
+        <v>580</v>
+      </c>
+      <c r="I14" s="4"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
@@ -2340,7 +2328,7 @@
       <c r="C15" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="5">
         <v>46589</v>
       </c>
       <c r="E15" s="2" t="s">
@@ -2352,10 +2340,10 @@
       <c r="G15" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H15" s="5">
+      <c r="H15" s="6">
         <v>1200</v>
       </c>
-      <c r="I15" s="5"/>
+      <c r="I15" s="4"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
@@ -2367,7 +2355,7 @@
       <c r="C16" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="5">
         <v>46568</v>
       </c>
       <c r="E16" s="2" t="s">
@@ -2379,10 +2367,10 @@
       <c r="G16" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H16" s="5">
+      <c r="H16" s="6">
         <v>630</v>
       </c>
-      <c r="I16" s="5"/>
+      <c r="I16" s="4"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
@@ -2392,13 +2380,13 @@
         <v>4010013692</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="D17" s="4">
+        <v>156</v>
+      </c>
+      <c r="D17" s="5">
         <v>46549</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>9</v>
@@ -2406,10 +2394,10 @@
       <c r="G17" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H17" s="5">
+      <c r="H17" s="6">
         <v>940</v>
       </c>
-      <c r="I17" s="5"/>
+      <c r="I17" s="4"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
@@ -2419,13 +2407,13 @@
         <v>4010013693</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="D18" s="4">
-        <v>46549</v>
+        <v>158</v>
+      </c>
+      <c r="D18" s="5">
+        <v>46587</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>9</v>
@@ -2433,10 +2421,10 @@
       <c r="G18" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H18" s="5">
-        <v>480</v>
-      </c>
-      <c r="I18" s="5"/>
+      <c r="H18" s="6">
+        <v>420</v>
+      </c>
+      <c r="I18" s="4"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
@@ -2446,13 +2434,13 @@
         <v>4010013693</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D19" s="5">
+        <v>46549</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>160</v>
-      </c>
-      <c r="D19" s="4">
-        <v>46587</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>162</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>9</v>
@@ -2460,10 +2448,10 @@
       <c r="G19" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H19" s="5">
-        <v>420</v>
-      </c>
-      <c r="I19" s="5"/>
+      <c r="H19" s="6">
+        <v>480</v>
+      </c>
+      <c r="I19" s="4"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
@@ -2473,24 +2461,24 @@
         <v>4010013578</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D20" s="5">
+        <v>46640</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D20" s="4">
-        <v>46640</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>90</v>
-      </c>
       <c r="F20" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H20" s="5">
+      <c r="H20" s="6">
         <v>290</v>
       </c>
-      <c r="I20" s="5"/>
+      <c r="I20" s="4"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
@@ -2500,24 +2488,24 @@
         <v>4010013580</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D21" s="5">
+        <v>46666</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D21" s="4">
-        <v>46666</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F21" s="2" t="s">
-        <v>93</v>
-      </c>
       <c r="G21" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H21" s="5">
+      <c r="H21" s="6">
         <v>520</v>
       </c>
-      <c r="I21" s="5"/>
+      <c r="I21" s="4"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
@@ -2527,24 +2515,24 @@
         <v>4010013551</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D22" s="5">
+        <v>46598</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D22" s="4">
-        <v>46598</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>82</v>
-      </c>
       <c r="F22" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H22" s="5">
-        <v>1360</v>
-      </c>
-      <c r="I22" s="5"/>
+      <c r="H22" s="6">
+        <v>1160</v>
+      </c>
+      <c r="I22" s="4"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
@@ -2554,24 +2542,24 @@
         <v>4010013660</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="D23" s="4">
+        <v>143</v>
+      </c>
+      <c r="D23" s="5">
         <v>46518</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H23" s="5">
+      <c r="H23" s="6">
         <v>380</v>
       </c>
-      <c r="I23" s="5"/>
+      <c r="I23" s="4"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
@@ -2581,13 +2569,13 @@
         <v>4010013694</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="D24" s="4">
+        <v>161</v>
+      </c>
+      <c r="D24" s="5">
         <v>46536</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>9</v>
@@ -2595,10 +2583,10 @@
       <c r="G24" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H24" s="5">
+      <c r="H24" s="6">
         <v>670</v>
       </c>
-      <c r="I24" s="5"/>
+      <c r="I24" s="4"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
@@ -2608,24 +2596,24 @@
         <v>6010000065</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D25" s="5">
+        <v>46447</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="F25" s="2" t="s">
         <v>181</v>
-      </c>
-      <c r="D25" s="4">
-        <v>46447</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>183</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H25" s="5">
-        <v>2200</v>
-      </c>
-      <c r="I25" s="5"/>
+      <c r="H25" s="6">
+        <v>2000</v>
+      </c>
+      <c r="I25" s="4"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
@@ -2635,24 +2623,24 @@
         <v>4010013582</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D26" s="5">
+        <v>46392</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="D26" s="4">
-        <v>46392</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="F26" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="F26" s="2" t="s">
-        <v>100</v>
-      </c>
       <c r="G26" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H26" s="5">
+      <c r="H26" s="6">
         <v>400</v>
       </c>
-      <c r="I26" s="5"/>
+      <c r="I26" s="4"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
@@ -2662,24 +2650,24 @@
         <v>4010013582</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D27" s="4">
+        <v>97</v>
+      </c>
+      <c r="D27" s="5">
         <v>46541</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H27" s="5">
+      <c r="H27" s="6">
         <v>320</v>
       </c>
-      <c r="I27" s="5"/>
+      <c r="I27" s="4"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
@@ -2689,24 +2677,24 @@
         <v>4010013581</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D28" s="5">
+        <v>46412</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D28" s="4">
-        <v>46412</v>
-      </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="F28" s="2" t="s">
-        <v>96</v>
-      </c>
       <c r="G28" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H28" s="5">
+      <c r="H28" s="6">
         <v>360</v>
       </c>
-      <c r="I28" s="5"/>
+      <c r="I28" s="4"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
@@ -2716,47 +2704,47 @@
         <v>4010013581</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D29" s="4">
+        <v>93</v>
+      </c>
+      <c r="D29" s="5">
         <v>46541</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H29" s="5">
+      <c r="H29" s="6">
         <v>4880</v>
       </c>
-      <c r="I29" s="5"/>
+      <c r="I29" s="4"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B30" s="8">
+      <c r="B30" s="9">
         <v>6010000066</v>
       </c>
-      <c r="C30" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="D30" s="10"/>
-      <c r="E30" s="9" t="s">
+      <c r="C30" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="D30" s="11"/>
+      <c r="E30" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="F30" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="G30" s="9" t="s">
+      <c r="F30" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="G30" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="H30" s="11"/>
-      <c r="I30" s="11">
+      <c r="H30" s="12"/>
+      <c r="I30" s="13">
         <v>900</v>
       </c>
     </row>
@@ -2768,22 +2756,22 @@
         <v>7050000018</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="D31" s="4"/>
+        <v>468</v>
+      </c>
+      <c r="D31" s="5"/>
       <c r="E31" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H31" s="5">
+      <c r="H31" s="6">
         <v>100</v>
       </c>
-      <c r="I31" s="5"/>
+      <c r="I31" s="4"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
@@ -2793,22 +2781,22 @@
         <v>7050000016</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="D32" s="4"/>
+        <v>466</v>
+      </c>
+      <c r="D32" s="5"/>
       <c r="E32" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H32" s="5">
+      <c r="H32" s="6">
         <v>100</v>
       </c>
-      <c r="I32" s="5"/>
+      <c r="I32" s="4"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
@@ -2818,22 +2806,22 @@
         <v>7050000015</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="D33" s="4"/>
+        <v>465</v>
+      </c>
+      <c r="D33" s="5"/>
       <c r="E33" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H33" s="5">
+      <c r="H33" s="6">
         <v>100</v>
       </c>
-      <c r="I33" s="5"/>
+      <c r="I33" s="4"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
@@ -2843,22 +2831,22 @@
         <v>7050000014</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="D34" s="4"/>
+        <v>463</v>
+      </c>
+      <c r="D34" s="5"/>
       <c r="E34" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H34" s="5">
+      <c r="H34" s="6">
         <v>100</v>
       </c>
-      <c r="I34" s="5"/>
+      <c r="I34" s="4"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
@@ -2868,74 +2856,74 @@
         <v>7050000017</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="D35" s="4"/>
+        <v>467</v>
+      </c>
+      <c r="D35" s="5"/>
       <c r="E35" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H35" s="5">
+      <c r="H35" s="6">
         <v>100</v>
       </c>
-      <c r="I35" s="5"/>
+      <c r="I35" s="4"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B36" s="8">
+      <c r="B36" s="3">
         <v>4010013550</v>
       </c>
-      <c r="C36" s="9" t="s">
+      <c r="C36" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D36" s="5">
+        <v>46568</v>
+      </c>
+      <c r="E36" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D36" s="10"/>
-      <c r="E36" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="G36" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="H36" s="11"/>
-      <c r="I36" s="11">
-        <v>360</v>
-      </c>
+      <c r="F36" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H36" s="6">
+        <v>1170</v>
+      </c>
+      <c r="I36" s="4"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B37" s="3">
+      <c r="B37" s="9">
         <v>4010013550</v>
       </c>
-      <c r="C37" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D37" s="4">
-        <v>46568</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H37" s="5">
-        <v>1170</v>
-      </c>
-      <c r="I37" s="5"/>
+      <c r="C37" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D37" s="11"/>
+      <c r="E37" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G37" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="H37" s="12"/>
+      <c r="I37" s="13">
+        <v>360</v>
+      </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
@@ -2945,24 +2933,24 @@
         <v>4010013550</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D38" s="4">
+        <v>77</v>
+      </c>
+      <c r="D38" s="5">
         <v>46404</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H38" s="5">
+      <c r="H38" s="6">
         <v>270</v>
       </c>
-      <c r="I38" s="5"/>
+      <c r="I38" s="4"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
@@ -2972,24 +2960,24 @@
         <v>4010013478</v>
       </c>
       <c r="C39" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D39" s="5">
+        <v>46551</v>
+      </c>
+      <c r="E39" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D39" s="4">
-        <v>46551</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="F39" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H39" s="5">
+      <c r="H39" s="6">
         <v>240</v>
       </c>
-      <c r="I39" s="5"/>
+      <c r="I39" s="4"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
@@ -2999,24 +2987,24 @@
         <v>6010000154</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="D40" s="4">
+        <v>346</v>
+      </c>
+      <c r="D40" s="5">
         <v>47007</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H40" s="5">
-        <v>639</v>
-      </c>
-      <c r="I40" s="5"/>
+      <c r="H40" s="6">
+        <v>449</v>
+      </c>
+      <c r="I40" s="4"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
@@ -3026,13 +3014,13 @@
         <v>6010000158</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="D41" s="4">
+        <v>353</v>
+      </c>
+      <c r="D41" s="5">
         <v>46752</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>9</v>
@@ -3040,429 +3028,429 @@
       <c r="G41" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H41" s="5">
-        <v>600</v>
-      </c>
-      <c r="I41" s="5"/>
+      <c r="H41" s="6">
+        <v>440</v>
+      </c>
+      <c r="I41" s="4"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B42" s="8">
+      <c r="B42" s="3">
         <v>6010000068</v>
       </c>
-      <c r="C42" s="9" t="s">
+      <c r="C42" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D42" s="5">
+        <v>46495</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="F42" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="D42" s="10"/>
-      <c r="E42" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="F42" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="G42" s="9" t="s">
+      <c r="G42" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H42" s="11"/>
-      <c r="I42" s="11">
-        <v>1500</v>
-      </c>
+      <c r="H42" s="6">
+        <v>1290</v>
+      </c>
+      <c r="I42" s="4"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B43" s="3">
+      <c r="B43" s="9">
         <v>6010000068</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="D43" s="11"/>
+      <c r="E43" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="D43" s="4">
-        <v>46495</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="G43" s="2" t="s">
+      <c r="G43" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="H43" s="5">
-        <v>1290</v>
-      </c>
-      <c r="I43" s="5"/>
+      <c r="H43" s="12"/>
+      <c r="I43" s="13">
+        <v>1500</v>
+      </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B44" s="3">
-        <v>6010000159</v>
+        <v>6010000160</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="D44" s="4">
+        <v>355</v>
+      </c>
+      <c r="D44" s="5">
         <v>46780</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>31</v>
+        <v>357</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H44" s="5">
-        <v>160</v>
-      </c>
-      <c r="I44" s="5"/>
+      <c r="H44" s="6">
+        <v>1520</v>
+      </c>
+      <c r="I44" s="4"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B45" s="3">
-        <v>6010000160</v>
+        <v>6010000100</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="D45" s="4">
-        <v>46780</v>
+        <v>260</v>
+      </c>
+      <c r="D45" s="5">
+        <v>46579</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>362</v>
+        <v>261</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>363</v>
+        <v>23</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H45" s="5">
-        <v>1520</v>
-      </c>
-      <c r="I45" s="5"/>
+      <c r="H45" s="6">
+        <v>2100</v>
+      </c>
+      <c r="I45" s="4"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B46" s="3">
-        <v>6010000100</v>
+        <v>6010000234</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="D46" s="4">
-        <v>46579</v>
+        <v>443</v>
+      </c>
+      <c r="D46" s="5">
+        <v>46726</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>263</v>
+        <v>444</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H46" s="5">
-        <v>2100</v>
-      </c>
-      <c r="I46" s="5"/>
+      <c r="H46" s="6">
+        <v>7920</v>
+      </c>
+      <c r="I46" s="4"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B47" s="3">
-        <v>6010000100</v>
+        <v>6010000234</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="D47" s="4">
-        <v>46539</v>
+        <v>443</v>
+      </c>
+      <c r="D47" s="5">
+        <v>46661</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>264</v>
+        <v>445</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H47" s="5">
-        <v>420</v>
-      </c>
-      <c r="I47" s="5"/>
+      <c r="H47" s="6">
+        <v>340</v>
+      </c>
+      <c r="I47" s="4"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B48" s="3">
-        <v>6010000234</v>
+        <v>6010000191</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="D48" s="4">
-        <v>46661</v>
+        <v>388</v>
+      </c>
+      <c r="D48" s="5">
+        <v>46568</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>451</v>
+        <v>389</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>24</v>
+        <v>390</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H48" s="5">
-        <v>340</v>
-      </c>
-      <c r="I48" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="H48" s="6">
+        <v>224</v>
+      </c>
+      <c r="I48" s="4"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B49" s="3">
-        <v>6010000234</v>
+        <v>6010000239</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="D49" s="4">
-        <v>46726</v>
+        <v>448</v>
+      </c>
+      <c r="D49" s="5">
+        <v>46507</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>24</v>
+        <v>390</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H49" s="5">
-        <v>7920</v>
-      </c>
-      <c r="I49" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="H49" s="6">
+        <v>1247</v>
+      </c>
+      <c r="I49" s="4"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B50" s="3">
-        <v>6010000191</v>
+        <v>6010000217</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="D50" s="4">
-        <v>46568</v>
+        <v>428</v>
+      </c>
+      <c r="D50" s="5">
+        <v>46751</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>395</v>
+        <v>429</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>396</v>
+        <v>30</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H50" s="5">
-        <v>324</v>
-      </c>
-      <c r="I50" s="5"/>
+        <v>6</v>
+      </c>
+      <c r="H50" s="6">
+        <v>10</v>
+      </c>
+      <c r="I50" s="4"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B51" s="3">
-        <v>6010000239</v>
+        <v>6010000217</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="D51" s="4">
-        <v>46507</v>
+        <v>428</v>
+      </c>
+      <c r="D51" s="5">
+        <v>46721</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>456</v>
+        <v>430</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>396</v>
+        <v>30</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H51" s="5">
-        <v>1247</v>
-      </c>
-      <c r="I51" s="5"/>
+        <v>6</v>
+      </c>
+      <c r="H51" s="6">
+        <v>310</v>
+      </c>
+      <c r="I51" s="4"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B52" s="3">
-        <v>6010000217</v>
+        <v>6010000071</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="D52" s="4">
-        <v>46751</v>
+        <v>187</v>
+      </c>
+      <c r="D52" s="5">
+        <v>46797</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>436</v>
+        <v>188</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>31</v>
+        <v>189</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H52" s="5">
-        <v>10</v>
-      </c>
-      <c r="I52" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="H52" s="6">
+        <v>9000</v>
+      </c>
+      <c r="I52" s="4"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B53" s="3">
-        <v>6010000217</v>
+        <v>4010013389</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="D53" s="4">
-        <v>46721</v>
+        <v>39</v>
+      </c>
+      <c r="D53" s="5">
+        <v>46621</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>437</v>
+        <v>40</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H53" s="5">
+      <c r="H53" s="6">
         <v>710</v>
       </c>
-      <c r="I53" s="5"/>
+      <c r="I53" s="4"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B54" s="3">
-        <v>6010000071</v>
+        <v>4010013389</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="D54" s="4">
-        <v>46797</v>
+        <v>39</v>
+      </c>
+      <c r="D54" s="5">
+        <v>46681</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>190</v>
+        <v>42</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>191</v>
+        <v>41</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H54" s="5">
-        <v>9000</v>
-      </c>
-      <c r="I54" s="5"/>
+        <v>6</v>
+      </c>
+      <c r="H54" s="6">
+        <v>1120</v>
+      </c>
+      <c r="I54" s="4"/>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B55" s="3">
-        <v>4010013389</v>
+        <v>4010013266</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D55" s="4">
-        <v>46621</v>
+        <v>17</v>
+      </c>
+      <c r="D55" s="5">
+        <v>46575</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H55" s="5">
-        <v>710</v>
-      </c>
-      <c r="I55" s="5"/>
+      <c r="H55" s="6">
+        <v>560</v>
+      </c>
+      <c r="I55" s="4"/>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B56" s="3">
-        <v>4010013389</v>
+        <v>4010013267</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D56" s="4">
-        <v>46681</v>
+        <v>19</v>
+      </c>
+      <c r="D56" s="5">
+        <v>46598</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H56" s="5">
-        <v>1120</v>
-      </c>
-      <c r="I56" s="5"/>
+      <c r="H56" s="6">
+        <v>640</v>
+      </c>
+      <c r="I56" s="4"/>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B57" s="3">
-        <v>4010013266</v>
+        <v>4010013553</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D57" s="4">
+        <v>82</v>
+      </c>
+      <c r="D57" s="5">
         <v>46575</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>19</v>
+        <v>83</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>9</v>
@@ -3470,26 +3458,26 @@
       <c r="G57" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H57" s="5">
-        <v>560</v>
-      </c>
-      <c r="I57" s="5"/>
+      <c r="H57" s="6">
+        <v>880</v>
+      </c>
+      <c r="I57" s="4"/>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B58" s="3">
-        <v>4010013267</v>
+        <v>4010013397</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D58" s="4">
-        <v>46598</v>
+        <v>43</v>
+      </c>
+      <c r="D58" s="5">
+        <v>46545</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>9</v>
@@ -3497,1941 +3485,1941 @@
       <c r="G58" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H58" s="5">
-        <v>640</v>
-      </c>
-      <c r="I58" s="5"/>
+      <c r="H58" s="6">
+        <v>1080</v>
+      </c>
+      <c r="I58" s="4"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B59" s="3">
-        <v>4010013553</v>
+        <v>6010000189</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D59" s="4">
-        <v>46575</v>
+        <v>386</v>
+      </c>
+      <c r="D59" s="5">
+        <v>46539</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>84</v>
+        <v>387</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H59" s="5">
-        <v>880</v>
-      </c>
-      <c r="I59" s="5"/>
+      <c r="H59" s="6">
+        <v>160</v>
+      </c>
+      <c r="I59" s="4"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B60" s="3">
-        <v>4010013397</v>
+        <v>6010000224</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D60" s="4">
-        <v>46545</v>
+        <v>434</v>
+      </c>
+      <c r="D60" s="5">
+        <v>46711</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>45</v>
+        <v>435</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H60" s="5">
-        <v>1080</v>
-      </c>
-      <c r="I60" s="5"/>
+      <c r="H60" s="6">
+        <v>520</v>
+      </c>
+      <c r="I60" s="4"/>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B61" s="3">
-        <v>6010000189</v>
+        <v>6010000101</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="D61" s="4">
+        <v>262</v>
+      </c>
+      <c r="D61" s="5">
         <v>46539</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>393</v>
+        <v>263</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H61" s="5">
-        <v>160</v>
-      </c>
-      <c r="I61" s="5"/>
+      <c r="H61" s="6">
+        <v>290</v>
+      </c>
+      <c r="I61" s="4"/>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B62" s="3">
-        <v>6010000224</v>
+        <v>6010000101</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="D62" s="4">
-        <v>46711</v>
+        <v>262</v>
+      </c>
+      <c r="D62" s="5">
+        <v>46447</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>442</v>
+        <v>264</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H62" s="5">
-        <v>520</v>
-      </c>
-      <c r="I62" s="5"/>
+      <c r="H62" s="6">
+        <v>330</v>
+      </c>
+      <c r="I62" s="4"/>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B63" s="3">
-        <v>6010000101</v>
+        <v>6010000232</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="D63" s="4">
-        <v>46539</v>
+        <v>439</v>
+      </c>
+      <c r="D63" s="5">
+        <v>46692</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>266</v>
+        <v>440</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H63" s="5">
-        <v>290</v>
-      </c>
-      <c r="I63" s="5"/>
+      <c r="H63" s="6">
+        <v>3160</v>
+      </c>
+      <c r="I63" s="4"/>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B64" s="3">
-        <v>6010000101</v>
+        <v>6010000232</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="D64" s="4">
-        <v>46447</v>
+        <v>439</v>
+      </c>
+      <c r="D64" s="5">
+        <v>46726</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>267</v>
+        <v>441</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H64" s="5">
-        <v>330</v>
-      </c>
-      <c r="I64" s="5"/>
+      <c r="H64" s="6">
+        <v>14400</v>
+      </c>
+      <c r="I64" s="4"/>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B65" s="3">
-        <v>6010000232</v>
+        <v>6010000240</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="D65" s="4">
-        <v>46726</v>
+        <v>450</v>
+      </c>
+      <c r="D65" s="5">
+        <v>46527</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>16</v>
+        <v>452</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H65" s="5">
-        <v>14400</v>
-      </c>
-      <c r="I65" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="H65" s="6">
+        <v>72</v>
+      </c>
+      <c r="I65" s="4"/>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B66" s="3">
-        <v>6010000232</v>
+        <v>6010000073</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="D66" s="4">
-        <v>46692</v>
+        <v>190</v>
+      </c>
+      <c r="D66" s="5">
+        <v>46511</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>448</v>
+        <v>191</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>16</v>
+        <v>192</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H66" s="5">
-        <v>3160</v>
-      </c>
-      <c r="I66" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="H66" s="6">
+        <v>1870</v>
+      </c>
+      <c r="I66" s="4"/>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B67" s="3">
-        <v>6010000240</v>
+        <v>6010000169</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="D67" s="4">
-        <v>46527</v>
+        <v>364</v>
+      </c>
+      <c r="D67" s="5">
+        <v>46751</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>458</v>
+        <v>365</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>459</v>
+        <v>116</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H67" s="5">
-        <v>102</v>
-      </c>
-      <c r="I67" s="5"/>
+        <v>6</v>
+      </c>
+      <c r="H67" s="6">
+        <v>2110</v>
+      </c>
+      <c r="I67" s="4"/>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B68" s="3">
-        <v>6010000073</v>
+        <v>6010000170</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="D68" s="4">
-        <v>46511</v>
+        <v>366</v>
+      </c>
+      <c r="D68" s="5">
+        <v>46721</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>193</v>
+        <v>367</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>194</v>
+        <v>116</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H68" s="5">
-        <v>1870</v>
-      </c>
-      <c r="I68" s="5"/>
+        <v>6</v>
+      </c>
+      <c r="H68" s="6">
+        <v>2590</v>
+      </c>
+      <c r="I68" s="4"/>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B69" s="3">
-        <v>6010000169</v>
+        <v>6010000139</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="D69" s="4">
-        <v>46751</v>
+        <v>323</v>
+      </c>
+      <c r="D69" s="5">
+        <v>46711</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>371</v>
+        <v>324</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>118</v>
+        <v>325</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H69" s="5">
-        <v>2110</v>
-      </c>
-      <c r="I69" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="H69" s="6">
+        <v>1488</v>
+      </c>
+      <c r="I69" s="4"/>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B70" s="3">
-        <v>6010000170</v>
+        <v>6010000141</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="D70" s="4">
-        <v>46721</v>
+        <v>326</v>
+      </c>
+      <c r="D70" s="5">
+        <v>46746</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>373</v>
+        <v>327</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>118</v>
+        <v>325</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H70" s="5">
-        <v>2590</v>
-      </c>
-      <c r="I70" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="H70" s="6">
+        <v>2425</v>
+      </c>
+      <c r="I70" s="4"/>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B71" s="3">
-        <v>6010000139</v>
+        <v>6010000205</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="D71" s="4">
-        <v>46711</v>
+        <v>418</v>
+      </c>
+      <c r="D71" s="5">
+        <v>46692</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>327</v>
+        <v>419</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>328</v>
+        <v>420</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H71" s="5">
-        <v>1488</v>
-      </c>
-      <c r="I71" s="5"/>
+      <c r="H71" s="6">
+        <v>16950</v>
+      </c>
+      <c r="I71" s="4"/>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B72" s="3">
-        <v>6010000141</v>
+        <v>4010013583</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="D72" s="4">
-        <v>46746</v>
+        <v>101</v>
+      </c>
+      <c r="D72" s="5">
+        <v>46504</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>330</v>
+        <v>102</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>328</v>
+        <v>74</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H72" s="5">
-        <v>2665</v>
-      </c>
-      <c r="I72" s="5"/>
+        <v>6</v>
+      </c>
+      <c r="H72" s="6">
+        <v>620</v>
+      </c>
+      <c r="I72" s="4"/>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B73" s="3">
-        <v>6010000205</v>
+        <v>6010000074</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="D73" s="4">
-        <v>46692</v>
+        <v>193</v>
+      </c>
+      <c r="D73" s="5">
+        <v>46721</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>425</v>
+        <v>194</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>426</v>
+        <v>195</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H73" s="5">
-        <v>18900</v>
-      </c>
-      <c r="I73" s="5"/>
+      <c r="H73" s="6">
+        <v>1920</v>
+      </c>
+      <c r="I73" s="4"/>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B74" s="3">
-        <v>4010013583</v>
+        <v>6010000074</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D74" s="4">
-        <v>46504</v>
+        <v>193</v>
+      </c>
+      <c r="D74" s="5">
+        <v>46721</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>103</v>
+        <v>196</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>75</v>
+        <v>195</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H74" s="5">
-        <v>620</v>
-      </c>
-      <c r="I74" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="H74" s="6">
+        <v>3456</v>
+      </c>
+      <c r="I74" s="4"/>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B75" s="3">
-        <v>6010000074</v>
+        <v>6010000102</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="D75" s="4">
-        <v>46721</v>
+        <v>265</v>
+      </c>
+      <c r="D75" s="5">
+        <v>46631</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>196</v>
+        <v>266</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>197</v>
+        <v>23</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H75" s="5">
-        <v>3456</v>
-      </c>
-      <c r="I75" s="5"/>
+        <v>6</v>
+      </c>
+      <c r="H75" s="6">
+        <v>1160</v>
+      </c>
+      <c r="I75" s="4"/>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B76" s="3">
-        <v>6010000074</v>
+        <v>6010000102</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="D76" s="4">
-        <v>46721</v>
+        <v>265</v>
+      </c>
+      <c r="D76" s="5">
+        <v>46780</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>198</v>
+        <v>267</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>197</v>
+        <v>23</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H76" s="5">
-        <v>3072</v>
-      </c>
-      <c r="I76" s="5"/>
+        <v>6</v>
+      </c>
+      <c r="H76" s="6">
+        <v>3200</v>
+      </c>
+      <c r="I76" s="4"/>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B77" s="3">
-        <v>6010000102</v>
+        <v>6010000103</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="D77" s="4">
-        <v>46631</v>
+      <c r="D77" s="5">
+        <v>46645</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>269</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H77" s="5">
-        <v>3160</v>
-      </c>
-      <c r="I77" s="5"/>
+      <c r="H77" s="6">
+        <v>3320</v>
+      </c>
+      <c r="I77" s="4"/>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B78" s="3">
-        <v>6010000102</v>
+        <v>6010000196</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="D78" s="4">
-        <v>46780</v>
+        <v>401</v>
+      </c>
+      <c r="D78" s="5">
+        <v>46606</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>270</v>
+        <v>402</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>24</v>
+        <v>403</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H78" s="5">
-        <v>3200</v>
-      </c>
-      <c r="I78" s="5"/>
+      <c r="H78" s="6">
+        <v>1840</v>
+      </c>
+      <c r="I78" s="4"/>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B79" s="3">
-        <v>6010000103</v>
+        <v>6010000104</v>
       </c>
       <c r="C79" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D79" s="5">
+        <v>46429</v>
+      </c>
+      <c r="E79" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="D79" s="4">
-        <v>46645</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>272</v>
-      </c>
       <c r="F79" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H79" s="5">
-        <v>3320</v>
-      </c>
-      <c r="I79" s="5"/>
+      <c r="H79" s="6">
+        <v>100</v>
+      </c>
+      <c r="I79" s="4"/>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B80" s="3">
-        <v>6010000196</v>
+        <v>4010013473</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="D80" s="4">
-        <v>46606</v>
+        <v>53</v>
+      </c>
+      <c r="D80" s="5">
+        <v>46524</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>408</v>
+        <v>54</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>409</v>
+        <v>30</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H80" s="5">
-        <v>1840</v>
-      </c>
-      <c r="I80" s="5"/>
+      <c r="H80" s="6">
+        <v>430</v>
+      </c>
+      <c r="I80" s="4"/>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B81" s="3">
-        <v>6010000104</v>
+        <v>6010000151</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="D81" s="4">
-        <v>46429</v>
+        <v>343</v>
+      </c>
+      <c r="D81" s="5">
+        <v>46692</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>274</v>
+        <v>344</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>24</v>
+        <v>345</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H81" s="5">
-        <v>100</v>
-      </c>
-      <c r="I81" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="H81" s="6">
+        <v>1112</v>
+      </c>
+      <c r="I81" s="4"/>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B82" s="3">
-        <v>4010013473</v>
+        <v>6010000241</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D82" s="4">
-        <v>46524</v>
+        <v>453</v>
+      </c>
+      <c r="D82" s="5">
+        <v>46596</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>55</v>
+        <v>454</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>31</v>
+        <v>452</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H82" s="5">
-        <v>430</v>
-      </c>
-      <c r="I82" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="H82" s="6">
+        <v>162</v>
+      </c>
+      <c r="I82" s="4"/>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B83" s="3">
-        <v>6010000151</v>
+        <v>6010000194</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="D83" s="4">
-        <v>46692</v>
+        <v>396</v>
+      </c>
+      <c r="D83" s="5">
+        <v>46803</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>348</v>
+        <v>397</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>349</v>
+        <v>30</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H83" s="5">
-        <v>1112</v>
-      </c>
-      <c r="I83" s="5"/>
+        <v>6</v>
+      </c>
+      <c r="H83" s="6">
+        <v>1470</v>
+      </c>
+      <c r="I83" s="4"/>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B84" s="3">
-        <v>6010000241</v>
+        <v>6010000194</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="D84" s="4">
-        <v>46596</v>
+        <v>396</v>
+      </c>
+      <c r="D84" s="5">
+        <v>46721</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>461</v>
+        <v>398</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>459</v>
+        <v>30</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H84" s="5">
-        <v>162</v>
-      </c>
-      <c r="I84" s="5"/>
+        <v>6</v>
+      </c>
+      <c r="H84" s="6">
+        <v>4760</v>
+      </c>
+      <c r="I84" s="4"/>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B85" s="3">
-        <v>6010000194</v>
+        <v>6010000192</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="D85" s="4">
-        <v>46803</v>
+        <v>391</v>
+      </c>
+      <c r="D85" s="5">
+        <v>46367</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>31</v>
+        <v>390</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H85" s="5">
-        <v>1470</v>
-      </c>
-      <c r="I85" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="H85" s="6">
+        <v>365</v>
+      </c>
+      <c r="I85" s="4"/>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B86" s="3">
-        <v>6010000194</v>
+        <v>6010000155</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="D86" s="4">
-        <v>46721</v>
+        <v>349</v>
+      </c>
+      <c r="D86" s="5">
+        <v>46447</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>404</v>
+        <v>350</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H86" s="5">
-        <v>5360</v>
-      </c>
-      <c r="I86" s="5"/>
+      <c r="H86" s="6">
+        <v>400</v>
+      </c>
+      <c r="I86" s="4"/>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B87" s="3">
-        <v>6010000192</v>
+        <v>6010000108</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="D87" s="4">
-        <v>46367</v>
+        <v>272</v>
+      </c>
+      <c r="D87" s="5">
+        <v>46574</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>398</v>
+        <v>273</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>396</v>
+        <v>16</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H87" s="5">
-        <v>365</v>
-      </c>
-      <c r="I87" s="5"/>
+        <v>6</v>
+      </c>
+      <c r="H87" s="6">
+        <v>560</v>
+      </c>
+      <c r="I87" s="4"/>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B88" s="3">
-        <v>6010000155</v>
+        <v>6010000193</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="D88" s="4">
-        <v>46447</v>
+        <v>393</v>
+      </c>
+      <c r="D88" s="5">
+        <v>46711</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>354</v>
+        <v>394</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H88" s="5">
-        <v>400</v>
-      </c>
-      <c r="I88" s="5"/>
+      <c r="H88" s="6">
+        <v>270</v>
+      </c>
+      <c r="I88" s="4"/>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B89" s="3">
-        <v>6010000108</v>
+        <v>6010000193</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D89" s="4">
-        <v>46574</v>
+        <v>393</v>
+      </c>
+      <c r="D89" s="5">
+        <v>46726</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>276</v>
+        <v>395</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H89" s="5">
-        <v>660</v>
-      </c>
-      <c r="I89" s="5"/>
+      <c r="H89" s="6">
+        <v>80</v>
+      </c>
+      <c r="I89" s="4"/>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B90" s="3">
-        <v>6010000193</v>
+        <v>6010000216</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="D90" s="4">
-        <v>46711</v>
+        <v>426</v>
+      </c>
+      <c r="D90" s="5">
+        <v>46690</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>400</v>
+        <v>427</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H90" s="5">
-        <v>270</v>
-      </c>
-      <c r="I90" s="5"/>
+      <c r="H90" s="6">
+        <v>170</v>
+      </c>
+      <c r="I90" s="4"/>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B91" s="3">
-        <v>6010000193</v>
+        <v>6010000235</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="D91" s="4">
-        <v>46726</v>
+        <v>446</v>
+      </c>
+      <c r="D91" s="5">
+        <v>46808</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>401</v>
+        <v>447</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H91" s="5">
-        <v>80</v>
-      </c>
-      <c r="I91" s="5"/>
+      <c r="H91" s="6">
+        <v>3340</v>
+      </c>
+      <c r="I91" s="4"/>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B92" s="3">
-        <v>6010000216</v>
+        <v>4010013662</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="D92" s="4">
-        <v>46690</v>
+        <v>145</v>
+      </c>
+      <c r="D92" s="5">
+        <v>46546</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>434</v>
+        <v>146</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H92" s="5">
-        <v>170</v>
-      </c>
-      <c r="I92" s="5"/>
+      <c r="H92" s="6">
+        <v>420</v>
+      </c>
+      <c r="I92" s="4"/>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B93" s="3">
-        <v>6010000235</v>
+        <v>4010013662</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="D93" s="4">
-        <v>46808</v>
+        <v>145</v>
+      </c>
+      <c r="D93" s="5">
+        <v>46537</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>454</v>
+        <v>147</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H93" s="5">
-        <v>3800</v>
-      </c>
-      <c r="I93" s="5"/>
+      <c r="H93" s="6">
+        <v>330</v>
+      </c>
+      <c r="I93" s="4"/>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B94" s="3">
-        <v>4010013662</v>
+        <v>6010000076</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="D94" s="4">
-        <v>46546</v>
+        <v>197</v>
+      </c>
+      <c r="D94" s="5">
+        <v>46483</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>148</v>
+        <v>198</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>31</v>
+        <v>195</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H94" s="5">
-        <v>420</v>
-      </c>
-      <c r="I94" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="H94" s="6">
+        <v>3556</v>
+      </c>
+      <c r="I94" s="4"/>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B95" s="3">
-        <v>4010013662</v>
+        <v>6010000076</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="D95" s="4">
-        <v>46537</v>
+        <v>197</v>
+      </c>
+      <c r="D95" s="5">
+        <v>46415</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>149</v>
+        <v>199</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>31</v>
+        <v>195</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H95" s="5">
-        <v>330</v>
-      </c>
-      <c r="I95" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="H95" s="6">
+        <v>1152</v>
+      </c>
+      <c r="I95" s="4"/>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B96" s="3">
-        <v>6010000076</v>
+        <v>6010000110</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="D96" s="4">
-        <v>46483</v>
+        <v>274</v>
+      </c>
+      <c r="D96" s="5">
+        <v>46640</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>200</v>
+        <v>275</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>197</v>
+        <v>5</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H96" s="5">
-        <v>3556</v>
-      </c>
-      <c r="I96" s="5"/>
+        <v>6</v>
+      </c>
+      <c r="H96" s="6">
+        <v>1100</v>
+      </c>
+      <c r="I96" s="4"/>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B97" s="3">
-        <v>6010000076</v>
+        <v>6010000111</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="D97" s="4">
-        <v>46415</v>
+        <v>276</v>
+      </c>
+      <c r="D97" s="5">
+        <v>46640</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>201</v>
+        <v>277</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>197</v>
+        <v>5</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H97" s="5">
-        <v>1152</v>
-      </c>
-      <c r="I97" s="5"/>
+        <v>6</v>
+      </c>
+      <c r="H97" s="6">
+        <v>2640</v>
+      </c>
+      <c r="I97" s="4"/>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B98" s="3">
-        <v>6010000110</v>
+        <v>4010013584</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="D98" s="4">
-        <v>46640</v>
+        <v>103</v>
+      </c>
+      <c r="D98" s="5">
+        <v>46532</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>278</v>
+        <v>104</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>5</v>
+        <v>92</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H98" s="5">
-        <v>1100</v>
-      </c>
-      <c r="I98" s="5"/>
+      <c r="H98" s="6">
+        <v>500</v>
+      </c>
+      <c r="I98" s="4"/>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B99" s="3">
-        <v>6010000111</v>
+        <v>4010013584</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D99" s="4">
-        <v>46640</v>
+        <v>103</v>
+      </c>
+      <c r="D99" s="5">
+        <v>46537</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>280</v>
+        <v>105</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>5</v>
+        <v>92</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H99" s="5">
-        <v>2640</v>
-      </c>
-      <c r="I99" s="5"/>
+      <c r="H99" s="6">
+        <v>380</v>
+      </c>
+      <c r="I99" s="4"/>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B100" s="3">
-        <v>4010013584</v>
+        <v>6010000171</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D100" s="4">
-        <v>46537</v>
+        <v>368</v>
+      </c>
+      <c r="D100" s="5">
+        <v>46579</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>105</v>
+        <v>369</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H100" s="5">
-        <v>380</v>
-      </c>
-      <c r="I100" s="5"/>
+      <c r="H100" s="6">
+        <v>1500</v>
+      </c>
+      <c r="I100" s="4"/>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B101" s="3">
-        <v>4010013584</v>
+        <v>4010013585</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D101" s="4">
-        <v>46532</v>
+        <v>106</v>
+      </c>
+      <c r="D101" s="5">
+        <v>46568</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H101" s="5">
-        <v>700</v>
-      </c>
-      <c r="I101" s="5"/>
+      <c r="H101" s="6">
+        <v>1500</v>
+      </c>
+      <c r="I101" s="4"/>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B102" s="3">
-        <v>6010000171</v>
+        <v>6010000172</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="D102" s="4">
+        <v>370</v>
+      </c>
+      <c r="D102" s="5">
         <v>46579</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H102" s="5">
-        <v>1500</v>
-      </c>
-      <c r="I102" s="5"/>
+      <c r="H102" s="6">
+        <v>1700</v>
+      </c>
+      <c r="I102" s="4"/>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B103" s="3">
-        <v>4010013585</v>
+        <v>6010000077</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D103" s="4">
-        <v>46568</v>
+        <v>200</v>
+      </c>
+      <c r="D103" s="5">
+        <v>46471</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>108</v>
+        <v>201</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>93</v>
+        <v>202</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H103" s="5">
-        <v>1500</v>
-      </c>
-      <c r="I103" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="H103" s="6">
+        <v>6130</v>
+      </c>
+      <c r="I103" s="4"/>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B104" s="3">
-        <v>6010000172</v>
+        <v>6010000078</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="D104" s="4">
-        <v>46579</v>
+        <v>203</v>
+      </c>
+      <c r="D104" s="5">
+        <v>46780</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>377</v>
+        <v>204</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>93</v>
+        <v>205</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H104" s="5">
-        <v>1700</v>
-      </c>
-      <c r="I104" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="H104" s="6">
+        <v>12750</v>
+      </c>
+      <c r="I104" s="4"/>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B105" s="3">
-        <v>6010000077</v>
+        <v>6010000079</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="D105" s="4">
-        <v>46471</v>
+        <v>206</v>
+      </c>
+      <c r="D105" s="5">
+        <v>46512</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H105" s="5">
-        <v>6180</v>
-      </c>
-      <c r="I105" s="5"/>
+      <c r="H105" s="6">
+        <v>720</v>
+      </c>
+      <c r="I105" s="4"/>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B106" s="3">
-        <v>6010000078</v>
+        <v>4010013593</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="D106" s="4">
-        <v>46780</v>
+        <v>117</v>
+      </c>
+      <c r="D106" s="5">
+        <v>46526</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>206</v>
+        <v>118</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>207</v>
+        <v>30</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H106" s="5">
-        <v>12850</v>
-      </c>
-      <c r="I106" s="5"/>
+        <v>6</v>
+      </c>
+      <c r="H106" s="6">
+        <v>260</v>
+      </c>
+      <c r="I106" s="4"/>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B107" s="3">
-        <v>6010000079</v>
+        <v>4010013593</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="D107" s="4">
-        <v>46512</v>
+        <v>117</v>
+      </c>
+      <c r="D107" s="5">
+        <v>46758</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>209</v>
+        <v>119</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>210</v>
+        <v>30</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H107" s="5">
-        <v>760</v>
-      </c>
-      <c r="I107" s="5"/>
+        <v>6</v>
+      </c>
+      <c r="H107" s="6">
+        <v>560</v>
+      </c>
+      <c r="I107" s="4"/>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B108" s="3">
-        <v>4010013593</v>
+        <v>4010014329</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="D108" s="4">
-        <v>46526</v>
+        <v>170</v>
+      </c>
+      <c r="D108" s="5">
+        <v>46641</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>120</v>
+        <v>171</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H108" s="5">
-        <v>260</v>
-      </c>
-      <c r="I108" s="5"/>
+      <c r="H108" s="6">
+        <v>230</v>
+      </c>
+      <c r="I108" s="4"/>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B109" s="3">
-        <v>4010013593</v>
+        <v>4010013594</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="D109" s="4">
-        <v>46758</v>
+        <v>120</v>
+      </c>
+      <c r="D109" s="5">
+        <v>46573</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>121</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H109" s="5">
-        <v>560</v>
-      </c>
-      <c r="I109" s="5"/>
+      <c r="H109" s="6">
+        <v>1250</v>
+      </c>
+      <c r="I109" s="4"/>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B110" s="3">
-        <v>4010014329</v>
+        <v>4010014330</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="D110" s="4">
-        <v>46641</v>
+      <c r="D110" s="5">
+        <v>46610</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>173</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G110" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H110" s="5">
-        <v>230</v>
-      </c>
-      <c r="I110" s="5"/>
+      <c r="H110" s="6">
+        <v>280</v>
+      </c>
+      <c r="I110" s="4"/>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B111" s="3">
-        <v>4010013594</v>
+        <v>6010000156</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D111" s="4">
-        <v>46573</v>
+        <v>351</v>
+      </c>
+      <c r="D111" s="5">
+        <v>46447</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>123</v>
+        <v>352</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H111" s="5">
-        <v>1550</v>
-      </c>
-      <c r="I111" s="5"/>
+      <c r="H111" s="6">
+        <v>300</v>
+      </c>
+      <c r="I111" s="4"/>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B112" s="3">
-        <v>4010014330</v>
+        <v>6010000233</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="D112" s="4">
-        <v>46610</v>
+        <v>351</v>
+      </c>
+      <c r="D112" s="5">
+        <v>46721</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>175</v>
+        <v>442</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H112" s="5">
-        <v>280</v>
-      </c>
-      <c r="I112" s="5"/>
+      <c r="H112" s="6">
+        <v>770</v>
+      </c>
+      <c r="I112" s="4"/>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B113" s="3">
-        <v>6010000156</v>
+        <v>6010000080</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="D113" s="4">
-        <v>46447</v>
+        <v>209</v>
+      </c>
+      <c r="D113" s="5">
+        <v>46423</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>356</v>
+        <v>210</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>31</v>
+        <v>211</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H113" s="5">
-        <v>300</v>
-      </c>
-      <c r="I113" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="H113" s="6">
+        <v>500</v>
+      </c>
+      <c r="I113" s="4"/>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B114" s="3">
-        <v>6010000233</v>
+        <v>6010000113</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="D114" s="4">
-        <v>46721</v>
+        <v>278</v>
+      </c>
+      <c r="D114" s="5">
+        <v>46598</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>449</v>
+        <v>279</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="G114" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H114" s="5">
-        <v>920</v>
-      </c>
-      <c r="I114" s="5"/>
+      <c r="H114" s="6">
+        <v>8740</v>
+      </c>
+      <c r="I114" s="4"/>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B115" s="3">
-        <v>6010000080</v>
+        <v>4010013656</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="D115" s="4">
+        <v>132</v>
+      </c>
+      <c r="D115" s="5">
         <v>46423</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>212</v>
+        <v>133</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>213</v>
+        <v>134</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H115" s="5">
-        <v>500</v>
-      </c>
-      <c r="I115" s="5"/>
+        <v>6</v>
+      </c>
+      <c r="H115" s="6">
+        <v>240</v>
+      </c>
+      <c r="I115" s="4"/>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B116" s="3">
-        <v>6010000113</v>
+        <v>4010013656</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="D116" s="4">
-        <v>46598</v>
+        <v>132</v>
+      </c>
+      <c r="D116" s="5">
+        <v>46510</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>282</v>
+        <v>135</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>24</v>
+        <v>134</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H116" s="5">
-        <v>9540</v>
-      </c>
-      <c r="I116" s="5"/>
+      <c r="H116" s="6">
+        <v>2380</v>
+      </c>
+      <c r="I116" s="4"/>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B117" s="3">
-        <v>4010013656</v>
-      </c>
-      <c r="C117" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="D117" s="4">
-        <v>46510</v>
-      </c>
-      <c r="E117" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F117" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="G117" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H117" s="5">
-        <v>2380</v>
-      </c>
-      <c r="I117" s="5"/>
+      <c r="B117" s="9">
+        <v>4010013595</v>
+      </c>
+      <c r="C117" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="D117" s="11"/>
+      <c r="E117" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="F117" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G117" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="H117" s="12"/>
+      <c r="I117" s="13">
+        <v>300</v>
+      </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B118" s="3">
-        <v>4010013656</v>
+        <v>6010000174</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="D118" s="4">
-        <v>46423</v>
+        <v>372</v>
+      </c>
+      <c r="D118" s="5">
+        <v>46586</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>137</v>
+        <v>373</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>136</v>
+        <v>374</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H118" s="5">
-        <v>240</v>
-      </c>
-      <c r="I118" s="5"/>
+      <c r="H118" s="6">
+        <v>1160</v>
+      </c>
+      <c r="I118" s="4"/>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B119" s="8">
-        <v>4010013595</v>
-      </c>
-      <c r="C119" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="D119" s="10"/>
-      <c r="E119" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="F119" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="G119" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="H119" s="11"/>
-      <c r="I119" s="11">
-        <v>300</v>
-      </c>
+      <c r="B119" s="3">
+        <v>6010000114</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D119" s="5">
+        <v>46488</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="F119" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G119" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H119" s="6">
+        <v>2000</v>
+      </c>
+      <c r="I119" s="4"/>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B120" s="3">
-        <v>6010000174</v>
+        <v>6010000081</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="D120" s="4">
-        <v>46586</v>
+        <v>212</v>
+      </c>
+      <c r="D120" s="5">
+        <v>46660</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>379</v>
+        <v>213</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>380</v>
+        <v>3</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H120" s="5">
-        <v>1160</v>
-      </c>
-      <c r="I120" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="H120" s="6">
+        <v>750</v>
+      </c>
+      <c r="I120" s="4"/>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B121" s="3">
-        <v>6010000114</v>
+        <v>6010000082</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="D121" s="4">
-        <v>46488</v>
+        <v>214</v>
+      </c>
+      <c r="D121" s="5">
+        <v>46505</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>284</v>
+        <v>215</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>118</v>
+        <v>216</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H121" s="5">
-        <v>2000</v>
-      </c>
-      <c r="I121" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="H121" s="6">
+        <v>13300</v>
+      </c>
+      <c r="I121" s="4"/>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B122" s="3">
-        <v>6010000081</v>
+        <v>6010000175</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="D122" s="4">
-        <v>46660</v>
+        <v>375</v>
+      </c>
+      <c r="D122" s="5">
+        <v>46556</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>215</v>
+        <v>376</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>3</v>
+        <v>377</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H122" s="5">
-        <v>750</v>
-      </c>
-      <c r="I122" s="5"/>
+        <v>6</v>
+      </c>
+      <c r="H122" s="6">
+        <v>1900</v>
+      </c>
+      <c r="I122" s="4"/>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B123" s="3">
-        <v>6010000082</v>
+        <v>6010000176</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="D123" s="4">
-        <v>46505</v>
+        <v>378</v>
+      </c>
+      <c r="D123" s="5">
+        <v>46586</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>217</v>
+        <v>379</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>218</v>
+        <v>377</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H123" s="5">
-        <v>13800</v>
-      </c>
-      <c r="I123" s="5"/>
+        <v>6</v>
+      </c>
+      <c r="H123" s="6">
+        <v>1980</v>
+      </c>
+      <c r="I123" s="4"/>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B124" s="3">
-        <v>6010000175</v>
+        <v>6010000201</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="D124" s="4">
-        <v>46556</v>
+        <v>411</v>
+      </c>
+      <c r="D124" s="5">
+        <v>46624</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>382</v>
+        <v>412</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>383</v>
+        <v>413</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H124" s="5">
-        <v>1900</v>
-      </c>
-      <c r="I124" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="H124" s="6">
+        <v>910</v>
+      </c>
+      <c r="I124" s="4"/>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B125" s="3">
-        <v>6010000176</v>
+        <v>6010000202</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="D125" s="4">
-        <v>46586</v>
+        <v>414</v>
+      </c>
+      <c r="D125" s="5">
+        <v>46685</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>385</v>
+        <v>415</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>383</v>
+        <v>413</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H125" s="5">
-        <v>1980</v>
-      </c>
-      <c r="I125" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="H125" s="6">
+        <v>830</v>
+      </c>
+      <c r="I125" s="4"/>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B126" s="3">
-        <v>6010000201</v>
+        <v>4010013262</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="D126" s="4">
-        <v>46624</v>
+        <v>14</v>
+      </c>
+      <c r="D126" s="5">
+        <v>46549</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>418</v>
+        <v>15</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H126" s="5">
-        <v>910</v>
-      </c>
-      <c r="I126" s="5"/>
+        <v>6</v>
+      </c>
+      <c r="H126" s="6">
+        <v>520</v>
+      </c>
+      <c r="I126" s="4"/>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B127" s="3">
-        <v>6010000202</v>
+        <v>4010013465</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="D127" s="4">
-        <v>46685</v>
+        <v>47</v>
+      </c>
+      <c r="D127" s="5">
+        <v>46637</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>421</v>
+        <v>48</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>419</v>
+        <v>16</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H127" s="5">
-        <v>830</v>
-      </c>
-      <c r="I127" s="5"/>
+        <v>6</v>
+      </c>
+      <c r="H127" s="6">
+        <v>2320</v>
+      </c>
+      <c r="I127" s="4"/>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B128" s="3">
-        <v>4010013262</v>
+        <v>4010013466</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D128" s="4">
-        <v>46549</v>
+        <v>49</v>
+      </c>
+      <c r="D128" s="5">
+        <v>46704</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H128" s="5">
-        <v>520</v>
-      </c>
-      <c r="I128" s="5"/>
+      <c r="H128" s="6">
+        <v>120</v>
+      </c>
+      <c r="I128" s="4"/>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B129" s="3">
-        <v>4010013262</v>
+        <v>4010013466</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D129" s="4">
-        <v>46475</v>
+        <v>49</v>
+      </c>
+      <c r="D129" s="5">
+        <v>46388</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="G129" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H129" s="5">
-        <v>20</v>
-      </c>
-      <c r="I129" s="5"/>
+      <c r="H129" s="6">
+        <v>200</v>
+      </c>
+      <c r="I129" s="4"/>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B130" s="3">
-        <v>4010013465</v>
+        <v>4010013671</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D130" s="4">
-        <v>46637</v>
+        <v>154</v>
+      </c>
+      <c r="D130" s="5">
+        <v>46566</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>49</v>
+        <v>155</v>
       </c>
       <c r="F130" s="2" t="s">
         <v>16</v>
@@ -5439,437 +5427,435 @@
       <c r="G130" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H130" s="5">
-        <v>3020</v>
-      </c>
-      <c r="I130" s="5"/>
+      <c r="H130" s="6">
+        <v>1640</v>
+      </c>
+      <c r="I130" s="4"/>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B131" s="3">
-        <v>4010013466</v>
+        <v>6010000252</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D131" s="4">
-        <v>46388</v>
+        <v>459</v>
+      </c>
+      <c r="D131" s="5">
+        <v>46780</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>51</v>
+        <v>460</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>52</v>
+        <v>461</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H131" s="5">
-        <v>200</v>
-      </c>
-      <c r="I131" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="H131" s="6">
+        <v>1500</v>
+      </c>
+      <c r="I131" s="4"/>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B132" s="3">
-        <v>4010013466</v>
+        <v>6010000252</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D132" s="4">
-        <v>46704</v>
+        <v>459</v>
+      </c>
+      <c r="D132" s="5">
+        <v>46661</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>53</v>
+        <v>462</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>52</v>
+        <v>461</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H132" s="5">
-        <v>120</v>
-      </c>
-      <c r="I132" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="H132" s="6">
+        <v>890</v>
+      </c>
+      <c r="I132" s="4"/>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B133" s="3">
-        <v>4010013671</v>
+        <v>6010000218</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="D133" s="4">
-        <v>46566</v>
+        <v>431</v>
+      </c>
+      <c r="D133" s="5">
+        <v>46780</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>157</v>
+        <v>432</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>16</v>
+        <v>433</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H133" s="5">
-        <v>1640</v>
-      </c>
-      <c r="I133" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="H133" s="6">
+        <v>2000</v>
+      </c>
+      <c r="I133" s="4"/>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B134" s="3">
-        <v>6010000252</v>
+        <v>6010000083</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="D134" s="4">
-        <v>46780</v>
+        <v>217</v>
+      </c>
+      <c r="D134" s="5">
+        <v>46537</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>467</v>
+        <v>218</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>468</v>
+        <v>219</v>
       </c>
       <c r="G134" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H134" s="5">
-        <v>1500</v>
-      </c>
-      <c r="I134" s="5"/>
+      <c r="H134" s="6">
+        <v>800</v>
+      </c>
+      <c r="I134" s="4"/>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B135" s="3">
-        <v>6010000252</v>
+        <v>6010000084</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="D135" s="4">
-        <v>46661</v>
+        <v>220</v>
+      </c>
+      <c r="D135" s="5">
+        <v>46711</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>469</v>
+        <v>221</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>468</v>
+        <v>222</v>
       </c>
       <c r="G135" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H135" s="5">
-        <v>890</v>
-      </c>
-      <c r="I135" s="5"/>
+      <c r="H135" s="6">
+        <v>6220</v>
+      </c>
+      <c r="I135" s="4"/>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B136" s="3">
-        <v>6010000218</v>
+        <v>6010000115</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="D136" s="4">
-        <v>46780</v>
+        <v>282</v>
+      </c>
+      <c r="D136" s="5">
+        <v>46971</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>439</v>
+        <v>283</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>440</v>
+        <v>23</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H136" s="5">
-        <v>2000</v>
-      </c>
-      <c r="I136" s="5"/>
+        <v>6</v>
+      </c>
+      <c r="H136" s="6">
+        <v>2400</v>
+      </c>
+      <c r="I136" s="4"/>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B137" s="3">
-        <v>6010000083</v>
+        <v>6010000116</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="D137" s="4">
-        <v>46537</v>
+        <v>284</v>
+      </c>
+      <c r="D137" s="5">
+        <v>46971</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>220</v>
+        <v>285</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>221</v>
+        <v>5</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H137" s="5">
-        <v>1100</v>
-      </c>
-      <c r="I137" s="5"/>
+        <v>6</v>
+      </c>
+      <c r="H137" s="6">
+        <v>4480</v>
+      </c>
+      <c r="I137" s="4"/>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B138" s="3">
-        <v>6010000084</v>
+        <v>7050000019</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="D138" s="4">
-        <v>46711</v>
-      </c>
+        <v>469</v>
+      </c>
+      <c r="D138" s="5"/>
       <c r="E138" s="2" t="s">
-        <v>223</v>
+        <v>3</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>224</v>
+        <v>3</v>
       </c>
       <c r="G138" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H138" s="5">
-        <v>6220</v>
-      </c>
-      <c r="I138" s="5"/>
+      <c r="H138" s="6">
+        <v>530</v>
+      </c>
+      <c r="I138" s="4"/>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B139" s="3">
-        <v>6010000115</v>
+        <v>6010000117</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="D139" s="4">
-        <v>46971</v>
+        <v>286</v>
+      </c>
+      <c r="D139" s="5">
+        <v>46711</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G139" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H139" s="5">
-        <v>2400</v>
-      </c>
-      <c r="I139" s="5"/>
+      <c r="H139" s="6">
+        <v>6100</v>
+      </c>
+      <c r="I139" s="4"/>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B140" s="3">
-        <v>6010000116</v>
+        <v>6010000118</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="D140" s="4">
-        <v>46971</v>
+        <v>288</v>
+      </c>
+      <c r="D140" s="5">
+        <v>46574</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="G140" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H140" s="5">
-        <v>4480</v>
-      </c>
-      <c r="I140" s="5"/>
+      <c r="H140" s="6">
+        <v>10640</v>
+      </c>
+      <c r="I140" s="4"/>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B141" s="3">
-        <v>7050000019</v>
+        <v>6010000148</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="D141" s="4"/>
+        <v>341</v>
+      </c>
+      <c r="D141" s="5">
+        <v>46751</v>
+      </c>
       <c r="E141" s="2" t="s">
-        <v>3</v>
+        <v>342</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H141" s="5">
-        <v>530</v>
-      </c>
-      <c r="I141" s="5"/>
+        <v>6</v>
+      </c>
+      <c r="H141" s="6">
+        <v>2520</v>
+      </c>
+      <c r="I141" s="4"/>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B142" s="3">
-        <v>6010000117</v>
-      </c>
-      <c r="C142" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="D142" s="4">
-        <v>46711</v>
-      </c>
-      <c r="E142" s="2" t="s">
+      <c r="B142" s="9">
+        <v>6010000119</v>
+      </c>
+      <c r="C142" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="F142" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G142" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H142" s="5">
-        <v>6100</v>
-      </c>
-      <c r="I142" s="5"/>
+      <c r="D142" s="11"/>
+      <c r="E142" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="F142" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="G142" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="H142" s="12"/>
+      <c r="I142" s="13">
+        <v>300</v>
+      </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B143" s="3">
-        <v>6010000118</v>
+        <v>6010000085</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="D143" s="4">
-        <v>46574</v>
+        <v>223</v>
+      </c>
+      <c r="D143" s="5">
+        <v>46388</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>292</v>
+        <v>224</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>24</v>
+        <v>225</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H143" s="5">
-        <v>10640</v>
-      </c>
-      <c r="I143" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="H143" s="6">
+        <v>31500</v>
+      </c>
+      <c r="I143" s="4"/>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B144" s="3">
-        <v>6010000148</v>
+        <v>6010000123</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="D144" s="4">
-        <v>46751</v>
+        <v>292</v>
+      </c>
+      <c r="D144" s="5">
+        <v>46692</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>345</v>
+        <v>293</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>24</v>
+        <v>92</v>
       </c>
       <c r="G144" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H144" s="5">
-        <v>2520</v>
-      </c>
-      <c r="I144" s="5"/>
+      <c r="H144" s="6">
+        <v>420</v>
+      </c>
+      <c r="I144" s="4"/>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B145" s="3">
-        <v>6010000148</v>
+        <v>6010000123</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="D145" s="4">
-        <v>46574</v>
+        <v>292</v>
+      </c>
+      <c r="D145" s="5">
+        <v>46752</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>346</v>
+        <v>294</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>24</v>
+        <v>92</v>
       </c>
       <c r="G145" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H145" s="5">
-        <v>780</v>
-      </c>
-      <c r="I145" s="5"/>
+      <c r="H145" s="6">
+        <v>5080</v>
+      </c>
+      <c r="I145" s="4"/>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B146" s="8">
-        <v>6010000119</v>
-      </c>
-      <c r="C146" s="9" t="s">
-        <v>293</v>
-      </c>
-      <c r="D146" s="10"/>
-      <c r="E146" s="9" t="s">
+      <c r="B146" s="9">
+        <v>6010000230</v>
+      </c>
+      <c r="C146" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="D146" s="11"/>
+      <c r="E146" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="F146" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="G146" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="H146" s="11"/>
-      <c r="I146" s="11">
-        <v>300</v>
+      <c r="F146" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G146" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="H146" s="12"/>
+      <c r="I146" s="13">
+        <v>3600</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
@@ -5877,876 +5863,878 @@
         <v>0</v>
       </c>
       <c r="B147" s="3">
-        <v>6010000085</v>
+        <v>6010000086</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="D147" s="4">
-        <v>46388</v>
+        <v>226</v>
+      </c>
+      <c r="D147" s="5">
+        <v>46641</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G147" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H147" s="5">
-        <v>31700</v>
-      </c>
-      <c r="I147" s="5"/>
+      <c r="H147" s="6">
+        <v>9400</v>
+      </c>
+      <c r="I147" s="4"/>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B148" s="3">
-        <v>6010000123</v>
+        <v>6010000125</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="D148" s="4">
-        <v>46752</v>
+      <c r="D148" s="5">
+        <v>46574</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>296</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>93</v>
+        <v>23</v>
       </c>
       <c r="G148" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H148" s="5">
-        <v>5080</v>
-      </c>
-      <c r="I148" s="5"/>
+      <c r="H148" s="6">
+        <v>360</v>
+      </c>
+      <c r="I148" s="4"/>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B149" s="3">
-        <v>6010000123</v>
+        <v>6010000144</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="D149" s="4">
-        <v>46692</v>
+        <v>333</v>
+      </c>
+      <c r="D149" s="5">
+        <v>46605</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>297</v>
+        <v>334</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>93</v>
+        <v>325</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H149" s="5">
-        <v>620</v>
-      </c>
-      <c r="I149" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="H149" s="6">
+        <v>1250</v>
+      </c>
+      <c r="I149" s="4"/>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B150" s="8">
-        <v>6010000230</v>
-      </c>
-      <c r="C150" s="9" t="s">
-        <v>445</v>
-      </c>
-      <c r="D150" s="10"/>
-      <c r="E150" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="F150" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="G150" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="H150" s="11"/>
-      <c r="I150" s="11">
-        <v>3600</v>
-      </c>
+      <c r="B150" s="3">
+        <v>6010000214</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="D150" s="5">
+        <v>46692</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="F150" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="G150" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H150" s="6">
+        <v>360</v>
+      </c>
+      <c r="I150" s="4"/>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B151" s="3">
-        <v>6010000086</v>
+        <v>6010000215</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D151" s="4">
-        <v>46641</v>
+        <v>423</v>
+      </c>
+      <c r="D151" s="5">
+        <v>46726</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>229</v>
+        <v>424</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>230</v>
+        <v>425</v>
       </c>
       <c r="G151" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H151" s="5">
-        <v>9400</v>
-      </c>
-      <c r="I151" s="5"/>
+      <c r="H151" s="6">
+        <v>1240</v>
+      </c>
+      <c r="I151" s="4"/>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B152" s="3">
-        <v>6010000125</v>
-      </c>
-      <c r="C152" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="D152" s="4">
-        <v>46574</v>
-      </c>
-      <c r="E152" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="F152" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G152" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H152" s="5">
-        <v>560</v>
-      </c>
-      <c r="I152" s="5"/>
+      <c r="B152" s="9">
+        <v>6010000142</v>
+      </c>
+      <c r="C152" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="D152" s="11"/>
+      <c r="E152" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="F152" s="10" t="s">
+        <v>329</v>
+      </c>
+      <c r="G152" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="H152" s="12"/>
+      <c r="I152" s="13">
+        <v>250</v>
+      </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B153" s="3">
-        <v>6010000144</v>
+        <v>6010000143</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="D153" s="4">
-        <v>46605</v>
+        <v>330</v>
+      </c>
+      <c r="D153" s="5">
+        <v>46425</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G153" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H153" s="5">
-        <v>1250</v>
-      </c>
-      <c r="I153" s="5"/>
+      <c r="H153" s="6">
+        <v>110</v>
+      </c>
+      <c r="I153" s="4"/>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B154" s="3">
-        <v>6010000214</v>
+        <v>6010000145</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="D154" s="4">
-        <v>46692</v>
+        <v>335</v>
+      </c>
+      <c r="D154" s="5">
+        <v>46556</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>428</v>
+        <v>336</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="G154" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H154" s="5">
-        <v>360</v>
-      </c>
-      <c r="I154" s="5"/>
+      <c r="H154" s="6">
+        <v>259</v>
+      </c>
+      <c r="I154" s="4"/>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B155" s="3">
-        <v>6010000215</v>
+        <v>4010013596</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="D155" s="4">
-        <v>46726</v>
+        <v>123</v>
+      </c>
+      <c r="D155" s="5">
+        <v>46446</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>430</v>
+        <v>124</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>431</v>
+        <v>30</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H155" s="5">
-        <v>12</v>
-      </c>
-      <c r="I155" s="5"/>
+        <v>6</v>
+      </c>
+      <c r="H155" s="6">
+        <v>420</v>
+      </c>
+      <c r="I155" s="4"/>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B156" s="3">
-        <v>6010000215</v>
+        <v>4010013655</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="D156" s="4">
-        <v>46726</v>
+        <v>130</v>
+      </c>
+      <c r="D156" s="5">
+        <v>46550</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>432</v>
+        <v>131</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>431</v>
+        <v>30</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H156" s="5">
-        <v>1278</v>
-      </c>
-      <c r="I156" s="5"/>
+        <v>6</v>
+      </c>
+      <c r="H156" s="6">
+        <v>1000</v>
+      </c>
+      <c r="I156" s="4"/>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B157" s="8">
-        <v>6010000142</v>
-      </c>
-      <c r="C157" s="9" t="s">
-        <v>331</v>
-      </c>
-      <c r="D157" s="10"/>
-      <c r="E157" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="F157" s="9" t="s">
-        <v>332</v>
-      </c>
-      <c r="G157" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="H157" s="11"/>
-      <c r="I157" s="11">
-        <v>250</v>
-      </c>
+      <c r="B157" s="3">
+        <v>4010013474</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D157" s="5">
+        <v>46511</v>
+      </c>
+      <c r="E157" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F157" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G157" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H157" s="6">
+        <v>290</v>
+      </c>
+      <c r="I157" s="4"/>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B158" s="3">
-        <v>6010000143</v>
+        <v>4010013474</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="D158" s="4">
-        <v>46425</v>
+        <v>55</v>
+      </c>
+      <c r="D158" s="5">
+        <v>46579</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>334</v>
+        <v>57</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>335</v>
+        <v>30</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H158" s="5">
-        <v>110</v>
-      </c>
-      <c r="I158" s="5"/>
+        <v>6</v>
+      </c>
+      <c r="H158" s="6">
+        <v>590</v>
+      </c>
+      <c r="I158" s="4"/>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B159" s="3">
-        <v>6010000145</v>
+        <v>4010013475</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="D159" s="4">
-        <v>46556</v>
+        <v>58</v>
+      </c>
+      <c r="D159" s="5">
+        <v>46525</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>339</v>
+        <v>59</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>340</v>
+        <v>30</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H159" s="5">
-        <v>259</v>
-      </c>
-      <c r="I159" s="5"/>
+        <v>6</v>
+      </c>
+      <c r="H159" s="6">
+        <v>1330</v>
+      </c>
+      <c r="I159" s="4"/>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B160" s="3">
-        <v>4010013596</v>
+        <v>6010000087</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="D160" s="4">
-        <v>46446</v>
+        <v>229</v>
+      </c>
+      <c r="D160" s="5">
+        <v>46388</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>126</v>
+        <v>230</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>31</v>
+        <v>216</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H160" s="5">
-        <v>420</v>
-      </c>
-      <c r="I160" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="H160" s="6">
+        <v>18100</v>
+      </c>
+      <c r="I160" s="4"/>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B161" s="3">
-        <v>4010013655</v>
+        <v>6010000126</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D161" s="4">
-        <v>46550</v>
+        <v>297</v>
+      </c>
+      <c r="D161" s="5">
+        <v>46780</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>133</v>
+        <v>298</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="G161" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H161" s="5">
-        <v>1000</v>
-      </c>
-      <c r="I161" s="5"/>
+      <c r="H161" s="6">
+        <v>6200</v>
+      </c>
+      <c r="I161" s="4"/>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B162" s="3">
-        <v>4010013474</v>
+        <v>6010000227</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D162" s="4">
-        <v>46511</v>
+        <v>436</v>
+      </c>
+      <c r="D162" s="5">
+        <v>46645</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>57</v>
+        <v>437</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="G162" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H162" s="5">
-        <v>290</v>
-      </c>
-      <c r="I162" s="5"/>
+      <c r="H162" s="6">
+        <v>2340</v>
+      </c>
+      <c r="I162" s="4"/>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B163" s="3">
-        <v>4010013474</v>
+        <v>6010000088</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D163" s="4">
-        <v>46579</v>
+        <v>231</v>
+      </c>
+      <c r="D163" s="5">
+        <v>46661</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>58</v>
+        <v>232</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>31</v>
+        <v>233</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H163" s="5">
-        <v>590</v>
-      </c>
-      <c r="I163" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="H163" s="6">
+        <v>2660</v>
+      </c>
+      <c r="I163" s="4"/>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B164" s="3">
-        <v>4010013475</v>
+        <v>4010013666</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D164" s="4">
-        <v>46525</v>
+        <v>151</v>
+      </c>
+      <c r="D164" s="5">
+        <v>46625</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>60</v>
+        <v>152</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G164" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H164" s="5">
-        <v>1330</v>
-      </c>
-      <c r="I164" s="5"/>
+      <c r="H164" s="6">
+        <v>100</v>
+      </c>
+      <c r="I164" s="4"/>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B165" s="3">
-        <v>6010000087</v>
+        <v>4010013666</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="D165" s="4">
-        <v>46388</v>
+        <v>151</v>
+      </c>
+      <c r="D165" s="5">
+        <v>46593</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>232</v>
+        <v>153</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>218</v>
+        <v>30</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H165" s="5">
-        <v>18100</v>
-      </c>
-      <c r="I165" s="5"/>
+        <v>6</v>
+      </c>
+      <c r="H165" s="6">
+        <v>200</v>
+      </c>
+      <c r="I165" s="4"/>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B166" s="3">
-        <v>6010000126</v>
+        <v>6010000128</v>
       </c>
       <c r="C166" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="D166" s="5">
+        <v>46721</v>
+      </c>
+      <c r="E166" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="D166" s="4">
-        <v>46780</v>
-      </c>
-      <c r="E166" s="2" t="s">
-        <v>301</v>
-      </c>
       <c r="F166" s="2" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G166" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H166" s="5">
-        <v>6400</v>
-      </c>
-      <c r="I166" s="5"/>
+      <c r="H166" s="6">
+        <v>550</v>
+      </c>
+      <c r="I166" s="4"/>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B167" s="3">
-        <v>6010000227</v>
+        <v>6010000129</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="D167" s="4">
-        <v>46645</v>
+        <v>301</v>
+      </c>
+      <c r="D167" s="5">
+        <v>46569</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>444</v>
+        <v>302</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G167" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H167" s="5">
-        <v>2540</v>
-      </c>
-      <c r="I167" s="5"/>
+      <c r="H167" s="6">
+        <v>250</v>
+      </c>
+      <c r="I167" s="4"/>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B168" s="3">
-        <v>6010000088</v>
+        <v>6010000129</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="D168" s="4">
-        <v>46661</v>
+        <v>301</v>
+      </c>
+      <c r="D168" s="5">
+        <v>46758</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>234</v>
+        <v>303</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>235</v>
+        <v>16</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H168" s="5">
-        <v>2660</v>
-      </c>
-      <c r="I168" s="5"/>
+        <v>6</v>
+      </c>
+      <c r="H168" s="6">
+        <v>700</v>
+      </c>
+      <c r="I168" s="4"/>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B169" s="3">
-        <v>4010013666</v>
+        <v>6010000130</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="D169" s="4">
-        <v>46625</v>
+        <v>304</v>
+      </c>
+      <c r="D169" s="5">
+        <v>46753</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>154</v>
+        <v>305</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G169" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H169" s="5">
-        <v>100</v>
-      </c>
-      <c r="I169" s="5"/>
+      <c r="H169" s="6">
+        <v>630</v>
+      </c>
+      <c r="I169" s="4"/>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B170" s="3">
-        <v>4010013666</v>
+        <v>6010000130</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="D170" s="4">
-        <v>46593</v>
+        <v>304</v>
+      </c>
+      <c r="D170" s="5">
+        <v>46569</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>155</v>
+        <v>306</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G170" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H170" s="5">
-        <v>200</v>
-      </c>
-      <c r="I170" s="5"/>
+      <c r="H170" s="6">
+        <v>230</v>
+      </c>
+      <c r="I170" s="4"/>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B171" s="3">
-        <v>6010000128</v>
+        <v>6010000198</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="D171" s="4">
-        <v>46721</v>
+        <v>404</v>
+      </c>
+      <c r="D171" s="5">
+        <v>46568</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>303</v>
+        <v>405</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="G171" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H171" s="5">
-        <v>750</v>
-      </c>
-      <c r="I171" s="5"/>
+      <c r="H171" s="6">
+        <v>640</v>
+      </c>
+      <c r="I171" s="4"/>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B172" s="3">
-        <v>6010000129</v>
+        <v>4010013586</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="D172" s="4">
-        <v>46569</v>
+        <v>108</v>
+      </c>
+      <c r="D172" s="5">
+        <v>46537</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>305</v>
+        <v>109</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G172" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H172" s="5">
-        <v>450</v>
-      </c>
-      <c r="I172" s="5"/>
+      <c r="H172" s="6">
+        <v>1460</v>
+      </c>
+      <c r="I172" s="4"/>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B173" s="3">
-        <v>6010000129</v>
+        <v>4010013587</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="D173" s="4">
-        <v>46758</v>
+        <v>110</v>
+      </c>
+      <c r="D173" s="5">
+        <v>46537</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>306</v>
+        <v>111</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="G173" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H173" s="5">
-        <v>700</v>
-      </c>
-      <c r="I173" s="5"/>
+      <c r="H173" s="6">
+        <v>300</v>
+      </c>
+      <c r="I173" s="4"/>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B174" s="3">
-        <v>6010000130</v>
+        <v>4010013549</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="D174" s="4">
-        <v>46569</v>
+        <v>75</v>
+      </c>
+      <c r="D174" s="5">
+        <v>46525</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>308</v>
+        <v>76</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="G174" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H174" s="5">
-        <v>430</v>
-      </c>
-      <c r="I174" s="5"/>
+      <c r="H174" s="6">
+        <v>1080</v>
+      </c>
+      <c r="I174" s="4"/>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B175" s="3">
-        <v>6010000130</v>
+        <v>4010013249</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="D175" s="4">
-        <v>46753</v>
+        <v>1</v>
+      </c>
+      <c r="D175" s="5">
+        <v>46442</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>309</v>
+        <v>2</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="G175" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H175" s="5">
-        <v>630</v>
-      </c>
-      <c r="I175" s="5"/>
+      <c r="H175" s="6">
+        <v>860</v>
+      </c>
+      <c r="I175" s="4"/>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B176" s="3">
-        <v>6010000198</v>
+        <v>4010013573</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="D176" s="4">
-        <v>46568</v>
+        <v>84</v>
+      </c>
+      <c r="D176" s="5">
+        <v>46423</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>411</v>
+        <v>85</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G176" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H176" s="5">
-        <v>640</v>
-      </c>
-      <c r="I176" s="5"/>
+      <c r="H176" s="6">
+        <v>600</v>
+      </c>
+      <c r="I176" s="4"/>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B177" s="3">
-        <v>4010013586</v>
+        <v>4010013574</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="D177" s="4">
-        <v>46537</v>
+        <v>86</v>
+      </c>
+      <c r="D177" s="5">
+        <v>46545</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G177" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H177" s="5">
-        <v>1460</v>
-      </c>
-      <c r="I177" s="5"/>
+      <c r="H177" s="6">
+        <v>660</v>
+      </c>
+      <c r="I177" s="4"/>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B178" s="3">
-        <v>4010013586</v>
+        <v>4010013588</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="D178" s="4">
-        <v>46439</v>
+        <v>112</v>
+      </c>
+      <c r="D178" s="5">
+        <v>46582</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G178" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H178" s="5">
-        <v>30</v>
-      </c>
-      <c r="I178" s="5"/>
+      <c r="H178" s="6">
+        <v>3280</v>
+      </c>
+      <c r="I178" s="4"/>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B179" s="3">
-        <v>4010013587</v>
+        <v>4010013479</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D179" s="4">
-        <v>46537</v>
+        <v>66</v>
+      </c>
+      <c r="D179" s="5">
+        <v>46594</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>113</v>
+        <v>67</v>
       </c>
       <c r="F179" s="2" t="s">
         <v>5</v>
@@ -6754,53 +6742,53 @@
       <c r="G179" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H179" s="5">
-        <v>300</v>
-      </c>
-      <c r="I179" s="5"/>
+      <c r="H179" s="6">
+        <v>400</v>
+      </c>
+      <c r="I179" s="4"/>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B180" s="3">
-        <v>4010013549</v>
+        <v>4010013479</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D180" s="4">
-        <v>46525</v>
+        <v>66</v>
+      </c>
+      <c r="D180" s="5">
+        <v>46536</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G180" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H180" s="5">
-        <v>1180</v>
-      </c>
-      <c r="I180" s="5"/>
+      <c r="H180" s="6">
+        <v>320</v>
+      </c>
+      <c r="I180" s="4"/>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B181" s="3">
-        <v>4010013249</v>
+        <v>4010013479</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D181" s="4">
-        <v>46442</v>
+        <v>66</v>
+      </c>
+      <c r="D181" s="5">
+        <v>46419</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="F181" s="2" t="s">
         <v>5</v>
@@ -6808,26 +6796,26 @@
       <c r="G181" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H181" s="5">
-        <v>860</v>
-      </c>
-      <c r="I181" s="5"/>
+      <c r="H181" s="6">
+        <v>240</v>
+      </c>
+      <c r="I181" s="4"/>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B182" s="3">
-        <v>4010013573</v>
+        <v>4010013700</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D182" s="4">
-        <v>46423</v>
+        <v>165</v>
+      </c>
+      <c r="D182" s="5">
+        <v>46446</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>86</v>
+        <v>166</v>
       </c>
       <c r="F182" s="2" t="s">
         <v>5</v>
@@ -6835,53 +6823,53 @@
       <c r="G182" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H182" s="5">
+      <c r="H182" s="6">
         <v>600</v>
       </c>
-      <c r="I182" s="5"/>
+      <c r="I182" s="4"/>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B183" s="3">
-        <v>4010013574</v>
+        <v>4010013700</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D183" s="4">
-        <v>46545</v>
+        <v>165</v>
+      </c>
+      <c r="D183" s="5">
+        <v>46533</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>88</v>
+        <v>167</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G183" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H183" s="5">
-        <v>660</v>
-      </c>
-      <c r="I183" s="5"/>
+      <c r="H183" s="6">
+        <v>300</v>
+      </c>
+      <c r="I183" s="4"/>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B184" s="3">
-        <v>4010013588</v>
+        <v>4010013701</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="D184" s="4">
-        <v>46582</v>
+        <v>168</v>
+      </c>
+      <c r="D184" s="5">
+        <v>46589</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>115</v>
+        <v>169</v>
       </c>
       <c r="F184" s="2" t="s">
         <v>5</v>
@@ -6889,1183 +6877,1183 @@
       <c r="G184" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H184" s="5">
-        <v>3480</v>
-      </c>
-      <c r="I184" s="5"/>
+      <c r="H184" s="6">
+        <v>1200</v>
+      </c>
+      <c r="I184" s="4"/>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B185" s="3">
-        <v>4010013479</v>
+        <v>4010013657</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D185" s="4">
-        <v>46419</v>
+        <v>136</v>
+      </c>
+      <c r="D185" s="5">
+        <v>46513</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>68</v>
+        <v>137</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G185" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H185" s="5">
-        <v>240</v>
-      </c>
-      <c r="I185" s="5"/>
+      <c r="H185" s="6">
+        <v>1060</v>
+      </c>
+      <c r="I185" s="4"/>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B186" s="3">
-        <v>4010013479</v>
+        <v>4010013658</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D186" s="4">
-        <v>46594</v>
+        <v>138</v>
+      </c>
+      <c r="D186" s="5">
+        <v>46563</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>69</v>
+        <v>139</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G186" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H186" s="5">
-        <v>400</v>
-      </c>
-      <c r="I186" s="5"/>
+      <c r="H186" s="6">
+        <v>90</v>
+      </c>
+      <c r="I186" s="4"/>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B187" s="3">
-        <v>4010013479</v>
+        <v>4010013658</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D187" s="4">
-        <v>46536</v>
+        <v>138</v>
+      </c>
+      <c r="D187" s="5">
+        <v>46587</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G187" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H187" s="5">
-        <v>320</v>
-      </c>
-      <c r="I187" s="5"/>
+      <c r="H187" s="6">
+        <v>1200</v>
+      </c>
+      <c r="I187" s="4"/>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B188" s="3">
-        <v>4010013700</v>
+        <v>4010013548</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="D188" s="4">
-        <v>46446</v>
+        <v>72</v>
+      </c>
+      <c r="D188" s="5">
+        <v>46469</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>168</v>
+        <v>73</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>5</v>
+        <v>74</v>
       </c>
       <c r="G188" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H188" s="5">
-        <v>600</v>
-      </c>
-      <c r="I188" s="5"/>
+      <c r="H188" s="6">
+        <v>830</v>
+      </c>
+      <c r="I188" s="4"/>
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B189" s="3">
-        <v>4010013700</v>
+        <v>4010013480</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="D189" s="4">
-        <v>46533</v>
+        <v>70</v>
+      </c>
+      <c r="D189" s="5">
+        <v>46408</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>169</v>
+        <v>71</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G189" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H189" s="5">
-        <v>300</v>
-      </c>
-      <c r="I189" s="5"/>
+      <c r="H189" s="6">
+        <v>1230</v>
+      </c>
+      <c r="I189" s="4"/>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B190" s="3">
-        <v>4010013701</v>
+        <v>4010013477</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="D190" s="4">
-        <v>46589</v>
+        <v>62</v>
+      </c>
+      <c r="D190" s="5">
+        <v>46574</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>171</v>
+        <v>63</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G190" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H190" s="5">
-        <v>1200</v>
-      </c>
-      <c r="I190" s="5"/>
+      <c r="H190" s="6">
+        <v>600</v>
+      </c>
+      <c r="I190" s="4"/>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B191" s="3">
-        <v>4010013657</v>
+        <v>6010000131</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D191" s="4">
-        <v>46513</v>
+        <v>307</v>
+      </c>
+      <c r="D191" s="5">
+        <v>46784</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>139</v>
+        <v>308</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="G191" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H191" s="5">
-        <v>1060</v>
-      </c>
-      <c r="I191" s="5"/>
+      <c r="H191" s="6">
+        <v>2600</v>
+      </c>
+      <c r="I191" s="4"/>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B192" s="3">
-        <v>4010013658</v>
+        <v>4010013699</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="D192" s="4">
-        <v>46563</v>
+        <v>163</v>
+      </c>
+      <c r="D192" s="5">
+        <v>46438</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="G192" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H192" s="5">
-        <v>90</v>
-      </c>
-      <c r="I192" s="5"/>
+      <c r="H192" s="6">
+        <v>380</v>
+      </c>
+      <c r="I192" s="4"/>
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B193" s="3">
-        <v>4010013658</v>
+        <v>6010000089</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="D193" s="4">
-        <v>46587</v>
+        <v>234</v>
+      </c>
+      <c r="D193" s="5">
+        <v>46424</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>142</v>
+        <v>235</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>9</v>
+        <v>236</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H193" s="5">
-        <v>1200</v>
-      </c>
-      <c r="I193" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="H193" s="6">
+        <v>2360</v>
+      </c>
+      <c r="I193" s="4"/>
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B194" s="3">
-        <v>4010013548</v>
+        <v>6010000089</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D194" s="4">
-        <v>46469</v>
+        <v>234</v>
+      </c>
+      <c r="D194" s="5">
+        <v>46871</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>74</v>
+        <v>237</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>75</v>
+        <v>236</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H194" s="5">
-        <v>830</v>
-      </c>
-      <c r="I194" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="H194" s="6">
+        <v>2300</v>
+      </c>
+      <c r="I194" s="4"/>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B195" s="3">
-        <v>4010013480</v>
+        <v>6010000132</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D195" s="4">
-        <v>46408</v>
+        <v>309</v>
+      </c>
+      <c r="D195" s="5">
+        <v>46614</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>72</v>
+        <v>3</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="G195" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H195" s="5">
-        <v>1230</v>
-      </c>
-      <c r="I195" s="5"/>
+      <c r="H195" s="6">
+        <v>3600</v>
+      </c>
+      <c r="I195" s="4"/>
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B196" s="3">
-        <v>4010013477</v>
+        <v>6010000146</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D196" s="4">
-        <v>46574</v>
+        <v>338</v>
+      </c>
+      <c r="D196" s="5">
+        <v>46746</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>64</v>
+        <v>339</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>9</v>
+        <v>340</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H196" s="5">
-        <v>900</v>
-      </c>
-      <c r="I196" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="H196" s="6">
+        <v>560</v>
+      </c>
+      <c r="I196" s="4"/>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B197" s="3">
-        <v>6010000131</v>
+        <v>6010000090</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="D197" s="4">
-        <v>46784</v>
+        <v>238</v>
+      </c>
+      <c r="D197" s="5">
+        <v>46482</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>311</v>
+        <v>239</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>24</v>
+        <v>240</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H197" s="5">
-        <v>2900</v>
-      </c>
-      <c r="I197" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="H197" s="6">
+        <v>4650</v>
+      </c>
+      <c r="I197" s="4"/>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B198" s="3">
-        <v>4010013699</v>
+        <v>6010000200</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="D198" s="4">
-        <v>46438</v>
+        <v>408</v>
+      </c>
+      <c r="D198" s="5">
+        <v>46593</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>166</v>
+        <v>409</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>31</v>
+        <v>410</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H198" s="5">
-        <v>380</v>
-      </c>
-      <c r="I198" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="H198" s="6">
+        <v>310</v>
+      </c>
+      <c r="I198" s="4"/>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B199" s="3">
-        <v>6010000089</v>
+        <v>6010000199</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="D199" s="4">
-        <v>46871</v>
+        <v>406</v>
+      </c>
+      <c r="D199" s="5">
+        <v>46556</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>237</v>
+        <v>407</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>238</v>
+        <v>23</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H199" s="5">
-        <v>2300</v>
-      </c>
-      <c r="I199" s="5"/>
+        <v>6</v>
+      </c>
+      <c r="H199" s="6">
+        <v>1680</v>
+      </c>
+      <c r="I199" s="4"/>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B200" s="3">
-        <v>6010000089</v>
+        <v>6010000133</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="D200" s="4">
-        <v>46424</v>
+        <v>310</v>
+      </c>
+      <c r="D200" s="5">
+        <v>46388</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>239</v>
+        <v>311</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>238</v>
+        <v>92</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H200" s="5">
-        <v>2360</v>
-      </c>
-      <c r="I200" s="5"/>
+        <v>6</v>
+      </c>
+      <c r="H200" s="6">
+        <v>1220</v>
+      </c>
+      <c r="I200" s="4"/>
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B201" s="3">
-        <v>6010000132</v>
+        <v>6010000134</v>
       </c>
       <c r="C201" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="D201" s="4">
-        <v>46614</v>
+      <c r="D201" s="5">
+        <v>46488</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>3</v>
+        <v>313</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>31</v>
+        <v>92</v>
       </c>
       <c r="G201" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H201" s="5">
-        <v>3600</v>
-      </c>
-      <c r="I201" s="5"/>
+      <c r="H201" s="6">
+        <v>1600</v>
+      </c>
+      <c r="I201" s="4"/>
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B202" s="3">
-        <v>6010000146</v>
+        <v>6010000135</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="D202" s="4">
-        <v>46746</v>
+        <v>314</v>
+      </c>
+      <c r="D202" s="5">
+        <v>46388</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>342</v>
+        <v>315</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>343</v>
+        <v>92</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H202" s="5">
-        <v>600</v>
-      </c>
-      <c r="I202" s="5"/>
+        <v>6</v>
+      </c>
+      <c r="H202" s="6">
+        <v>1560</v>
+      </c>
+      <c r="I202" s="4"/>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B203" s="3">
-        <v>6010000090</v>
+        <v>6010000136</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="D203" s="4">
-        <v>46482</v>
+        <v>316</v>
+      </c>
+      <c r="D203" s="5">
+        <v>46496</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>241</v>
+        <v>317</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>242</v>
+        <v>30</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H203" s="5">
-        <v>4650</v>
-      </c>
-      <c r="I203" s="5"/>
+        <v>6</v>
+      </c>
+      <c r="H203" s="6">
+        <v>490</v>
+      </c>
+      <c r="I203" s="4"/>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B204" s="3">
-        <v>6010000200</v>
+        <v>6010000137</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="D204" s="4">
-        <v>46593</v>
+        <v>318</v>
+      </c>
+      <c r="D204" s="5">
+        <v>46496</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>415</v>
+        <v>319</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>416</v>
+        <v>30</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H204" s="5">
-        <v>410</v>
-      </c>
-      <c r="I204" s="5"/>
+        <v>6</v>
+      </c>
+      <c r="H204" s="6">
+        <v>850</v>
+      </c>
+      <c r="I204" s="4"/>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B205" s="3">
-        <v>6010000199</v>
+        <v>4010013269</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="D205" s="4">
-        <v>46556</v>
+        <v>21</v>
+      </c>
+      <c r="D205" s="5">
+        <v>46558</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>413</v>
+        <v>22</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G205" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H205" s="5">
-        <v>1680</v>
-      </c>
-      <c r="I205" s="5"/>
+      <c r="H205" s="6">
+        <v>1000</v>
+      </c>
+      <c r="I205" s="4"/>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B206" s="3">
-        <v>6010000133</v>
+        <v>6010000177</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="D206" s="4">
-        <v>46388</v>
+        <v>380</v>
+      </c>
+      <c r="D206" s="5">
+        <v>46971</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>314</v>
+        <v>381</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>93</v>
+        <v>382</v>
       </c>
       <c r="G206" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H206" s="5">
-        <v>1420</v>
-      </c>
-      <c r="I206" s="5"/>
+      <c r="H206" s="6">
+        <v>2980</v>
+      </c>
+      <c r="I206" s="4"/>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B207" s="3">
-        <v>6010000134</v>
+        <v>6010000178</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="D207" s="4">
-        <v>46488</v>
+        <v>383</v>
+      </c>
+      <c r="D207" s="5">
+        <v>47087</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>316</v>
+        <v>384</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>93</v>
+        <v>385</v>
       </c>
       <c r="G207" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H207" s="5">
-        <v>1860</v>
-      </c>
-      <c r="I207" s="5"/>
+      <c r="H207" s="6">
+        <v>1260</v>
+      </c>
+      <c r="I207" s="4"/>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B208" s="3">
-        <v>6010000135</v>
+        <v>4010013597</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="D208" s="4">
-        <v>46388</v>
+        <v>125</v>
+      </c>
+      <c r="D208" s="5">
+        <v>46525</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>318</v>
+        <v>126</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>93</v>
+        <v>12</v>
       </c>
       <c r="G208" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H208" s="5">
-        <v>1560</v>
-      </c>
-      <c r="I208" s="5"/>
+      <c r="H208" s="6">
+        <v>620</v>
+      </c>
+      <c r="I208" s="4"/>
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B209" s="3">
-        <v>6010000136</v>
+        <v>4010013368</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="D209" s="4">
-        <v>46496</v>
+        <v>32</v>
+      </c>
+      <c r="D209" s="5">
+        <v>46533</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>320</v>
+        <v>33</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="G209" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H209" s="5">
-        <v>590</v>
-      </c>
-      <c r="I209" s="5"/>
+      <c r="H209" s="6">
+        <v>160</v>
+      </c>
+      <c r="I209" s="4"/>
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B210" s="3">
-        <v>6010000137</v>
+        <v>4010013368</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="D210" s="4">
-        <v>46496</v>
+        <v>32</v>
+      </c>
+      <c r="D210" s="5">
+        <v>46457</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>322</v>
+        <v>34</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="G210" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H210" s="5">
-        <v>850</v>
-      </c>
-      <c r="I210" s="5"/>
+      <c r="H210" s="6">
+        <v>100</v>
+      </c>
+      <c r="I210" s="4"/>
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B211" s="3">
-        <v>4010013269</v>
+        <v>4010013369</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D211" s="4">
-        <v>46558</v>
+        <v>35</v>
+      </c>
+      <c r="D211" s="5">
+        <v>46429</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="G211" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H211" s="5">
-        <v>1000</v>
-      </c>
-      <c r="I211" s="5"/>
+      <c r="H211" s="6">
+        <v>440</v>
+      </c>
+      <c r="I211" s="4"/>
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B212" s="3">
-        <v>6010000177</v>
+        <v>4010013369</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="D212" s="4">
-        <v>46971</v>
+        <v>35</v>
+      </c>
+      <c r="D212" s="5">
+        <v>46533</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>387</v>
+        <v>37</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>388</v>
+        <v>5</v>
       </c>
       <c r="G212" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H212" s="5">
-        <v>2980</v>
-      </c>
-      <c r="I212" s="5"/>
+      <c r="H212" s="6">
+        <v>80</v>
+      </c>
+      <c r="I212" s="4"/>
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B213" s="3">
-        <v>6010000178</v>
+        <v>4010013598</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="D213" s="4">
-        <v>47087</v>
+        <v>127</v>
+      </c>
+      <c r="D213" s="5">
+        <v>47043</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>390</v>
+        <v>128</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>391</v>
+        <v>129</v>
       </c>
       <c r="G213" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H213" s="5">
-        <v>1260</v>
-      </c>
-      <c r="I213" s="5"/>
+      <c r="H213" s="6">
+        <v>320</v>
+      </c>
+      <c r="I213" s="4"/>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B214" s="3">
-        <v>4010013597</v>
+        <v>6010000091</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D214" s="4">
-        <v>46525</v>
+        <v>241</v>
+      </c>
+      <c r="D214" s="5">
+        <v>46721</v>
       </c>
       <c r="E214" s="2" t="s">
-        <v>128</v>
+        <v>242</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>12</v>
+        <v>243</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H214" s="5">
-        <v>620</v>
-      </c>
-      <c r="I214" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="H214" s="6">
+        <v>450</v>
+      </c>
+      <c r="I214" s="4"/>
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B215" s="3">
-        <v>4010013368</v>
+        <v>6010000091</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D215" s="4">
-        <v>46533</v>
+        <v>241</v>
+      </c>
+      <c r="D215" s="5">
+        <v>46392</v>
       </c>
       <c r="E215" s="2" t="s">
-        <v>34</v>
+        <v>244</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>5</v>
+        <v>243</v>
       </c>
       <c r="G215" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H215" s="5">
-        <v>160</v>
-      </c>
-      <c r="I215" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="H215" s="6">
+        <v>420</v>
+      </c>
+      <c r="I215" s="4"/>
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B216" s="3">
-        <v>4010013368</v>
+        <v>4010013399</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D216" s="4">
-        <v>46457</v>
+        <v>45</v>
+      </c>
+      <c r="D216" s="5">
+        <v>46532</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="G216" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H216" s="5">
-        <v>100</v>
-      </c>
-      <c r="I216" s="5"/>
+      <c r="H216" s="6">
+        <v>570</v>
+      </c>
+      <c r="I216" s="4"/>
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B217" s="3">
-        <v>4010013369</v>
+        <v>6010000203</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D217" s="4">
-        <v>46429</v>
+        <v>416</v>
+      </c>
+      <c r="D217" s="5">
+        <v>46606</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>37</v>
+        <v>417</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>5</v>
+        <v>413</v>
       </c>
       <c r="G217" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H217" s="5">
-        <v>440</v>
-      </c>
-      <c r="I217" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="H217" s="6">
+        <v>510</v>
+      </c>
+      <c r="I217" s="4"/>
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B218" s="3">
-        <v>4010013369</v>
+        <v>4010013592</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D218" s="4">
-        <v>46533</v>
+        <v>114</v>
+      </c>
+      <c r="D218" s="5">
+        <v>46514</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>38</v>
+        <v>115</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>5</v>
+        <v>116</v>
       </c>
       <c r="G218" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H218" s="5">
-        <v>80</v>
-      </c>
-      <c r="I218" s="5"/>
+      <c r="H218" s="6">
+        <v>250</v>
+      </c>
+      <c r="I218" s="4"/>
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B219" s="3">
-        <v>4010013598</v>
+        <v>4010014926</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="D219" s="4">
-        <v>47043</v>
+        <v>174</v>
+      </c>
+      <c r="D219" s="5">
+        <v>46768</v>
       </c>
       <c r="E219" s="2" t="s">
-        <v>130</v>
+        <v>175</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>131</v>
+        <v>176</v>
       </c>
       <c r="G219" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H219" s="5">
-        <v>420</v>
-      </c>
-      <c r="I219" s="5"/>
+      <c r="H219" s="6">
+        <v>780</v>
+      </c>
+      <c r="I219" s="4"/>
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B220" s="3">
-        <v>6010000091</v>
+        <v>7050000020</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="D220" s="4">
-        <v>46392</v>
-      </c>
+        <v>470</v>
+      </c>
+      <c r="D220" s="5"/>
       <c r="E220" s="2" t="s">
-        <v>244</v>
+        <v>3</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>245</v>
+        <v>3</v>
       </c>
       <c r="G220" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H220" s="5">
-        <v>420</v>
-      </c>
-      <c r="I220" s="5"/>
+      <c r="H220" s="6">
+        <v>70</v>
+      </c>
+      <c r="I220" s="4"/>
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B221" s="3">
-        <v>6010000091</v>
+        <v>7050000020</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="D221" s="4">
-        <v>46721</v>
-      </c>
+        <v>470</v>
+      </c>
+      <c r="D221" s="5"/>
       <c r="E221" s="2" t="s">
-        <v>246</v>
+        <v>3</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>245</v>
+        <v>3</v>
       </c>
       <c r="G221" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H221" s="5">
-        <v>450</v>
-      </c>
-      <c r="I221" s="5"/>
+      <c r="H221" s="6">
+        <v>30</v>
+      </c>
+      <c r="I221" s="4"/>
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B222" s="3">
-        <v>4010013399</v>
+        <v>4010013659</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D222" s="4">
-        <v>46532</v>
+        <v>141</v>
+      </c>
+      <c r="D222" s="5">
+        <v>46526</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>47</v>
+        <v>142</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="G222" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H222" s="5">
-        <v>570</v>
-      </c>
-      <c r="I222" s="5"/>
+      <c r="H222" s="6">
+        <v>670</v>
+      </c>
+      <c r="I222" s="4"/>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B223" s="3">
-        <v>6010000203</v>
+        <v>4010013273</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="D223" s="4">
-        <v>46606</v>
+        <v>28</v>
+      </c>
+      <c r="D223" s="5">
+        <v>46444</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>423</v>
+        <v>29</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>419</v>
+        <v>30</v>
       </c>
       <c r="G223" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H223" s="5">
-        <v>510</v>
-      </c>
-      <c r="I223" s="5"/>
+        <v>6</v>
+      </c>
+      <c r="H223" s="6">
+        <v>80</v>
+      </c>
+      <c r="I223" s="4"/>
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B224" s="3">
-        <v>4010013592</v>
+        <v>4010013273</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D224" s="4">
-        <v>46514</v>
+        <v>28</v>
+      </c>
+      <c r="D224" s="5">
+        <v>46444</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>117</v>
+        <v>31</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>118</v>
+        <v>30</v>
       </c>
       <c r="G224" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H224" s="5">
-        <v>250</v>
-      </c>
-      <c r="I224" s="5"/>
+      <c r="H224" s="6">
+        <v>710</v>
+      </c>
+      <c r="I224" s="4"/>
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B225" s="3">
-        <v>4010014926</v>
+        <v>4010013271</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="D225" s="4">
-        <v>46768</v>
+        <v>24</v>
+      </c>
+      <c r="D225" s="5">
+        <v>46402</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>177</v>
+        <v>25</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>178</v>
+        <v>9</v>
       </c>
       <c r="G225" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H225" s="5">
-        <v>780</v>
-      </c>
-      <c r="I225" s="5"/>
+      <c r="H225" s="6">
+        <v>320</v>
+      </c>
+      <c r="I225" s="4"/>
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B226" s="3">
-        <v>7050000020</v>
+        <v>4010013272</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="D226" s="4"/>
+        <v>26</v>
+      </c>
+      <c r="D226" s="5">
+        <v>46523</v>
+      </c>
       <c r="E226" s="2" t="s">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G226" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H226" s="5">
-        <v>30</v>
-      </c>
-      <c r="I226" s="5"/>
+        <v>6</v>
+      </c>
+      <c r="H226" s="6">
+        <v>1020</v>
+      </c>
+      <c r="I226" s="4"/>
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B227" s="3">
-        <v>7050000020</v>
+        <v>4010013663</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="D227" s="4"/>
+        <v>148</v>
+      </c>
+      <c r="D227" s="5">
+        <v>46612</v>
+      </c>
       <c r="E227" s="2" t="s">
-        <v>3</v>
+        <v>149</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G227" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H227" s="5">
-        <v>70</v>
-      </c>
-      <c r="I227" s="5"/>
+        <v>6</v>
+      </c>
+      <c r="H227" s="6">
+        <v>1200</v>
+      </c>
+      <c r="I227" s="4"/>
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B228" s="3">
-        <v>4010013659</v>
+        <v>4010013663</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D228" s="4">
-        <v>46526</v>
+        <v>148</v>
+      </c>
+      <c r="D228" s="5">
+        <v>46514</v>
       </c>
       <c r="E228" s="2" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="F228" s="2" t="s">
         <v>9</v>
@@ -8073,339 +8061,177 @@
       <c r="G228" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H228" s="5">
-        <v>870</v>
-      </c>
-      <c r="I228" s="5"/>
+      <c r="H228" s="6">
+        <v>200</v>
+      </c>
+      <c r="I228" s="4"/>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B229" s="3">
-        <v>4010013273</v>
+        <v>6010000245</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D229" s="4">
-        <v>46444</v>
+        <v>455</v>
+      </c>
+      <c r="D229" s="5">
+        <v>46574</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>30</v>
+        <v>456</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>31</v>
+        <v>457</v>
       </c>
       <c r="G229" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H229" s="5">
-        <v>710</v>
-      </c>
-      <c r="I229" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="H229" s="6">
+        <v>6700</v>
+      </c>
+      <c r="I229" s="4"/>
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B230" s="3">
-        <v>4010013273</v>
+        <v>6010000245</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D230" s="4">
-        <v>46444</v>
+        <v>455</v>
+      </c>
+      <c r="D230" s="5">
+        <v>46629</v>
       </c>
       <c r="E230" s="2" t="s">
-        <v>32</v>
+        <v>458</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>31</v>
+        <v>457</v>
       </c>
       <c r="G230" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H230" s="5">
-        <v>80</v>
-      </c>
-      <c r="I230" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="H230" s="6">
+        <v>500</v>
+      </c>
+      <c r="I230" s="4"/>
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B231" s="3">
-        <v>4010013271</v>
+        <v>6010000093</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D231" s="4">
-        <v>46402</v>
+        <v>245</v>
+      </c>
+      <c r="D231" s="5">
+        <v>46504</v>
       </c>
       <c r="E231" s="2" t="s">
-        <v>26</v>
+        <v>246</v>
       </c>
       <c r="F231" s="2" t="s">
-        <v>9</v>
+        <v>247</v>
       </c>
       <c r="G231" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H231" s="5">
-        <v>320</v>
-      </c>
-      <c r="I231" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="H231" s="6">
+        <v>600</v>
+      </c>
+      <c r="I231" s="4"/>
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B232" s="3">
-        <v>4010013272</v>
+        <v>6010000093</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D232" s="4">
-        <v>46523</v>
+        <v>245</v>
+      </c>
+      <c r="D232" s="5">
+        <v>46504</v>
       </c>
       <c r="E232" s="2" t="s">
-        <v>28</v>
+        <v>248</v>
       </c>
       <c r="F232" s="2" t="s">
-        <v>9</v>
+        <v>247</v>
       </c>
       <c r="G232" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H232" s="5">
-        <v>1320</v>
-      </c>
-      <c r="I232" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="H232" s="6">
+        <v>18000</v>
+      </c>
+      <c r="I232" s="4"/>
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B233" s="3">
-        <v>4010013663</v>
+        <v>6010000161</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="D233" s="4">
-        <v>46514</v>
+        <v>358</v>
+      </c>
+      <c r="D233" s="5">
+        <v>47087</v>
       </c>
       <c r="E233" s="2" t="s">
-        <v>151</v>
+        <v>359</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>9</v>
+        <v>360</v>
       </c>
       <c r="G233" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H233" s="5">
-        <v>200</v>
-      </c>
-      <c r="I233" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="H233" s="6">
+        <v>774</v>
+      </c>
+      <c r="I233" s="4"/>
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A234" s="1" t="s">
+      <c r="A234" s="8" t="s">
         <v>0</v>
       </c>
       <c r="B234" s="3">
-        <v>4010013663</v>
+        <v>6010000162</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="D234" s="4">
-        <v>46612</v>
+        <v>361</v>
+      </c>
+      <c r="D234" s="5">
+        <v>47087</v>
       </c>
       <c r="E234" s="2" t="s">
-        <v>152</v>
+        <v>362</v>
       </c>
       <c r="F234" s="2" t="s">
-        <v>9</v>
+        <v>363</v>
       </c>
       <c r="G234" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H234" s="5">
+        <v>4</v>
+      </c>
+      <c r="H234" s="6">
         <v>1200</v>
       </c>
-      <c r="I234" s="5"/>
-    </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A235" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B235" s="3">
-        <v>6010000245</v>
-      </c>
-      <c r="C235" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="D235" s="4">
-        <v>46629</v>
-      </c>
-      <c r="E235" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="F235" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="G235" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H235" s="5">
-        <v>500</v>
-      </c>
-      <c r="I235" s="5"/>
-    </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A236" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B236" s="3">
-        <v>6010000245</v>
-      </c>
-      <c r="C236" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="D236" s="4">
-        <v>46574</v>
-      </c>
-      <c r="E236" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="F236" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="G236" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H236" s="5">
-        <v>6700</v>
-      </c>
-      <c r="I236" s="5"/>
-    </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A237" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B237" s="3">
-        <v>6010000093</v>
-      </c>
-      <c r="C237" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="D237" s="4">
-        <v>46504</v>
-      </c>
-      <c r="E237" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="F237" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="G237" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H237" s="5">
-        <v>600</v>
-      </c>
-      <c r="I237" s="5"/>
-    </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A238" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B238" s="3">
-        <v>6010000093</v>
-      </c>
-      <c r="C238" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="D238" s="4">
-        <v>46504</v>
-      </c>
-      <c r="E238" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="F238" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="G238" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H238" s="5">
-        <v>18000</v>
-      </c>
-      <c r="I238" s="5"/>
-    </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A239" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B239" s="3">
-        <v>6010000161</v>
-      </c>
-      <c r="C239" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="D239" s="4">
-        <v>47087</v>
-      </c>
-      <c r="E239" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="F239" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="G239" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H239" s="5">
-        <v>936</v>
-      </c>
-      <c r="I239" s="5"/>
-    </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A240" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B240" s="3">
-        <v>6010000162</v>
-      </c>
-      <c r="C240" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="D240" s="4">
-        <v>47087</v>
-      </c>
-      <c r="E240" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="F240" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="G240" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H240" s="5">
-        <v>1344</v>
-      </c>
-      <c r="I240" s="5"/>
+      <c r="I234" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I240">
-    <sortState ref="A2:I240">
-      <sortCondition ref="C1:C240"/>
+  <autoFilter ref="A1:I234">
+    <sortState ref="A2:I234">
+      <sortCondition ref="C1:C234"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="0" type="noConversion"/>

--- a/KSTOCK.xlsx
+++ b/KSTOCK.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
   </bookViews>
@@ -2183,7 +2183,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2191,6 +2191,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:AF252"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>

--- a/KSTOCK.xlsx
+++ b/KSTOCK.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
@@ -10,14 +10,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$248</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$247</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="991" uniqueCount="462">
   <si>
     <t>ROSUSEP-20</t>
   </si>
@@ -49,15 +49,15 @@
     <t>ATROLIA CV 20/75</t>
   </si>
   <si>
+    <t>25S3GCA131</t>
+  </si>
+  <si>
+    <t>10X3X10</t>
+  </si>
+  <si>
     <t>25S3GCA110</t>
   </si>
   <si>
-    <t>10X3X10</t>
-  </si>
-  <si>
-    <t>25S3GCA131</t>
-  </si>
-  <si>
     <t>Montalia AB</t>
   </si>
   <si>
@@ -133,15 +133,15 @@
     <t>CHYMOACTIVE-FORTE</t>
   </si>
   <si>
+    <t>25S3GTB348</t>
+  </si>
+  <si>
+    <t>10X20</t>
+  </si>
+  <si>
     <t>25S3GTB083</t>
   </si>
   <si>
-    <t>10X20</t>
-  </si>
-  <si>
-    <t>25S3GTB348</t>
-  </si>
-  <si>
     <t>CILNIEASE-T</t>
   </si>
   <si>
@@ -178,12 +178,12 @@
     <t>PROGISPHERE SR 200</t>
   </si>
   <si>
+    <t>25S2HTA612</t>
+  </si>
+  <si>
     <t>25S2HTA863</t>
   </si>
   <si>
-    <t>25S2HTA612</t>
-  </si>
-  <si>
     <t>PROGISPHERE SR 300</t>
   </si>
   <si>
@@ -214,12 +214,12 @@
     <t>25S3GCA105</t>
   </si>
   <si>
+    <t>25S3GCA138</t>
+  </si>
+  <si>
     <t>25S3GCA034</t>
   </si>
   <si>
-    <t>25S3GCA138</t>
-  </si>
-  <si>
     <t>SITAFREE-MET 1000 IR</t>
   </si>
   <si>
@@ -391,15 +391,15 @@
     <t>LEVELISH 500</t>
   </si>
   <si>
+    <t>25S2GTB370</t>
+  </si>
+  <si>
+    <t>10X10</t>
+  </si>
+  <si>
     <t>25S2GTA561</t>
   </si>
   <si>
-    <t>10X10</t>
-  </si>
-  <si>
-    <t>25S2GTB370</t>
-  </si>
-  <si>
     <t>SITAFREE-100</t>
   </si>
   <si>
@@ -409,12 +409,12 @@
     <t>SITAFREE-50</t>
   </si>
   <si>
+    <t>25S2GTC059</t>
+  </si>
+  <si>
     <t>25S2GTB786</t>
   </si>
   <si>
-    <t>25S2GTC059</t>
-  </si>
-  <si>
     <t>VILDAPHARM-50</t>
   </si>
   <si>
@@ -430,12 +430,12 @@
     <t>GABAKAT NT-400</t>
   </si>
   <si>
+    <t>25S3GTA585</t>
+  </si>
+  <si>
     <t>25S3GTA850</t>
   </si>
   <si>
-    <t>25S3GTA585</t>
-  </si>
-  <si>
     <t>VILDAPHARM-OD 100</t>
   </si>
   <si>
@@ -559,12 +559,12 @@
     <t>CEFTAPACE-1G</t>
   </si>
   <si>
+    <t>NL2742601</t>
+  </si>
+  <si>
     <t>1X10ML</t>
   </si>
   <si>
-    <t>NL2742601</t>
-  </si>
-  <si>
     <t>CLAVMYCIN IV</t>
   </si>
   <si>
@@ -577,12 +577,12 @@
     <t>DECAHIT INJECTION</t>
   </si>
   <si>
+    <t>96X2ML</t>
+  </si>
+  <si>
     <t>NL2722504</t>
   </si>
   <si>
-    <t>96X2ML</t>
-  </si>
-  <si>
     <t>NL2722503</t>
   </si>
   <si>
@@ -646,12 +646,12 @@
     <t>NEUROKAT 1500 INJ</t>
   </si>
   <si>
+    <t>NL2762502</t>
+  </si>
+  <si>
     <t>1X1ML</t>
   </si>
   <si>
-    <t>NL2762502</t>
-  </si>
-  <si>
     <t>NICIN 500 INJ.</t>
   </si>
   <si>
@@ -697,15 +697,15 @@
     <t>SYNACORT</t>
   </si>
   <si>
+    <t>NL2682502</t>
+  </si>
+  <si>
+    <t>10X8X1ML</t>
+  </si>
+  <si>
     <t>NL2682501</t>
   </si>
   <si>
-    <t>10X8X1ML</t>
-  </si>
-  <si>
-    <t>NL2682502</t>
-  </si>
-  <si>
     <t>TAZCILLIN-P 4.5 INJ</t>
   </si>
   <si>
@@ -739,15 +739,15 @@
     <t>AMLINA-5 TABLET</t>
   </si>
   <si>
+    <t>T60096A</t>
+  </si>
+  <si>
+    <t>20X30</t>
+  </si>
+  <si>
     <t>T50499A</t>
   </si>
   <si>
-    <t>20X30</t>
-  </si>
-  <si>
-    <t>T60096A</t>
-  </si>
-  <si>
     <t>AMLINA-AT TABLET</t>
   </si>
   <si>
@@ -775,12 +775,12 @@
     <t>DICLODARD-MR TABLET</t>
   </si>
   <si>
+    <t>MT2602058B</t>
+  </si>
+  <si>
     <t>MT2510403A</t>
   </si>
   <si>
-    <t>MT2602058B</t>
-  </si>
-  <si>
     <t>DICLODARD-P TABLET</t>
   </si>
   <si>
@@ -1156,21 +1156,21 @@
     <t>Faropharm 200 Tablet</t>
   </si>
   <si>
+    <t>CBT25115D</t>
+  </si>
+  <si>
     <t>CBT26001B</t>
   </si>
   <si>
-    <t>CBT25115D</t>
-  </si>
-  <si>
     <t>EPODOX-200 DT Tablet</t>
   </si>
   <si>
+    <t>CT26107C</t>
+  </si>
+  <si>
     <t>CT25507F</t>
   </si>
   <si>
-    <t>CT26107C</t>
-  </si>
-  <si>
     <t>ATROLIA - F TABLET</t>
   </si>
   <si>
@@ -1261,21 +1261,21 @@
     <t>CEFIXLIA-O 200 TABLET</t>
   </si>
   <si>
+    <t>CT25488B</t>
+  </si>
+  <si>
     <t>CT26007G</t>
   </si>
   <si>
-    <t>CT25488B</t>
-  </si>
-  <si>
     <t>MONTALIA-LC 60ML SYRUP</t>
   </si>
   <si>
+    <t>DL602011A</t>
+  </si>
+  <si>
     <t>60 ML</t>
   </si>
   <si>
-    <t>DL602011A</t>
-  </si>
-  <si>
     <t>CLAVMYCIN 375 DUO TABLET (20x1x10)</t>
   </si>
   <si>
@@ -1297,21 +1297,18 @@
     <t>50046010</t>
   </si>
   <si>
-    <t>50045258</t>
-  </si>
-  <si>
     <t>CT25512H</t>
   </si>
   <si>
     <t>CEFIXLIA - 200 DT TABLET</t>
   </si>
   <si>
+    <t>CT26039A</t>
+  </si>
+  <si>
     <t>CT25427</t>
   </si>
   <si>
-    <t>CT26039A</t>
-  </si>
-  <si>
     <t>FERRIFINE XT TABLET</t>
   </si>
   <si>
@@ -1327,24 +1324,24 @@
     <t>EPODOX 50 DRY SYRUP (Glass Bottle)</t>
   </si>
   <si>
+    <t>CD26083B</t>
+  </si>
+  <si>
     <t>30ML + SWFI</t>
   </si>
   <si>
-    <t>CD26083B</t>
-  </si>
-  <si>
     <t>VOLOPAIN AQ INJECTION</t>
   </si>
   <si>
+    <t>NL3062501</t>
+  </si>
+  <si>
+    <t>20 X 5 X 1ML</t>
+  </si>
+  <si>
     <t>NL3062502</t>
   </si>
   <si>
-    <t>20 X 5 X 1ML</t>
-  </si>
-  <si>
-    <t>NL3062501</t>
-  </si>
-  <si>
     <t>MONTALIA-LC 30ML SYRUP</t>
   </si>
   <si>
@@ -1393,19 +1390,19 @@
     <t>Item Name</t>
   </si>
   <si>
-    <t>Unrestricted Qty</t>
-  </si>
-  <si>
     <t>PACK STYLE</t>
   </si>
   <si>
     <t>Sales Unit</t>
   </si>
   <si>
-    <t>Batch No.</t>
-  </si>
-  <si>
     <t>Expiry</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Batch No.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Unrestricted Qty</t>
   </si>
 </sst>
 </file>
@@ -1436,13 +1433,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1478,10 +1475,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1571,7 +1568,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1623,7 +1620,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1845,73 +1842,77 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G248"/>
+  <dimension ref="A1:G247"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.21875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="32.6640625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="14.109375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="15.109375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="14.88671875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="12" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.88671875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="2"/>
+    <col min="1" max="1" width="13" style="1" customWidth="1"/>
+    <col min="2" max="2" width="33.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.5546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.21875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>456</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="E1" s="6" t="s">
         <v>457</v>
       </c>
-      <c r="C1" s="6" t="s">
-        <v>462</v>
-      </c>
-      <c r="D1" s="6" t="s">
+      <c r="F1" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="G1" s="7" t="s">
         <v>461</v>
       </c>
-      <c r="E1" s="6" t="s">
-        <v>459</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>458</v>
-      </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
+      <c r="A2" s="2">
         <v>6010000095</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="9" t="s">
+      <c r="C2" s="4">
+        <v>46559</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="11"/>
+      <c r="F2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="5">
+        <v>920</v>
+      </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
+      <c r="A3" s="2">
         <v>6010000095</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>234</v>
       </c>
       <c r="C3" s="4">
-        <v>46559</v>
+        <v>46568</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>22</v>
@@ -1920,34 +1921,30 @@
         <v>5</v>
       </c>
       <c r="G3" s="5">
-        <v>920</v>
+        <v>5460</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
+      <c r="A4" s="8">
         <v>6010000095</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="C4" s="4">
-        <v>46568</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="E4" s="3" t="s">
+      <c r="C4" s="10"/>
+      <c r="D4" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G4" s="5">
-        <v>5460</v>
-      </c>
+      <c r="F4" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="11"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
+      <c r="A5" s="2">
         <v>6010000096</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -1989,7 +1986,7 @@
       <c r="G6" s="11"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
+      <c r="A7" s="2">
         <v>6010000138</v>
       </c>
       <c r="B7" s="3" t="s">
@@ -2012,7 +2009,7 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
+      <c r="A8" s="2">
         <v>4010015107</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -2035,7 +2032,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
+      <c r="A9" s="2">
         <v>4010013476</v>
       </c>
       <c r="B9" s="3" t="s">
@@ -2058,14 +2055,14 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
+      <c r="A10" s="2">
         <v>6010000097</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>239</v>
       </c>
       <c r="C10" s="4">
-        <v>46556</v>
+        <v>46751</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>240</v>
@@ -2077,18 +2074,18 @@
         <v>5</v>
       </c>
       <c r="G10" s="5">
-        <v>300</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
+      <c r="A11" s="2">
         <v>6010000097</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>239</v>
       </c>
       <c r="C11" s="4">
-        <v>46751</v>
+        <v>46556</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>242</v>
@@ -2100,11 +2097,11 @@
         <v>5</v>
       </c>
       <c r="G11" s="5">
-        <v>160</v>
+        <v>300</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
+      <c r="A12" s="2">
         <v>6010000098</v>
       </c>
       <c r="B12" s="3" t="s">
@@ -2127,7 +2124,7 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
+      <c r="A13" s="2">
         <v>6010000195</v>
       </c>
       <c r="B13" s="3" t="s">
@@ -2150,7 +2147,7 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
+      <c r="A14" s="2">
         <v>4010013259</v>
       </c>
       <c r="B14" s="3" t="s">
@@ -2173,14 +2170,14 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
+      <c r="A15" s="2">
         <v>4010013260</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="4">
-        <v>46568</v>
+        <v>46589</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>10</v>
@@ -2192,18 +2189,18 @@
         <v>5</v>
       </c>
       <c r="G15" s="5">
-        <v>570</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
+      <c r="A16" s="2">
         <v>4010013260</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="4">
-        <v>46589</v>
+        <v>46568</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>12</v>
@@ -2215,11 +2212,11 @@
         <v>5</v>
       </c>
       <c r="G16" s="5">
-        <v>1200</v>
+        <v>570</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
+      <c r="A17" s="2">
         <v>4010013692</v>
       </c>
       <c r="B17" s="3" t="s">
@@ -2242,7 +2239,7 @@
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
+      <c r="A18" s="2">
         <v>4010013693</v>
       </c>
       <c r="B18" s="3" t="s">
@@ -2265,7 +2262,7 @@
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
+      <c r="A19" s="2">
         <v>4010013693</v>
       </c>
       <c r="B19" s="3" t="s">
@@ -2288,49 +2285,49 @@
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
+      <c r="A20" s="8">
         <v>4010013578</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="C20" s="4">
+      <c r="C20" s="10"/>
+      <c r="D20" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G20" s="11"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>4010013578</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21" s="4">
         <v>46640</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E21" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G20" s="5">
+      <c r="F21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G21" s="5">
         <v>270</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="8">
-        <v>4010013578</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="C21" s="10"/>
-      <c r="D21" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G21" s="11"/>
-    </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
+      <c r="A22" s="2">
         <v>4010013580</v>
       </c>
       <c r="B22" s="3" t="s">
@@ -2353,7 +2350,7 @@
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
+      <c r="A23" s="2">
         <v>4010013551</v>
       </c>
       <c r="B23" s="3" t="s">
@@ -2376,7 +2373,7 @@
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
+      <c r="A24" s="2">
         <v>4010013660</v>
       </c>
       <c r="B24" s="3" t="s">
@@ -2399,7 +2396,7 @@
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
+      <c r="A25" s="2">
         <v>4010013694</v>
       </c>
       <c r="B25" s="3" t="s">
@@ -2441,7 +2438,7 @@
       <c r="G26" s="11"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
+      <c r="A27" s="2">
         <v>6010000065</v>
       </c>
       <c r="B27" s="3" t="s">
@@ -2464,7 +2461,7 @@
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
+      <c r="A28" s="2">
         <v>4010013581</v>
       </c>
       <c r="B28" s="3" t="s">
@@ -2506,18 +2503,18 @@
       <c r="G29" s="11"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="1">
+      <c r="A30" s="2">
         <v>7050000018</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C30" s="4"/>
       <c r="D30" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>3</v>
@@ -2527,18 +2524,18 @@
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="1">
+      <c r="A31" s="2">
         <v>7050000016</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C31" s="4"/>
       <c r="D31" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>3</v>
@@ -2548,18 +2545,18 @@
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="1">
+      <c r="A32" s="2">
         <v>7050000015</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C32" s="4"/>
       <c r="D32" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>3</v>
@@ -2569,18 +2566,18 @@
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="1">
+      <c r="A33" s="2">
         <v>7050000014</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C33" s="4"/>
       <c r="D33" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>3</v>
@@ -2590,18 +2587,18 @@
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="1">
+      <c r="A34" s="2">
         <v>7050000017</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C34" s="4"/>
       <c r="D34" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>3</v>
@@ -2611,49 +2608,49 @@
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="1">
+      <c r="A35" s="8">
         <v>4010013550</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C35" s="4">
+      <c r="C35" s="10"/>
+      <c r="D35" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G35" s="11"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
+        <v>4010013550</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C36" s="4">
         <v>46568</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="D36" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E35" s="3" t="s">
+      <c r="E36" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G35" s="5">
+      <c r="F36" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G36" s="5">
         <v>1070</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="8">
-        <v>4010013550</v>
-      </c>
-      <c r="B36" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C36" s="10"/>
-      <c r="D36" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="E36" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G36" s="11"/>
-    </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="1">
+      <c r="A37" s="2">
         <v>4010013478</v>
       </c>
       <c r="B37" s="3" t="s">
@@ -2695,7 +2692,7 @@
       <c r="G38" s="11"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="1">
+      <c r="A39" s="2">
         <v>6010000154</v>
       </c>
       <c r="B39" s="3" t="s">
@@ -2718,7 +2715,7 @@
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="1">
+      <c r="A40" s="2">
         <v>6010000158</v>
       </c>
       <c r="B40" s="3" t="s">
@@ -2798,7 +2795,7 @@
       <c r="G43" s="11"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="1">
+      <c r="A44" s="2">
         <v>6010000160</v>
       </c>
       <c r="B44" s="3" t="s">
@@ -2821,7 +2818,7 @@
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="1">
+      <c r="A45" s="2">
         <v>6010000100</v>
       </c>
       <c r="B45" s="3" t="s">
@@ -2844,17 +2841,17 @@
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="1">
+      <c r="A46" s="2">
         <v>6010000234</v>
       </c>
       <c r="B46" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="C46" s="4">
+        <v>46726</v>
+      </c>
+      <c r="D46" s="3" t="s">
         <v>428</v>
-      </c>
-      <c r="C46" s="4">
-        <v>46661</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>429</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>22</v>
@@ -2863,21 +2860,21 @@
         <v>5</v>
       </c>
       <c r="G46" s="5">
-        <v>340</v>
+        <v>7920</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="1">
+      <c r="A47" s="2">
         <v>6010000234</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C47" s="4">
-        <v>46726</v>
+        <v>46661</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>22</v>
@@ -2886,21 +2883,21 @@
         <v>5</v>
       </c>
       <c r="G47" s="5">
-        <v>7920</v>
+        <v>340</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="1">
+      <c r="A48" s="2">
         <v>6010000239</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C48" s="4">
         <v>46507</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>377</v>
@@ -2913,30 +2910,26 @@
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="1">
+      <c r="A49" s="8">
         <v>6010000217</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="B49" s="9" t="s">
         <v>413</v>
       </c>
-      <c r="C49" s="4">
-        <v>46751</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="E49" s="3" t="s">
+      <c r="C49" s="10"/>
+      <c r="D49" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E49" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="F49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G49" s="5">
-        <v>10</v>
-      </c>
+      <c r="F49" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G49" s="11"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="1">
+      <c r="A50" s="2">
         <v>6010000217</v>
       </c>
       <c r="B50" s="3" t="s">
@@ -2946,7 +2939,7 @@
         <v>46721</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>29</v>
@@ -2959,23 +2952,27 @@
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="8">
+      <c r="A51" s="2">
         <v>6010000217</v>
       </c>
-      <c r="B51" s="9" t="s">
+      <c r="B51" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="C51" s="10"/>
-      <c r="D51" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="E51" s="9" t="s">
+      <c r="C51" s="4">
+        <v>46751</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="E51" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F51" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G51" s="11"/>
+      <c r="F51" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G51" s="5">
+        <v>10</v>
+      </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="8">
@@ -2997,56 +2994,56 @@
       <c r="G52" s="11"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="8">
+      <c r="A53" s="2">
         <v>6010000071</v>
       </c>
-      <c r="B53" s="9" t="s">
+      <c r="B53" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C53" s="10"/>
-      <c r="D53" s="9" t="s">
+      <c r="C53" s="4">
+        <v>46797</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G53" s="5">
+        <v>4050</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="8">
+        <v>6010000071</v>
+      </c>
+      <c r="B54" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="C54" s="10"/>
+      <c r="D54" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E53" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="F53" s="9" t="s">
+      <c r="E54" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="F54" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="G53" s="11"/>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="1">
-        <v>6010000071</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="C54" s="4">
-        <v>46797</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G54" s="5">
-        <v>8050</v>
-      </c>
+      <c r="G54" s="11"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="1">
+      <c r="A55" s="2">
         <v>4010013389</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>37</v>
       </c>
       <c r="C55" s="4">
-        <v>46621</v>
+        <v>46681</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>38</v>
@@ -3058,18 +3055,18 @@
         <v>5</v>
       </c>
       <c r="G55" s="5">
-        <v>510</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="1">
+      <c r="A56" s="2">
         <v>4010013389</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>37</v>
       </c>
       <c r="C56" s="4">
-        <v>46681</v>
+        <v>46621</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>40</v>
@@ -3081,11 +3078,11 @@
         <v>5</v>
       </c>
       <c r="G56" s="5">
-        <v>1120</v>
+        <v>510</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="1">
+      <c r="A57" s="2">
         <v>4010013266</v>
       </c>
       <c r="B57" s="3" t="s">
@@ -3108,7 +3105,7 @@
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="1">
+      <c r="A58" s="2">
         <v>4010013267</v>
       </c>
       <c r="B58" s="3" t="s">
@@ -3131,7 +3128,7 @@
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="1">
+      <c r="A59" s="2">
         <v>4010013553</v>
       </c>
       <c r="B59" s="3" t="s">
@@ -3154,7 +3151,7 @@
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="1">
+      <c r="A60" s="2">
         <v>4010013397</v>
       </c>
       <c r="B60" s="3" t="s">
@@ -3177,7 +3174,7 @@
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="1">
+      <c r="A61" s="2">
         <v>6010000189</v>
       </c>
       <c r="B61" s="3" t="s">
@@ -3200,7 +3197,7 @@
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="1">
+      <c r="A62" s="2">
         <v>6010000224</v>
       </c>
       <c r="B62" s="3" t="s">
@@ -3223,7 +3220,7 @@
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="1">
+      <c r="A63" s="2">
         <v>6010000101</v>
       </c>
       <c r="B63" s="3" t="s">
@@ -3246,7 +3243,7 @@
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="1">
+      <c r="A64" s="2">
         <v>6010000101</v>
       </c>
       <c r="B64" s="3" t="s">
@@ -3269,7 +3266,7 @@
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="1">
+      <c r="A65" s="2">
         <v>6010000232</v>
       </c>
       <c r="B65" s="3" t="s">
@@ -3288,67 +3285,67 @@
         <v>5</v>
       </c>
       <c r="G65" s="5">
-        <v>14400</v>
+        <v>2840</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="1">
-        <v>6010000232</v>
+      <c r="A66" s="2">
+        <v>6010000073</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>424</v>
+        <v>182</v>
       </c>
       <c r="C66" s="4">
-        <v>46692</v>
+        <v>46511</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>426</v>
+        <v>183</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>15</v>
+        <v>184</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G66" s="5">
-        <v>2840</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A67" s="1">
-        <v>6010000073</v>
+      <c r="A67" s="2">
+        <v>6010000169</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>182</v>
+        <v>351</v>
       </c>
       <c r="C67" s="4">
-        <v>46511</v>
+        <v>46751</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>183</v>
+        <v>352</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>184</v>
+        <v>107</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G67" s="5">
-        <v>1630</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="1">
-        <v>6010000169</v>
+      <c r="A68" s="2">
+        <v>6010000170</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C68" s="4">
-        <v>46751</v>
+        <v>46721</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>107</v>
@@ -3357,145 +3354,141 @@
         <v>5</v>
       </c>
       <c r="G68" s="5">
-        <v>2110</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="1">
-        <v>6010000170</v>
+      <c r="A69" s="2">
+        <v>6010000139</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>353</v>
+        <v>308</v>
       </c>
       <c r="C69" s="4">
-        <v>46721</v>
+        <v>46711</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>354</v>
+        <v>309</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>107</v>
+        <v>310</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G69" s="5">
-        <v>2590</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="1">
-        <v>6010000139</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="C70" s="4">
-        <v>46711</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="E70" s="3" t="s">
+      <c r="A70" s="8">
+        <v>6010000267</v>
+      </c>
+      <c r="B70" s="9" t="s">
+        <v>445</v>
+      </c>
+      <c r="C70" s="10"/>
+      <c r="D70" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E70" s="9" t="s">
+        <v>446</v>
+      </c>
+      <c r="F70" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="G70" s="11"/>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="2">
+        <v>6010000141</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C71" s="4">
+        <v>46746</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E71" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="F70" s="3" t="s">
+      <c r="F71" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G70" s="5">
-        <v>1488</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="8">
-        <v>6010000267</v>
-      </c>
-      <c r="B71" s="9" t="s">
-        <v>446</v>
-      </c>
-      <c r="C71" s="10"/>
-      <c r="D71" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="E71" s="9" t="s">
-        <v>447</v>
-      </c>
-      <c r="F71" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="G71" s="11"/>
+      <c r="G71" s="5">
+        <v>2425</v>
+      </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="1">
-        <v>6010000141</v>
+      <c r="A72" s="2">
+        <v>6010000205</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>311</v>
+        <v>403</v>
       </c>
       <c r="C72" s="4">
-        <v>46746</v>
+        <v>46692</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>312</v>
+        <v>404</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>310</v>
+        <v>405</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G72" s="5">
-        <v>2425</v>
+        <v>12750</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="1">
-        <v>6010000205</v>
+      <c r="A73" s="2">
+        <v>4010013583</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>403</v>
+        <v>92</v>
       </c>
       <c r="C73" s="4">
-        <v>46692</v>
+        <v>46504</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>404</v>
+        <v>93</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>405</v>
+        <v>71</v>
       </c>
       <c r="F73" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G73" s="5">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" s="8">
+        <v>6010000074</v>
+      </c>
+      <c r="B74" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="C74" s="10"/>
+      <c r="D74" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E74" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="F74" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="G73" s="5">
-        <v>12750</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="1">
-        <v>4010013583</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C74" s="4">
-        <v>46504</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="E74" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F74" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G74" s="5">
-        <v>620</v>
-      </c>
+      <c r="G74" s="11"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="1">
+      <c r="A75" s="2">
         <v>6010000074</v>
       </c>
       <c r="B75" s="3" t="s">
@@ -3505,10 +3498,10 @@
         <v>46721</v>
       </c>
       <c r="D75" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E75" s="3" t="s">
         <v>186</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>187</v>
       </c>
       <c r="F75" s="3" t="s">
         <v>3</v>
@@ -3518,7 +3511,7 @@
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="1">
+      <c r="A76" s="2">
         <v>6010000074</v>
       </c>
       <c r="B76" s="3" t="s">
@@ -3531,88 +3524,92 @@
         <v>188</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G76" s="5">
-        <v>768</v>
+        <v>288</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="8">
-        <v>6010000074</v>
-      </c>
-      <c r="B77" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="C77" s="10"/>
-      <c r="D77" s="9" t="s">
+      <c r="A77" s="2">
+        <v>6010000102</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C77" s="4">
+        <v>46780</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G77" s="5">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" s="8">
+        <v>6010000102</v>
+      </c>
+      <c r="B78" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="C78" s="10"/>
+      <c r="D78" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E77" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="F77" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="G77" s="11"/>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="1">
+      <c r="E78" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F78" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G78" s="11"/>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" s="2">
         <v>6010000102</v>
       </c>
-      <c r="B78" s="3" t="s">
+      <c r="B79" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="C78" s="4">
+      <c r="C79" s="4">
         <v>46631</v>
       </c>
-      <c r="D78" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="E78" s="3" t="s">
+      <c r="D79" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E79" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F78" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G78" s="5">
+      <c r="F79" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G79" s="5">
         <v>920</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="8">
-        <v>6010000102</v>
-      </c>
-      <c r="B79" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="C79" s="10"/>
-      <c r="D79" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="E79" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F79" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G79" s="11"/>
-    </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="1">
-        <v>6010000102</v>
+      <c r="A80" s="2">
+        <v>6010000103</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C80" s="4">
-        <v>46780</v>
+        <v>46645</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>22</v>
@@ -3621,122 +3618,122 @@
         <v>5</v>
       </c>
       <c r="G80" s="5">
-        <v>3200</v>
+        <v>2920</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A81" s="1">
-        <v>6010000103</v>
+      <c r="A81" s="2">
+        <v>6010000196</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>254</v>
+        <v>386</v>
       </c>
       <c r="C81" s="4">
-        <v>46645</v>
+        <v>46606</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>255</v>
+        <v>387</v>
       </c>
       <c r="E81" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G81" s="5">
+        <v>1840</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A82" s="2">
+        <v>6010000104</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="C82" s="4">
+        <v>46429</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="E82" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G81" s="5">
-        <v>2920</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="1">
-        <v>6010000196</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="C82" s="4">
-        <v>46606</v>
-      </c>
-      <c r="D82" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="E82" s="3" t="s">
-        <v>388</v>
-      </c>
       <c r="F82" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G82" s="5">
-        <v>1840</v>
+        <v>40</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="1">
-        <v>6010000104</v>
+      <c r="A83" s="2">
+        <v>4010013473</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>256</v>
+        <v>50</v>
       </c>
       <c r="C83" s="4">
-        <v>46429</v>
+        <v>46524</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>257</v>
+        <v>51</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G83" s="5">
-        <v>40</v>
+        <v>420</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="1">
-        <v>4010013473</v>
+      <c r="A84" s="2">
+        <v>6010000151</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>50</v>
+        <v>329</v>
       </c>
       <c r="C84" s="4">
-        <v>46524</v>
+        <v>46692</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>51</v>
+        <v>330</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>29</v>
+        <v>331</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G84" s="5">
-        <v>420</v>
+        <v>595</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="1">
-        <v>6010000151</v>
+      <c r="A85" s="2">
+        <v>6010000241</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>329</v>
+        <v>434</v>
       </c>
       <c r="C85" s="4">
-        <v>46692</v>
+        <v>46596</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>330</v>
+        <v>435</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>331</v>
+        <v>436</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G85" s="5">
-        <v>595</v>
+        <v>162</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -3744,7 +3741,7 @@
         <v>6010000241</v>
       </c>
       <c r="B86" s="9" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C86" s="10"/>
       <c r="D86" s="9" t="s">
@@ -3759,30 +3756,30 @@
       <c r="G86" s="11"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="1">
-        <v>6010000241</v>
+      <c r="A87" s="2">
+        <v>6010000194</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>435</v>
+        <v>381</v>
       </c>
       <c r="C87" s="4">
-        <v>46596</v>
+        <v>46803</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>437</v>
+        <v>382</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>436</v>
+        <v>29</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G87" s="5">
-        <v>162</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="1">
+      <c r="A88" s="2">
         <v>6010000194</v>
       </c>
       <c r="B88" s="3" t="s">
@@ -3792,7 +3789,7 @@
         <v>46721</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>29</v>
@@ -3805,106 +3802,102 @@
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="1">
-        <v>6010000194</v>
+      <c r="A89" s="2">
+        <v>6010000192</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="C89" s="4">
-        <v>46803</v>
+        <v>46367</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="E89" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G89" s="5">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A90" s="2">
+        <v>6010000155</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="C90" s="4">
+        <v>46447</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="E90" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G89" s="5">
-        <v>1470</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="1">
-        <v>6010000192</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="C90" s="4">
-        <v>46367</v>
-      </c>
-      <c r="D90" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="E90" s="3" t="s">
-        <v>377</v>
-      </c>
       <c r="F90" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G90" s="5">
-        <v>365</v>
+        <v>400</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="1">
-        <v>6010000155</v>
+      <c r="A91" s="2">
+        <v>6010000108</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>335</v>
+        <v>258</v>
       </c>
       <c r="C91" s="4">
-        <v>46447</v>
+        <v>46574</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>336</v>
+        <v>259</v>
       </c>
       <c r="E91" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G91" s="5">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A92" s="8">
+        <v>6010000193</v>
+      </c>
+      <c r="B92" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="C92" s="10"/>
+      <c r="D92" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E92" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G91" s="5">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="1">
-        <v>6010000108</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="C92" s="4">
-        <v>46574</v>
-      </c>
-      <c r="D92" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="E92" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F92" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G92" s="5">
-        <v>560</v>
-      </c>
+      <c r="F92" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G92" s="11"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="1">
+      <c r="A93" s="2">
         <v>6010000193</v>
       </c>
       <c r="B93" s="3" t="s">
         <v>378</v>
       </c>
       <c r="C93" s="4">
-        <v>46726</v>
+        <v>46711</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>379</v>
@@ -3916,40 +3909,44 @@
         <v>5</v>
       </c>
       <c r="G93" s="5">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A94" s="2">
+        <v>6010000193</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C94" s="4">
+        <v>46726</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G94" s="5">
         <v>80</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="8">
-        <v>6010000193</v>
-      </c>
-      <c r="B94" s="9" t="s">
-        <v>378</v>
-      </c>
-      <c r="C94" s="10"/>
-      <c r="D94" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="E94" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="F94" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G94" s="11"/>
-    </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="1">
-        <v>6010000193</v>
+      <c r="A95" s="2">
+        <v>6010000216</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>378</v>
+        <v>411</v>
       </c>
       <c r="C95" s="4">
-        <v>46711</v>
+        <v>46690</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>380</v>
+        <v>412</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>29</v>
@@ -3958,57 +3955,57 @@
         <v>5</v>
       </c>
       <c r="G95" s="5">
-        <v>250</v>
+        <v>170</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="1">
-        <v>6010000216</v>
+      <c r="A96" s="2">
+        <v>6010000235</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>411</v>
+        <v>430</v>
       </c>
       <c r="C96" s="4">
-        <v>46690</v>
+        <v>46808</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>412</v>
+        <v>431</v>
       </c>
       <c r="E96" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G96" s="5">
+        <v>3040</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A97" s="2">
+        <v>4010013662</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C97" s="4">
+        <v>46537</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E97" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G96" s="5">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="1">
-        <v>6010000235</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>431</v>
-      </c>
-      <c r="C97" s="4">
-        <v>46808</v>
-      </c>
-      <c r="D97" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="E97" s="3" t="s">
-        <v>15</v>
-      </c>
       <c r="F97" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G97" s="5">
-        <v>3040</v>
+        <v>290</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" s="1">
+      <c r="A98" s="2">
         <v>4010013662</v>
       </c>
       <c r="B98" s="3" t="s">
@@ -4018,7 +4015,7 @@
         <v>46546</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>29</v>
@@ -4031,63 +4028,63 @@
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" s="1">
-        <v>4010013662</v>
+      <c r="A99" s="2">
+        <v>6010000076</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>136</v>
+        <v>189</v>
       </c>
       <c r="C99" s="4">
-        <v>46537</v>
+        <v>46483</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>138</v>
+        <v>190</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>29</v>
+        <v>186</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G99" s="5">
-        <v>290</v>
+        <v>3076</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="1">
-        <v>6010000076</v>
+      <c r="A100" s="2">
+        <v>6010000110</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>189</v>
+        <v>260</v>
       </c>
       <c r="C100" s="4">
-        <v>46483</v>
+        <v>46640</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>190</v>
+        <v>261</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>187</v>
+        <v>4</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G100" s="5">
-        <v>3076</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="1">
-        <v>6010000110</v>
+      <c r="A101" s="2">
+        <v>6010000111</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C101" s="4">
         <v>46640</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>4</v>
@@ -4096,44 +4093,44 @@
         <v>5</v>
       </c>
       <c r="G101" s="5">
-        <v>1100</v>
+        <v>2640</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="1">
-        <v>6010000111</v>
+      <c r="A102" s="2">
+        <v>4010013584</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>262</v>
+        <v>94</v>
       </c>
       <c r="C102" s="4">
-        <v>46640</v>
+        <v>46537</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>263</v>
+        <v>95</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>4</v>
+        <v>88</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G102" s="5">
-        <v>2640</v>
+        <v>380</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="1">
+      <c r="A103" s="2">
         <v>4010013584</v>
       </c>
       <c r="B103" s="3" t="s">
         <v>94</v>
       </c>
       <c r="C103" s="4">
-        <v>46537</v>
+        <v>46532</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E103" s="3" t="s">
         <v>88</v>
@@ -4142,21 +4139,21 @@
         <v>5</v>
       </c>
       <c r="G103" s="5">
-        <v>380</v>
+        <v>500</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="1">
-        <v>4010013584</v>
+      <c r="A104" s="2">
+        <v>6010000171</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>94</v>
+        <v>355</v>
       </c>
       <c r="C104" s="4">
-        <v>46532</v>
+        <v>46579</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>96</v>
+        <v>356</v>
       </c>
       <c r="E104" s="3" t="s">
         <v>88</v>
@@ -4165,21 +4162,21 @@
         <v>5</v>
       </c>
       <c r="G104" s="5">
-        <v>500</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="1">
-        <v>6010000171</v>
+      <c r="A105" s="2">
+        <v>4010013585</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>355</v>
+        <v>97</v>
       </c>
       <c r="C105" s="4">
-        <v>46579</v>
+        <v>46568</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>356</v>
+        <v>98</v>
       </c>
       <c r="E105" s="3" t="s">
         <v>88</v>
@@ -4192,17 +4189,17 @@
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="1">
-        <v>4010013585</v>
+      <c r="A106" s="2">
+        <v>6010000172</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>97</v>
+        <v>357</v>
       </c>
       <c r="C106" s="4">
-        <v>46568</v>
+        <v>46579</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>98</v>
+        <v>358</v>
       </c>
       <c r="E106" s="3" t="s">
         <v>88</v>
@@ -4211,113 +4208,113 @@
         <v>5</v>
       </c>
       <c r="G106" s="5">
-        <v>1500</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="1">
-        <v>6010000172</v>
+      <c r="A107" s="2">
+        <v>6010000077</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>357</v>
+        <v>191</v>
       </c>
       <c r="C107" s="4">
-        <v>46579</v>
+        <v>46471</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>358</v>
+        <v>192</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>88</v>
+        <v>193</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G107" s="5">
-        <v>1700</v>
+        <v>5520</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="1">
-        <v>6010000077</v>
+      <c r="A108" s="2">
+        <v>6010000078</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C108" s="4">
-        <v>46471</v>
+        <v>46780</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="F108" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G108" s="5">
-        <v>5520</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="1">
-        <v>6010000078</v>
+      <c r="A109" s="2">
+        <v>6010000079</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C109" s="4">
-        <v>46780</v>
+        <v>46512</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F109" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G109" s="5">
-        <v>11200</v>
+        <v>660</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A110" s="1">
-        <v>6010000079</v>
+      <c r="A110" s="2">
+        <v>4010013593</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>197</v>
+        <v>108</v>
       </c>
       <c r="C110" s="4">
-        <v>46512</v>
+        <v>46758</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>198</v>
+        <v>109</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>199</v>
+        <v>29</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G110" s="5">
-        <v>660</v>
+        <v>560</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A111" s="1">
+      <c r="A111" s="2">
         <v>4010013593</v>
       </c>
       <c r="B111" s="3" t="s">
         <v>108</v>
       </c>
       <c r="C111" s="4">
-        <v>46758</v>
+        <v>46526</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E111" s="3" t="s">
         <v>29</v>
@@ -4326,21 +4323,21 @@
         <v>5</v>
       </c>
       <c r="G111" s="5">
-        <v>560</v>
+        <v>160</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A112" s="1">
-        <v>4010013593</v>
+      <c r="A112" s="2">
+        <v>4010014329</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>108</v>
+        <v>161</v>
       </c>
       <c r="C112" s="4">
-        <v>46526</v>
+        <v>46641</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>110</v>
+        <v>162</v>
       </c>
       <c r="E112" s="3" t="s">
         <v>29</v>
@@ -4349,21 +4346,21 @@
         <v>5</v>
       </c>
       <c r="G112" s="5">
-        <v>160</v>
+        <v>230</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A113" s="1">
-        <v>4010014329</v>
+      <c r="A113" s="2">
+        <v>4010013594</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>161</v>
+        <v>111</v>
       </c>
       <c r="C113" s="4">
-        <v>46641</v>
+        <v>46573</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>162</v>
+        <v>112</v>
       </c>
       <c r="E113" s="3" t="s">
         <v>29</v>
@@ -4372,21 +4369,21 @@
         <v>5</v>
       </c>
       <c r="G113" s="5">
-        <v>230</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A114" s="1">
-        <v>4010013594</v>
+      <c r="A114" s="2">
+        <v>4010014330</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>111</v>
+        <v>163</v>
       </c>
       <c r="C114" s="4">
-        <v>46573</v>
+        <v>46610</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>112</v>
+        <v>164</v>
       </c>
       <c r="E114" s="3" t="s">
         <v>29</v>
@@ -4395,21 +4392,21 @@
         <v>5</v>
       </c>
       <c r="G114" s="5">
-        <v>1070</v>
+        <v>280</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A115" s="1">
-        <v>4010014330</v>
+      <c r="A115" s="2">
+        <v>6010000156</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>163</v>
+        <v>337</v>
       </c>
       <c r="C115" s="4">
-        <v>46610</v>
+        <v>46447</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>164</v>
+        <v>338</v>
       </c>
       <c r="E115" s="3" t="s">
         <v>29</v>
@@ -4418,21 +4415,21 @@
         <v>5</v>
       </c>
       <c r="G115" s="5">
-        <v>280</v>
+        <v>300</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A116" s="1">
-        <v>6010000156</v>
+      <c r="A116" s="2">
+        <v>6010000233</v>
       </c>
       <c r="B116" s="3" t="s">
         <v>337</v>
       </c>
       <c r="C116" s="4">
-        <v>46447</v>
+        <v>46721</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>338</v>
+        <v>426</v>
       </c>
       <c r="E116" s="3" t="s">
         <v>29</v>
@@ -4441,80 +4438,80 @@
         <v>5</v>
       </c>
       <c r="G116" s="5">
-        <v>300</v>
+        <v>170</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A117" s="1">
-        <v>6010000233</v>
+      <c r="A117" s="2">
+        <v>6010000080</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>337</v>
+        <v>200</v>
       </c>
       <c r="C117" s="4">
-        <v>46721</v>
+        <v>46423</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>427</v>
+        <v>201</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>29</v>
+        <v>202</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G117" s="5">
-        <v>170</v>
+        <v>500</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A118" s="1">
-        <v>6010000080</v>
+      <c r="A118" s="2">
+        <v>6010000113</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>200</v>
+        <v>264</v>
       </c>
       <c r="C118" s="4">
-        <v>46423</v>
+        <v>46598</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>201</v>
+        <v>265</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>202</v>
+        <v>22</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G118" s="5">
-        <v>500</v>
+        <v>8640</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A119" s="1">
-        <v>6010000113</v>
+      <c r="A119" s="2">
+        <v>4010013656</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>264</v>
+        <v>123</v>
       </c>
       <c r="C119" s="4">
-        <v>46598</v>
+        <v>46510</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>265</v>
+        <v>124</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="F119" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G119" s="5">
-        <v>8640</v>
+        <v>2380</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A120" s="1">
+      <c r="A120" s="2">
         <v>4010013656</v>
       </c>
       <c r="B120" s="3" t="s">
@@ -4524,7 +4521,7 @@
         <v>46423</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E120" s="3" t="s">
         <v>125</v>
@@ -4537,151 +4534,151 @@
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A121" s="1">
-        <v>4010013656</v>
-      </c>
-      <c r="B121" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C121" s="4">
-        <v>46510</v>
-      </c>
-      <c r="D121" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="E121" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="F121" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G121" s="5">
-        <v>2380</v>
-      </c>
+      <c r="A121" s="8">
+        <v>4010013595</v>
+      </c>
+      <c r="B121" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="C121" s="10"/>
+      <c r="D121" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E121" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F121" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G121" s="11"/>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A122" s="8">
-        <v>4010013595</v>
-      </c>
-      <c r="B122" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="C122" s="10"/>
-      <c r="D122" s="9" t="s">
+      <c r="A122" s="2">
+        <v>6010000174</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="C122" s="4">
+        <v>46586</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="F122" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G122" s="5">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A123" s="2">
+        <v>6010000114</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C123" s="4">
+        <v>46488</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="E123" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="F123" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G123" s="5">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A124" s="2">
+        <v>6010000081</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C124" s="4">
+        <v>46660</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E124" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E122" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="F122" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G122" s="11"/>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A123" s="1">
-        <v>6010000174</v>
-      </c>
-      <c r="B123" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="C123" s="4">
-        <v>46586</v>
-      </c>
-      <c r="D123" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="E123" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="F123" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G123" s="5">
-        <v>1140</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A124" s="1">
-        <v>6010000114</v>
-      </c>
-      <c r="B124" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="C124" s="4">
-        <v>46488</v>
-      </c>
-      <c r="D124" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="E124" s="3" t="s">
-        <v>107</v>
-      </c>
       <c r="F124" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G124" s="5">
-        <v>2000</v>
+        <v>750</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A125" s="1">
-        <v>6010000081</v>
+      <c r="A125" s="2">
+        <v>6010000082</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C125" s="4">
-        <v>46660</v>
+        <v>46505</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>2</v>
+        <v>207</v>
       </c>
       <c r="F125" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G125" s="5">
-        <v>750</v>
+        <v>11100</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A126" s="1">
-        <v>6010000082</v>
+      <c r="A126" s="2">
+        <v>6010000175</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>205</v>
+        <v>362</v>
       </c>
       <c r="C126" s="4">
-        <v>46505</v>
+        <v>46556</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>206</v>
+        <v>363</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>207</v>
+        <v>364</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G126" s="5">
-        <v>11100</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A127" s="1">
-        <v>6010000175</v>
+      <c r="A127" s="2">
+        <v>6010000176</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C127" s="4">
-        <v>46556</v>
+        <v>46586</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="E127" s="3" t="s">
         <v>364</v>
@@ -4690,44 +4687,44 @@
         <v>5</v>
       </c>
       <c r="G127" s="5">
-        <v>1900</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A128" s="1">
-        <v>6010000176</v>
+      <c r="A128" s="2">
+        <v>6010000201</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>365</v>
+        <v>396</v>
       </c>
       <c r="C128" s="4">
-        <v>46586</v>
+        <v>46624</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>366</v>
+        <v>397</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>364</v>
+        <v>398</v>
       </c>
       <c r="F128" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G128" s="5">
-        <v>1980</v>
+        <v>910</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A129" s="1">
-        <v>6010000201</v>
+      <c r="A129" s="2">
+        <v>6010000202</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C129" s="4">
-        <v>46624</v>
+        <v>46685</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="E129" s="3" t="s">
         <v>398</v>
@@ -4736,44 +4733,44 @@
         <v>3</v>
       </c>
       <c r="G129" s="5">
-        <v>910</v>
+        <v>830</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A130" s="1">
-        <v>6010000202</v>
+      <c r="A130" s="2">
+        <v>4010013262</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="C130" s="4">
-        <v>46685</v>
+        <v>46549</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>400</v>
+        <v>14</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>398</v>
+        <v>15</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G130" s="5">
-        <v>830</v>
+        <v>420</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A131" s="1">
-        <v>4010013262</v>
+      <c r="A131" s="2">
+        <v>4010013465</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C131" s="4">
-        <v>46549</v>
+        <v>46637</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="E131" s="3" t="s">
         <v>15</v>
@@ -4782,122 +4779,122 @@
         <v>5</v>
       </c>
       <c r="G131" s="5">
-        <v>420</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A132" s="1">
-        <v>4010013465</v>
+      <c r="A132" s="2">
+        <v>4010013466</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C132" s="4">
-        <v>46637</v>
+        <v>46704</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E132" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F132" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G132" s="5">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A133" s="2">
+        <v>4010013671</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C133" s="4">
+        <v>46566</v>
+      </c>
+      <c r="D133" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E133" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F132" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G132" s="5">
-        <v>2120</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A133" s="1">
-        <v>4010013466</v>
-      </c>
-      <c r="B133" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C133" s="4">
-        <v>46704</v>
-      </c>
-      <c r="D133" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E133" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="F133" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G133" s="5">
-        <v>120</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A134" s="1">
-        <v>4010013671</v>
+      <c r="A134" s="2">
+        <v>6010000252</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>145</v>
+        <v>441</v>
       </c>
       <c r="C134" s="4">
-        <v>46566</v>
+        <v>46661</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>146</v>
+        <v>442</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>15</v>
+        <v>443</v>
       </c>
       <c r="F134" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G134" s="5">
-        <v>1380</v>
+        <v>690</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A135" s="1">
+      <c r="A135" s="2">
         <v>6010000252</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C135" s="4">
-        <v>46661</v>
+        <v>46780</v>
       </c>
       <c r="D135" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="E135" s="3" t="s">
         <v>443</v>
-      </c>
-      <c r="E135" s="3" t="s">
-        <v>444</v>
       </c>
       <c r="F135" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G135" s="5">
-        <v>690</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A136" s="1">
-        <v>6010000252</v>
+      <c r="A136" s="2">
+        <v>6010000218</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>442</v>
+        <v>416</v>
       </c>
       <c r="C136" s="4">
         <v>46780</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>445</v>
+        <v>417</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>444</v>
+        <v>418</v>
       </c>
       <c r="F136" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G136" s="5">
-        <v>1500</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
@@ -4912,7 +4909,7 @@
         <v>2</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>3</v>
@@ -4920,26 +4917,26 @@
       <c r="G137" s="11"/>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A138" s="1">
-        <v>6010000218</v>
+      <c r="A138" s="2">
+        <v>6010000083</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>416</v>
+        <v>208</v>
       </c>
       <c r="C138" s="4">
-        <v>46780</v>
+        <v>46537</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>418</v>
+        <v>209</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>417</v>
+        <v>210</v>
       </c>
       <c r="F138" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G138" s="5">
-        <v>1900</v>
+        <v>680</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
@@ -4954,7 +4951,7 @@
         <v>2</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>3</v>
@@ -4962,49 +4959,49 @@
       <c r="G139" s="11"/>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A140" s="1">
-        <v>6010000083</v>
+      <c r="A140" s="2">
+        <v>6010000084</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C140" s="4">
-        <v>46537</v>
+        <v>46711</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="F140" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G140" s="5">
-        <v>680</v>
+        <v>5980</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A141" s="1">
-        <v>6010000084</v>
+      <c r="A141" s="2">
+        <v>6010000115</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>211</v>
+        <v>268</v>
       </c>
       <c r="C141" s="4">
-        <v>46711</v>
+        <v>46971</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>212</v>
+        <v>269</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>213</v>
+        <v>22</v>
       </c>
       <c r="F141" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G141" s="5">
-        <v>5980</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -5027,103 +5024,103 @@
       <c r="G142" s="11"/>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A143" s="1">
-        <v>6010000115</v>
-      </c>
-      <c r="B143" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="C143" s="4">
+      <c r="A143" s="8">
+        <v>6010000116</v>
+      </c>
+      <c r="B143" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="C143" s="10"/>
+      <c r="D143" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E143" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F143" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G143" s="11"/>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A144" s="2">
+        <v>6010000116</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="C144" s="4">
         <v>46971</v>
       </c>
-      <c r="D143" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="E143" s="3" t="s">
+      <c r="D144" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="E144" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F144" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G144" s="5">
+        <v>3680</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A145" s="2">
+        <v>7050000019</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="C145" s="4"/>
+      <c r="D145" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E145" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F145" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G145" s="5">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A146" s="2">
+        <v>6010000117</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="C146" s="4">
+        <v>46711</v>
+      </c>
+      <c r="D146" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="E146" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F143" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G143" s="5">
-        <v>2300</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A144" s="8">
-        <v>6010000116</v>
-      </c>
-      <c r="B144" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="C144" s="10"/>
-      <c r="D144" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="E144" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="F144" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G144" s="11"/>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A145" s="1">
-        <v>6010000116</v>
-      </c>
-      <c r="B145" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="C145" s="4">
-        <v>46971</v>
-      </c>
-      <c r="D145" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="E145" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F145" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G145" s="5">
-        <v>3680</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A146" s="1">
-        <v>7050000019</v>
-      </c>
-      <c r="B146" s="3" t="s">
-        <v>454</v>
-      </c>
-      <c r="C146" s="4"/>
-      <c r="D146" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E146" s="3" t="s">
-        <v>2</v>
-      </c>
       <c r="F146" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G146" s="5">
-        <v>530</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A147" s="1">
-        <v>6010000117</v>
+      <c r="A147" s="2">
+        <v>6010000118</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C147" s="4">
-        <v>46711</v>
+        <v>46574</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E147" s="3" t="s">
         <v>22</v>
@@ -5132,21 +5129,21 @@
         <v>5</v>
       </c>
       <c r="G147" s="5">
-        <v>6100</v>
+        <v>10240</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A148" s="1">
-        <v>6010000118</v>
+      <c r="A148" s="2">
+        <v>6010000148</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>274</v>
+        <v>327</v>
       </c>
       <c r="C148" s="4">
-        <v>46574</v>
+        <v>46751</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>275</v>
+        <v>328</v>
       </c>
       <c r="E148" s="3" t="s">
         <v>22</v>
@@ -5155,346 +5152,346 @@
         <v>5</v>
       </c>
       <c r="G148" s="5">
-        <v>10240</v>
+        <v>2520</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A149" s="1">
-        <v>6010000148</v>
-      </c>
-      <c r="B149" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="C149" s="4">
-        <v>46751</v>
-      </c>
-      <c r="D149" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="E149" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F149" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G149" s="5">
-        <v>2520</v>
-      </c>
+      <c r="A149" s="8">
+        <v>6010000119</v>
+      </c>
+      <c r="B149" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="C149" s="10"/>
+      <c r="D149" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E149" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="F149" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G149" s="11"/>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="8">
-        <v>6010000119</v>
+        <v>6010000085</v>
       </c>
       <c r="B150" s="9" t="s">
-        <v>276</v>
+        <v>214</v>
       </c>
       <c r="C150" s="10"/>
       <c r="D150" s="9" t="s">
         <v>2</v>
       </c>
       <c r="E150" s="9" t="s">
-        <v>277</v>
+        <v>215</v>
       </c>
       <c r="F150" s="9" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G150" s="11"/>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A151" s="8">
+      <c r="A151" s="2">
         <v>6010000085</v>
       </c>
-      <c r="B151" s="9" t="s">
+      <c r="B151" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="C151" s="10"/>
-      <c r="D151" s="9" t="s">
+      <c r="C151" s="4">
+        <v>46388</v>
+      </c>
+      <c r="D151" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="E151" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="F151" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G151" s="5">
+        <v>31500</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A152" s="2">
+        <v>6010000123</v>
+      </c>
+      <c r="B152" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="C152" s="4">
+        <v>46752</v>
+      </c>
+      <c r="D152" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="E152" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F152" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G152" s="5">
+        <v>4960</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A153" s="8">
+        <v>6010000230</v>
+      </c>
+      <c r="B153" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="C153" s="10"/>
+      <c r="D153" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E151" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="F151" s="9" t="s">
+      <c r="E153" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F153" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G153" s="11"/>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A154" s="2">
+        <v>6010000086</v>
+      </c>
+      <c r="B154" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C154" s="4">
+        <v>46641</v>
+      </c>
+      <c r="D154" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="E154" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="F154" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G151" s="11"/>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A152" s="1">
-        <v>6010000085</v>
-      </c>
-      <c r="B152" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="C152" s="4">
-        <v>46388</v>
-      </c>
-      <c r="D152" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="E152" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="F152" s="3" t="s">
+      <c r="G154" s="5">
+        <v>9400</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A155" s="2">
+        <v>6010000125</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="C155" s="4">
+        <v>46574</v>
+      </c>
+      <c r="D155" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="E155" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F155" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G155" s="5">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A156" s="8">
+        <v>6010000147</v>
+      </c>
+      <c r="B156" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="C156" s="10"/>
+      <c r="D156" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E156" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="F156" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="G152" s="5">
-        <v>31500</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A153" s="1">
-        <v>6010000123</v>
-      </c>
-      <c r="B153" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="C153" s="4">
-        <v>46752</v>
-      </c>
-      <c r="D153" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="E153" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="F153" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G153" s="5">
-        <v>4960</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A154" s="8">
-        <v>6010000230</v>
-      </c>
-      <c r="B154" s="9" t="s">
-        <v>423</v>
-      </c>
-      <c r="C154" s="10"/>
-      <c r="D154" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="E154" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F154" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G154" s="11"/>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A155" s="1">
-        <v>6010000086</v>
-      </c>
-      <c r="B155" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="C155" s="4">
-        <v>46641</v>
-      </c>
-      <c r="D155" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="E155" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="F155" s="3" t="s">
+      <c r="G156" s="11"/>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A157" s="2">
+        <v>6010000144</v>
+      </c>
+      <c r="B157" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="C157" s="4">
+        <v>46605</v>
+      </c>
+      <c r="D157" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="E157" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="F157" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G155" s="5">
-        <v>9400</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A156" s="1">
-        <v>6010000125</v>
-      </c>
-      <c r="B156" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="C156" s="4">
-        <v>46574</v>
-      </c>
-      <c r="D156" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="E156" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F156" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G156" s="5">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A157" s="8">
-        <v>6010000147</v>
-      </c>
-      <c r="B157" s="9" t="s">
-        <v>326</v>
-      </c>
-      <c r="C157" s="10"/>
-      <c r="D157" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="E157" s="9" t="s">
-        <v>310</v>
-      </c>
-      <c r="F157" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="G157" s="11"/>
+      <c r="G157" s="5">
+        <v>890</v>
+      </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A158" s="1">
-        <v>6010000144</v>
+      <c r="A158" s="2">
+        <v>6010000214</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>318</v>
+        <v>406</v>
       </c>
       <c r="C158" s="4">
-        <v>46605</v>
+        <v>46692</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>319</v>
+        <v>407</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="F158" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G158" s="5">
-        <v>890</v>
+        <v>340</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A159" s="1">
-        <v>6010000214</v>
+      <c r="A159" s="2">
+        <v>6010000215</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C159" s="4">
-        <v>46692</v>
+        <v>46726</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
       <c r="F159" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G159" s="5">
-        <v>340</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A160" s="1">
-        <v>6010000215</v>
-      </c>
-      <c r="B160" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="C160" s="4">
-        <v>46726</v>
-      </c>
-      <c r="D160" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="E160" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="F160" s="3" t="s">
+      <c r="A160" s="8">
+        <v>6010000142</v>
+      </c>
+      <c r="B160" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="C160" s="10"/>
+      <c r="D160" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E160" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="F160" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="G160" s="5">
-        <v>1006</v>
-      </c>
+      <c r="G160" s="11"/>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A161" s="8">
-        <v>6010000142</v>
-      </c>
-      <c r="B161" s="9" t="s">
-        <v>313</v>
-      </c>
-      <c r="C161" s="10"/>
-      <c r="D161" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="E161" s="9" t="s">
-        <v>314</v>
-      </c>
-      <c r="F161" s="9" t="s">
+      <c r="A161" s="2">
+        <v>6010000143</v>
+      </c>
+      <c r="B161" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C161" s="4">
+        <v>46425</v>
+      </c>
+      <c r="D161" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="E161" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="F161" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G161" s="11"/>
+      <c r="G161" s="5">
+        <v>110</v>
+      </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A162" s="1">
-        <v>6010000143</v>
+      <c r="A162" s="2">
+        <v>6010000145</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="C162" s="4">
-        <v>46425</v>
+        <v>46556</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="F162" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G162" s="5">
-        <v>110</v>
+        <v>239</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A163" s="1">
-        <v>6010000145</v>
+      <c r="A163" s="2">
+        <v>4010013596</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>320</v>
+        <v>114</v>
       </c>
       <c r="C163" s="4">
-        <v>46556</v>
+        <v>46446</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>321</v>
+        <v>115</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>322</v>
+        <v>29</v>
       </c>
       <c r="F163" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G163" s="5">
-        <v>239</v>
+        <v>370</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A164" s="1">
-        <v>4010013596</v>
+      <c r="A164" s="2">
+        <v>4010013655</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C164" s="4">
-        <v>46446</v>
+        <v>46550</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="E164" s="3" t="s">
         <v>29</v>
@@ -5503,21 +5500,21 @@
         <v>5</v>
       </c>
       <c r="G164" s="5">
-        <v>370</v>
+        <v>950</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A165" s="1">
-        <v>4010013655</v>
+      <c r="A165" s="2">
+        <v>4010013474</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>121</v>
+        <v>52</v>
       </c>
       <c r="C165" s="4">
-        <v>46550</v>
+        <v>46511</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>122</v>
+        <v>53</v>
       </c>
       <c r="E165" s="3" t="s">
         <v>29</v>
@@ -5526,11 +5523,11 @@
         <v>5</v>
       </c>
       <c r="G165" s="5">
-        <v>950</v>
+        <v>290</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A166" s="1">
+      <c r="A166" s="2">
         <v>4010013474</v>
       </c>
       <c r="B166" s="3" t="s">
@@ -5540,7 +5537,7 @@
         <v>46579</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E166" s="3" t="s">
         <v>29</v>
@@ -5553,17 +5550,17 @@
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A167" s="1">
-        <v>4010013474</v>
+      <c r="A167" s="2">
+        <v>4010013475</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C167" s="4">
-        <v>46511</v>
+        <v>46525</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E167" s="3" t="s">
         <v>29</v>
@@ -5572,174 +5569,174 @@
         <v>5</v>
       </c>
       <c r="G167" s="5">
-        <v>290</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A168" s="1">
-        <v>4010013475</v>
-      </c>
-      <c r="B168" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C168" s="4">
-        <v>46525</v>
-      </c>
-      <c r="D168" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E168" s="3" t="s">
+      <c r="A168" s="8">
+        <v>6010000087</v>
+      </c>
+      <c r="B168" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="C168" s="10"/>
+      <c r="D168" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E168" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="F168" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="G168" s="11"/>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A169" s="2">
+        <v>6010000087</v>
+      </c>
+      <c r="B169" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C169" s="4">
+        <v>46388</v>
+      </c>
+      <c r="D169" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="E169" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="F169" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G169" s="5">
+        <v>14950</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A170" s="2">
+        <v>6010000126</v>
+      </c>
+      <c r="B170" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C170" s="4">
+        <v>46780</v>
+      </c>
+      <c r="D170" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="E170" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F170" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G170" s="5">
+        <v>5700</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A171" s="8">
+        <v>6010000227</v>
+      </c>
+      <c r="B171" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="C171" s="10"/>
+      <c r="D171" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E171" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F171" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G171" s="11"/>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A172" s="2">
+        <v>6010000227</v>
+      </c>
+      <c r="B172" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="C172" s="4">
+        <v>46645</v>
+      </c>
+      <c r="D172" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="E172" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F172" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G172" s="5">
+        <v>2240</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A173" s="2">
+        <v>6010000088</v>
+      </c>
+      <c r="B173" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C173" s="4">
+        <v>46661</v>
+      </c>
+      <c r="D173" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E173" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="F173" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G173" s="5">
+        <v>2660</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A174" s="2">
+        <v>4010013666</v>
+      </c>
+      <c r="B174" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C174" s="4">
+        <v>46625</v>
+      </c>
+      <c r="D174" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E174" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F168" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G168" s="5">
-        <v>1330</v>
-      </c>
-    </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A169" s="8">
-        <v>6010000087</v>
-      </c>
-      <c r="B169" s="9" t="s">
-        <v>220</v>
-      </c>
-      <c r="C169" s="10"/>
-      <c r="D169" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="E169" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="F169" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="G169" s="11"/>
-    </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A170" s="1">
-        <v>6010000087</v>
-      </c>
-      <c r="B170" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="C170" s="4">
-        <v>46388</v>
-      </c>
-      <c r="D170" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="E170" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="F170" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G170" s="5">
-        <v>14950</v>
-      </c>
-    </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A171" s="1">
-        <v>6010000126</v>
-      </c>
-      <c r="B171" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="C171" s="4">
-        <v>46780</v>
-      </c>
-      <c r="D171" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="E171" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F171" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G171" s="5">
-        <v>5700</v>
-      </c>
-    </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A172" s="8">
-        <v>6010000227</v>
-      </c>
-      <c r="B172" s="9" t="s">
-        <v>421</v>
-      </c>
-      <c r="C172" s="10"/>
-      <c r="D172" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="E172" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F172" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G172" s="11"/>
-    </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A173" s="1">
-        <v>6010000227</v>
-      </c>
-      <c r="B173" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="C173" s="4">
-        <v>46645</v>
-      </c>
-      <c r="D173" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="E173" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F173" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G173" s="5">
-        <v>2240</v>
-      </c>
-    </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A174" s="1">
-        <v>6010000088</v>
-      </c>
-      <c r="B174" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="C174" s="4">
-        <v>46661</v>
-      </c>
-      <c r="D174" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="E174" s="3" t="s">
-        <v>224</v>
-      </c>
       <c r="F174" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G174" s="5">
-        <v>2660</v>
+        <v>100</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A175" s="1">
+      <c r="A175" s="2">
         <v>4010013666</v>
       </c>
       <c r="B175" s="3" t="s">
         <v>142</v>
       </c>
       <c r="C175" s="4">
-        <v>46625</v>
+        <v>46593</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E175" s="3" t="s">
         <v>29</v>
@@ -5748,34 +5745,30 @@
         <v>5</v>
       </c>
       <c r="G175" s="5">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A176" s="1">
-        <v>4010013666</v>
-      </c>
-      <c r="B176" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C176" s="4">
-        <v>46593</v>
-      </c>
-      <c r="D176" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="E176" s="3" t="s">
+      <c r="A176" s="8">
+        <v>6010000128</v>
+      </c>
+      <c r="B176" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="C176" s="10"/>
+      <c r="D176" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E176" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="F176" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G176" s="5">
-        <v>200</v>
-      </c>
+      <c r="F176" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G176" s="11"/>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A177" s="1">
+      <c r="A177" s="2">
         <v>6010000128</v>
       </c>
       <c r="B177" s="3" t="s">
@@ -5798,36 +5791,40 @@
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A178" s="8">
-        <v>6010000128</v>
-      </c>
-      <c r="B178" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="C178" s="10"/>
-      <c r="D178" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="E178" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="F178" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G178" s="11"/>
+      <c r="A178" s="2">
+        <v>6010000129</v>
+      </c>
+      <c r="B178" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="C178" s="4">
+        <v>46569</v>
+      </c>
+      <c r="D178" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="E178" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F178" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G178" s="5">
+        <v>250</v>
+      </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A179" s="1">
+      <c r="A179" s="2">
         <v>6010000129</v>
       </c>
       <c r="B179" s="3" t="s">
         <v>286</v>
       </c>
       <c r="C179" s="4">
-        <v>46569</v>
+        <v>46758</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E179" s="3" t="s">
         <v>15</v>
@@ -5836,44 +5833,44 @@
         <v>5</v>
       </c>
       <c r="G179" s="5">
-        <v>250</v>
+        <v>700</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A180" s="1">
-        <v>6010000129</v>
+      <c r="A180" s="2">
+        <v>6010000130</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C180" s="4">
-        <v>46758</v>
+        <v>46569</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F180" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G180" s="5">
-        <v>700</v>
+        <v>220</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A181" s="1">
+      <c r="A181" s="2">
         <v>6010000130</v>
       </c>
       <c r="B181" s="3" t="s">
         <v>289</v>
       </c>
       <c r="C181" s="4">
-        <v>46569</v>
+        <v>46753</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E181" s="3" t="s">
         <v>29</v>
@@ -5882,136 +5879,136 @@
         <v>5</v>
       </c>
       <c r="G181" s="5">
-        <v>220</v>
+        <v>630</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A182" s="1">
-        <v>6010000130</v>
+      <c r="A182" s="2">
+        <v>6010000198</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>289</v>
+        <v>389</v>
       </c>
       <c r="C182" s="4">
-        <v>46753</v>
+        <v>46568</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>291</v>
+        <v>390</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F182" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G182" s="5">
-        <v>630</v>
+        <v>640</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A183" s="1">
-        <v>6010000198</v>
+      <c r="A183" s="2">
+        <v>4010013586</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>389</v>
+        <v>99</v>
       </c>
       <c r="C183" s="4">
-        <v>46568</v>
+        <v>46537</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>390</v>
+        <v>100</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F183" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G183" s="5">
-        <v>640</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A184" s="1">
-        <v>4010013586</v>
+      <c r="A184" s="2">
+        <v>4010013587</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C184" s="4">
         <v>46537</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E184" s="3" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F184" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G184" s="5">
-        <v>1340</v>
+        <v>240</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A185" s="1">
-        <v>4010013587</v>
+      <c r="A185" s="2">
+        <v>4010013549</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="C185" s="4">
-        <v>46537</v>
+        <v>46525</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>102</v>
+        <v>73</v>
       </c>
       <c r="E185" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F185" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G185" s="5">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A186" s="2">
+        <v>4010013249</v>
+      </c>
+      <c r="B186" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C186" s="4">
+        <v>46442</v>
+      </c>
+      <c r="D186" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E186" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F185" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G185" s="5">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A186" s="1">
-        <v>4010013549</v>
-      </c>
-      <c r="B186" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C186" s="4">
-        <v>46525</v>
-      </c>
-      <c r="D186" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="E186" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F186" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G186" s="5">
-        <v>1080</v>
+        <v>460</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A187" s="1">
-        <v>4010013249</v>
+      <c r="A187" s="2">
+        <v>4010013573</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="C187" s="4">
-        <v>46442</v>
+        <v>46423</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>1</v>
+        <v>81</v>
       </c>
       <c r="E187" s="3" t="s">
         <v>4</v>
@@ -6020,67 +6017,67 @@
         <v>5</v>
       </c>
       <c r="G187" s="5">
-        <v>460</v>
+        <v>600</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A188" s="1">
-        <v>4010013573</v>
+      <c r="A188" s="2">
+        <v>4010013574</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C188" s="4">
-        <v>46423</v>
+        <v>46545</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E188" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F188" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G188" s="5">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A189" s="2">
+        <v>4010013588</v>
+      </c>
+      <c r="B189" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C189" s="4">
+        <v>46582</v>
+      </c>
+      <c r="D189" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E189" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F188" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G188" s="5">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A189" s="1">
-        <v>4010013574</v>
-      </c>
-      <c r="B189" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C189" s="4">
-        <v>46545</v>
-      </c>
-      <c r="D189" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E189" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F189" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G189" s="5">
-        <v>660</v>
+        <v>3140</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A190" s="1">
-        <v>4010013588</v>
+      <c r="A190" s="2">
+        <v>4010013479</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>103</v>
+        <v>63</v>
       </c>
       <c r="C190" s="4">
-        <v>46582</v>
+        <v>46536</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>104</v>
+        <v>64</v>
       </c>
       <c r="E190" s="3" t="s">
         <v>4</v>
@@ -6089,21 +6086,21 @@
         <v>5</v>
       </c>
       <c r="G190" s="5">
-        <v>3140</v>
+        <v>320</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A191" s="1">
+      <c r="A191" s="2">
         <v>4010013479</v>
       </c>
       <c r="B191" s="3" t="s">
         <v>63</v>
       </c>
       <c r="C191" s="4">
-        <v>46536</v>
+        <v>46594</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E191" s="3" t="s">
         <v>4</v>
@@ -6112,11 +6109,11 @@
         <v>5</v>
       </c>
       <c r="G191" s="5">
-        <v>320</v>
+        <v>400</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A192" s="1">
+      <c r="A192" s="2">
         <v>4010013479</v>
       </c>
       <c r="B192" s="3" t="s">
@@ -6126,7 +6123,7 @@
         <v>46419</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E192" s="3" t="s">
         <v>4</v>
@@ -6139,17 +6136,17 @@
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A193" s="1">
-        <v>4010013479</v>
+      <c r="A193" s="2">
+        <v>4010013700</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>63</v>
+        <v>156</v>
       </c>
       <c r="C193" s="4">
-        <v>46594</v>
+        <v>46533</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>66</v>
+        <v>157</v>
       </c>
       <c r="E193" s="3" t="s">
         <v>4</v>
@@ -6158,21 +6155,21 @@
         <v>5</v>
       </c>
       <c r="G193" s="5">
-        <v>400</v>
+        <v>300</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A194" s="1">
+      <c r="A194" s="2">
         <v>4010013700</v>
       </c>
       <c r="B194" s="3" t="s">
         <v>156</v>
       </c>
       <c r="C194" s="4">
-        <v>46533</v>
+        <v>46446</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E194" s="3" t="s">
         <v>4</v>
@@ -6181,21 +6178,21 @@
         <v>5</v>
       </c>
       <c r="G194" s="5">
-        <v>300</v>
+        <v>560</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A195" s="1">
-        <v>4010013700</v>
+      <c r="A195" s="2">
+        <v>4010013701</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C195" s="4">
-        <v>46446</v>
+        <v>46589</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E195" s="3" t="s">
         <v>4</v>
@@ -6204,44 +6201,44 @@
         <v>5</v>
       </c>
       <c r="G195" s="5">
-        <v>560</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A196" s="1">
-        <v>4010013701</v>
+      <c r="A196" s="2">
+        <v>4010013657</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>159</v>
+        <v>127</v>
       </c>
       <c r="C196" s="4">
-        <v>46589</v>
+        <v>46513</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>160</v>
+        <v>128</v>
       </c>
       <c r="E196" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F196" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G196" s="5">
-        <v>1160</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A197" s="1">
-        <v>4010013657</v>
+      <c r="A197" s="2">
+        <v>4010013658</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C197" s="4">
-        <v>46513</v>
+        <v>46587</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E197" s="3" t="s">
         <v>8</v>
@@ -6250,11 +6247,11 @@
         <v>5</v>
       </c>
       <c r="G197" s="5">
-        <v>1000</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A198" s="1">
+      <c r="A198" s="2">
         <v>4010013658</v>
       </c>
       <c r="B198" s="3" t="s">
@@ -6264,7 +6261,7 @@
         <v>46563</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E198" s="3" t="s">
         <v>8</v>
@@ -6277,63 +6274,63 @@
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A199" s="1">
-        <v>4010013658</v>
+      <c r="A199" s="2">
+        <v>4010013548</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>129</v>
+        <v>69</v>
       </c>
       <c r="C199" s="4">
-        <v>46587</v>
+        <v>46469</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>131</v>
+        <v>70</v>
       </c>
       <c r="E199" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F199" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G199" s="5">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A200" s="2">
+        <v>4010013480</v>
+      </c>
+      <c r="B200" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C200" s="4">
+        <v>46408</v>
+      </c>
+      <c r="D200" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E200" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F199" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G199" s="5">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A200" s="1">
-        <v>4010013548</v>
-      </c>
-      <c r="B200" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C200" s="4">
-        <v>46469</v>
-      </c>
-      <c r="D200" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E200" s="3" t="s">
-        <v>71</v>
-      </c>
       <c r="F200" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G200" s="5">
-        <v>830</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A201" s="1">
-        <v>4010013480</v>
+      <c r="A201" s="2">
+        <v>4010013477</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C201" s="4">
-        <v>46408</v>
+        <v>46574</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E201" s="3" t="s">
         <v>8</v>
@@ -6342,7 +6339,7 @@
         <v>5</v>
       </c>
       <c r="G201" s="5">
-        <v>1230</v>
+        <v>600</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.25">
@@ -6365,76 +6362,76 @@
       <c r="G202" s="11"/>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A203" s="1">
-        <v>4010013477</v>
+      <c r="A203" s="2">
+        <v>6010000131</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>59</v>
+        <v>292</v>
       </c>
       <c r="C203" s="4">
-        <v>46574</v>
+        <v>46784</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>60</v>
+        <v>293</v>
       </c>
       <c r="E203" s="3" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F203" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G203" s="5">
-        <v>600</v>
+        <v>2460</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A204" s="1">
-        <v>6010000131</v>
+      <c r="A204" s="2">
+        <v>4010013699</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>292</v>
+        <v>154</v>
       </c>
       <c r="C204" s="4">
-        <v>46784</v>
+        <v>46438</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>293</v>
+        <v>155</v>
       </c>
       <c r="E204" s="3" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F204" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G204" s="5">
-        <v>2460</v>
+        <v>360</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A205" s="1">
-        <v>4010013699</v>
+      <c r="A205" s="2">
+        <v>6010000089</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>154</v>
+        <v>225</v>
       </c>
       <c r="C205" s="4">
-        <v>46438</v>
+        <v>46871</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>155</v>
+        <v>226</v>
       </c>
       <c r="E205" s="3" t="s">
-        <v>29</v>
+        <v>227</v>
       </c>
       <c r="F205" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G205" s="5">
-        <v>360</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A206" s="1">
+      <c r="A206" s="2">
         <v>6010000089</v>
       </c>
       <c r="B206" s="3" t="s">
@@ -6444,7 +6441,7 @@
         <v>46424</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E206" s="3" t="s">
         <v>227</v>
@@ -6457,155 +6454,155 @@
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A207" s="1">
-        <v>6010000089</v>
+      <c r="A207" s="2">
+        <v>6010000132</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>225</v>
+        <v>294</v>
       </c>
       <c r="C207" s="4">
-        <v>46871</v>
+        <v>46614</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>228</v>
+        <v>2</v>
       </c>
       <c r="E207" s="3" t="s">
-        <v>227</v>
+        <v>29</v>
       </c>
       <c r="F207" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G207" s="5">
+        <v>3360</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A208" s="2">
+        <v>6010000146</v>
+      </c>
+      <c r="B208" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="C208" s="4">
+        <v>46746</v>
+      </c>
+      <c r="D208" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="E208" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="F208" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G207" s="5">
-        <v>2300</v>
-      </c>
-    </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A208" s="1">
-        <v>6010000132</v>
-      </c>
-      <c r="B208" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="C208" s="4">
-        <v>46614</v>
-      </c>
-      <c r="D208" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E208" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F208" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G208" s="5">
-        <v>3360</v>
+        <v>480</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A209" s="1">
-        <v>6010000146</v>
+      <c r="A209" s="2">
+        <v>6010000090</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>323</v>
+        <v>229</v>
       </c>
       <c r="C209" s="4">
-        <v>46746</v>
+        <v>46482</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>324</v>
+        <v>230</v>
       </c>
       <c r="E209" s="3" t="s">
-        <v>325</v>
+        <v>178</v>
       </c>
       <c r="F209" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G209" s="5">
-        <v>480</v>
+        <v>4650</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A210" s="1">
-        <v>6010000090</v>
+      <c r="A210" s="2">
+        <v>6010000200</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>229</v>
+        <v>393</v>
       </c>
       <c r="C210" s="4">
-        <v>46482</v>
+        <v>46593</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>230</v>
+        <v>394</v>
       </c>
       <c r="E210" s="3" t="s">
-        <v>178</v>
+        <v>395</v>
       </c>
       <c r="F210" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G210" s="5">
-        <v>4650</v>
+        <v>260</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A211" s="1">
-        <v>6010000200</v>
+      <c r="A211" s="2">
+        <v>6010000199</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C211" s="4">
-        <v>46593</v>
+        <v>46556</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E211" s="3" t="s">
-        <v>395</v>
+        <v>22</v>
       </c>
       <c r="F211" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G211" s="5">
-        <v>260</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A212" s="1">
-        <v>6010000199</v>
+      <c r="A212" s="2">
+        <v>6010000133</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>391</v>
+        <v>295</v>
       </c>
       <c r="C212" s="4">
-        <v>46556</v>
+        <v>46388</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>392</v>
+        <v>296</v>
       </c>
       <c r="E212" s="3" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="F212" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G212" s="5">
-        <v>1680</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A213" s="1">
-        <v>6010000133</v>
+      <c r="A213" s="2">
+        <v>6010000134</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C213" s="4">
-        <v>46388</v>
+        <v>46488</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="E213" s="3" t="s">
         <v>88</v>
@@ -6614,21 +6611,21 @@
         <v>5</v>
       </c>
       <c r="G213" s="5">
-        <v>1200</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A214" s="1">
-        <v>6010000134</v>
+      <c r="A214" s="2">
+        <v>6010000135</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C214" s="4">
-        <v>46488</v>
+        <v>46388</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="E214" s="3" t="s">
         <v>88</v>
@@ -6637,63 +6634,63 @@
         <v>5</v>
       </c>
       <c r="G214" s="5">
-        <v>1480</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A215" s="1">
-        <v>6010000135</v>
-      </c>
-      <c r="B215" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="C215" s="4">
-        <v>46388</v>
-      </c>
-      <c r="D215" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="E215" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="F215" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G215" s="5">
-        <v>1560</v>
-      </c>
+      <c r="A215" s="8">
+        <v>6010000136</v>
+      </c>
+      <c r="B215" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="C215" s="10"/>
+      <c r="D215" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E215" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F215" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G215" s="11"/>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A216" s="8">
+      <c r="A216" s="2">
         <v>6010000136</v>
       </c>
-      <c r="B216" s="9" t="s">
+      <c r="B216" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="C216" s="10"/>
-      <c r="D216" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="E216" s="9" t="s">
+      <c r="C216" s="4">
+        <v>46496</v>
+      </c>
+      <c r="D216" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="E216" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F216" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G216" s="11"/>
+      <c r="F216" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G216" s="5">
+        <v>450</v>
+      </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A217" s="1">
-        <v>6010000136</v>
+      <c r="A217" s="2">
+        <v>6010000137</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C217" s="4">
         <v>46496</v>
       </c>
       <c r="D217" s="3" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E217" s="3" t="s">
         <v>29</v>
@@ -6702,136 +6699,136 @@
         <v>5</v>
       </c>
       <c r="G217" s="5">
-        <v>450</v>
+        <v>810</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A218" s="1">
-        <v>6010000137</v>
+      <c r="A218" s="2">
+        <v>4010013269</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>303</v>
+        <v>20</v>
       </c>
       <c r="C218" s="4">
-        <v>46496</v>
+        <v>46558</v>
       </c>
       <c r="D218" s="3" t="s">
-        <v>304</v>
+        <v>21</v>
       </c>
       <c r="E218" s="3" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F218" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G218" s="5">
-        <v>810</v>
+        <v>900</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A219" s="1">
-        <v>4010013269</v>
+      <c r="A219" s="2">
+        <v>6010000177</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>20</v>
+        <v>367</v>
       </c>
       <c r="C219" s="4">
-        <v>46558</v>
+        <v>46971</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>21</v>
+        <v>368</v>
       </c>
       <c r="E219" s="3" t="s">
-        <v>22</v>
+        <v>369</v>
       </c>
       <c r="F219" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G219" s="5">
-        <v>900</v>
+        <v>2980</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A220" s="1">
-        <v>6010000177</v>
+      <c r="A220" s="2">
+        <v>6010000178</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C220" s="4">
-        <v>46971</v>
+        <v>47087</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="E220" s="3" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="F220" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G220" s="5">
-        <v>2980</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A221" s="1">
-        <v>6010000178</v>
+      <c r="A221" s="2">
+        <v>4010013597</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>370</v>
+        <v>116</v>
       </c>
       <c r="C221" s="4">
-        <v>47087</v>
+        <v>46525</v>
       </c>
       <c r="D221" s="3" t="s">
-        <v>371</v>
+        <v>117</v>
       </c>
       <c r="E221" s="3" t="s">
-        <v>372</v>
+        <v>11</v>
       </c>
       <c r="F221" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G221" s="5">
-        <v>1260</v>
+        <v>620</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A222" s="1">
-        <v>4010013597</v>
+      <c r="A222" s="2">
+        <v>4010013368</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>116</v>
+        <v>31</v>
       </c>
       <c r="C222" s="4">
-        <v>46525</v>
+        <v>46533</v>
       </c>
       <c r="D222" s="3" t="s">
-        <v>117</v>
+        <v>32</v>
       </c>
       <c r="E222" s="3" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F222" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G222" s="5">
-        <v>620</v>
+        <v>160</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A223" s="1">
-        <v>4010013368</v>
+      <c r="A223" s="2">
+        <v>4010013369</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C223" s="4">
-        <v>46533</v>
+        <v>46429</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E223" s="3" t="s">
         <v>4</v>
@@ -6840,21 +6837,21 @@
         <v>5</v>
       </c>
       <c r="G223" s="5">
-        <v>160</v>
+        <v>440</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A224" s="1">
+      <c r="A224" s="2">
         <v>4010013369</v>
       </c>
       <c r="B224" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C224" s="4">
-        <v>46429</v>
+        <v>46533</v>
       </c>
       <c r="D224" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E224" s="3" t="s">
         <v>4</v>
@@ -6863,172 +6860,170 @@
         <v>5</v>
       </c>
       <c r="G224" s="5">
-        <v>440</v>
+        <v>80</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A225" s="1">
-        <v>4010013369</v>
+      <c r="A225" s="2">
+        <v>4010013598</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>33</v>
+        <v>118</v>
       </c>
       <c r="C225" s="4">
-        <v>46533</v>
+        <v>47043</v>
       </c>
       <c r="D225" s="3" t="s">
-        <v>35</v>
+        <v>119</v>
       </c>
       <c r="E225" s="3" t="s">
-        <v>4</v>
+        <v>120</v>
       </c>
       <c r="F225" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G225" s="5">
-        <v>80</v>
+        <v>170</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A226" s="1">
-        <v>4010013598</v>
+      <c r="A226" s="2">
+        <v>4010013399</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>118</v>
+        <v>43</v>
       </c>
       <c r="C226" s="4">
-        <v>47043</v>
+        <v>46532</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>119</v>
+        <v>44</v>
       </c>
       <c r="E226" s="3" t="s">
-        <v>120</v>
+        <v>22</v>
       </c>
       <c r="F226" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G226" s="5">
-        <v>170</v>
+        <v>410</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A227" s="1">
+      <c r="A227" s="8">
         <v>4010013399</v>
       </c>
-      <c r="B227" s="3" t="s">
+      <c r="B227" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C227" s="4">
-        <v>46532</v>
-      </c>
-      <c r="D227" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E227" s="3" t="s">
+      <c r="C227" s="10"/>
+      <c r="D227" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E227" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F227" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G227" s="5">
-        <v>410</v>
-      </c>
+      <c r="F227" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G227" s="11"/>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A228" s="8">
-        <v>4010013399</v>
-      </c>
-      <c r="B228" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="C228" s="10"/>
-      <c r="D228" s="9" t="s">
+      <c r="A228" s="2">
+        <v>6010000203</v>
+      </c>
+      <c r="B228" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="C228" s="4">
+        <v>46606</v>
+      </c>
+      <c r="D228" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="E228" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="F228" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G228" s="5">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A229" s="2">
+        <v>4010013592</v>
+      </c>
+      <c r="B229" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C229" s="4">
+        <v>46514</v>
+      </c>
+      <c r="D229" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E229" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="F229" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G229" s="5">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A230" s="2">
+        <v>4010014926</v>
+      </c>
+      <c r="B230" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C230" s="4">
+        <v>46768</v>
+      </c>
+      <c r="D230" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="E230" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F230" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G230" s="5">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A231" s="2">
+        <v>7050000020</v>
+      </c>
+      <c r="B231" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="C231" s="4"/>
+      <c r="D231" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E228" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F228" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G228" s="11"/>
-    </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A229" s="1">
-        <v>6010000203</v>
-      </c>
-      <c r="B229" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="C229" s="4">
-        <v>46606</v>
-      </c>
-      <c r="D229" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="E229" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="F229" s="3" t="s">
+      <c r="E231" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F231" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G229" s="5">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A230" s="1">
-        <v>4010013592</v>
-      </c>
-      <c r="B230" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C230" s="4">
-        <v>46514</v>
-      </c>
-      <c r="D230" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="E230" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="F230" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G230" s="5">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A231" s="1">
-        <v>4010014926</v>
-      </c>
-      <c r="B231" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="C231" s="4">
-        <v>46768</v>
-      </c>
-      <c r="D231" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="E231" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="F231" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G231" s="5">
-        <v>780</v>
+        <v>70</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A232" s="1">
+      <c r="A232" s="2">
         <v>7050000020</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C232" s="4"/>
       <c r="D232" s="3" t="s">
@@ -7041,74 +7036,76 @@
         <v>3</v>
       </c>
       <c r="G232" s="5">
-        <v>70</v>
+        <v>30</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A233" s="1">
-        <v>7050000020</v>
-      </c>
-      <c r="B233" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="C233" s="4"/>
-      <c r="D233" s="3" t="s">
+      <c r="A233" s="8">
+        <v>4010013659</v>
+      </c>
+      <c r="B233" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="C233" s="10"/>
+      <c r="D233" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E233" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F233" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G233" s="5">
-        <v>30</v>
-      </c>
+      <c r="E233" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F233" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G233" s="11"/>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A234" s="8">
+      <c r="A234" s="2">
         <v>4010013659</v>
       </c>
-      <c r="B234" s="9" t="s">
+      <c r="B234" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C234" s="10"/>
-      <c r="D234" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="E234" s="9" t="s">
+      <c r="C234" s="4">
+        <v>46526</v>
+      </c>
+      <c r="D234" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E234" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F234" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G234" s="11"/>
+      <c r="F234" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G234" s="5">
+        <v>670</v>
+      </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A235" s="1">
-        <v>4010013659</v>
+      <c r="A235" s="2">
+        <v>4010013273</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>132</v>
+        <v>27</v>
       </c>
       <c r="C235" s="4">
-        <v>46526</v>
+        <v>46444</v>
       </c>
       <c r="D235" s="3" t="s">
-        <v>133</v>
+        <v>28</v>
       </c>
       <c r="E235" s="3" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="F235" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G235" s="5">
-        <v>670</v>
+        <v>710</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A236" s="1">
+      <c r="A236" s="2">
         <v>4010013273</v>
       </c>
       <c r="B236" s="3" t="s">
@@ -7118,7 +7115,7 @@
         <v>46444</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E236" s="3" t="s">
         <v>29</v>
@@ -7127,44 +7124,44 @@
         <v>5</v>
       </c>
       <c r="G236" s="5">
-        <v>710</v>
+        <v>80</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A237" s="1">
-        <v>4010013273</v>
+      <c r="A237" s="2">
+        <v>4010013271</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C237" s="4">
-        <v>46444</v>
+        <v>46402</v>
       </c>
       <c r="D237" s="3" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E237" s="3" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F237" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G237" s="5">
-        <v>80</v>
+        <v>300</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A238" s="1">
-        <v>4010013271</v>
+      <c r="A238" s="2">
+        <v>4010013272</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C238" s="4">
-        <v>46402</v>
+        <v>46523</v>
       </c>
       <c r="D238" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E238" s="3" t="s">
         <v>8</v>
@@ -7173,7 +7170,7 @@
         <v>5</v>
       </c>
       <c r="G238" s="5">
-        <v>300</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.25">
@@ -7196,17 +7193,17 @@
       <c r="G239" s="11"/>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A240" s="1">
-        <v>4010013272</v>
+      <c r="A240" s="2">
+        <v>4010013663</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>25</v>
+        <v>139</v>
       </c>
       <c r="C240" s="4">
-        <v>46523</v>
+        <v>46612</v>
       </c>
       <c r="D240" s="3" t="s">
-        <v>26</v>
+        <v>140</v>
       </c>
       <c r="E240" s="3" t="s">
         <v>8</v>
@@ -7215,21 +7212,21 @@
         <v>5</v>
       </c>
       <c r="G240" s="5">
-        <v>1020</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A241" s="1">
+      <c r="A241" s="2">
         <v>4010013663</v>
       </c>
       <c r="B241" s="3" t="s">
         <v>139</v>
       </c>
       <c r="C241" s="4">
-        <v>46612</v>
+        <v>46514</v>
       </c>
       <c r="D241" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E241" s="3" t="s">
         <v>8</v>
@@ -7238,47 +7235,47 @@
         <v>5</v>
       </c>
       <c r="G241" s="5">
-        <v>1200</v>
+        <v>200</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A242" s="1">
-        <v>4010013663</v>
+      <c r="A242" s="2">
+        <v>6010000245</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>139</v>
+        <v>437</v>
       </c>
       <c r="C242" s="4">
-        <v>46514</v>
+        <v>46574</v>
       </c>
       <c r="D242" s="3" t="s">
-        <v>141</v>
+        <v>438</v>
       </c>
       <c r="E242" s="3" t="s">
-        <v>8</v>
+        <v>439</v>
       </c>
       <c r="F242" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G242" s="5">
-        <v>200</v>
+        <v>3700</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A243" s="1">
+      <c r="A243" s="2">
         <v>6010000245</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C243" s="4">
         <v>46629</v>
       </c>
       <c r="D243" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="E243" s="3" t="s">
         <v>439</v>
-      </c>
-      <c r="E243" s="3" t="s">
-        <v>440</v>
       </c>
       <c r="F243" s="3" t="s">
         <v>3</v>
@@ -7288,120 +7285,97 @@
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A244" s="1">
-        <v>6010000245</v>
+      <c r="A244" s="2">
+        <v>6010000093</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>438</v>
+        <v>231</v>
       </c>
       <c r="C244" s="4">
-        <v>46574</v>
+        <v>46504</v>
       </c>
       <c r="D244" s="3" t="s">
-        <v>441</v>
+        <v>232</v>
       </c>
       <c r="E244" s="3" t="s">
-        <v>440</v>
+        <v>233</v>
       </c>
       <c r="F244" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G244" s="5">
-        <v>3700</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A245" s="1">
+      <c r="A245" s="8">
         <v>6010000093</v>
       </c>
-      <c r="B245" s="3" t="s">
+      <c r="B245" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="C245" s="4">
-        <v>46504</v>
-      </c>
-      <c r="D245" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="E245" s="3" t="s">
+      <c r="C245" s="10"/>
+      <c r="D245" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E245" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="F245" s="3" t="s">
+      <c r="F245" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="G245" s="5">
-        <v>15000</v>
-      </c>
+      <c r="G245" s="11"/>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A246" s="8">
-        <v>6010000093</v>
-      </c>
-      <c r="B246" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="C246" s="10"/>
-      <c r="D246" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="E246" s="9" t="s">
-        <v>233</v>
-      </c>
-      <c r="F246" s="9" t="s">
+      <c r="A246" s="2">
+        <v>6010000161</v>
+      </c>
+      <c r="B246" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C246" s="4">
+        <v>47087</v>
+      </c>
+      <c r="D246" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="E246" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="F246" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G246" s="11"/>
+      <c r="G246" s="5">
+        <v>708</v>
+      </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A247" s="1">
-        <v>6010000161</v>
+      <c r="A247" s="2">
+        <v>6010000162</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C247" s="4">
         <v>47087</v>
       </c>
       <c r="D247" s="3" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="E247" s="3" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="F247" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G247" s="5">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A248" s="1">
-        <v>6010000162</v>
-      </c>
-      <c r="B248" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="C248" s="4">
-        <v>47087</v>
-      </c>
-      <c r="D248" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="E248" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="F248" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G248" s="5">
         <v>1164</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G248">
-    <sortState ref="A2:H248">
-      <sortCondition ref="B1:B248"/>
+  <autoFilter ref="A1:G247">
+    <sortState ref="A2:H247">
+      <sortCondition ref="B1:B247"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="0" type="noConversion"/>

--- a/KSTOCK.xlsx
+++ b/KSTOCK.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$226</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$222</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="455">
   <si>
     <t>ROSUSEP-20</t>
   </si>
@@ -49,15 +49,15 @@
     <t>ATROLIA CV 20/75</t>
   </si>
   <si>
+    <t>25S3GCA110</t>
+  </si>
+  <si>
+    <t>10X3X10</t>
+  </si>
+  <si>
     <t>25S3GCA131</t>
   </si>
   <si>
-    <t>10X3X10</t>
-  </si>
-  <si>
-    <t>25S3GCA110</t>
-  </si>
-  <si>
     <t>Montalia AB</t>
   </si>
   <si>
@@ -97,24 +97,24 @@
     <t>Vildapharm-Met 500</t>
   </si>
   <si>
+    <t>25S3GTA972</t>
+  </si>
+  <si>
     <t>25S3GTA610</t>
   </si>
   <si>
-    <t>25S3GTA972</t>
-  </si>
-  <si>
     <t>VILDAPHARM-DP</t>
   </si>
   <si>
+    <t>25S3GTA308</t>
+  </si>
+  <si>
+    <t>10X1X10</t>
+  </si>
+  <si>
     <t>25S3GTA311</t>
   </si>
   <si>
-    <t>10X1X10</t>
-  </si>
-  <si>
-    <t>25S3GTA308</t>
-  </si>
-  <si>
     <t>TENEJEET-M 1000</t>
   </si>
   <si>
@@ -142,9 +142,6 @@
     <t>10X20</t>
   </si>
   <si>
-    <t>25S3GTB083</t>
-  </si>
-  <si>
     <t>CILNIEASE-T</t>
   </si>
   <si>
@@ -391,15 +388,12 @@
     <t>LEVELISH 500</t>
   </si>
   <si>
-    <t>25S2GTA561</t>
+    <t>25S2GTB370</t>
   </si>
   <si>
     <t>10X10</t>
   </si>
   <si>
-    <t>25S2GTB370</t>
-  </si>
-  <si>
     <t>SITAFREE-100</t>
   </si>
   <si>
@@ -409,12 +403,12 @@
     <t>SITAFREE-50</t>
   </si>
   <si>
+    <t>25S2GTB786</t>
+  </si>
+  <si>
     <t>25S2GTC059</t>
   </si>
   <si>
-    <t>25S2GTB786</t>
-  </si>
-  <si>
     <t>VILDAPHARM-50</t>
   </si>
   <si>
@@ -469,12 +463,12 @@
     <t>ATROLIA GOLD 20/75</t>
   </si>
   <si>
+    <t>25S3GCA113</t>
+  </si>
+  <si>
     <t>25S3GCA129</t>
   </si>
   <si>
-    <t>25S3GCA113</t>
-  </si>
-  <si>
     <t>Atrolia-ASP 75</t>
   </si>
   <si>
@@ -715,12 +709,12 @@
     <t>VOLOPAIN INJ</t>
   </si>
   <si>
+    <t>20X5X3ML</t>
+  </si>
+  <si>
     <t>NL2702507</t>
   </si>
   <si>
-    <t>20X5X3ML</t>
-  </si>
-  <si>
     <t>NL2702506</t>
   </si>
   <si>
@@ -739,15 +733,15 @@
     <t>AMLINA-5 TABLET</t>
   </si>
   <si>
+    <t>T50499A</t>
+  </si>
+  <si>
+    <t>20X30</t>
+  </si>
+  <si>
     <t>T60096A</t>
   </si>
   <si>
-    <t>20X30</t>
-  </si>
-  <si>
-    <t>T50499A</t>
-  </si>
-  <si>
     <t>AMLINA-AT TABLET</t>
   </si>
   <si>
@@ -859,21 +853,21 @@
     <t>RIFIXIEM 400 TABLET</t>
   </si>
   <si>
+    <t>GA845001</t>
+  </si>
+  <si>
     <t>GA845010</t>
   </si>
   <si>
-    <t>GA845001</t>
-  </si>
-  <si>
     <t>RIFIXIEM 550 TABLET</t>
   </si>
   <si>
+    <t>GE545020</t>
+  </si>
+  <si>
     <t>GE545002B</t>
   </si>
   <si>
-    <t>GE545020</t>
-  </si>
-  <si>
     <t>SPASMOSAFE-MF TABLET</t>
   </si>
   <si>
@@ -1138,15 +1132,15 @@
     <t>Faropharm 200 Tablet</t>
   </si>
   <si>
+    <t>CBT26025B</t>
+  </si>
+  <si>
+    <t>CBT26001B</t>
+  </si>
+  <si>
     <t>CBT25115D</t>
   </si>
   <si>
-    <t>CBT26025B</t>
-  </si>
-  <si>
-    <t>CBT26001B</t>
-  </si>
-  <si>
     <t>EPODOX-200 DT Tablet</t>
   </si>
   <si>
@@ -1255,15 +1249,15 @@
     <t>MONTALIA-LC 60ML SYRUP</t>
   </si>
   <si>
+    <t>DL603008</t>
+  </si>
+  <si>
+    <t>60 ML</t>
+  </si>
+  <si>
     <t>DL602011A</t>
   </si>
   <si>
-    <t>60 ML</t>
-  </si>
-  <si>
-    <t>DL603008</t>
-  </si>
-  <si>
     <t>CLAVMYCIN 375 DUO TABLET (20x1x10)</t>
   </si>
   <si>
@@ -1273,12 +1267,12 @@
     <t>REBEHIT DSR CAPSULE</t>
   </si>
   <si>
+    <t>MC2510116</t>
+  </si>
+  <si>
     <t>MC2510117</t>
   </si>
   <si>
-    <t>MC2510116</t>
-  </si>
-  <si>
     <t>PANTAHIT DSR CAPSULE (20x10)</t>
   </si>
   <si>
@@ -1321,18 +1315,6 @@
     <t>30ML + SWFI</t>
   </si>
   <si>
-    <t>VOLOPAIN AQ INJECTION</t>
-  </si>
-  <si>
-    <t>NL3062502</t>
-  </si>
-  <si>
-    <t>20 X 5 X 1ML</t>
-  </si>
-  <si>
-    <t>NL3062501</t>
-  </si>
-  <si>
     <t>MONTALIA-LC 30ML SYRUP</t>
   </si>
   <si>
@@ -1399,16 +1381,13 @@
     <t xml:space="preserve"> Batch No.</t>
   </si>
   <si>
-    <t>Transit Qty</t>
+    <t xml:space="preserve"> Transit Qty</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.000"/>
-  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -1468,20 +1447,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1489,12 +1465,6 @@
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1505,11 +1475,14 @@
     <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1845,58 +1818,58 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H226"/>
+  <dimension ref="A1:H222"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="31.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.44140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.33203125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="11.6640625" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="13.21875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="29.6640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.88671875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="13.5546875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="18" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.109375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="12.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="10" t="s">
+        <v>447</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>452</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>453</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="E1" s="10" t="s">
+        <v>450</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>451</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>449</v>
+      </c>
+      <c r="H1" s="10" t="s">
         <v>454</v>
       </c>
-      <c r="C1" s="7" t="s">
-        <v>458</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>459</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>456</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>457</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>455</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>460</v>
-      </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
+      <c r="A2" s="1">
         <v>6010000095</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="C2" s="5">
+        <v>233</v>
+      </c>
+      <c r="C2" s="4">
         <v>46568</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>22</v>
@@ -1904,45 +1877,45 @@
       <c r="F2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="6">
-        <v>3980</v>
-      </c>
-      <c r="H2" s="4"/>
+      <c r="G2" s="5">
+        <v>3680</v>
+      </c>
+      <c r="H2" s="5"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="9">
+      <c r="A3" s="6">
         <v>6010000095</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="C3" s="8"/>
+      <c r="D3" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>6010000096</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="C3" s="11"/>
-      <c r="D3" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3" s="12"/>
-      <c r="H3" s="13">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
-        <v>6010000096</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="C4" s="5">
+      <c r="C4" s="4">
         <v>46559</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>22</v>
@@ -1950,93 +1923,93 @@
       <c r="F4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="5">
         <v>500</v>
       </c>
-      <c r="H4" s="4"/>
+      <c r="H4" s="5"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="9">
+      <c r="A5" s="6">
         <v>4010013388</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="11"/>
-      <c r="D5" s="10" t="s">
+      <c r="C5" s="8"/>
+      <c r="D5" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G5" s="12"/>
-      <c r="H5" s="13">
+      <c r="F5" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9">
         <v>1280</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
+      <c r="A6" s="1">
         <v>6010000138</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="C6" s="4">
+        <v>46746</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>298</v>
-      </c>
-      <c r="C6" s="5">
-        <v>46746</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>300</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="5">
         <v>653</v>
       </c>
-      <c r="H6" s="4"/>
+      <c r="H6" s="5"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
+      <c r="A7" s="1">
         <v>4010015107</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="C7" s="5">
+        <v>166</v>
+      </c>
+      <c r="C7" s="4">
         <v>46752</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="5">
         <v>1040</v>
       </c>
-      <c r="H7" s="4"/>
+      <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
+      <c r="A8" s="1">
         <v>4010013476</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="4">
+        <v>46548</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="C8" s="5">
-        <v>46548</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>30</v>
@@ -2044,95 +2017,95 @@
       <c r="F8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="5">
         <v>170</v>
       </c>
-      <c r="H8" s="4"/>
+      <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
+      <c r="A9" s="1">
         <v>6010000097</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C9" s="4">
+        <v>46556</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="C9" s="5">
+      <c r="F9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G9" s="5">
+        <v>300</v>
+      </c>
+      <c r="H9" s="5"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>6010000097</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C10" s="4">
         <v>46751</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E10" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G10" s="5">
+        <v>160</v>
+      </c>
+      <c r="H10" s="5"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>6010000098</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G9" s="6">
-        <v>160</v>
-      </c>
-      <c r="H9" s="4"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
-        <v>6010000097</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="C10" s="5">
-        <v>46556</v>
-      </c>
-      <c r="D10" s="3" t="s">
+      <c r="C11" s="4">
+        <v>46539</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="6">
-        <v>300</v>
-      </c>
-      <c r="H10" s="4"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
-        <v>6010000098</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="C11" s="5">
-        <v>46539</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>244</v>
-      </c>
       <c r="E11" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G11" s="5">
         <v>1340</v>
       </c>
-      <c r="H11" s="4"/>
+      <c r="H11" s="5"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
+      <c r="A12" s="1">
         <v>6010000195</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="C12" s="5">
+        <v>377</v>
+      </c>
+      <c r="C12" s="4">
         <v>46549</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>22</v>
@@ -2140,19 +2113,19 @@
       <c r="F12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="5">
         <v>420</v>
       </c>
-      <c r="H12" s="4"/>
+      <c r="H12" s="5"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
+      <c r="A13" s="1">
         <v>4010013259</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C13" s="4">
         <v>46568</v>
       </c>
       <c r="D13" s="3" t="s">
@@ -2164,20 +2137,20 @@
       <c r="F13" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G13" s="6">
+      <c r="G13" s="5">
         <v>440</v>
       </c>
-      <c r="H13" s="4"/>
+      <c r="H13" s="5"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
+      <c r="A14" s="1">
         <v>4010013260</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="5">
-        <v>46589</v>
+      <c r="C14" s="4">
+        <v>46568</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>10</v>
@@ -2188,20 +2161,20 @@
       <c r="F14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G14" s="6">
-        <v>1200</v>
-      </c>
-      <c r="H14" s="4"/>
+      <c r="G14" s="5">
+        <v>510</v>
+      </c>
+      <c r="H14" s="5"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
+      <c r="A15" s="1">
         <v>4010013260</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="5">
-        <v>46568</v>
+      <c r="C15" s="4">
+        <v>46589</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>12</v>
@@ -2212,23 +2185,23 @@
       <c r="F15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G15" s="6">
-        <v>570</v>
-      </c>
-      <c r="H15" s="4"/>
+      <c r="G15" s="5">
+        <v>1200</v>
+      </c>
+      <c r="H15" s="5"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
+      <c r="A16" s="1">
         <v>4010013692</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="C16" s="5">
+        <v>145</v>
+      </c>
+      <c r="C16" s="4">
         <v>46549</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>8</v>
@@ -2236,23 +2209,23 @@
       <c r="F16" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G16" s="6">
-        <v>920</v>
-      </c>
-      <c r="H16" s="4"/>
+      <c r="G16" s="5">
+        <v>880</v>
+      </c>
+      <c r="H16" s="5"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
+      <c r="A17" s="1">
         <v>4010013693</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="C17" s="5">
-        <v>46587</v>
+        <v>147</v>
+      </c>
+      <c r="C17" s="4">
+        <v>46549</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>8</v>
@@ -2260,23 +2233,23 @@
       <c r="F17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G17" s="6">
-        <v>420</v>
-      </c>
-      <c r="H17" s="4"/>
+      <c r="G17" s="5">
+        <v>460</v>
+      </c>
+      <c r="H17" s="5"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
+      <c r="A18" s="1">
         <v>4010013693</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C18" s="4">
+        <v>46587</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>149</v>
-      </c>
-      <c r="C18" s="5">
-        <v>46549</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>151</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>8</v>
@@ -2284,23 +2257,23 @@
       <c r="F18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G18" s="6">
-        <v>460</v>
-      </c>
-      <c r="H18" s="4"/>
+      <c r="G18" s="5">
+        <v>420</v>
+      </c>
+      <c r="H18" s="5"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
+      <c r="A19" s="1">
         <v>4010013578</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C19" s="4">
+        <v>46640</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="C19" s="5">
-        <v>46640</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>86</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>22</v>
@@ -2308,47 +2281,47 @@
       <c r="F19" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G19" s="6">
+      <c r="G19" s="5">
         <v>770</v>
       </c>
-      <c r="H19" s="4"/>
+      <c r="H19" s="5"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
+      <c r="A20" s="1">
         <v>4010013580</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C20" s="4">
+        <v>46666</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C20" s="5">
-        <v>46666</v>
-      </c>
-      <c r="D20" s="3" t="s">
+      <c r="E20" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>89</v>
-      </c>
       <c r="F20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G20" s="6">
+      <c r="G20" s="5">
         <v>500</v>
       </c>
-      <c r="H20" s="4"/>
+      <c r="H20" s="5"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
+      <c r="A21" s="1">
         <v>4010013551</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C21" s="4">
+        <v>46598</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="C21" s="5">
-        <v>46598</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>78</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>22</v>
@@ -2356,23 +2329,23 @@
       <c r="F21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G21" s="6">
+      <c r="G21" s="5">
         <v>840</v>
       </c>
-      <c r="H21" s="4"/>
+      <c r="H21" s="5"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
+      <c r="A22" s="1">
         <v>4010013660</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="C22" s="5">
+        <v>132</v>
+      </c>
+      <c r="C22" s="4">
         <v>46518</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>22</v>
@@ -2380,23 +2353,23 @@
       <c r="F22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G22" s="6">
+      <c r="G22" s="5">
         <v>360</v>
       </c>
-      <c r="H22" s="4"/>
+      <c r="H22" s="5"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
+      <c r="A23" s="1">
         <v>4010013694</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="C23" s="5">
+        <v>150</v>
+      </c>
+      <c r="C23" s="4">
         <v>46536</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>8</v>
@@ -2404,203 +2377,203 @@
       <c r="F23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G23" s="6">
-        <v>770</v>
-      </c>
-      <c r="H23" s="4"/>
+      <c r="G23" s="5">
+        <v>750</v>
+      </c>
+      <c r="H23" s="5"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="2">
+      <c r="A24" s="1">
         <v>6010000065</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C24" s="4">
+        <v>46447</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="E24" s="3" t="s">
         <v>170</v>
-      </c>
-      <c r="C24" s="5">
-        <v>46447</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>172</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G24" s="6">
-        <v>1950</v>
-      </c>
-      <c r="H24" s="4"/>
+      <c r="G24" s="5">
+        <v>1900</v>
+      </c>
+      <c r="H24" s="5"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="2">
+      <c r="A25" s="1">
         <v>4010013581</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C25" s="4">
+        <v>46541</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C25" s="5">
-        <v>46541</v>
-      </c>
-      <c r="D25" s="3" t="s">
+      <c r="E25" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E25" s="3" t="s">
-        <v>92</v>
-      </c>
       <c r="F25" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G25" s="6">
+      <c r="G25" s="5">
         <v>3580</v>
       </c>
-      <c r="H25" s="4"/>
+      <c r="H25" s="5"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="9">
+      <c r="A26" s="6">
         <v>6010000066</v>
       </c>
-      <c r="B26" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="C26" s="11"/>
-      <c r="D26" s="10" t="s">
+      <c r="B26" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="C26" s="8"/>
+      <c r="D26" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="E26" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="F26" s="10" t="s">
+      <c r="E26" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="F26" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G26" s="12"/>
-      <c r="H26" s="13">
+      <c r="G26" s="9"/>
+      <c r="H26" s="9">
         <v>900</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="2">
+      <c r="A27" s="1">
         <v>7050000018</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="C27" s="5"/>
+        <v>444</v>
+      </c>
+      <c r="C27" s="4"/>
       <c r="D27" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G27" s="6">
+      <c r="G27" s="5">
         <v>100</v>
       </c>
-      <c r="H27" s="4"/>
+      <c r="H27" s="5"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="2">
+      <c r="A28" s="1">
         <v>7050000016</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="C28" s="5"/>
+        <v>442</v>
+      </c>
+      <c r="C28" s="4"/>
       <c r="D28" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G28" s="6">
+      <c r="G28" s="5">
         <v>100</v>
       </c>
-      <c r="H28" s="4"/>
+      <c r="H28" s="5"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="2">
+      <c r="A29" s="1">
         <v>7050000015</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="C29" s="5"/>
+        <v>441</v>
+      </c>
+      <c r="C29" s="4"/>
       <c r="D29" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G29" s="6">
+      <c r="G29" s="5">
         <v>100</v>
       </c>
-      <c r="H29" s="4"/>
+      <c r="H29" s="5"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
+      <c r="A30" s="1">
         <v>7050000014</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>445</v>
-      </c>
-      <c r="C30" s="5"/>
+        <v>439</v>
+      </c>
+      <c r="C30" s="4"/>
       <c r="D30" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G30" s="6">
+      <c r="G30" s="5">
         <v>100</v>
       </c>
-      <c r="H30" s="4"/>
+      <c r="H30" s="5"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
+      <c r="A31" s="1">
         <v>7050000017</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>449</v>
-      </c>
-      <c r="C31" s="5"/>
+        <v>443</v>
+      </c>
+      <c r="C31" s="4"/>
       <c r="D31" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G31" s="6">
+      <c r="G31" s="5">
         <v>100</v>
       </c>
-      <c r="H31" s="4"/>
+      <c r="H31" s="5"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="2">
+      <c r="A32" s="1">
         <v>4010013550</v>
       </c>
       <c r="B32" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C32" s="4">
+        <v>46568</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="C32" s="5">
-        <v>46568</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>76</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>30</v>
@@ -2608,45 +2581,45 @@
       <c r="F32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G32" s="6">
+      <c r="G32" s="5">
         <v>970</v>
       </c>
-      <c r="H32" s="4"/>
+      <c r="H32" s="5"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="9">
+      <c r="A33" s="6">
         <v>4010013550</v>
       </c>
-      <c r="B33" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C33" s="11"/>
-      <c r="D33" s="10" t="s">
+      <c r="B33" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C33" s="8"/>
+      <c r="D33" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="E33" s="10" t="s">
+      <c r="E33" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="F33" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G33" s="12"/>
-      <c r="H33" s="13">
+      <c r="F33" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9">
         <v>360</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="2">
+      <c r="A34" s="1">
         <v>4010013478</v>
       </c>
       <c r="B34" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C34" s="4">
+        <v>46551</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="C34" s="5">
-        <v>46551</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>63</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>30</v>
@@ -2654,47 +2627,47 @@
       <c r="F34" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G34" s="6">
+      <c r="G34" s="5">
         <v>230</v>
       </c>
-      <c r="H34" s="4"/>
+      <c r="H34" s="5"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="2">
+      <c r="A35" s="1">
         <v>6010000154</v>
       </c>
       <c r="B35" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C35" s="4">
+        <v>47007</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="E35" s="3" t="s">
         <v>326</v>
-      </c>
-      <c r="C35" s="5">
-        <v>47007</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>328</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G35" s="6">
+      <c r="G35" s="5">
         <v>829</v>
       </c>
-      <c r="H35" s="4"/>
+      <c r="H35" s="5"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="2">
+      <c r="A36" s="1">
         <v>6010000158</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="C36" s="5">
+        <v>331</v>
+      </c>
+      <c r="C36" s="4">
         <v>46752</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>8</v>
@@ -2702,113 +2675,113 @@
       <c r="F36" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G36" s="6">
+      <c r="G36" s="5">
         <v>440</v>
       </c>
-      <c r="H36" s="4"/>
+      <c r="H36" s="5"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="9">
+      <c r="A37" s="6">
         <v>6010000068</v>
       </c>
-      <c r="B37" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="C37" s="11"/>
-      <c r="D37" s="10" t="s">
+      <c r="B37" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C37" s="8"/>
+      <c r="D37" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="E37" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="F37" s="10" t="s">
+      <c r="E37" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="F37" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G37" s="12"/>
-      <c r="H37" s="13">
+      <c r="G37" s="9"/>
+      <c r="H37" s="9">
         <v>1500</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="9">
+      <c r="A38" s="6">
         <v>6010000159</v>
       </c>
-      <c r="B38" s="10" t="s">
+      <c r="B38" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="C38" s="8"/>
+      <c r="D38" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G38" s="9"/>
+      <c r="H38" s="9">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="6">
+        <v>6010000099</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="C39" s="8"/>
+      <c r="D39" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G39" s="9"/>
+      <c r="H39" s="9">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <v>6010000160</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="C40" s="4">
+        <v>46780</v>
+      </c>
+      <c r="D40" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="C38" s="11"/>
-      <c r="D38" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="E38" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F38" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G38" s="12"/>
-      <c r="H38" s="13">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="9">
-        <v>6010000099</v>
-      </c>
-      <c r="B39" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="C39" s="11"/>
-      <c r="D39" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="E39" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="F39" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G39" s="12"/>
-      <c r="H39" s="13">
-        <v>4800</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="2">
-        <v>6010000160</v>
-      </c>
-      <c r="B40" s="3" t="s">
+      <c r="E40" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="C40" s="5">
-        <v>46780</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>338</v>
-      </c>
       <c r="F40" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G40" s="6">
-        <v>1260</v>
-      </c>
-      <c r="H40" s="4"/>
+      <c r="G40" s="5">
+        <v>1200</v>
+      </c>
+      <c r="H40" s="5"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="2">
+      <c r="A41" s="1">
         <v>6010000234</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>424</v>
-      </c>
-      <c r="C41" s="5">
+        <v>422</v>
+      </c>
+      <c r="C41" s="4">
         <v>46661</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>22</v>
@@ -2816,23 +2789,23 @@
       <c r="F41" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G41" s="6">
+      <c r="G41" s="5">
         <v>340</v>
       </c>
-      <c r="H41" s="4"/>
+      <c r="H41" s="5"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="2">
+      <c r="A42" s="1">
         <v>6010000234</v>
       </c>
       <c r="B42" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="C42" s="4">
+        <v>46726</v>
+      </c>
+      <c r="D42" s="3" t="s">
         <v>424</v>
-      </c>
-      <c r="C42" s="5">
-        <v>46726</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>426</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>22</v>
@@ -2840,47 +2813,47 @@
       <c r="F42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G42" s="6">
+      <c r="G42" s="5">
         <v>7920</v>
       </c>
-      <c r="H42" s="4"/>
+      <c r="H42" s="5"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="2">
+      <c r="A43" s="1">
         <v>6010000239</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="C43" s="5">
+        <v>427</v>
+      </c>
+      <c r="C43" s="4">
         <v>46507</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G43" s="6">
-        <v>807</v>
-      </c>
-      <c r="H43" s="4"/>
+      <c r="G43" s="5">
+        <v>757</v>
+      </c>
+      <c r="H43" s="5"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="2">
+      <c r="A44" s="1">
         <v>6010000217</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="C44" s="5">
+        <v>406</v>
+      </c>
+      <c r="C44" s="4">
         <v>46751</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>30</v>
@@ -2888,23 +2861,23 @@
       <c r="F44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G44" s="6">
+      <c r="G44" s="5">
         <v>610</v>
       </c>
-      <c r="H44" s="4"/>
+      <c r="H44" s="5"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="2">
+      <c r="A45" s="1">
         <v>6010000217</v>
       </c>
       <c r="B45" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="C45" s="4">
+        <v>46721</v>
+      </c>
+      <c r="D45" s="3" t="s">
         <v>408</v>
-      </c>
-      <c r="C45" s="5">
-        <v>46721</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>410</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>30</v>
@@ -2912,67 +2885,67 @@
       <c r="F45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G45" s="6">
+      <c r="G45" s="5">
         <v>260</v>
       </c>
-      <c r="H45" s="4"/>
+      <c r="H45" s="5"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="2">
+      <c r="A46" s="1">
         <v>6010000070</v>
       </c>
       <c r="B46" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C46" s="4">
+        <v>46721</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E46" s="3" t="s">
         <v>177</v>
-      </c>
-      <c r="C46" s="5">
-        <v>46721</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>179</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G46" s="6">
+      <c r="G46" s="5">
         <v>840</v>
       </c>
-      <c r="H46" s="4"/>
+      <c r="H46" s="5"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="2">
+      <c r="A47" s="1">
         <v>6010000071</v>
       </c>
       <c r="B47" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C47" s="4">
+        <v>46797</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E47" s="3" t="s">
         <v>180</v>
-      </c>
-      <c r="C47" s="5">
-        <v>46797</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>182</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G47" s="6">
+      <c r="G47" s="5">
         <v>3250</v>
       </c>
-      <c r="H47" s="4"/>
+      <c r="H47" s="5"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="2">
+      <c r="A48" s="1">
         <v>4010013389</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C48" s="5">
+      <c r="C48" s="4">
         <v>46681</v>
       </c>
       <c r="D48" s="3" t="s">
@@ -2984,47 +2957,47 @@
       <c r="F48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G48" s="6">
-        <v>1120</v>
-      </c>
-      <c r="H48" s="4"/>
+      <c r="G48" s="5">
+        <v>1100</v>
+      </c>
+      <c r="H48" s="5"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="2">
-        <v>4010013389</v>
+      <c r="A49" s="1">
+        <v>4010013266</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C49" s="5">
-        <v>46621</v>
+        <v>16</v>
+      </c>
+      <c r="C49" s="4">
+        <v>46575</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G49" s="6">
-        <v>10</v>
-      </c>
-      <c r="H49" s="4"/>
+      <c r="G49" s="5">
+        <v>460</v>
+      </c>
+      <c r="H49" s="5"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="2">
-        <v>4010013266</v>
+      <c r="A50" s="1">
+        <v>4010013267</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C50" s="5">
-        <v>46575</v>
+        <v>18</v>
+      </c>
+      <c r="C50" s="4">
+        <v>46598</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>8</v>
@@ -3032,23 +3005,23 @@
       <c r="F50" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G50" s="6">
-        <v>460</v>
-      </c>
-      <c r="H50" s="4"/>
+      <c r="G50" s="5">
+        <v>640</v>
+      </c>
+      <c r="H50" s="5"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="2">
-        <v>4010013267</v>
+      <c r="A51" s="1">
+        <v>4010013553</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C51" s="5">
-        <v>46598</v>
+        <v>78</v>
+      </c>
+      <c r="C51" s="4">
+        <v>46575</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>8</v>
@@ -3056,23 +3029,23 @@
       <c r="F51" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G51" s="6">
-        <v>640</v>
-      </c>
-      <c r="H51" s="4"/>
+      <c r="G51" s="5">
+        <v>860</v>
+      </c>
+      <c r="H51" s="5"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="2">
-        <v>4010013553</v>
+      <c r="A52" s="1">
+        <v>4010013397</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C52" s="5">
-        <v>46575</v>
+        <v>41</v>
+      </c>
+      <c r="C52" s="4">
+        <v>46545</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>8</v>
@@ -3080,95 +3053,95 @@
       <c r="F52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G52" s="6">
-        <v>860</v>
-      </c>
-      <c r="H52" s="4"/>
+      <c r="G52" s="5">
+        <v>880</v>
+      </c>
+      <c r="H52" s="5"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="2">
-        <v>4010013397</v>
+      <c r="A53" s="1">
+        <v>6010000189</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C53" s="5">
-        <v>46545</v>
+        <v>365</v>
+      </c>
+      <c r="C53" s="4">
+        <v>46539</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>43</v>
+        <v>366</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G53" s="6">
-        <v>880</v>
-      </c>
-      <c r="H53" s="4"/>
+      <c r="G53" s="5">
+        <v>160</v>
+      </c>
+      <c r="H53" s="5"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="2">
-        <v>6010000189</v>
+      <c r="A54" s="1">
+        <v>6010000224</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="C54" s="5">
+        <v>413</v>
+      </c>
+      <c r="C54" s="4">
+        <v>46711</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G54" s="5">
+        <v>420</v>
+      </c>
+      <c r="H54" s="5"/>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
+        <v>6010000101</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C55" s="4">
         <v>46539</v>
       </c>
-      <c r="D54" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="E54" s="3" t="s">
+      <c r="D55" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="E55" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G54" s="6">
-        <v>160</v>
-      </c>
-      <c r="H54" s="4"/>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="2">
-        <v>6010000224</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="C55" s="5">
-        <v>46711</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>15</v>
-      </c>
       <c r="F55" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G55" s="6">
-        <v>420</v>
-      </c>
-      <c r="H55" s="4"/>
+      <c r="G55" s="5">
+        <v>290</v>
+      </c>
+      <c r="H55" s="5"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="2">
+      <c r="A56" s="1">
         <v>6010000101</v>
       </c>
       <c r="B56" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C56" s="4">
+        <v>46447</v>
+      </c>
+      <c r="D56" s="3" t="s">
         <v>246</v>
-      </c>
-      <c r="C56" s="5">
-        <v>46539</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>247</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>30</v>
@@ -3176,284 +3149,284 @@
       <c r="F56" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G56" s="6">
-        <v>290</v>
-      </c>
-      <c r="H56" s="4"/>
+      <c r="G56" s="5">
+        <v>230</v>
+      </c>
+      <c r="H56" s="5"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="2">
-        <v>6010000101</v>
+      <c r="A57" s="1">
+        <v>6010000232</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="C57" s="5">
-        <v>46447</v>
+        <v>419</v>
+      </c>
+      <c r="C57" s="4">
+        <v>46726</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>248</v>
+        <v>420</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G57" s="6">
-        <v>230</v>
-      </c>
-      <c r="H57" s="4"/>
+      <c r="G57" s="5">
+        <v>2840</v>
+      </c>
+      <c r="H57" s="5"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="2">
-        <v>6010000232</v>
+      <c r="A58" s="1">
+        <v>6010000073</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="C58" s="5">
-        <v>46726</v>
+        <v>181</v>
+      </c>
+      <c r="C58" s="4">
+        <v>46511</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>422</v>
+        <v>182</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>15</v>
+        <v>183</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G58" s="6">
-        <v>2840</v>
-      </c>
-      <c r="H58" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G58" s="5">
+        <v>1150</v>
+      </c>
+      <c r="H58" s="5"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="2">
-        <v>6010000073</v>
+      <c r="A59" s="1">
+        <v>6010000169</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="C59" s="5">
-        <v>46511</v>
+        <v>343</v>
+      </c>
+      <c r="C59" s="4">
+        <v>46751</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>184</v>
+        <v>344</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>185</v>
+        <v>107</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G59" s="6">
-        <v>1150</v>
-      </c>
-      <c r="H59" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="G59" s="5">
+        <v>2110</v>
+      </c>
+      <c r="H59" s="5"/>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="2">
-        <v>6010000169</v>
+      <c r="A60" s="1">
+        <v>6010000170</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="C60" s="5">
-        <v>46751</v>
+      <c r="C60" s="4">
+        <v>46721</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>346</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G60" s="6">
-        <v>2110</v>
-      </c>
-      <c r="H60" s="4"/>
+      <c r="G60" s="5">
+        <v>2590</v>
+      </c>
+      <c r="H60" s="5"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="2">
-        <v>6010000170</v>
+      <c r="A61" s="1">
+        <v>6010000139</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="C61" s="5">
-        <v>46721</v>
+        <v>299</v>
+      </c>
+      <c r="C61" s="4">
+        <v>46711</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>348</v>
+        <v>300</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>108</v>
+        <v>301</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G61" s="6">
-        <v>2590</v>
-      </c>
-      <c r="H61" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G61" s="5">
+        <v>1488</v>
+      </c>
+      <c r="H61" s="5"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="2">
-        <v>6010000139</v>
+      <c r="A62" s="1">
+        <v>6010000267</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="C62" s="5">
-        <v>46711</v>
+        <v>436</v>
+      </c>
+      <c r="C62" s="4">
+        <v>46813</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>302</v>
+        <v>437</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>303</v>
+        <v>438</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G62" s="6">
-        <v>1488</v>
-      </c>
-      <c r="H62" s="4"/>
+      <c r="G62" s="5">
+        <v>680</v>
+      </c>
+      <c r="H62" s="5"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="2">
-        <v>6010000267</v>
+      <c r="A63" s="1">
+        <v>6010000141</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="C63" s="5">
-        <v>46813</v>
+        <v>302</v>
+      </c>
+      <c r="C63" s="4">
+        <v>46746</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>443</v>
+        <v>303</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>444</v>
+        <v>301</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G63" s="6">
-        <v>800</v>
-      </c>
-      <c r="H63" s="4"/>
+      <c r="G63" s="5">
+        <v>2425</v>
+      </c>
+      <c r="H63" s="5"/>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="2">
-        <v>6010000141</v>
+      <c r="A64" s="1">
+        <v>6010000205</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="C64" s="5">
-        <v>46746</v>
+        <v>396</v>
+      </c>
+      <c r="C64" s="4">
+        <v>46692</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>305</v>
+        <v>397</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>303</v>
+        <v>398</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G64" s="6">
-        <v>2425</v>
-      </c>
-      <c r="H64" s="4"/>
+      <c r="G64" s="5">
+        <v>10050</v>
+      </c>
+      <c r="H64" s="5"/>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="2">
-        <v>6010000205</v>
+      <c r="A65" s="1">
+        <v>4010013583</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="C65" s="5">
-        <v>46692</v>
+        <v>92</v>
+      </c>
+      <c r="C65" s="4">
+        <v>46504</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>399</v>
+        <v>93</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>400</v>
+        <v>71</v>
       </c>
       <c r="F65" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G65" s="5">
+        <v>620</v>
+      </c>
+      <c r="H65" s="5"/>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
+        <v>6010000074</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C66" s="4">
+        <v>46721</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G65" s="6">
-        <v>10050</v>
-      </c>
-      <c r="H65" s="4"/>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="2">
-        <v>4010013583</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C66" s="5">
-        <v>46504</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="E66" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G66" s="6">
-        <v>620</v>
-      </c>
-      <c r="H66" s="4"/>
+      <c r="G66" s="5">
+        <v>6048</v>
+      </c>
+      <c r="H66" s="5"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="2">
-        <v>6010000074</v>
+      <c r="A67" s="1">
+        <v>6010000102</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="C67" s="5">
-        <v>46721</v>
+        <v>247</v>
+      </c>
+      <c r="C67" s="4">
+        <v>46780</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>187</v>
+        <v>248</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>188</v>
+        <v>22</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G67" s="6">
-        <v>7200</v>
-      </c>
-      <c r="H67" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="G67" s="5">
+        <v>4020</v>
+      </c>
+      <c r="H67" s="5"/>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="2">
-        <v>6010000102</v>
+      <c r="A68" s="1">
+        <v>6010000103</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="C68" s="5">
-        <v>46780</v>
+      <c r="C68" s="4">
+        <v>46645</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>250</v>
@@ -3464,143 +3437,143 @@
       <c r="F68" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G68" s="6">
-        <v>4220</v>
-      </c>
-      <c r="H68" s="4"/>
+      <c r="G68" s="5">
+        <v>2920</v>
+      </c>
+      <c r="H68" s="5"/>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="2">
-        <v>6010000103</v>
+      <c r="A69" s="1">
+        <v>6010000196</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="C69" s="5">
-        <v>46645</v>
+        <v>379</v>
+      </c>
+      <c r="C69" s="4">
+        <v>46606</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>252</v>
+        <v>380</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>22</v>
+        <v>381</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G69" s="6">
-        <v>2920</v>
-      </c>
-      <c r="H69" s="4"/>
+      <c r="G69" s="5">
+        <v>1640</v>
+      </c>
+      <c r="H69" s="5"/>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="2">
-        <v>6010000196</v>
+      <c r="A70" s="1">
+        <v>4010013473</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="C70" s="5">
-        <v>46606</v>
+        <v>50</v>
+      </c>
+      <c r="C70" s="4">
+        <v>46524</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>382</v>
+        <v>51</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>383</v>
+        <v>30</v>
       </c>
       <c r="F70" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G70" s="6">
-        <v>1640</v>
-      </c>
-      <c r="H70" s="4"/>
+      <c r="G70" s="5">
+        <v>420</v>
+      </c>
+      <c r="H70" s="5"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="2">
-        <v>4010013473</v>
+      <c r="A71" s="1">
+        <v>6010000151</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C71" s="5">
-        <v>46524</v>
+        <v>321</v>
+      </c>
+      <c r="C71" s="4">
+        <v>46692</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>52</v>
+        <v>322</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>30</v>
+        <v>323</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G71" s="6">
-        <v>420</v>
-      </c>
-      <c r="H71" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G71" s="5">
+        <v>540</v>
+      </c>
+      <c r="H71" s="5"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="2">
-        <v>6010000151</v>
+      <c r="A72" s="1">
+        <v>6010000241</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="C72" s="5">
-        <v>46692</v>
+        <v>429</v>
+      </c>
+      <c r="C72" s="4">
+        <v>46596</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>324</v>
+        <v>430</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>325</v>
+        <v>431</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G72" s="6">
-        <v>595</v>
-      </c>
-      <c r="H72" s="4"/>
+      <c r="G72" s="5">
+        <v>486</v>
+      </c>
+      <c r="H72" s="5"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="2">
-        <v>6010000241</v>
+      <c r="A73" s="1">
+        <v>6010000194</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>431</v>
-      </c>
-      <c r="C73" s="5">
-        <v>46596</v>
+        <v>374</v>
+      </c>
+      <c r="C73" s="4">
+        <v>46803</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>432</v>
+        <v>375</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>433</v>
+        <v>30</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G73" s="6">
-        <v>486</v>
-      </c>
-      <c r="H73" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="G73" s="5">
+        <v>1470</v>
+      </c>
+      <c r="H73" s="5"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="2">
+      <c r="A74" s="1">
         <v>6010000194</v>
       </c>
       <c r="B74" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="C74" s="4">
+        <v>46721</v>
+      </c>
+      <c r="D74" s="3" t="s">
         <v>376</v>
-      </c>
-      <c r="C74" s="5">
-        <v>46803</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>377</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>30</v>
@@ -3608,119 +3581,119 @@
       <c r="F74" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G74" s="6">
-        <v>1470</v>
-      </c>
-      <c r="H74" s="4"/>
+      <c r="G74" s="5">
+        <v>4080</v>
+      </c>
+      <c r="H74" s="5"/>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="2">
-        <v>6010000194</v>
+      <c r="A75" s="1">
+        <v>6010000192</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="C75" s="5">
-        <v>46721</v>
+        <v>367</v>
+      </c>
+      <c r="C75" s="4">
+        <v>46367</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="E75" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G75" s="5">
+        <v>365</v>
+      </c>
+      <c r="H75" s="5"/>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" s="1">
+        <v>6010000155</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C76" s="4">
+        <v>46447</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="E76" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F75" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G75" s="6">
-        <v>4080</v>
-      </c>
-      <c r="H75" s="4"/>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="2">
-        <v>6010000192</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="C76" s="5">
-        <v>46367</v>
-      </c>
-      <c r="D76" s="3" t="s">
+      <c r="F76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G76" s="5">
+        <v>380</v>
+      </c>
+      <c r="H76" s="5"/>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" s="1">
+        <v>6010000108</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C77" s="4">
+        <v>46574</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G77" s="5">
+        <v>560</v>
+      </c>
+      <c r="H77" s="5"/>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" s="1">
+        <v>6010000193</v>
+      </c>
+      <c r="B78" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="E76" s="3" t="s">
+      <c r="C78" s="4">
+        <v>46803</v>
+      </c>
+      <c r="D78" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="F76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G76" s="6">
-        <v>365</v>
-      </c>
-      <c r="H76" s="4"/>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="2">
-        <v>6010000155</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="C77" s="5">
-        <v>46447</v>
-      </c>
-      <c r="D77" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="E77" s="3" t="s">
+      <c r="E78" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F77" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G77" s="6">
-        <v>390</v>
-      </c>
-      <c r="H77" s="4"/>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="2">
-        <v>6010000108</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="C78" s="5">
-        <v>46574</v>
-      </c>
-      <c r="D78" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="E78" s="3" t="s">
-        <v>15</v>
-      </c>
       <c r="F78" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G78" s="6">
-        <v>560</v>
-      </c>
-      <c r="H78" s="4"/>
+      <c r="G78" s="5">
+        <v>380</v>
+      </c>
+      <c r="H78" s="5"/>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="2">
+      <c r="A79" s="1">
         <v>6010000193</v>
       </c>
       <c r="B79" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="C79" s="4">
+        <v>46726</v>
+      </c>
+      <c r="D79" s="3" t="s">
         <v>372</v>
-      </c>
-      <c r="C79" s="5">
-        <v>46711</v>
-      </c>
-      <c r="D79" s="3" t="s">
-        <v>373</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>30</v>
@@ -3728,23 +3701,23 @@
       <c r="F79" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G79" s="6">
-        <v>170</v>
-      </c>
-      <c r="H79" s="4"/>
+      <c r="G79" s="5">
+        <v>80</v>
+      </c>
+      <c r="H79" s="5"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="2">
+      <c r="A80" s="1">
         <v>6010000193</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="C80" s="5">
-        <v>46803</v>
+        <v>370</v>
+      </c>
+      <c r="C80" s="4">
+        <v>46711</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>30</v>
@@ -3752,23 +3725,23 @@
       <c r="F80" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G80" s="6">
-        <v>380</v>
-      </c>
-      <c r="H80" s="4"/>
+      <c r="G80" s="5">
+        <v>170</v>
+      </c>
+      <c r="H80" s="5"/>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="2">
-        <v>6010000193</v>
+      <c r="A81" s="1">
+        <v>6010000216</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="C81" s="5">
-        <v>46726</v>
+        <v>404</v>
+      </c>
+      <c r="C81" s="4">
+        <v>46690</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>375</v>
+        <v>405</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>30</v>
@@ -3776,71 +3749,71 @@
       <c r="F81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G81" s="6">
-        <v>80</v>
-      </c>
-      <c r="H81" s="4"/>
+      <c r="G81" s="5">
+        <v>140</v>
+      </c>
+      <c r="H81" s="5"/>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="2">
-        <v>6010000216</v>
+      <c r="A82" s="1">
+        <v>6010000235</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="C82" s="5">
-        <v>46690</v>
+        <v>425</v>
+      </c>
+      <c r="C82" s="4">
+        <v>46808</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>407</v>
+        <v>426</v>
       </c>
       <c r="E82" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G82" s="5">
+        <v>1640</v>
+      </c>
+      <c r="H82" s="5"/>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" s="1">
+        <v>4010013662</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C83" s="4">
+        <v>46537</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E83" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F82" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G82" s="6">
-        <v>140</v>
-      </c>
-      <c r="H82" s="4"/>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="2">
-        <v>6010000235</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>427</v>
-      </c>
-      <c r="C83" s="5">
-        <v>46808</v>
-      </c>
-      <c r="D83" s="3" t="s">
-        <v>428</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>15</v>
-      </c>
       <c r="F83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G83" s="6">
-        <v>1640</v>
-      </c>
-      <c r="H83" s="4"/>
+      <c r="G83" s="5">
+        <v>190</v>
+      </c>
+      <c r="H83" s="5"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="2">
+      <c r="A84" s="1">
         <v>4010013662</v>
       </c>
       <c r="B84" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C84" s="4">
+        <v>46546</v>
+      </c>
+      <c r="D84" s="3" t="s">
         <v>136</v>
-      </c>
-      <c r="C84" s="5">
-        <v>46537</v>
-      </c>
-      <c r="D84" s="3" t="s">
-        <v>137</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>30</v>
@@ -3848,67 +3821,67 @@
       <c r="F84" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G84" s="6">
-        <v>190</v>
-      </c>
-      <c r="H84" s="4"/>
+      <c r="G84" s="5">
+        <v>420</v>
+      </c>
+      <c r="H84" s="5"/>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="2">
-        <v>4010013662</v>
+      <c r="A85" s="1">
+        <v>6010000076</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="C85" s="5">
-        <v>46546</v>
+        <v>187</v>
+      </c>
+      <c r="C85" s="4">
+        <v>46483</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>138</v>
+        <v>188</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>30</v>
+        <v>186</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G85" s="6">
-        <v>420</v>
-      </c>
-      <c r="H85" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G85" s="5">
+        <v>3076</v>
+      </c>
+      <c r="H85" s="5"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" s="2">
-        <v>6010000076</v>
+      <c r="A86" s="1">
+        <v>6010000110</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="C86" s="5">
-        <v>46483</v>
+        <v>253</v>
+      </c>
+      <c r="C86" s="4">
+        <v>46640</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>190</v>
+        <v>254</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>188</v>
+        <v>4</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G86" s="6">
-        <v>3076</v>
-      </c>
-      <c r="H86" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="G86" s="5">
+        <v>1000</v>
+      </c>
+      <c r="H86" s="5"/>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" s="2">
-        <v>6010000110</v>
+      <c r="A87" s="1">
+        <v>6010000111</v>
       </c>
       <c r="B87" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="C87" s="5">
+      <c r="C87" s="4">
         <v>46640</v>
       </c>
       <c r="D87" s="3" t="s">
@@ -3920,239 +3893,239 @@
       <c r="F87" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G87" s="6">
-        <v>1000</v>
-      </c>
-      <c r="H87" s="4"/>
+      <c r="G87" s="5">
+        <v>2640</v>
+      </c>
+      <c r="H87" s="5"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="2">
-        <v>6010000111</v>
+      <c r="A88" s="1">
+        <v>4010013584</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="C88" s="5">
-        <v>46640</v>
+        <v>94</v>
+      </c>
+      <c r="C88" s="4">
+        <v>46532</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>258</v>
+        <v>95</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>4</v>
+        <v>88</v>
       </c>
       <c r="F88" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G88" s="6">
-        <v>2640</v>
-      </c>
-      <c r="H88" s="4"/>
+      <c r="G88" s="5">
+        <v>200</v>
+      </c>
+      <c r="H88" s="5"/>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="2">
+      <c r="A89" s="1">
         <v>4010013584</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C89" s="5">
-        <v>46532</v>
+        <v>94</v>
+      </c>
+      <c r="C89" s="4">
+        <v>46537</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>96</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G89" s="6">
-        <v>200</v>
-      </c>
-      <c r="H89" s="4"/>
+      <c r="G89" s="5">
+        <v>380</v>
+      </c>
+      <c r="H89" s="5"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90" s="2">
-        <v>4010013584</v>
+      <c r="A90" s="1">
+        <v>6010000171</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C90" s="5">
-        <v>46537</v>
+        <v>347</v>
+      </c>
+      <c r="C90" s="4">
+        <v>46579</v>
       </c>
       <c r="D90" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G90" s="5">
+        <v>1500</v>
+      </c>
+      <c r="H90" s="5"/>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" s="1">
+        <v>4010013585</v>
+      </c>
+      <c r="B91" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="E90" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="F90" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G90" s="6">
-        <v>380</v>
-      </c>
-      <c r="H90" s="4"/>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A91" s="2">
-        <v>6010000171</v>
-      </c>
-      <c r="B91" s="3" t="s">
+      <c r="C91" s="4">
+        <v>46568</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G91" s="5">
+        <v>1500</v>
+      </c>
+      <c r="H91" s="5"/>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" s="1">
+        <v>6010000172</v>
+      </c>
+      <c r="B92" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="C91" s="5">
+      <c r="C92" s="4">
         <v>46579</v>
       </c>
-      <c r="D91" s="3" t="s">
+      <c r="D92" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="E91" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="F91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G91" s="6">
-        <v>1500</v>
-      </c>
-      <c r="H91" s="4"/>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A92" s="2">
-        <v>4010013585</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C92" s="5">
-        <v>46568</v>
-      </c>
-      <c r="D92" s="3" t="s">
-        <v>99</v>
-      </c>
       <c r="E92" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F92" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G92" s="6">
-        <v>1500</v>
-      </c>
-      <c r="H92" s="4"/>
+      <c r="G92" s="5">
+        <v>1700</v>
+      </c>
+      <c r="H92" s="5"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A93" s="2">
-        <v>6010000172</v>
+      <c r="A93" s="1">
+        <v>6010000077</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="C93" s="5">
-        <v>46579</v>
+        <v>189</v>
+      </c>
+      <c r="C93" s="4">
+        <v>46471</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>352</v>
+        <v>190</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>89</v>
+        <v>191</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G93" s="6">
-        <v>1700</v>
-      </c>
-      <c r="H93" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G93" s="5">
+        <v>5070</v>
+      </c>
+      <c r="H93" s="5"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A94" s="2">
-        <v>6010000077</v>
+      <c r="A94" s="1">
+        <v>6010000078</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="C94" s="5">
-        <v>46471</v>
+        <v>192</v>
+      </c>
+      <c r="C94" s="4">
+        <v>46780</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G94" s="6">
-        <v>5220</v>
-      </c>
-      <c r="H94" s="4"/>
+      <c r="G94" s="5">
+        <v>7200</v>
+      </c>
+      <c r="H94" s="5"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A95" s="2">
-        <v>6010000078</v>
+      <c r="A95" s="1">
+        <v>6010000079</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="C95" s="5">
-        <v>46780</v>
+        <v>195</v>
+      </c>
+      <c r="C95" s="4">
+        <v>46512</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F95" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G95" s="6">
-        <v>7200</v>
-      </c>
-      <c r="H95" s="4"/>
+      <c r="G95" s="5">
+        <v>310</v>
+      </c>
+      <c r="H95" s="5"/>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A96" s="2">
-        <v>6010000079</v>
+      <c r="A96" s="1">
+        <v>4010013593</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="C96" s="5">
-        <v>46512</v>
+        <v>108</v>
+      </c>
+      <c r="C96" s="4">
+        <v>46758</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>198</v>
+        <v>109</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>199</v>
+        <v>30</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G96" s="6">
-        <v>310</v>
-      </c>
-      <c r="H96" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="G96" s="5">
+        <v>560</v>
+      </c>
+      <c r="H96" s="5"/>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A97" s="2">
-        <v>4010013593</v>
+      <c r="A97" s="1">
+        <v>4010014329</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C97" s="5">
-        <v>46758</v>
+        <v>159</v>
+      </c>
+      <c r="C97" s="4">
+        <v>46641</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>30</v>
@@ -4160,23 +4133,23 @@
       <c r="F97" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G97" s="6">
-        <v>560</v>
-      </c>
-      <c r="H97" s="4"/>
+      <c r="G97" s="5">
+        <v>230</v>
+      </c>
+      <c r="H97" s="5"/>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A98" s="2">
-        <v>4010014329</v>
+      <c r="A98" s="1">
+        <v>4010013594</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="C98" s="5">
-        <v>46641</v>
+        <v>110</v>
+      </c>
+      <c r="C98" s="4">
+        <v>46573</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>30</v>
@@ -4184,23 +4157,23 @@
       <c r="F98" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G98" s="6">
-        <v>230</v>
-      </c>
-      <c r="H98" s="4"/>
+      <c r="G98" s="5">
+        <v>760</v>
+      </c>
+      <c r="H98" s="5"/>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A99" s="2">
-        <v>4010013594</v>
+      <c r="A99" s="1">
+        <v>4010014330</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C99" s="5">
-        <v>46573</v>
+        <v>161</v>
+      </c>
+      <c r="C99" s="4">
+        <v>46610</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>112</v>
+        <v>162</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>30</v>
@@ -4208,23 +4181,23 @@
       <c r="F99" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G99" s="6">
-        <v>820</v>
-      </c>
-      <c r="H99" s="4"/>
+      <c r="G99" s="5">
+        <v>280</v>
+      </c>
+      <c r="H99" s="5"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A100" s="2">
-        <v>4010014330</v>
+      <c r="A100" s="1">
+        <v>6010000156</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="C100" s="5">
-        <v>46610</v>
+        <v>329</v>
+      </c>
+      <c r="C100" s="4">
+        <v>46447</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>164</v>
+        <v>330</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>30</v>
@@ -4232,23 +4205,23 @@
       <c r="F100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G100" s="6">
-        <v>280</v>
-      </c>
-      <c r="H100" s="4"/>
+      <c r="G100" s="5">
+        <v>300</v>
+      </c>
+      <c r="H100" s="5"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A101" s="2">
-        <v>6010000156</v>
+      <c r="A101" s="1">
+        <v>6010000233</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="C101" s="5">
-        <v>46447</v>
+        <v>329</v>
+      </c>
+      <c r="C101" s="4">
+        <v>46721</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>332</v>
+        <v>421</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>30</v>
@@ -4256,381 +4229,381 @@
       <c r="F101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G101" s="6">
+      <c r="G101" s="5">
+        <v>110</v>
+      </c>
+      <c r="H101" s="5"/>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" s="1">
+        <v>6010000080</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C102" s="4">
+        <v>46423</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G102" s="5">
+        <v>500</v>
+      </c>
+      <c r="H102" s="5"/>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" s="1">
+        <v>6010000113</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C103" s="4">
+        <v>46598</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F103" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G103" s="5">
+        <v>8340</v>
+      </c>
+      <c r="H103" s="5"/>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" s="1">
+        <v>4010013656</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C104" s="4">
+        <v>46510</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G104" s="5">
+        <v>2340</v>
+      </c>
+      <c r="H104" s="5"/>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" s="6">
+        <v>4010013595</v>
+      </c>
+      <c r="B105" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C105" s="8"/>
+      <c r="D105" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E105" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F105" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G105" s="9"/>
+      <c r="H105" s="9">
         <v>300</v>
       </c>
-      <c r="H101" s="4"/>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A102" s="2">
-        <v>6010000233</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="C102" s="5">
-        <v>46721</v>
-      </c>
-      <c r="D102" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G102" s="6">
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" s="1">
+        <v>6010000174</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="C106" s="4">
+        <v>46586</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G106" s="5">
+        <v>1120</v>
+      </c>
+      <c r="H106" s="5"/>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" s="1">
+        <v>6010000114</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C107" s="4">
+        <v>46488</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="E107" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="F107" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G107" s="5">
+        <v>2000</v>
+      </c>
+      <c r="H107" s="5"/>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" s="1">
+        <v>6010000081</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C108" s="4">
+        <v>46660</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F108" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G108" s="5">
+        <v>750</v>
+      </c>
+      <c r="H108" s="5"/>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" s="1">
+        <v>6010000082</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C109" s="4">
+        <v>46505</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="F109" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G109" s="5">
+        <v>11100</v>
+      </c>
+      <c r="H109" s="5"/>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" s="1">
+        <v>6010000175</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="C110" s="4">
+        <v>46556</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="F110" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G110" s="5">
+        <v>1900</v>
+      </c>
+      <c r="H110" s="5"/>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" s="1">
+        <v>6010000176</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="C111" s="4">
+        <v>46586</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="F111" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G111" s="5">
+        <v>1980</v>
+      </c>
+      <c r="H111" s="5"/>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" s="1">
+        <v>6010000201</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="C112" s="4">
+        <v>46624</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G112" s="5">
+        <v>910</v>
+      </c>
+      <c r="H112" s="5"/>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" s="1">
+        <v>6010000202</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="C113" s="4">
+        <v>46685</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="F113" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G113" s="5">
+        <v>830</v>
+      </c>
+      <c r="H113" s="5"/>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" s="1">
+        <v>4010013262</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C114" s="4">
+        <v>46549</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G114" s="5">
+        <v>420</v>
+      </c>
+      <c r="H114" s="5"/>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" s="1">
+        <v>4010013465</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C115" s="4">
+        <v>46637</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F115" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G115" s="5">
+        <v>1720</v>
+      </c>
+      <c r="H115" s="5"/>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" s="1">
+        <v>4010013466</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C116" s="4">
+        <v>46704</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G116" s="5">
         <v>120</v>
       </c>
-      <c r="H102" s="4"/>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A103" s="2">
-        <v>6010000080</v>
-      </c>
-      <c r="B103" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="C103" s="5">
-        <v>46423</v>
-      </c>
-      <c r="D103" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="E103" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="F103" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G103" s="6">
-        <v>500</v>
-      </c>
-      <c r="H103" s="4"/>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A104" s="2">
-        <v>6010000113</v>
-      </c>
-      <c r="B104" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="C104" s="5">
-        <v>46598</v>
-      </c>
-      <c r="D104" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="E104" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F104" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G104" s="6">
-        <v>8640</v>
-      </c>
-      <c r="H104" s="4"/>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A105" s="2">
-        <v>4010013656</v>
-      </c>
-      <c r="B105" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C105" s="5">
-        <v>46423</v>
-      </c>
-      <c r="D105" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="E105" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="F105" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G105" s="6">
-        <v>20</v>
-      </c>
-      <c r="H105" s="4"/>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A106" s="2">
-        <v>4010013656</v>
-      </c>
-      <c r="B106" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C106" s="5">
-        <v>46510</v>
-      </c>
-      <c r="D106" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="E106" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="F106" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G106" s="6">
-        <v>2380</v>
-      </c>
-      <c r="H106" s="4"/>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A107" s="9">
-        <v>4010013595</v>
-      </c>
-      <c r="B107" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="C107" s="11"/>
-      <c r="D107" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="E107" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F107" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G107" s="12"/>
-      <c r="H107" s="13">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A108" s="2">
-        <v>6010000174</v>
-      </c>
-      <c r="B108" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="C108" s="5">
-        <v>46586</v>
-      </c>
-      <c r="D108" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="E108" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="F108" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G108" s="6">
-        <v>1140</v>
-      </c>
-      <c r="H108" s="4"/>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A109" s="2">
-        <v>6010000114</v>
-      </c>
-      <c r="B109" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="C109" s="5">
-        <v>46488</v>
-      </c>
-      <c r="D109" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="E109" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="F109" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G109" s="6">
-        <v>2000</v>
-      </c>
-      <c r="H109" s="4"/>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A110" s="2">
-        <v>6010000081</v>
-      </c>
-      <c r="B110" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="C110" s="5">
-        <v>46660</v>
-      </c>
-      <c r="D110" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="E110" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F110" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G110" s="6">
-        <v>750</v>
-      </c>
-      <c r="H110" s="4"/>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A111" s="2">
-        <v>6010000082</v>
-      </c>
-      <c r="B111" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="C111" s="5">
-        <v>46505</v>
-      </c>
-      <c r="D111" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="E111" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="F111" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G111" s="6">
-        <v>11100</v>
-      </c>
-      <c r="H111" s="4"/>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A112" s="2">
-        <v>6010000175</v>
-      </c>
-      <c r="B112" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="C112" s="5">
-        <v>46556</v>
-      </c>
-      <c r="D112" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="E112" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="F112" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G112" s="6">
-        <v>1900</v>
-      </c>
-      <c r="H112" s="4"/>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A113" s="2">
-        <v>6010000176</v>
-      </c>
-      <c r="B113" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="C113" s="5">
-        <v>46586</v>
-      </c>
-      <c r="D113" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="E113" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="F113" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G113" s="6">
-        <v>1980</v>
-      </c>
-      <c r="H113" s="4"/>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A114" s="2">
-        <v>6010000201</v>
-      </c>
-      <c r="B114" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="C114" s="5">
-        <v>46624</v>
-      </c>
-      <c r="D114" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="E114" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="F114" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G114" s="6">
-        <v>910</v>
-      </c>
-      <c r="H114" s="4"/>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A115" s="2">
-        <v>6010000202</v>
-      </c>
-      <c r="B115" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="C115" s="5">
-        <v>46685</v>
-      </c>
-      <c r="D115" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="E115" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="F115" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G115" s="6">
-        <v>830</v>
-      </c>
-      <c r="H115" s="4"/>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A116" s="2">
-        <v>4010013262</v>
-      </c>
-      <c r="B116" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C116" s="5">
-        <v>46549</v>
-      </c>
-      <c r="D116" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E116" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F116" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G116" s="6">
-        <v>420</v>
-      </c>
-      <c r="H116" s="4"/>
+      <c r="H116" s="5"/>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A117" s="2">
-        <v>4010013465</v>
+      <c r="A117" s="1">
+        <v>4010013671</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C117" s="5">
-        <v>46637</v>
+        <v>143</v>
+      </c>
+      <c r="C117" s="4">
+        <v>46566</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="E117" s="3" t="s">
         <v>15</v>
@@ -4638,307 +4611,307 @@
       <c r="F117" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G117" s="6">
-        <v>1720</v>
-      </c>
-      <c r="H117" s="4"/>
+      <c r="G117" s="5">
+        <v>980</v>
+      </c>
+      <c r="H117" s="5"/>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A118" s="2">
-        <v>4010013466</v>
+      <c r="A118" s="1">
+        <v>6010000252</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C118" s="5">
-        <v>46704</v>
+        <v>432</v>
+      </c>
+      <c r="C118" s="4">
+        <v>46780</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>49</v>
+        <v>433</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>50</v>
+        <v>434</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G118" s="6">
-        <v>120</v>
-      </c>
-      <c r="H118" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G118" s="5">
+        <v>1500</v>
+      </c>
+      <c r="H118" s="5"/>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A119" s="2">
-        <v>4010013671</v>
+      <c r="A119" s="1">
+        <v>6010000252</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C119" s="5">
-        <v>46566</v>
+        <v>432</v>
+      </c>
+      <c r="C119" s="4">
+        <v>46661</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>146</v>
+        <v>435</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>15</v>
+        <v>434</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G119" s="6">
-        <v>980</v>
-      </c>
-      <c r="H119" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G119" s="5">
+        <v>690</v>
+      </c>
+      <c r="H119" s="5"/>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A120" s="2">
-        <v>6010000252</v>
+      <c r="A120" s="1">
+        <v>6010000218</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>438</v>
-      </c>
-      <c r="C120" s="5">
-        <v>46780</v>
+        <v>409</v>
+      </c>
+      <c r="C120" s="4">
+        <v>46812</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>439</v>
+        <v>410</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>440</v>
+        <v>411</v>
       </c>
       <c r="F120" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G120" s="6">
-        <v>1500</v>
-      </c>
-      <c r="H120" s="4"/>
+      <c r="G120" s="5">
+        <v>500</v>
+      </c>
+      <c r="H120" s="5"/>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A121" s="2">
-        <v>6010000252</v>
+      <c r="A121" s="1">
+        <v>6010000218</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>438</v>
-      </c>
-      <c r="C121" s="5">
-        <v>46661</v>
+        <v>409</v>
+      </c>
+      <c r="C121" s="4">
+        <v>46780</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>441</v>
+        <v>412</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>440</v>
+        <v>411</v>
       </c>
       <c r="F121" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G121" s="6">
-        <v>690</v>
-      </c>
-      <c r="H121" s="4"/>
+      <c r="G121" s="5">
+        <v>2400</v>
+      </c>
+      <c r="H121" s="5"/>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A122" s="2">
-        <v>6010000218</v>
+      <c r="A122" s="1">
+        <v>6010000083</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="C122" s="5">
-        <v>46780</v>
+        <v>206</v>
+      </c>
+      <c r="C122" s="4">
+        <v>46537</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>412</v>
+        <v>207</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>413</v>
+        <v>208</v>
       </c>
       <c r="F122" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G122" s="6">
-        <v>2400</v>
-      </c>
-      <c r="H122" s="4"/>
+      <c r="G122" s="5">
+        <v>1280</v>
+      </c>
+      <c r="H122" s="5"/>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A123" s="2">
-        <v>6010000218</v>
+      <c r="A123" s="1">
+        <v>6010000084</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="C123" s="5">
-        <v>46812</v>
+        <v>209</v>
+      </c>
+      <c r="C123" s="4">
+        <v>46711</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>414</v>
+        <v>210</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>413</v>
+        <v>211</v>
       </c>
       <c r="F123" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G123" s="6">
-        <v>500</v>
-      </c>
-      <c r="H123" s="4"/>
+      <c r="G123" s="5">
+        <v>4580</v>
+      </c>
+      <c r="H123" s="5"/>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A124" s="2">
-        <v>6010000083</v>
-      </c>
-      <c r="B124" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="C124" s="5">
-        <v>46537</v>
-      </c>
-      <c r="D124" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="E124" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="F124" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G124" s="6">
-        <v>1280</v>
-      </c>
-      <c r="H124" s="4"/>
+      <c r="A124" s="6">
+        <v>6010000115</v>
+      </c>
+      <c r="B124" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C124" s="8"/>
+      <c r="D124" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E124" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F124" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G124" s="9"/>
+      <c r="H124" s="9">
+        <v>6000</v>
+      </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A125" s="2">
-        <v>6010000084</v>
+      <c r="A125" s="1">
+        <v>6010000115</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="C125" s="5">
-        <v>46711</v>
+        <v>261</v>
+      </c>
+      <c r="C125" s="4">
+        <v>46971</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>212</v>
+        <v>262</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>213</v>
+        <v>22</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G125" s="6">
-        <v>4580</v>
-      </c>
-      <c r="H125" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="G125" s="5">
+        <v>3500</v>
+      </c>
+      <c r="H125" s="5"/>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A126" s="2">
-        <v>6010000115</v>
+      <c r="A126" s="1">
+        <v>6010000116</v>
       </c>
       <c r="B126" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="C126" s="5">
+      <c r="C126" s="4">
         <v>46971</v>
       </c>
       <c r="D126" s="3" t="s">
         <v>264</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F126" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G126" s="6">
-        <v>3500</v>
-      </c>
-      <c r="H126" s="4"/>
+      <c r="G126" s="5">
+        <v>4880</v>
+      </c>
+      <c r="H126" s="5"/>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A127" s="9">
-        <v>6010000115</v>
-      </c>
-      <c r="B127" s="10" t="s">
-        <v>263</v>
-      </c>
-      <c r="C127" s="11"/>
-      <c r="D127" s="10" t="s">
+      <c r="A127" s="1">
+        <v>7050000019</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="C127" s="4"/>
+      <c r="D127" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E127" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="F127" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G127" s="12"/>
-      <c r="H127" s="13">
-        <v>6000</v>
-      </c>
+      <c r="E127" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F127" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G127" s="5">
+        <v>530</v>
+      </c>
+      <c r="H127" s="5"/>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A128" s="2">
-        <v>6010000116</v>
+      <c r="A128" s="1">
+        <v>6010000117</v>
       </c>
       <c r="B128" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="C128" s="5">
-        <v>46971</v>
+      <c r="C128" s="4">
+        <v>46711</v>
       </c>
       <c r="D128" s="3" t="s">
         <v>266</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F128" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G128" s="6">
-        <v>4880</v>
-      </c>
-      <c r="H128" s="4"/>
+      <c r="G128" s="5">
+        <v>6100</v>
+      </c>
+      <c r="H128" s="5"/>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A129" s="2">
-        <v>7050000019</v>
+      <c r="A129" s="1">
+        <v>6010000118</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="C129" s="5"/>
+        <v>267</v>
+      </c>
+      <c r="C129" s="4">
+        <v>46574</v>
+      </c>
       <c r="D129" s="3" t="s">
-        <v>2</v>
+        <v>268</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="F129" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G129" s="6">
-        <v>530</v>
-      </c>
-      <c r="H129" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="G129" s="5">
+        <v>10240</v>
+      </c>
+      <c r="H129" s="5"/>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A130" s="2">
-        <v>6010000117</v>
+      <c r="A130" s="1">
+        <v>6010000148</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="C130" s="5">
-        <v>46711</v>
+        <v>319</v>
+      </c>
+      <c r="C130" s="4">
+        <v>46751</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>268</v>
+        <v>320</v>
       </c>
       <c r="E130" s="3" t="s">
         <v>22</v>
@@ -4946,375 +4919,375 @@
       <c r="F130" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G130" s="6">
-        <v>6100</v>
-      </c>
-      <c r="H130" s="4"/>
+      <c r="G130" s="5">
+        <v>2420</v>
+      </c>
+      <c r="H130" s="5"/>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A131" s="2">
-        <v>6010000118</v>
-      </c>
-      <c r="B131" s="3" t="s">
+      <c r="A131" s="6">
+        <v>6010000119</v>
+      </c>
+      <c r="B131" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="C131" s="5">
-        <v>46574</v>
-      </c>
-      <c r="D131" s="3" t="s">
+      <c r="C131" s="8"/>
+      <c r="D131" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E131" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="E131" s="3" t="s">
+      <c r="F131" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G131" s="9"/>
+      <c r="H131" s="9">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" s="1">
+        <v>6010000085</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C132" s="4">
+        <v>46388</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E132" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="F132" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G132" s="5">
+        <v>1000</v>
+      </c>
+      <c r="H132" s="5"/>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133" s="6">
+        <v>6010000085</v>
+      </c>
+      <c r="B133" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="C133" s="8"/>
+      <c r="D133" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E133" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="F133" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="G133" s="9"/>
+      <c r="H133" s="9">
+        <v>54000</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134" s="1">
+        <v>6010000123</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C134" s="4">
+        <v>46752</v>
+      </c>
+      <c r="D134" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E134" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F134" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G134" s="5">
+        <v>4960</v>
+      </c>
+      <c r="H134" s="5"/>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" s="6">
+        <v>6010000230</v>
+      </c>
+      <c r="B135" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="C135" s="8"/>
+      <c r="D135" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E135" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="F131" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G131" s="6">
-        <v>10240</v>
-      </c>
-      <c r="H131" s="4"/>
-    </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A132" s="2">
-        <v>6010000148</v>
-      </c>
-      <c r="B132" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="C132" s="5">
-        <v>46751</v>
-      </c>
-      <c r="D132" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="E132" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F132" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G132" s="6">
-        <v>2420</v>
-      </c>
-      <c r="H132" s="4"/>
-    </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A133" s="9">
-        <v>6010000119</v>
-      </c>
-      <c r="B133" s="10" t="s">
-        <v>271</v>
-      </c>
-      <c r="C133" s="11"/>
-      <c r="D133" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="E133" s="10" t="s">
-        <v>272</v>
-      </c>
-      <c r="F133" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G133" s="12"/>
-      <c r="H133" s="13">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A134" s="2">
-        <v>6010000085</v>
-      </c>
-      <c r="B134" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="C134" s="5">
-        <v>46388</v>
-      </c>
-      <c r="D134" s="3" t="s">
+      <c r="F135" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G135" s="9"/>
+      <c r="H135" s="9">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136" s="1">
+        <v>6010000086</v>
+      </c>
+      <c r="B136" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="E134" s="3" t="s">
+      <c r="C136" s="4">
+        <v>46641</v>
+      </c>
+      <c r="D136" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="F134" s="3" t="s">
+      <c r="E136" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="F136" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G134" s="6">
-        <v>1500</v>
-      </c>
-      <c r="H134" s="4"/>
-    </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A135" s="9">
-        <v>6010000085</v>
-      </c>
-      <c r="B135" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="C135" s="11"/>
-      <c r="D135" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="E135" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="F135" s="10" t="s">
+      <c r="G136" s="5">
+        <v>7500</v>
+      </c>
+      <c r="H136" s="5"/>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137" s="1">
+        <v>6010000147</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="C137" s="4">
+        <v>46813</v>
+      </c>
+      <c r="D137" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E137" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="F137" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G135" s="12"/>
-      <c r="H135" s="13">
-        <v>54000</v>
-      </c>
-    </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A136" s="2">
-        <v>6010000123</v>
-      </c>
-      <c r="B136" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="C136" s="5">
-        <v>46752</v>
-      </c>
-      <c r="D136" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="E136" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="F136" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G136" s="6">
-        <v>4960</v>
-      </c>
-      <c r="H136" s="4"/>
-    </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A137" s="9">
-        <v>6010000230</v>
-      </c>
-      <c r="B137" s="10" t="s">
-        <v>420</v>
-      </c>
-      <c r="C137" s="11"/>
-      <c r="D137" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="E137" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="F137" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G137" s="12"/>
-      <c r="H137" s="13">
-        <v>3600</v>
-      </c>
+      <c r="G137" s="5">
+        <v>700</v>
+      </c>
+      <c r="H137" s="5"/>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A138" s="2">
-        <v>6010000086</v>
+      <c r="A138" s="1">
+        <v>6010000144</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="C138" s="5">
-        <v>46641</v>
+        <v>309</v>
+      </c>
+      <c r="C138" s="4">
+        <v>46605</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>218</v>
+        <v>310</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>219</v>
+        <v>301</v>
       </c>
       <c r="F138" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G138" s="6">
-        <v>7600</v>
-      </c>
-      <c r="H138" s="4"/>
+      <c r="G138" s="5">
+        <v>890</v>
+      </c>
+      <c r="H138" s="5"/>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A139" s="2">
-        <v>6010000147</v>
+      <c r="A139" s="1">
+        <v>6010000214</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="C139" s="5">
-        <v>46813</v>
+        <v>399</v>
+      </c>
+      <c r="C139" s="4">
+        <v>46692</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>320</v>
+        <v>400</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="F139" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G139" s="6">
-        <v>700</v>
-      </c>
-      <c r="H139" s="4"/>
+      <c r="G139" s="5">
+        <v>340</v>
+      </c>
+      <c r="H139" s="5"/>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A140" s="2">
-        <v>6010000144</v>
+      <c r="A140" s="1">
+        <v>6010000215</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="C140" s="5">
-        <v>46605</v>
+        <v>401</v>
+      </c>
+      <c r="C140" s="4">
+        <v>46726</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>312</v>
+        <v>402</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>303</v>
+        <v>403</v>
       </c>
       <c r="F140" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G140" s="6">
-        <v>890</v>
-      </c>
-      <c r="H140" s="4"/>
+      <c r="G140" s="5">
+        <v>506</v>
+      </c>
+      <c r="H140" s="5"/>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A141" s="2">
-        <v>6010000214</v>
-      </c>
-      <c r="B141" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="C141" s="5">
-        <v>46692</v>
-      </c>
-      <c r="D141" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="E141" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="F141" s="3" t="s">
+      <c r="A141" s="6">
+        <v>6010000142</v>
+      </c>
+      <c r="B141" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="C141" s="8"/>
+      <c r="D141" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E141" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="F141" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G141" s="6">
-        <v>340</v>
-      </c>
-      <c r="H141" s="4"/>
+      <c r="G141" s="9"/>
+      <c r="H141" s="9">
+        <v>250</v>
+      </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A142" s="2">
-        <v>6010000215</v>
+      <c r="A142" s="1">
+        <v>6010000143</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="C142" s="5">
-        <v>46726</v>
+        <v>306</v>
+      </c>
+      <c r="C142" s="4">
+        <v>46425</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>404</v>
+        <v>307</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>405</v>
+        <v>308</v>
       </c>
       <c r="F142" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G142" s="6">
-        <v>506</v>
-      </c>
-      <c r="H142" s="4"/>
+      <c r="G142" s="5">
+        <v>107</v>
+      </c>
+      <c r="H142" s="5"/>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A143" s="9">
-        <v>6010000142</v>
-      </c>
-      <c r="B143" s="10" t="s">
-        <v>306</v>
-      </c>
-      <c r="C143" s="11"/>
-      <c r="D143" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="E143" s="10" t="s">
-        <v>307</v>
-      </c>
-      <c r="F143" s="10" t="s">
+      <c r="A143" s="1">
+        <v>6010000145</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C143" s="4">
+        <v>46556</v>
+      </c>
+      <c r="D143" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E143" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="F143" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G143" s="12"/>
-      <c r="H143" s="13">
-        <v>250</v>
-      </c>
+      <c r="G143" s="5">
+        <v>239</v>
+      </c>
+      <c r="H143" s="5"/>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A144" s="2">
-        <v>6010000143</v>
+      <c r="A144" s="1">
+        <v>4010013596</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="C144" s="5">
-        <v>46425</v>
+        <v>113</v>
+      </c>
+      <c r="C144" s="4">
+        <v>46446</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>309</v>
+        <v>114</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>310</v>
+        <v>30</v>
       </c>
       <c r="F144" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G144" s="6">
-        <v>107</v>
-      </c>
-      <c r="H144" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="G144" s="5">
+        <v>370</v>
+      </c>
+      <c r="H144" s="5"/>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A145" s="2">
-        <v>6010000145</v>
+      <c r="A145" s="1">
+        <v>4010013655</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="C145" s="5">
-        <v>46556</v>
+        <v>120</v>
+      </c>
+      <c r="C145" s="4">
+        <v>46550</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>314</v>
+        <v>121</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>315</v>
+        <v>30</v>
       </c>
       <c r="F145" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G145" s="6">
-        <v>239</v>
-      </c>
-      <c r="H145" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="G145" s="5">
+        <v>700</v>
+      </c>
+      <c r="H145" s="5"/>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A146" s="2">
-        <v>4010013596</v>
+      <c r="A146" s="1">
+        <v>4010013474</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C146" s="5">
-        <v>46446</v>
+        <v>52</v>
+      </c>
+      <c r="C146" s="4">
+        <v>46579</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>115</v>
+        <v>53</v>
       </c>
       <c r="E146" s="3" t="s">
         <v>30</v>
@@ -5322,23 +5295,23 @@
       <c r="F146" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G146" s="6">
-        <v>370</v>
-      </c>
-      <c r="H146" s="4"/>
+      <c r="G146" s="5">
+        <v>590</v>
+      </c>
+      <c r="H146" s="5"/>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A147" s="2">
-        <v>4010013655</v>
+      <c r="A147" s="1">
+        <v>4010013474</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C147" s="5">
-        <v>46550</v>
+        <v>52</v>
+      </c>
+      <c r="C147" s="4">
+        <v>46511</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>122</v>
+        <v>54</v>
       </c>
       <c r="E147" s="3" t="s">
         <v>30</v>
@@ -5346,23 +5319,23 @@
       <c r="F147" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G147" s="6">
-        <v>700</v>
-      </c>
-      <c r="H147" s="4"/>
+      <c r="G147" s="5">
+        <v>290</v>
+      </c>
+      <c r="H147" s="5"/>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A148" s="2">
-        <v>4010013474</v>
+      <c r="A148" s="1">
+        <v>4010013475</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C148" s="5">
-        <v>46579</v>
+        <v>55</v>
+      </c>
+      <c r="C148" s="4">
+        <v>46525</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E148" s="3" t="s">
         <v>30</v>
@@ -5370,117 +5343,117 @@
       <c r="F148" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G148" s="6">
-        <v>590</v>
-      </c>
-      <c r="H148" s="4"/>
+      <c r="G148" s="5">
+        <v>1330</v>
+      </c>
+      <c r="H148" s="5"/>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A149" s="2">
-        <v>4010013474</v>
+      <c r="A149" s="1">
+        <v>6010000087</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C149" s="5">
-        <v>46511</v>
+        <v>218</v>
+      </c>
+      <c r="C149" s="4">
+        <v>46388</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>55</v>
+        <v>219</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>30</v>
+        <v>205</v>
       </c>
       <c r="F149" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G149" s="6">
-        <v>290</v>
-      </c>
-      <c r="H149" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G149" s="5">
+        <v>4700</v>
+      </c>
+      <c r="H149" s="5"/>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A150" s="2">
-        <v>4010013475</v>
-      </c>
-      <c r="B150" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C150" s="5">
-        <v>46525</v>
-      </c>
-      <c r="D150" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E150" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F150" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G150" s="6">
-        <v>1330</v>
-      </c>
-      <c r="H150" s="4"/>
+      <c r="A150" s="6">
+        <v>6010000087</v>
+      </c>
+      <c r="B150" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C150" s="8"/>
+      <c r="D150" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E150" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="F150" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="G150" s="9"/>
+      <c r="H150" s="9">
+        <v>10000</v>
+      </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A151" s="9">
-        <v>6010000087</v>
-      </c>
-      <c r="B151" s="10" t="s">
-        <v>220</v>
-      </c>
-      <c r="C151" s="11"/>
-      <c r="D151" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="E151" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="F151" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="G151" s="12"/>
-      <c r="H151" s="13">
-        <v>10000</v>
-      </c>
+      <c r="A151" s="1">
+        <v>6010000126</v>
+      </c>
+      <c r="B151" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="C151" s="4">
+        <v>46780</v>
+      </c>
+      <c r="D151" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="E151" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F151" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G151" s="5">
+        <v>5500</v>
+      </c>
+      <c r="H151" s="5"/>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A152" s="2">
-        <v>6010000087</v>
+      <c r="A152" s="1">
+        <v>6010000227</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="C152" s="5">
-        <v>46388</v>
+        <v>415</v>
+      </c>
+      <c r="C152" s="4">
+        <v>46645</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>221</v>
+        <v>416</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>207</v>
+        <v>22</v>
       </c>
       <c r="F152" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G152" s="6">
-        <v>4950</v>
-      </c>
-      <c r="H152" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="G152" s="5">
+        <v>2240</v>
+      </c>
+      <c r="H152" s="5"/>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A153" s="2">
-        <v>6010000126</v>
+      <c r="A153" s="1">
+        <v>6010000227</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="C153" s="5">
-        <v>46780</v>
+        <v>415</v>
+      </c>
+      <c r="C153" s="4">
+        <v>46631</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>276</v>
+        <v>417</v>
       </c>
       <c r="E153" s="3" t="s">
         <v>22</v>
@@ -5488,95 +5461,95 @@
       <c r="F153" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G153" s="6">
-        <v>5500</v>
-      </c>
-      <c r="H153" s="4"/>
+      <c r="G153" s="5">
+        <v>4800</v>
+      </c>
+      <c r="H153" s="5"/>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A154" s="2">
-        <v>6010000227</v>
+      <c r="A154" s="1">
+        <v>6010000088</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="C154" s="5">
-        <v>46631</v>
+        <v>220</v>
+      </c>
+      <c r="C154" s="4">
+        <v>46661</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>418</v>
+        <v>221</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>22</v>
+        <v>222</v>
       </c>
       <c r="F154" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G154" s="6">
-        <v>5000</v>
-      </c>
-      <c r="H154" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G154" s="5">
+        <v>2660</v>
+      </c>
+      <c r="H154" s="5"/>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A155" s="2">
-        <v>6010000227</v>
+      <c r="A155" s="1">
+        <v>4010013666</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="C155" s="5">
-        <v>46645</v>
+        <v>140</v>
+      </c>
+      <c r="C155" s="4">
+        <v>46625</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>419</v>
+        <v>141</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F155" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G155" s="6">
-        <v>2240</v>
-      </c>
-      <c r="H155" s="4"/>
+      <c r="G155" s="5">
+        <v>100</v>
+      </c>
+      <c r="H155" s="5"/>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A156" s="2">
-        <v>6010000088</v>
+      <c r="A156" s="1">
+        <v>4010013666</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="C156" s="5">
-        <v>46661</v>
+        <v>140</v>
+      </c>
+      <c r="C156" s="4">
+        <v>46593</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>223</v>
+        <v>142</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>224</v>
+        <v>30</v>
       </c>
       <c r="F156" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G156" s="6">
-        <v>2660</v>
-      </c>
-      <c r="H156" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="G156" s="5">
+        <v>200</v>
+      </c>
+      <c r="H156" s="5"/>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A157" s="2">
-        <v>4010013666</v>
+      <c r="A157" s="1">
+        <v>6010000128</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C157" s="5">
-        <v>46625</v>
+        <v>275</v>
+      </c>
+      <c r="C157" s="4">
+        <v>46721</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>143</v>
+        <v>276</v>
       </c>
       <c r="E157" s="3" t="s">
         <v>30</v>
@@ -5584,215 +5557,215 @@
       <c r="F157" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G157" s="6">
-        <v>100</v>
-      </c>
-      <c r="H157" s="4"/>
+      <c r="G157" s="5">
+        <v>640</v>
+      </c>
+      <c r="H157" s="5"/>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A158" s="2">
-        <v>4010013666</v>
+      <c r="A158" s="1">
+        <v>6010000129</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C158" s="5">
-        <v>46593</v>
+        <v>277</v>
+      </c>
+      <c r="C158" s="4">
+        <v>46569</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>144</v>
+        <v>278</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F158" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G158" s="6">
-        <v>200</v>
-      </c>
-      <c r="H158" s="4"/>
+      <c r="G158" s="5">
+        <v>50</v>
+      </c>
+      <c r="H158" s="5"/>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A159" s="2">
-        <v>6010000128</v>
+      <c r="A159" s="1">
+        <v>6010000129</v>
       </c>
       <c r="B159" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="C159" s="5">
-        <v>46721</v>
+      <c r="C159" s="4">
+        <v>46758</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E159" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F159" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G159" s="5">
+        <v>700</v>
+      </c>
+      <c r="H159" s="5"/>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A160" s="1">
+        <v>6010000130</v>
+      </c>
+      <c r="B160" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="C160" s="4">
+        <v>46753</v>
+      </c>
+      <c r="D160" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="E160" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F159" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G159" s="6">
-        <v>640</v>
-      </c>
-      <c r="H159" s="4"/>
-    </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A160" s="2">
-        <v>6010000129</v>
-      </c>
-      <c r="B160" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="C160" s="5">
-        <v>46758</v>
-      </c>
-      <c r="D160" s="3" t="s">
+      <c r="F160" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G160" s="5">
+        <v>630</v>
+      </c>
+      <c r="H160" s="5"/>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A161" s="1">
+        <v>6010000130</v>
+      </c>
+      <c r="B161" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="E160" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F160" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G160" s="6">
-        <v>700</v>
-      </c>
-      <c r="H160" s="4"/>
-    </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A161" s="2">
-        <v>6010000129</v>
-      </c>
-      <c r="B161" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="C161" s="5">
+      <c r="C161" s="4">
         <v>46569</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F161" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G161" s="6">
-        <v>50</v>
-      </c>
-      <c r="H161" s="4"/>
+      <c r="G161" s="5">
+        <v>20</v>
+      </c>
+      <c r="H161" s="5"/>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A162" s="2">
-        <v>6010000130</v>
+      <c r="A162" s="1">
+        <v>6010000198</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="C162" s="5">
-        <v>46569</v>
+        <v>382</v>
+      </c>
+      <c r="C162" s="4">
+        <v>46568</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>283</v>
+        <v>383</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F162" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G162" s="6">
-        <v>20</v>
-      </c>
-      <c r="H162" s="4"/>
+      <c r="G162" s="5">
+        <v>600</v>
+      </c>
+      <c r="H162" s="5"/>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A163" s="2">
-        <v>6010000130</v>
+      <c r="A163" s="1">
+        <v>4010013586</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="C163" s="5">
-        <v>46753</v>
+        <v>99</v>
+      </c>
+      <c r="C163" s="4">
+        <v>46537</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>284</v>
+        <v>100</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F163" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G163" s="6">
-        <v>630</v>
-      </c>
-      <c r="H163" s="4"/>
+      <c r="G163" s="5">
+        <v>1340</v>
+      </c>
+      <c r="H163" s="5"/>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A164" s="2">
-        <v>6010000198</v>
+      <c r="A164" s="1">
+        <v>4010013587</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="C164" s="5">
-        <v>46568</v>
+        <v>101</v>
+      </c>
+      <c r="C164" s="4">
+        <v>46537</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>385</v>
+        <v>102</v>
       </c>
       <c r="E164" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F164" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G164" s="5">
+        <v>200</v>
+      </c>
+      <c r="H164" s="5"/>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A165" s="1">
+        <v>4010013549</v>
+      </c>
+      <c r="B165" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C165" s="4">
+        <v>46525</v>
+      </c>
+      <c r="D165" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E165" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F164" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G164" s="6">
-        <v>600</v>
-      </c>
-      <c r="H164" s="4"/>
-    </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A165" s="2">
-        <v>4010013586</v>
-      </c>
-      <c r="B165" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C165" s="5">
-        <v>46537</v>
-      </c>
-      <c r="D165" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E165" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="F165" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G165" s="6">
-        <v>1340</v>
-      </c>
-      <c r="H165" s="4"/>
+      <c r="G165" s="5">
+        <v>980</v>
+      </c>
+      <c r="H165" s="5"/>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A166" s="2">
-        <v>4010013587</v>
+      <c r="A166" s="1">
+        <v>4010013249</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C166" s="5">
-        <v>46537</v>
+        <v>0</v>
+      </c>
+      <c r="C166" s="4">
+        <v>46442</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>103</v>
+        <v>1</v>
       </c>
       <c r="E166" s="3" t="s">
         <v>4</v>
@@ -5800,71 +5773,71 @@
       <c r="F166" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G166" s="6">
-        <v>240</v>
-      </c>
-      <c r="H166" s="4"/>
+      <c r="G166" s="5">
+        <v>460</v>
+      </c>
+      <c r="H166" s="5"/>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A167" s="2">
-        <v>4010013549</v>
+      <c r="A167" s="1">
+        <v>4010013573</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C167" s="5">
-        <v>46525</v>
+        <v>80</v>
+      </c>
+      <c r="C167" s="4">
+        <v>46423</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="E167" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F167" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G167" s="5">
+        <v>500</v>
+      </c>
+      <c r="H167" s="5"/>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A168" s="1">
+        <v>4010013574</v>
+      </c>
+      <c r="B168" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C168" s="4">
+        <v>46545</v>
+      </c>
+      <c r="D168" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E168" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F167" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G167" s="6">
-        <v>980</v>
-      </c>
-      <c r="H167" s="4"/>
-    </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A168" s="2">
-        <v>4010013249</v>
-      </c>
-      <c r="B168" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C168" s="5">
-        <v>46442</v>
-      </c>
-      <c r="D168" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E168" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F168" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G168" s="6">
-        <v>460</v>
-      </c>
-      <c r="H168" s="4"/>
+      <c r="G168" s="5">
+        <v>660</v>
+      </c>
+      <c r="H168" s="5"/>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A169" s="2">
-        <v>4010013573</v>
+      <c r="A169" s="1">
+        <v>4010013588</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C169" s="5">
-        <v>46423</v>
+        <v>103</v>
+      </c>
+      <c r="C169" s="4">
+        <v>46582</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="E169" s="3" t="s">
         <v>4</v>
@@ -5872,47 +5845,47 @@
       <c r="F169" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G169" s="6">
-        <v>500</v>
-      </c>
-      <c r="H169" s="4"/>
+      <c r="G169" s="5">
+        <v>3100</v>
+      </c>
+      <c r="H169" s="5"/>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A170" s="2">
-        <v>4010013574</v>
+      <c r="A170" s="1">
+        <v>4010013479</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C170" s="5">
-        <v>46545</v>
+        <v>63</v>
+      </c>
+      <c r="C170" s="4">
+        <v>46536</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F170" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G170" s="6">
-        <v>660</v>
-      </c>
-      <c r="H170" s="4"/>
+      <c r="G170" s="5">
+        <v>320</v>
+      </c>
+      <c r="H170" s="5"/>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A171" s="2">
-        <v>4010013588</v>
+      <c r="A171" s="1">
+        <v>4010013479</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="C171" s="5">
-        <v>46582</v>
+        <v>63</v>
+      </c>
+      <c r="C171" s="4">
+        <v>46594</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>105</v>
+        <v>65</v>
       </c>
       <c r="E171" s="3" t="s">
         <v>4</v>
@@ -5920,23 +5893,23 @@
       <c r="F171" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G171" s="6">
-        <v>3140</v>
-      </c>
-      <c r="H171" s="4"/>
+      <c r="G171" s="5">
+        <v>400</v>
+      </c>
+      <c r="H171" s="5"/>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A172" s="2">
+      <c r="A172" s="1">
         <v>4010013479</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C172" s="5">
-        <v>46536</v>
+        <v>63</v>
+      </c>
+      <c r="C172" s="4">
+        <v>46419</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E172" s="3" t="s">
         <v>4</v>
@@ -5944,23 +5917,23 @@
       <c r="F172" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G172" s="6">
-        <v>320</v>
-      </c>
-      <c r="H172" s="4"/>
+      <c r="G172" s="5">
+        <v>200</v>
+      </c>
+      <c r="H172" s="5"/>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A173" s="2">
-        <v>4010013479</v>
+      <c r="A173" s="1">
+        <v>4010013700</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C173" s="5">
-        <v>46594</v>
+        <v>154</v>
+      </c>
+      <c r="C173" s="4">
+        <v>46446</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>66</v>
+        <v>155</v>
       </c>
       <c r="E173" s="3" t="s">
         <v>4</v>
@@ -5968,23 +5941,23 @@
       <c r="F173" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G173" s="6">
-        <v>400</v>
-      </c>
-      <c r="H173" s="4"/>
+      <c r="G173" s="5">
+        <v>560</v>
+      </c>
+      <c r="H173" s="5"/>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A174" s="2">
-        <v>4010013479</v>
+      <c r="A174" s="1">
+        <v>4010013700</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C174" s="5">
-        <v>46419</v>
+        <v>154</v>
+      </c>
+      <c r="C174" s="4">
+        <v>46533</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>67</v>
+        <v>156</v>
       </c>
       <c r="E174" s="3" t="s">
         <v>4</v>
@@ -5992,23 +5965,23 @@
       <c r="F174" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G174" s="6">
-        <v>200</v>
-      </c>
-      <c r="H174" s="4"/>
+      <c r="G174" s="5">
+        <v>300</v>
+      </c>
+      <c r="H174" s="5"/>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A175" s="2">
-        <v>4010013700</v>
+      <c r="A175" s="1">
+        <v>4010013701</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="C175" s="5">
-        <v>46446</v>
+        <v>157</v>
+      </c>
+      <c r="C175" s="4">
+        <v>46589</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E175" s="3" t="s">
         <v>4</v>
@@ -6016,71 +5989,71 @@
       <c r="F175" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G175" s="6">
-        <v>560</v>
-      </c>
-      <c r="H175" s="4"/>
+      <c r="G175" s="5">
+        <v>1160</v>
+      </c>
+      <c r="H175" s="5"/>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A176" s="2">
-        <v>4010013700</v>
+      <c r="A176" s="1">
+        <v>4010013657</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="C176" s="5">
-        <v>46533</v>
+        <v>125</v>
+      </c>
+      <c r="C176" s="4">
+        <v>46513</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>158</v>
+        <v>126</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F176" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G176" s="6">
-        <v>300</v>
-      </c>
-      <c r="H176" s="4"/>
+      <c r="G176" s="5">
+        <v>800</v>
+      </c>
+      <c r="H176" s="5"/>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A177" s="2">
-        <v>4010013701</v>
+      <c r="A177" s="1">
+        <v>4010013658</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="C177" s="5">
-        <v>46589</v>
+        <v>127</v>
+      </c>
+      <c r="C177" s="4">
+        <v>46563</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>160</v>
+        <v>128</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F177" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G177" s="6">
-        <v>1160</v>
-      </c>
-      <c r="H177" s="4"/>
+      <c r="G177" s="5">
+        <v>70</v>
+      </c>
+      <c r="H177" s="5"/>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A178" s="2">
-        <v>4010013657</v>
+      <c r="A178" s="1">
+        <v>4010013658</v>
       </c>
       <c r="B178" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="C178" s="5">
-        <v>46513</v>
+      <c r="C178" s="4">
+        <v>46587</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E178" s="3" t="s">
         <v>8</v>
@@ -6088,47 +6061,47 @@
       <c r="F178" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G178" s="6">
-        <v>800</v>
-      </c>
-      <c r="H178" s="4"/>
+      <c r="G178" s="5">
+        <v>1200</v>
+      </c>
+      <c r="H178" s="5"/>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A179" s="2">
-        <v>4010013658</v>
+      <c r="A179" s="1">
+        <v>4010013548</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="C179" s="5">
-        <v>46587</v>
+        <v>69</v>
+      </c>
+      <c r="C179" s="4">
+        <v>46469</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>8</v>
+        <v>71</v>
       </c>
       <c r="F179" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G179" s="6">
-        <v>1200</v>
-      </c>
-      <c r="H179" s="4"/>
+      <c r="G179" s="5">
+        <v>830</v>
+      </c>
+      <c r="H179" s="5"/>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A180" s="2">
-        <v>4010013658</v>
+      <c r="A180" s="1">
+        <v>4010013480</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="C180" s="5">
-        <v>46563</v>
+        <v>67</v>
+      </c>
+      <c r="C180" s="4">
+        <v>46408</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>131</v>
+        <v>68</v>
       </c>
       <c r="E180" s="3" t="s">
         <v>8</v>
@@ -6136,527 +6109,527 @@
       <c r="F180" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G180" s="6">
-        <v>70</v>
-      </c>
-      <c r="H180" s="4"/>
+      <c r="G180" s="5">
+        <v>1230</v>
+      </c>
+      <c r="H180" s="5"/>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A181" s="2">
-        <v>4010013548</v>
+      <c r="A181" s="1">
+        <v>4010013477</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C181" s="5">
-        <v>46469</v>
+        <v>59</v>
+      </c>
+      <c r="C181" s="4">
+        <v>46574</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>72</v>
+        <v>8</v>
       </c>
       <c r="F181" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G181" s="6">
-        <v>830</v>
-      </c>
-      <c r="H181" s="4"/>
+      <c r="G181" s="5">
+        <v>780</v>
+      </c>
+      <c r="H181" s="5"/>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A182" s="2">
-        <v>4010013480</v>
+      <c r="A182" s="1">
+        <v>6010000131</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C182" s="5">
-        <v>46408</v>
+        <v>283</v>
+      </c>
+      <c r="C182" s="4">
+        <v>46784</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>69</v>
+        <v>284</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F182" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G182" s="6">
-        <v>1230</v>
-      </c>
-      <c r="H182" s="4"/>
+      <c r="G182" s="5">
+        <v>2060</v>
+      </c>
+      <c r="H182" s="5"/>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A183" s="2">
-        <v>4010013477</v>
+      <c r="A183" s="1">
+        <v>4010013699</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C183" s="5">
-        <v>46574</v>
+        <v>152</v>
+      </c>
+      <c r="C183" s="4">
+        <v>46438</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>61</v>
+        <v>153</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F183" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G183" s="6">
-        <v>980</v>
-      </c>
-      <c r="H183" s="4"/>
+      <c r="G183" s="5">
+        <v>350</v>
+      </c>
+      <c r="H183" s="5"/>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A184" s="2">
-        <v>6010000131</v>
+      <c r="A184" s="1">
+        <v>6010000089</v>
       </c>
       <c r="B184" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C184" s="4">
+        <v>46871</v>
+      </c>
+      <c r="D184" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="E184" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="F184" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G184" s="5">
+        <v>2300</v>
+      </c>
+      <c r="H184" s="5"/>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A185" s="1">
+        <v>6010000089</v>
+      </c>
+      <c r="B185" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C185" s="4">
+        <v>46424</v>
+      </c>
+      <c r="D185" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E185" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="F185" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G185" s="5">
+        <v>2360</v>
+      </c>
+      <c r="H185" s="5"/>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A186" s="1">
+        <v>6010000132</v>
+      </c>
+      <c r="B186" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="C184" s="5">
-        <v>46784</v>
-      </c>
-      <c r="D184" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="E184" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F184" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G184" s="6">
-        <v>2260</v>
-      </c>
-      <c r="H184" s="4"/>
-    </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A185" s="2">
-        <v>4010013699</v>
-      </c>
-      <c r="B185" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="C185" s="5">
-        <v>46438</v>
-      </c>
-      <c r="D185" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="E185" s="3" t="s">
+      <c r="C186" s="4">
+        <v>46614</v>
+      </c>
+      <c r="D186" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E186" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F185" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G185" s="6">
-        <v>360</v>
-      </c>
-      <c r="H185" s="4"/>
-    </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A186" s="2">
-        <v>6010000089</v>
-      </c>
-      <c r="B186" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="C186" s="5">
-        <v>46871</v>
-      </c>
-      <c r="D186" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="E186" s="3" t="s">
-        <v>227</v>
-      </c>
       <c r="F186" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G186" s="6">
-        <v>2300</v>
-      </c>
-      <c r="H186" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="G186" s="5">
+        <v>2860</v>
+      </c>
+      <c r="H186" s="5"/>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A187" s="2">
-        <v>6010000089</v>
+      <c r="A187" s="1">
+        <v>6010000146</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="C187" s="5">
-        <v>46424</v>
+        <v>314</v>
+      </c>
+      <c r="C187" s="4">
+        <v>46746</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>228</v>
+        <v>315</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>227</v>
+        <v>316</v>
       </c>
       <c r="F187" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G187" s="6">
-        <v>2360</v>
-      </c>
-      <c r="H187" s="4"/>
+      <c r="G187" s="5">
+        <v>480</v>
+      </c>
+      <c r="H187" s="5"/>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A188" s="2">
-        <v>6010000132</v>
+      <c r="A188" s="1">
+        <v>6010000090</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="C188" s="5">
-        <v>46614</v>
+        <v>227</v>
+      </c>
+      <c r="C188" s="4">
+        <v>46482</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>2</v>
+        <v>228</v>
       </c>
       <c r="E188" s="3" t="s">
-        <v>30</v>
+        <v>177</v>
       </c>
       <c r="F188" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G188" s="6">
-        <v>2860</v>
-      </c>
-      <c r="H188" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G188" s="5">
+        <v>4560</v>
+      </c>
+      <c r="H188" s="5"/>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A189" s="2">
-        <v>6010000146</v>
+      <c r="A189" s="1">
+        <v>6010000200</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="C189" s="5">
-        <v>46746</v>
+        <v>386</v>
+      </c>
+      <c r="C189" s="4">
+        <v>46593</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>317</v>
+        <v>387</v>
       </c>
       <c r="E189" s="3" t="s">
-        <v>318</v>
+        <v>388</v>
       </c>
       <c r="F189" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G189" s="6">
-        <v>480</v>
-      </c>
-      <c r="H189" s="4"/>
+      <c r="G189" s="5">
+        <v>60</v>
+      </c>
+      <c r="H189" s="5"/>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A190" s="2">
-        <v>6010000090</v>
+      <c r="A190" s="1">
+        <v>6010000199</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="C190" s="5">
-        <v>46482</v>
+        <v>384</v>
+      </c>
+      <c r="C190" s="4">
+        <v>46556</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>230</v>
+        <v>385</v>
       </c>
       <c r="E190" s="3" t="s">
-        <v>179</v>
+        <v>22</v>
       </c>
       <c r="F190" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G190" s="6">
-        <v>4620</v>
-      </c>
-      <c r="H190" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="G190" s="5">
+        <v>1680</v>
+      </c>
+      <c r="H190" s="5"/>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A191" s="2">
-        <v>6010000200</v>
+      <c r="A191" s="1">
+        <v>6010000133</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="C191" s="5">
-        <v>46593</v>
+        <v>286</v>
+      </c>
+      <c r="C191" s="4">
+        <v>46388</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>389</v>
+        <v>287</v>
       </c>
       <c r="E191" s="3" t="s">
-        <v>390</v>
+        <v>88</v>
       </c>
       <c r="F191" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G191" s="6">
-        <v>60</v>
-      </c>
-      <c r="H191" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="G191" s="5">
+        <v>1200</v>
+      </c>
+      <c r="H191" s="5"/>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A192" s="2">
-        <v>6010000199</v>
+      <c r="A192" s="1">
+        <v>6010000134</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="C192" s="5">
-        <v>46556</v>
+        <v>288</v>
+      </c>
+      <c r="C192" s="4">
+        <v>46488</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>387</v>
+        <v>289</v>
       </c>
       <c r="E192" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F192" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G192" s="5">
+        <v>1180</v>
+      </c>
+      <c r="H192" s="5"/>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A193" s="1">
+        <v>6010000135</v>
+      </c>
+      <c r="B193" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="C193" s="4">
+        <v>46388</v>
+      </c>
+      <c r="D193" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="E193" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F193" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G193" s="5">
+        <v>1560</v>
+      </c>
+      <c r="H193" s="5"/>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A194" s="1">
+        <v>6010000136</v>
+      </c>
+      <c r="B194" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="C194" s="4">
+        <v>46496</v>
+      </c>
+      <c r="D194" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="E194" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F194" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G194" s="5">
+        <v>750</v>
+      </c>
+      <c r="H194" s="5"/>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A195" s="1">
+        <v>6010000137</v>
+      </c>
+      <c r="B195" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="C195" s="4">
+        <v>46496</v>
+      </c>
+      <c r="D195" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="E195" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F195" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G195" s="5">
+        <v>590</v>
+      </c>
+      <c r="H195" s="5"/>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A196" s="1">
+        <v>4010013269</v>
+      </c>
+      <c r="B196" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C196" s="4">
+        <v>46558</v>
+      </c>
+      <c r="D196" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E196" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F192" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G192" s="6">
-        <v>1680</v>
-      </c>
-      <c r="H192" s="4"/>
-    </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A193" s="2">
-        <v>6010000133</v>
-      </c>
-      <c r="B193" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="C193" s="5">
-        <v>46388</v>
-      </c>
-      <c r="D193" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="E193" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="F193" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G193" s="6">
-        <v>1200</v>
-      </c>
-      <c r="H193" s="4"/>
-    </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A194" s="2">
-        <v>6010000134</v>
-      </c>
-      <c r="B194" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="C194" s="5">
-        <v>46488</v>
-      </c>
-      <c r="D194" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="E194" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="F194" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G194" s="6">
-        <v>1180</v>
-      </c>
-      <c r="H194" s="4"/>
-    </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A195" s="2">
-        <v>6010000135</v>
-      </c>
-      <c r="B195" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="C195" s="5">
-        <v>46388</v>
-      </c>
-      <c r="D195" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="E195" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="F195" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G195" s="6">
-        <v>1560</v>
-      </c>
-      <c r="H195" s="4"/>
-    </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A196" s="2">
-        <v>6010000136</v>
-      </c>
-      <c r="B196" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="C196" s="5">
-        <v>46496</v>
-      </c>
-      <c r="D196" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="E196" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="F196" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G196" s="6">
-        <v>750</v>
-      </c>
-      <c r="H196" s="4"/>
+      <c r="G196" s="5">
+        <v>900</v>
+      </c>
+      <c r="H196" s="5"/>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A197" s="2">
-        <v>6010000137</v>
+      <c r="A197" s="1">
+        <v>6010000177</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="C197" s="5">
-        <v>46496</v>
+        <v>359</v>
+      </c>
+      <c r="C197" s="4">
+        <v>46971</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>297</v>
+        <v>360</v>
       </c>
       <c r="E197" s="3" t="s">
-        <v>30</v>
+        <v>361</v>
       </c>
       <c r="F197" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G197" s="6">
-        <v>610</v>
-      </c>
-      <c r="H197" s="4"/>
+      <c r="G197" s="5">
+        <v>2980</v>
+      </c>
+      <c r="H197" s="5"/>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A198" s="2">
-        <v>4010013269</v>
+      <c r="A198" s="1">
+        <v>6010000178</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C198" s="5">
-        <v>46558</v>
+        <v>362</v>
+      </c>
+      <c r="C198" s="4">
+        <v>47087</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>21</v>
+        <v>363</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>22</v>
+        <v>364</v>
       </c>
       <c r="F198" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G198" s="6">
-        <v>900</v>
-      </c>
-      <c r="H198" s="4"/>
+      <c r="G198" s="5">
+        <v>1260</v>
+      </c>
+      <c r="H198" s="5"/>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A199" s="2">
-        <v>6010000177</v>
+      <c r="A199" s="1">
+        <v>4010013597</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="C199" s="5">
-        <v>46971</v>
+        <v>115</v>
+      </c>
+      <c r="C199" s="4">
+        <v>46525</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>362</v>
+        <v>116</v>
       </c>
       <c r="E199" s="3" t="s">
-        <v>363</v>
+        <v>11</v>
       </c>
       <c r="F199" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G199" s="6">
-        <v>2980</v>
-      </c>
-      <c r="H199" s="4"/>
+      <c r="G199" s="5">
+        <v>620</v>
+      </c>
+      <c r="H199" s="5"/>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A200" s="2">
-        <v>6010000178</v>
+      <c r="A200" s="1">
+        <v>4010013368</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="C200" s="5">
-        <v>47087</v>
+        <v>32</v>
+      </c>
+      <c r="C200" s="4">
+        <v>46533</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>365</v>
+        <v>33</v>
       </c>
       <c r="E200" s="3" t="s">
-        <v>366</v>
+        <v>4</v>
       </c>
       <c r="F200" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G200" s="6">
-        <v>1260</v>
-      </c>
-      <c r="H200" s="4"/>
+      <c r="G200" s="5">
+        <v>160</v>
+      </c>
+      <c r="H200" s="5"/>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A201" s="2">
-        <v>4010013597</v>
+      <c r="A201" s="1">
+        <v>4010013369</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C201" s="5">
-        <v>46525</v>
+        <v>34</v>
+      </c>
+      <c r="C201" s="4">
+        <v>46429</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>117</v>
+        <v>35</v>
       </c>
       <c r="E201" s="3" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F201" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G201" s="6">
-        <v>620</v>
-      </c>
-      <c r="H201" s="4"/>
+      <c r="G201" s="5">
+        <v>340</v>
+      </c>
+      <c r="H201" s="5"/>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A202" s="2">
-        <v>4010013368</v>
+      <c r="A202" s="1">
+        <v>4010013369</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C202" s="5">
+        <v>34</v>
+      </c>
+      <c r="C202" s="4">
         <v>46533</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E202" s="3" t="s">
         <v>4</v>
@@ -6664,307 +6637,307 @@
       <c r="F202" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G202" s="6">
-        <v>160</v>
-      </c>
-      <c r="H202" s="4"/>
+      <c r="G202" s="5">
+        <v>80</v>
+      </c>
+      <c r="H202" s="5"/>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A203" s="2">
-        <v>4010013369</v>
+      <c r="A203" s="1">
+        <v>4010013598</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C203" s="5">
-        <v>46429</v>
+        <v>117</v>
+      </c>
+      <c r="C203" s="4">
+        <v>47043</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>35</v>
+        <v>118</v>
       </c>
       <c r="E203" s="3" t="s">
-        <v>4</v>
+        <v>119</v>
       </c>
       <c r="F203" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G203" s="6">
-        <v>440</v>
-      </c>
-      <c r="H203" s="4"/>
+      <c r="G203" s="5">
+        <v>140</v>
+      </c>
+      <c r="H203" s="5"/>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A204" s="2">
-        <v>4010013369</v>
+      <c r="A204" s="1">
+        <v>4010013399</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C204" s="5">
-        <v>46533</v>
+        <v>43</v>
+      </c>
+      <c r="C204" s="4">
+        <v>46532</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E204" s="3" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F204" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G204" s="6">
+      <c r="G204" s="5">
+        <v>1310</v>
+      </c>
+      <c r="H204" s="5"/>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A205" s="1">
+        <v>6010000203</v>
+      </c>
+      <c r="B205" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="C205" s="4">
+        <v>46606</v>
+      </c>
+      <c r="D205" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="E205" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="F205" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G205" s="5">
+        <v>460</v>
+      </c>
+      <c r="H205" s="5"/>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A206" s="1">
+        <v>4010013592</v>
+      </c>
+      <c r="B206" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C206" s="4">
+        <v>46514</v>
+      </c>
+      <c r="D206" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E206" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="F206" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G206" s="5">
+        <v>250</v>
+      </c>
+      <c r="H206" s="5"/>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A207" s="1">
+        <v>4010014926</v>
+      </c>
+      <c r="B207" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C207" s="4">
+        <v>46768</v>
+      </c>
+      <c r="D207" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="E207" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="F207" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G207" s="5">
+        <v>780</v>
+      </c>
+      <c r="H207" s="5"/>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A208" s="1">
+        <v>7050000020</v>
+      </c>
+      <c r="B208" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C208" s="4"/>
+      <c r="D208" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E208" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F208" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G208" s="5">
+        <v>70</v>
+      </c>
+      <c r="H208" s="5"/>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A209" s="1">
+        <v>7050000020</v>
+      </c>
+      <c r="B209" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C209" s="4"/>
+      <c r="D209" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E209" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F209" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G209" s="5">
+        <v>30</v>
+      </c>
+      <c r="H209" s="5"/>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A210" s="1">
+        <v>4010013659</v>
+      </c>
+      <c r="B210" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C210" s="4">
+        <v>46526</v>
+      </c>
+      <c r="D210" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E210" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F210" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G210" s="5">
+        <v>1390</v>
+      </c>
+      <c r="H210" s="5"/>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A211" s="1">
+        <v>4010013273</v>
+      </c>
+      <c r="B211" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C211" s="4">
+        <v>46444</v>
+      </c>
+      <c r="D211" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E211" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F211" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G211" s="5">
         <v>80</v>
       </c>
-      <c r="H204" s="4"/>
-    </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A205" s="2">
-        <v>4010013598</v>
-      </c>
-      <c r="B205" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C205" s="5">
-        <v>47043</v>
-      </c>
-      <c r="D205" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="E205" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="F205" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G205" s="6">
-        <v>170</v>
-      </c>
-      <c r="H205" s="4"/>
-    </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A206" s="2">
-        <v>4010013399</v>
-      </c>
-      <c r="B206" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C206" s="5">
-        <v>46532</v>
-      </c>
-      <c r="D206" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E206" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F206" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G206" s="6">
-        <v>1310</v>
-      </c>
-      <c r="H206" s="4"/>
-    </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A207" s="2">
-        <v>6010000203</v>
-      </c>
-      <c r="B207" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="C207" s="5">
-        <v>46606</v>
-      </c>
-      <c r="D207" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="E207" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="F207" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G207" s="6">
-        <v>460</v>
-      </c>
-      <c r="H207" s="4"/>
-    </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A208" s="2">
-        <v>4010013592</v>
-      </c>
-      <c r="B208" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="C208" s="5">
-        <v>46514</v>
-      </c>
-      <c r="D208" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="E208" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="F208" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G208" s="6">
-        <v>250</v>
-      </c>
-      <c r="H208" s="4"/>
-    </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A209" s="2">
-        <v>4010014926</v>
-      </c>
-      <c r="B209" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="C209" s="5">
-        <v>46768</v>
-      </c>
-      <c r="D209" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="E209" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="F209" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G209" s="6">
-        <v>780</v>
-      </c>
-      <c r="H209" s="4"/>
-    </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A210" s="2">
-        <v>7050000020</v>
-      </c>
-      <c r="B210" s="3" t="s">
-        <v>452</v>
-      </c>
-      <c r="C210" s="5"/>
-      <c r="D210" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E210" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F210" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G210" s="6">
+      <c r="H211" s="5"/>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A212" s="1">
+        <v>4010013273</v>
+      </c>
+      <c r="B212" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C212" s="4">
+        <v>46444</v>
+      </c>
+      <c r="D212" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E212" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H210" s="4"/>
-    </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A211" s="2">
-        <v>7050000020</v>
-      </c>
-      <c r="B211" s="3" t="s">
-        <v>452</v>
-      </c>
-      <c r="C211" s="5"/>
-      <c r="D211" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E211" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F211" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G211" s="6">
-        <v>70</v>
-      </c>
-      <c r="H211" s="4"/>
-    </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A212" s="2">
-        <v>4010013659</v>
-      </c>
-      <c r="B212" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="C212" s="5">
-        <v>46526</v>
-      </c>
-      <c r="D212" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="E212" s="3" t="s">
+      <c r="F212" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G212" s="5">
+        <v>710</v>
+      </c>
+      <c r="H212" s="5"/>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A213" s="1">
+        <v>4010013271</v>
+      </c>
+      <c r="B213" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C213" s="4">
+        <v>46402</v>
+      </c>
+      <c r="D213" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E213" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F212" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G212" s="6">
-        <v>1390</v>
-      </c>
-      <c r="H212" s="4"/>
-    </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A213" s="2">
-        <v>4010013273</v>
-      </c>
-      <c r="B213" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C213" s="5">
-        <v>46444</v>
-      </c>
-      <c r="D213" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E213" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="F213" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G213" s="6">
-        <v>710</v>
-      </c>
-      <c r="H213" s="4"/>
+      <c r="G213" s="5">
+        <v>300</v>
+      </c>
+      <c r="H213" s="5"/>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A214" s="2">
-        <v>4010013273</v>
+      <c r="A214" s="1">
+        <v>4010013272</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C214" s="5">
-        <v>46444</v>
+        <v>25</v>
+      </c>
+      <c r="C214" s="4">
+        <v>46594</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E214" s="3" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F214" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G214" s="6">
-        <v>80</v>
-      </c>
-      <c r="H214" s="4"/>
+      <c r="G214" s="5">
+        <v>360</v>
+      </c>
+      <c r="H214" s="5"/>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A215" s="2">
-        <v>4010013271</v>
+      <c r="A215" s="1">
+        <v>4010013272</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C215" s="5">
-        <v>46402</v>
+        <v>25</v>
+      </c>
+      <c r="C215" s="4">
+        <v>46523</v>
       </c>
       <c r="D215" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E215" s="3" t="s">
         <v>8</v>
@@ -6972,23 +6945,23 @@
       <c r="F215" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G215" s="6">
-        <v>300</v>
-      </c>
-      <c r="H215" s="4"/>
+      <c r="G215" s="5">
+        <v>1140</v>
+      </c>
+      <c r="H215" s="5"/>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A216" s="2">
-        <v>4010013272</v>
+      <c r="A216" s="1">
+        <v>4010013663</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C216" s="5">
-        <v>46523</v>
+        <v>137</v>
+      </c>
+      <c r="C216" s="4">
+        <v>46514</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>26</v>
+        <v>138</v>
       </c>
       <c r="E216" s="3" t="s">
         <v>8</v>
@@ -6996,23 +6969,23 @@
       <c r="F216" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G216" s="6">
-        <v>1140</v>
-      </c>
-      <c r="H216" s="4"/>
+      <c r="G216" s="5">
+        <v>200</v>
+      </c>
+      <c r="H216" s="5"/>
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A217" s="2">
-        <v>4010013272</v>
+      <c r="A217" s="1">
+        <v>4010013663</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C217" s="5">
-        <v>46594</v>
+        <v>137</v>
+      </c>
+      <c r="C217" s="4">
+        <v>46612</v>
       </c>
       <c r="D217" s="3" t="s">
-        <v>27</v>
+        <v>139</v>
       </c>
       <c r="E217" s="3" t="s">
         <v>8</v>
@@ -7020,229 +6993,133 @@
       <c r="F217" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G217" s="6">
-        <v>360</v>
-      </c>
-      <c r="H217" s="4"/>
+      <c r="G217" s="5">
+        <v>1200</v>
+      </c>
+      <c r="H217" s="5"/>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A218" s="2">
-        <v>4010013663</v>
-      </c>
-      <c r="B218" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="C218" s="5">
-        <v>46514</v>
-      </c>
-      <c r="D218" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="E218" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F218" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G218" s="6">
-        <v>200</v>
-      </c>
-      <c r="H218" s="4"/>
+      <c r="A218" s="6">
+        <v>6010000093</v>
+      </c>
+      <c r="B218" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="C218" s="8"/>
+      <c r="D218" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E218" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="F218" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="G218" s="9"/>
+      <c r="H218" s="9">
+        <v>18000</v>
+      </c>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A219" s="2">
-        <v>4010013663</v>
+      <c r="A219" s="1">
+        <v>6010000093</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="C219" s="5">
-        <v>46612</v>
+        <v>229</v>
+      </c>
+      <c r="C219" s="4">
+        <v>46484</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>141</v>
+        <v>231</v>
       </c>
       <c r="E219" s="3" t="s">
-        <v>8</v>
+        <v>230</v>
       </c>
       <c r="F219" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G219" s="6">
-        <v>1200</v>
-      </c>
-      <c r="H219" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G219" s="5">
+        <v>16200</v>
+      </c>
+      <c r="H219" s="5"/>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A220" s="2">
-        <v>6010000245</v>
+      <c r="A220" s="1">
+        <v>6010000093</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>434</v>
-      </c>
-      <c r="C220" s="5">
-        <v>46629</v>
+        <v>229</v>
+      </c>
+      <c r="C220" s="4">
+        <v>46504</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>435</v>
+        <v>232</v>
       </c>
       <c r="E220" s="3" t="s">
-        <v>436</v>
+        <v>230</v>
       </c>
       <c r="F220" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G220" s="6">
-        <v>500</v>
-      </c>
-      <c r="H220" s="4"/>
+      <c r="G220" s="5">
+        <v>15000</v>
+      </c>
+      <c r="H220" s="5"/>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A221" s="2">
-        <v>6010000245</v>
+      <c r="A221" s="1">
+        <v>6010000161</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>434</v>
-      </c>
-      <c r="C221" s="5">
-        <v>46574</v>
+        <v>337</v>
+      </c>
+      <c r="C221" s="4">
+        <v>47087</v>
       </c>
       <c r="D221" s="3" t="s">
-        <v>437</v>
+        <v>338</v>
       </c>
       <c r="E221" s="3" t="s">
-        <v>436</v>
+        <v>339</v>
       </c>
       <c r="F221" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G221" s="6">
-        <v>1700</v>
-      </c>
-      <c r="H221" s="4"/>
+      <c r="G221" s="5">
+        <v>708</v>
+      </c>
+      <c r="H221" s="5"/>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A222" s="2">
-        <v>6010000093</v>
+      <c r="A222" s="1">
+        <v>6010000162</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="C222" s="5">
-        <v>46484</v>
+        <v>340</v>
+      </c>
+      <c r="C222" s="4">
+        <v>47087</v>
       </c>
       <c r="D222" s="3" t="s">
-        <v>232</v>
+        <v>341</v>
       </c>
       <c r="E222" s="3" t="s">
-        <v>233</v>
+        <v>342</v>
       </c>
       <c r="F222" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G222" s="6">
-        <v>16200</v>
-      </c>
-      <c r="H222" s="4"/>
-    </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A223" s="9">
-        <v>6010000093</v>
-      </c>
-      <c r="B223" s="10" t="s">
-        <v>231</v>
-      </c>
-      <c r="C223" s="11"/>
-      <c r="D223" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="E223" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="F223" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="G223" s="12"/>
-      <c r="H223" s="13">
-        <v>18000</v>
-      </c>
-    </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A224" s="2">
-        <v>6010000093</v>
-      </c>
-      <c r="B224" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="C224" s="5">
-        <v>46504</v>
-      </c>
-      <c r="D224" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="E224" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="F224" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G224" s="6">
-        <v>15000</v>
-      </c>
-      <c r="H224" s="4"/>
-    </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A225" s="2">
-        <v>6010000161</v>
-      </c>
-      <c r="B225" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="C225" s="5">
-        <v>47087</v>
-      </c>
-      <c r="D225" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="E225" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="F225" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G225" s="6">
-        <v>708</v>
-      </c>
-      <c r="H225" s="4"/>
-    </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A226" s="2">
-        <v>6010000162</v>
-      </c>
-      <c r="B226" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="C226" s="5">
-        <v>47087</v>
-      </c>
-      <c r="D226" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="E226" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="F226" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G226" s="6">
+      <c r="G222" s="5">
         <v>1164</v>
       </c>
-      <c r="H226" s="4"/>
+      <c r="H222" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H226">
-    <sortState ref="A2:H226">
-      <sortCondition ref="B1:B226"/>
+  <autoFilter ref="A1:H222">
+    <sortState ref="A2:H222">
+      <sortCondition ref="B1:B222"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="0" type="noConversion"/>

--- a/KSTOCK.xlsx
+++ b/KSTOCK.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c2e6f8dd72a68295/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="49" documentId="11_A7D6DF42C4094E9AB632FCC5BECBCE050FC1EEE7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F126FF46-C126-41EE-A856-C44A33B43D00}"/>
+  <xr:revisionPtr revIDLastSave="47" documentId="11_A3A2BE43C4094E9AB632FCC5BE959E8329D20925" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E845CD26-0456-4C13-924A-BC59C2E30ED7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$219</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$251</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="454">
   <si>
     <t>ROSUSEP-20</t>
   </si>
@@ -55,15 +55,15 @@
     <t>ATROLIA CV 20/75</t>
   </si>
   <si>
+    <t>25S3GCA110</t>
+  </si>
+  <si>
+    <t>10X3X10</t>
+  </si>
+  <si>
     <t>25S3GCA131</t>
   </si>
   <si>
-    <t>10X3X10</t>
-  </si>
-  <si>
-    <t>25S3GCA110</t>
-  </si>
-  <si>
     <t>Montalia AB</t>
   </si>
   <si>
@@ -103,12 +103,12 @@
     <t>Vildapharm-Met 500</t>
   </si>
   <si>
+    <t>25S3GTA972</t>
+  </si>
+  <si>
     <t>25S3GTA610</t>
   </si>
   <si>
-    <t>25S3GTA972</t>
-  </si>
-  <si>
     <t>VILDAPHARM-DP</t>
   </si>
   <si>
@@ -136,9 +136,6 @@
     <t>25S3GTA657</t>
   </si>
   <si>
-    <t>ACECLOPHARM-SP FORTE</t>
-  </si>
-  <si>
     <t>CHYMOACTIVE-FORTE</t>
   </si>
   <si>
@@ -184,12 +181,12 @@
     <t>PROGISPHERE SR 200</t>
   </si>
   <si>
+    <t>25S2HTA863</t>
+  </si>
+  <si>
     <t>25S2HTA612</t>
   </si>
   <si>
-    <t>25S2HTA863</t>
-  </si>
-  <si>
     <t>PROGISPHERE SR 300</t>
   </si>
   <si>
@@ -217,15 +214,15 @@
     <t>ROSUSEP-ASP 20</t>
   </si>
   <si>
+    <t>25S3GCA034</t>
+  </si>
+  <si>
+    <t>25S3GCA138</t>
+  </si>
+  <si>
     <t>25S3GCA105</t>
   </si>
   <si>
-    <t>25S3GCA138</t>
-  </si>
-  <si>
-    <t>25S3GCA034</t>
-  </si>
-  <si>
     <t>SITAFREE-MET 1000 IR</t>
   </si>
   <si>
@@ -310,12 +307,12 @@
     <t>GLIMKAT-MET 1 (PR)</t>
   </si>
   <si>
+    <t>25S3GTA625</t>
+  </si>
+  <si>
     <t>25S3GTA626</t>
   </si>
   <si>
-    <t>25S3GTA625</t>
-  </si>
-  <si>
     <t>GLIMKAT-MET 2 (PR)</t>
   </si>
   <si>
@@ -364,6 +361,9 @@
     <t>LEZIOD 600</t>
   </si>
   <si>
+    <t>25S2GTC412</t>
+  </si>
+  <si>
     <t>PREGAWALK NT 50/10</t>
   </si>
   <si>
@@ -400,12 +400,12 @@
     <t>SITAFREE-50</t>
   </si>
   <si>
+    <t>25S2GTB786</t>
+  </si>
+  <si>
     <t>25S2GTC059</t>
   </si>
   <si>
-    <t>25S2GTB786</t>
-  </si>
-  <si>
     <t>VILDAPHARM-50</t>
   </si>
   <si>
@@ -421,12 +421,12 @@
     <t>GABAKAT NT-400</t>
   </si>
   <si>
+    <t>25S3GTA850</t>
+  </si>
+  <si>
     <t>25S3GTA585</t>
   </si>
   <si>
-    <t>25S3GTA850</t>
-  </si>
-  <si>
     <t>VILDAPHARM-OD 100</t>
   </si>
   <si>
@@ -460,12 +460,12 @@
     <t>ATROLIA GOLD 20/75</t>
   </si>
   <si>
+    <t>25S3GCA113</t>
+  </si>
+  <si>
     <t>25S3GCA129</t>
   </si>
   <si>
-    <t>25S3GCA113</t>
-  </si>
-  <si>
     <t>Atrolia-ASP 75</t>
   </si>
   <si>
@@ -532,12 +532,18 @@
     <t>BAKUMIDE 1ML INJECTION</t>
   </si>
   <si>
+    <t>NL2932502</t>
+  </si>
+  <si>
     <t>10X1ML</t>
   </si>
   <si>
     <t>CALWINIT D3 INJ</t>
   </si>
   <si>
+    <t>NL2922501</t>
+  </si>
+  <si>
     <t>10X6X1ML</t>
   </si>
   <si>
@@ -562,21 +568,21 @@
     <t>CLAVMYCIN IV</t>
   </si>
   <si>
+    <t>10X1X1.2 G(SWFI)</t>
+  </si>
+  <si>
     <t>NKCL12502</t>
   </si>
   <si>
-    <t>10X1X1.2 G(SWFI)</t>
-  </si>
-  <si>
     <t>DECAHIT INJECTION</t>
   </si>
   <si>
+    <t>96X2ML</t>
+  </si>
+  <si>
     <t>NL2722504</t>
   </si>
   <si>
-    <t>96X2ML</t>
-  </si>
-  <si>
     <t>GENTAHIT INJ</t>
   </si>
   <si>
@@ -595,12 +601,12 @@
     <t>HITCORT 100</t>
   </si>
   <si>
+    <t>1X7.5ML+SWFI</t>
+  </si>
+  <si>
     <t>NL3926001</t>
   </si>
   <si>
-    <t>1X7.5ML+SWFI</t>
-  </si>
-  <si>
     <t>IRRONIT INJ</t>
   </si>
   <si>
@@ -655,12 +661,12 @@
     <t>ONMOTRON INJ 2ML</t>
   </si>
   <si>
+    <t>20X5X2ML</t>
+  </si>
+  <si>
     <t>NL2692503</t>
   </si>
   <si>
-    <t>20X5X2ML</t>
-  </si>
-  <si>
     <t>PANTAHIT IV</t>
   </si>
   <si>
@@ -721,6 +727,9 @@
     <t>MT2508331A</t>
   </si>
   <si>
+    <t>MT2507316</t>
+  </si>
+  <si>
     <t>AMLINA-5 TABLET</t>
   </si>
   <si>
@@ -748,9 +757,6 @@
     <t>50045093</t>
   </si>
   <si>
-    <t>DZE01AAA</t>
-  </si>
-  <si>
     <t>DICLODARD-MR TABLET</t>
   </si>
   <si>
@@ -820,6 +826,9 @@
     <t>OMNISYN 20 CAPSULE</t>
   </si>
   <si>
+    <t>MC2508084</t>
+  </si>
+  <si>
     <t>20X20</t>
   </si>
   <si>
@@ -853,12 +862,12 @@
     <t>RIFIXIEM 550 TABLET</t>
   </si>
   <si>
+    <t>GE545020</t>
+  </si>
+  <si>
     <t>GE545002B</t>
   </si>
   <si>
-    <t>GE545020</t>
-  </si>
-  <si>
     <t>SPASMOSAFE-MF TABLET</t>
   </si>
   <si>
@@ -925,6 +934,9 @@
     <t>POVIALL OINTMENT 15 GM</t>
   </si>
   <si>
+    <t>GLN25014</t>
+  </si>
+  <si>
     <t>1X15GM</t>
   </si>
   <si>
@@ -973,15 +985,18 @@
     <t>T60106A</t>
   </si>
   <si>
+    <t>ENOXAEASE 40 INJ</t>
+  </si>
+  <si>
+    <t>1X1</t>
+  </si>
+  <si>
     <t>ENOXAEASE 60 INJ</t>
   </si>
   <si>
     <t>L1542564B</t>
   </si>
   <si>
-    <t>1X1</t>
-  </si>
-  <si>
     <t>CADIKAT DUSTING POWDER 75GM</t>
   </si>
   <si>
@@ -1135,12 +1150,12 @@
     <t>EPODOX-200 DT Tablet</t>
   </si>
   <si>
+    <t>CT26107C</t>
+  </si>
+  <si>
     <t>CT25507F</t>
   </si>
   <si>
-    <t>CT26107C</t>
-  </si>
-  <si>
     <t>ATROLIA - F TABLET</t>
   </si>
   <si>
@@ -1192,12 +1207,12 @@
     <t>DANSOFT SHAMPOO 7.5ML SACHET</t>
   </si>
   <si>
+    <t>7.5ML</t>
+  </si>
+  <si>
     <t>N13250001</t>
   </si>
   <si>
-    <t>7.5ML</t>
-  </si>
-  <si>
     <t>POVIALL 7.5% SCRUB  500ML</t>
   </si>
   <si>
@@ -1207,12 +1222,12 @@
     <t>POVIALL OINTMENT 125GM</t>
   </si>
   <si>
+    <t>125GM</t>
+  </si>
+  <si>
     <t>GLN26004</t>
   </si>
   <si>
-    <t>125GM</t>
-  </si>
-  <si>
     <t>FAROPHARM 300 ER TABLET</t>
   </si>
   <si>
@@ -1222,12 +1237,12 @@
     <t>CEFIXLIA-O 200 TABLET</t>
   </si>
   <si>
+    <t>CT26007G</t>
+  </si>
+  <si>
     <t>CT25488B</t>
   </si>
   <si>
-    <t>CT26007G</t>
-  </si>
-  <si>
     <t>MONTALIA-LC 60ML SYRUP</t>
   </si>
   <si>
@@ -1249,15 +1264,21 @@
     <t>REBEHIT DSR CAPSULE</t>
   </si>
   <si>
+    <t>MC2510117</t>
+  </si>
+  <si>
     <t>MC2510116</t>
   </si>
   <si>
-    <t>MC2510117</t>
-  </si>
-  <si>
     <t>PANTAHIT DSR CAPSULE (20x10)</t>
   </si>
   <si>
+    <t>MC2509103</t>
+  </si>
+  <si>
+    <t>MC2509105A</t>
+  </si>
+  <si>
     <t>CLAVMYCIN 625 DUO TABLET (20x1x10)</t>
   </si>
   <si>
@@ -1270,12 +1291,12 @@
     <t>CEFIXLIA - 200 DT TABLET</t>
   </si>
   <si>
+    <t>CT26039A</t>
+  </si>
+  <si>
     <t>CT25427</t>
   </si>
   <si>
-    <t>CT26039A</t>
-  </si>
-  <si>
     <t>FERRIFINE XT TABLET</t>
   </si>
   <si>
@@ -1348,9 +1369,6 @@
     <t>Item Name</t>
   </si>
   <si>
-    <t>Unrestricted Qty</t>
-  </si>
-  <si>
     <t>PACK STYLE</t>
   </si>
   <si>
@@ -1360,10 +1378,13 @@
     <t>Expiry</t>
   </si>
   <si>
-    <t>Batch No.</t>
+    <t xml:space="preserve"> Batch No.</t>
   </si>
   <si>
     <t xml:space="preserve"> Transit Qty</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Unrestricted Qty</t>
   </si>
 </sst>
 </file>
@@ -1400,7 +1421,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1432,7 +1453,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -1452,6 +1473,9 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1806,44 +1830,44 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H219"/>
+  <dimension ref="A1:H251"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="38.5546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.44140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10.21875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.109375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="11" style="1" customWidth="1"/>
+    <col min="1" max="1" width="15.21875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="36.77734375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9.5546875" style="1" customWidth="1"/>
     <col min="9" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>445</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>442</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>443</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>441</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>446</v>
+        <v>451</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>449</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -1851,13 +1875,13 @@
         <v>6010000095</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C2" s="5">
         <v>46568</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>22</v>
@@ -1871,64 +1895,66 @@
       <c r="H2" s="4"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
+      <c r="A3" s="9">
         <v>6010000095</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="9" t="s">
+      <c r="B3" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="C3" s="11"/>
+      <c r="D3" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3" s="11"/>
-      <c r="H3" s="12">
+      <c r="F3" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="12"/>
+      <c r="H3" s="13">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>6010000095</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C4" s="5">
+        <v>46559</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="6">
         <v>1200</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
-        <v>4010013388</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G4" s="11"/>
-      <c r="H4" s="12">
-        <v>1280</v>
-      </c>
+      <c r="H4" s="4"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>6010000138</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="C5" s="5">
         <v>46746</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>3</v>
@@ -1967,13 +1993,13 @@
         <v>4010013476</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C7" s="5">
         <v>46548</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>30</v>
@@ -1991,16 +2017,16 @@
         <v>6010000097</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C8" s="5">
         <v>46751</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>5</v>
@@ -2015,16 +2041,16 @@
         <v>6010000097</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C9" s="5">
         <v>46556</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>5</v>
@@ -2039,16 +2065,16 @@
         <v>6010000098</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C10" s="5">
         <v>46539</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>5</v>
@@ -2063,13 +2089,13 @@
         <v>6010000195</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="C11" s="5">
         <v>46549</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>22</v>
@@ -2107,28 +2133,26 @@
       <c r="H12" s="4"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
-        <v>4010013260</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="5">
-        <v>46589</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G13" s="6">
-        <v>1200</v>
-      </c>
-      <c r="H13" s="4"/>
+      <c r="A13" s="9">
+        <v>4010013259</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="11"/>
+      <c r="D13" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G13" s="12"/>
+      <c r="H13" s="13">
+        <v>240</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
@@ -2141,7 +2165,7 @@
         <v>46568</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>11</v>
@@ -2155,65 +2179,63 @@
       <c r="H14" s="4"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
-        <v>4010013692</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C15" s="5">
-        <v>46549</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G15" s="6">
-        <v>880</v>
-      </c>
-      <c r="H15" s="4"/>
+      <c r="A15" s="9">
+        <v>4010013260</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="11"/>
+      <c r="D15" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G15" s="12"/>
+      <c r="H15" s="13">
+        <v>20</v>
+      </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
-        <v>4010013693</v>
+        <v>4010013260</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>144</v>
+        <v>9</v>
       </c>
       <c r="C16" s="5">
-        <v>46587</v>
+        <v>46589</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>145</v>
+        <v>12</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G16" s="6">
-        <v>420</v>
+        <v>1200</v>
       </c>
       <c r="H16" s="4"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
-        <v>4010013693</v>
+        <v>4010013692</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C17" s="5">
         <v>46549</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>8</v>
@@ -2222,70 +2244,70 @@
         <v>5</v>
       </c>
       <c r="G17" s="6">
-        <v>460</v>
+        <v>880</v>
       </c>
       <c r="H17" s="4"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <v>4010013578</v>
+        <v>4010013693</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>84</v>
+        <v>144</v>
       </c>
       <c r="C18" s="5">
-        <v>46640</v>
+        <v>46549</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>85</v>
+        <v>145</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G18" s="6">
-        <v>770</v>
+        <v>460</v>
       </c>
       <c r="H18" s="4"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
-        <v>4010013580</v>
+        <v>4010013693</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>86</v>
+        <v>144</v>
       </c>
       <c r="C19" s="5">
-        <v>46666</v>
+        <v>46587</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>87</v>
+        <v>146</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>88</v>
+        <v>8</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G19" s="6">
-        <v>500</v>
+        <v>420</v>
       </c>
       <c r="H19" s="4"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
-        <v>4010013551</v>
+        <v>4010013578</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C20" s="5">
-        <v>46598</v>
+        <v>46640</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>22</v>
@@ -2294,207 +2316,213 @@
         <v>5</v>
       </c>
       <c r="G20" s="6">
-        <v>840</v>
+        <v>770</v>
       </c>
       <c r="H20" s="4"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
-        <v>4010013660</v>
+        <v>4010013580</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>129</v>
+        <v>85</v>
       </c>
       <c r="C21" s="5">
-        <v>46518</v>
+        <v>46666</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>130</v>
+        <v>86</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>22</v>
+        <v>87</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G21" s="6">
-        <v>360</v>
+        <v>500</v>
       </c>
       <c r="H21" s="4"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
-        <v>4010013694</v>
+        <v>4010013551</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>147</v>
+        <v>75</v>
       </c>
       <c r="C22" s="5">
-        <v>46536</v>
+        <v>46598</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>148</v>
+        <v>76</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G22" s="6">
-        <v>750</v>
+        <v>840</v>
       </c>
       <c r="H22" s="4"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
-        <v>6010000065</v>
+        <v>4010013660</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>165</v>
+        <v>129</v>
       </c>
       <c r="C23" s="5">
-        <v>46447</v>
+        <v>46518</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>166</v>
+        <v>130</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>167</v>
+        <v>22</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G23" s="6">
-        <v>1900</v>
+        <v>340</v>
       </c>
       <c r="H23" s="4"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
-        <v>4010013581</v>
+        <v>4010013694</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="C24" s="5">
-        <v>46541</v>
+        <v>46536</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>90</v>
+        <v>148</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>91</v>
+        <v>8</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G24" s="6">
-        <v>3580</v>
+        <v>750</v>
       </c>
       <c r="H24" s="4"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="8">
-        <v>6010000066</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="C25" s="10"/>
-      <c r="D25" s="9" t="s">
+      <c r="A25" s="9">
+        <v>4010013694</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="C25" s="11"/>
+      <c r="D25" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E25" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="G25" s="11"/>
-      <c r="H25" s="12">
-        <v>900</v>
+      <c r="E25" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G25" s="12"/>
+      <c r="H25" s="13">
+        <v>240</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
-        <v>7050000018</v>
+        <v>6010000065</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="C26" s="5"/>
+        <v>165</v>
+      </c>
+      <c r="C26" s="5">
+        <v>46447</v>
+      </c>
       <c r="D26" s="3" t="s">
-        <v>2</v>
+        <v>166</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>432</v>
+        <v>167</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G26" s="6">
-        <v>100</v>
+        <v>1900</v>
       </c>
       <c r="H26" s="4"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
-        <v>7050000016</v>
+        <v>4010013581</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>434</v>
-      </c>
-      <c r="C27" s="5"/>
+        <v>88</v>
+      </c>
+      <c r="C27" s="5">
+        <v>46541</v>
+      </c>
       <c r="D27" s="3" t="s">
-        <v>2</v>
+        <v>89</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>432</v>
+        <v>90</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G27" s="6">
-        <v>100</v>
+        <v>3580</v>
       </c>
       <c r="H27" s="4"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
-        <v>7050000015</v>
+        <v>6010000066</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>433</v>
-      </c>
-      <c r="C28" s="5"/>
+        <v>168</v>
+      </c>
+      <c r="C28" s="5">
+        <v>46575</v>
+      </c>
       <c r="D28" s="3" t="s">
-        <v>2</v>
+        <v>169</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>432</v>
+        <v>170</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G28" s="6">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H28" s="4"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
-        <v>7050000014</v>
+        <v>7050000018</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>3</v>
@@ -2506,17 +2534,17 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
-        <v>7050000017</v>
+        <v>7050000016</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>3</v>
@@ -2528,1112 +2556,1096 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
-        <v>4010013550</v>
+        <v>7050000015</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C31" s="5">
-        <v>46568</v>
-      </c>
+        <v>440</v>
+      </c>
+      <c r="C31" s="5"/>
       <c r="D31" s="3" t="s">
-        <v>75</v>
+        <v>2</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>30</v>
+        <v>439</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G31" s="6">
-        <v>970</v>
+        <v>100</v>
       </c>
       <c r="H31" s="4"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="8">
-        <v>4010013550</v>
-      </c>
-      <c r="B32" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C32" s="10"/>
-      <c r="D32" s="9" t="s">
+      <c r="A32" s="2">
+        <v>7050000014</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="C32" s="5"/>
+      <c r="D32" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E32" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F32" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G32" s="11"/>
-      <c r="H32" s="12">
-        <v>360</v>
-      </c>
+      <c r="E32" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="6">
+        <v>100</v>
+      </c>
+      <c r="H32" s="4"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
-        <v>4010013478</v>
+        <v>7050000017</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C33" s="5">
-        <v>46551</v>
-      </c>
+        <v>442</v>
+      </c>
+      <c r="C33" s="5"/>
       <c r="D33" s="3" t="s">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>30</v>
+        <v>439</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G33" s="6">
-        <v>230</v>
+        <v>100</v>
       </c>
       <c r="H33" s="4"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
-        <v>6010000154</v>
+        <v>4010013550</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>319</v>
+        <v>73</v>
       </c>
       <c r="C34" s="5">
-        <v>47007</v>
+        <v>46568</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>320</v>
+        <v>74</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>321</v>
+        <v>30</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G34" s="6">
-        <v>814</v>
+        <v>1330</v>
       </c>
       <c r="H34" s="4"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
+        <v>4010013478</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C35" s="5">
+        <v>46551</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G35" s="6">
+        <v>230</v>
+      </c>
+      <c r="H35" s="4"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
+        <v>6010000154</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C36" s="5">
+        <v>47007</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G36" s="6">
+        <v>814</v>
+      </c>
+      <c r="H36" s="4"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
         <v>6010000158</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="C35" s="5">
+      <c r="B37" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C37" s="5">
         <v>46752</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="E35" s="3" t="s">
+      <c r="D37" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="E37" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G35" s="6">
+      <c r="F37" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G37" s="6">
         <v>440</v>
       </c>
-      <c r="H35" s="4"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="8">
+      <c r="H37" s="4"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
         <v>6010000068</v>
       </c>
-      <c r="B36" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="C36" s="10"/>
-      <c r="D36" s="9" t="s">
+      <c r="B38" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C38" s="5">
+        <v>46495</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G38" s="6">
+        <v>1500</v>
+      </c>
+      <c r="H38" s="4"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="9">
+        <v>6010000159</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="C39" s="11"/>
+      <c r="D39" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E36" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="G36" s="11"/>
-      <c r="H36" s="12">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="8">
-        <v>6010000159</v>
-      </c>
-      <c r="B37" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="C37" s="10"/>
-      <c r="D37" s="9" t="s">
+      <c r="E39" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G39" s="12"/>
+      <c r="H39" s="13">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="9">
+        <v>6010000099</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="C40" s="11"/>
+      <c r="D40" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E37" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F37" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G37" s="11"/>
-      <c r="H37" s="12">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="8">
-        <v>6010000099</v>
-      </c>
-      <c r="B38" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="C38" s="10"/>
-      <c r="D38" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="E38" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="F38" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G38" s="11"/>
-      <c r="H38" s="12">
-        <v>4800</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="2">
-        <v>6010000160</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="C39" s="5">
-        <v>46780</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G39" s="6">
-        <v>1200</v>
-      </c>
-      <c r="H39" s="4"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="2">
-        <v>6010000234</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="C40" s="5">
-        <v>46661</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G40" s="6">
-        <v>280</v>
-      </c>
-      <c r="H40" s="4"/>
+      <c r="E40" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="F40" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G40" s="12"/>
+      <c r="H40" s="13">
+        <v>6000</v>
+      </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
-        <v>6010000234</v>
+        <v>6010000160</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>414</v>
+        <v>334</v>
       </c>
       <c r="C41" s="5">
-        <v>46726</v>
+        <v>46780</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>416</v>
+        <v>335</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>22</v>
+        <v>336</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G41" s="6">
-        <v>7920</v>
+        <v>1200</v>
       </c>
       <c r="H41" s="4"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
-        <v>6010000239</v>
+        <v>6010000234</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C42" s="5">
-        <v>46507</v>
+        <v>46726</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>364</v>
+        <v>22</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G42" s="6">
-        <v>757</v>
+        <v>7920</v>
       </c>
       <c r="H42" s="4"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
-        <v>6010000217</v>
+        <v>6010000234</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>398</v>
+        <v>421</v>
       </c>
       <c r="C43" s="5">
-        <v>46721</v>
+        <v>46661</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>399</v>
+        <v>423</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G43" s="6">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="H43" s="4"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
-        <v>6010000217</v>
+        <v>6010000239</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>398</v>
+        <v>426</v>
       </c>
       <c r="C44" s="5">
-        <v>46751</v>
+        <v>46507</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>400</v>
+        <v>427</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>30</v>
+        <v>369</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G44" s="6">
-        <v>610</v>
+        <v>757</v>
       </c>
       <c r="H44" s="4"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="2">
-        <v>6010000070</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="C45" s="5">
-        <v>46721</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="F45" s="3" t="s">
+      <c r="A45" s="9">
+        <v>6010000239</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>426</v>
+      </c>
+      <c r="C45" s="11"/>
+      <c r="D45" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E45" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="F45" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="G45" s="6">
-        <v>765</v>
-      </c>
-      <c r="H45" s="4"/>
+      <c r="G45" s="12"/>
+      <c r="H45" s="13">
+        <v>810</v>
+      </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
-        <v>6010000071</v>
+        <v>6010000217</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>175</v>
+        <v>403</v>
       </c>
       <c r="C46" s="5">
-        <v>46797</v>
+        <v>46751</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>176</v>
+        <v>404</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>177</v>
+        <v>30</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G46" s="6">
-        <v>3250</v>
+        <v>610</v>
       </c>
       <c r="H46" s="4"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
-        <v>4010013389</v>
+        <v>6010000217</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>38</v>
+        <v>403</v>
       </c>
       <c r="C47" s="5">
-        <v>46681</v>
+        <v>46721</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>39</v>
+        <v>405</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G47" s="6">
-        <v>1100</v>
+        <v>240</v>
       </c>
       <c r="H47" s="4"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
-        <v>4010013266</v>
+        <v>6010000070</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>16</v>
+        <v>174</v>
       </c>
       <c r="C48" s="5">
-        <v>46575</v>
+        <v>46721</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>17</v>
+        <v>175</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>8</v>
+        <v>176</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G48" s="6">
-        <v>460</v>
+        <v>765</v>
       </c>
       <c r="H48" s="4"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
-        <v>4010013267</v>
+        <v>6010000071</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>18</v>
+        <v>177</v>
       </c>
       <c r="C49" s="5">
-        <v>46598</v>
+        <v>46797</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>19</v>
+        <v>178</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>8</v>
+        <v>179</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G49" s="6">
-        <v>640</v>
+        <v>3250</v>
       </c>
       <c r="H49" s="4"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="2">
-        <v>4010013553</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C50" s="5">
-        <v>46575</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G50" s="6">
-        <v>860</v>
-      </c>
-      <c r="H50" s="4"/>
+      <c r="A50" s="9">
+        <v>6010000071</v>
+      </c>
+      <c r="B50" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="C50" s="11"/>
+      <c r="D50" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E50" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="F50" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="G50" s="12"/>
+      <c r="H50" s="13">
+        <v>400</v>
+      </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
-        <v>4010013397</v>
+        <v>4010013389</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C51" s="5">
-        <v>46545</v>
+        <v>46681</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G51" s="6">
-        <v>880</v>
+        <v>1090</v>
       </c>
       <c r="H51" s="4"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
-        <v>6010000189</v>
+        <v>4010013266</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>360</v>
+        <v>16</v>
       </c>
       <c r="C52" s="5">
-        <v>46539</v>
+        <v>46575</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>361</v>
+        <v>17</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G52" s="6">
-        <v>160</v>
+        <v>460</v>
       </c>
       <c r="H52" s="4"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
-        <v>6010000224</v>
+        <v>4010013267</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>405</v>
+        <v>18</v>
       </c>
       <c r="C53" s="5">
-        <v>46711</v>
+        <v>46598</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>406</v>
+        <v>19</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G53" s="6">
-        <v>420</v>
+        <v>640</v>
       </c>
       <c r="H53" s="4"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
-        <v>6010000101</v>
+        <v>4010013553</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>239</v>
+        <v>77</v>
       </c>
       <c r="C54" s="5">
-        <v>46539</v>
+        <v>46575</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>240</v>
+        <v>78</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G54" s="6">
-        <v>290</v>
+        <v>860</v>
       </c>
       <c r="H54" s="4"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
-        <v>6010000101</v>
+        <v>4010013397</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>239</v>
+        <v>40</v>
       </c>
       <c r="C55" s="5">
-        <v>46447</v>
+        <v>46545</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>241</v>
+        <v>41</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G55" s="6">
-        <v>230</v>
+        <v>880</v>
       </c>
       <c r="H55" s="4"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
-        <v>6010000232</v>
+        <v>6010000189</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>411</v>
+        <v>365</v>
       </c>
       <c r="C56" s="5">
-        <v>46726</v>
+        <v>46539</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>412</v>
+        <v>366</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G56" s="6">
-        <v>2840</v>
+        <v>160</v>
       </c>
       <c r="H56" s="4"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
-        <v>6010000073</v>
+        <v>6010000224</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>178</v>
+        <v>410</v>
       </c>
       <c r="C57" s="5">
-        <v>46511</v>
+        <v>46711</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>179</v>
+        <v>411</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>180</v>
+        <v>15</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G57" s="6">
-        <v>1150</v>
+        <v>420</v>
       </c>
       <c r="H57" s="4"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
-        <v>6010000169</v>
+        <v>6010000101</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>338</v>
+        <v>242</v>
       </c>
       <c r="C58" s="5">
-        <v>46751</v>
+        <v>46539</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>339</v>
+        <v>243</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>107</v>
+        <v>30</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G58" s="6">
-        <v>2110</v>
+        <v>220</v>
       </c>
       <c r="H58" s="4"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
-        <v>6010000170</v>
+        <v>6010000232</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>340</v>
+        <v>418</v>
       </c>
       <c r="C59" s="5">
-        <v>46721</v>
+        <v>46726</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>341</v>
+        <v>419</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>107</v>
+        <v>15</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G59" s="6">
-        <v>2590</v>
+        <v>2840</v>
       </c>
       <c r="H59" s="4"/>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="2">
-        <v>6010000139</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="C60" s="5">
-        <v>46711</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="F60" s="3" t="s">
+      <c r="A60" s="9">
+        <v>6010000232</v>
+      </c>
+      <c r="B60" s="10" t="s">
+        <v>418</v>
+      </c>
+      <c r="C60" s="11"/>
+      <c r="D60" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E60" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F60" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G60" s="12"/>
+      <c r="H60" s="13">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="9">
+        <v>6010000073</v>
+      </c>
+      <c r="B61" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="C61" s="11"/>
+      <c r="D61" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E61" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="F61" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="G60" s="6">
-        <v>1488</v>
-      </c>
-      <c r="H60" s="4"/>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="2">
-        <v>6010000267</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>428</v>
-      </c>
-      <c r="C61" s="5">
-        <v>46813</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>430</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G61" s="6">
-        <v>650</v>
-      </c>
-      <c r="H61" s="4"/>
+      <c r="G61" s="12"/>
+      <c r="H61" s="13">
+        <v>720</v>
+      </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
-        <v>6010000141</v>
+        <v>6010000073</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>297</v>
+        <v>180</v>
       </c>
       <c r="C62" s="5">
-        <v>46746</v>
+        <v>46511</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>298</v>
+        <v>182</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>296</v>
+        <v>181</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G62" s="6">
-        <v>2425</v>
+        <v>1150</v>
       </c>
       <c r="H62" s="4"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
-        <v>6010000205</v>
+        <v>6010000169</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>388</v>
+        <v>343</v>
       </c>
       <c r="C63" s="5">
-        <v>46692</v>
+        <v>46751</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>389</v>
+        <v>344</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>390</v>
+        <v>106</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G63" s="6">
-        <v>10050</v>
+        <v>2110</v>
       </c>
       <c r="H63" s="4"/>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
-        <v>4010013583</v>
+        <v>6010000170</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>92</v>
+        <v>345</v>
       </c>
       <c r="C64" s="5">
-        <v>46504</v>
+        <v>46721</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>93</v>
+        <v>346</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>71</v>
+        <v>106</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G64" s="6">
-        <v>620</v>
+        <v>2590</v>
       </c>
       <c r="H64" s="4"/>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
-        <v>6010000074</v>
+        <v>6010000139</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>181</v>
+        <v>297</v>
       </c>
       <c r="C65" s="5">
-        <v>46721</v>
+        <v>46711</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>182</v>
+        <v>298</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>183</v>
+        <v>299</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G65" s="6">
-        <v>6048</v>
+        <v>1438</v>
       </c>
       <c r="H65" s="4"/>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
-        <v>6010000102</v>
+        <v>6010000267</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>242</v>
+        <v>435</v>
       </c>
       <c r="C66" s="5">
-        <v>46780</v>
+        <v>46813</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>243</v>
+        <v>436</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>22</v>
+        <v>437</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G66" s="6">
-        <v>4020</v>
+        <v>620</v>
       </c>
       <c r="H66" s="4"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
-        <v>6010000103</v>
+        <v>6010000141</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>244</v>
+        <v>300</v>
       </c>
       <c r="C67" s="5">
-        <v>46645</v>
+        <v>46746</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>245</v>
+        <v>301</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>22</v>
+        <v>299</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G67" s="6">
-        <v>2920</v>
+        <v>2425</v>
       </c>
       <c r="H67" s="4"/>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="2">
-        <v>6010000196</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="C68" s="5">
-        <v>46606</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="E68" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G68" s="6">
-        <v>1640</v>
-      </c>
-      <c r="H68" s="4"/>
+      <c r="A68" s="9">
+        <v>6010000205</v>
+      </c>
+      <c r="B68" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C68" s="11"/>
+      <c r="D68" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E68" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="F68" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="G68" s="12"/>
+      <c r="H68" s="13">
+        <v>7200</v>
+      </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
-        <v>4010013473</v>
+        <v>6010000205</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>50</v>
+        <v>393</v>
       </c>
       <c r="C69" s="5">
-        <v>46524</v>
+        <v>46692</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>51</v>
+        <v>395</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>30</v>
+        <v>394</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G69" s="6">
-        <v>420</v>
+        <v>10050</v>
       </c>
       <c r="H69" s="4"/>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
-        <v>6010000151</v>
+        <v>4010013583</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>316</v>
+        <v>91</v>
       </c>
       <c r="C70" s="5">
-        <v>46692</v>
+        <v>46504</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>317</v>
+        <v>92</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>318</v>
+        <v>70</v>
       </c>
       <c r="F70" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G70" s="6">
+        <v>620</v>
+      </c>
+      <c r="H70" s="4"/>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" s="9">
+        <v>6010000074</v>
+      </c>
+      <c r="B71" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="C71" s="11"/>
+      <c r="D71" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E71" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="F71" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="G70" s="6">
-        <v>540</v>
-      </c>
-      <c r="H70" s="4"/>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="2">
-        <v>6010000241</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="C71" s="5">
-        <v>46596</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="E71" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="F71" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G71" s="6">
-        <v>486</v>
-      </c>
-      <c r="H71" s="4"/>
+      <c r="G71" s="12"/>
+      <c r="H71" s="13">
+        <v>5760</v>
+      </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
-        <v>6010000194</v>
+        <v>6010000074</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>369</v>
+        <v>183</v>
       </c>
       <c r="C72" s="5">
         <v>46721</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>370</v>
+        <v>185</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>30</v>
+        <v>184</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G72" s="6">
-        <v>4020</v>
+        <v>6048</v>
       </c>
       <c r="H72" s="4"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="2">
-        <v>6010000194</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="C73" s="5">
-        <v>46803</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="E73" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F73" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G73" s="6">
-        <v>1470</v>
-      </c>
-      <c r="H73" s="4"/>
+      <c r="A73" s="9">
+        <v>6010000102</v>
+      </c>
+      <c r="B73" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="C73" s="11"/>
+      <c r="D73" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E73" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F73" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G73" s="12"/>
+      <c r="H73" s="13">
+        <v>1600</v>
+      </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
-        <v>6010000192</v>
+        <v>6010000102</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>362</v>
+        <v>244</v>
       </c>
       <c r="C74" s="5">
-        <v>46367</v>
+        <v>46780</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>363</v>
+        <v>245</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>364</v>
+        <v>22</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G74" s="6">
-        <v>365</v>
+        <v>3980</v>
       </c>
       <c r="H74" s="4"/>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
-        <v>6010000155</v>
+        <v>6010000103</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>322</v>
+        <v>246</v>
       </c>
       <c r="C75" s="5">
-        <v>46447</v>
+        <v>46645</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>323</v>
+        <v>247</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F75" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G75" s="6">
-        <v>380</v>
+        <v>2920</v>
       </c>
       <c r="H75" s="4"/>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
-        <v>6010000108</v>
+        <v>6010000196</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>246</v>
+        <v>379</v>
       </c>
       <c r="C76" s="5">
-        <v>46574</v>
+        <v>46606</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>247</v>
+        <v>380</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>15</v>
+        <v>381</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G76" s="6">
-        <v>560</v>
+        <v>1640</v>
       </c>
       <c r="H76" s="4"/>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
-        <v>6010000193</v>
+        <v>4010013473</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>365</v>
+        <v>49</v>
       </c>
       <c r="C77" s="5">
-        <v>46803</v>
+        <v>46524</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>366</v>
+        <v>50</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>30</v>
@@ -3642,118 +3654,116 @@
         <v>5</v>
       </c>
       <c r="G77" s="6">
-        <v>380</v>
+        <v>420</v>
       </c>
       <c r="H77" s="4"/>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="2">
-        <v>6010000193</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="C78" s="5">
-        <v>46726</v>
-      </c>
-      <c r="D78" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="E78" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F78" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G78" s="6">
-        <v>80</v>
-      </c>
-      <c r="H78" s="4"/>
+      <c r="A78" s="9">
+        <v>6010000150</v>
+      </c>
+      <c r="B78" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="C78" s="11"/>
+      <c r="D78" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E78" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="F78" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="G78" s="12"/>
+      <c r="H78" s="13">
+        <v>880</v>
+      </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
-        <v>6010000193</v>
+        <v>6010000151</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>365</v>
+        <v>322</v>
       </c>
       <c r="C79" s="5">
-        <v>46711</v>
+        <v>46692</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>368</v>
+        <v>323</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>30</v>
+        <v>321</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G79" s="6">
-        <v>170</v>
+        <v>540</v>
       </c>
       <c r="H79" s="4"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
-        <v>6010000216</v>
+        <v>6010000241</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>396</v>
+        <v>428</v>
       </c>
       <c r="C80" s="5">
-        <v>46690</v>
+        <v>46596</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>397</v>
+        <v>429</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>30</v>
+        <v>430</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G80" s="6">
-        <v>140</v>
+        <v>486</v>
       </c>
       <c r="H80" s="4"/>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
-        <v>6010000235</v>
+        <v>6010000194</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>417</v>
+        <v>374</v>
       </c>
       <c r="C81" s="5">
-        <v>46808</v>
+        <v>46803</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>418</v>
+        <v>375</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G81" s="6">
-        <v>1640</v>
+        <v>1470</v>
       </c>
       <c r="H81" s="4"/>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
-        <v>4010013662</v>
+        <v>6010000194</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>131</v>
+        <v>374</v>
       </c>
       <c r="C82" s="5">
-        <v>46537</v>
+        <v>46721</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>132</v>
+        <v>376</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>30</v>
@@ -3762,1662 +3772,1654 @@
         <v>5</v>
       </c>
       <c r="G82" s="6">
-        <v>190</v>
+        <v>4020</v>
       </c>
       <c r="H82" s="4"/>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
-        <v>4010013662</v>
+        <v>6010000192</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>131</v>
+        <v>367</v>
       </c>
       <c r="C83" s="5">
-        <v>46546</v>
+        <v>46367</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>133</v>
+        <v>368</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>30</v>
+        <v>369</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G83" s="6">
-        <v>420</v>
+        <v>365</v>
       </c>
       <c r="H83" s="4"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
-        <v>6010000076</v>
+        <v>6010000155</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>184</v>
+        <v>327</v>
       </c>
       <c r="C84" s="5">
-        <v>46483</v>
+        <v>46447</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>185</v>
+        <v>328</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>183</v>
+        <v>30</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G84" s="6">
-        <v>3076</v>
+        <v>380</v>
       </c>
       <c r="H84" s="4"/>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
-        <v>6010000110</v>
+        <v>6010000108</v>
       </c>
       <c r="B85" s="3" t="s">
         <v>248</v>
       </c>
       <c r="C85" s="5">
-        <v>46640</v>
+        <v>46574</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>249</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G85" s="6">
-        <v>1000</v>
+        <v>560</v>
       </c>
       <c r="H85" s="4"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
-        <v>6010000111</v>
+        <v>6010000193</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>250</v>
+        <v>370</v>
       </c>
       <c r="C86" s="5">
-        <v>46640</v>
+        <v>46803</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>251</v>
+        <v>371</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F86" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G86" s="6">
-        <v>2640</v>
+        <v>380</v>
       </c>
       <c r="H86" s="4"/>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
-        <v>4010013584</v>
+        <v>6010000193</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>94</v>
+        <v>370</v>
       </c>
       <c r="C87" s="5">
-        <v>46532</v>
+        <v>46726</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>95</v>
+        <v>372</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>88</v>
+        <v>30</v>
       </c>
       <c r="F87" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G87" s="6">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="H87" s="4"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
-        <v>4010013584</v>
+        <v>6010000193</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>94</v>
+        <v>370</v>
       </c>
       <c r="C88" s="5">
-        <v>46537</v>
+        <v>46711</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>96</v>
+        <v>373</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>88</v>
+        <v>30</v>
       </c>
       <c r="F88" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G88" s="6">
-        <v>380</v>
+        <v>170</v>
       </c>
       <c r="H88" s="4"/>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
-        <v>6010000171</v>
+        <v>6010000216</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>342</v>
+        <v>401</v>
       </c>
       <c r="C89" s="5">
-        <v>46579</v>
+        <v>46690</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>343</v>
+        <v>402</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>88</v>
+        <v>30</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G89" s="6">
-        <v>1500</v>
+        <v>140</v>
       </c>
       <c r="H89" s="4"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
-        <v>4010013585</v>
+        <v>6010000235</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>97</v>
+        <v>424</v>
       </c>
       <c r="C90" s="5">
-        <v>46568</v>
+        <v>46808</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>98</v>
+        <v>425</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>88</v>
+        <v>15</v>
       </c>
       <c r="F90" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G90" s="6">
-        <v>1500</v>
+        <v>1540</v>
       </c>
       <c r="H90" s="4"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
-        <v>6010000172</v>
+        <v>4010013662</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>344</v>
+        <v>131</v>
       </c>
       <c r="C91" s="5">
-        <v>46579</v>
+        <v>46546</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>345</v>
+        <v>132</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>88</v>
+        <v>30</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G91" s="6">
-        <v>1700</v>
+        <v>420</v>
       </c>
       <c r="H91" s="4"/>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
-        <v>6010000077</v>
+        <v>4010013662</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>186</v>
+        <v>131</v>
       </c>
       <c r="C92" s="5">
-        <v>46471</v>
+        <v>46537</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>187</v>
+        <v>133</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>188</v>
+        <v>30</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G92" s="6">
-        <v>5070</v>
+        <v>190</v>
       </c>
       <c r="H92" s="4"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
-        <v>6010000078</v>
+        <v>6010000076</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C93" s="5">
-        <v>46780</v>
+        <v>46483</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="F93" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G93" s="6">
-        <v>7150</v>
+        <v>3076</v>
       </c>
       <c r="H93" s="4"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
-        <v>6010000079</v>
+        <v>6010000110</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>192</v>
+        <v>250</v>
       </c>
       <c r="C94" s="5">
-        <v>46512</v>
+        <v>46640</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>193</v>
+        <v>251</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>194</v>
+        <v>4</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G94" s="6">
-        <v>310</v>
+        <v>1000</v>
       </c>
       <c r="H94" s="4"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
-        <v>4010013593</v>
+        <v>6010000111</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>108</v>
+        <v>252</v>
       </c>
       <c r="C95" s="5">
-        <v>46758</v>
+        <v>46640</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>109</v>
+        <v>253</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F95" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G95" s="6">
-        <v>560</v>
+        <v>2640</v>
       </c>
       <c r="H95" s="4"/>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A96" s="2">
-        <v>4010014329</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="C96" s="5">
-        <v>46641</v>
-      </c>
-      <c r="D96" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G96" s="6">
-        <v>230</v>
-      </c>
-      <c r="H96" s="4"/>
+      <c r="A96" s="9">
+        <v>4010013584</v>
+      </c>
+      <c r="B96" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="C96" s="11"/>
+      <c r="D96" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E96" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="F96" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G96" s="12"/>
+      <c r="H96" s="13">
+        <v>900</v>
+      </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
-        <v>4010013594</v>
+        <v>4010013584</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="C97" s="5">
-        <v>46573</v>
+        <v>46537</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>30</v>
+        <v>87</v>
       </c>
       <c r="F97" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G97" s="6">
-        <v>760</v>
+        <v>380</v>
       </c>
       <c r="H97" s="4"/>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
-        <v>4010014330</v>
+        <v>4010013584</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>158</v>
+        <v>93</v>
       </c>
       <c r="C98" s="5">
-        <v>46610</v>
+        <v>46532</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>159</v>
+        <v>95</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>30</v>
+        <v>87</v>
       </c>
       <c r="F98" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G98" s="6">
-        <v>280</v>
+        <v>200</v>
       </c>
       <c r="H98" s="4"/>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
-        <v>6010000156</v>
+        <v>6010000171</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>324</v>
+        <v>347</v>
       </c>
       <c r="C99" s="5">
-        <v>46447</v>
+        <v>46579</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>30</v>
+        <v>87</v>
       </c>
       <c r="F99" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G99" s="6">
-        <v>270</v>
+        <v>1500</v>
       </c>
       <c r="H99" s="4"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
-        <v>6010000233</v>
+        <v>4010013585</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>324</v>
+        <v>96</v>
       </c>
       <c r="C100" s="5">
-        <v>46721</v>
+        <v>46568</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>413</v>
+        <v>97</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>30</v>
+        <v>87</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G100" s="6">
-        <v>110</v>
+        <v>1500</v>
       </c>
       <c r="H100" s="4"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
-        <v>6010000080</v>
+        <v>6010000172</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>195</v>
+        <v>349</v>
       </c>
       <c r="C101" s="5">
-        <v>46423</v>
+        <v>46579</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>196</v>
+        <v>350</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>197</v>
+        <v>87</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G101" s="6">
-        <v>500</v>
+        <v>1620</v>
       </c>
       <c r="H101" s="4"/>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
-        <v>6010000113</v>
+        <v>6010000077</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>252</v>
+        <v>188</v>
       </c>
       <c r="C102" s="5">
-        <v>46598</v>
+        <v>46471</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>253</v>
+        <v>189</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>22</v>
+        <v>190</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G102" s="6">
-        <v>8340</v>
+        <v>5070</v>
       </c>
       <c r="H102" s="4"/>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A103" s="2">
-        <v>4010013656</v>
-      </c>
-      <c r="B103" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C103" s="5">
-        <v>46510</v>
-      </c>
-      <c r="D103" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="E103" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="F103" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G103" s="6">
-        <v>2340</v>
-      </c>
-      <c r="H103" s="4"/>
+      <c r="A103" s="9">
+        <v>6010000078</v>
+      </c>
+      <c r="B103" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="C103" s="11"/>
+      <c r="D103" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E103" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="F103" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="G103" s="12"/>
+      <c r="H103" s="13">
+        <v>125</v>
+      </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A104" s="8">
-        <v>4010013595</v>
-      </c>
-      <c r="B104" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="C104" s="10"/>
-      <c r="D104" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="E104" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F104" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G104" s="11"/>
-      <c r="H104" s="12">
-        <v>300</v>
-      </c>
+      <c r="A104" s="2">
+        <v>6010000078</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="C104" s="5">
+        <v>46780</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G104" s="6">
+        <v>7150</v>
+      </c>
+      <c r="H104" s="4"/>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
-        <v>6010000174</v>
+        <v>6010000079</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>346</v>
+        <v>194</v>
       </c>
       <c r="C105" s="5">
-        <v>46586</v>
+        <v>46512</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>347</v>
+        <v>195</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>348</v>
+        <v>196</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G105" s="6">
-        <v>1120</v>
+        <v>310</v>
       </c>
       <c r="H105" s="4"/>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
-        <v>6010000114</v>
+        <v>4010013593</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>254</v>
+        <v>107</v>
       </c>
       <c r="C106" s="5">
-        <v>46488</v>
+        <v>46758</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>255</v>
+        <v>108</v>
       </c>
       <c r="E106" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G106" s="6">
+        <v>560</v>
+      </c>
+      <c r="H106" s="4"/>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" s="9">
+        <v>4010013593</v>
+      </c>
+      <c r="B107" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="F106" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G106" s="6">
-        <v>2000</v>
-      </c>
-      <c r="H106" s="4"/>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A107" s="2">
-        <v>6010000081</v>
-      </c>
-      <c r="B107" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="C107" s="5">
-        <v>46660</v>
-      </c>
-      <c r="D107" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="E107" s="3" t="s">
+      <c r="C107" s="11"/>
+      <c r="D107" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="F107" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G107" s="6">
-        <v>750</v>
-      </c>
-      <c r="H107" s="4"/>
+      <c r="E107" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F107" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G107" s="12"/>
+      <c r="H107" s="13">
+        <v>560</v>
+      </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
-        <v>6010000082</v>
+        <v>4010014329</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>200</v>
+        <v>156</v>
       </c>
       <c r="C108" s="5">
-        <v>46505</v>
+        <v>46641</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>201</v>
+        <v>157</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>202</v>
+        <v>30</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G108" s="6">
-        <v>11100</v>
+        <v>230</v>
       </c>
       <c r="H108" s="4"/>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
-        <v>6010000175</v>
+        <v>4010013594</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>349</v>
+        <v>109</v>
       </c>
       <c r="C109" s="5">
-        <v>46556</v>
+        <v>46573</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>350</v>
+        <v>110</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>351</v>
+        <v>30</v>
       </c>
       <c r="F109" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G109" s="6">
-        <v>1900</v>
+        <v>760</v>
       </c>
       <c r="H109" s="4"/>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A110" s="2">
-        <v>6010000176</v>
-      </c>
-      <c r="B110" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="C110" s="5">
-        <v>46586</v>
-      </c>
-      <c r="D110" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="E110" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="F110" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G110" s="6">
-        <v>1980</v>
-      </c>
-      <c r="H110" s="4"/>
+      <c r="A110" s="9">
+        <v>4010013594</v>
+      </c>
+      <c r="B110" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="C110" s="11"/>
+      <c r="D110" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E110" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F110" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G110" s="12"/>
+      <c r="H110" s="13">
+        <v>1120</v>
+      </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
-        <v>6010000201</v>
+        <v>4010014330</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>381</v>
+        <v>158</v>
       </c>
       <c r="C111" s="5">
-        <v>46624</v>
+        <v>46610</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>382</v>
+        <v>159</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>383</v>
+        <v>30</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G111" s="6">
-        <v>910</v>
+        <v>280</v>
       </c>
       <c r="H111" s="4"/>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
-        <v>6010000202</v>
+        <v>6010000156</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>384</v>
+        <v>329</v>
       </c>
       <c r="C112" s="5">
-        <v>46685</v>
+        <v>46447</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>385</v>
+        <v>330</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>383</v>
+        <v>30</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G112" s="6">
-        <v>830</v>
+        <v>270</v>
       </c>
       <c r="H112" s="4"/>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="2">
-        <v>4010013262</v>
+        <v>6010000233</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>13</v>
+        <v>329</v>
       </c>
       <c r="C113" s="5">
-        <v>46549</v>
+        <v>46721</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>14</v>
+        <v>420</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F113" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G113" s="6">
-        <v>420</v>
+        <v>110</v>
       </c>
       <c r="H113" s="4"/>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A114" s="2">
-        <v>4010013465</v>
-      </c>
-      <c r="B114" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C114" s="5">
-        <v>46637</v>
-      </c>
-      <c r="D114" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E114" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F114" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G114" s="6">
-        <v>1720</v>
-      </c>
-      <c r="H114" s="4"/>
+      <c r="A114" s="9">
+        <v>6010000233</v>
+      </c>
+      <c r="B114" s="10" t="s">
+        <v>329</v>
+      </c>
+      <c r="C114" s="11"/>
+      <c r="D114" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E114" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F114" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G114" s="12"/>
+      <c r="H114" s="13">
+        <v>1350</v>
+      </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
-        <v>4010013466</v>
+        <v>6010000080</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>47</v>
+        <v>197</v>
       </c>
       <c r="C115" s="5">
-        <v>46704</v>
+        <v>46423</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>48</v>
+        <v>198</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G115" s="6">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="H115" s="4"/>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
-        <v>4010013671</v>
+        <v>6010000113</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>140</v>
+        <v>254</v>
       </c>
       <c r="C116" s="5">
-        <v>46566</v>
+        <v>46598</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>141</v>
+        <v>255</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F116" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G116" s="6">
-        <v>980</v>
+        <v>8340</v>
       </c>
       <c r="H116" s="4"/>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
-        <v>6010000252</v>
+        <v>4010013656</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>424</v>
+        <v>119</v>
       </c>
       <c r="C117" s="5">
-        <v>46780</v>
+        <v>46510</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>425</v>
+        <v>120</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>426</v>
+        <v>121</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G117" s="6">
-        <v>1500</v>
+        <v>2320</v>
       </c>
       <c r="H117" s="4"/>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
-        <v>6010000252</v>
+        <v>4010013595</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>424</v>
+        <v>111</v>
       </c>
       <c r="C118" s="5">
-        <v>46661</v>
+        <v>46623</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>427</v>
+        <v>112</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>426</v>
+        <v>30</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G118" s="6">
-        <v>690</v>
+        <v>100</v>
       </c>
       <c r="H118" s="4"/>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
-        <v>6010000218</v>
+        <v>6010000174</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>401</v>
+        <v>351</v>
       </c>
       <c r="C119" s="5">
-        <v>46780</v>
+        <v>46586</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>402</v>
+        <v>352</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>403</v>
+        <v>353</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G119" s="6">
-        <v>2400</v>
+        <v>1120</v>
       </c>
       <c r="H119" s="4"/>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" s="2">
-        <v>6010000218</v>
+        <v>6010000114</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>401</v>
+        <v>256</v>
       </c>
       <c r="C120" s="5">
-        <v>46812</v>
+        <v>46488</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>404</v>
+        <v>257</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>403</v>
+        <v>106</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G120" s="6">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="H120" s="4"/>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
-        <v>6010000083</v>
+        <v>6010000081</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C121" s="5">
-        <v>46537</v>
+        <v>46660</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>205</v>
+        <v>2</v>
       </c>
       <c r="F121" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G121" s="6">
-        <v>1280</v>
+        <v>750</v>
       </c>
       <c r="H121" s="4"/>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
-        <v>6010000084</v>
+        <v>6010000082</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C122" s="5">
-        <v>46711</v>
+        <v>46505</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="F122" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G122" s="6">
-        <v>4420</v>
+        <v>11100</v>
       </c>
       <c r="H122" s="4"/>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A123" s="8">
-        <v>6010000115</v>
-      </c>
-      <c r="B123" s="9" t="s">
-        <v>256</v>
-      </c>
-      <c r="C123" s="10"/>
-      <c r="D123" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="E123" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F123" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G123" s="11"/>
-      <c r="H123" s="12">
-        <v>6000</v>
-      </c>
+      <c r="A123" s="2">
+        <v>6010000175</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="C123" s="5">
+        <v>46556</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E123" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="F123" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G123" s="6">
+        <v>1880</v>
+      </c>
+      <c r="H123" s="4"/>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" s="2">
-        <v>6010000115</v>
+        <v>6010000176</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>256</v>
+        <v>357</v>
       </c>
       <c r="C124" s="5">
-        <v>46971</v>
+        <v>46586</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>257</v>
+        <v>358</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>22</v>
+        <v>356</v>
       </c>
       <c r="F124" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G124" s="6">
-        <v>3500</v>
+        <v>1980</v>
       </c>
       <c r="H124" s="4"/>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" s="2">
-        <v>6010000116</v>
+        <v>6010000201</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>258</v>
+        <v>386</v>
       </c>
       <c r="C125" s="5">
-        <v>46971</v>
+        <v>46624</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>259</v>
+        <v>387</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>4</v>
+        <v>388</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G125" s="6">
-        <v>4880</v>
+        <v>910</v>
       </c>
       <c r="H125" s="4"/>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" s="2">
-        <v>7050000019</v>
+        <v>6010000202</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>437</v>
-      </c>
-      <c r="C126" s="5"/>
+        <v>389</v>
+      </c>
+      <c r="C126" s="5">
+        <v>46685</v>
+      </c>
       <c r="D126" s="3" t="s">
-        <v>2</v>
+        <v>390</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>2</v>
+        <v>388</v>
       </c>
       <c r="F126" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G126" s="6">
-        <v>530</v>
+        <v>830</v>
       </c>
       <c r="H126" s="4"/>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" s="2">
-        <v>6010000117</v>
+        <v>4010013262</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>260</v>
+        <v>13</v>
       </c>
       <c r="C127" s="5">
-        <v>46711</v>
+        <v>46549</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>261</v>
+        <v>14</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F127" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G127" s="6">
-        <v>6040</v>
+        <v>380</v>
       </c>
       <c r="H127" s="4"/>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" s="2">
-        <v>6010000118</v>
+        <v>4010013465</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>262</v>
+        <v>44</v>
       </c>
       <c r="C128" s="5">
-        <v>46574</v>
+        <v>46637</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>263</v>
+        <v>45</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F128" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G128" s="6">
-        <v>10240</v>
+        <v>1680</v>
       </c>
       <c r="H128" s="4"/>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
-        <v>6010000148</v>
+        <v>4010013466</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>314</v>
+        <v>46</v>
       </c>
       <c r="C129" s="5">
-        <v>46751</v>
+        <v>46704</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>315</v>
+        <v>47</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="F129" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G129" s="6">
-        <v>2420</v>
+        <v>80</v>
       </c>
       <c r="H129" s="4"/>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A130" s="8">
-        <v>6010000119</v>
-      </c>
-      <c r="B130" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="C130" s="10"/>
-      <c r="D130" s="9" t="s">
+      <c r="A130" s="2">
+        <v>4010013671</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C130" s="5">
+        <v>46566</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E130" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F130" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G130" s="6">
+        <v>980</v>
+      </c>
+      <c r="H130" s="4"/>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" s="9">
+        <v>4010013671</v>
+      </c>
+      <c r="B131" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="C131" s="11"/>
+      <c r="D131" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E130" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="F130" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G130" s="11"/>
-      <c r="H130" s="12">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A131" s="2">
-        <v>6010000085</v>
-      </c>
-      <c r="B131" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="C131" s="5">
-        <v>46388</v>
-      </c>
-      <c r="D131" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="E131" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="F131" s="3" t="s">
+      <c r="E131" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F131" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G131" s="12"/>
+      <c r="H131" s="13">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" s="2">
+        <v>6010000252</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="C132" s="5">
+        <v>46780</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="E132" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="F132" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G131" s="6">
-        <v>800</v>
-      </c>
-      <c r="H131" s="4"/>
-    </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A132" s="8">
-        <v>6010000085</v>
-      </c>
-      <c r="B132" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="C132" s="10"/>
-      <c r="D132" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="E132" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="F132" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="G132" s="11"/>
-      <c r="H132" s="12">
-        <v>54000</v>
-      </c>
+      <c r="G132" s="6">
+        <v>1500</v>
+      </c>
+      <c r="H132" s="4"/>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" s="2">
-        <v>6010000123</v>
+        <v>6010000252</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>266</v>
+        <v>431</v>
       </c>
       <c r="C133" s="5">
-        <v>46752</v>
+        <v>46661</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>267</v>
+        <v>434</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>88</v>
+        <v>433</v>
       </c>
       <c r="F133" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G133" s="6">
-        <v>4860</v>
+        <v>690</v>
       </c>
       <c r="H133" s="4"/>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A134" s="8">
-        <v>6010000230</v>
-      </c>
-      <c r="B134" s="9" t="s">
-        <v>410</v>
-      </c>
-      <c r="C134" s="10"/>
-      <c r="D134" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="E134" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F134" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G134" s="11"/>
-      <c r="H134" s="12">
-        <v>3600</v>
-      </c>
+      <c r="A134" s="2">
+        <v>6010000218</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="C134" s="5">
+        <v>46780</v>
+      </c>
+      <c r="D134" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="E134" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="F134" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G134" s="6">
+        <v>2375</v>
+      </c>
+      <c r="H134" s="4"/>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" s="2">
-        <v>6010000086</v>
+        <v>6010000218</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>212</v>
+        <v>406</v>
       </c>
       <c r="C135" s="5">
-        <v>46641</v>
+        <v>46812</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>213</v>
+        <v>409</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>214</v>
+        <v>408</v>
       </c>
       <c r="F135" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G135" s="6">
-        <v>7500</v>
+        <v>500</v>
       </c>
       <c r="H135" s="4"/>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" s="2">
-        <v>6010000147</v>
+        <v>6010000083</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>312</v>
+        <v>205</v>
       </c>
       <c r="C136" s="5">
-        <v>46813</v>
+        <v>46537</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>313</v>
+        <v>206</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>296</v>
+        <v>207</v>
       </c>
       <c r="F136" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G136" s="6">
-        <v>700</v>
+        <v>1270</v>
       </c>
       <c r="H136" s="4"/>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A137" s="2">
-        <v>6010000144</v>
-      </c>
-      <c r="B137" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="C137" s="5">
-        <v>46605</v>
-      </c>
-      <c r="D137" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="E137" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="F137" s="3" t="s">
+      <c r="A137" s="9">
+        <v>6010000083</v>
+      </c>
+      <c r="B137" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="C137" s="11"/>
+      <c r="D137" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E137" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="F137" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="G137" s="6">
-        <v>840</v>
-      </c>
-      <c r="H137" s="4"/>
+      <c r="G137" s="12"/>
+      <c r="H137" s="13">
+        <v>300</v>
+      </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" s="2">
-        <v>6010000214</v>
+        <v>6010000084</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>391</v>
+        <v>208</v>
       </c>
       <c r="C138" s="5">
-        <v>46692</v>
+        <v>46711</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>392</v>
+        <v>209</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>308</v>
+        <v>210</v>
       </c>
       <c r="F138" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G138" s="6">
-        <v>340</v>
+        <v>4420</v>
       </c>
       <c r="H138" s="4"/>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" s="2">
-        <v>6010000215</v>
+        <v>6010000115</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>393</v>
+        <v>258</v>
       </c>
       <c r="C139" s="5">
-        <v>46726</v>
+        <v>46971</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>394</v>
+        <v>259</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>395</v>
+        <v>22</v>
       </c>
       <c r="F139" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G139" s="6">
-        <v>506</v>
+        <v>3500</v>
       </c>
       <c r="H139" s="4"/>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A140" s="8">
-        <v>6010000142</v>
-      </c>
-      <c r="B140" s="9" t="s">
-        <v>299</v>
-      </c>
-      <c r="C140" s="10"/>
-      <c r="D140" s="9" t="s">
+      <c r="A140" s="9">
+        <v>6010000115</v>
+      </c>
+      <c r="B140" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="C140" s="11"/>
+      <c r="D140" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E140" s="9" t="s">
-        <v>300</v>
-      </c>
-      <c r="F140" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="G140" s="11"/>
-      <c r="H140" s="12">
-        <v>250</v>
+      <c r="E140" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F140" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G140" s="12"/>
+      <c r="H140" s="13">
+        <v>6000</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" s="2">
-        <v>6010000143</v>
+        <v>6010000116</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>301</v>
+        <v>260</v>
       </c>
       <c r="C141" s="5">
-        <v>46425</v>
+        <v>46971</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>302</v>
+        <v>261</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>303</v>
+        <v>4</v>
       </c>
       <c r="F141" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G141" s="6">
-        <v>107</v>
+        <v>4880</v>
       </c>
       <c r="H141" s="4"/>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A142" s="2">
-        <v>6010000145</v>
-      </c>
-      <c r="B142" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="C142" s="5">
-        <v>46556</v>
-      </c>
-      <c r="D142" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="E142" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="F142" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G142" s="6">
-        <v>179</v>
-      </c>
-      <c r="H142" s="4"/>
+      <c r="A142" s="9">
+        <v>6010000116</v>
+      </c>
+      <c r="B142" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="C142" s="11"/>
+      <c r="D142" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E142" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F142" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G142" s="12"/>
+      <c r="H142" s="13">
+        <v>3600</v>
+      </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" s="2">
-        <v>4010013596</v>
+        <v>7050000019</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C143" s="5">
-        <v>46446</v>
-      </c>
+        <v>444</v>
+      </c>
+      <c r="C143" s="5"/>
       <c r="D143" s="3" t="s">
-        <v>114</v>
+        <v>2</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="F143" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G143" s="6">
-        <v>370</v>
+        <v>530</v>
       </c>
       <c r="H143" s="4"/>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" s="2">
-        <v>4010013655</v>
+        <v>6010000117</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>117</v>
+        <v>262</v>
       </c>
       <c r="C144" s="5">
-        <v>46550</v>
+        <v>46711</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>118</v>
+        <v>263</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F144" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G144" s="6">
-        <v>700</v>
+        <v>6040</v>
       </c>
       <c r="H144" s="4"/>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" s="2">
-        <v>4010013474</v>
+        <v>6010000118</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>52</v>
+        <v>264</v>
       </c>
       <c r="C145" s="5">
-        <v>46511</v>
+        <v>46574</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>53</v>
+        <v>265</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F145" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G145" s="6">
-        <v>290</v>
+        <v>10240</v>
       </c>
       <c r="H145" s="4"/>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A146" s="2">
-        <v>4010013474</v>
-      </c>
-      <c r="B146" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C146" s="5">
-        <v>46579</v>
-      </c>
-      <c r="D146" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E146" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F146" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G146" s="6">
-        <v>590</v>
-      </c>
-      <c r="H146" s="4"/>
+      <c r="A146" s="9">
+        <v>6010000148</v>
+      </c>
+      <c r="B146" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="C146" s="11"/>
+      <c r="D146" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E146" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F146" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G146" s="12"/>
+      <c r="H146" s="13">
+        <v>20</v>
+      </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" s="2">
-        <v>4010013475</v>
+        <v>6010000148</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>55</v>
+        <v>318</v>
       </c>
       <c r="C147" s="5">
-        <v>46525</v>
+        <v>46751</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>56</v>
+        <v>319</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F147" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G147" s="6">
-        <v>1330</v>
+        <v>2400</v>
       </c>
       <c r="H147" s="4"/>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A148" s="8">
-        <v>6010000087</v>
-      </c>
-      <c r="B148" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="C148" s="10"/>
-      <c r="D148" s="9" t="s">
+      <c r="A148" s="2">
+        <v>6010000119</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C148" s="5">
+        <v>46598</v>
+      </c>
+      <c r="D148" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="E148" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="F148" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G148" s="6">
+        <v>300</v>
+      </c>
+      <c r="H148" s="4"/>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A149" s="9">
+        <v>6010000085</v>
+      </c>
+      <c r="B149" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="C149" s="11"/>
+      <c r="D149" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E148" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="F148" s="9" t="s">
+      <c r="E149" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="F149" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="G148" s="11"/>
-      <c r="H148" s="12">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A149" s="2">
-        <v>6010000087</v>
-      </c>
-      <c r="B149" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="C149" s="5">
-        <v>46388</v>
-      </c>
-      <c r="D149" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="E149" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="F149" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G149" s="6">
-        <v>4700</v>
-      </c>
-      <c r="H149" s="4"/>
+      <c r="G149" s="12"/>
+      <c r="H149" s="13">
+        <v>54000</v>
+      </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" s="2">
-        <v>6010000126</v>
+        <v>6010000085</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>268</v>
+        <v>211</v>
       </c>
       <c r="C150" s="5">
-        <v>46780</v>
+        <v>46388</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>269</v>
+        <v>213</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>22</v>
+        <v>212</v>
       </c>
       <c r="F150" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G150" s="6">
-        <v>5500</v>
+        <v>800</v>
       </c>
       <c r="H150" s="4"/>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" s="2">
-        <v>6010000227</v>
+        <v>6010000123</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>407</v>
+        <v>269</v>
       </c>
       <c r="C151" s="5">
-        <v>46645</v>
+        <v>46752</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>408</v>
+        <v>270</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>22</v>
+        <v>87</v>
       </c>
       <c r="F151" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G151" s="6">
-        <v>2240</v>
+        <v>4860</v>
       </c>
       <c r="H151" s="4"/>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" s="2">
-        <v>6010000227</v>
+        <v>6010000230</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="C152" s="5">
-        <v>46631</v>
+        <v>46614</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="E152" s="3" t="s">
         <v>22</v>
@@ -5426,718 +5428,700 @@
         <v>5</v>
       </c>
       <c r="G152" s="6">
-        <v>4700</v>
+        <v>2980</v>
       </c>
       <c r="H152" s="4"/>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" s="2">
-        <v>6010000088</v>
+        <v>6010000230</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>217</v>
+        <v>415</v>
       </c>
       <c r="C153" s="5">
-        <v>46661</v>
+        <v>46600</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>218</v>
+        <v>417</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>219</v>
+        <v>22</v>
       </c>
       <c r="F153" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G153" s="6">
-        <v>2660</v>
+        <v>620</v>
       </c>
       <c r="H153" s="4"/>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" s="2">
-        <v>4010013666</v>
+        <v>6010000086</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>137</v>
+        <v>214</v>
       </c>
       <c r="C154" s="5">
-        <v>46625</v>
+        <v>46641</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>138</v>
+        <v>215</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>30</v>
+        <v>216</v>
       </c>
       <c r="F154" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G154" s="6">
-        <v>100</v>
+        <v>7500</v>
       </c>
       <c r="H154" s="4"/>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A155" s="2">
-        <v>4010013666</v>
-      </c>
-      <c r="B155" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="C155" s="5">
-        <v>46593</v>
-      </c>
-      <c r="D155" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="E155" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F155" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G155" s="6">
-        <v>200</v>
-      </c>
-      <c r="H155" s="4"/>
+      <c r="A155" s="9">
+        <v>6010000086</v>
+      </c>
+      <c r="B155" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="C155" s="11"/>
+      <c r="D155" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E155" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="F155" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="G155" s="12"/>
+      <c r="H155" s="13">
+        <v>2000</v>
+      </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A156" s="2">
-        <v>6010000128</v>
-      </c>
-      <c r="B156" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="C156" s="5">
-        <v>46721</v>
-      </c>
-      <c r="D156" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="E156" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F156" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G156" s="6">
-        <v>640</v>
-      </c>
-      <c r="H156" s="4"/>
+      <c r="A156" s="9">
+        <v>6010000147</v>
+      </c>
+      <c r="B156" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="C156" s="11"/>
+      <c r="D156" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E156" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="F156" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="G156" s="12"/>
+      <c r="H156" s="13">
+        <v>500</v>
+      </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" s="2">
-        <v>6010000129</v>
+        <v>6010000147</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>272</v>
+        <v>316</v>
       </c>
       <c r="C157" s="5">
-        <v>46569</v>
+        <v>46813</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>273</v>
+        <v>317</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>15</v>
+        <v>299</v>
       </c>
       <c r="F157" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G157" s="6">
-        <v>50</v>
+        <v>700</v>
       </c>
       <c r="H157" s="4"/>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" s="2">
-        <v>6010000129</v>
+        <v>6010000144</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>272</v>
+        <v>308</v>
       </c>
       <c r="C158" s="5">
-        <v>46758</v>
+        <v>46605</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>274</v>
+        <v>309</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>15</v>
+        <v>299</v>
       </c>
       <c r="F158" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G158" s="6">
-        <v>700</v>
+        <v>810</v>
       </c>
       <c r="H158" s="4"/>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A159" s="2">
-        <v>6010000130</v>
-      </c>
-      <c r="B159" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="C159" s="5">
-        <v>46569</v>
-      </c>
-      <c r="D159" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="E159" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F159" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G159" s="6">
-        <v>20</v>
-      </c>
-      <c r="H159" s="4"/>
+      <c r="A159" s="9">
+        <v>6010000144</v>
+      </c>
+      <c r="B159" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="C159" s="11"/>
+      <c r="D159" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E159" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="F159" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="G159" s="12"/>
+      <c r="H159" s="13">
+        <v>100</v>
+      </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" s="2">
-        <v>6010000130</v>
+        <v>6010000214</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>275</v>
+        <v>396</v>
       </c>
       <c r="C160" s="5">
-        <v>46753</v>
+        <v>46692</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>277</v>
+        <v>397</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>30</v>
+        <v>312</v>
       </c>
       <c r="F160" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G160" s="6">
-        <v>630</v>
+        <v>340</v>
       </c>
       <c r="H160" s="4"/>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A161" s="2">
-        <v>6010000198</v>
-      </c>
-      <c r="B161" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="C161" s="5">
-        <v>46568</v>
-      </c>
-      <c r="D161" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="E161" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F161" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G161" s="6">
-        <v>600</v>
-      </c>
-      <c r="H161" s="4"/>
+      <c r="A161" s="9">
+        <v>6010000215</v>
+      </c>
+      <c r="B161" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C161" s="11"/>
+      <c r="D161" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E161" s="10" t="s">
+        <v>399</v>
+      </c>
+      <c r="F161" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="G161" s="12"/>
+      <c r="H161" s="13">
+        <v>1000</v>
+      </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" s="2">
-        <v>4010013586</v>
+        <v>6010000215</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>99</v>
+        <v>398</v>
       </c>
       <c r="C162" s="5">
-        <v>46537</v>
+        <v>46726</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>11</v>
+        <v>399</v>
       </c>
       <c r="F162" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G162" s="6">
-        <v>1340</v>
+        <v>504</v>
       </c>
       <c r="H162" s="4"/>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" s="2">
-        <v>4010013587</v>
+        <v>6010000142</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>101</v>
+        <v>302</v>
       </c>
       <c r="C163" s="5">
-        <v>46537</v>
+        <v>46610</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>102</v>
+        <v>303</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>4</v>
+        <v>304</v>
       </c>
       <c r="F163" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G163" s="6">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="H163" s="4"/>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" s="2">
-        <v>4010013549</v>
+        <v>6010000143</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>72</v>
+        <v>305</v>
       </c>
       <c r="C164" s="5">
-        <v>46525</v>
+        <v>46425</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>73</v>
+        <v>306</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>8</v>
+        <v>307</v>
       </c>
       <c r="F164" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G164" s="6">
-        <v>980</v>
+        <v>107</v>
       </c>
       <c r="H164" s="4"/>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" s="2">
-        <v>4010013249</v>
+        <v>6010000145</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>0</v>
+        <v>310</v>
       </c>
       <c r="C165" s="5">
-        <v>46442</v>
+        <v>46556</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>1</v>
+        <v>311</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>4</v>
+        <v>312</v>
       </c>
       <c r="F165" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G165" s="6">
-        <v>460</v>
+        <v>179</v>
       </c>
       <c r="H165" s="4"/>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" s="2">
-        <v>4010013573</v>
+        <v>4010013596</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="C166" s="5">
-        <v>46423</v>
+        <v>46446</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F166" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G166" s="6">
-        <v>500</v>
+        <v>370</v>
       </c>
       <c r="H166" s="4"/>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A167" s="2">
-        <v>4010013574</v>
-      </c>
-      <c r="B167" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C167" s="5">
-        <v>46545</v>
-      </c>
-      <c r="D167" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E167" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F167" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G167" s="6">
-        <v>660</v>
-      </c>
-      <c r="H167" s="4"/>
+      <c r="A167" s="9">
+        <v>4010013655</v>
+      </c>
+      <c r="B167" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="C167" s="11"/>
+      <c r="D167" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E167" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F167" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G167" s="12"/>
+      <c r="H167" s="13">
+        <v>400</v>
+      </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" s="2">
-        <v>4010013588</v>
+        <v>4010013655</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="C168" s="5">
-        <v>46582</v>
+        <v>46550</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F168" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G168" s="6">
-        <v>3100</v>
+        <v>700</v>
       </c>
       <c r="H168" s="4"/>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" s="2">
-        <v>4010013479</v>
+        <v>4010013474</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="C169" s="5">
-        <v>46536</v>
+        <v>46579</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F169" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G169" s="6">
-        <v>320</v>
+        <v>590</v>
       </c>
       <c r="H169" s="4"/>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" s="2">
-        <v>4010013479</v>
+        <v>4010013474</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="C170" s="5">
-        <v>46594</v>
+        <v>46511</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F170" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G170" s="6">
-        <v>400</v>
+        <v>290</v>
       </c>
       <c r="H170" s="4"/>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" s="2">
-        <v>4010013479</v>
+        <v>4010013475</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="C171" s="5">
-        <v>46419</v>
+        <v>46525</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F171" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G171" s="6">
-        <v>200</v>
+        <v>1330</v>
       </c>
       <c r="H171" s="4"/>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A172" s="2">
-        <v>4010013700</v>
-      </c>
-      <c r="B172" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="C172" s="5">
-        <v>46446</v>
-      </c>
-      <c r="D172" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="E172" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F172" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G172" s="6">
-        <v>560</v>
-      </c>
-      <c r="H172" s="4"/>
+      <c r="A172" s="9">
+        <v>6010000087</v>
+      </c>
+      <c r="B172" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="C172" s="11"/>
+      <c r="D172" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E172" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="F172" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="G172" s="12"/>
+      <c r="H172" s="13">
+        <v>10000</v>
+      </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" s="2">
-        <v>4010013700</v>
+        <v>6010000087</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>151</v>
+        <v>217</v>
       </c>
       <c r="C173" s="5">
-        <v>46533</v>
+        <v>46388</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>153</v>
+        <v>218</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>4</v>
+        <v>204</v>
       </c>
       <c r="F173" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G173" s="6">
-        <v>300</v>
+        <v>4700</v>
       </c>
       <c r="H173" s="4"/>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" s="2">
-        <v>4010013701</v>
+        <v>6010000126</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>154</v>
+        <v>271</v>
       </c>
       <c r="C174" s="5">
-        <v>46589</v>
+        <v>46780</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>155</v>
+        <v>272</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F174" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G174" s="6">
-        <v>1160</v>
+        <v>5500</v>
       </c>
       <c r="H174" s="4"/>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A175" s="2">
-        <v>4010013657</v>
-      </c>
-      <c r="B175" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C175" s="5">
-        <v>46513</v>
-      </c>
-      <c r="D175" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E175" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F175" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G175" s="6">
-        <v>800</v>
-      </c>
-      <c r="H175" s="4"/>
+      <c r="A175" s="9">
+        <v>6010000126</v>
+      </c>
+      <c r="B175" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="C175" s="11"/>
+      <c r="D175" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E175" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F175" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G175" s="12"/>
+      <c r="H175" s="13">
+        <v>2000</v>
+      </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" s="2">
-        <v>4010013658</v>
+        <v>6010000227</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>124</v>
+        <v>412</v>
       </c>
       <c r="C176" s="5">
-        <v>46587</v>
+        <v>46631</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>125</v>
+        <v>413</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F176" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G176" s="6">
+        <v>4700</v>
+      </c>
+      <c r="H176" s="4"/>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A177" s="9">
+        <v>6010000227</v>
+      </c>
+      <c r="B177" s="10" t="s">
+        <v>412</v>
+      </c>
+      <c r="C177" s="11"/>
+      <c r="D177" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E177" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F177" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G177" s="12"/>
+      <c r="H177" s="13">
         <v>1200</v>
       </c>
-      <c r="H176" s="4"/>
-    </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A177" s="2">
-        <v>4010013658</v>
-      </c>
-      <c r="B177" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="C177" s="5">
-        <v>46563</v>
-      </c>
-      <c r="D177" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="E177" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F177" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G177" s="6">
-        <v>70</v>
-      </c>
-      <c r="H177" s="4"/>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" s="2">
-        <v>4010013548</v>
+        <v>6010000227</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>69</v>
+        <v>412</v>
       </c>
       <c r="C178" s="5">
-        <v>46469</v>
+        <v>46645</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>70</v>
+        <v>414</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>71</v>
+        <v>22</v>
       </c>
       <c r="F178" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G178" s="6">
-        <v>830</v>
+        <v>2240</v>
       </c>
       <c r="H178" s="4"/>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" s="2">
-        <v>4010013480</v>
+        <v>6010000088</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>67</v>
+        <v>219</v>
       </c>
       <c r="C179" s="5">
-        <v>46408</v>
+        <v>46661</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>68</v>
+        <v>220</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>8</v>
+        <v>221</v>
       </c>
       <c r="F179" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G179" s="6">
-        <v>1230</v>
+        <v>2660</v>
       </c>
       <c r="H179" s="4"/>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A180" s="2">
-        <v>4010013477</v>
-      </c>
-      <c r="B180" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C180" s="5">
-        <v>46574</v>
-      </c>
-      <c r="D180" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E180" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F180" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G180" s="6">
-        <v>780</v>
-      </c>
-      <c r="H180" s="4"/>
+      <c r="A180" s="9">
+        <v>4010013666</v>
+      </c>
+      <c r="B180" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="C180" s="11"/>
+      <c r="D180" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E180" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F180" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G180" s="12"/>
+      <c r="H180" s="13">
+        <v>200</v>
+      </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" s="2">
-        <v>6010000131</v>
+        <v>4010013666</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>278</v>
+        <v>137</v>
       </c>
       <c r="C181" s="5">
-        <v>46784</v>
+        <v>46625</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>279</v>
+        <v>138</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F181" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G181" s="6">
-        <v>2060</v>
+        <v>100</v>
       </c>
       <c r="H181" s="4"/>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" s="2">
-        <v>4010013699</v>
+        <v>4010013666</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="C182" s="5">
-        <v>46438</v>
+        <v>46593</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E182" s="3" t="s">
         <v>30</v>
@@ -6146,382 +6130,376 @@
         <v>5</v>
       </c>
       <c r="G182" s="6">
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="H182" s="4"/>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" s="2">
-        <v>6010000089</v>
+        <v>6010000128</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>220</v>
+        <v>273</v>
       </c>
       <c r="C183" s="5">
-        <v>46871</v>
+        <v>46721</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>221</v>
+        <v>274</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>222</v>
+        <v>30</v>
       </c>
       <c r="F183" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G183" s="6">
-        <v>2300</v>
+        <v>640</v>
       </c>
       <c r="H183" s="4"/>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A184" s="2">
-        <v>6010000089</v>
-      </c>
-      <c r="B184" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="C184" s="5">
-        <v>46424</v>
-      </c>
-      <c r="D184" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="E184" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="F184" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G184" s="6">
-        <v>2360</v>
-      </c>
-      <c r="H184" s="4"/>
+      <c r="A184" s="9">
+        <v>6010000128</v>
+      </c>
+      <c r="B184" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="C184" s="11"/>
+      <c r="D184" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E184" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F184" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G184" s="12"/>
+      <c r="H184" s="13">
+        <v>300</v>
+      </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" s="2">
-        <v>6010000132</v>
+        <v>6010000129</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="C185" s="5">
-        <v>46614</v>
+        <v>46569</v>
       </c>
       <c r="D185" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="E185" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F185" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G185" s="6">
+        <v>50</v>
+      </c>
+      <c r="H185" s="4"/>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A186" s="9">
+        <v>6010000129</v>
+      </c>
+      <c r="B186" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="C186" s="11"/>
+      <c r="D186" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E185" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F185" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G185" s="6">
-        <v>2860</v>
-      </c>
-      <c r="H185" s="4"/>
-    </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A186" s="2">
-        <v>6010000146</v>
-      </c>
-      <c r="B186" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="C186" s="5">
-        <v>46746</v>
-      </c>
-      <c r="D186" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="E186" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="F186" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G186" s="6">
+      <c r="E186" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F186" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G186" s="12"/>
+      <c r="H186" s="13">
         <v>480</v>
       </c>
-      <c r="H186" s="4"/>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187" s="2">
-        <v>6010000090</v>
+        <v>6010000129</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>224</v>
+        <v>275</v>
       </c>
       <c r="C187" s="5">
-        <v>46482</v>
+        <v>46758</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>225</v>
+        <v>277</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="F187" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G187" s="6">
-        <v>4450</v>
+        <v>700</v>
       </c>
       <c r="H187" s="4"/>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" s="2">
-        <v>6010000199</v>
+        <v>6010000130</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>379</v>
+        <v>278</v>
       </c>
       <c r="C188" s="5">
-        <v>46556</v>
+        <v>46753</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>380</v>
+        <v>279</v>
       </c>
       <c r="E188" s="3" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F188" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G188" s="6">
-        <v>1680</v>
+        <v>630</v>
       </c>
       <c r="H188" s="4"/>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A189" s="2">
-        <v>6010000133</v>
-      </c>
-      <c r="B189" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="C189" s="5">
-        <v>46388</v>
-      </c>
-      <c r="D189" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="E189" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="F189" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G189" s="6">
-        <v>1200</v>
-      </c>
-      <c r="H189" s="4"/>
+      <c r="A189" s="9">
+        <v>6010000130</v>
+      </c>
+      <c r="B189" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="C189" s="11"/>
+      <c r="D189" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E189" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F189" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G189" s="12"/>
+      <c r="H189" s="13">
+        <v>300</v>
+      </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190" s="2">
-        <v>6010000134</v>
+        <v>6010000130</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="C190" s="5">
-        <v>46488</v>
+        <v>46569</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="E190" s="3" t="s">
-        <v>88</v>
+        <v>30</v>
       </c>
       <c r="F190" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G190" s="6">
-        <v>1180</v>
+        <v>20</v>
       </c>
       <c r="H190" s="4"/>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" s="2">
-        <v>6010000135</v>
+        <v>6010000198</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>285</v>
+        <v>382</v>
       </c>
       <c r="C191" s="5">
-        <v>46388</v>
+        <v>46568</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>286</v>
+        <v>383</v>
       </c>
       <c r="E191" s="3" t="s">
-        <v>88</v>
+        <v>8</v>
       </c>
       <c r="F191" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G191" s="6">
-        <v>1560</v>
+        <v>600</v>
       </c>
       <c r="H191" s="4"/>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192" s="2">
-        <v>6010000136</v>
+        <v>4010013586</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>287</v>
+        <v>98</v>
       </c>
       <c r="C192" s="5">
-        <v>46496</v>
+        <v>46537</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>288</v>
+        <v>99</v>
       </c>
       <c r="E192" s="3" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F192" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G192" s="6">
-        <v>750</v>
+        <v>1280</v>
       </c>
       <c r="H192" s="4"/>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" s="2">
-        <v>6010000137</v>
+        <v>4010013587</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>289</v>
+        <v>100</v>
       </c>
       <c r="C193" s="5">
-        <v>46496</v>
+        <v>46537</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>290</v>
+        <v>101</v>
       </c>
       <c r="E193" s="3" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F193" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G193" s="6">
-        <v>590</v>
+        <v>140</v>
       </c>
       <c r="H193" s="4"/>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" s="2">
-        <v>4010013269</v>
+        <v>4010013549</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="C194" s="5">
-        <v>46558</v>
+        <v>46525</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F194" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G194" s="6">
-        <v>900</v>
+        <v>980</v>
       </c>
       <c r="H194" s="4"/>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" s="2">
-        <v>6010000177</v>
+        <v>4010013249</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>354</v>
+        <v>0</v>
       </c>
       <c r="C195" s="5">
-        <v>46971</v>
+        <v>46442</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>355</v>
+        <v>1</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>356</v>
+        <v>4</v>
       </c>
       <c r="F195" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G195" s="6">
-        <v>2980</v>
+        <v>460</v>
       </c>
       <c r="H195" s="4"/>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" s="2">
-        <v>6010000178</v>
+        <v>4010013573</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>357</v>
+        <v>79</v>
       </c>
       <c r="C196" s="5">
-        <v>47087</v>
+        <v>46423</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>358</v>
+        <v>80</v>
       </c>
       <c r="E196" s="3" t="s">
-        <v>359</v>
+        <v>4</v>
       </c>
       <c r="F196" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G196" s="6">
-        <v>1260</v>
+        <v>500</v>
       </c>
       <c r="H196" s="4"/>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" s="2">
-        <v>4010013597</v>
+        <v>4010013574</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="C197" s="5">
-        <v>46525</v>
+        <v>46545</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="E197" s="3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F197" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G197" s="6">
-        <v>620</v>
+        <v>660</v>
       </c>
       <c r="H197" s="4"/>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" s="2">
-        <v>4010013368</v>
+        <v>4010013588</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>32</v>
+        <v>102</v>
       </c>
       <c r="C198" s="5">
-        <v>46533</v>
+        <v>46582</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>33</v>
+        <v>103</v>
       </c>
       <c r="E198" s="3" t="s">
         <v>4</v>
@@ -6530,22 +6508,22 @@
         <v>5</v>
       </c>
       <c r="G198" s="6">
-        <v>160</v>
+        <v>3000</v>
       </c>
       <c r="H198" s="4"/>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" s="2">
-        <v>4010013369</v>
+        <v>4010013479</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="C199" s="5">
-        <v>46429</v>
+        <v>46419</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="E199" s="3" t="s">
         <v>4</v>
@@ -6554,22 +6532,22 @@
         <v>5</v>
       </c>
       <c r="G199" s="6">
-        <v>340</v>
+        <v>200</v>
       </c>
       <c r="H199" s="4"/>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" s="2">
-        <v>4010013369</v>
+        <v>4010013479</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="C200" s="5">
-        <v>46533</v>
+        <v>46594</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="E200" s="3" t="s">
         <v>4</v>
@@ -6578,162 +6556,164 @@
         <v>5</v>
       </c>
       <c r="G200" s="6">
-        <v>80</v>
+        <v>400</v>
       </c>
       <c r="H200" s="4"/>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" s="2">
-        <v>4010013399</v>
+        <v>4010013479</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="C201" s="5">
-        <v>46532</v>
+        <v>46536</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="E201" s="3" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F201" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G201" s="6">
-        <v>1310</v>
+        <v>320</v>
       </c>
       <c r="H201" s="4"/>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202" s="2">
-        <v>6010000203</v>
+        <v>4010013700</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>386</v>
+        <v>151</v>
       </c>
       <c r="C202" s="5">
-        <v>46606</v>
+        <v>46446</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>387</v>
+        <v>152</v>
       </c>
       <c r="E202" s="3" t="s">
-        <v>383</v>
+        <v>4</v>
       </c>
       <c r="F202" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G202" s="6">
-        <v>460</v>
+        <v>560</v>
       </c>
       <c r="H202" s="4"/>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203" s="2">
-        <v>4010013592</v>
+        <v>4010013700</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>105</v>
+        <v>151</v>
       </c>
       <c r="C203" s="5">
-        <v>46514</v>
+        <v>46533</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>106</v>
+        <v>153</v>
       </c>
       <c r="E203" s="3" t="s">
-        <v>107</v>
+        <v>4</v>
       </c>
       <c r="F203" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G203" s="6">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="H203" s="4"/>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204" s="2">
-        <v>4010014926</v>
+        <v>4010013701</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="C204" s="5">
-        <v>46768</v>
+        <v>46589</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="E204" s="3" t="s">
-        <v>162</v>
+        <v>4</v>
       </c>
       <c r="F204" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G204" s="6">
-        <v>780</v>
+        <v>1160</v>
       </c>
       <c r="H204" s="4"/>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205" s="2">
-        <v>7050000020</v>
+        <v>4010013657</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>438</v>
-      </c>
-      <c r="C205" s="5"/>
+        <v>122</v>
+      </c>
+      <c r="C205" s="5">
+        <v>46513</v>
+      </c>
       <c r="D205" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E205" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F205" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G205" s="6">
+        <v>800</v>
+      </c>
+      <c r="H205" s="4"/>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A206" s="9">
+        <v>4010013657</v>
+      </c>
+      <c r="B206" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="C206" s="11"/>
+      <c r="D206" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E205" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F205" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G205" s="6">
-        <v>70</v>
-      </c>
-      <c r="H205" s="4"/>
-    </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A206" s="2">
-        <v>7050000020</v>
-      </c>
-      <c r="B206" s="3" t="s">
-        <v>438</v>
-      </c>
-      <c r="C206" s="5"/>
-      <c r="D206" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E206" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F206" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G206" s="6">
-        <v>30</v>
-      </c>
-      <c r="H206" s="4"/>
+      <c r="E206" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F206" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G206" s="12"/>
+      <c r="H206" s="13">
+        <v>160</v>
+      </c>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A207" s="2">
-        <v>4010013659</v>
+        <v>4010013658</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C207" s="5">
-        <v>46526</v>
+        <v>46563</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E207" s="3" t="s">
         <v>8</v>
@@ -6742,70 +6722,70 @@
         <v>5</v>
       </c>
       <c r="G207" s="6">
-        <v>1390</v>
+        <v>70</v>
       </c>
       <c r="H207" s="4"/>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208" s="2">
-        <v>4010013273</v>
+        <v>4010013658</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>28</v>
+        <v>124</v>
       </c>
       <c r="C208" s="5">
-        <v>46444</v>
+        <v>46587</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>29</v>
+        <v>126</v>
       </c>
       <c r="E208" s="3" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F208" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G208" s="6">
-        <v>710</v>
+        <v>1200</v>
       </c>
       <c r="H208" s="4"/>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" s="2">
-        <v>4010013273</v>
+        <v>4010013548</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="C209" s="5">
-        <v>46444</v>
+        <v>46469</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="E209" s="3" t="s">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="F209" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G209" s="6">
-        <v>80</v>
+        <v>830</v>
       </c>
       <c r="H209" s="4"/>
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210" s="2">
-        <v>4010013271</v>
+        <v>4010013480</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="C210" s="5">
-        <v>46402</v>
+        <v>46408</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E210" s="3" t="s">
         <v>8</v>
@@ -6814,22 +6794,22 @@
         <v>5</v>
       </c>
       <c r="G210" s="6">
-        <v>300</v>
+        <v>1230</v>
       </c>
       <c r="H210" s="4"/>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211" s="2">
-        <v>4010013272</v>
+        <v>4010013477</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="C211" s="5">
-        <v>46523</v>
+        <v>46574</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="E211" s="3" t="s">
         <v>8</v>
@@ -6838,204 +6818,966 @@
         <v>5</v>
       </c>
       <c r="G211" s="6">
-        <v>1140</v>
+        <v>780</v>
       </c>
       <c r="H211" s="4"/>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212" s="2">
-        <v>4010013272</v>
+        <v>6010000131</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>25</v>
+        <v>281</v>
       </c>
       <c r="C212" s="5">
-        <v>46594</v>
+        <v>46784</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>27</v>
+        <v>282</v>
       </c>
       <c r="E212" s="3" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F212" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G212" s="6">
-        <v>360</v>
+        <v>2060</v>
       </c>
       <c r="H212" s="4"/>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213" s="2">
-        <v>4010013663</v>
+        <v>4010013699</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="C213" s="5">
-        <v>46612</v>
+        <v>46438</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="E213" s="3" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F213" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G213" s="6">
-        <v>1200</v>
+        <v>350</v>
       </c>
       <c r="H213" s="4"/>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214" s="2">
-        <v>4010013663</v>
+        <v>6010000089</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>134</v>
+        <v>222</v>
       </c>
       <c r="C214" s="5">
-        <v>46514</v>
+        <v>46871</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>136</v>
+        <v>223</v>
       </c>
       <c r="E214" s="3" t="s">
-        <v>8</v>
+        <v>224</v>
       </c>
       <c r="F214" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G214" s="6">
-        <v>200</v>
+        <v>2300</v>
       </c>
       <c r="H214" s="4"/>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A215" s="2">
-        <v>6010000093</v>
+        <v>6010000089</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C215" s="5">
-        <v>46504</v>
+        <v>46424</v>
       </c>
       <c r="D215" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E215" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="F215" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G215" s="6">
-        <v>15000</v>
+        <v>2360</v>
       </c>
       <c r="H215" s="4"/>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A216" s="2">
-        <v>6010000093</v>
+        <v>6010000132</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>226</v>
+        <v>283</v>
       </c>
       <c r="C216" s="5">
-        <v>46484</v>
+        <v>46614</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>229</v>
+        <v>2</v>
       </c>
       <c r="E216" s="3" t="s">
-        <v>228</v>
+        <v>30</v>
       </c>
       <c r="F216" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G216" s="6">
+        <v>2860</v>
+      </c>
+      <c r="H216" s="4"/>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A217" s="2">
+        <v>6010000146</v>
+      </c>
+      <c r="B217" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C217" s="5">
+        <v>46746</v>
+      </c>
+      <c r="D217" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="E217" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="F217" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G216" s="6">
-        <v>16000</v>
-      </c>
-      <c r="H216" s="4"/>
-    </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A217" s="8">
-        <v>6010000093</v>
-      </c>
-      <c r="B217" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="C217" s="10"/>
-      <c r="D217" s="9" t="s">
+      <c r="G217" s="6">
+        <v>480</v>
+      </c>
+      <c r="H217" s="4"/>
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A218" s="9">
+        <v>6010000146</v>
+      </c>
+      <c r="B218" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="C218" s="11"/>
+      <c r="D218" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E217" s="9" t="s">
-        <v>228</v>
-      </c>
-      <c r="F217" s="9" t="s">
+      <c r="E218" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="F218" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="G217" s="11"/>
-      <c r="H217" s="12">
-        <v>18000</v>
-      </c>
-    </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A218" s="2">
-        <v>6010000161</v>
-      </c>
-      <c r="B218" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="C218" s="5">
-        <v>47087</v>
-      </c>
-      <c r="D218" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="E218" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="F218" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G218" s="6">
-        <v>696</v>
-      </c>
-      <c r="H218" s="4"/>
+      <c r="G218" s="12"/>
+      <c r="H218" s="13">
+        <v>480</v>
+      </c>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" s="2">
-        <v>6010000162</v>
+        <v>6010000090</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>335</v>
+        <v>226</v>
       </c>
       <c r="C219" s="5">
-        <v>47087</v>
+        <v>46482</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>336</v>
+        <v>227</v>
       </c>
       <c r="E219" s="3" t="s">
-        <v>337</v>
+        <v>176</v>
       </c>
       <c r="F219" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G219" s="6">
+        <v>4450</v>
+      </c>
+      <c r="H219" s="4"/>
+    </row>
+    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A220" s="2">
+        <v>6010000199</v>
+      </c>
+      <c r="B220" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="C220" s="5">
+        <v>46556</v>
+      </c>
+      <c r="D220" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="E220" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F220" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G220" s="6">
+        <v>1680</v>
+      </c>
+      <c r="H220" s="4"/>
+    </row>
+    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A221" s="2">
+        <v>6010000133</v>
+      </c>
+      <c r="B221" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="C221" s="5">
+        <v>46388</v>
+      </c>
+      <c r="D221" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="E221" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F221" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G221" s="6">
+        <v>1200</v>
+      </c>
+      <c r="H221" s="4"/>
+    </row>
+    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A222" s="2">
+        <v>6010000134</v>
+      </c>
+      <c r="B222" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="C222" s="5">
+        <v>46488</v>
+      </c>
+      <c r="D222" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="E222" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F222" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G222" s="6">
+        <v>1180</v>
+      </c>
+      <c r="H222" s="4"/>
+    </row>
+    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A223" s="2">
+        <v>6010000135</v>
+      </c>
+      <c r="B223" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C223" s="5">
+        <v>46388</v>
+      </c>
+      <c r="D223" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="E223" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F223" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G223" s="6">
+        <v>1560</v>
+      </c>
+      <c r="H223" s="4"/>
+    </row>
+    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A224" s="2">
+        <v>6010000136</v>
+      </c>
+      <c r="B224" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="C224" s="5">
+        <v>46496</v>
+      </c>
+      <c r="D224" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="E224" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F224" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G224" s="6">
+        <v>730</v>
+      </c>
+      <c r="H224" s="4"/>
+    </row>
+    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A225" s="2">
+        <v>6010000137</v>
+      </c>
+      <c r="B225" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="C225" s="5">
+        <v>46496</v>
+      </c>
+      <c r="D225" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="E225" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F225" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G225" s="6">
+        <v>570</v>
+      </c>
+      <c r="H225" s="4"/>
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A226" s="2">
+        <v>4010013269</v>
+      </c>
+      <c r="B226" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C226" s="5">
+        <v>46558</v>
+      </c>
+      <c r="D226" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E226" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F226" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G226" s="6">
+        <v>900</v>
+      </c>
+      <c r="H226" s="4"/>
+    </row>
+    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A227" s="2">
+        <v>6010000177</v>
+      </c>
+      <c r="B227" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="C227" s="5">
+        <v>46971</v>
+      </c>
+      <c r="D227" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="E227" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="F227" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G227" s="6">
+        <v>2980</v>
+      </c>
+      <c r="H227" s="4"/>
+    </row>
+    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A228" s="2">
+        <v>6010000178</v>
+      </c>
+      <c r="B228" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="C228" s="5">
+        <v>47087</v>
+      </c>
+      <c r="D228" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="E228" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="F228" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G228" s="6">
+        <v>1260</v>
+      </c>
+      <c r="H228" s="4"/>
+    </row>
+    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A229" s="2">
+        <v>4010013597</v>
+      </c>
+      <c r="B229" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C229" s="5">
+        <v>46525</v>
+      </c>
+      <c r="D229" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E229" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F229" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G229" s="6">
+        <v>620</v>
+      </c>
+      <c r="H229" s="4"/>
+    </row>
+    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A230" s="2">
+        <v>4010013368</v>
+      </c>
+      <c r="B230" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C230" s="5">
+        <v>46533</v>
+      </c>
+      <c r="D230" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E230" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F230" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G230" s="6">
+        <v>160</v>
+      </c>
+      <c r="H230" s="4"/>
+    </row>
+    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A231" s="2">
+        <v>4010013369</v>
+      </c>
+      <c r="B231" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C231" s="5">
+        <v>46429</v>
+      </c>
+      <c r="D231" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E231" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F231" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G231" s="6">
+        <v>340</v>
+      </c>
+      <c r="H231" s="4"/>
+    </row>
+    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A232" s="2">
+        <v>4010013369</v>
+      </c>
+      <c r="B232" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C232" s="5">
+        <v>46533</v>
+      </c>
+      <c r="D232" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E232" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F232" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G232" s="6">
+        <v>80</v>
+      </c>
+      <c r="H232" s="4"/>
+    </row>
+    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A233" s="2">
+        <v>4010013399</v>
+      </c>
+      <c r="B233" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C233" s="5">
+        <v>46532</v>
+      </c>
+      <c r="D233" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E233" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F233" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G233" s="6">
+        <v>1290</v>
+      </c>
+      <c r="H233" s="4"/>
+    </row>
+    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A234" s="2">
+        <v>6010000203</v>
+      </c>
+      <c r="B234" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="C234" s="5">
+        <v>46606</v>
+      </c>
+      <c r="D234" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="E234" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="F234" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G234" s="6">
+        <v>460</v>
+      </c>
+      <c r="H234" s="4"/>
+    </row>
+    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A235" s="2">
+        <v>4010013592</v>
+      </c>
+      <c r="B235" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C235" s="5">
+        <v>46514</v>
+      </c>
+      <c r="D235" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E235" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="F235" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G235" s="6">
+        <v>240</v>
+      </c>
+      <c r="H235" s="4"/>
+    </row>
+    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A236" s="2">
+        <v>4010014926</v>
+      </c>
+      <c r="B236" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C236" s="5">
+        <v>46768</v>
+      </c>
+      <c r="D236" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="E236" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="F236" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G236" s="6">
+        <v>780</v>
+      </c>
+      <c r="H236" s="4"/>
+    </row>
+    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A237" s="2">
+        <v>7050000020</v>
+      </c>
+      <c r="B237" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="C237" s="5"/>
+      <c r="D237" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E237" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F237" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G237" s="6">
+        <v>70</v>
+      </c>
+      <c r="H237" s="4"/>
+    </row>
+    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A238" s="2">
+        <v>7050000020</v>
+      </c>
+      <c r="B238" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="C238" s="5"/>
+      <c r="D238" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E238" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F238" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G238" s="6">
+        <v>30</v>
+      </c>
+      <c r="H238" s="4"/>
+    </row>
+    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A239" s="2">
+        <v>4010013659</v>
+      </c>
+      <c r="B239" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C239" s="5">
+        <v>46526</v>
+      </c>
+      <c r="D239" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E239" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F239" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G239" s="6">
+        <v>1370</v>
+      </c>
+      <c r="H239" s="4"/>
+    </row>
+    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A240" s="2">
+        <v>4010013273</v>
+      </c>
+      <c r="B240" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C240" s="5">
+        <v>46444</v>
+      </c>
+      <c r="D240" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E240" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F240" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G240" s="6">
+        <v>710</v>
+      </c>
+      <c r="H240" s="4"/>
+    </row>
+    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A241" s="2">
+        <v>4010013273</v>
+      </c>
+      <c r="B241" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C241" s="5">
+        <v>46444</v>
+      </c>
+      <c r="D241" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E241" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F241" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G241" s="6">
+        <v>70</v>
+      </c>
+      <c r="H241" s="4"/>
+    </row>
+    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A242" s="2">
+        <v>4010013271</v>
+      </c>
+      <c r="B242" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C242" s="5">
+        <v>46402</v>
+      </c>
+      <c r="D242" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E242" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F242" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G242" s="6">
+        <v>300</v>
+      </c>
+      <c r="H242" s="4"/>
+    </row>
+    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A243" s="2">
+        <v>4010013272</v>
+      </c>
+      <c r="B243" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C243" s="5">
+        <v>46594</v>
+      </c>
+      <c r="D243" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E243" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F243" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G243" s="6">
+        <v>360</v>
+      </c>
+      <c r="H243" s="4"/>
+    </row>
+    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A244" s="2">
+        <v>4010013272</v>
+      </c>
+      <c r="B244" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C244" s="5">
+        <v>46523</v>
+      </c>
+      <c r="D244" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E244" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F244" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G244" s="6">
+        <v>1100</v>
+      </c>
+      <c r="H244" s="4"/>
+    </row>
+    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A245" s="2">
+        <v>4010013663</v>
+      </c>
+      <c r="B245" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C245" s="5">
+        <v>46612</v>
+      </c>
+      <c r="D245" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E245" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F245" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G245" s="6">
+        <v>1200</v>
+      </c>
+      <c r="H245" s="4"/>
+    </row>
+    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A246" s="2">
+        <v>4010013663</v>
+      </c>
+      <c r="B246" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C246" s="5">
+        <v>46514</v>
+      </c>
+      <c r="D246" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E246" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F246" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G246" s="6">
+        <v>200</v>
+      </c>
+      <c r="H246" s="4"/>
+    </row>
+    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A247" s="2">
+        <v>6010000093</v>
+      </c>
+      <c r="B247" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C247" s="5">
+        <v>46504</v>
+      </c>
+      <c r="D247" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="E247" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="F247" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G247" s="6">
+        <v>15000</v>
+      </c>
+      <c r="H247" s="4"/>
+    </row>
+    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A248" s="9">
+        <v>6010000093</v>
+      </c>
+      <c r="B248" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="C248" s="11"/>
+      <c r="D248" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E248" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="F248" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="G248" s="12"/>
+      <c r="H248" s="13">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A249" s="2">
+        <v>6010000093</v>
+      </c>
+      <c r="B249" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C249" s="5">
+        <v>46484</v>
+      </c>
+      <c r="D249" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="E249" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="F249" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G249" s="6">
+        <v>16000</v>
+      </c>
+      <c r="H249" s="4"/>
+    </row>
+    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A250" s="2">
+        <v>6010000161</v>
+      </c>
+      <c r="B250" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="C250" s="5">
+        <v>47087</v>
+      </c>
+      <c r="D250" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="E250" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="F250" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G250" s="6">
+        <v>696</v>
+      </c>
+      <c r="H250" s="4"/>
+    </row>
+    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A251" s="2">
+        <v>6010000162</v>
+      </c>
+      <c r="B251" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="C251" s="5">
+        <v>47087</v>
+      </c>
+      <c r="D251" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="E251" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="F251" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G251" s="6">
         <v>1164</v>
       </c>
-      <c r="H219" s="4"/>
+      <c r="H251" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H219" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H219">
-      <sortCondition ref="B1:B219"/>
+  <autoFilter ref="A1:H251" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H251">
+      <sortCondition ref="B1:B251"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="0" type="noConversion"/>

--- a/KSTOCK.xlsx
+++ b/KSTOCK.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c2e6f8dd72a68295/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="47" documentId="11_A3A2BE43C4094E9AB632FCC5BE959E8329D20925" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E845CD26-0456-4C13-924A-BC59C2E30ED7}"/>
+  <xr:revisionPtr revIDLastSave="47" documentId="11_88E2BF43C4094E9AB632FCC5BE959E8329D2792D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AEDE99E0-0040-4E26-8C13-8AF1017A89EF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1378,13 +1378,13 @@
     <t>Expiry</t>
   </si>
   <si>
-    <t xml:space="preserve"> Batch No.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Transit Qty</t>
+    <t>Batch No.</t>
   </si>
   <si>
     <t xml:space="preserve"> Unrestricted Qty</t>
+  </si>
+  <si>
+    <t>Transit Qty</t>
   </si>
 </sst>
 </file>
@@ -1415,13 +1415,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1475,25 +1475,25 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1831,20 +1831,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H251"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="13.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.21875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="36.77734375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14.109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9.5546875" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="13.44140625" style="1"/>
+    <col min="2" max="2" width="31.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.77734375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.33203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.44140625" style="1"/>
+    <col min="8" max="8" width="11.88671875" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="13.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>446</v>
       </c>
@@ -1857,17 +1857,17 @@
       <c r="D1" s="7" t="s">
         <v>451</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="7" t="s">
         <v>448</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="7" t="s">
         <v>449</v>
       </c>
       <c r="G1" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="H1" s="7" t="s">
         <v>453</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -2946,7 +2946,7 @@
         <v>5</v>
       </c>
       <c r="G47" s="6">
-        <v>240</v>
+        <v>190</v>
       </c>
       <c r="H47" s="4"/>
     </row>
@@ -3940,7 +3940,7 @@
         <v>5</v>
       </c>
       <c r="G89" s="6">
-        <v>140</v>
+        <v>90</v>
       </c>
       <c r="H89" s="4"/>
     </row>
@@ -4344,7 +4344,7 @@
         <v>5</v>
       </c>
       <c r="G106" s="6">
-        <v>560</v>
+        <v>530</v>
       </c>
       <c r="H106" s="4"/>
     </row>

--- a/KSTOCK.xlsx
+++ b/KSTOCK.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c2e6f8dd72a68295/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="47" documentId="11_88E2BF43C4094E9AB632FCC5BE959E8329D2792D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AEDE99E0-0040-4E26-8C13-8AF1017A89EF}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="11_C6DA9F49C4094E9AB632FCC5BEBB5E003CBCC164" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{635629A2-7C01-442E-953D-32588DE7AF46}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$251</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$249</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="457">
   <si>
     <t>ROSUSEP-20</t>
   </si>
@@ -55,12 +55,12 @@
     <t>ATROLIA CV 20/75</t>
   </si>
   <si>
+    <t>10X3X10</t>
+  </si>
+  <si>
     <t>25S3GCA110</t>
   </si>
   <si>
-    <t>10X3X10</t>
-  </si>
-  <si>
     <t>25S3GCA131</t>
   </si>
   <si>
@@ -103,12 +103,12 @@
     <t>Vildapharm-Met 500</t>
   </si>
   <si>
+    <t>25S3GTA610</t>
+  </si>
+  <si>
     <t>25S3GTA972</t>
   </si>
   <si>
-    <t>25S3GTA610</t>
-  </si>
-  <si>
     <t>VILDAPHARM-DP</t>
   </si>
   <si>
@@ -130,12 +130,12 @@
     <t>TENEJEET-M 500</t>
   </si>
   <si>
+    <t>25S3GTA657</t>
+  </si>
+  <si>
     <t>25S3GTA221</t>
   </si>
   <si>
-    <t>25S3GTA657</t>
-  </si>
-  <si>
     <t>CHYMOACTIVE-FORTE</t>
   </si>
   <si>
@@ -181,12 +181,12 @@
     <t>PROGISPHERE SR 200</t>
   </si>
   <si>
+    <t>25S2HTA612</t>
+  </si>
+  <si>
     <t>25S2HTA863</t>
   </si>
   <si>
-    <t>25S2HTA612</t>
-  </si>
-  <si>
     <t>PROGISPHERE SR 300</t>
   </si>
   <si>
@@ -214,12 +214,12 @@
     <t>ROSUSEP-ASP 20</t>
   </si>
   <si>
+    <t>25S3GCA138</t>
+  </si>
+  <si>
     <t>25S3GCA034</t>
   </si>
   <si>
-    <t>25S3GCA138</t>
-  </si>
-  <si>
     <t>25S3GCA105</t>
   </si>
   <si>
@@ -307,12 +307,12 @@
     <t>GLIMKAT-MET 1 (PR)</t>
   </si>
   <si>
+    <t>25S3GTA626</t>
+  </si>
+  <si>
     <t>25S3GTA625</t>
   </si>
   <si>
-    <t>25S3GTA626</t>
-  </si>
-  <si>
     <t>GLIMKAT-MET 2 (PR)</t>
   </si>
   <si>
@@ -400,9 +400,6 @@
     <t>SITAFREE-50</t>
   </si>
   <si>
-    <t>25S2GTB786</t>
-  </si>
-  <si>
     <t>25S2GTC059</t>
   </si>
   <si>
@@ -577,12 +574,12 @@
     <t>DECAHIT INJECTION</t>
   </si>
   <si>
+    <t>NL2722504</t>
+  </si>
+  <si>
     <t>96X2ML</t>
   </si>
   <si>
-    <t>NL2722504</t>
-  </si>
-  <si>
     <t>GENTAHIT INJ</t>
   </si>
   <si>
@@ -661,10 +658,13 @@
     <t>ONMOTRON INJ 2ML</t>
   </si>
   <si>
+    <t>NL2692503</t>
+  </si>
+  <si>
     <t>20X5X2ML</t>
   </si>
   <si>
-    <t>NL2692503</t>
+    <t>NL2692504</t>
   </si>
   <si>
     <t>PANTAHIT IV</t>
@@ -682,6 +682,9 @@
     <t>NL1442501</t>
   </si>
   <si>
+    <t>NL1442502</t>
+  </si>
+  <si>
     <t>REBEHIT IV</t>
   </si>
   <si>
@@ -712,15 +715,15 @@
     <t>VOLOPAIN INJ</t>
   </si>
   <si>
+    <t>NL2702507</t>
+  </si>
+  <si>
+    <t>20X5X3ML</t>
+  </si>
+  <si>
     <t>NL2702506</t>
   </si>
   <si>
-    <t>20X5X3ML</t>
-  </si>
-  <si>
-    <t>NL2702507</t>
-  </si>
-  <si>
     <t>ACECLOPHARM-MR TABLET</t>
   </si>
   <si>
@@ -751,6 +754,9 @@
     <t>CALWINIT-500 TABLET</t>
   </si>
   <si>
+    <t>DRQ01AAB</t>
+  </si>
+  <si>
     <t>CLAVMYCIN 625 DUO TABLET</t>
   </si>
   <si>
@@ -862,12 +868,12 @@
     <t>RIFIXIEM 550 TABLET</t>
   </si>
   <si>
+    <t>GE545002B</t>
+  </si>
+  <si>
     <t>GE545020</t>
   </si>
   <si>
-    <t>GE545002B</t>
-  </si>
-  <si>
     <t>SPASMOSAFE-MF TABLET</t>
   </si>
   <si>
@@ -1027,6 +1033,9 @@
     <t>CALWINIT K2-7 SOFTGEL CAPSULE 10S</t>
   </si>
   <si>
+    <t>36D260126B</t>
+  </si>
+  <si>
     <t>CALWINIT-D3 SOFTGEL CAPSULE</t>
   </si>
   <si>
@@ -1138,15 +1147,15 @@
     <t>Faropharm 200 Tablet</t>
   </si>
   <si>
+    <t>CBT25115D</t>
+  </si>
+  <si>
+    <t>CBT26001B</t>
+  </si>
+  <si>
     <t>CBT26025B</t>
   </si>
   <si>
-    <t>CBT26001B</t>
-  </si>
-  <si>
-    <t>CBT25115D</t>
-  </si>
-  <si>
     <t>EPODOX-200 DT Tablet</t>
   </si>
   <si>
@@ -1237,24 +1246,24 @@
     <t>CEFIXLIA-O 200 TABLET</t>
   </si>
   <si>
+    <t>CT25488B</t>
+  </si>
+  <si>
     <t>CT26007G</t>
   </si>
   <si>
-    <t>CT25488B</t>
-  </si>
-  <si>
     <t>MONTALIA-LC 60ML SYRUP</t>
   </si>
   <si>
+    <t>DL603008</t>
+  </si>
+  <si>
+    <t>60 ML</t>
+  </si>
+  <si>
     <t>DL602011A</t>
   </si>
   <si>
-    <t>60 ML</t>
-  </si>
-  <si>
-    <t>DL603008</t>
-  </si>
-  <si>
     <t>CLAVMYCIN 375 DUO TABLET (20x1x10)</t>
   </si>
   <si>
@@ -1264,21 +1273,21 @@
     <t>REBEHIT DSR CAPSULE</t>
   </si>
   <si>
+    <t>MC2510116</t>
+  </si>
+  <si>
     <t>MC2510117</t>
   </si>
   <si>
-    <t>MC2510116</t>
-  </si>
-  <si>
     <t>PANTAHIT DSR CAPSULE (20x10)</t>
   </si>
   <si>
+    <t>MC2509105A</t>
+  </si>
+  <si>
     <t>MC2509103</t>
   </si>
   <si>
-    <t>MC2509105A</t>
-  </si>
-  <si>
     <t>CLAVMYCIN 625 DUO TABLET (20x1x10)</t>
   </si>
   <si>
@@ -1291,12 +1300,12 @@
     <t>CEFIXLIA - 200 DT TABLET</t>
   </si>
   <si>
+    <t>CT25427</t>
+  </si>
+  <si>
     <t>CT26039A</t>
   </si>
   <si>
-    <t>CT25427</t>
-  </si>
-  <si>
     <t>FERRIFINE XT TABLET</t>
   </si>
   <si>
@@ -1378,7 +1387,7 @@
     <t>Expiry</t>
   </si>
   <si>
-    <t>Batch No.</t>
+    <t xml:space="preserve"> Batch No.</t>
   </si>
   <si>
     <t xml:space="preserve"> Unrestricted Qty</t>
@@ -1466,20 +1475,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1495,6 +1498,12 @@
     </xf>
     <xf numFmtId="3" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1830,104 +1839,104 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H251"/>
-  <sheetFormatPr defaultColWidth="13.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H249"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.44140625" style="1"/>
-    <col min="2" max="2" width="31.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.77734375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16.33203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5546875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.44140625" style="1"/>
-    <col min="8" max="8" width="11.88671875" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="13.44140625" style="1"/>
+    <col min="1" max="1" width="13.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="33.77734375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.88671875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="20" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
-        <v>446</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>447</v>
-      </c>
-      <c r="C1" s="7" t="s">
+      <c r="A1" s="12" t="s">
+        <v>449</v>
+      </c>
+      <c r="B1" s="12" t="s">
         <v>450</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="C1" s="12" t="s">
+        <v>453</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>454</v>
+      </c>
+      <c r="E1" s="12" t="s">
         <v>451</v>
       </c>
-      <c r="E1" s="7" t="s">
-        <v>448</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>449</v>
-      </c>
-      <c r="G1" s="8" t="s">
+      <c r="F1" s="12" t="s">
         <v>452</v>
       </c>
-      <c r="H1" s="7" t="s">
-        <v>453</v>
+      <c r="G1" s="13" t="s">
+        <v>455</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
+      <c r="A2" s="7">
         <v>6010000095</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="C2" s="5">
+      <c r="B2" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="C2" s="9"/>
+      <c r="D2" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="10"/>
+      <c r="H2" s="11">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>6010000095</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="C3" s="4">
         <v>46568</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="E2" s="3" t="s">
+      <c r="D3" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="6">
+      <c r="F3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="6">
         <v>3680</v>
       </c>
-      <c r="H2" s="4"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="9">
-        <v>6010000095</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>232</v>
-      </c>
-      <c r="C3" s="11"/>
-      <c r="D3" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3" s="12"/>
-      <c r="H3" s="13">
-        <v>3600</v>
-      </c>
+      <c r="H3" s="5"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>6010000095</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="C4" s="5">
+        <v>233</v>
+      </c>
+      <c r="C4" s="4">
         <v>46559</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>22</v>
@@ -1938,44 +1947,44 @@
       <c r="G4" s="6">
         <v>1200</v>
       </c>
-      <c r="H4" s="4"/>
+      <c r="H4" s="5"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>6010000138</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="C5" s="5">
+        <v>296</v>
+      </c>
+      <c r="C5" s="4">
         <v>46746</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G5" s="6">
-        <v>623</v>
-      </c>
-      <c r="H5" s="4"/>
+        <v>603</v>
+      </c>
+      <c r="H5" s="5"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>4010015107</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C6" s="4">
+        <v>46752</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>163</v>
-      </c>
-      <c r="C6" s="5">
-        <v>46752</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>164</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>121</v>
@@ -1986,7 +1995,7 @@
       <c r="G6" s="6">
         <v>1040</v>
       </c>
-      <c r="H6" s="4"/>
+      <c r="H6" s="5"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
@@ -1995,7 +2004,7 @@
       <c r="B7" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="4">
         <v>46548</v>
       </c>
       <c r="D7" s="3" t="s">
@@ -2010,23 +2019,23 @@
       <c r="G7" s="6">
         <v>170</v>
       </c>
-      <c r="H7" s="4"/>
+      <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>6010000097</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="C8" s="5">
+        <v>236</v>
+      </c>
+      <c r="C8" s="4">
         <v>46751</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>5</v>
@@ -2034,23 +2043,23 @@
       <c r="G8" s="6">
         <v>160</v>
       </c>
-      <c r="H8" s="4"/>
+      <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>6010000097</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="C9" s="5">
+        <v>236</v>
+      </c>
+      <c r="C9" s="4">
         <v>46556</v>
       </c>
       <c r="D9" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>238</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>237</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>5</v>
@@ -2058,20 +2067,20 @@
       <c r="G9" s="6">
         <v>300</v>
       </c>
-      <c r="H9" s="4"/>
+      <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>6010000098</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="C10" s="5">
+        <v>240</v>
+      </c>
+      <c r="C10" s="4">
         <v>46539</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>87</v>
@@ -2082,20 +2091,20 @@
       <c r="G10" s="6">
         <v>1340</v>
       </c>
-      <c r="H10" s="4"/>
+      <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>6010000195</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="C11" s="5">
+        <v>380</v>
+      </c>
+      <c r="C11" s="4">
         <v>46549</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>22</v>
@@ -2106,7 +2115,7 @@
       <c r="G11" s="6">
         <v>420</v>
       </c>
-      <c r="H11" s="4"/>
+      <c r="H11" s="5"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
@@ -2115,7 +2124,7 @@
       <c r="B12" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="4">
         <v>46568</v>
       </c>
       <c r="D12" s="3" t="s">
@@ -2130,75 +2139,75 @@
       <c r="G12" s="6">
         <v>440</v>
       </c>
-      <c r="H12" s="4"/>
+      <c r="H12" s="5"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="9">
+      <c r="A13" s="7">
         <v>4010013259</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="10" t="s">
+      <c r="C13" s="9"/>
+      <c r="D13" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F13" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G13" s="12"/>
-      <c r="H13" s="13">
+      <c r="F13" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G13" s="10"/>
+      <c r="H13" s="11">
         <v>240</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
+      <c r="A14" s="7">
         <v>4010013260</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="9"/>
+      <c r="D14" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="10"/>
+      <c r="H14" s="11">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>4010013260</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="4">
         <v>46568</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G14" s="6">
+      <c r="F15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G15" s="6">
         <v>510</v>
       </c>
-      <c r="H14" s="4"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="9">
-        <v>4010013260</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="11"/>
-      <c r="D15" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G15" s="12"/>
-      <c r="H15" s="13">
-        <v>20</v>
-      </c>
+      <c r="H15" s="5"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
@@ -2207,14 +2216,14 @@
       <c r="B16" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C16" s="4">
         <v>46589</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>5</v>
@@ -2222,20 +2231,20 @@
       <c r="G16" s="6">
         <v>1200</v>
       </c>
-      <c r="H16" s="4"/>
+      <c r="H16" s="5"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>4010013692</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C17" s="4">
+        <v>46549</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>142</v>
-      </c>
-      <c r="C17" s="5">
-        <v>46549</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>143</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>8</v>
@@ -2246,20 +2255,20 @@
       <c r="G17" s="6">
         <v>880</v>
       </c>
-      <c r="H17" s="4"/>
+      <c r="H17" s="5"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>4010013693</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C18" s="4">
+        <v>46549</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>144</v>
-      </c>
-      <c r="C18" s="5">
-        <v>46549</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>145</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>8</v>
@@ -2270,20 +2279,20 @@
       <c r="G18" s="6">
         <v>460</v>
       </c>
-      <c r="H18" s="4"/>
+      <c r="H18" s="5"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>4010013693</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="C19" s="5">
+        <v>143</v>
+      </c>
+      <c r="C19" s="4">
         <v>46587</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>8</v>
@@ -2294,7 +2303,7 @@
       <c r="G19" s="6">
         <v>420</v>
       </c>
-      <c r="H19" s="4"/>
+      <c r="H19" s="5"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
@@ -2303,7 +2312,7 @@
       <c r="B20" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C20" s="5">
+      <c r="C20" s="4">
         <v>46640</v>
       </c>
       <c r="D20" s="3" t="s">
@@ -2316,9 +2325,9 @@
         <v>5</v>
       </c>
       <c r="G20" s="6">
-        <v>770</v>
-      </c>
-      <c r="H20" s="4"/>
+        <v>670</v>
+      </c>
+      <c r="H20" s="5"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
@@ -2327,7 +2336,7 @@
       <c r="B21" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C21" s="5">
+      <c r="C21" s="4">
         <v>46666</v>
       </c>
       <c r="D21" s="3" t="s">
@@ -2340,9 +2349,9 @@
         <v>5</v>
       </c>
       <c r="G21" s="6">
-        <v>500</v>
-      </c>
-      <c r="H21" s="4"/>
+        <v>400</v>
+      </c>
+      <c r="H21" s="5"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
@@ -2351,7 +2360,7 @@
       <c r="B22" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C22" s="5">
+      <c r="C22" s="4">
         <v>46598</v>
       </c>
       <c r="D22" s="3" t="s">
@@ -2366,20 +2375,20 @@
       <c r="G22" s="6">
         <v>840</v>
       </c>
-      <c r="H22" s="4"/>
+      <c r="H22" s="5"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>4010013660</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C23" s="4">
+        <v>46518</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="C23" s="5">
-        <v>46518</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>130</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>22</v>
@@ -2390,77 +2399,77 @@
       <c r="G23" s="6">
         <v>340</v>
       </c>
-      <c r="H23" s="4"/>
+      <c r="H23" s="5"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="2">
+      <c r="A24" s="7">
         <v>4010013694</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="C24" s="9"/>
+      <c r="D24" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G24" s="10"/>
+      <c r="H24" s="11">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
+        <v>4010013694</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C25" s="4">
+        <v>46536</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="C24" s="5">
-        <v>46536</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="E24" s="3" t="s">
+      <c r="E25" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G24" s="6">
+      <c r="F25" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G25" s="6">
         <v>750</v>
       </c>
-      <c r="H24" s="4"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="9">
-        <v>4010013694</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="C25" s="11"/>
-      <c r="D25" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G25" s="12"/>
-      <c r="H25" s="13">
-        <v>240</v>
-      </c>
+      <c r="H25" s="5"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>6010000065</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C26" s="4">
+        <v>46447</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="C26" s="5">
-        <v>46447</v>
-      </c>
-      <c r="D26" s="3" t="s">
+      <c r="E26" s="3" t="s">
         <v>166</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>167</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G26" s="6">
-        <v>1900</v>
-      </c>
-      <c r="H26" s="4"/>
+        <v>1800</v>
+      </c>
+      <c r="H26" s="5"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
@@ -2469,7 +2478,7 @@
       <c r="B27" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C27" s="5">
+      <c r="C27" s="4">
         <v>46541</v>
       </c>
       <c r="D27" s="3" t="s">
@@ -2482,47 +2491,47 @@
         <v>5</v>
       </c>
       <c r="G27" s="6">
-        <v>3580</v>
-      </c>
-      <c r="H27" s="4"/>
+        <v>3480</v>
+      </c>
+      <c r="H27" s="5"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>6010000066</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C28" s="4">
+        <v>46575</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C28" s="5">
-        <v>46575</v>
-      </c>
-      <c r="D28" s="3" t="s">
+      <c r="E28" s="3" t="s">
         <v>169</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>170</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G28" s="6">
-        <v>200</v>
-      </c>
-      <c r="H28" s="4"/>
+        <v>100</v>
+      </c>
+      <c r="H28" s="5"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>7050000018</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>443</v>
-      </c>
-      <c r="C29" s="5"/>
+        <v>446</v>
+      </c>
+      <c r="C29" s="4"/>
       <c r="D29" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>3</v>
@@ -2530,21 +2539,21 @@
       <c r="G29" s="6">
         <v>100</v>
       </c>
-      <c r="H29" s="4"/>
+      <c r="H29" s="5"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>7050000016</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>441</v>
-      </c>
-      <c r="C30" s="5"/>
+        <v>444</v>
+      </c>
+      <c r="C30" s="4"/>
       <c r="D30" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>3</v>
@@ -2552,21 +2561,21 @@
       <c r="G30" s="6">
         <v>100</v>
       </c>
-      <c r="H30" s="4"/>
+      <c r="H30" s="5"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>7050000015</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>440</v>
-      </c>
-      <c r="C31" s="5"/>
+        <v>443</v>
+      </c>
+      <c r="C31" s="4"/>
       <c r="D31" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>3</v>
@@ -2574,21 +2583,21 @@
       <c r="G31" s="6">
         <v>100</v>
       </c>
-      <c r="H31" s="4"/>
+      <c r="H31" s="5"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>7050000014</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>438</v>
-      </c>
-      <c r="C32" s="5"/>
+        <v>441</v>
+      </c>
+      <c r="C32" s="4"/>
       <c r="D32" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>3</v>
@@ -2596,21 +2605,21 @@
       <c r="G32" s="6">
         <v>100</v>
       </c>
-      <c r="H32" s="4"/>
+      <c r="H32" s="5"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>7050000017</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="C33" s="5"/>
+        <v>445</v>
+      </c>
+      <c r="C33" s="4"/>
       <c r="D33" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>3</v>
@@ -2618,7 +2627,7 @@
       <c r="G33" s="6">
         <v>100</v>
       </c>
-      <c r="H33" s="4"/>
+      <c r="H33" s="5"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
@@ -2627,7 +2636,7 @@
       <c r="B34" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C34" s="5">
+      <c r="C34" s="4">
         <v>46568</v>
       </c>
       <c r="D34" s="3" t="s">
@@ -2642,7 +2651,7 @@
       <c r="G34" s="6">
         <v>1330</v>
       </c>
-      <c r="H34" s="4"/>
+      <c r="H34" s="5"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
@@ -2651,7 +2660,7 @@
       <c r="B35" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C35" s="5">
+      <c r="C35" s="4">
         <v>46551</v>
       </c>
       <c r="D35" s="3" t="s">
@@ -2666,44 +2675,44 @@
       <c r="G35" s="6">
         <v>230</v>
       </c>
-      <c r="H35" s="4"/>
+      <c r="H35" s="5"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>6010000154</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="C36" s="5">
+        <v>326</v>
+      </c>
+      <c r="C36" s="4">
         <v>47007</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G36" s="6">
-        <v>814</v>
-      </c>
-      <c r="H36" s="4"/>
+        <v>799</v>
+      </c>
+      <c r="H36" s="5"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>6010000158</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="C37" s="5">
+        <v>333</v>
+      </c>
+      <c r="C37" s="4">
         <v>46752</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>8</v>
@@ -2714,23 +2723,23 @@
       <c r="G37" s="6">
         <v>440</v>
       </c>
-      <c r="H37" s="4"/>
+      <c r="H37" s="5"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>6010000068</v>
       </c>
       <c r="B38" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C38" s="4">
+        <v>46495</v>
+      </c>
+      <c r="D38" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C38" s="5">
-        <v>46495</v>
-      </c>
-      <c r="D38" s="3" t="s">
+      <c r="E38" s="3" t="s">
         <v>172</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>173</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>3</v>
@@ -2738,112 +2747,114 @@
       <c r="G38" s="6">
         <v>1500</v>
       </c>
-      <c r="H38" s="4"/>
+      <c r="H38" s="5"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="9">
+      <c r="A39" s="2">
         <v>6010000159</v>
       </c>
-      <c r="B39" s="10" t="s">
-        <v>333</v>
-      </c>
-      <c r="C39" s="11"/>
-      <c r="D39" s="10" t="s">
+      <c r="B39" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="C39" s="4">
+        <v>46780</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G39" s="6">
+        <v>400</v>
+      </c>
+      <c r="H39" s="5"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="7">
+        <v>6010000099</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="C40" s="9"/>
+      <c r="D40" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E39" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F39" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G39" s="12"/>
-      <c r="H39" s="13">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="9">
-        <v>6010000099</v>
-      </c>
-      <c r="B40" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="C40" s="11"/>
-      <c r="D40" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="E40" s="10" t="s">
+      <c r="E40" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="F40" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G40" s="12"/>
-      <c r="H40" s="13">
-        <v>6000</v>
+      <c r="F40" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G40" s="10"/>
+      <c r="H40" s="11">
+        <v>1200</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
-        <v>6010000160</v>
+        <v>6010000099</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="C41" s="5">
-        <v>46780</v>
+        <v>242</v>
+      </c>
+      <c r="C41" s="4">
+        <v>46813</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>335</v>
+        <v>243</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>336</v>
+        <v>87</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G41" s="6">
-        <v>1200</v>
-      </c>
-      <c r="H41" s="4"/>
+        <v>4760</v>
+      </c>
+      <c r="H41" s="5"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
-        <v>6010000234</v>
+        <v>6010000160</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="C42" s="5">
-        <v>46726</v>
+        <v>337</v>
+      </c>
+      <c r="C42" s="4">
+        <v>46780</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>422</v>
+        <v>338</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>22</v>
+        <v>339</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G42" s="6">
-        <v>7920</v>
-      </c>
-      <c r="H42" s="4"/>
+        <v>900</v>
+      </c>
+      <c r="H42" s="5"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>6010000234</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="C43" s="5">
+        <v>424</v>
+      </c>
+      <c r="C43" s="4">
         <v>46661</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>22</v>
@@ -2854,90 +2865,90 @@
       <c r="G43" s="6">
         <v>280</v>
       </c>
-      <c r="H43" s="4"/>
+      <c r="H43" s="5"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
+        <v>6010000234</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="C44" s="4">
+        <v>46726</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="6">
+        <v>7920</v>
+      </c>
+      <c r="H44" s="5"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="7">
         <v>6010000239</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="C44" s="5">
-        <v>46507</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>427</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="F44" s="3" t="s">
+      <c r="B45" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="C45" s="9"/>
+      <c r="D45" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="F45" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G44" s="6">
-        <v>757</v>
-      </c>
-      <c r="H44" s="4"/>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="9">
-        <v>6010000239</v>
-      </c>
-      <c r="B45" s="10" t="s">
-        <v>426</v>
-      </c>
-      <c r="C45" s="11"/>
-      <c r="D45" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="E45" s="10" t="s">
-        <v>369</v>
-      </c>
-      <c r="F45" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="G45" s="12"/>
-      <c r="H45" s="13">
+      <c r="G45" s="10"/>
+      <c r="H45" s="11">
         <v>810</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
-        <v>6010000217</v>
+        <v>6010000239</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="C46" s="5">
-        <v>46751</v>
+        <v>429</v>
+      </c>
+      <c r="C46" s="4">
+        <v>46507</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>404</v>
+        <v>430</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>30</v>
+        <v>372</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G46" s="6">
-        <v>610</v>
-      </c>
-      <c r="H46" s="4"/>
+        <v>727</v>
+      </c>
+      <c r="H46" s="5"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>6010000217</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="C47" s="5">
+        <v>406</v>
+      </c>
+      <c r="C47" s="4">
         <v>46721</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>30</v>
@@ -2946,140 +2957,140 @@
         <v>5</v>
       </c>
       <c r="G47" s="6">
-        <v>190</v>
-      </c>
-      <c r="H47" s="4"/>
+        <v>50</v>
+      </c>
+      <c r="H47" s="5"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
-        <v>6010000070</v>
+        <v>6010000217</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="C48" s="5">
-        <v>46721</v>
+        <v>406</v>
+      </c>
+      <c r="C48" s="4">
+        <v>46751</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>175</v>
+        <v>408</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>176</v>
+        <v>30</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G48" s="6">
-        <v>765</v>
-      </c>
-      <c r="H48" s="4"/>
+        <v>610</v>
+      </c>
+      <c r="H48" s="5"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
-        <v>6010000071</v>
+        <v>6010000070</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C49" s="5">
-        <v>46797</v>
+        <v>173</v>
+      </c>
+      <c r="C49" s="4">
+        <v>46721</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G49" s="6">
+        <v>765</v>
+      </c>
+      <c r="H49" s="5"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="2">
+        <v>6010000071</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C50" s="4">
+        <v>46797</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G50" s="6">
         <v>3250</v>
       </c>
-      <c r="H49" s="4"/>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="9">
+      <c r="H50" s="5"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="7">
         <v>6010000071</v>
       </c>
-      <c r="B50" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="C50" s="11"/>
-      <c r="D50" s="10" t="s">
+      <c r="B51" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="C51" s="9"/>
+      <c r="D51" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E50" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="F50" s="10" t="s">
+      <c r="E51" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="F51" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G50" s="12"/>
-      <c r="H50" s="13">
+      <c r="G51" s="10"/>
+      <c r="H51" s="11">
         <v>400</v>
       </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="2">
-        <v>4010013389</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C51" s="5">
-        <v>46681</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G51" s="6">
-        <v>1090</v>
-      </c>
-      <c r="H51" s="4"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
-        <v>4010013266</v>
+        <v>4010013389</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C52" s="5">
-        <v>46575</v>
+        <v>37</v>
+      </c>
+      <c r="C52" s="4">
+        <v>46681</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G52" s="6">
-        <v>460</v>
-      </c>
-      <c r="H52" s="4"/>
+        <v>1070</v>
+      </c>
+      <c r="H52" s="5"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
-        <v>4010013267</v>
+        <v>4010013266</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C53" s="5">
-        <v>46598</v>
+        <v>16</v>
+      </c>
+      <c r="C53" s="4">
+        <v>46575</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>8</v>
@@ -3088,22 +3099,22 @@
         <v>5</v>
       </c>
       <c r="G53" s="6">
-        <v>640</v>
-      </c>
-      <c r="H53" s="4"/>
+        <v>440</v>
+      </c>
+      <c r="H53" s="5"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
-        <v>4010013553</v>
+        <v>4010013267</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C54" s="5">
-        <v>46575</v>
+        <v>18</v>
+      </c>
+      <c r="C54" s="4">
+        <v>46598</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>78</v>
+        <v>19</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>8</v>
@@ -3112,22 +3123,22 @@
         <v>5</v>
       </c>
       <c r="G54" s="6">
-        <v>860</v>
-      </c>
-      <c r="H54" s="4"/>
+        <v>640</v>
+      </c>
+      <c r="H54" s="5"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
-        <v>4010013397</v>
+        <v>4010013553</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C55" s="5">
-        <v>46545</v>
+        <v>77</v>
+      </c>
+      <c r="C55" s="4">
+        <v>46575</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>8</v>
@@ -3136,210 +3147,210 @@
         <v>5</v>
       </c>
       <c r="G55" s="6">
-        <v>880</v>
-      </c>
-      <c r="H55" s="4"/>
+        <v>840</v>
+      </c>
+      <c r="H55" s="5"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
-        <v>6010000189</v>
+        <v>4010013397</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="C56" s="5">
-        <v>46539</v>
+        <v>40</v>
+      </c>
+      <c r="C56" s="4">
+        <v>46545</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>366</v>
+        <v>41</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G56" s="6">
-        <v>160</v>
-      </c>
-      <c r="H56" s="4"/>
+        <v>880</v>
+      </c>
+      <c r="H56" s="5"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
-        <v>6010000224</v>
+        <v>6010000189</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="C57" s="5">
-        <v>46711</v>
+        <v>368</v>
+      </c>
+      <c r="C57" s="4">
+        <v>46539</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>411</v>
+        <v>369</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G57" s="6">
-        <v>420</v>
-      </c>
-      <c r="H57" s="4"/>
+        <v>110</v>
+      </c>
+      <c r="H57" s="5"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
-        <v>6010000101</v>
+        <v>6010000224</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="C58" s="5">
-        <v>46539</v>
+        <v>413</v>
+      </c>
+      <c r="C58" s="4">
+        <v>46711</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>243</v>
+        <v>414</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G58" s="6">
-        <v>220</v>
-      </c>
-      <c r="H58" s="4"/>
+        <v>420</v>
+      </c>
+      <c r="H58" s="5"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
+        <v>6010000101</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C59" s="4">
+        <v>46539</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G59" s="6">
+        <v>120</v>
+      </c>
+      <c r="H59" s="5"/>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="2">
         <v>6010000232</v>
       </c>
-      <c r="B59" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="C59" s="5">
+      <c r="B60" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="C60" s="4">
         <v>46726</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>419</v>
-      </c>
-      <c r="E59" s="3" t="s">
+      <c r="D60" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="E60" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G59" s="6">
+      <c r="F60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G60" s="6">
         <v>2840</v>
       </c>
-      <c r="H59" s="4"/>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="9">
+      <c r="H60" s="5"/>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="7">
         <v>6010000232</v>
       </c>
-      <c r="B60" s="10" t="s">
-        <v>418</v>
-      </c>
-      <c r="C60" s="11"/>
-      <c r="D60" s="10" t="s">
+      <c r="B61" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="C61" s="9"/>
+      <c r="D61" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E60" s="10" t="s">
+      <c r="E61" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F60" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G60" s="12"/>
-      <c r="H60" s="13">
+      <c r="F61" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G61" s="10"/>
+      <c r="H61" s="11">
         <v>7200</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="9">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" s="7">
         <v>6010000073</v>
       </c>
-      <c r="B61" s="10" t="s">
+      <c r="B62" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="C62" s="9"/>
+      <c r="D62" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E62" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="C61" s="11"/>
-      <c r="D61" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="E61" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="F61" s="10" t="s">
+      <c r="F62" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G61" s="12"/>
-      <c r="H61" s="13">
+      <c r="G62" s="10"/>
+      <c r="H62" s="11">
         <v>720</v>
       </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="2">
-        <v>6010000073</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="C62" s="5">
-        <v>46511</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G62" s="6">
-        <v>1150</v>
-      </c>
-      <c r="H62" s="4"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
-        <v>6010000169</v>
+        <v>6010000073</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="C63" s="5">
-        <v>46751</v>
+        <v>179</v>
+      </c>
+      <c r="C63" s="4">
+        <v>46511</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>344</v>
+        <v>181</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>106</v>
+        <v>180</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G63" s="6">
-        <v>2110</v>
-      </c>
-      <c r="H63" s="4"/>
+        <v>1150</v>
+      </c>
+      <c r="H63" s="5"/>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
-        <v>6010000170</v>
+        <v>6010000169</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="C64" s="5">
-        <v>46721</v>
+        <v>346</v>
+      </c>
+      <c r="C64" s="4">
+        <v>46751</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>106</v>
@@ -3348,186 +3359,188 @@
         <v>5</v>
       </c>
       <c r="G64" s="6">
-        <v>2590</v>
-      </c>
-      <c r="H64" s="4"/>
+        <v>2110</v>
+      </c>
+      <c r="H64" s="5"/>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
-        <v>6010000139</v>
+        <v>6010000170</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="C65" s="5">
-        <v>46711</v>
+        <v>348</v>
+      </c>
+      <c r="C65" s="4">
+        <v>46721</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>298</v>
+        <v>349</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>299</v>
+        <v>106</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G65" s="6">
-        <v>1438</v>
-      </c>
-      <c r="H65" s="4"/>
+        <v>2590</v>
+      </c>
+      <c r="H65" s="5"/>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
-        <v>6010000267</v>
+        <v>6010000139</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>435</v>
-      </c>
-      <c r="C66" s="5">
-        <v>46813</v>
+        <v>299</v>
+      </c>
+      <c r="C66" s="4">
+        <v>46711</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>436</v>
+        <v>300</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>437</v>
+        <v>301</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G66" s="6">
-        <v>620</v>
-      </c>
-      <c r="H66" s="4"/>
+        <v>1438</v>
+      </c>
+      <c r="H66" s="5"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
-        <v>6010000141</v>
+        <v>6010000267</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="C67" s="5">
-        <v>46746</v>
+        <v>438</v>
+      </c>
+      <c r="C67" s="4">
+        <v>46813</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>301</v>
+        <v>439</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>299</v>
+        <v>440</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G67" s="6">
+        <v>620</v>
+      </c>
+      <c r="H67" s="5"/>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" s="2">
+        <v>6010000141</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C68" s="4">
+        <v>46746</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G68" s="6">
         <v>2425</v>
       </c>
-      <c r="H67" s="4"/>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="9">
+      <c r="H68" s="5"/>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" s="7">
         <v>6010000205</v>
       </c>
-      <c r="B68" s="10" t="s">
-        <v>393</v>
-      </c>
-      <c r="C68" s="11"/>
-      <c r="D68" s="10" t="s">
+      <c r="B69" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="C69" s="9"/>
+      <c r="D69" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E68" s="10" t="s">
-        <v>394</v>
-      </c>
-      <c r="F68" s="10" t="s">
+      <c r="E69" s="8" t="s">
+        <v>397</v>
+      </c>
+      <c r="F69" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G68" s="12"/>
-      <c r="H68" s="13">
+      <c r="G69" s="10"/>
+      <c r="H69" s="11">
         <v>7200</v>
       </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="2">
-        <v>6010000205</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="C69" s="5">
-        <v>46692</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="E69" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G69" s="6">
-        <v>10050</v>
-      </c>
-      <c r="H69" s="4"/>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
+        <v>6010000205</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="C70" s="4">
+        <v>46692</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G70" s="6">
+        <v>9450</v>
+      </c>
+      <c r="H70" s="5"/>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" s="2">
         <v>4010013583</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="B71" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C70" s="5">
+      <c r="C71" s="4">
         <v>46504</v>
       </c>
-      <c r="D70" s="3" t="s">
+      <c r="D71" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="E70" s="3" t="s">
+      <c r="E71" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F70" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G70" s="6">
-        <v>620</v>
-      </c>
-      <c r="H70" s="4"/>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="9">
-        <v>6010000074</v>
-      </c>
-      <c r="B71" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="C71" s="11"/>
-      <c r="D71" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="E71" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="F71" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="G71" s="12"/>
-      <c r="H71" s="13">
-        <v>5760</v>
-      </c>
+      <c r="F71" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G71" s="6">
+        <v>520</v>
+      </c>
+      <c r="H71" s="5"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>6010000074</v>
       </c>
       <c r="B72" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C72" s="4">
+        <v>46721</v>
+      </c>
+      <c r="D72" s="3" t="s">
         <v>183</v>
-      </c>
-      <c r="C72" s="5">
-        <v>46721</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>185</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>184</v>
@@ -3538,63 +3551,61 @@
       <c r="G72" s="6">
         <v>6048</v>
       </c>
-      <c r="H72" s="4"/>
+      <c r="H72" s="5"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="9">
+      <c r="A73" s="7">
+        <v>6010000074</v>
+      </c>
+      <c r="B73" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="C73" s="9"/>
+      <c r="D73" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="F73" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="G73" s="10"/>
+      <c r="H73" s="11">
+        <v>5760</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" s="7">
         <v>6010000102</v>
       </c>
-      <c r="B73" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="C73" s="11"/>
-      <c r="D73" s="10" t="s">
+      <c r="B74" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="C74" s="9"/>
+      <c r="D74" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E73" s="10" t="s">
+      <c r="E74" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F73" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G73" s="12"/>
-      <c r="H73" s="13">
+      <c r="F74" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G74" s="10"/>
+      <c r="H74" s="11">
         <v>1600</v>
       </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="2">
-        <v>6010000102</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="C74" s="5">
-        <v>46780</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="E74" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F74" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G74" s="6">
-        <v>3980</v>
-      </c>
-      <c r="H74" s="4"/>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
-        <v>6010000103</v>
+        <v>6010000102</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="C75" s="5">
-        <v>46645</v>
+      <c r="C75" s="4">
+        <v>46780</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>247</v>
@@ -3606,164 +3617,164 @@
         <v>5</v>
       </c>
       <c r="G75" s="6">
-        <v>2920</v>
-      </c>
-      <c r="H75" s="4"/>
+        <v>3980</v>
+      </c>
+      <c r="H75" s="5"/>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
-        <v>6010000196</v>
+        <v>6010000103</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="C76" s="5">
-        <v>46606</v>
+        <v>248</v>
+      </c>
+      <c r="C76" s="4">
+        <v>46645</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>380</v>
+        <v>249</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>381</v>
+        <v>22</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G76" s="6">
-        <v>1640</v>
-      </c>
-      <c r="H76" s="4"/>
+        <v>2920</v>
+      </c>
+      <c r="H76" s="5"/>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
+        <v>6010000196</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="C77" s="4">
+        <v>46606</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G77" s="6">
+        <v>1640</v>
+      </c>
+      <c r="H77" s="5"/>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" s="2">
         <v>4010013473</v>
       </c>
-      <c r="B77" s="3" t="s">
+      <c r="B78" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C77" s="5">
+      <c r="C78" s="4">
         <v>46524</v>
       </c>
-      <c r="D77" s="3" t="s">
+      <c r="D78" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E77" s="3" t="s">
+      <c r="E78" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F77" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G77" s="6">
+      <c r="F78" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G78" s="6">
         <v>420</v>
       </c>
-      <c r="H77" s="4"/>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="9">
+      <c r="H78" s="5"/>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" s="7">
         <v>6010000150</v>
       </c>
-      <c r="B78" s="10" t="s">
-        <v>320</v>
-      </c>
-      <c r="C78" s="11"/>
-      <c r="D78" s="10" t="s">
+      <c r="B79" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="C79" s="9"/>
+      <c r="D79" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E78" s="10" t="s">
-        <v>321</v>
-      </c>
-      <c r="F78" s="10" t="s">
+      <c r="E79" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="F79" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G78" s="12"/>
-      <c r="H78" s="13">
+      <c r="G79" s="10"/>
+      <c r="H79" s="11">
         <v>880</v>
       </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="2">
-        <v>6010000151</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="C79" s="5">
-        <v>46692</v>
-      </c>
-      <c r="D79" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="E79" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="F79" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G79" s="6">
-        <v>540</v>
-      </c>
-      <c r="H79" s="4"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
-        <v>6010000241</v>
+        <v>6010000151</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>428</v>
-      </c>
-      <c r="C80" s="5">
-        <v>46596</v>
+        <v>324</v>
+      </c>
+      <c r="C80" s="4">
+        <v>46692</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>429</v>
+        <v>325</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>430</v>
+        <v>323</v>
       </c>
       <c r="F80" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G80" s="6">
-        <v>486</v>
-      </c>
-      <c r="H80" s="4"/>
+        <v>540</v>
+      </c>
+      <c r="H80" s="5"/>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
-        <v>6010000194</v>
+        <v>6010000241</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="C81" s="5">
-        <v>46803</v>
+        <v>431</v>
+      </c>
+      <c r="C81" s="4">
+        <v>46596</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>375</v>
+        <v>432</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>30</v>
+        <v>433</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G81" s="6">
-        <v>1470</v>
-      </c>
-      <c r="H81" s="4"/>
+        <v>466</v>
+      </c>
+      <c r="H81" s="5"/>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>6010000194</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="C82" s="5">
-        <v>46721</v>
+        <v>377</v>
+      </c>
+      <c r="C82" s="4">
+        <v>46803</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>30</v>
@@ -3772,118 +3783,118 @@
         <v>5</v>
       </c>
       <c r="G82" s="6">
-        <v>4020</v>
-      </c>
-      <c r="H82" s="4"/>
+        <v>1470</v>
+      </c>
+      <c r="H82" s="5"/>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
-        <v>6010000192</v>
+        <v>6010000194</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="C83" s="5">
-        <v>46367</v>
+        <v>377</v>
+      </c>
+      <c r="C83" s="4">
+        <v>46721</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>369</v>
+        <v>30</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G83" s="6">
-        <v>365</v>
-      </c>
-      <c r="H83" s="4"/>
+        <v>4020</v>
+      </c>
+      <c r="H83" s="5"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
-        <v>6010000155</v>
+        <v>6010000192</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="C84" s="5">
-        <v>46447</v>
+        <v>370</v>
+      </c>
+      <c r="C84" s="4">
+        <v>46367</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>328</v>
+        <v>371</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>30</v>
+        <v>372</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G84" s="6">
-        <v>380</v>
-      </c>
-      <c r="H84" s="4"/>
+        <v>345</v>
+      </c>
+      <c r="H84" s="5"/>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
-        <v>6010000108</v>
+        <v>6010000155</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="C85" s="5">
-        <v>46574</v>
+        <v>329</v>
+      </c>
+      <c r="C85" s="4">
+        <v>46447</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>249</v>
+        <v>330</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G85" s="6">
-        <v>560</v>
-      </c>
-      <c r="H85" s="4"/>
+        <v>380</v>
+      </c>
+      <c r="H85" s="5"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
-        <v>6010000193</v>
+        <v>6010000108</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="C86" s="5">
-        <v>46803</v>
+        <v>250</v>
+      </c>
+      <c r="C86" s="4">
+        <v>46574</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>371</v>
+        <v>251</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F86" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G86" s="6">
-        <v>380</v>
-      </c>
-      <c r="H86" s="4"/>
+        <v>560</v>
+      </c>
+      <c r="H86" s="5"/>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>6010000193</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="C87" s="5">
-        <v>46726</v>
+        <v>373</v>
+      </c>
+      <c r="C87" s="4">
+        <v>46711</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>30</v>
@@ -3892,22 +3903,22 @@
         <v>5</v>
       </c>
       <c r="G87" s="6">
-        <v>80</v>
-      </c>
-      <c r="H87" s="4"/>
+        <v>170</v>
+      </c>
+      <c r="H87" s="5"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>6010000193</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="C88" s="5">
-        <v>46711</v>
+        <v>373</v>
+      </c>
+      <c r="C88" s="4">
+        <v>46726</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>30</v>
@@ -3916,22 +3927,22 @@
         <v>5</v>
       </c>
       <c r="G88" s="6">
-        <v>170</v>
-      </c>
-      <c r="H88" s="4"/>
+        <v>80</v>
+      </c>
+      <c r="H88" s="5"/>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
-        <v>6010000216</v>
+        <v>6010000193</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="C89" s="5">
-        <v>46690</v>
+        <v>373</v>
+      </c>
+      <c r="C89" s="4">
+        <v>46803</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>402</v>
+        <v>376</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>30</v>
@@ -3940,70 +3951,70 @@
         <v>5</v>
       </c>
       <c r="G89" s="6">
-        <v>90</v>
-      </c>
-      <c r="H89" s="4"/>
+        <v>380</v>
+      </c>
+      <c r="H89" s="5"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
-        <v>6010000235</v>
+        <v>6010000216</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>424</v>
-      </c>
-      <c r="C90" s="5">
-        <v>46808</v>
+        <v>404</v>
+      </c>
+      <c r="C90" s="4">
+        <v>46690</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>425</v>
+        <v>405</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F90" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G90" s="6">
-        <v>1540</v>
-      </c>
-      <c r="H90" s="4"/>
+        <v>90</v>
+      </c>
+      <c r="H90" s="5"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
-        <v>4010013662</v>
+        <v>6010000235</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="C91" s="5">
-        <v>46546</v>
+        <v>427</v>
+      </c>
+      <c r="C91" s="4">
+        <v>46808</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>132</v>
+        <v>428</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G91" s="6">
-        <v>420</v>
-      </c>
-      <c r="H91" s="4"/>
+        <v>1540</v>
+      </c>
+      <c r="H91" s="5"/>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>4010013662</v>
       </c>
       <c r="B92" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C92" s="4">
+        <v>46546</v>
+      </c>
+      <c r="D92" s="3" t="s">
         <v>131</v>
-      </c>
-      <c r="C92" s="5">
-        <v>46537</v>
-      </c>
-      <c r="D92" s="3" t="s">
-        <v>133</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>30</v>
@@ -4012,66 +4023,66 @@
         <v>5</v>
       </c>
       <c r="G92" s="6">
-        <v>190</v>
-      </c>
-      <c r="H92" s="4"/>
+        <v>420</v>
+      </c>
+      <c r="H92" s="5"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
-        <v>6010000076</v>
+        <v>4010013662</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="C93" s="5">
-        <v>46483</v>
+        <v>130</v>
+      </c>
+      <c r="C93" s="4">
+        <v>46537</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>187</v>
+        <v>132</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>184</v>
+        <v>30</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G93" s="6">
-        <v>3076</v>
-      </c>
-      <c r="H93" s="4"/>
+        <v>190</v>
+      </c>
+      <c r="H93" s="5"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
-        <v>6010000110</v>
+        <v>6010000076</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="C94" s="5">
-        <v>46640</v>
+        <v>185</v>
+      </c>
+      <c r="C94" s="4">
+        <v>46483</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>251</v>
+        <v>186</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>4</v>
+        <v>184</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G94" s="6">
-        <v>1000</v>
-      </c>
-      <c r="H94" s="4"/>
+        <v>2876</v>
+      </c>
+      <c r="H94" s="5"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
-        <v>6010000111</v>
+        <v>6010000110</v>
       </c>
       <c r="B95" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="C95" s="5">
+      <c r="C95" s="4">
         <v>46640</v>
       </c>
       <c r="D95" s="3" t="s">
@@ -4084,31 +4095,33 @@
         <v>5</v>
       </c>
       <c r="G95" s="6">
+        <v>1000</v>
+      </c>
+      <c r="H95" s="5"/>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" s="2">
+        <v>6010000111</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="C96" s="4">
+        <v>46640</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G96" s="6">
         <v>2640</v>
       </c>
-      <c r="H95" s="4"/>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A96" s="9">
-        <v>4010013584</v>
-      </c>
-      <c r="B96" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="C96" s="11"/>
-      <c r="D96" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="E96" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="F96" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G96" s="12"/>
-      <c r="H96" s="13">
-        <v>900</v>
-      </c>
+      <c r="H96" s="5"/>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
@@ -4117,8 +4130,8 @@
       <c r="B97" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C97" s="5">
-        <v>46537</v>
+      <c r="C97" s="4">
+        <v>46532</v>
       </c>
       <c r="D97" s="3" t="s">
         <v>94</v>
@@ -4130,9 +4143,9 @@
         <v>5</v>
       </c>
       <c r="G97" s="6">
-        <v>380</v>
-      </c>
-      <c r="H97" s="4"/>
+        <v>200</v>
+      </c>
+      <c r="H97" s="5"/>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
@@ -4141,8 +4154,8 @@
       <c r="B98" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C98" s="5">
-        <v>46532</v>
+      <c r="C98" s="4">
+        <v>46537</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>95</v>
@@ -4154,46 +4167,44 @@
         <v>5</v>
       </c>
       <c r="G98" s="6">
-        <v>200</v>
-      </c>
-      <c r="H98" s="4"/>
+        <v>380</v>
+      </c>
+      <c r="H98" s="5"/>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A99" s="2">
-        <v>6010000171</v>
-      </c>
-      <c r="B99" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="C99" s="5">
-        <v>46579</v>
-      </c>
-      <c r="D99" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="E99" s="3" t="s">
+      <c r="A99" s="7">
+        <v>4010013584</v>
+      </c>
+      <c r="B99" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C99" s="9"/>
+      <c r="D99" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E99" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="F99" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G99" s="6">
-        <v>1500</v>
-      </c>
-      <c r="H99" s="4"/>
+      <c r="F99" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G99" s="10"/>
+      <c r="H99" s="11">
+        <v>900</v>
+      </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
-        <v>4010013585</v>
+        <v>6010000171</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C100" s="5">
-        <v>46568</v>
+        <v>350</v>
+      </c>
+      <c r="C100" s="4">
+        <v>46579</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>97</v>
+        <v>351</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>87</v>
@@ -4204,20 +4215,20 @@
       <c r="G100" s="6">
         <v>1500</v>
       </c>
-      <c r="H100" s="4"/>
+      <c r="H100" s="5"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
-        <v>6010000172</v>
+        <v>4010013585</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="C101" s="5">
-        <v>46579</v>
+        <v>96</v>
+      </c>
+      <c r="C101" s="4">
+        <v>46568</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>350</v>
+        <v>97</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>87</v>
@@ -4226,186 +4237,186 @@
         <v>5</v>
       </c>
       <c r="G101" s="6">
-        <v>1620</v>
-      </c>
-      <c r="H101" s="4"/>
+        <v>1500</v>
+      </c>
+      <c r="H101" s="5"/>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
+        <v>6010000172</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="C102" s="4">
+        <v>46579</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G102" s="6">
+        <v>1620</v>
+      </c>
+      <c r="H102" s="5"/>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" s="2">
         <v>6010000077</v>
       </c>
-      <c r="B102" s="3" t="s">
+      <c r="B103" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C103" s="4">
+        <v>46471</v>
+      </c>
+      <c r="D103" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="C102" s="5">
-        <v>46471</v>
-      </c>
-      <c r="D102" s="3" t="s">
+      <c r="E103" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="E102" s="3" t="s">
+      <c r="F103" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G103" s="6">
+        <v>4970</v>
+      </c>
+      <c r="H103" s="5"/>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" s="7">
+        <v>6010000078</v>
+      </c>
+      <c r="B104" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="F102" s="3" t="s">
+      <c r="C104" s="9"/>
+      <c r="D104" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E104" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="F104" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G102" s="6">
-        <v>5070</v>
-      </c>
-      <c r="H102" s="4"/>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A103" s="9">
-        <v>6010000078</v>
-      </c>
-      <c r="B103" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="C103" s="11"/>
-      <c r="D103" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="E103" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="F103" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="G103" s="12"/>
-      <c r="H103" s="13">
+      <c r="G104" s="10"/>
+      <c r="H104" s="11">
         <v>125</v>
       </c>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A104" s="2">
-        <v>6010000078</v>
-      </c>
-      <c r="B104" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="C104" s="5">
-        <v>46780</v>
-      </c>
-      <c r="D104" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="E104" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="F104" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G104" s="6">
-        <v>7150</v>
-      </c>
-      <c r="H104" s="4"/>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
-        <v>6010000079</v>
+        <v>6010000078</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="C105" s="5">
-        <v>46512</v>
+        <v>190</v>
+      </c>
+      <c r="C105" s="4">
+        <v>46780</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="F105" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G105" s="6">
-        <v>310</v>
-      </c>
-      <c r="H105" s="4"/>
+        <v>7100</v>
+      </c>
+      <c r="H105" s="5"/>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
+        <v>6010000079</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C106" s="4">
+        <v>46512</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G106" s="6">
+        <v>310</v>
+      </c>
+      <c r="H106" s="5"/>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" s="2">
         <v>4010013593</v>
       </c>
-      <c r="B106" s="3" t="s">
+      <c r="B107" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C106" s="5">
+      <c r="C107" s="4">
         <v>46758</v>
       </c>
-      <c r="D106" s="3" t="s">
+      <c r="D107" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="E106" s="3" t="s">
+      <c r="E107" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F106" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G106" s="6">
+      <c r="F107" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G107" s="6">
         <v>530</v>
       </c>
-      <c r="H106" s="4"/>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A107" s="9">
+      <c r="H107" s="5"/>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" s="7">
         <v>4010013593</v>
       </c>
-      <c r="B107" s="10" t="s">
+      <c r="B108" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C107" s="11"/>
-      <c r="D107" s="10" t="s">
+      <c r="C108" s="9"/>
+      <c r="D108" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E107" s="10" t="s">
+      <c r="E108" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F107" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G107" s="12"/>
-      <c r="H107" s="13">
+      <c r="F108" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G108" s="10"/>
+      <c r="H108" s="11">
         <v>560</v>
       </c>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A108" s="2">
-        <v>4010014329</v>
-      </c>
-      <c r="B108" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="C108" s="5">
-        <v>46641</v>
-      </c>
-      <c r="D108" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="E108" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F108" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G108" s="6">
-        <v>230</v>
-      </c>
-      <c r="H108" s="4"/>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
-        <v>4010013594</v>
+        <v>4010014329</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C109" s="5">
-        <v>46573</v>
+        <v>155</v>
+      </c>
+      <c r="C109" s="4">
+        <v>46641</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>110</v>
+        <v>156</v>
       </c>
       <c r="E109" s="3" t="s">
         <v>30</v>
@@ -4414,68 +4425,68 @@
         <v>5</v>
       </c>
       <c r="G109" s="6">
+        <v>230</v>
+      </c>
+      <c r="H109" s="5"/>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" s="2">
+        <v>4010013594</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C110" s="4">
+        <v>46573</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F110" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G110" s="6">
         <v>760</v>
       </c>
-      <c r="H109" s="4"/>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A110" s="9">
+      <c r="H110" s="5"/>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" s="7">
         <v>4010013594</v>
       </c>
-      <c r="B110" s="10" t="s">
+      <c r="B111" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="C110" s="11"/>
-      <c r="D110" s="10" t="s">
+      <c r="C111" s="9"/>
+      <c r="D111" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E110" s="10" t="s">
+      <c r="E111" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F110" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G110" s="12"/>
-      <c r="H110" s="13">
+      <c r="F111" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G111" s="10"/>
+      <c r="H111" s="11">
         <v>1120</v>
       </c>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A111" s="2">
-        <v>4010014330</v>
-      </c>
-      <c r="B111" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C111" s="5">
-        <v>46610</v>
-      </c>
-      <c r="D111" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="E111" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F111" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G111" s="6">
-        <v>280</v>
-      </c>
-      <c r="H111" s="4"/>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
-        <v>6010000156</v>
+        <v>4010014330</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="C112" s="5">
-        <v>46447</v>
+        <v>157</v>
+      </c>
+      <c r="C112" s="4">
+        <v>46610</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>330</v>
+        <v>158</v>
       </c>
       <c r="E112" s="3" t="s">
         <v>30</v>
@@ -4484,22 +4495,22 @@
         <v>5</v>
       </c>
       <c r="G112" s="6">
-        <v>270</v>
-      </c>
-      <c r="H112" s="4"/>
+        <v>280</v>
+      </c>
+      <c r="H112" s="5"/>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="2">
-        <v>6010000233</v>
+        <v>6010000156</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="C113" s="5">
-        <v>46721</v>
+        <v>331</v>
+      </c>
+      <c r="C113" s="4">
+        <v>46447</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>420</v>
+        <v>332</v>
       </c>
       <c r="E113" s="3" t="s">
         <v>30</v>
@@ -4508,356 +4519,356 @@
         <v>5</v>
       </c>
       <c r="G113" s="6">
-        <v>110</v>
-      </c>
-      <c r="H113" s="4"/>
+        <v>270</v>
+      </c>
+      <c r="H113" s="5"/>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A114" s="9">
+      <c r="A114" s="2">
         <v>6010000233</v>
       </c>
-      <c r="B114" s="10" t="s">
-        <v>329</v>
-      </c>
-      <c r="C114" s="11"/>
-      <c r="D114" s="10" t="s">
+      <c r="B114" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C114" s="4">
+        <v>46721</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G114" s="6">
+        <v>90</v>
+      </c>
+      <c r="H114" s="5"/>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" s="7">
+        <v>6010000233</v>
+      </c>
+      <c r="B115" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="C115" s="9"/>
+      <c r="D115" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E114" s="10" t="s">
+      <c r="E115" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F114" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G114" s="12"/>
-      <c r="H114" s="13">
+      <c r="F115" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G115" s="10"/>
+      <c r="H115" s="11">
         <v>1350</v>
       </c>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A115" s="2">
-        <v>6010000080</v>
-      </c>
-      <c r="B115" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="C115" s="5">
-        <v>46423</v>
-      </c>
-      <c r="D115" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E115" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="F115" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G115" s="6">
-        <v>500</v>
-      </c>
-      <c r="H115" s="4"/>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
-        <v>6010000113</v>
+        <v>6010000080</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="C116" s="5">
-        <v>46598</v>
+        <v>196</v>
+      </c>
+      <c r="C116" s="4">
+        <v>46423</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>255</v>
+        <v>197</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>22</v>
+        <v>198</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G116" s="6">
-        <v>8340</v>
-      </c>
-      <c r="H116" s="4"/>
+        <v>500</v>
+      </c>
+      <c r="H116" s="5"/>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
-        <v>4010013656</v>
+        <v>6010000113</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C117" s="5">
-        <v>46510</v>
+        <v>256</v>
+      </c>
+      <c r="C117" s="4">
+        <v>46598</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>120</v>
+        <v>257</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>121</v>
+        <v>22</v>
       </c>
       <c r="F117" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G117" s="6">
-        <v>2320</v>
-      </c>
-      <c r="H117" s="4"/>
+        <v>8340</v>
+      </c>
+      <c r="H117" s="5"/>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
-        <v>4010013595</v>
+        <v>4010013656</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C118" s="5">
-        <v>46623</v>
+        <v>119</v>
+      </c>
+      <c r="C118" s="4">
+        <v>46510</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>30</v>
+        <v>121</v>
       </c>
       <c r="F118" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G118" s="6">
-        <v>100</v>
-      </c>
-      <c r="H118" s="4"/>
+        <v>2300</v>
+      </c>
+      <c r="H118" s="5"/>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
-        <v>6010000174</v>
+        <v>4010013595</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="C119" s="5">
-        <v>46586</v>
+        <v>111</v>
+      </c>
+      <c r="C119" s="4">
+        <v>46623</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>352</v>
+        <v>112</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>353</v>
+        <v>30</v>
       </c>
       <c r="F119" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G119" s="6">
-        <v>1120</v>
-      </c>
-      <c r="H119" s="4"/>
+        <v>100</v>
+      </c>
+      <c r="H119" s="5"/>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" s="2">
-        <v>6010000114</v>
+        <v>6010000174</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="C120" s="5">
-        <v>46488</v>
+        <v>354</v>
+      </c>
+      <c r="C120" s="4">
+        <v>46586</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>257</v>
+        <v>355</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>106</v>
+        <v>356</v>
       </c>
       <c r="F120" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G120" s="6">
-        <v>2000</v>
-      </c>
-      <c r="H120" s="4"/>
+        <v>1120</v>
+      </c>
+      <c r="H120" s="5"/>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
-        <v>6010000081</v>
+        <v>6010000114</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="C121" s="5">
-        <v>46660</v>
+        <v>258</v>
+      </c>
+      <c r="C121" s="4">
+        <v>46488</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>201</v>
+        <v>259</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>2</v>
+        <v>106</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G121" s="6">
-        <v>750</v>
-      </c>
-      <c r="H121" s="4"/>
+        <v>2000</v>
+      </c>
+      <c r="H121" s="5"/>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
-        <v>6010000082</v>
+        <v>6010000081</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="C122" s="5">
-        <v>46505</v>
+        <v>199</v>
+      </c>
+      <c r="C122" s="4">
+        <v>46660</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>204</v>
+        <v>2</v>
       </c>
       <c r="F122" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G122" s="6">
-        <v>11100</v>
-      </c>
-      <c r="H122" s="4"/>
+        <v>750</v>
+      </c>
+      <c r="H122" s="5"/>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
-        <v>6010000175</v>
+        <v>6010000082</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="C123" s="5">
-        <v>46556</v>
+        <v>201</v>
+      </c>
+      <c r="C123" s="4">
+        <v>46505</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>355</v>
+        <v>202</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>356</v>
+        <v>203</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G123" s="6">
-        <v>1880</v>
-      </c>
-      <c r="H123" s="4"/>
+        <v>11100</v>
+      </c>
+      <c r="H123" s="5"/>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" s="2">
-        <v>6010000176</v>
+        <v>6010000175</v>
       </c>
       <c r="B124" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="5">
-        <v>46586</v>
+      <c r="C124" s="4">
+        <v>46556</v>
       </c>
       <c r="D124" s="3" t="s">
         <v>358</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="F124" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G124" s="6">
-        <v>1980</v>
-      </c>
-      <c r="H124" s="4"/>
+        <v>1880</v>
+      </c>
+      <c r="H124" s="5"/>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" s="2">
-        <v>6010000201</v>
+        <v>6010000176</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="C125" s="5">
-        <v>46624</v>
+        <v>360</v>
+      </c>
+      <c r="C125" s="4">
+        <v>46586</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>387</v>
+        <v>361</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>388</v>
+        <v>359</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G125" s="6">
-        <v>910</v>
-      </c>
-      <c r="H125" s="4"/>
+        <v>1980</v>
+      </c>
+      <c r="H125" s="5"/>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" s="2">
-        <v>6010000202</v>
+        <v>6010000201</v>
       </c>
       <c r="B126" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="C126" s="5">
-        <v>46685</v>
+      <c r="C126" s="4">
+        <v>46624</v>
       </c>
       <c r="D126" s="3" t="s">
         <v>390</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="F126" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G126" s="6">
-        <v>830</v>
-      </c>
-      <c r="H126" s="4"/>
+        <v>910</v>
+      </c>
+      <c r="H126" s="5"/>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" s="2">
-        <v>4010013262</v>
+        <v>6010000202</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C127" s="5">
-        <v>46549</v>
+        <v>392</v>
+      </c>
+      <c r="C127" s="4">
+        <v>46685</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>14</v>
+        <v>393</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>15</v>
+        <v>391</v>
       </c>
       <c r="F127" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G127" s="6">
-        <v>380</v>
-      </c>
-      <c r="H127" s="4"/>
+        <v>830</v>
+      </c>
+      <c r="H127" s="5"/>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" s="2">
-        <v>4010013465</v>
+        <v>4010013262</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C128" s="5">
-        <v>46637</v>
+        <v>13</v>
+      </c>
+      <c r="C128" s="4">
+        <v>46549</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="E128" s="3" t="s">
         <v>15</v>
@@ -4866,167 +4877,167 @@
         <v>5</v>
       </c>
       <c r="G128" s="6">
-        <v>1680</v>
-      </c>
-      <c r="H128" s="4"/>
+        <v>380</v>
+      </c>
+      <c r="H128" s="5"/>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
-        <v>4010013466</v>
+        <v>4010013465</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C129" s="5">
-        <v>46704</v>
+        <v>44</v>
+      </c>
+      <c r="C129" s="4">
+        <v>46637</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="F129" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G129" s="6">
-        <v>80</v>
-      </c>
-      <c r="H129" s="4"/>
+        <v>1680</v>
+      </c>
+      <c r="H129" s="5"/>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
+        <v>4010013466</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C130" s="4">
+        <v>46704</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E130" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F130" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G130" s="6">
+        <v>80</v>
+      </c>
+      <c r="H130" s="5"/>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" s="2">
         <v>4010013671</v>
       </c>
-      <c r="B130" s="3" t="s">
+      <c r="B131" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C131" s="4">
+        <v>46566</v>
+      </c>
+      <c r="D131" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="C130" s="5">
-        <v>46566</v>
-      </c>
-      <c r="D130" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="E130" s="3" t="s">
+      <c r="E131" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F130" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G130" s="6">
+      <c r="F131" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G131" s="6">
         <v>980</v>
       </c>
-      <c r="H130" s="4"/>
-    </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A131" s="9">
+      <c r="H131" s="5"/>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" s="7">
         <v>4010013671</v>
       </c>
-      <c r="B131" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="C131" s="11"/>
-      <c r="D131" s="10" t="s">
+      <c r="B132" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="C132" s="9"/>
+      <c r="D132" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E131" s="10" t="s">
+      <c r="E132" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F131" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G131" s="12"/>
-      <c r="H131" s="13">
+      <c r="F132" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G132" s="10"/>
+      <c r="H132" s="11">
         <v>1440</v>
       </c>
-    </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A132" s="2">
-        <v>6010000252</v>
-      </c>
-      <c r="B132" s="3" t="s">
-        <v>431</v>
-      </c>
-      <c r="C132" s="5">
-        <v>46780</v>
-      </c>
-      <c r="D132" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="E132" s="3" t="s">
-        <v>433</v>
-      </c>
-      <c r="F132" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G132" s="6">
-        <v>1500</v>
-      </c>
-      <c r="H132" s="4"/>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" s="2">
         <v>6010000252</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>431</v>
-      </c>
-      <c r="C133" s="5">
-        <v>46661</v>
+        <v>434</v>
+      </c>
+      <c r="C133" s="4">
+        <v>46780</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="F133" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G133" s="6">
-        <v>690</v>
-      </c>
-      <c r="H133" s="4"/>
+        <v>1500</v>
+      </c>
+      <c r="H133" s="5"/>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
-        <v>6010000218</v>
+        <v>6010000252</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="C134" s="5">
-        <v>46780</v>
+        <v>434</v>
+      </c>
+      <c r="C134" s="4">
+        <v>46661</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>407</v>
+        <v>437</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>408</v>
+        <v>436</v>
       </c>
       <c r="F134" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G134" s="6">
-        <v>2375</v>
-      </c>
-      <c r="H134" s="4"/>
+        <v>690</v>
+      </c>
+      <c r="H134" s="5"/>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" s="2">
         <v>6010000218</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="C135" s="5">
+        <v>409</v>
+      </c>
+      <c r="C135" s="4">
         <v>46812</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="F135" s="3" t="s">
         <v>3</v>
@@ -5034,136 +5045,138 @@
       <c r="G135" s="6">
         <v>500</v>
       </c>
-      <c r="H135" s="4"/>
+      <c r="H135" s="5"/>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" s="2">
-        <v>6010000083</v>
+        <v>6010000218</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="C136" s="5">
-        <v>46537</v>
+        <v>409</v>
+      </c>
+      <c r="C136" s="4">
+        <v>46780</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>206</v>
+        <v>412</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>207</v>
+        <v>411</v>
       </c>
       <c r="F136" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G136" s="6">
+        <v>2375</v>
+      </c>
+      <c r="H136" s="5"/>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137" s="2">
+        <v>6010000083</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C137" s="4">
+        <v>46537</v>
+      </c>
+      <c r="D137" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="E137" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="F137" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G137" s="6">
         <v>1270</v>
       </c>
-      <c r="H136" s="4"/>
-    </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A137" s="9">
+      <c r="H137" s="5"/>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A138" s="7">
         <v>6010000083</v>
       </c>
-      <c r="B137" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="C137" s="11"/>
-      <c r="D137" s="10" t="s">
+      <c r="B138" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="C138" s="9"/>
+      <c r="D138" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E137" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="F137" s="10" t="s">
+      <c r="E138" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="F138" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G137" s="12"/>
-      <c r="H137" s="13">
+      <c r="G138" s="10"/>
+      <c r="H138" s="11">
         <v>300</v>
       </c>
-    </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A138" s="2">
-        <v>6010000084</v>
-      </c>
-      <c r="B138" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="C138" s="5">
-        <v>46711</v>
-      </c>
-      <c r="D138" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="E138" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="F138" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G138" s="6">
-        <v>4420</v>
-      </c>
-      <c r="H138" s="4"/>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" s="2">
+        <v>6010000084</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="C139" s="4">
+        <v>46711</v>
+      </c>
+      <c r="D139" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="E139" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="F139" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G139" s="6">
+        <v>4420</v>
+      </c>
+      <c r="H139" s="5"/>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A140" s="2">
         <v>6010000115</v>
       </c>
-      <c r="B139" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="C139" s="5">
+      <c r="B140" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="C140" s="4">
         <v>46971</v>
       </c>
-      <c r="D139" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="E139" s="3" t="s">
+      <c r="D140" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="E140" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F139" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G139" s="6">
-        <v>3500</v>
-      </c>
-      <c r="H139" s="4"/>
-    </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A140" s="9">
-        <v>6010000115</v>
-      </c>
-      <c r="B140" s="10" t="s">
-        <v>258</v>
-      </c>
-      <c r="C140" s="11"/>
-      <c r="D140" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="E140" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="F140" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G140" s="12"/>
-      <c r="H140" s="13">
-        <v>6000</v>
-      </c>
+      <c r="F140" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G140" s="6">
+        <v>9500</v>
+      </c>
+      <c r="H140" s="5"/>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" s="2">
         <v>6010000116</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="C141" s="5">
+        <v>262</v>
+      </c>
+      <c r="C141" s="4">
         <v>46971</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E141" s="3" t="s">
         <v>4</v>
@@ -5174,27 +5187,27 @@
       <c r="G141" s="6">
         <v>4880</v>
       </c>
-      <c r="H141" s="4"/>
+      <c r="H141" s="5"/>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A142" s="9">
+      <c r="A142" s="7">
         <v>6010000116</v>
       </c>
-      <c r="B142" s="10" t="s">
-        <v>260</v>
-      </c>
-      <c r="C142" s="11"/>
-      <c r="D142" s="10" t="s">
+      <c r="B142" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="C142" s="9"/>
+      <c r="D142" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E142" s="10" t="s">
+      <c r="E142" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F142" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G142" s="12"/>
-      <c r="H142" s="13">
+      <c r="F142" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G142" s="10"/>
+      <c r="H142" s="11">
         <v>3600</v>
       </c>
     </row>
@@ -5203,9 +5216,9 @@
         <v>7050000019</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>444</v>
-      </c>
-      <c r="C143" s="5"/>
+        <v>447</v>
+      </c>
+      <c r="C143" s="4"/>
       <c r="D143" s="3" t="s">
         <v>2</v>
       </c>
@@ -5218,20 +5231,20 @@
       <c r="G143" s="6">
         <v>530</v>
       </c>
-      <c r="H143" s="4"/>
+      <c r="H143" s="5"/>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" s="2">
         <v>6010000117</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="C144" s="5">
+        <v>264</v>
+      </c>
+      <c r="C144" s="4">
         <v>46711</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E144" s="3" t="s">
         <v>22</v>
@@ -5240,22 +5253,22 @@
         <v>5</v>
       </c>
       <c r="G144" s="6">
-        <v>6040</v>
-      </c>
-      <c r="H144" s="4"/>
+        <v>5960</v>
+      </c>
+      <c r="H144" s="5"/>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" s="2">
         <v>6010000118</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="C145" s="5">
+        <v>266</v>
+      </c>
+      <c r="C145" s="4">
         <v>46574</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E145" s="3" t="s">
         <v>22</v>
@@ -5266,27 +5279,27 @@
       <c r="G145" s="6">
         <v>10240</v>
       </c>
-      <c r="H145" s="4"/>
+      <c r="H145" s="5"/>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A146" s="9">
+      <c r="A146" s="7">
         <v>6010000148</v>
       </c>
-      <c r="B146" s="10" t="s">
-        <v>318</v>
-      </c>
-      <c r="C146" s="11"/>
-      <c r="D146" s="10" t="s">
+      <c r="B146" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="C146" s="9"/>
+      <c r="D146" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E146" s="10" t="s">
+      <c r="E146" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F146" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G146" s="12"/>
-      <c r="H146" s="13">
+      <c r="F146" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G146" s="10"/>
+      <c r="H146" s="11">
         <v>20</v>
       </c>
     </row>
@@ -5295,13 +5308,13 @@
         <v>6010000148</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="C147" s="5">
+        <v>320</v>
+      </c>
+      <c r="C147" s="4">
         <v>46751</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E147" s="3" t="s">
         <v>22</v>
@@ -5310,25 +5323,25 @@
         <v>5</v>
       </c>
       <c r="G147" s="6">
-        <v>2400</v>
-      </c>
-      <c r="H147" s="4"/>
+        <v>2360</v>
+      </c>
+      <c r="H147" s="5"/>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" s="2">
         <v>6010000119</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="C148" s="5">
+        <v>268</v>
+      </c>
+      <c r="C148" s="4">
         <v>46598</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F148" s="3" t="s">
         <v>5</v>
@@ -5336,38 +5349,40 @@
       <c r="G148" s="6">
         <v>300</v>
       </c>
-      <c r="H148" s="4"/>
+      <c r="H148" s="5"/>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A149" s="9">
+      <c r="A149" s="2">
         <v>6010000085</v>
       </c>
-      <c r="B149" s="10" t="s">
+      <c r="B149" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C149" s="4">
+        <v>46388</v>
+      </c>
+      <c r="D149" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="C149" s="11"/>
-      <c r="D149" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="E149" s="10" t="s">
+      <c r="E149" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="F149" s="10" t="s">
+      <c r="F149" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G149" s="12"/>
-      <c r="H149" s="13">
-        <v>54000</v>
-      </c>
+      <c r="G149" s="6">
+        <v>41100</v>
+      </c>
+      <c r="H149" s="5"/>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" s="2">
         <v>6010000085</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="C150" s="5">
+        <v>210</v>
+      </c>
+      <c r="C150" s="4">
         <v>46388</v>
       </c>
       <c r="D150" s="3" t="s">
@@ -5380,22 +5395,22 @@
         <v>3</v>
       </c>
       <c r="G150" s="6">
-        <v>800</v>
-      </c>
-      <c r="H150" s="4"/>
+        <v>13500</v>
+      </c>
+      <c r="H150" s="5"/>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" s="2">
         <v>6010000123</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="C151" s="5">
+        <v>271</v>
+      </c>
+      <c r="C151" s="4">
         <v>46752</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E151" s="3" t="s">
         <v>87</v>
@@ -5406,20 +5421,20 @@
       <c r="G151" s="6">
         <v>4860</v>
       </c>
-      <c r="H151" s="4"/>
+      <c r="H151" s="5"/>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" s="2">
         <v>6010000230</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="C152" s="5">
-        <v>46614</v>
+        <v>418</v>
+      </c>
+      <c r="C152" s="4">
+        <v>46600</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E152" s="3" t="s">
         <v>22</v>
@@ -5428,22 +5443,22 @@
         <v>5</v>
       </c>
       <c r="G152" s="6">
-        <v>2980</v>
-      </c>
-      <c r="H152" s="4"/>
+        <v>620</v>
+      </c>
+      <c r="H152" s="5"/>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" s="2">
         <v>6010000230</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="C153" s="5">
-        <v>46600</v>
+        <v>418</v>
+      </c>
+      <c r="C153" s="4">
+        <v>46614</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E153" s="3" t="s">
         <v>22</v>
@@ -5452,9 +5467,9 @@
         <v>5</v>
       </c>
       <c r="G153" s="6">
-        <v>620</v>
-      </c>
-      <c r="H153" s="4"/>
+        <v>2980</v>
+      </c>
+      <c r="H153" s="5"/>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" s="2">
@@ -5463,7 +5478,7 @@
       <c r="B154" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="C154" s="5">
+      <c r="C154" s="4">
         <v>46641</v>
       </c>
       <c r="D154" s="3" t="s">
@@ -5476,51 +5491,51 @@
         <v>3</v>
       </c>
       <c r="G154" s="6">
-        <v>7500</v>
-      </c>
-      <c r="H154" s="4"/>
+        <v>7100</v>
+      </c>
+      <c r="H154" s="5"/>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A155" s="9">
+      <c r="A155" s="7">
         <v>6010000086</v>
       </c>
-      <c r="B155" s="10" t="s">
+      <c r="B155" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="C155" s="11"/>
-      <c r="D155" s="10" t="s">
+      <c r="C155" s="9"/>
+      <c r="D155" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E155" s="10" t="s">
+      <c r="E155" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="F155" s="10" t="s">
+      <c r="F155" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G155" s="12"/>
-      <c r="H155" s="13">
+      <c r="G155" s="10"/>
+      <c r="H155" s="11">
         <v>2000</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A156" s="9">
+      <c r="A156" s="7">
         <v>6010000147</v>
       </c>
-      <c r="B156" s="10" t="s">
-        <v>316</v>
-      </c>
-      <c r="C156" s="11"/>
-      <c r="D156" s="10" t="s">
+      <c r="B156" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="C156" s="9"/>
+      <c r="D156" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E156" s="10" t="s">
-        <v>299</v>
-      </c>
-      <c r="F156" s="10" t="s">
+      <c r="E156" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="F156" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G156" s="12"/>
-      <c r="H156" s="13">
+      <c r="G156" s="10"/>
+      <c r="H156" s="11">
         <v>500</v>
       </c>
     </row>
@@ -5529,86 +5544,86 @@
         <v>6010000147</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="C157" s="5">
+        <v>318</v>
+      </c>
+      <c r="C157" s="4">
         <v>46813</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F157" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G157" s="6">
-        <v>700</v>
-      </c>
-      <c r="H157" s="4"/>
+        <v>680</v>
+      </c>
+      <c r="H157" s="5"/>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A158" s="2">
+      <c r="A158" s="7">
         <v>6010000144</v>
       </c>
-      <c r="B158" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="C158" s="5">
+      <c r="B158" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="C158" s="9"/>
+      <c r="D158" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E158" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="F158" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="G158" s="10"/>
+      <c r="H158" s="11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A159" s="2">
+        <v>6010000144</v>
+      </c>
+      <c r="B159" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="C159" s="4">
         <v>46605</v>
       </c>
-      <c r="D158" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="E158" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="F158" s="3" t="s">
+      <c r="D159" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="E159" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="F159" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G158" s="6">
-        <v>810</v>
-      </c>
-      <c r="H158" s="4"/>
-    </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A159" s="9">
-        <v>6010000144</v>
-      </c>
-      <c r="B159" s="10" t="s">
-        <v>308</v>
-      </c>
-      <c r="C159" s="11"/>
-      <c r="D159" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="E159" s="10" t="s">
-        <v>299</v>
-      </c>
-      <c r="F159" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="G159" s="12"/>
-      <c r="H159" s="13">
-        <v>100</v>
-      </c>
+      <c r="G159" s="6">
+        <v>760</v>
+      </c>
+      <c r="H159" s="5"/>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" s="2">
         <v>6010000214</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="C160" s="5">
+        <v>399</v>
+      </c>
+      <c r="C160" s="4">
         <v>46692</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F160" s="3" t="s">
         <v>3</v>
@@ -5616,27 +5631,27 @@
       <c r="G160" s="6">
         <v>340</v>
       </c>
-      <c r="H160" s="4"/>
+      <c r="H160" s="5"/>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A161" s="9">
+      <c r="A161" s="7">
         <v>6010000215</v>
       </c>
-      <c r="B161" s="10" t="s">
-        <v>398</v>
-      </c>
-      <c r="C161" s="11"/>
-      <c r="D161" s="10" t="s">
+      <c r="B161" s="8" t="s">
+        <v>401</v>
+      </c>
+      <c r="C161" s="9"/>
+      <c r="D161" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E161" s="10" t="s">
-        <v>399</v>
-      </c>
-      <c r="F161" s="10" t="s">
+      <c r="E161" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="F161" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G161" s="12"/>
-      <c r="H161" s="13">
+      <c r="G161" s="10"/>
+      <c r="H161" s="11">
         <v>1000</v>
       </c>
     </row>
@@ -5645,16 +5660,16 @@
         <v>6010000215</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="C162" s="5">
+        <v>401</v>
+      </c>
+      <c r="C162" s="4">
         <v>46726</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="F162" s="3" t="s">
         <v>3</v>
@@ -5662,47 +5677,47 @@
       <c r="G162" s="6">
         <v>504</v>
       </c>
-      <c r="H162" s="4"/>
+      <c r="H162" s="5"/>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" s="2">
         <v>6010000142</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="C163" s="5">
+        <v>304</v>
+      </c>
+      <c r="C163" s="4">
         <v>46610</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F163" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G163" s="6">
-        <v>250</v>
-      </c>
-      <c r="H163" s="4"/>
+        <v>200</v>
+      </c>
+      <c r="H163" s="5"/>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" s="2">
         <v>6010000143</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="C164" s="5">
+        <v>307</v>
+      </c>
+      <c r="C164" s="4">
         <v>46425</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F164" s="3" t="s">
         <v>3</v>
@@ -5710,23 +5725,23 @@
       <c r="G164" s="6">
         <v>107</v>
       </c>
-      <c r="H164" s="4"/>
+      <c r="H164" s="5"/>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" s="2">
         <v>6010000145</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="C165" s="5">
+        <v>312</v>
+      </c>
+      <c r="C165" s="4">
         <v>46556</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F165" s="3" t="s">
         <v>3</v>
@@ -5734,7 +5749,7 @@
       <c r="G165" s="6">
         <v>179</v>
       </c>
-      <c r="H165" s="4"/>
+      <c r="H165" s="5"/>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" s="2">
@@ -5743,7 +5758,7 @@
       <c r="B166" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C166" s="5">
+      <c r="C166" s="4">
         <v>46446</v>
       </c>
       <c r="D166" s="3" t="s">
@@ -5758,53 +5773,53 @@
       <c r="G166" s="6">
         <v>370</v>
       </c>
-      <c r="H166" s="4"/>
+      <c r="H166" s="5"/>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A167" s="9">
+      <c r="A167" s="2">
         <v>4010013655</v>
       </c>
-      <c r="B167" s="10" t="s">
+      <c r="B167" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C167" s="11"/>
-      <c r="D167" s="10" t="s">
+      <c r="C167" s="4">
+        <v>46550</v>
+      </c>
+      <c r="D167" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E167" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F167" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G167" s="6">
+        <v>670</v>
+      </c>
+      <c r="H167" s="5"/>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A168" s="7">
+        <v>4010013655</v>
+      </c>
+      <c r="B168" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="C168" s="9"/>
+      <c r="D168" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E167" s="10" t="s">
+      <c r="E168" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F167" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G167" s="12"/>
-      <c r="H167" s="13">
+      <c r="F168" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G168" s="10"/>
+      <c r="H168" s="11">
         <v>400</v>
       </c>
-    </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A168" s="2">
-        <v>4010013655</v>
-      </c>
-      <c r="B168" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C168" s="5">
-        <v>46550</v>
-      </c>
-      <c r="D168" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="E168" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F168" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G168" s="6">
-        <v>700</v>
-      </c>
-      <c r="H168" s="4"/>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" s="2">
@@ -5813,8 +5828,8 @@
       <c r="B169" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C169" s="5">
-        <v>46579</v>
+      <c r="C169" s="4">
+        <v>46511</v>
       </c>
       <c r="D169" s="3" t="s">
         <v>52</v>
@@ -5826,9 +5841,9 @@
         <v>5</v>
       </c>
       <c r="G169" s="6">
-        <v>590</v>
-      </c>
-      <c r="H169" s="4"/>
+        <v>290</v>
+      </c>
+      <c r="H169" s="5"/>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" s="2">
@@ -5837,8 +5852,8 @@
       <c r="B170" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C170" s="5">
-        <v>46511</v>
+      <c r="C170" s="4">
+        <v>46579</v>
       </c>
       <c r="D170" s="3" t="s">
         <v>53</v>
@@ -5850,9 +5865,9 @@
         <v>5</v>
       </c>
       <c r="G170" s="6">
-        <v>290</v>
-      </c>
-      <c r="H170" s="4"/>
+        <v>590</v>
+      </c>
+      <c r="H170" s="5"/>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" s="2">
@@ -5861,7 +5876,7 @@
       <c r="B171" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C171" s="5">
+      <c r="C171" s="4">
         <v>46525</v>
       </c>
       <c r="D171" s="3" t="s">
@@ -5876,29 +5891,31 @@
       <c r="G171" s="6">
         <v>1330</v>
       </c>
-      <c r="H171" s="4"/>
+      <c r="H171" s="5"/>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A172" s="9">
+      <c r="A172" s="2">
         <v>6010000087</v>
       </c>
-      <c r="B172" s="10" t="s">
+      <c r="B172" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="C172" s="11"/>
-      <c r="D172" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="E172" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="F172" s="10" t="s">
+      <c r="C172" s="4">
+        <v>46388</v>
+      </c>
+      <c r="D172" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="E172" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="F172" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G172" s="12"/>
-      <c r="H172" s="13">
-        <v>10000</v>
-      </c>
+      <c r="G172" s="6">
+        <v>4400</v>
+      </c>
+      <c r="H172" s="5"/>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" s="2">
@@ -5907,35 +5924,35 @@
       <c r="B173" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="C173" s="5">
-        <v>46388</v>
+      <c r="C173" s="4">
+        <v>46484</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F173" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G173" s="6">
-        <v>4700</v>
-      </c>
-      <c r="H173" s="4"/>
+        <v>10000</v>
+      </c>
+      <c r="H173" s="5"/>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" s="2">
         <v>6010000126</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="C174" s="5">
+        <v>273</v>
+      </c>
+      <c r="C174" s="4">
         <v>46780</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E174" s="3" t="s">
         <v>22</v>
@@ -5946,27 +5963,27 @@
       <c r="G174" s="6">
         <v>5500</v>
       </c>
-      <c r="H174" s="4"/>
+      <c r="H174" s="5"/>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A175" s="9">
+      <c r="A175" s="7">
         <v>6010000126</v>
       </c>
-      <c r="B175" s="10" t="s">
-        <v>271</v>
-      </c>
-      <c r="C175" s="11"/>
-      <c r="D175" s="10" t="s">
+      <c r="B175" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="C175" s="9"/>
+      <c r="D175" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E175" s="10" t="s">
+      <c r="E175" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F175" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G175" s="12"/>
-      <c r="H175" s="13">
+      <c r="F175" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G175" s="10"/>
+      <c r="H175" s="11">
         <v>2000</v>
       </c>
     </row>
@@ -5975,13 +5992,13 @@
         <v>6010000227</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="C176" s="5">
-        <v>46631</v>
+        <v>415</v>
+      </c>
+      <c r="C176" s="4">
+        <v>46645</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="E176" s="3" t="s">
         <v>22</v>
@@ -5990,29 +6007,29 @@
         <v>5</v>
       </c>
       <c r="G176" s="6">
-        <v>4700</v>
-      </c>
-      <c r="H176" s="4"/>
+        <v>2240</v>
+      </c>
+      <c r="H176" s="5"/>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A177" s="9">
+      <c r="A177" s="7">
         <v>6010000227</v>
       </c>
-      <c r="B177" s="10" t="s">
-        <v>412</v>
-      </c>
-      <c r="C177" s="11"/>
-      <c r="D177" s="10" t="s">
+      <c r="B177" s="8" t="s">
+        <v>415</v>
+      </c>
+      <c r="C177" s="9"/>
+      <c r="D177" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E177" s="10" t="s">
+      <c r="E177" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F177" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G177" s="12"/>
-      <c r="H177" s="13">
+      <c r="F177" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G177" s="10"/>
+      <c r="H177" s="11">
         <v>1200</v>
       </c>
     </row>
@@ -6021,13 +6038,13 @@
         <v>6010000227</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="C178" s="5">
-        <v>46645</v>
+        <v>415</v>
+      </c>
+      <c r="C178" s="4">
+        <v>46631</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E178" s="3" t="s">
         <v>22</v>
@@ -6036,25 +6053,25 @@
         <v>5</v>
       </c>
       <c r="G178" s="6">
-        <v>2240</v>
-      </c>
-      <c r="H178" s="4"/>
+        <v>4700</v>
+      </c>
+      <c r="H178" s="5"/>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" s="2">
         <v>6010000088</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="C179" s="5">
+        <v>220</v>
+      </c>
+      <c r="C179" s="4">
         <v>46661</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F179" s="3" t="s">
         <v>3</v>
@@ -6062,27 +6079,27 @@
       <c r="G179" s="6">
         <v>2660</v>
       </c>
-      <c r="H179" s="4"/>
+      <c r="H179" s="5"/>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A180" s="9">
+      <c r="A180" s="7">
         <v>4010013666</v>
       </c>
-      <c r="B180" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="C180" s="11"/>
-      <c r="D180" s="10" t="s">
+      <c r="B180" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="C180" s="9"/>
+      <c r="D180" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E180" s="10" t="s">
+      <c r="E180" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F180" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G180" s="12"/>
-      <c r="H180" s="13">
+      <c r="F180" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G180" s="10"/>
+      <c r="H180" s="11">
         <v>200</v>
       </c>
     </row>
@@ -6091,13 +6108,13 @@
         <v>4010013666</v>
       </c>
       <c r="B181" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C181" s="4">
+        <v>46625</v>
+      </c>
+      <c r="D181" s="3" t="s">
         <v>137</v>
-      </c>
-      <c r="C181" s="5">
-        <v>46625</v>
-      </c>
-      <c r="D181" s="3" t="s">
-        <v>138</v>
       </c>
       <c r="E181" s="3" t="s">
         <v>30</v>
@@ -6108,20 +6125,20 @@
       <c r="G181" s="6">
         <v>100</v>
       </c>
-      <c r="H181" s="4"/>
+      <c r="H181" s="5"/>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" s="2">
         <v>4010013666</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="C182" s="5">
+        <v>136</v>
+      </c>
+      <c r="C182" s="4">
         <v>46593</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E182" s="3" t="s">
         <v>30</v>
@@ -6132,20 +6149,20 @@
       <c r="G182" s="6">
         <v>200</v>
       </c>
-      <c r="H182" s="4"/>
+      <c r="H182" s="5"/>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" s="2">
         <v>6010000128</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="C183" s="5">
+        <v>275</v>
+      </c>
+      <c r="C183" s="4">
         <v>46721</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E183" s="3" t="s">
         <v>30</v>
@@ -6156,88 +6173,88 @@
       <c r="G183" s="6">
         <v>640</v>
       </c>
-      <c r="H183" s="4"/>
+      <c r="H183" s="5"/>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A184" s="9">
+      <c r="A184" s="7">
         <v>6010000128</v>
       </c>
-      <c r="B184" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="C184" s="11"/>
-      <c r="D184" s="10" t="s">
+      <c r="B184" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="C184" s="9"/>
+      <c r="D184" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E184" s="10" t="s">
+      <c r="E184" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F184" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G184" s="12"/>
-      <c r="H184" s="13">
+      <c r="F184" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G184" s="10"/>
+      <c r="H184" s="11">
         <v>300</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A185" s="2">
+      <c r="A185" s="7">
         <v>6010000129</v>
       </c>
-      <c r="B185" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="C185" s="5">
+      <c r="B185" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="C185" s="9"/>
+      <c r="D185" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E185" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F185" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G185" s="10"/>
+      <c r="H185" s="11">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A186" s="2">
+        <v>6010000129</v>
+      </c>
+      <c r="B186" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="C186" s="4">
         <v>46569</v>
       </c>
-      <c r="D185" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="E185" s="3" t="s">
+      <c r="D186" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="E186" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F185" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G185" s="6">
+      <c r="F186" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G186" s="6">
         <v>50</v>
       </c>
-      <c r="H185" s="4"/>
-    </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A186" s="9">
-        <v>6010000129</v>
-      </c>
-      <c r="B186" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="C186" s="11"/>
-      <c r="D186" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="E186" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F186" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G186" s="12"/>
-      <c r="H186" s="13">
-        <v>480</v>
-      </c>
+      <c r="H186" s="5"/>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187" s="2">
         <v>6010000129</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="C187" s="5">
+        <v>277</v>
+      </c>
+      <c r="C187" s="4">
         <v>46758</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E187" s="3" t="s">
         <v>15</v>
@@ -6248,20 +6265,20 @@
       <c r="G187" s="6">
         <v>700</v>
       </c>
-      <c r="H187" s="4"/>
+      <c r="H187" s="5"/>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" s="2">
         <v>6010000130</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="C188" s="5">
-        <v>46753</v>
+        <v>280</v>
+      </c>
+      <c r="C188" s="4">
+        <v>46569</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E188" s="3" t="s">
         <v>30</v>
@@ -6270,68 +6287,68 @@
         <v>5</v>
       </c>
       <c r="G188" s="6">
+        <v>20</v>
+      </c>
+      <c r="H188" s="5"/>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A189" s="2">
+        <v>6010000130</v>
+      </c>
+      <c r="B189" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="C189" s="4">
+        <v>46753</v>
+      </c>
+      <c r="D189" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="E189" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F189" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G189" s="6">
         <v>630</v>
       </c>
-      <c r="H188" s="4"/>
-    </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A189" s="9">
+      <c r="H189" s="5"/>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A190" s="7">
         <v>6010000130</v>
       </c>
-      <c r="B189" s="10" t="s">
-        <v>278</v>
-      </c>
-      <c r="C189" s="11"/>
-      <c r="D189" s="10" t="s">
+      <c r="B190" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="C190" s="9"/>
+      <c r="D190" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E189" s="10" t="s">
+      <c r="E190" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F189" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G189" s="12"/>
-      <c r="H189" s="13">
+      <c r="F190" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G190" s="10"/>
+      <c r="H190" s="11">
         <v>300</v>
       </c>
-    </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A190" s="2">
-        <v>6010000130</v>
-      </c>
-      <c r="B190" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="C190" s="5">
-        <v>46569</v>
-      </c>
-      <c r="D190" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="E190" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F190" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G190" s="6">
-        <v>20</v>
-      </c>
-      <c r="H190" s="4"/>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" s="2">
         <v>6010000198</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="C191" s="5">
+        <v>385</v>
+      </c>
+      <c r="C191" s="4">
         <v>46568</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="E191" s="3" t="s">
         <v>8</v>
@@ -6342,7 +6359,7 @@
       <c r="G191" s="6">
         <v>600</v>
       </c>
-      <c r="H191" s="4"/>
+      <c r="H191" s="5"/>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192" s="2">
@@ -6351,14 +6368,14 @@
       <c r="B192" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C192" s="5">
+      <c r="C192" s="4">
         <v>46537</v>
       </c>
       <c r="D192" s="3" t="s">
         <v>99</v>
       </c>
       <c r="E192" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F192" s="3" t="s">
         <v>5</v>
@@ -6366,7 +6383,7 @@
       <c r="G192" s="6">
         <v>1280</v>
       </c>
-      <c r="H192" s="4"/>
+      <c r="H192" s="5"/>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" s="2">
@@ -6375,7 +6392,7 @@
       <c r="B193" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C193" s="5">
+      <c r="C193" s="4">
         <v>46537</v>
       </c>
       <c r="D193" s="3" t="s">
@@ -6390,7 +6407,7 @@
       <c r="G193" s="6">
         <v>140</v>
       </c>
-      <c r="H193" s="4"/>
+      <c r="H193" s="5"/>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" s="2">
@@ -6399,7 +6416,7 @@
       <c r="B194" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C194" s="5">
+      <c r="C194" s="4">
         <v>46525</v>
       </c>
       <c r="D194" s="3" t="s">
@@ -6414,7 +6431,7 @@
       <c r="G194" s="6">
         <v>980</v>
       </c>
-      <c r="H194" s="4"/>
+      <c r="H194" s="5"/>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" s="2">
@@ -6423,7 +6440,7 @@
       <c r="B195" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C195" s="5">
+      <c r="C195" s="4">
         <v>46442</v>
       </c>
       <c r="D195" s="3" t="s">
@@ -6436,9 +6453,9 @@
         <v>5</v>
       </c>
       <c r="G195" s="6">
-        <v>460</v>
-      </c>
-      <c r="H195" s="4"/>
+        <v>420</v>
+      </c>
+      <c r="H195" s="5"/>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" s="2">
@@ -6447,7 +6464,7 @@
       <c r="B196" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C196" s="5">
+      <c r="C196" s="4">
         <v>46423</v>
       </c>
       <c r="D196" s="3" t="s">
@@ -6462,7 +6479,7 @@
       <c r="G196" s="6">
         <v>500</v>
       </c>
-      <c r="H196" s="4"/>
+      <c r="H196" s="5"/>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" s="2">
@@ -6471,7 +6488,7 @@
       <c r="B197" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C197" s="5">
+      <c r="C197" s="4">
         <v>46545</v>
       </c>
       <c r="D197" s="3" t="s">
@@ -6484,9 +6501,9 @@
         <v>5</v>
       </c>
       <c r="G197" s="6">
-        <v>660</v>
-      </c>
-      <c r="H197" s="4"/>
+        <v>600</v>
+      </c>
+      <c r="H197" s="5"/>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" s="2">
@@ -6495,7 +6512,7 @@
       <c r="B198" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C198" s="5">
+      <c r="C198" s="4">
         <v>46582</v>
       </c>
       <c r="D198" s="3" t="s">
@@ -6510,7 +6527,7 @@
       <c r="G198" s="6">
         <v>3000</v>
       </c>
-      <c r="H198" s="4"/>
+      <c r="H198" s="5"/>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" s="2">
@@ -6519,8 +6536,8 @@
       <c r="B199" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C199" s="5">
-        <v>46419</v>
+      <c r="C199" s="4">
+        <v>46594</v>
       </c>
       <c r="D199" s="3" t="s">
         <v>63</v>
@@ -6532,9 +6549,9 @@
         <v>5</v>
       </c>
       <c r="G199" s="6">
-        <v>200</v>
-      </c>
-      <c r="H199" s="4"/>
+        <v>400</v>
+      </c>
+      <c r="H199" s="5"/>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" s="2">
@@ -6543,8 +6560,8 @@
       <c r="B200" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C200" s="5">
-        <v>46594</v>
+      <c r="C200" s="4">
+        <v>46419</v>
       </c>
       <c r="D200" s="3" t="s">
         <v>64</v>
@@ -6556,9 +6573,9 @@
         <v>5</v>
       </c>
       <c r="G200" s="6">
-        <v>400</v>
-      </c>
-      <c r="H200" s="4"/>
+        <v>200</v>
+      </c>
+      <c r="H200" s="5"/>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" s="2">
@@ -6567,7 +6584,7 @@
       <c r="B201" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C201" s="5">
+      <c r="C201" s="4">
         <v>46536</v>
       </c>
       <c r="D201" s="3" t="s">
@@ -6582,20 +6599,20 @@
       <c r="G201" s="6">
         <v>320</v>
       </c>
-      <c r="H201" s="4"/>
+      <c r="H201" s="5"/>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202" s="2">
         <v>4010013700</v>
       </c>
       <c r="B202" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C202" s="4">
+        <v>46446</v>
+      </c>
+      <c r="D202" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="C202" s="5">
-        <v>46446</v>
-      </c>
-      <c r="D202" s="3" t="s">
-        <v>152</v>
       </c>
       <c r="E202" s="3" t="s">
         <v>4</v>
@@ -6606,20 +6623,20 @@
       <c r="G202" s="6">
         <v>560</v>
       </c>
-      <c r="H202" s="4"/>
+      <c r="H202" s="5"/>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203" s="2">
         <v>4010013700</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="C203" s="5">
+        <v>150</v>
+      </c>
+      <c r="C203" s="4">
         <v>46533</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E203" s="3" t="s">
         <v>4</v>
@@ -6630,20 +6647,20 @@
       <c r="G203" s="6">
         <v>300</v>
       </c>
-      <c r="H203" s="4"/>
+      <c r="H203" s="5"/>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204" s="2">
         <v>4010013701</v>
       </c>
       <c r="B204" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C204" s="4">
+        <v>46589</v>
+      </c>
+      <c r="D204" s="3" t="s">
         <v>154</v>
-      </c>
-      <c r="C204" s="5">
-        <v>46589</v>
-      </c>
-      <c r="D204" s="3" t="s">
-        <v>155</v>
       </c>
       <c r="E204" s="3" t="s">
         <v>4</v>
@@ -6654,7 +6671,7 @@
       <c r="G204" s="6">
         <v>1160</v>
       </c>
-      <c r="H204" s="4"/>
+      <c r="H204" s="5"/>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205" s="2">
@@ -6663,7 +6680,7 @@
       <c r="B205" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C205" s="5">
+      <c r="C205" s="4">
         <v>46513</v>
       </c>
       <c r="D205" s="3" t="s">
@@ -6678,27 +6695,27 @@
       <c r="G205" s="6">
         <v>800</v>
       </c>
-      <c r="H205" s="4"/>
+      <c r="H205" s="5"/>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A206" s="9">
+      <c r="A206" s="7">
         <v>4010013657</v>
       </c>
-      <c r="B206" s="10" t="s">
+      <c r="B206" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="C206" s="11"/>
-      <c r="D206" s="10" t="s">
+      <c r="C206" s="9"/>
+      <c r="D206" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E206" s="10" t="s">
+      <c r="E206" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F206" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G206" s="12"/>
-      <c r="H206" s="13">
+      <c r="F206" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G206" s="10"/>
+      <c r="H206" s="11">
         <v>160</v>
       </c>
     </row>
@@ -6709,8 +6726,8 @@
       <c r="B207" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="C207" s="5">
-        <v>46563</v>
+      <c r="C207" s="4">
+        <v>46587</v>
       </c>
       <c r="D207" s="3" t="s">
         <v>125</v>
@@ -6722,70 +6739,70 @@
         <v>5</v>
       </c>
       <c r="G207" s="6">
-        <v>70</v>
-      </c>
-      <c r="H207" s="4"/>
+        <v>1170</v>
+      </c>
+      <c r="H207" s="5"/>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208" s="2">
-        <v>4010013658</v>
+        <v>4010013548</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="C208" s="5">
-        <v>46587</v>
+        <v>68</v>
+      </c>
+      <c r="C208" s="4">
+        <v>46469</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>126</v>
+        <v>69</v>
       </c>
       <c r="E208" s="3" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="F208" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G208" s="6">
-        <v>1200</v>
-      </c>
-      <c r="H208" s="4"/>
+        <v>830</v>
+      </c>
+      <c r="H208" s="5"/>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" s="2">
-        <v>4010013548</v>
+        <v>4010013480</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C209" s="5">
-        <v>46469</v>
+        <v>66</v>
+      </c>
+      <c r="C209" s="4">
+        <v>46408</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E209" s="3" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="F209" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G209" s="6">
-        <v>830</v>
-      </c>
-      <c r="H209" s="4"/>
+        <v>1230</v>
+      </c>
+      <c r="H209" s="5"/>
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210" s="2">
-        <v>4010013480</v>
+        <v>4010013477</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C210" s="5">
-        <v>46408</v>
+        <v>58</v>
+      </c>
+      <c r="C210" s="4">
+        <v>46574</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="E210" s="3" t="s">
         <v>8</v>
@@ -6794,260 +6811,260 @@
         <v>5</v>
       </c>
       <c r="G210" s="6">
-        <v>1230</v>
-      </c>
-      <c r="H210" s="4"/>
+        <v>680</v>
+      </c>
+      <c r="H210" s="5"/>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211" s="2">
-        <v>4010013477</v>
+        <v>6010000131</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C211" s="5">
-        <v>46574</v>
+        <v>283</v>
+      </c>
+      <c r="C211" s="4">
+        <v>46784</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>59</v>
+        <v>284</v>
       </c>
       <c r="E211" s="3" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F211" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G211" s="6">
-        <v>780</v>
-      </c>
-      <c r="H211" s="4"/>
+        <v>1960</v>
+      </c>
+      <c r="H211" s="5"/>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212" s="2">
-        <v>6010000131</v>
+        <v>4010013699</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="C212" s="5">
-        <v>46784</v>
+        <v>148</v>
+      </c>
+      <c r="C212" s="4">
+        <v>46438</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>282</v>
+        <v>149</v>
       </c>
       <c r="E212" s="3" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F212" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G212" s="6">
-        <v>2060</v>
-      </c>
-      <c r="H212" s="4"/>
+        <v>350</v>
+      </c>
+      <c r="H212" s="5"/>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213" s="2">
-        <v>4010013699</v>
+        <v>6010000089</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="C213" s="5">
-        <v>46438</v>
+        <v>223</v>
+      </c>
+      <c r="C213" s="4">
+        <v>46871</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>150</v>
+        <v>224</v>
       </c>
       <c r="E213" s="3" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="F213" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G213" s="6">
-        <v>350</v>
-      </c>
-      <c r="H213" s="4"/>
+        <v>2300</v>
+      </c>
+      <c r="H213" s="5"/>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214" s="2">
         <v>6010000089</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="C214" s="5">
-        <v>46871</v>
+        <v>223</v>
+      </c>
+      <c r="C214" s="4">
+        <v>46424</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E214" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F214" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G214" s="6">
-        <v>2300</v>
-      </c>
-      <c r="H214" s="4"/>
+        <v>2360</v>
+      </c>
+      <c r="H214" s="5"/>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A215" s="2">
-        <v>6010000089</v>
+        <v>6010000132</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="C215" s="5">
-        <v>46424</v>
+        <v>285</v>
+      </c>
+      <c r="C215" s="4">
+        <v>46614</v>
       </c>
       <c r="D215" s="3" t="s">
-        <v>225</v>
+        <v>2</v>
       </c>
       <c r="E215" s="3" t="s">
-        <v>224</v>
+        <v>30</v>
       </c>
       <c r="F215" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G215" s="6">
-        <v>2360</v>
-      </c>
-      <c r="H215" s="4"/>
+        <v>2860</v>
+      </c>
+      <c r="H215" s="5"/>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A216" s="2">
-        <v>6010000132</v>
+        <v>6010000146</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="C216" s="5">
-        <v>46614</v>
+        <v>315</v>
+      </c>
+      <c r="C216" s="4">
+        <v>46746</v>
       </c>
       <c r="D216" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="E216" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="F216" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G216" s="6">
+        <v>480</v>
+      </c>
+      <c r="H216" s="5"/>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A217" s="7">
+        <v>6010000146</v>
+      </c>
+      <c r="B217" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="C217" s="9"/>
+      <c r="D217" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E216" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F216" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G216" s="6">
-        <v>2860</v>
-      </c>
-      <c r="H216" s="4"/>
-    </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A217" s="2">
-        <v>6010000146</v>
-      </c>
-      <c r="B217" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="C217" s="5">
-        <v>46746</v>
-      </c>
-      <c r="D217" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="E217" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="F217" s="3" t="s">
+      <c r="E217" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="F217" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G217" s="6">
+      <c r="G217" s="10"/>
+      <c r="H217" s="11">
         <v>480</v>
       </c>
-      <c r="H217" s="4"/>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A218" s="9">
-        <v>6010000146</v>
-      </c>
-      <c r="B218" s="10" t="s">
-        <v>313</v>
-      </c>
-      <c r="C218" s="11"/>
-      <c r="D218" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="E218" s="10" t="s">
-        <v>315</v>
-      </c>
-      <c r="F218" s="10" t="s">
+      <c r="A218" s="2">
+        <v>6010000090</v>
+      </c>
+      <c r="B218" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C218" s="4">
+        <v>46482</v>
+      </c>
+      <c r="D218" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="E218" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F218" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G218" s="12"/>
-      <c r="H218" s="13">
-        <v>480</v>
-      </c>
+      <c r="G218" s="6">
+        <v>4420</v>
+      </c>
+      <c r="H218" s="5"/>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" s="2">
-        <v>6010000090</v>
+        <v>6010000199</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="C219" s="5">
-        <v>46482</v>
+        <v>387</v>
+      </c>
+      <c r="C219" s="4">
+        <v>46556</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>227</v>
+        <v>388</v>
       </c>
       <c r="E219" s="3" t="s">
-        <v>176</v>
+        <v>22</v>
       </c>
       <c r="F219" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G219" s="6">
-        <v>4450</v>
-      </c>
-      <c r="H219" s="4"/>
+        <v>1680</v>
+      </c>
+      <c r="H219" s="5"/>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A220" s="2">
-        <v>6010000199</v>
+        <v>6010000133</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="C220" s="5">
-        <v>46556</v>
+        <v>286</v>
+      </c>
+      <c r="C220" s="4">
+        <v>46388</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>385</v>
+        <v>287</v>
       </c>
       <c r="E220" s="3" t="s">
-        <v>22</v>
+        <v>87</v>
       </c>
       <c r="F220" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G220" s="6">
-        <v>1680</v>
-      </c>
-      <c r="H220" s="4"/>
+        <v>1100</v>
+      </c>
+      <c r="H220" s="5"/>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221" s="2">
-        <v>6010000133</v>
+        <v>6010000134</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="C221" s="5">
-        <v>46388</v>
+        <v>288</v>
+      </c>
+      <c r="C221" s="4">
+        <v>46488</v>
       </c>
       <c r="D221" s="3" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="E221" s="3" t="s">
         <v>87</v>
@@ -7056,22 +7073,22 @@
         <v>5</v>
       </c>
       <c r="G221" s="6">
-        <v>1200</v>
-      </c>
-      <c r="H221" s="4"/>
+        <v>1180</v>
+      </c>
+      <c r="H221" s="5"/>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A222" s="2">
-        <v>6010000134</v>
+        <v>6010000135</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="C222" s="5">
-        <v>46488</v>
+        <v>290</v>
+      </c>
+      <c r="C222" s="4">
+        <v>46388</v>
       </c>
       <c r="D222" s="3" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="E222" s="3" t="s">
         <v>87</v>
@@ -7080,46 +7097,46 @@
         <v>5</v>
       </c>
       <c r="G222" s="6">
-        <v>1180</v>
-      </c>
-      <c r="H222" s="4"/>
+        <v>1560</v>
+      </c>
+      <c r="H222" s="5"/>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A223" s="2">
-        <v>6010000135</v>
+        <v>6010000136</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="C223" s="5">
-        <v>46388</v>
+        <v>292</v>
+      </c>
+      <c r="C223" s="4">
+        <v>46496</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E223" s="3" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="F223" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G223" s="6">
-        <v>1560</v>
-      </c>
-      <c r="H223" s="4"/>
+        <v>530</v>
+      </c>
+      <c r="H223" s="5"/>
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A224" s="2">
-        <v>6010000136</v>
+        <v>6010000137</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="C224" s="5">
+        <v>294</v>
+      </c>
+      <c r="C224" s="4">
         <v>46496</v>
       </c>
       <c r="D224" s="3" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="E224" s="3" t="s">
         <v>30</v>
@@ -7128,142 +7145,142 @@
         <v>5</v>
       </c>
       <c r="G224" s="6">
-        <v>730</v>
-      </c>
-      <c r="H224" s="4"/>
+        <v>370</v>
+      </c>
+      <c r="H224" s="5"/>
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A225" s="2">
-        <v>6010000137</v>
+        <v>4010013269</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="C225" s="5">
-        <v>46496</v>
+        <v>20</v>
+      </c>
+      <c r="C225" s="4">
+        <v>46558</v>
       </c>
       <c r="D225" s="3" t="s">
-        <v>293</v>
+        <v>21</v>
       </c>
       <c r="E225" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F225" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G225" s="6">
-        <v>570</v>
-      </c>
-      <c r="H225" s="4"/>
+        <v>900</v>
+      </c>
+      <c r="H225" s="5"/>
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226" s="2">
-        <v>4010013269</v>
+        <v>6010000177</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C226" s="5">
-        <v>46558</v>
+        <v>362</v>
+      </c>
+      <c r="C226" s="4">
+        <v>46971</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>21</v>
+        <v>363</v>
       </c>
       <c r="E226" s="3" t="s">
-        <v>22</v>
+        <v>364</v>
       </c>
       <c r="F226" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G226" s="6">
-        <v>900</v>
-      </c>
-      <c r="H226" s="4"/>
+        <v>2880</v>
+      </c>
+      <c r="H226" s="5"/>
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A227" s="2">
-        <v>6010000177</v>
+        <v>6010000178</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="C227" s="5">
-        <v>46971</v>
+        <v>365</v>
+      </c>
+      <c r="C227" s="4">
+        <v>47087</v>
       </c>
       <c r="D227" s="3" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="E227" s="3" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="F227" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G227" s="6">
-        <v>2980</v>
-      </c>
-      <c r="H227" s="4"/>
+        <v>1140</v>
+      </c>
+      <c r="H227" s="5"/>
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228" s="2">
-        <v>6010000178</v>
+        <v>4010013597</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="C228" s="5">
-        <v>47087</v>
+        <v>115</v>
+      </c>
+      <c r="C228" s="4">
+        <v>46525</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>363</v>
+        <v>116</v>
       </c>
       <c r="E228" s="3" t="s">
-        <v>364</v>
+        <v>10</v>
       </c>
       <c r="F228" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G228" s="6">
-        <v>1260</v>
-      </c>
-      <c r="H228" s="4"/>
+        <v>620</v>
+      </c>
+      <c r="H228" s="5"/>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A229" s="2">
-        <v>4010013597</v>
+        <v>4010013368</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C229" s="5">
-        <v>46525</v>
+        <v>32</v>
+      </c>
+      <c r="C229" s="4">
+        <v>46533</v>
       </c>
       <c r="D229" s="3" t="s">
-        <v>116</v>
+        <v>33</v>
       </c>
       <c r="E229" s="3" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F229" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G229" s="6">
-        <v>620</v>
-      </c>
-      <c r="H229" s="4"/>
+        <v>160</v>
+      </c>
+      <c r="H229" s="5"/>
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A230" s="2">
-        <v>4010013368</v>
+        <v>4010013369</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C230" s="5">
+        <v>34</v>
+      </c>
+      <c r="C230" s="4">
         <v>46533</v>
       </c>
       <c r="D230" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E230" s="3" t="s">
         <v>4</v>
@@ -7272,9 +7289,9 @@
         <v>5</v>
       </c>
       <c r="G230" s="6">
-        <v>160</v>
-      </c>
-      <c r="H230" s="4"/>
+        <v>80</v>
+      </c>
+      <c r="H230" s="5"/>
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A231" s="2">
@@ -7283,11 +7300,11 @@
       <c r="B231" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C231" s="5">
+      <c r="C231" s="4">
         <v>46429</v>
       </c>
       <c r="D231" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E231" s="3" t="s">
         <v>4</v>
@@ -7298,136 +7315,134 @@
       <c r="G231" s="6">
         <v>340</v>
       </c>
-      <c r="H231" s="4"/>
+      <c r="H231" s="5"/>
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A232" s="2">
-        <v>4010013369</v>
+        <v>4010013399</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C232" s="5">
-        <v>46533</v>
+        <v>42</v>
+      </c>
+      <c r="C232" s="4">
+        <v>46532</v>
       </c>
       <c r="D232" s="3" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E232" s="3" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F232" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G232" s="6">
-        <v>80</v>
-      </c>
-      <c r="H232" s="4"/>
+        <v>1290</v>
+      </c>
+      <c r="H232" s="5"/>
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A233" s="2">
-        <v>4010013399</v>
+        <v>6010000203</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C233" s="5">
-        <v>46532</v>
+        <v>394</v>
+      </c>
+      <c r="C233" s="4">
+        <v>46606</v>
       </c>
       <c r="D233" s="3" t="s">
-        <v>43</v>
+        <v>395</v>
       </c>
       <c r="E233" s="3" t="s">
-        <v>22</v>
+        <v>391</v>
       </c>
       <c r="F233" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G233" s="6">
-        <v>1290</v>
-      </c>
-      <c r="H233" s="4"/>
+        <v>460</v>
+      </c>
+      <c r="H233" s="5"/>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A234" s="2">
-        <v>6010000203</v>
+        <v>4010013592</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="C234" s="5">
-        <v>46606</v>
+        <v>104</v>
+      </c>
+      <c r="C234" s="4">
+        <v>46514</v>
       </c>
       <c r="D234" s="3" t="s">
-        <v>392</v>
+        <v>105</v>
       </c>
       <c r="E234" s="3" t="s">
-        <v>388</v>
+        <v>106</v>
       </c>
       <c r="F234" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G234" s="6">
-        <v>460</v>
-      </c>
-      <c r="H234" s="4"/>
+        <v>240</v>
+      </c>
+      <c r="H234" s="5"/>
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A235" s="2">
-        <v>4010013592</v>
+        <v>4010014926</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="C235" s="5">
-        <v>46514</v>
+        <v>159</v>
+      </c>
+      <c r="C235" s="4">
+        <v>46768</v>
       </c>
       <c r="D235" s="3" t="s">
-        <v>105</v>
+        <v>160</v>
       </c>
       <c r="E235" s="3" t="s">
-        <v>106</v>
+        <v>161</v>
       </c>
       <c r="F235" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G235" s="6">
-        <v>240</v>
-      </c>
-      <c r="H235" s="4"/>
+        <v>780</v>
+      </c>
+      <c r="H235" s="5"/>
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A236" s="2">
-        <v>4010014926</v>
+        <v>7050000020</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C236" s="5">
-        <v>46768</v>
-      </c>
+        <v>448</v>
+      </c>
+      <c r="C236" s="4"/>
       <c r="D236" s="3" t="s">
-        <v>161</v>
+        <v>2</v>
       </c>
       <c r="E236" s="3" t="s">
-        <v>162</v>
+        <v>2</v>
       </c>
       <c r="F236" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G236" s="6">
-        <v>780</v>
-      </c>
-      <c r="H236" s="4"/>
+        <v>30</v>
+      </c>
+      <c r="H236" s="5"/>
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A237" s="2">
         <v>7050000020</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>445</v>
-      </c>
-      <c r="C237" s="5"/>
+        <v>448</v>
+      </c>
+      <c r="C237" s="4"/>
       <c r="D237" s="3" t="s">
         <v>2</v>
       </c>
@@ -7440,53 +7455,55 @@
       <c r="G237" s="6">
         <v>70</v>
       </c>
-      <c r="H237" s="4"/>
+      <c r="H237" s="5"/>
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238" s="2">
-        <v>7050000020</v>
+        <v>4010013659</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>445</v>
-      </c>
-      <c r="C238" s="5"/>
+        <v>126</v>
+      </c>
+      <c r="C238" s="4">
+        <v>46526</v>
+      </c>
       <c r="D238" s="3" t="s">
-        <v>2</v>
+        <v>127</v>
       </c>
       <c r="E238" s="3" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F238" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G238" s="6">
-        <v>30</v>
-      </c>
-      <c r="H238" s="4"/>
+        <v>1270</v>
+      </c>
+      <c r="H238" s="5"/>
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A239" s="2">
-        <v>4010013659</v>
+        <v>4010013273</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C239" s="5">
-        <v>46526</v>
+        <v>28</v>
+      </c>
+      <c r="C239" s="4">
+        <v>46444</v>
       </c>
       <c r="D239" s="3" t="s">
-        <v>128</v>
+        <v>29</v>
       </c>
       <c r="E239" s="3" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F239" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G239" s="6">
-        <v>1370</v>
-      </c>
-      <c r="H239" s="4"/>
+        <v>710</v>
+      </c>
+      <c r="H239" s="5"/>
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A240" s="2">
@@ -7495,11 +7512,11 @@
       <c r="B240" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C240" s="5">
+      <c r="C240" s="4">
         <v>46444</v>
       </c>
       <c r="D240" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E240" s="3" t="s">
         <v>30</v>
@@ -7508,46 +7525,46 @@
         <v>5</v>
       </c>
       <c r="G240" s="6">
-        <v>710</v>
-      </c>
-      <c r="H240" s="4"/>
+        <v>20</v>
+      </c>
+      <c r="H240" s="5"/>
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A241" s="2">
-        <v>4010013273</v>
+        <v>4010013271</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C241" s="5">
-        <v>46444</v>
+        <v>23</v>
+      </c>
+      <c r="C241" s="4">
+        <v>46402</v>
       </c>
       <c r="D241" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="E241" s="3" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F241" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G241" s="6">
-        <v>70</v>
-      </c>
-      <c r="H241" s="4"/>
+        <v>300</v>
+      </c>
+      <c r="H241" s="5"/>
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242" s="2">
-        <v>4010013271</v>
+        <v>4010013272</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C242" s="5">
-        <v>46402</v>
+        <v>25</v>
+      </c>
+      <c r="C242" s="4">
+        <v>46523</v>
       </c>
       <c r="D242" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E242" s="3" t="s">
         <v>8</v>
@@ -7556,9 +7573,9 @@
         <v>5</v>
       </c>
       <c r="G242" s="6">
-        <v>300</v>
-      </c>
-      <c r="H242" s="4"/>
+        <v>1100</v>
+      </c>
+      <c r="H242" s="5"/>
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A243" s="2">
@@ -7567,11 +7584,11 @@
       <c r="B243" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C243" s="5">
+      <c r="C243" s="4">
         <v>46594</v>
       </c>
       <c r="D243" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E243" s="3" t="s">
         <v>8</v>
@@ -7582,20 +7599,20 @@
       <c r="G243" s="6">
         <v>360</v>
       </c>
-      <c r="H243" s="4"/>
+      <c r="H243" s="5"/>
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A244" s="2">
-        <v>4010013272</v>
+        <v>4010013663</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C244" s="5">
-        <v>46523</v>
+        <v>133</v>
+      </c>
+      <c r="C244" s="4">
+        <v>46612</v>
       </c>
       <c r="D244" s="3" t="s">
-        <v>27</v>
+        <v>134</v>
       </c>
       <c r="E244" s="3" t="s">
         <v>8</v>
@@ -7604,19 +7621,19 @@
         <v>5</v>
       </c>
       <c r="G244" s="6">
-        <v>1100</v>
-      </c>
-      <c r="H244" s="4"/>
+        <v>1200</v>
+      </c>
+      <c r="H244" s="5"/>
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A245" s="2">
         <v>4010013663</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="C245" s="5">
-        <v>46612</v>
+        <v>133</v>
+      </c>
+      <c r="C245" s="4">
+        <v>46514</v>
       </c>
       <c r="D245" s="3" t="s">
         <v>135</v>
@@ -7628,49 +7645,49 @@
         <v>5</v>
       </c>
       <c r="G245" s="6">
-        <v>1200</v>
-      </c>
-      <c r="H245" s="4"/>
+        <v>100</v>
+      </c>
+      <c r="H245" s="5"/>
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A246" s="2">
-        <v>4010013663</v>
+        <v>6010000093</v>
       </c>
       <c r="B246" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="C246" s="5">
-        <v>46514</v>
+        <v>229</v>
+      </c>
+      <c r="C246" s="4">
+        <v>46484</v>
       </c>
       <c r="D246" s="3" t="s">
-        <v>136</v>
+        <v>230</v>
       </c>
       <c r="E246" s="3" t="s">
-        <v>8</v>
+        <v>231</v>
       </c>
       <c r="F246" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G246" s="6">
-        <v>200</v>
-      </c>
-      <c r="H246" s="4"/>
+        <v>33000</v>
+      </c>
+      <c r="H246" s="5"/>
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A247" s="2">
         <v>6010000093</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="C247" s="5">
+        <v>229</v>
+      </c>
+      <c r="C247" s="4">
         <v>46504</v>
       </c>
       <c r="D247" s="3" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E247" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F247" s="3" t="s">
         <v>3</v>
@@ -7678,106 +7695,60 @@
       <c r="G247" s="6">
         <v>15000</v>
       </c>
-      <c r="H247" s="4"/>
+      <c r="H247" s="5"/>
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A248" s="9">
-        <v>6010000093</v>
-      </c>
-      <c r="B248" s="10" t="s">
-        <v>228</v>
-      </c>
-      <c r="C248" s="11"/>
-      <c r="D248" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="E248" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="F248" s="10" t="s">
+      <c r="A248" s="2">
+        <v>6010000161</v>
+      </c>
+      <c r="B248" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="C248" s="4">
+        <v>47087</v>
+      </c>
+      <c r="D248" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="E248" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="F248" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G248" s="12"/>
-      <c r="H248" s="13">
-        <v>18000</v>
-      </c>
+      <c r="G248" s="6">
+        <v>666</v>
+      </c>
+      <c r="H248" s="5"/>
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A249" s="2">
-        <v>6010000093</v>
+        <v>6010000162</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="C249" s="5">
-        <v>46484</v>
+        <v>343</v>
+      </c>
+      <c r="C249" s="4">
+        <v>47087</v>
       </c>
       <c r="D249" s="3" t="s">
-        <v>231</v>
+        <v>344</v>
       </c>
       <c r="E249" s="3" t="s">
-        <v>230</v>
+        <v>345</v>
       </c>
       <c r="F249" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G249" s="6">
-        <v>16000</v>
-      </c>
-      <c r="H249" s="4"/>
-    </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A250" s="2">
-        <v>6010000161</v>
-      </c>
-      <c r="B250" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="C250" s="5">
-        <v>47087</v>
-      </c>
-      <c r="D250" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="E250" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="F250" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G250" s="6">
-        <v>696</v>
-      </c>
-      <c r="H250" s="4"/>
-    </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A251" s="2">
-        <v>6010000162</v>
-      </c>
-      <c r="B251" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="C251" s="5">
-        <v>47087</v>
-      </c>
-      <c r="D251" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="E251" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="F251" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G251" s="6">
-        <v>1164</v>
-      </c>
-      <c r="H251" s="4"/>
+        <v>1152</v>
+      </c>
+      <c r="H249" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H251" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H251">
-      <sortCondition ref="B1:B251"/>
+  <autoFilter ref="A1:H249" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H249">
+      <sortCondition ref="B1:B249"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="0" type="noConversion"/>

--- a/KSTOCK.xlsx
+++ b/KSTOCK.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c2e6f8dd72a68295/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="11_C6DA9F49C4094E9AB632FCC5BEBB5E003CBCC164" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{635629A2-7C01-442E-953D-32588DE7AF46}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="11_C77A5E4CC4094E9AB632FCC5BEAE6EC728EA7920" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2FA3125-9E54-4E3D-8A49-C091624C6967}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$249</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$247</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="454">
   <si>
     <t>ROSUSEP-20</t>
   </si>
@@ -55,12 +55,12 @@
     <t>ATROLIA CV 20/75</t>
   </si>
   <si>
+    <t>25S3GCA110</t>
+  </si>
+  <si>
     <t>10X3X10</t>
   </si>
   <si>
-    <t>25S3GCA110</t>
-  </si>
-  <si>
     <t>25S3GCA131</t>
   </si>
   <si>
@@ -112,15 +112,15 @@
     <t>VILDAPHARM-DP</t>
   </si>
   <si>
+    <t>25S3GTA308</t>
+  </si>
+  <si>
+    <t>10X1X10</t>
+  </si>
+  <si>
     <t>25S3GTA311</t>
   </si>
   <si>
-    <t>10X1X10</t>
-  </si>
-  <si>
-    <t>25S3GTA308</t>
-  </si>
-  <si>
     <t>TENEJEET-M 1000</t>
   </si>
   <si>
@@ -130,12 +130,12 @@
     <t>TENEJEET-M 500</t>
   </si>
   <si>
+    <t>25S3GTA221</t>
+  </si>
+  <si>
     <t>25S3GTA657</t>
   </si>
   <si>
-    <t>25S3GTA221</t>
-  </si>
-  <si>
     <t>CHYMOACTIVE-FORTE</t>
   </si>
   <si>
@@ -217,12 +217,12 @@
     <t>25S3GCA138</t>
   </si>
   <si>
+    <t>25S3GCA105</t>
+  </si>
+  <si>
     <t>25S3GCA034</t>
   </si>
   <si>
-    <t>25S3GCA105</t>
-  </si>
-  <si>
     <t>SITAFREE-MET 1000 IR</t>
   </si>
   <si>
@@ -307,12 +307,12 @@
     <t>GLIMKAT-MET 1 (PR)</t>
   </si>
   <si>
+    <t>25S3GTA625</t>
+  </si>
+  <si>
     <t>25S3GTA626</t>
   </si>
   <si>
-    <t>25S3GTA625</t>
-  </si>
-  <si>
     <t>GLIMKAT-MET 2 (PR)</t>
   </si>
   <si>
@@ -325,12 +325,6 @@
     <t>25S3GCA094</t>
   </si>
   <si>
-    <t>ROSUSEP- GOLD 20</t>
-  </si>
-  <si>
-    <t>25S3GCA095</t>
-  </si>
-  <si>
     <t>ROSUSEP-ASP 10</t>
   </si>
   <si>
@@ -427,12 +421,12 @@
     <t>VILDAPHARM-OD 100</t>
   </si>
   <si>
+    <t>25S1GTA463</t>
+  </si>
+  <si>
     <t>25S1GTA780</t>
   </si>
   <si>
-    <t>25S1GTA463</t>
-  </si>
-  <si>
     <t>REBEHIT-LS</t>
   </si>
   <si>
@@ -457,12 +451,12 @@
     <t>ATROLIA GOLD 20/75</t>
   </si>
   <si>
+    <t>25S3GCA129</t>
+  </si>
+  <si>
     <t>25S3GCA113</t>
   </si>
   <si>
-    <t>25S3GCA129</t>
-  </si>
-  <si>
     <t>Atrolia-ASP 75</t>
   </si>
   <si>
@@ -556,30 +550,30 @@
     <t>CEFTAPACE-1G</t>
   </si>
   <si>
+    <t>1X10ML</t>
+  </si>
+  <si>
     <t>NL2742601</t>
   </si>
   <si>
-    <t>1X10ML</t>
-  </si>
-  <si>
     <t>CLAVMYCIN IV</t>
   </si>
   <si>
+    <t>NKCL12502</t>
+  </si>
+  <si>
     <t>10X1X1.2 G(SWFI)</t>
   </si>
   <si>
-    <t>NKCL12502</t>
-  </si>
-  <si>
     <t>DECAHIT INJECTION</t>
   </si>
   <si>
+    <t>96X2ML</t>
+  </si>
+  <si>
     <t>NL2722504</t>
   </si>
   <si>
-    <t>96X2ML</t>
-  </si>
-  <si>
     <t>GENTAHIT INJ</t>
   </si>
   <si>
@@ -598,12 +592,12 @@
     <t>HITCORT 100</t>
   </si>
   <si>
+    <t>NL3926001</t>
+  </si>
+  <si>
     <t>1X7.5ML+SWFI</t>
   </si>
   <si>
-    <t>NL3926001</t>
-  </si>
-  <si>
     <t>IRRONIT INJ</t>
   </si>
   <si>
@@ -658,15 +652,15 @@
     <t>ONMOTRON INJ 2ML</t>
   </si>
   <si>
+    <t>NL2692504</t>
+  </si>
+  <si>
+    <t>20X5X2ML</t>
+  </si>
+  <si>
     <t>NL2692503</t>
   </si>
   <si>
-    <t>20X5X2ML</t>
-  </si>
-  <si>
-    <t>NL2692504</t>
-  </si>
-  <si>
     <t>PANTAHIT IV</t>
   </si>
   <si>
@@ -679,12 +673,12 @@
     <t>RANINIT INJ</t>
   </si>
   <si>
+    <t>NL1442502</t>
+  </si>
+  <si>
     <t>NL1442501</t>
   </si>
   <si>
-    <t>NL1442502</t>
-  </si>
-  <si>
     <t>REBEHIT IV</t>
   </si>
   <si>
@@ -697,15 +691,15 @@
     <t>SYNACORT</t>
   </si>
   <si>
+    <t>NL2682501</t>
+  </si>
+  <si>
+    <t>10X8X1ML</t>
+  </si>
+  <si>
     <t>NL2682502</t>
   </si>
   <si>
-    <t>10X8X1ML</t>
-  </si>
-  <si>
-    <t>NL2682501</t>
-  </si>
-  <si>
     <t>TAZCILLIN-P 4.5 INJ</t>
   </si>
   <si>
@@ -736,15 +730,15 @@
     <t>AMLINA-5 TABLET</t>
   </si>
   <si>
+    <t>T50499A</t>
+  </si>
+  <si>
+    <t>20X30</t>
+  </si>
+  <si>
     <t>T60096A</t>
   </si>
   <si>
-    <t>20X30</t>
-  </si>
-  <si>
-    <t>T50499A</t>
-  </si>
-  <si>
     <t>AMLINA-AT TABLET</t>
   </si>
   <si>
@@ -868,12 +862,12 @@
     <t>RIFIXIEM 550 TABLET</t>
   </si>
   <si>
+    <t>GE545020</t>
+  </si>
+  <si>
     <t>GE545002B</t>
   </si>
   <si>
-    <t>GE545020</t>
-  </si>
-  <si>
     <t>SPASMOSAFE-MF TABLET</t>
   </si>
   <si>
@@ -1147,24 +1141,24 @@
     <t>Faropharm 200 Tablet</t>
   </si>
   <si>
+    <t>CBT26001B</t>
+  </si>
+  <si>
+    <t>CBT26025B</t>
+  </si>
+  <si>
     <t>CBT25115D</t>
   </si>
   <si>
-    <t>CBT26001B</t>
-  </si>
-  <si>
-    <t>CBT26025B</t>
-  </si>
-  <si>
     <t>EPODOX-200 DT Tablet</t>
   </si>
   <si>
+    <t>CT25507F</t>
+  </si>
+  <si>
     <t>CT26107C</t>
   </si>
   <si>
-    <t>CT25507F</t>
-  </si>
-  <si>
     <t>ATROLIA - F TABLET</t>
   </si>
   <si>
@@ -1246,24 +1240,24 @@
     <t>CEFIXLIA-O 200 TABLET</t>
   </si>
   <si>
+    <t>CT26007G</t>
+  </si>
+  <si>
     <t>CT25488B</t>
   </si>
   <si>
-    <t>CT26007G</t>
-  </si>
-  <si>
     <t>MONTALIA-LC 60ML SYRUP</t>
   </si>
   <si>
+    <t>DL602011A</t>
+  </si>
+  <si>
+    <t>60 ML</t>
+  </si>
+  <si>
     <t>DL603008</t>
   </si>
   <si>
-    <t>60 ML</t>
-  </si>
-  <si>
-    <t>DL602011A</t>
-  </si>
-  <si>
     <t>CLAVMYCIN 375 DUO TABLET (20x1x10)</t>
   </si>
   <si>
@@ -1273,18 +1267,15 @@
     <t>REBEHIT DSR CAPSULE</t>
   </si>
   <si>
+    <t>MC2510117</t>
+  </si>
+  <si>
     <t>MC2510116</t>
   </si>
   <si>
-    <t>MC2510117</t>
-  </si>
-  <si>
     <t>PANTAHIT DSR CAPSULE (20x10)</t>
   </si>
   <si>
-    <t>MC2509105A</t>
-  </si>
-  <si>
     <t>MC2509103</t>
   </si>
   <si>
@@ -1300,12 +1291,12 @@
     <t>CEFIXLIA - 200 DT TABLET</t>
   </si>
   <si>
+    <t>CT26039A</t>
+  </si>
+  <si>
     <t>CT25427</t>
   </si>
   <si>
-    <t>CT26039A</t>
-  </si>
-  <si>
     <t>FERRIFINE XT TABLET</t>
   </si>
   <si>
@@ -1393,7 +1384,7 @@
     <t xml:space="preserve"> Unrestricted Qty</t>
   </si>
   <si>
-    <t>Transit Qty</t>
+    <t xml:space="preserve"> Transit Qty</t>
   </si>
 </sst>
 </file>
@@ -1424,13 +1415,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1475,35 +1466,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1839,104 +1830,104 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H249"/>
+  <dimension ref="A1:H247"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="33.77734375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11.88671875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="40.5546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.21875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.21875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.21875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.21875" style="1" customWidth="1"/>
     <col min="8" max="8" width="12" style="1" customWidth="1"/>
     <col min="9" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:8" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>451</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="F1" s="8" t="s">
         <v>449</v>
       </c>
-      <c r="B1" s="12" t="s">
-        <v>450</v>
-      </c>
-      <c r="C1" s="12" t="s">
+      <c r="G1" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="H1" s="7" t="s">
         <v>453</v>
       </c>
-      <c r="D1" s="12" t="s">
-        <v>454</v>
-      </c>
-      <c r="E1" s="12" t="s">
-        <v>451</v>
-      </c>
-      <c r="F1" s="12" t="s">
-        <v>452</v>
-      </c>
-      <c r="G1" s="13" t="s">
-        <v>455</v>
-      </c>
-      <c r="H1" s="12" t="s">
-        <v>456</v>
-      </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
+      <c r="A2" s="2">
         <v>6010000095</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="8" t="s">
+      <c r="B2" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C2" s="5">
+        <v>46568</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="6">
+        <v>3680</v>
+      </c>
+      <c r="H2" s="4"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="9">
+        <v>6010000095</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="C3" s="11"/>
+      <c r="D3" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E3" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="10"/>
-      <c r="H2" s="11">
+      <c r="F3" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="12"/>
+      <c r="H3" s="13">
         <v>3600</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
-        <v>6010000095</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="C3" s="4">
-        <v>46568</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3" s="6">
-        <v>3680</v>
-      </c>
-      <c r="H3" s="5"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>6010000095</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C4" s="5">
+        <v>46559</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>233</v>
-      </c>
-      <c r="C4" s="4">
-        <v>46559</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>235</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>22</v>
@@ -1945,25 +1936,25 @@
         <v>5</v>
       </c>
       <c r="G4" s="6">
-        <v>1200</v>
-      </c>
-      <c r="H4" s="5"/>
+        <v>1100</v>
+      </c>
+      <c r="H4" s="4"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>6010000138</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="C5" s="5">
+        <v>46746</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>296</v>
-      </c>
-      <c r="C5" s="4">
-        <v>46746</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>298</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>3</v>
@@ -1971,23 +1962,23 @@
       <c r="G5" s="6">
         <v>603</v>
       </c>
-      <c r="H5" s="5"/>
+      <c r="H5" s="4"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>4010015107</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="C6" s="4">
+        <v>160</v>
+      </c>
+      <c r="C6" s="5">
         <v>46752</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>5</v>
@@ -1995,7 +1986,7 @@
       <c r="G6" s="6">
         <v>1040</v>
       </c>
-      <c r="H6" s="5"/>
+      <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
@@ -2004,7 +1995,7 @@
       <c r="B7" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="5">
         <v>46548</v>
       </c>
       <c r="D7" s="3" t="s">
@@ -2019,68 +2010,68 @@
       <c r="G7" s="6">
         <v>170</v>
       </c>
-      <c r="H7" s="5"/>
+      <c r="H7" s="4"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>6010000097</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="C8" s="5">
+        <v>46556</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="C8" s="4">
-        <v>46751</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>238</v>
-      </c>
       <c r="F8" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G8" s="6">
-        <v>160</v>
-      </c>
-      <c r="H8" s="5"/>
+        <v>300</v>
+      </c>
+      <c r="H8" s="4"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>6010000097</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="C9" s="5">
+        <v>46751</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="C9" s="4">
-        <v>46556</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>238</v>
-      </c>
       <c r="F9" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G9" s="6">
-        <v>300</v>
-      </c>
-      <c r="H9" s="5"/>
+        <v>160</v>
+      </c>
+      <c r="H9" s="4"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>6010000098</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="C10" s="4">
+        <v>238</v>
+      </c>
+      <c r="C10" s="5">
         <v>46539</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>87</v>
@@ -2091,20 +2082,20 @@
       <c r="G10" s="6">
         <v>1340</v>
       </c>
-      <c r="H10" s="5"/>
+      <c r="H10" s="4"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>6010000195</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="C11" s="4">
+        <v>378</v>
+      </c>
+      <c r="C11" s="5">
         <v>46549</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>22</v>
@@ -2115,7 +2106,7 @@
       <c r="G11" s="6">
         <v>420</v>
       </c>
-      <c r="H11" s="5"/>
+      <c r="H11" s="4"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
@@ -2124,7 +2115,7 @@
       <c r="B12" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="5">
         <v>46568</v>
       </c>
       <c r="D12" s="3" t="s">
@@ -2139,75 +2130,75 @@
       <c r="G12" s="6">
         <v>440</v>
       </c>
-      <c r="H12" s="5"/>
+      <c r="H12" s="4"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="7">
+      <c r="A13" s="9">
         <v>4010013259</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="8" t="s">
+      <c r="C13" s="11"/>
+      <c r="D13" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="F13" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G13" s="10"/>
-      <c r="H13" s="11">
+      <c r="F13" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G13" s="12"/>
+      <c r="H13" s="13">
         <v>240</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="7">
+      <c r="A14" s="2">
         <v>4010013260</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="9"/>
-      <c r="D14" s="8" t="s">
+      <c r="C14" s="5">
+        <v>46568</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="6">
+        <v>510</v>
+      </c>
+      <c r="H14" s="4"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="9">
+        <v>4010013260</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="11"/>
+      <c r="D15" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E14" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="11">
+      <c r="E15" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G15" s="12"/>
+      <c r="H15" s="13">
         <v>20</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
-        <v>4010013260</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="4">
-        <v>46568</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G15" s="6">
-        <v>510</v>
-      </c>
-      <c r="H15" s="5"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
@@ -2216,14 +2207,14 @@
       <c r="B16" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16" s="5">
         <v>46589</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>5</v>
@@ -2231,20 +2222,20 @@
       <c r="G16" s="6">
         <v>1200</v>
       </c>
-      <c r="H16" s="5"/>
+      <c r="H16" s="4"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>4010013692</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="C17" s="4">
+        <v>139</v>
+      </c>
+      <c r="C17" s="5">
         <v>46549</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>8</v>
@@ -2255,20 +2246,20 @@
       <c r="G17" s="6">
         <v>880</v>
       </c>
-      <c r="H17" s="5"/>
+      <c r="H17" s="4"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>4010013693</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="C18" s="4">
-        <v>46549</v>
+        <v>141</v>
+      </c>
+      <c r="C18" s="5">
+        <v>46587</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>8</v>
@@ -2277,22 +2268,22 @@
         <v>5</v>
       </c>
       <c r="G18" s="6">
-        <v>460</v>
-      </c>
-      <c r="H18" s="5"/>
+        <v>420</v>
+      </c>
+      <c r="H18" s="4"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>4010013693</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C19" s="5">
+        <v>46549</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>143</v>
-      </c>
-      <c r="C19" s="4">
-        <v>46587</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>145</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>8</v>
@@ -2301,9 +2292,9 @@
         <v>5</v>
       </c>
       <c r="G19" s="6">
-        <v>420</v>
-      </c>
-      <c r="H19" s="5"/>
+        <v>460</v>
+      </c>
+      <c r="H19" s="4"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
@@ -2312,7 +2303,7 @@
       <c r="B20" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C20" s="4">
+      <c r="C20" s="5">
         <v>46640</v>
       </c>
       <c r="D20" s="3" t="s">
@@ -2327,7 +2318,7 @@
       <c r="G20" s="6">
         <v>670</v>
       </c>
-      <c r="H20" s="5"/>
+      <c r="H20" s="4"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
@@ -2336,7 +2327,7 @@
       <c r="B21" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C21" s="4">
+      <c r="C21" s="5">
         <v>46666</v>
       </c>
       <c r="D21" s="3" t="s">
@@ -2351,7 +2342,7 @@
       <c r="G21" s="6">
         <v>400</v>
       </c>
-      <c r="H21" s="5"/>
+      <c r="H21" s="4"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
@@ -2360,7 +2351,7 @@
       <c r="B22" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C22" s="4">
+      <c r="C22" s="5">
         <v>46598</v>
       </c>
       <c r="D22" s="3" t="s">
@@ -2375,20 +2366,20 @@
       <c r="G22" s="6">
         <v>840</v>
       </c>
-      <c r="H22" s="5"/>
+      <c r="H22" s="4"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>4010013660</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="C23" s="4">
+        <v>126</v>
+      </c>
+      <c r="C23" s="5">
         <v>46518</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>22</v>
@@ -2399,27 +2390,27 @@
       <c r="G23" s="6">
         <v>340</v>
       </c>
-      <c r="H23" s="5"/>
+      <c r="H23" s="4"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="7">
+      <c r="A24" s="9">
         <v>4010013694</v>
       </c>
-      <c r="B24" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="C24" s="9"/>
-      <c r="D24" s="8" t="s">
+      <c r="B24" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="C24" s="11"/>
+      <c r="D24" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E24" s="8" t="s">
+      <c r="E24" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="F24" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G24" s="10"/>
-      <c r="H24" s="11">
+      <c r="F24" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G24" s="12"/>
+      <c r="H24" s="13">
         <v>240</v>
       </c>
     </row>
@@ -2428,13 +2419,13 @@
         <v>4010013694</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="C25" s="4">
+        <v>144</v>
+      </c>
+      <c r="C25" s="5">
         <v>46536</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>8</v>
@@ -2445,23 +2436,23 @@
       <c r="G25" s="6">
         <v>750</v>
       </c>
-      <c r="H25" s="5"/>
+      <c r="H25" s="4"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>6010000065</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C26" s="5">
+        <v>46447</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="E26" s="3" t="s">
         <v>164</v>
-      </c>
-      <c r="C26" s="4">
-        <v>46447</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>166</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>3</v>
@@ -2469,7 +2460,7 @@
       <c r="G26" s="6">
         <v>1800</v>
       </c>
-      <c r="H26" s="5"/>
+      <c r="H26" s="4"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
@@ -2478,7 +2469,7 @@
       <c r="B27" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C27" s="4">
+      <c r="C27" s="5">
         <v>46541</v>
       </c>
       <c r="D27" s="3" t="s">
@@ -2491,25 +2482,25 @@
         <v>5</v>
       </c>
       <c r="G27" s="6">
-        <v>3480</v>
-      </c>
-      <c r="H27" s="5"/>
+        <v>2880</v>
+      </c>
+      <c r="H27" s="4"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>6010000066</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C28" s="5">
+        <v>46575</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="E28" s="3" t="s">
         <v>167</v>
-      </c>
-      <c r="C28" s="4">
-        <v>46575</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>169</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>3</v>
@@ -2517,21 +2508,21 @@
       <c r="G28" s="6">
         <v>100</v>
       </c>
-      <c r="H28" s="5"/>
+      <c r="H28" s="4"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>7050000018</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>446</v>
-      </c>
-      <c r="C29" s="4"/>
+        <v>443</v>
+      </c>
+      <c r="C29" s="5"/>
       <c r="D29" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>3</v>
@@ -2539,21 +2530,21 @@
       <c r="G29" s="6">
         <v>100</v>
       </c>
-      <c r="H29" s="5"/>
+      <c r="H29" s="4"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>7050000016</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>444</v>
-      </c>
-      <c r="C30" s="4"/>
+        <v>441</v>
+      </c>
+      <c r="C30" s="5"/>
       <c r="D30" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>3</v>
@@ -2561,21 +2552,21 @@
       <c r="G30" s="6">
         <v>100</v>
       </c>
-      <c r="H30" s="5"/>
+      <c r="H30" s="4"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>7050000015</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>443</v>
-      </c>
-      <c r="C31" s="4"/>
+        <v>440</v>
+      </c>
+      <c r="C31" s="5"/>
       <c r="D31" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>3</v>
@@ -2583,21 +2574,21 @@
       <c r="G31" s="6">
         <v>100</v>
       </c>
-      <c r="H31" s="5"/>
+      <c r="H31" s="4"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>7050000014</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>441</v>
-      </c>
-      <c r="C32" s="4"/>
+        <v>438</v>
+      </c>
+      <c r="C32" s="5"/>
       <c r="D32" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>3</v>
@@ -2605,21 +2596,21 @@
       <c r="G32" s="6">
         <v>100</v>
       </c>
-      <c r="H32" s="5"/>
+      <c r="H32" s="4"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>7050000017</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>445</v>
-      </c>
-      <c r="C33" s="4"/>
+        <v>442</v>
+      </c>
+      <c r="C33" s="5"/>
       <c r="D33" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>3</v>
@@ -2627,7 +2618,7 @@
       <c r="G33" s="6">
         <v>100</v>
       </c>
-      <c r="H33" s="5"/>
+      <c r="H33" s="4"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
@@ -2636,7 +2627,7 @@
       <c r="B34" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C34" s="4">
+      <c r="C34" s="5">
         <v>46568</v>
       </c>
       <c r="D34" s="3" t="s">
@@ -2651,7 +2642,7 @@
       <c r="G34" s="6">
         <v>1330</v>
       </c>
-      <c r="H34" s="5"/>
+      <c r="H34" s="4"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
@@ -2660,7 +2651,7 @@
       <c r="B35" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C35" s="4">
+      <c r="C35" s="5">
         <v>46551</v>
       </c>
       <c r="D35" s="3" t="s">
@@ -2673,25 +2664,25 @@
         <v>5</v>
       </c>
       <c r="G35" s="6">
-        <v>230</v>
-      </c>
-      <c r="H35" s="5"/>
+        <v>130</v>
+      </c>
+      <c r="H35" s="4"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>6010000154</v>
       </c>
       <c r="B36" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C36" s="5">
+        <v>47007</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="E36" s="3" t="s">
         <v>326</v>
-      </c>
-      <c r="C36" s="4">
-        <v>47007</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>328</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>3</v>
@@ -2699,20 +2690,20 @@
       <c r="G36" s="6">
         <v>799</v>
       </c>
-      <c r="H36" s="5"/>
+      <c r="H36" s="4"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>6010000158</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="C37" s="4">
+        <v>331</v>
+      </c>
+      <c r="C37" s="5">
         <v>46752</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>8</v>
@@ -2723,23 +2714,23 @@
       <c r="G37" s="6">
         <v>440</v>
       </c>
-      <c r="H37" s="5"/>
+      <c r="H37" s="4"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>6010000068</v>
       </c>
       <c r="B38" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C38" s="5">
+        <v>46495</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="E38" s="3" t="s">
         <v>170</v>
-      </c>
-      <c r="C38" s="4">
-        <v>46495</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>172</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>3</v>
@@ -2747,20 +2738,20 @@
       <c r="G38" s="6">
         <v>1500</v>
       </c>
-      <c r="H38" s="5"/>
+      <c r="H38" s="4"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>6010000159</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="C39" s="4">
+        <v>333</v>
+      </c>
+      <c r="C39" s="5">
         <v>46780</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>30</v>
@@ -2771,27 +2762,27 @@
       <c r="G39" s="6">
         <v>400</v>
       </c>
-      <c r="H39" s="5"/>
+      <c r="H39" s="4"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="7">
+      <c r="A40" s="9">
         <v>6010000099</v>
       </c>
-      <c r="B40" s="8" t="s">
-        <v>242</v>
-      </c>
-      <c r="C40" s="9"/>
-      <c r="D40" s="8" t="s">
+      <c r="B40" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="C40" s="11"/>
+      <c r="D40" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E40" s="8" t="s">
+      <c r="E40" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="F40" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G40" s="10"/>
-      <c r="H40" s="11">
+      <c r="F40" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G40" s="12"/>
+      <c r="H40" s="13">
         <v>1200</v>
       </c>
     </row>
@@ -2800,13 +2791,13 @@
         <v>6010000099</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="C41" s="4">
+        <v>240</v>
+      </c>
+      <c r="C41" s="5">
         <v>46813</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>87</v>
@@ -2815,25 +2806,25 @@
         <v>5</v>
       </c>
       <c r="G41" s="6">
-        <v>4760</v>
-      </c>
-      <c r="H41" s="5"/>
+        <v>4160</v>
+      </c>
+      <c r="H41" s="4"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>6010000160</v>
       </c>
       <c r="B42" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="C42" s="5">
+        <v>46780</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="E42" s="3" t="s">
         <v>337</v>
-      </c>
-      <c r="C42" s="4">
-        <v>46780</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>339</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>5</v>
@@ -2841,20 +2832,20 @@
       <c r="G42" s="6">
         <v>900</v>
       </c>
-      <c r="H42" s="5"/>
+      <c r="H42" s="4"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>6010000234</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>424</v>
-      </c>
-      <c r="C43" s="4">
-        <v>46661</v>
+        <v>421</v>
+      </c>
+      <c r="C43" s="5">
+        <v>46726</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>22</v>
@@ -2863,22 +2854,22 @@
         <v>5</v>
       </c>
       <c r="G43" s="6">
-        <v>280</v>
-      </c>
-      <c r="H43" s="5"/>
+        <v>7920</v>
+      </c>
+      <c r="H43" s="4"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>6010000234</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>424</v>
-      </c>
-      <c r="C44" s="4">
-        <v>46726</v>
+        <v>421</v>
+      </c>
+      <c r="C44" s="5">
+        <v>46661</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>22</v>
@@ -2887,68 +2878,68 @@
         <v>5</v>
       </c>
       <c r="G44" s="6">
-        <v>7920</v>
-      </c>
-      <c r="H44" s="5"/>
+        <v>280</v>
+      </c>
+      <c r="H44" s="4"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="7">
+      <c r="A45" s="2">
         <v>6010000239</v>
       </c>
-      <c r="B45" s="8" t="s">
-        <v>429</v>
-      </c>
-      <c r="C45" s="9"/>
-      <c r="D45" s="8" t="s">
+      <c r="B45" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="C45" s="5">
+        <v>46507</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="6">
+        <v>727</v>
+      </c>
+      <c r="H45" s="4"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="9">
+        <v>6010000239</v>
+      </c>
+      <c r="B46" s="10" t="s">
+        <v>426</v>
+      </c>
+      <c r="C46" s="11"/>
+      <c r="D46" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E45" s="8" t="s">
-        <v>372</v>
-      </c>
-      <c r="F45" s="8" t="s">
+      <c r="E46" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="F46" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="G45" s="10"/>
-      <c r="H45" s="11">
+      <c r="G46" s="12"/>
+      <c r="H46" s="13">
         <v>810</v>
       </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="2">
-        <v>6010000239</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="C46" s="4">
-        <v>46507</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>430</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G46" s="6">
-        <v>727</v>
-      </c>
-      <c r="H46" s="5"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>6010000217</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="C47" s="4">
-        <v>46721</v>
+        <v>404</v>
+      </c>
+      <c r="C47" s="5">
+        <v>46751</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>30</v>
@@ -2957,22 +2948,22 @@
         <v>5</v>
       </c>
       <c r="G47" s="6">
-        <v>50</v>
-      </c>
-      <c r="H47" s="5"/>
+        <v>610</v>
+      </c>
+      <c r="H47" s="4"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>6010000217</v>
       </c>
       <c r="B48" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="C48" s="5">
+        <v>46721</v>
+      </c>
+      <c r="D48" s="3" t="s">
         <v>406</v>
-      </c>
-      <c r="C48" s="4">
-        <v>46751</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>408</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>30</v>
@@ -2981,79 +2972,79 @@
         <v>5</v>
       </c>
       <c r="G48" s="6">
-        <v>610</v>
-      </c>
-      <c r="H48" s="5"/>
+        <v>50</v>
+      </c>
+      <c r="H48" s="4"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>6010000070</v>
       </c>
       <c r="B49" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C49" s="5">
+        <v>46721</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="E49" s="3" t="s">
         <v>173</v>
-      </c>
-      <c r="C49" s="4">
-        <v>46721</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>175</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G49" s="6">
-        <v>765</v>
-      </c>
-      <c r="H49" s="5"/>
+        <v>525</v>
+      </c>
+      <c r="H49" s="4"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="2">
+      <c r="A50" s="9">
         <v>6010000071</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="B50" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="C50" s="11"/>
+      <c r="D50" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E50" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F50" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="G50" s="12"/>
+      <c r="H50" s="13">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="2">
+        <v>6010000071</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C51" s="5">
+        <v>46797</v>
+      </c>
+      <c r="D51" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="C50" s="4">
-        <v>46797</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="F50" s="3" t="s">
+      <c r="E51" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F51" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G50" s="6">
+      <c r="G51" s="6">
         <v>3250</v>
       </c>
-      <c r="H50" s="5"/>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="7">
-        <v>6010000071</v>
-      </c>
-      <c r="B51" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="C51" s="9"/>
-      <c r="D51" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="E51" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="F51" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="G51" s="10"/>
-      <c r="H51" s="11">
-        <v>400</v>
-      </c>
+      <c r="H51" s="4"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
@@ -3062,7 +3053,7 @@
       <c r="B52" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C52" s="4">
+      <c r="C52" s="5">
         <v>46681</v>
       </c>
       <c r="D52" s="3" t="s">
@@ -3077,7 +3068,7 @@
       <c r="G52" s="6">
         <v>1070</v>
       </c>
-      <c r="H52" s="5"/>
+      <c r="H52" s="4"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
@@ -3086,7 +3077,7 @@
       <c r="B53" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C53" s="4">
+      <c r="C53" s="5">
         <v>46575</v>
       </c>
       <c r="D53" s="3" t="s">
@@ -3101,7 +3092,7 @@
       <c r="G53" s="6">
         <v>440</v>
       </c>
-      <c r="H53" s="5"/>
+      <c r="H53" s="4"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
@@ -3110,7 +3101,7 @@
       <c r="B54" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C54" s="4">
+      <c r="C54" s="5">
         <v>46598</v>
       </c>
       <c r="D54" s="3" t="s">
@@ -3125,7 +3116,7 @@
       <c r="G54" s="6">
         <v>640</v>
       </c>
-      <c r="H54" s="5"/>
+      <c r="H54" s="4"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
@@ -3134,7 +3125,7 @@
       <c r="B55" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C55" s="4">
+      <c r="C55" s="5">
         <v>46575</v>
       </c>
       <c r="D55" s="3" t="s">
@@ -3149,7 +3140,7 @@
       <c r="G55" s="6">
         <v>840</v>
       </c>
-      <c r="H55" s="5"/>
+      <c r="H55" s="4"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
@@ -3158,7 +3149,7 @@
       <c r="B56" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C56" s="4">
+      <c r="C56" s="5">
         <v>46545</v>
       </c>
       <c r="D56" s="3" t="s">
@@ -3173,20 +3164,20 @@
       <c r="G56" s="6">
         <v>880</v>
       </c>
-      <c r="H56" s="5"/>
+      <c r="H56" s="4"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>6010000189</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="C57" s="4">
+        <v>366</v>
+      </c>
+      <c r="C57" s="5">
         <v>46539</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>30</v>
@@ -3197,20 +3188,20 @@
       <c r="G57" s="6">
         <v>110</v>
       </c>
-      <c r="H57" s="5"/>
+      <c r="H57" s="4"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>6010000224</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="C58" s="4">
+        <v>411</v>
+      </c>
+      <c r="C58" s="5">
         <v>46711</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>15</v>
@@ -3221,20 +3212,20 @@
       <c r="G58" s="6">
         <v>420</v>
       </c>
-      <c r="H58" s="5"/>
+      <c r="H58" s="4"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>6010000101</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="C59" s="4">
+        <v>242</v>
+      </c>
+      <c r="C59" s="5">
         <v>46539</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>30</v>
@@ -3245,20 +3236,20 @@
       <c r="G59" s="6">
         <v>120</v>
       </c>
-      <c r="H59" s="5"/>
+      <c r="H59" s="4"/>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>6010000232</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="C60" s="4">
+        <v>418</v>
+      </c>
+      <c r="C60" s="5">
         <v>46726</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>15</v>
@@ -3266,94 +3257,92 @@
       <c r="F60" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G60" s="6">
-        <v>2840</v>
-      </c>
-      <c r="H60" s="5"/>
+      <c r="G60" s="6"/>
+      <c r="H60" s="6"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="7">
+      <c r="A61" s="9">
         <v>6010000232</v>
       </c>
-      <c r="B61" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="C61" s="9"/>
-      <c r="D61" s="8" t="s">
+      <c r="B61" s="10" t="s">
+        <v>418</v>
+      </c>
+      <c r="C61" s="11"/>
+      <c r="D61" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E61" s="8" t="s">
+      <c r="E61" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F61" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G61" s="10"/>
-      <c r="H61" s="11">
+      <c r="F61" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G61" s="12"/>
+      <c r="H61" s="13">
         <v>7200</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="7">
+      <c r="A62" s="2">
         <v>6010000073</v>
       </c>
-      <c r="B62" s="8" t="s">
+      <c r="B62" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C62" s="5">
+        <v>46511</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="E62" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C62" s="9"/>
-      <c r="D62" s="8" t="s">
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="6">
+        <v>1150</v>
+      </c>
+      <c r="H62" s="4"/>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" s="9">
+        <v>6010000073</v>
+      </c>
+      <c r="B63" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="C63" s="11"/>
+      <c r="D63" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E62" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="F62" s="8" t="s">
+      <c r="E63" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="F63" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="G62" s="10"/>
-      <c r="H62" s="11">
+      <c r="G63" s="12"/>
+      <c r="H63" s="13">
         <v>720</v>
       </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="2">
-        <v>6010000073</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="C63" s="4">
-        <v>46511</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="E63" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G63" s="6">
-        <v>1150</v>
-      </c>
-      <c r="H63" s="5"/>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>6010000169</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="C64" s="4">
+        <v>344</v>
+      </c>
+      <c r="C64" s="5">
         <v>46751</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>5</v>
@@ -3361,47 +3350,47 @@
       <c r="G64" s="6">
         <v>2110</v>
       </c>
-      <c r="H64" s="5"/>
+      <c r="H64" s="4"/>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>6010000170</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="C65" s="4">
+        <v>346</v>
+      </c>
+      <c r="C65" s="5">
         <v>46721</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G65" s="6">
-        <v>2590</v>
-      </c>
-      <c r="H65" s="5"/>
+        <v>2490</v>
+      </c>
+      <c r="H65" s="4"/>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>6010000139</v>
       </c>
       <c r="B66" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="C66" s="5">
+        <v>46711</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="E66" s="3" t="s">
         <v>299</v>
-      </c>
-      <c r="C66" s="4">
-        <v>46711</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="E66" s="3" t="s">
-        <v>301</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>3</v>
@@ -3409,75 +3398,75 @@
       <c r="G66" s="6">
         <v>1438</v>
       </c>
-      <c r="H66" s="5"/>
+      <c r="H66" s="4"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>6010000267</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>438</v>
-      </c>
-      <c r="C67" s="4">
+        <v>435</v>
+      </c>
+      <c r="C67" s="5">
         <v>46813</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G67" s="6">
-        <v>620</v>
-      </c>
-      <c r="H67" s="5"/>
+        <v>430</v>
+      </c>
+      <c r="H67" s="4"/>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>6010000141</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="C68" s="4">
+        <v>300</v>
+      </c>
+      <c r="C68" s="5">
         <v>46746</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G68" s="6">
-        <v>2425</v>
-      </c>
-      <c r="H68" s="5"/>
+        <v>2395</v>
+      </c>
+      <c r="H68" s="4"/>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="7">
+      <c r="A69" s="9">
         <v>6010000205</v>
       </c>
-      <c r="B69" s="8" t="s">
-        <v>396</v>
-      </c>
-      <c r="C69" s="9"/>
-      <c r="D69" s="8" t="s">
+      <c r="B69" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="C69" s="11"/>
+      <c r="D69" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E69" s="8" t="s">
-        <v>397</v>
-      </c>
-      <c r="F69" s="8" t="s">
+      <c r="E69" s="10" t="s">
+        <v>395</v>
+      </c>
+      <c r="F69" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="G69" s="10"/>
-      <c r="H69" s="11">
+      <c r="G69" s="12"/>
+      <c r="H69" s="13">
         <v>7200</v>
       </c>
     </row>
@@ -3486,16 +3475,16 @@
         <v>6010000205</v>
       </c>
       <c r="B70" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="C70" s="5">
+        <v>46692</v>
+      </c>
+      <c r="D70" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="C70" s="4">
-        <v>46692</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>398</v>
-      </c>
       <c r="E70" s="3" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="F70" s="3" t="s">
         <v>3</v>
@@ -3503,7 +3492,7 @@
       <c r="G70" s="6">
         <v>9450</v>
       </c>
-      <c r="H70" s="5"/>
+      <c r="H70" s="4"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
@@ -3512,7 +3501,7 @@
       <c r="B71" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C71" s="4">
+      <c r="C71" s="5">
         <v>46504</v>
       </c>
       <c r="D71" s="3" t="s">
@@ -3527,73 +3516,73 @@
       <c r="G71" s="6">
         <v>520</v>
       </c>
-      <c r="H71" s="5"/>
+      <c r="H71" s="4"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="2">
+      <c r="A72" s="9">
         <v>6010000074</v>
       </c>
-      <c r="B72" s="3" t="s">
+      <c r="B72" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="C72" s="11"/>
+      <c r="D72" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E72" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="F72" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="G72" s="12"/>
+      <c r="H72" s="13">
+        <v>5760</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" s="2">
+        <v>6010000074</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C73" s="5">
+        <v>46721</v>
+      </c>
+      <c r="D73" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C72" s="4">
-        <v>46721</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="F72" s="3" t="s">
+      <c r="E73" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="F73" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G72" s="6">
-        <v>6048</v>
-      </c>
-      <c r="H72" s="5"/>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="7">
-        <v>6010000074</v>
-      </c>
-      <c r="B73" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="C73" s="9"/>
-      <c r="D73" s="8" t="s">
+      <c r="G73" s="6">
+        <v>5952</v>
+      </c>
+      <c r="H73" s="4"/>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" s="9">
+        <v>6010000102</v>
+      </c>
+      <c r="B74" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="C74" s="11"/>
+      <c r="D74" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E73" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="F73" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="G73" s="10"/>
-      <c r="H73" s="11">
-        <v>5760</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="7">
-        <v>6010000102</v>
-      </c>
-      <c r="B74" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="C74" s="9"/>
-      <c r="D74" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="E74" s="8" t="s">
+      <c r="E74" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F74" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G74" s="10"/>
-      <c r="H74" s="11">
+      <c r="F74" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G74" s="12"/>
+      <c r="H74" s="13">
         <v>1600</v>
       </c>
     </row>
@@ -3602,13 +3591,13 @@
         <v>6010000102</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="C75" s="4">
+        <v>244</v>
+      </c>
+      <c r="C75" s="5">
         <v>46780</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>22</v>
@@ -3617,22 +3606,22 @@
         <v>5</v>
       </c>
       <c r="G75" s="6">
-        <v>3980</v>
-      </c>
-      <c r="H75" s="5"/>
+        <v>3780</v>
+      </c>
+      <c r="H75" s="4"/>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>6010000103</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="C76" s="4">
+        <v>246</v>
+      </c>
+      <c r="C76" s="5">
         <v>46645</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>22</v>
@@ -3641,33 +3630,33 @@
         <v>5</v>
       </c>
       <c r="G76" s="6">
-        <v>2920</v>
-      </c>
-      <c r="H76" s="5"/>
+        <v>2820</v>
+      </c>
+      <c r="H76" s="4"/>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>6010000196</v>
       </c>
       <c r="B77" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="C77" s="5">
+        <v>46606</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="E77" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="C77" s="4">
-        <v>46606</v>
-      </c>
-      <c r="D77" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="E77" s="3" t="s">
-        <v>384</v>
-      </c>
       <c r="F77" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G77" s="6">
-        <v>1640</v>
-      </c>
-      <c r="H77" s="5"/>
+        <v>1140</v>
+      </c>
+      <c r="H77" s="4"/>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
@@ -3676,7 +3665,7 @@
       <c r="B78" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C78" s="4">
+      <c r="C78" s="5">
         <v>46524</v>
       </c>
       <c r="D78" s="3" t="s">
@@ -3691,27 +3680,27 @@
       <c r="G78" s="6">
         <v>420</v>
       </c>
-      <c r="H78" s="5"/>
+      <c r="H78" s="4"/>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="7">
+      <c r="A79" s="9">
         <v>6010000150</v>
       </c>
-      <c r="B79" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="C79" s="9"/>
-      <c r="D79" s="8" t="s">
+      <c r="B79" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="C79" s="11"/>
+      <c r="D79" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E79" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="F79" s="8" t="s">
+      <c r="E79" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="F79" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="G79" s="10"/>
-      <c r="H79" s="11">
+      <c r="G79" s="12"/>
+      <c r="H79" s="13">
         <v>880</v>
       </c>
     </row>
@@ -3720,16 +3709,16 @@
         <v>6010000151</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="C80" s="4">
+        <v>322</v>
+      </c>
+      <c r="C80" s="5">
         <v>46692</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F80" s="3" t="s">
         <v>3</v>
@@ -3737,23 +3726,23 @@
       <c r="G80" s="6">
         <v>540</v>
       </c>
-      <c r="H80" s="5"/>
+      <c r="H80" s="4"/>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>6010000241</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>431</v>
-      </c>
-      <c r="C81" s="4">
+        <v>428</v>
+      </c>
+      <c r="C81" s="5">
         <v>46596</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>3</v>
@@ -3761,20 +3750,20 @@
       <c r="G81" s="6">
         <v>466</v>
       </c>
-      <c r="H81" s="5"/>
+      <c r="H81" s="4"/>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>6010000194</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="C82" s="4">
-        <v>46803</v>
+        <v>375</v>
+      </c>
+      <c r="C82" s="5">
+        <v>46721</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>30</v>
@@ -3783,22 +3772,22 @@
         <v>5</v>
       </c>
       <c r="G82" s="6">
-        <v>1470</v>
-      </c>
-      <c r="H82" s="5"/>
+        <v>4020</v>
+      </c>
+      <c r="H82" s="4"/>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>6010000194</v>
       </c>
       <c r="B83" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="C83" s="5">
+        <v>46803</v>
+      </c>
+      <c r="D83" s="3" t="s">
         <v>377</v>
-      </c>
-      <c r="C83" s="4">
-        <v>46721</v>
-      </c>
-      <c r="D83" s="3" t="s">
-        <v>379</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>30</v>
@@ -3807,25 +3796,25 @@
         <v>5</v>
       </c>
       <c r="G83" s="6">
-        <v>4020</v>
-      </c>
-      <c r="H83" s="5"/>
+        <v>1470</v>
+      </c>
+      <c r="H83" s="4"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>6010000192</v>
       </c>
       <c r="B84" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C84" s="5">
+        <v>46367</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="E84" s="3" t="s">
         <v>370</v>
-      </c>
-      <c r="C84" s="4">
-        <v>46367</v>
-      </c>
-      <c r="D84" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="E84" s="3" t="s">
-        <v>372</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>3</v>
@@ -3833,20 +3822,20 @@
       <c r="G84" s="6">
         <v>345</v>
       </c>
-      <c r="H84" s="5"/>
+      <c r="H84" s="4"/>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>6010000155</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="C85" s="4">
+        <v>327</v>
+      </c>
+      <c r="C85" s="5">
         <v>46447</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>30</v>
@@ -3857,20 +3846,20 @@
       <c r="G85" s="6">
         <v>380</v>
       </c>
-      <c r="H85" s="5"/>
+      <c r="H85" s="4"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>6010000108</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="C86" s="4">
+        <v>248</v>
+      </c>
+      <c r="C86" s="5">
         <v>46574</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>15</v>
@@ -3881,20 +3870,20 @@
       <c r="G86" s="6">
         <v>560</v>
       </c>
-      <c r="H86" s="5"/>
+      <c r="H86" s="4"/>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>6010000193</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="C87" s="4">
-        <v>46711</v>
+        <v>371</v>
+      </c>
+      <c r="C87" s="5">
+        <v>46726</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>30</v>
@@ -3903,22 +3892,22 @@
         <v>5</v>
       </c>
       <c r="G87" s="6">
-        <v>170</v>
-      </c>
-      <c r="H87" s="5"/>
+        <v>80</v>
+      </c>
+      <c r="H87" s="4"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>6010000193</v>
       </c>
       <c r="B88" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="C88" s="5">
+        <v>46803</v>
+      </c>
+      <c r="D88" s="3" t="s">
         <v>373</v>
-      </c>
-      <c r="C88" s="4">
-        <v>46726</v>
-      </c>
-      <c r="D88" s="3" t="s">
-        <v>375</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>30</v>
@@ -3927,22 +3916,22 @@
         <v>5</v>
       </c>
       <c r="G88" s="6">
-        <v>80</v>
-      </c>
-      <c r="H88" s="5"/>
+        <v>380</v>
+      </c>
+      <c r="H88" s="4"/>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>6010000193</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="C89" s="4">
-        <v>46803</v>
+        <v>371</v>
+      </c>
+      <c r="C89" s="5">
+        <v>46711</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>30</v>
@@ -3951,22 +3940,22 @@
         <v>5</v>
       </c>
       <c r="G89" s="6">
-        <v>380</v>
-      </c>
-      <c r="H89" s="5"/>
+        <v>120</v>
+      </c>
+      <c r="H89" s="4"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>6010000216</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="C90" s="4">
+        <v>402</v>
+      </c>
+      <c r="C90" s="5">
         <v>46690</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>30</v>
@@ -3977,20 +3966,20 @@
       <c r="G90" s="6">
         <v>90</v>
       </c>
-      <c r="H90" s="5"/>
+      <c r="H90" s="4"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>6010000235</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>427</v>
-      </c>
-      <c r="C91" s="4">
+        <v>424</v>
+      </c>
+      <c r="C91" s="5">
         <v>46808</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>15</v>
@@ -4001,20 +3990,20 @@
       <c r="G91" s="6">
         <v>1540</v>
       </c>
-      <c r="H91" s="5"/>
+      <c r="H91" s="4"/>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>4010013662</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="C92" s="4">
+        <v>128</v>
+      </c>
+      <c r="C92" s="5">
         <v>46546</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>30</v>
@@ -4025,20 +4014,20 @@
       <c r="G92" s="6">
         <v>420</v>
       </c>
-      <c r="H92" s="5"/>
+      <c r="H92" s="4"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
         <v>4010013662</v>
       </c>
       <c r="B93" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C93" s="5">
+        <v>46537</v>
+      </c>
+      <c r="D93" s="3" t="s">
         <v>130</v>
-      </c>
-      <c r="C93" s="4">
-        <v>46537</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>132</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>30</v>
@@ -4049,23 +4038,23 @@
       <c r="G93" s="6">
         <v>190</v>
       </c>
-      <c r="H93" s="5"/>
+      <c r="H93" s="4"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>6010000076</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="C94" s="4">
+        <v>183</v>
+      </c>
+      <c r="C94" s="5">
         <v>46483</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>3</v>
@@ -4073,20 +4062,20 @@
       <c r="G94" s="6">
         <v>2876</v>
       </c>
-      <c r="H94" s="5"/>
+      <c r="H94" s="4"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
         <v>6010000110</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="C95" s="4">
+        <v>250</v>
+      </c>
+      <c r="C95" s="5">
         <v>46640</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>4</v>
@@ -4097,20 +4086,20 @@
       <c r="G95" s="6">
         <v>1000</v>
       </c>
-      <c r="H95" s="5"/>
+      <c r="H95" s="4"/>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <v>6010000111</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="C96" s="4">
+        <v>252</v>
+      </c>
+      <c r="C96" s="5">
         <v>46640</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>4</v>
@@ -4121,31 +4110,29 @@
       <c r="G96" s="6">
         <v>2640</v>
       </c>
-      <c r="H96" s="5"/>
+      <c r="H96" s="4"/>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A97" s="2">
+      <c r="A97" s="9">
         <v>4010013584</v>
       </c>
-      <c r="B97" s="3" t="s">
+      <c r="B97" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="C97" s="4">
-        <v>46532</v>
-      </c>
-      <c r="D97" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="E97" s="3" t="s">
+      <c r="C97" s="11"/>
+      <c r="D97" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E97" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="F97" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G97" s="6">
-        <v>200</v>
-      </c>
-      <c r="H97" s="5"/>
+      <c r="F97" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G97" s="12"/>
+      <c r="H97" s="13">
+        <v>900</v>
+      </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
@@ -4154,11 +4141,11 @@
       <c r="B98" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C98" s="4">
+      <c r="C98" s="5">
         <v>46537</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>87</v>
@@ -4169,42 +4156,44 @@
       <c r="G98" s="6">
         <v>380</v>
       </c>
-      <c r="H98" s="5"/>
+      <c r="H98" s="4"/>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A99" s="7">
+      <c r="A99" s="2">
         <v>4010013584</v>
       </c>
-      <c r="B99" s="8" t="s">
+      <c r="B99" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C99" s="9"/>
-      <c r="D99" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="E99" s="8" t="s">
+      <c r="C99" s="5">
+        <v>46532</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E99" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="F99" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G99" s="10"/>
-      <c r="H99" s="11">
-        <v>900</v>
-      </c>
+      <c r="F99" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G99" s="6">
+        <v>200</v>
+      </c>
+      <c r="H99" s="4"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
         <v>6010000171</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="C100" s="4">
+        <v>348</v>
+      </c>
+      <c r="C100" s="5">
         <v>46579</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>87</v>
@@ -4215,7 +4204,7 @@
       <c r="G100" s="6">
         <v>1500</v>
       </c>
-      <c r="H100" s="5"/>
+      <c r="H100" s="4"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
@@ -4224,7 +4213,7 @@
       <c r="B101" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C101" s="4">
+      <c r="C101" s="5">
         <v>46568</v>
       </c>
       <c r="D101" s="3" t="s">
@@ -4239,20 +4228,20 @@
       <c r="G101" s="6">
         <v>1500</v>
       </c>
-      <c r="H101" s="5"/>
+      <c r="H101" s="4"/>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
         <v>6010000172</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="C102" s="4">
+        <v>350</v>
+      </c>
+      <c r="C102" s="5">
         <v>46579</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E102" s="3" t="s">
         <v>87</v>
@@ -4263,23 +4252,23 @@
       <c r="G102" s="6">
         <v>1620</v>
       </c>
-      <c r="H102" s="5"/>
+      <c r="H102" s="4"/>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
         <v>6010000077</v>
       </c>
       <c r="B103" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C103" s="5">
+        <v>46471</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E103" s="3" t="s">
         <v>187</v>
-      </c>
-      <c r="C103" s="4">
-        <v>46471</v>
-      </c>
-      <c r="D103" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E103" s="3" t="s">
-        <v>189</v>
       </c>
       <c r="F103" s="3" t="s">
         <v>3</v>
@@ -4287,69 +4276,69 @@
       <c r="G103" s="6">
         <v>4970</v>
       </c>
-      <c r="H103" s="5"/>
+      <c r="H103" s="4"/>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A104" s="7">
+      <c r="A104" s="2">
         <v>6010000078</v>
       </c>
-      <c r="B104" s="8" t="s">
+      <c r="B104" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C104" s="5">
+        <v>46780</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="E104" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="C104" s="9"/>
-      <c r="D104" s="8" t="s">
+      <c r="F104" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G104" s="6">
+        <v>7100</v>
+      </c>
+      <c r="H104" s="4"/>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" s="9">
+        <v>6010000078</v>
+      </c>
+      <c r="B105" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="C105" s="11"/>
+      <c r="D105" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E104" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="F104" s="8" t="s">
+      <c r="E105" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="F105" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="G104" s="10"/>
-      <c r="H104" s="11">
+      <c r="G105" s="12"/>
+      <c r="H105" s="13">
         <v>125</v>
       </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A105" s="2">
-        <v>6010000078</v>
-      </c>
-      <c r="B105" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="C105" s="4">
-        <v>46780</v>
-      </c>
-      <c r="D105" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="E105" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="F105" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G105" s="6">
-        <v>7100</v>
-      </c>
-      <c r="H105" s="5"/>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
         <v>6010000079</v>
       </c>
       <c r="B106" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="C106" s="5">
+        <v>46512</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E106" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="C106" s="4">
-        <v>46512</v>
-      </c>
-      <c r="D106" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="E106" s="3" t="s">
-        <v>195</v>
       </c>
       <c r="F106" s="3" t="s">
         <v>3</v>
@@ -4357,66 +4346,66 @@
       <c r="G106" s="6">
         <v>310</v>
       </c>
-      <c r="H106" s="5"/>
+      <c r="H106" s="4"/>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A107" s="2">
+      <c r="A107" s="9">
         <v>4010013593</v>
       </c>
-      <c r="B107" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C107" s="4">
+      <c r="B107" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="C107" s="11"/>
+      <c r="D107" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E107" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F107" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G107" s="12"/>
+      <c r="H107" s="13">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" s="2">
+        <v>4010013593</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C108" s="5">
         <v>46758</v>
       </c>
-      <c r="D107" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="E107" s="3" t="s">
+      <c r="D108" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E108" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F107" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G107" s="6">
-        <v>530</v>
-      </c>
-      <c r="H107" s="5"/>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A108" s="7">
-        <v>4010013593</v>
-      </c>
-      <c r="B108" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="C108" s="9"/>
-      <c r="D108" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="E108" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F108" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G108" s="10"/>
-      <c r="H108" s="11">
-        <v>560</v>
-      </c>
+      <c r="F108" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G108" s="6">
+        <v>480</v>
+      </c>
+      <c r="H108" s="4"/>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
         <v>4010014329</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="C109" s="4">
+        <v>153</v>
+      </c>
+      <c r="C109" s="5">
         <v>46641</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E109" s="3" t="s">
         <v>30</v>
@@ -4427,20 +4416,20 @@
       <c r="G109" s="6">
         <v>230</v>
       </c>
-      <c r="H109" s="5"/>
+      <c r="H109" s="4"/>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
         <v>4010013594</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C110" s="4">
+        <v>107</v>
+      </c>
+      <c r="C110" s="5">
         <v>46573</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E110" s="3" t="s">
         <v>30</v>
@@ -4451,27 +4440,27 @@
       <c r="G110" s="6">
         <v>760</v>
       </c>
-      <c r="H110" s="5"/>
+      <c r="H110" s="4"/>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A111" s="7">
+      <c r="A111" s="9">
         <v>4010013594</v>
       </c>
-      <c r="B111" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="C111" s="9"/>
-      <c r="D111" s="8" t="s">
+      <c r="B111" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="C111" s="11"/>
+      <c r="D111" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E111" s="8" t="s">
+      <c r="E111" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F111" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G111" s="10"/>
-      <c r="H111" s="11">
+      <c r="F111" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G111" s="12"/>
+      <c r="H111" s="13">
         <v>1120</v>
       </c>
     </row>
@@ -4480,13 +4469,13 @@
         <v>4010014330</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="C112" s="4">
+        <v>155</v>
+      </c>
+      <c r="C112" s="5">
         <v>46610</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E112" s="3" t="s">
         <v>30</v>
@@ -4497,20 +4486,20 @@
       <c r="G112" s="6">
         <v>280</v>
       </c>
-      <c r="H112" s="5"/>
+      <c r="H112" s="4"/>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="2">
         <v>6010000156</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="C113" s="4">
+        <v>329</v>
+      </c>
+      <c r="C113" s="5">
         <v>46447</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E113" s="3" t="s">
         <v>30</v>
@@ -4521,20 +4510,20 @@
       <c r="G113" s="6">
         <v>270</v>
       </c>
-      <c r="H113" s="5"/>
+      <c r="H113" s="4"/>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
         <v>6010000233</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="C114" s="4">
+        <v>329</v>
+      </c>
+      <c r="C114" s="5">
         <v>46721</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="E114" s="3" t="s">
         <v>30</v>
@@ -4545,27 +4534,27 @@
       <c r="G114" s="6">
         <v>90</v>
       </c>
-      <c r="H114" s="5"/>
+      <c r="H114" s="4"/>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A115" s="7">
+      <c r="A115" s="9">
         <v>6010000233</v>
       </c>
-      <c r="B115" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="C115" s="9"/>
-      <c r="D115" s="8" t="s">
+      <c r="B115" s="10" t="s">
+        <v>329</v>
+      </c>
+      <c r="C115" s="11"/>
+      <c r="D115" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E115" s="8" t="s">
+      <c r="E115" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F115" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G115" s="10"/>
-      <c r="H115" s="11">
+      <c r="F115" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G115" s="12"/>
+      <c r="H115" s="13">
         <v>1350</v>
       </c>
     </row>
@@ -4574,16 +4563,16 @@
         <v>6010000080</v>
       </c>
       <c r="B116" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C116" s="5">
+        <v>46423</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E116" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="C116" s="4">
-        <v>46423</v>
-      </c>
-      <c r="D116" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="E116" s="3" t="s">
-        <v>198</v>
       </c>
       <c r="F116" s="3" t="s">
         <v>3</v>
@@ -4591,20 +4580,20 @@
       <c r="G116" s="6">
         <v>500</v>
       </c>
-      <c r="H116" s="5"/>
+      <c r="H116" s="4"/>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
         <v>6010000113</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="C117" s="4">
+        <v>254</v>
+      </c>
+      <c r="C117" s="5">
         <v>46598</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E117" s="3" t="s">
         <v>22</v>
@@ -4615,23 +4604,23 @@
       <c r="G117" s="6">
         <v>8340</v>
       </c>
-      <c r="H117" s="5"/>
+      <c r="H117" s="4"/>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
         <v>4010013656</v>
       </c>
       <c r="B118" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C118" s="5">
+        <v>46510</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E118" s="3" t="s">
         <v>119</v>
-      </c>
-      <c r="C118" s="4">
-        <v>46510</v>
-      </c>
-      <c r="D118" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="E118" s="3" t="s">
-        <v>121</v>
       </c>
       <c r="F118" s="3" t="s">
         <v>5</v>
@@ -4639,20 +4628,20 @@
       <c r="G118" s="6">
         <v>2300</v>
       </c>
-      <c r="H118" s="5"/>
+      <c r="H118" s="4"/>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
         <v>4010013595</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C119" s="4">
+        <v>109</v>
+      </c>
+      <c r="C119" s="5">
         <v>46623</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E119" s="3" t="s">
         <v>30</v>
@@ -4663,23 +4652,23 @@
       <c r="G119" s="6">
         <v>100</v>
       </c>
-      <c r="H119" s="5"/>
+      <c r="H119" s="4"/>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" s="2">
         <v>6010000174</v>
       </c>
       <c r="B120" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="C120" s="5">
+        <v>46586</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="E120" s="3" t="s">
         <v>354</v>
-      </c>
-      <c r="C120" s="4">
-        <v>46586</v>
-      </c>
-      <c r="D120" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="E120" s="3" t="s">
-        <v>356</v>
       </c>
       <c r="F120" s="3" t="s">
         <v>5</v>
@@ -4687,23 +4676,23 @@
       <c r="G120" s="6">
         <v>1120</v>
       </c>
-      <c r="H120" s="5"/>
+      <c r="H120" s="4"/>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
         <v>6010000114</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="C121" s="4">
+        <v>256</v>
+      </c>
+      <c r="C121" s="5">
         <v>46488</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F121" s="3" t="s">
         <v>5</v>
@@ -4711,20 +4700,20 @@
       <c r="G121" s="6">
         <v>2000</v>
       </c>
-      <c r="H121" s="5"/>
+      <c r="H121" s="4"/>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
         <v>6010000081</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="C122" s="4">
+        <v>197</v>
+      </c>
+      <c r="C122" s="5">
         <v>46660</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E122" s="3" t="s">
         <v>2</v>
@@ -4735,23 +4724,23 @@
       <c r="G122" s="6">
         <v>750</v>
       </c>
-      <c r="H122" s="5"/>
+      <c r="H122" s="4"/>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
         <v>6010000082</v>
       </c>
       <c r="B123" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C123" s="5">
+        <v>46505</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="E123" s="3" t="s">
         <v>201</v>
-      </c>
-      <c r="C123" s="4">
-        <v>46505</v>
-      </c>
-      <c r="D123" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="E123" s="3" t="s">
-        <v>203</v>
       </c>
       <c r="F123" s="3" t="s">
         <v>3</v>
@@ -4759,23 +4748,23 @@
       <c r="G123" s="6">
         <v>11100</v>
       </c>
-      <c r="H123" s="5"/>
+      <c r="H123" s="4"/>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" s="2">
         <v>6010000175</v>
       </c>
       <c r="B124" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C124" s="5">
+        <v>46556</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="E124" s="3" t="s">
         <v>357</v>
-      </c>
-      <c r="C124" s="4">
-        <v>46556</v>
-      </c>
-      <c r="D124" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="E124" s="3" t="s">
-        <v>359</v>
       </c>
       <c r="F124" s="3" t="s">
         <v>5</v>
@@ -4783,23 +4772,23 @@
       <c r="G124" s="6">
         <v>1880</v>
       </c>
-      <c r="H124" s="5"/>
+      <c r="H124" s="4"/>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" s="2">
         <v>6010000176</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="C125" s="4">
+        <v>358</v>
+      </c>
+      <c r="C125" s="5">
         <v>46586</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="F125" s="3" t="s">
         <v>5</v>
@@ -4807,23 +4796,23 @@
       <c r="G125" s="6">
         <v>1980</v>
       </c>
-      <c r="H125" s="5"/>
+      <c r="H125" s="4"/>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" s="2">
         <v>6010000201</v>
       </c>
       <c r="B126" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="C126" s="5">
+        <v>46624</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="E126" s="3" t="s">
         <v>389</v>
-      </c>
-      <c r="C126" s="4">
-        <v>46624</v>
-      </c>
-      <c r="D126" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="E126" s="3" t="s">
-        <v>391</v>
       </c>
       <c r="F126" s="3" t="s">
         <v>3</v>
@@ -4831,23 +4820,23 @@
       <c r="G126" s="6">
         <v>910</v>
       </c>
-      <c r="H126" s="5"/>
+      <c r="H126" s="4"/>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" s="2">
         <v>6010000202</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="C127" s="4">
+        <v>390</v>
+      </c>
+      <c r="C127" s="5">
         <v>46685</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="F127" s="3" t="s">
         <v>3</v>
@@ -4855,7 +4844,7 @@
       <c r="G127" s="6">
         <v>830</v>
       </c>
-      <c r="H127" s="5"/>
+      <c r="H127" s="4"/>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" s="2">
@@ -4864,7 +4853,7 @@
       <c r="B128" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C128" s="4">
+      <c r="C128" s="5">
         <v>46549</v>
       </c>
       <c r="D128" s="3" t="s">
@@ -4879,7 +4868,7 @@
       <c r="G128" s="6">
         <v>380</v>
       </c>
-      <c r="H128" s="5"/>
+      <c r="H128" s="4"/>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
@@ -4888,7 +4877,7 @@
       <c r="B129" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C129" s="4">
+      <c r="C129" s="5">
         <v>46637</v>
       </c>
       <c r="D129" s="3" t="s">
@@ -4903,7 +4892,7 @@
       <c r="G129" s="6">
         <v>1680</v>
       </c>
-      <c r="H129" s="5"/>
+      <c r="H129" s="4"/>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
@@ -4912,7 +4901,7 @@
       <c r="B130" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C130" s="4">
+      <c r="C130" s="5">
         <v>46704</v>
       </c>
       <c r="D130" s="3" t="s">
@@ -4927,69 +4916,69 @@
       <c r="G130" s="6">
         <v>80</v>
       </c>
-      <c r="H130" s="5"/>
+      <c r="H130" s="4"/>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A131" s="2">
+      <c r="A131" s="9">
         <v>4010013671</v>
       </c>
-      <c r="B131" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="C131" s="4">
+      <c r="B131" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="C131" s="11"/>
+      <c r="D131" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E131" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F131" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G131" s="12"/>
+      <c r="H131" s="13">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" s="2">
+        <v>4010013671</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C132" s="5">
         <v>46566</v>
       </c>
-      <c r="D131" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="E131" s="3" t="s">
+      <c r="D132" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E132" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F131" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G131" s="6">
+      <c r="F132" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G132" s="6">
         <v>980</v>
       </c>
-      <c r="H131" s="5"/>
-    </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A132" s="7">
-        <v>4010013671</v>
-      </c>
-      <c r="B132" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="C132" s="9"/>
-      <c r="D132" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="E132" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F132" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G132" s="10"/>
-      <c r="H132" s="11">
-        <v>1440</v>
-      </c>
+      <c r="H132" s="4"/>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" s="2">
         <v>6010000252</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>434</v>
-      </c>
-      <c r="C133" s="4">
+        <v>431</v>
+      </c>
+      <c r="C133" s="5">
         <v>46780</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="F133" s="3" t="s">
         <v>3</v>
@@ -4997,95 +4986,95 @@
       <c r="G133" s="6">
         <v>1500</v>
       </c>
-      <c r="H133" s="5"/>
+      <c r="H133" s="4"/>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
         <v>6010000252</v>
       </c>
       <c r="B134" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="C134" s="5">
+        <v>46661</v>
+      </c>
+      <c r="D134" s="3" t="s">
         <v>434</v>
       </c>
-      <c r="C134" s="4">
-        <v>46661</v>
-      </c>
-      <c r="D134" s="3" t="s">
-        <v>437</v>
-      </c>
       <c r="E134" s="3" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="F134" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G134" s="6">
-        <v>690</v>
-      </c>
-      <c r="H134" s="5"/>
+        <v>490</v>
+      </c>
+      <c r="H134" s="4"/>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" s="2">
         <v>6010000218</v>
       </c>
       <c r="B135" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="C135" s="5">
+        <v>46780</v>
+      </c>
+      <c r="D135" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="E135" s="3" t="s">
         <v>409</v>
-      </c>
-      <c r="C135" s="4">
-        <v>46812</v>
-      </c>
-      <c r="D135" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="E135" s="3" t="s">
-        <v>411</v>
       </c>
       <c r="F135" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G135" s="6">
-        <v>500</v>
-      </c>
-      <c r="H135" s="5"/>
+        <v>2375</v>
+      </c>
+      <c r="H135" s="4"/>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" s="2">
         <v>6010000218</v>
       </c>
       <c r="B136" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="C136" s="5">
+        <v>46812</v>
+      </c>
+      <c r="D136" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="E136" s="3" t="s">
         <v>409</v>
-      </c>
-      <c r="C136" s="4">
-        <v>46780</v>
-      </c>
-      <c r="D136" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="E136" s="3" t="s">
-        <v>411</v>
       </c>
       <c r="F136" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G136" s="6">
-        <v>2375</v>
-      </c>
-      <c r="H136" s="5"/>
+        <v>500</v>
+      </c>
+      <c r="H136" s="4"/>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" s="2">
         <v>6010000083</v>
       </c>
       <c r="B137" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C137" s="5">
+        <v>46537</v>
+      </c>
+      <c r="D137" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="E137" s="3" t="s">
         <v>204</v>
-      </c>
-      <c r="C137" s="4">
-        <v>46537</v>
-      </c>
-      <c r="D137" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="E137" s="3" t="s">
-        <v>206</v>
       </c>
       <c r="F137" s="3" t="s">
         <v>3</v>
@@ -5093,27 +5082,27 @@
       <c r="G137" s="6">
         <v>1270</v>
       </c>
-      <c r="H137" s="5"/>
+      <c r="H137" s="4"/>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A138" s="7">
+      <c r="A138" s="9">
         <v>6010000083</v>
       </c>
-      <c r="B138" s="8" t="s">
+      <c r="B138" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="C138" s="11"/>
+      <c r="D138" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E138" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="C138" s="9"/>
-      <c r="D138" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="E138" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="F138" s="8" t="s">
+      <c r="F138" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="G138" s="10"/>
-      <c r="H138" s="11">
+      <c r="G138" s="12"/>
+      <c r="H138" s="13">
         <v>300</v>
       </c>
     </row>
@@ -5122,37 +5111,37 @@
         <v>6010000084</v>
       </c>
       <c r="B139" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C139" s="5">
+        <v>46711</v>
+      </c>
+      <c r="D139" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="E139" s="3" t="s">
         <v>207</v>
-      </c>
-      <c r="C139" s="4">
-        <v>46711</v>
-      </c>
-      <c r="D139" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="E139" s="3" t="s">
-        <v>209</v>
       </c>
       <c r="F139" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G139" s="6">
-        <v>4420</v>
-      </c>
-      <c r="H139" s="5"/>
+        <v>3620</v>
+      </c>
+      <c r="H139" s="4"/>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" s="2">
         <v>6010000115</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="C140" s="4">
+        <v>258</v>
+      </c>
+      <c r="C140" s="5">
         <v>46971</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E140" s="3" t="s">
         <v>22</v>
@@ -5163,62 +5152,62 @@
       <c r="G140" s="6">
         <v>9500</v>
       </c>
-      <c r="H140" s="5"/>
+      <c r="H140" s="4"/>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A141" s="2">
+      <c r="A141" s="9">
         <v>6010000116</v>
       </c>
-      <c r="B141" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="C141" s="4">
+      <c r="B141" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="C141" s="11"/>
+      <c r="D141" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E141" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F141" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G141" s="12"/>
+      <c r="H141" s="13">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A142" s="2">
+        <v>6010000116</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="C142" s="5">
         <v>46971</v>
       </c>
-      <c r="D141" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="E141" s="3" t="s">
+      <c r="D142" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="E142" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F141" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G141" s="6">
+      <c r="F142" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G142" s="6">
         <v>4880</v>
       </c>
-      <c r="H141" s="5"/>
-    </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A142" s="7">
-        <v>6010000116</v>
-      </c>
-      <c r="B142" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="C142" s="9"/>
-      <c r="D142" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="E142" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="F142" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G142" s="10"/>
-      <c r="H142" s="11">
-        <v>3600</v>
-      </c>
+      <c r="H142" s="4"/>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" s="2">
         <v>7050000019</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="C143" s="4"/>
+        <v>444</v>
+      </c>
+      <c r="C143" s="5"/>
       <c r="D143" s="3" t="s">
         <v>2</v>
       </c>
@@ -5231,20 +5220,20 @@
       <c r="G143" s="6">
         <v>530</v>
       </c>
-      <c r="H143" s="5"/>
+      <c r="H143" s="4"/>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" s="2">
         <v>6010000117</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="C144" s="4">
+        <v>262</v>
+      </c>
+      <c r="C144" s="5">
         <v>46711</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E144" s="3" t="s">
         <v>22</v>
@@ -5253,22 +5242,22 @@
         <v>5</v>
       </c>
       <c r="G144" s="6">
-        <v>5960</v>
-      </c>
-      <c r="H144" s="5"/>
+        <v>5860</v>
+      </c>
+      <c r="H144" s="4"/>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" s="2">
         <v>6010000118</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="C145" s="4">
+        <v>264</v>
+      </c>
+      <c r="C145" s="5">
         <v>46574</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E145" s="3" t="s">
         <v>22</v>
@@ -5279,69 +5268,69 @@
       <c r="G145" s="6">
         <v>10240</v>
       </c>
-      <c r="H145" s="5"/>
+      <c r="H145" s="4"/>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A146" s="7">
+      <c r="A146" s="2">
         <v>6010000148</v>
       </c>
-      <c r="B146" s="8" t="s">
-        <v>320</v>
-      </c>
-      <c r="C146" s="9"/>
-      <c r="D146" s="8" t="s">
+      <c r="B146" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="C146" s="5">
+        <v>46751</v>
+      </c>
+      <c r="D146" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="E146" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F146" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G146" s="6">
+        <v>2360</v>
+      </c>
+      <c r="H146" s="4"/>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A147" s="9">
+        <v>6010000148</v>
+      </c>
+      <c r="B147" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="C147" s="11"/>
+      <c r="D147" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E146" s="8" t="s">
+      <c r="E147" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F146" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G146" s="10"/>
-      <c r="H146" s="11">
+      <c r="F147" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G147" s="12"/>
+      <c r="H147" s="13">
         <v>20</v>
       </c>
-    </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A147" s="2">
-        <v>6010000148</v>
-      </c>
-      <c r="B147" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="C147" s="4">
-        <v>46751</v>
-      </c>
-      <c r="D147" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="E147" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F147" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G147" s="6">
-        <v>2360</v>
-      </c>
-      <c r="H147" s="5"/>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" s="2">
         <v>6010000119</v>
       </c>
       <c r="B148" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C148" s="5">
+        <v>46598</v>
+      </c>
+      <c r="D148" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="E148" s="3" t="s">
         <v>268</v>
-      </c>
-      <c r="C148" s="4">
-        <v>46598</v>
-      </c>
-      <c r="D148" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="E148" s="3" t="s">
-        <v>270</v>
       </c>
       <c r="F148" s="3" t="s">
         <v>5</v>
@@ -5349,68 +5338,68 @@
       <c r="G148" s="6">
         <v>300</v>
       </c>
-      <c r="H148" s="5"/>
+      <c r="H148" s="4"/>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" s="2">
         <v>6010000085</v>
       </c>
       <c r="B149" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C149" s="5">
+        <v>46388</v>
+      </c>
+      <c r="D149" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="E149" s="3" t="s">
         <v>210</v>
-      </c>
-      <c r="C149" s="4">
-        <v>46388</v>
-      </c>
-      <c r="D149" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="E149" s="3" t="s">
-        <v>212</v>
       </c>
       <c r="F149" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G149" s="6">
-        <v>41100</v>
-      </c>
-      <c r="H149" s="5"/>
+        <v>13500</v>
+      </c>
+      <c r="H149" s="4"/>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" s="2">
         <v>6010000085</v>
       </c>
       <c r="B150" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C150" s="5">
+        <v>46388</v>
+      </c>
+      <c r="D150" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E150" s="3" t="s">
         <v>210</v>
-      </c>
-      <c r="C150" s="4">
-        <v>46388</v>
-      </c>
-      <c r="D150" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="E150" s="3" t="s">
-        <v>212</v>
       </c>
       <c r="F150" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G150" s="6">
-        <v>13500</v>
-      </c>
-      <c r="H150" s="5"/>
+        <v>41100</v>
+      </c>
+      <c r="H150" s="4"/>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" s="2">
         <v>6010000123</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="C151" s="4">
+        <v>269</v>
+      </c>
+      <c r="C151" s="5">
         <v>46752</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E151" s="3" t="s">
         <v>87</v>
@@ -5421,20 +5410,20 @@
       <c r="G151" s="6">
         <v>4860</v>
       </c>
-      <c r="H151" s="5"/>
+      <c r="H151" s="4"/>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" s="2">
         <v>6010000230</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="C152" s="4">
-        <v>46600</v>
+        <v>416</v>
+      </c>
+      <c r="C152" s="5">
+        <v>46614</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E152" s="3" t="s">
         <v>22</v>
@@ -5443,350 +5432,348 @@
         <v>5</v>
       </c>
       <c r="G152" s="6">
-        <v>620</v>
-      </c>
-      <c r="H152" s="5"/>
+        <v>2400</v>
+      </c>
+      <c r="H152" s="4"/>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" s="2">
-        <v>6010000230</v>
+        <v>6010000086</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="C153" s="4">
-        <v>46614</v>
+        <v>212</v>
+      </c>
+      <c r="C153" s="5">
+        <v>46641</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>420</v>
+        <v>213</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>22</v>
+        <v>214</v>
       </c>
       <c r="F153" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G153" s="6">
-        <v>2980</v>
-      </c>
-      <c r="H153" s="5"/>
+        <v>7000</v>
+      </c>
+      <c r="H153" s="4"/>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A154" s="2">
+      <c r="A154" s="9">
         <v>6010000086</v>
       </c>
-      <c r="B154" s="3" t="s">
+      <c r="B154" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="C154" s="11"/>
+      <c r="D154" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E154" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="C154" s="4">
-        <v>46641</v>
-      </c>
-      <c r="D154" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="E154" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="F154" s="3" t="s">
+      <c r="F154" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="G154" s="6">
-        <v>7100</v>
-      </c>
-      <c r="H154" s="5"/>
+      <c r="G154" s="12"/>
+      <c r="H154" s="13">
+        <v>2000</v>
+      </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A155" s="7">
-        <v>6010000086</v>
-      </c>
-      <c r="B155" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="C155" s="9"/>
-      <c r="D155" s="8" t="s">
+      <c r="A155" s="9">
+        <v>6010000147</v>
+      </c>
+      <c r="B155" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="C155" s="11"/>
+      <c r="D155" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E155" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="F155" s="8" t="s">
+      <c r="E155" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="F155" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="G155" s="10"/>
-      <c r="H155" s="11">
-        <v>2000</v>
+      <c r="G155" s="12"/>
+      <c r="H155" s="13">
+        <v>500</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A156" s="7">
+      <c r="A156" s="2">
         <v>6010000147</v>
       </c>
-      <c r="B156" s="8" t="s">
-        <v>318</v>
-      </c>
-      <c r="C156" s="9"/>
-      <c r="D156" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="E156" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="F156" s="8" t="s">
+      <c r="B156" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="C156" s="5">
+        <v>46813</v>
+      </c>
+      <c r="D156" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="E156" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="F156" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G156" s="10"/>
-      <c r="H156" s="11">
-        <v>500</v>
-      </c>
+      <c r="G156" s="6">
+        <v>680</v>
+      </c>
+      <c r="H156" s="4"/>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" s="2">
-        <v>6010000147</v>
+        <v>6010000144</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="C157" s="4">
-        <v>46813</v>
+        <v>308</v>
+      </c>
+      <c r="C157" s="5">
+        <v>46605</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F157" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G157" s="6">
-        <v>680</v>
-      </c>
-      <c r="H157" s="5"/>
+        <v>760</v>
+      </c>
+      <c r="H157" s="4"/>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A158" s="7">
+      <c r="A158" s="9">
         <v>6010000144</v>
       </c>
-      <c r="B158" s="8" t="s">
-        <v>310</v>
-      </c>
-      <c r="C158" s="9"/>
-      <c r="D158" s="8" t="s">
+      <c r="B158" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="C158" s="11"/>
+      <c r="D158" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E158" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="F158" s="8" t="s">
+      <c r="E158" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="F158" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="G158" s="10"/>
-      <c r="H158" s="11">
+      <c r="G158" s="12"/>
+      <c r="H158" s="13">
         <v>100</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" s="2">
-        <v>6010000144</v>
+        <v>6010000214</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="C159" s="4">
-        <v>46605</v>
+        <v>397</v>
+      </c>
+      <c r="C159" s="5">
+        <v>46692</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>311</v>
+        <v>398</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="F159" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G159" s="6">
-        <v>760</v>
-      </c>
-      <c r="H159" s="5"/>
+        <v>340</v>
+      </c>
+      <c r="H159" s="4"/>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A160" s="2">
-        <v>6010000214</v>
-      </c>
-      <c r="B160" s="3" t="s">
+      <c r="A160" s="9">
+        <v>6010000215</v>
+      </c>
+      <c r="B160" s="10" t="s">
         <v>399</v>
       </c>
-      <c r="C160" s="4">
-        <v>46692</v>
-      </c>
-      <c r="D160" s="3" t="s">
+      <c r="C160" s="11"/>
+      <c r="D160" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E160" s="10" t="s">
         <v>400</v>
       </c>
-      <c r="E160" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="F160" s="3" t="s">
+      <c r="F160" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="G160" s="6">
-        <v>340</v>
-      </c>
-      <c r="H160" s="5"/>
+      <c r="G160" s="12"/>
+      <c r="H160" s="13">
+        <v>1000</v>
+      </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A161" s="7">
+      <c r="A161" s="2">
         <v>6010000215</v>
       </c>
-      <c r="B161" s="8" t="s">
+      <c r="B161" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="C161" s="5">
+        <v>46726</v>
+      </c>
+      <c r="D161" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="C161" s="9"/>
-      <c r="D161" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="E161" s="8" t="s">
-        <v>402</v>
-      </c>
-      <c r="F161" s="8" t="s">
+      <c r="E161" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="F161" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G161" s="10"/>
-      <c r="H161" s="11">
-        <v>1000</v>
-      </c>
+      <c r="G161" s="6">
+        <v>504</v>
+      </c>
+      <c r="H161" s="4"/>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" s="2">
-        <v>6010000215</v>
+        <v>6010000142</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="C162" s="4">
-        <v>46726</v>
+        <v>302</v>
+      </c>
+      <c r="C162" s="5">
+        <v>46610</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>403</v>
+        <v>303</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>402</v>
+        <v>304</v>
       </c>
       <c r="F162" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G162" s="6">
-        <v>504</v>
-      </c>
-      <c r="H162" s="5"/>
+        <v>170</v>
+      </c>
+      <c r="H162" s="4"/>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" s="2">
-        <v>6010000142</v>
+        <v>6010000143</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="C163" s="4">
-        <v>46610</v>
+        <v>305</v>
+      </c>
+      <c r="C163" s="5">
+        <v>46425</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F163" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G163" s="6">
-        <v>200</v>
-      </c>
-      <c r="H163" s="5"/>
+        <v>107</v>
+      </c>
+      <c r="H163" s="4"/>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" s="2">
-        <v>6010000143</v>
+        <v>6010000145</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="C164" s="4">
-        <v>46425</v>
+        <v>310</v>
+      </c>
+      <c r="C164" s="5">
+        <v>46556</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="F164" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G164" s="6">
-        <v>107</v>
-      </c>
-      <c r="H164" s="5"/>
+        <v>179</v>
+      </c>
+      <c r="H164" s="4"/>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" s="2">
-        <v>6010000145</v>
+        <v>4010013596</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="C165" s="4">
-        <v>46556</v>
+        <v>111</v>
+      </c>
+      <c r="C165" s="5">
+        <v>46446</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>313</v>
+        <v>112</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>314</v>
+        <v>30</v>
       </c>
       <c r="F165" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G165" s="6">
-        <v>179</v>
-      </c>
-      <c r="H165" s="5"/>
+        <v>370</v>
+      </c>
+      <c r="H165" s="4"/>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A166" s="2">
-        <v>4010013596</v>
-      </c>
-      <c r="B166" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C166" s="4">
-        <v>46446</v>
-      </c>
-      <c r="D166" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E166" s="3" t="s">
+      <c r="A166" s="9">
+        <v>4010013655</v>
+      </c>
+      <c r="B166" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="C166" s="11"/>
+      <c r="D166" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E166" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F166" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G166" s="6">
-        <v>370</v>
-      </c>
-      <c r="H166" s="5"/>
+      <c r="F166" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G166" s="12"/>
+      <c r="H166" s="13">
+        <v>400</v>
+      </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" s="2">
         <v>4010013655</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C167" s="4">
+        <v>115</v>
+      </c>
+      <c r="C167" s="5">
         <v>46550</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E167" s="3" t="s">
         <v>30</v>
@@ -5797,29 +5784,31 @@
       <c r="G167" s="6">
         <v>670</v>
       </c>
-      <c r="H167" s="5"/>
+      <c r="H167" s="4"/>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A168" s="7">
-        <v>4010013655</v>
-      </c>
-      <c r="B168" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="C168" s="9"/>
-      <c r="D168" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="E168" s="8" t="s">
+      <c r="A168" s="2">
+        <v>4010013474</v>
+      </c>
+      <c r="B168" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C168" s="5">
+        <v>46511</v>
+      </c>
+      <c r="D168" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E168" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F168" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G168" s="10"/>
-      <c r="H168" s="11">
-        <v>400</v>
-      </c>
+      <c r="F168" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G168" s="6">
+        <v>290</v>
+      </c>
+      <c r="H168" s="4"/>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" s="2">
@@ -5828,11 +5817,11 @@
       <c r="B169" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C169" s="4">
-        <v>46511</v>
+      <c r="C169" s="5">
+        <v>46579</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E169" s="3" t="s">
         <v>30</v>
@@ -5841,22 +5830,22 @@
         <v>5</v>
       </c>
       <c r="G169" s="6">
-        <v>290</v>
-      </c>
-      <c r="H169" s="5"/>
+        <v>590</v>
+      </c>
+      <c r="H169" s="4"/>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" s="2">
-        <v>4010013474</v>
+        <v>4010013475</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C170" s="4">
-        <v>46579</v>
+        <v>54</v>
+      </c>
+      <c r="C170" s="5">
+        <v>46525</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E170" s="3" t="s">
         <v>30</v>
@@ -5865,49 +5854,49 @@
         <v>5</v>
       </c>
       <c r="G170" s="6">
-        <v>590</v>
-      </c>
-      <c r="H170" s="5"/>
+        <v>1330</v>
+      </c>
+      <c r="H170" s="4"/>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" s="2">
-        <v>4010013475</v>
+        <v>6010000087</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C171" s="4">
-        <v>46525</v>
+        <v>215</v>
+      </c>
+      <c r="C171" s="5">
+        <v>46484</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>55</v>
+        <v>216</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>30</v>
+        <v>201</v>
       </c>
       <c r="F171" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G171" s="6">
-        <v>1330</v>
-      </c>
-      <c r="H171" s="5"/>
+        <v>10000</v>
+      </c>
+      <c r="H171" s="4"/>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" s="2">
         <v>6010000087</v>
       </c>
       <c r="B172" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="C172" s="5">
+        <v>46388</v>
+      </c>
+      <c r="D172" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="C172" s="4">
-        <v>46388</v>
-      </c>
-      <c r="D172" s="3" t="s">
-        <v>218</v>
-      </c>
       <c r="E172" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F172" s="3" t="s">
         <v>3</v>
@@ -5915,191 +5904,191 @@
       <c r="G172" s="6">
         <v>4400</v>
       </c>
-      <c r="H172" s="5"/>
+      <c r="H172" s="4"/>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" s="2">
-        <v>6010000087</v>
+        <v>6010000126</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="C173" s="4">
-        <v>46484</v>
+        <v>271</v>
+      </c>
+      <c r="C173" s="5">
+        <v>46780</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>219</v>
+        <v>272</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>203</v>
+        <v>22</v>
       </c>
       <c r="F173" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G173" s="6">
-        <v>10000</v>
-      </c>
-      <c r="H173" s="5"/>
+        <v>5500</v>
+      </c>
+      <c r="H173" s="4"/>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A174" s="2">
+      <c r="A174" s="9">
         <v>6010000126</v>
       </c>
-      <c r="B174" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="C174" s="4">
-        <v>46780</v>
-      </c>
-      <c r="D174" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="E174" s="3" t="s">
+      <c r="B174" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="C174" s="11"/>
+      <c r="D174" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E174" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F174" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G174" s="6">
-        <v>5500</v>
-      </c>
-      <c r="H174" s="5"/>
+      <c r="F174" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G174" s="12"/>
+      <c r="H174" s="13">
+        <v>2000</v>
+      </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A175" s="7">
-        <v>6010000126</v>
-      </c>
-      <c r="B175" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="C175" s="9"/>
-      <c r="D175" s="8" t="s">
+      <c r="A175" s="2">
+        <v>6010000227</v>
+      </c>
+      <c r="B175" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="C175" s="5">
+        <v>46631</v>
+      </c>
+      <c r="D175" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="E175" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F175" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G175" s="6">
+        <v>4500</v>
+      </c>
+      <c r="H175" s="4"/>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A176" s="9">
+        <v>6010000227</v>
+      </c>
+      <c r="B176" s="10" t="s">
+        <v>413</v>
+      </c>
+      <c r="C176" s="11"/>
+      <c r="D176" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E175" s="8" t="s">
+      <c r="E176" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F175" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G175" s="10"/>
-      <c r="H175" s="11">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A176" s="2">
+      <c r="F176" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G176" s="12"/>
+      <c r="H176" s="13">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A177" s="2">
         <v>6010000227</v>
       </c>
-      <c r="B176" s="3" t="s">
+      <c r="B177" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="C177" s="5">
+        <v>46645</v>
+      </c>
+      <c r="D177" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="C176" s="4">
-        <v>46645</v>
-      </c>
-      <c r="D176" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="E176" s="3" t="s">
+      <c r="E177" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F176" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G176" s="6">
+      <c r="F177" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G177" s="6">
         <v>2240</v>
       </c>
-      <c r="H176" s="5"/>
-    </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A177" s="7">
-        <v>6010000227</v>
-      </c>
-      <c r="B177" s="8" t="s">
-        <v>415</v>
-      </c>
-      <c r="C177" s="9"/>
-      <c r="D177" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="E177" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F177" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G177" s="10"/>
-      <c r="H177" s="11">
-        <v>1200</v>
-      </c>
+      <c r="H177" s="4"/>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" s="2">
-        <v>6010000227</v>
+        <v>6010000088</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="C178" s="4">
-        <v>46631</v>
+        <v>218</v>
+      </c>
+      <c r="C178" s="5">
+        <v>46661</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>417</v>
+        <v>219</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>22</v>
+        <v>220</v>
       </c>
       <c r="F178" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G178" s="6">
-        <v>4700</v>
-      </c>
-      <c r="H178" s="5"/>
+        <v>2660</v>
+      </c>
+      <c r="H178" s="4"/>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" s="2">
-        <v>6010000088</v>
+        <v>4010013666</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="C179" s="4">
-        <v>46661</v>
+        <v>134</v>
+      </c>
+      <c r="C179" s="5">
+        <v>46625</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>221</v>
+        <v>135</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>222</v>
+        <v>30</v>
       </c>
       <c r="F179" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G179" s="6">
-        <v>2660</v>
-      </c>
-      <c r="H179" s="5"/>
+        <v>100</v>
+      </c>
+      <c r="H179" s="4"/>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A180" s="7">
+      <c r="A180" s="9">
         <v>4010013666</v>
       </c>
-      <c r="B180" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="C180" s="9"/>
-      <c r="D180" s="8" t="s">
+      <c r="B180" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="C180" s="11"/>
+      <c r="D180" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E180" s="8" t="s">
+      <c r="E180" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F180" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G180" s="10"/>
-      <c r="H180" s="11">
+      <c r="F180" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G180" s="12"/>
+      <c r="H180" s="13">
         <v>200</v>
       </c>
     </row>
@@ -6108,13 +6097,13 @@
         <v>4010013666</v>
       </c>
       <c r="B181" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C181" s="5">
+        <v>46593</v>
+      </c>
+      <c r="D181" s="3" t="s">
         <v>136</v>
-      </c>
-      <c r="C181" s="4">
-        <v>46625</v>
-      </c>
-      <c r="D181" s="3" t="s">
-        <v>137</v>
       </c>
       <c r="E181" s="3" t="s">
         <v>30</v>
@@ -6123,22 +6112,22 @@
         <v>5</v>
       </c>
       <c r="G181" s="6">
-        <v>100</v>
-      </c>
-      <c r="H181" s="5"/>
+        <v>200</v>
+      </c>
+      <c r="H181" s="4"/>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" s="2">
-        <v>4010013666</v>
+        <v>6010000128</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="C182" s="4">
-        <v>46593</v>
+        <v>273</v>
+      </c>
+      <c r="C182" s="5">
+        <v>46721</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>138</v>
+        <v>274</v>
       </c>
       <c r="E182" s="3" t="s">
         <v>30</v>
@@ -6147,75 +6136,75 @@
         <v>5</v>
       </c>
       <c r="G182" s="6">
-        <v>200</v>
-      </c>
-      <c r="H182" s="5"/>
+        <v>640</v>
+      </c>
+      <c r="H182" s="4"/>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A183" s="2">
+      <c r="A183" s="9">
         <v>6010000128</v>
       </c>
-      <c r="B183" s="3" t="s">
+      <c r="B183" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="C183" s="11"/>
+      <c r="D183" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E183" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F183" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G183" s="12"/>
+      <c r="H183" s="13">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A184" s="2">
+        <v>6010000129</v>
+      </c>
+      <c r="B184" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="C183" s="4">
-        <v>46721</v>
-      </c>
-      <c r="D183" s="3" t="s">
+      <c r="C184" s="5">
+        <v>46569</v>
+      </c>
+      <c r="D184" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="E183" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F183" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G183" s="6">
-        <v>640</v>
-      </c>
-      <c r="H183" s="5"/>
-    </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A184" s="7">
-        <v>6010000128</v>
-      </c>
-      <c r="B184" s="8" t="s">
+      <c r="E184" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F184" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G184" s="6">
+        <v>50</v>
+      </c>
+      <c r="H184" s="4"/>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A185" s="9">
+        <v>6010000129</v>
+      </c>
+      <c r="B185" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="C184" s="9"/>
-      <c r="D184" s="8" t="s">
+      <c r="C185" s="11"/>
+      <c r="D185" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E184" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F184" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G184" s="10"/>
-      <c r="H184" s="11">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A185" s="7">
-        <v>6010000129</v>
-      </c>
-      <c r="B185" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="C185" s="9"/>
-      <c r="D185" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="E185" s="8" t="s">
+      <c r="E185" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F185" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G185" s="10"/>
-      <c r="H185" s="11">
+      <c r="F185" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G185" s="12"/>
+      <c r="H185" s="13">
         <v>480</v>
       </c>
     </row>
@@ -6224,13 +6213,13 @@
         <v>6010000129</v>
       </c>
       <c r="B186" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C186" s="5">
+        <v>46758</v>
+      </c>
+      <c r="D186" s="3" t="s">
         <v>277</v>
-      </c>
-      <c r="C186" s="4">
-        <v>46569</v>
-      </c>
-      <c r="D186" s="3" t="s">
-        <v>278</v>
       </c>
       <c r="E186" s="3" t="s">
         <v>15</v>
@@ -6239,46 +6228,44 @@
         <v>5</v>
       </c>
       <c r="G186" s="6">
-        <v>50</v>
-      </c>
-      <c r="H186" s="5"/>
+        <v>700</v>
+      </c>
+      <c r="H186" s="4"/>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A187" s="2">
-        <v>6010000129</v>
-      </c>
-      <c r="B187" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="C187" s="4">
-        <v>46758</v>
-      </c>
-      <c r="D187" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="E187" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F187" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G187" s="6">
-        <v>700</v>
-      </c>
-      <c r="H187" s="5"/>
+      <c r="A187" s="9">
+        <v>6010000130</v>
+      </c>
+      <c r="B187" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="C187" s="11"/>
+      <c r="D187" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E187" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F187" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G187" s="12"/>
+      <c r="H187" s="13">
+        <v>300</v>
+      </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" s="2">
         <v>6010000130</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="C188" s="4">
-        <v>46569</v>
+        <v>278</v>
+      </c>
+      <c r="C188" s="5">
+        <v>46753</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E188" s="3" t="s">
         <v>30</v>
@@ -6287,22 +6274,22 @@
         <v>5</v>
       </c>
       <c r="G188" s="6">
-        <v>20</v>
-      </c>
-      <c r="H188" s="5"/>
+        <v>630</v>
+      </c>
+      <c r="H188" s="4"/>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" s="2">
         <v>6010000130</v>
       </c>
       <c r="B189" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="C189" s="5">
+        <v>46569</v>
+      </c>
+      <c r="D189" s="3" t="s">
         <v>280</v>
-      </c>
-      <c r="C189" s="4">
-        <v>46753</v>
-      </c>
-      <c r="D189" s="3" t="s">
-        <v>282</v>
       </c>
       <c r="E189" s="3" t="s">
         <v>30</v>
@@ -6311,92 +6298,94 @@
         <v>5</v>
       </c>
       <c r="G189" s="6">
-        <v>630</v>
-      </c>
-      <c r="H189" s="5"/>
+        <v>20</v>
+      </c>
+      <c r="H189" s="4"/>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A190" s="7">
-        <v>6010000130</v>
-      </c>
-      <c r="B190" s="8" t="s">
-        <v>280</v>
-      </c>
-      <c r="C190" s="9"/>
-      <c r="D190" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="E190" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F190" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G190" s="10"/>
-      <c r="H190" s="11">
-        <v>300</v>
-      </c>
+      <c r="A190" s="2">
+        <v>6010000198</v>
+      </c>
+      <c r="B190" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="C190" s="5">
+        <v>46568</v>
+      </c>
+      <c r="D190" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="E190" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F190" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G190" s="6">
+        <v>600</v>
+      </c>
+      <c r="H190" s="4"/>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" s="2">
-        <v>6010000198</v>
+        <v>4010013586</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="C191" s="4">
-        <v>46568</v>
+        <v>98</v>
+      </c>
+      <c r="C191" s="5">
+        <v>46537</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>386</v>
+        <v>99</v>
       </c>
       <c r="E191" s="3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F191" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G191" s="6">
-        <v>600</v>
-      </c>
-      <c r="H191" s="5"/>
+        <v>1280</v>
+      </c>
+      <c r="H191" s="4"/>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192" s="2">
-        <v>4010013586</v>
+        <v>4010013549</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C192" s="4">
-        <v>46537</v>
+        <v>71</v>
+      </c>
+      <c r="C192" s="5">
+        <v>46525</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="E192" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F192" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G192" s="6">
-        <v>1280</v>
-      </c>
-      <c r="H192" s="5"/>
+        <v>980</v>
+      </c>
+      <c r="H192" s="4"/>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" s="2">
-        <v>4010013587</v>
+        <v>4010013249</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C193" s="4">
-        <v>46537</v>
+        <v>0</v>
+      </c>
+      <c r="C193" s="5">
+        <v>46442</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="E193" s="3" t="s">
         <v>4</v>
@@ -6405,70 +6394,70 @@
         <v>5</v>
       </c>
       <c r="G193" s="6">
-        <v>140</v>
-      </c>
-      <c r="H193" s="5"/>
+        <v>420</v>
+      </c>
+      <c r="H193" s="4"/>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" s="2">
-        <v>4010013549</v>
+        <v>4010013573</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C194" s="4">
-        <v>46525</v>
+        <v>79</v>
+      </c>
+      <c r="C194" s="5">
+        <v>46423</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F194" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G194" s="6">
-        <v>980</v>
-      </c>
-      <c r="H194" s="5"/>
+        <v>500</v>
+      </c>
+      <c r="H194" s="4"/>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" s="2">
-        <v>4010013249</v>
+        <v>4010013574</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C195" s="4">
-        <v>46442</v>
+        <v>81</v>
+      </c>
+      <c r="C195" s="5">
+        <v>46545</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>1</v>
+        <v>82</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F195" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G195" s="6">
-        <v>420</v>
-      </c>
-      <c r="H195" s="5"/>
+        <v>600</v>
+      </c>
+      <c r="H195" s="4"/>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" s="2">
-        <v>4010013573</v>
+        <v>4010013588</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C196" s="4">
-        <v>46423</v>
+        <v>100</v>
+      </c>
+      <c r="C196" s="5">
+        <v>46582</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="E196" s="3" t="s">
         <v>4</v>
@@ -6477,46 +6466,46 @@
         <v>5</v>
       </c>
       <c r="G196" s="6">
-        <v>500</v>
-      </c>
-      <c r="H196" s="5"/>
+        <v>2800</v>
+      </c>
+      <c r="H196" s="4"/>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" s="2">
-        <v>4010013574</v>
+        <v>4010013479</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C197" s="4">
-        <v>46545</v>
+        <v>62</v>
+      </c>
+      <c r="C197" s="5">
+        <v>46594</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="E197" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F197" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G197" s="6">
-        <v>600</v>
-      </c>
-      <c r="H197" s="5"/>
+        <v>400</v>
+      </c>
+      <c r="H197" s="4"/>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" s="2">
-        <v>4010013588</v>
+        <v>4010013479</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C198" s="4">
-        <v>46582</v>
+        <v>62</v>
+      </c>
+      <c r="C198" s="5">
+        <v>46536</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>103</v>
+        <v>64</v>
       </c>
       <c r="E198" s="3" t="s">
         <v>4</v>
@@ -6525,9 +6514,9 @@
         <v>5</v>
       </c>
       <c r="G198" s="6">
-        <v>3000</v>
-      </c>
-      <c r="H198" s="5"/>
+        <v>320</v>
+      </c>
+      <c r="H198" s="4"/>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" s="2">
@@ -6536,11 +6525,11 @@
       <c r="B199" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C199" s="4">
-        <v>46594</v>
+      <c r="C199" s="5">
+        <v>46419</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E199" s="3" t="s">
         <v>4</v>
@@ -6549,22 +6538,22 @@
         <v>5</v>
       </c>
       <c r="G199" s="6">
-        <v>400</v>
-      </c>
-      <c r="H199" s="5"/>
+        <v>200</v>
+      </c>
+      <c r="H199" s="4"/>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" s="2">
-        <v>4010013479</v>
+        <v>4010013700</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C200" s="4">
-        <v>46419</v>
+        <v>148</v>
+      </c>
+      <c r="C200" s="5">
+        <v>46446</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>64</v>
+        <v>149</v>
       </c>
       <c r="E200" s="3" t="s">
         <v>4</v>
@@ -6573,22 +6562,22 @@
         <v>5</v>
       </c>
       <c r="G200" s="6">
-        <v>200</v>
-      </c>
-      <c r="H200" s="5"/>
+        <v>560</v>
+      </c>
+      <c r="H200" s="4"/>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" s="2">
-        <v>4010013479</v>
+        <v>4010013700</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C201" s="4">
-        <v>46536</v>
+        <v>148</v>
+      </c>
+      <c r="C201" s="5">
+        <v>46533</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="E201" s="3" t="s">
         <v>4</v>
@@ -6597,22 +6586,22 @@
         <v>5</v>
       </c>
       <c r="G201" s="6">
-        <v>320</v>
-      </c>
-      <c r="H201" s="5"/>
+        <v>300</v>
+      </c>
+      <c r="H201" s="4"/>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202" s="2">
-        <v>4010013700</v>
+        <v>4010013701</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C202" s="4">
-        <v>46446</v>
+        <v>151</v>
+      </c>
+      <c r="C202" s="5">
+        <v>46589</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E202" s="3" t="s">
         <v>4</v>
@@ -6621,67 +6610,65 @@
         <v>5</v>
       </c>
       <c r="G202" s="6">
-        <v>560</v>
-      </c>
-      <c r="H202" s="5"/>
+        <v>1160</v>
+      </c>
+      <c r="H202" s="4"/>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203" s="2">
-        <v>4010013700</v>
+        <v>4010013657</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C203" s="4">
-        <v>46533</v>
+        <v>120</v>
+      </c>
+      <c r="C203" s="5">
+        <v>46513</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>152</v>
+        <v>121</v>
       </c>
       <c r="E203" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F203" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G203" s="6">
-        <v>300</v>
-      </c>
-      <c r="H203" s="5"/>
+        <v>800</v>
+      </c>
+      <c r="H203" s="4"/>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A204" s="2">
-        <v>4010013701</v>
-      </c>
-      <c r="B204" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="C204" s="4">
-        <v>46589</v>
-      </c>
-      <c r="D204" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="E204" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F204" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G204" s="6">
-        <v>1160</v>
-      </c>
-      <c r="H204" s="5"/>
+      <c r="A204" s="9">
+        <v>4010013657</v>
+      </c>
+      <c r="B204" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="C204" s="11"/>
+      <c r="D204" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E204" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F204" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G204" s="12"/>
+      <c r="H204" s="13">
+        <v>160</v>
+      </c>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205" s="2">
-        <v>4010013657</v>
+        <v>4010013658</v>
       </c>
       <c r="B205" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C205" s="4">
-        <v>46513</v>
+      <c r="C205" s="5">
+        <v>46587</v>
       </c>
       <c r="D205" s="3" t="s">
         <v>123</v>
@@ -6693,44 +6680,46 @@
         <v>5</v>
       </c>
       <c r="G205" s="6">
-        <v>800</v>
-      </c>
-      <c r="H205" s="5"/>
+        <v>1170</v>
+      </c>
+      <c r="H205" s="4"/>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A206" s="7">
-        <v>4010013657</v>
-      </c>
-      <c r="B206" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="C206" s="9"/>
-      <c r="D206" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="E206" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F206" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G206" s="10"/>
-      <c r="H206" s="11">
-        <v>160</v>
-      </c>
+      <c r="A206" s="2">
+        <v>4010013548</v>
+      </c>
+      <c r="B206" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C206" s="5">
+        <v>46469</v>
+      </c>
+      <c r="D206" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E206" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F206" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G206" s="6">
+        <v>830</v>
+      </c>
+      <c r="H206" s="4"/>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A207" s="2">
-        <v>4010013658</v>
+        <v>4010013480</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="C207" s="4">
-        <v>46587</v>
+        <v>66</v>
+      </c>
+      <c r="C207" s="5">
+        <v>46408</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>125</v>
+        <v>67</v>
       </c>
       <c r="E207" s="3" t="s">
         <v>8</v>
@@ -6739,308 +6728,308 @@
         <v>5</v>
       </c>
       <c r="G207" s="6">
-        <v>1170</v>
-      </c>
-      <c r="H207" s="5"/>
+        <v>1230</v>
+      </c>
+      <c r="H207" s="4"/>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208" s="2">
-        <v>4010013548</v>
+        <v>4010013477</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C208" s="4">
-        <v>46469</v>
+        <v>58</v>
+      </c>
+      <c r="C208" s="5">
+        <v>46574</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E208" s="3" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="F208" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G208" s="6">
-        <v>830</v>
-      </c>
-      <c r="H208" s="5"/>
+        <v>680</v>
+      </c>
+      <c r="H208" s="4"/>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" s="2">
-        <v>4010013480</v>
+        <v>6010000131</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C209" s="4">
-        <v>46408</v>
+        <v>281</v>
+      </c>
+      <c r="C209" s="5">
+        <v>46784</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>67</v>
+        <v>282</v>
       </c>
       <c r="E209" s="3" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F209" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G209" s="6">
-        <v>1230</v>
-      </c>
-      <c r="H209" s="5"/>
+        <v>1960</v>
+      </c>
+      <c r="H209" s="4"/>
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210" s="2">
-        <v>4010013477</v>
+        <v>4010013699</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C210" s="4">
-        <v>46574</v>
+        <v>146</v>
+      </c>
+      <c r="C210" s="5">
+        <v>46438</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>59</v>
+        <v>147</v>
       </c>
       <c r="E210" s="3" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F210" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G210" s="6">
-        <v>680</v>
-      </c>
-      <c r="H210" s="5"/>
+        <v>350</v>
+      </c>
+      <c r="H210" s="4"/>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211" s="2">
-        <v>6010000131</v>
+        <v>6010000089</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="C211" s="4">
-        <v>46784</v>
+        <v>221</v>
+      </c>
+      <c r="C211" s="5">
+        <v>46424</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>284</v>
+        <v>222</v>
       </c>
       <c r="E211" s="3" t="s">
-        <v>22</v>
+        <v>223</v>
       </c>
       <c r="F211" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G211" s="6">
-        <v>1960</v>
-      </c>
-      <c r="H211" s="5"/>
+        <v>2360</v>
+      </c>
+      <c r="H211" s="4"/>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212" s="2">
-        <v>4010013699</v>
+        <v>6010000089</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="C212" s="4">
-        <v>46438</v>
+        <v>221</v>
+      </c>
+      <c r="C212" s="5">
+        <v>46871</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
       <c r="E212" s="3" t="s">
-        <v>30</v>
+        <v>223</v>
       </c>
       <c r="F212" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G212" s="6">
-        <v>350</v>
-      </c>
-      <c r="H212" s="5"/>
+        <v>2300</v>
+      </c>
+      <c r="H212" s="4"/>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213" s="2">
-        <v>6010000089</v>
+        <v>6010000132</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="C213" s="4">
-        <v>46871</v>
+        <v>283</v>
+      </c>
+      <c r="C213" s="5">
+        <v>46614</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>224</v>
+        <v>2</v>
       </c>
       <c r="E213" s="3" t="s">
-        <v>225</v>
+        <v>30</v>
       </c>
       <c r="F213" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G213" s="6">
-        <v>2300</v>
-      </c>
-      <c r="H213" s="5"/>
+        <v>2860</v>
+      </c>
+      <c r="H213" s="4"/>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214" s="2">
-        <v>6010000089</v>
+        <v>6010000146</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="C214" s="4">
-        <v>46424</v>
+        <v>313</v>
+      </c>
+      <c r="C214" s="5">
+        <v>46746</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>226</v>
+        <v>314</v>
       </c>
       <c r="E214" s="3" t="s">
-        <v>225</v>
+        <v>315</v>
       </c>
       <c r="F214" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G214" s="6">
-        <v>2360</v>
-      </c>
-      <c r="H214" s="5"/>
+        <v>480</v>
+      </c>
+      <c r="H214" s="4"/>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A215" s="2">
-        <v>6010000132</v>
-      </c>
-      <c r="B215" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="C215" s="4">
-        <v>46614</v>
-      </c>
-      <c r="D215" s="3" t="s">
+      <c r="A215" s="9">
+        <v>6010000146</v>
+      </c>
+      <c r="B215" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="C215" s="11"/>
+      <c r="D215" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E215" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F215" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G215" s="6">
-        <v>2860</v>
-      </c>
-      <c r="H215" s="5"/>
+      <c r="E215" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="F215" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="G215" s="12"/>
+      <c r="H215" s="13">
+        <v>480</v>
+      </c>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A216" s="2">
-        <v>6010000146</v>
+        <v>6010000090</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="C216" s="4">
-        <v>46746</v>
+        <v>225</v>
+      </c>
+      <c r="C216" s="5">
+        <v>46482</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>316</v>
+        <v>226</v>
       </c>
       <c r="E216" s="3" t="s">
-        <v>317</v>
+        <v>173</v>
       </c>
       <c r="F216" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G216" s="6">
-        <v>480</v>
-      </c>
-      <c r="H216" s="5"/>
+        <v>4420</v>
+      </c>
+      <c r="H216" s="4"/>
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A217" s="7">
-        <v>6010000146</v>
-      </c>
-      <c r="B217" s="8" t="s">
-        <v>315</v>
-      </c>
-      <c r="C217" s="9"/>
-      <c r="D217" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="E217" s="8" t="s">
-        <v>317</v>
-      </c>
-      <c r="F217" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="G217" s="10"/>
-      <c r="H217" s="11">
-        <v>480</v>
-      </c>
+      <c r="A217" s="2">
+        <v>6010000199</v>
+      </c>
+      <c r="B217" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="C217" s="5">
+        <v>46556</v>
+      </c>
+      <c r="D217" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="E217" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F217" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G217" s="6">
+        <v>1680</v>
+      </c>
+      <c r="H217" s="4"/>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218" s="2">
-        <v>6010000090</v>
+        <v>6010000133</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="C218" s="4">
-        <v>46482</v>
+        <v>284</v>
+      </c>
+      <c r="C218" s="5">
+        <v>46388</v>
       </c>
       <c r="D218" s="3" t="s">
-        <v>228</v>
+        <v>285</v>
       </c>
       <c r="E218" s="3" t="s">
-        <v>175</v>
+        <v>87</v>
       </c>
       <c r="F218" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G218" s="6">
-        <v>4420</v>
-      </c>
-      <c r="H218" s="5"/>
+        <v>1100</v>
+      </c>
+      <c r="H218" s="4"/>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" s="2">
-        <v>6010000199</v>
+        <v>6010000134</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="C219" s="4">
-        <v>46556</v>
+        <v>286</v>
+      </c>
+      <c r="C219" s="5">
+        <v>46488</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>388</v>
+        <v>287</v>
       </c>
       <c r="E219" s="3" t="s">
-        <v>22</v>
+        <v>87</v>
       </c>
       <c r="F219" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G219" s="6">
-        <v>1680</v>
-      </c>
-      <c r="H219" s="5"/>
+        <v>1180</v>
+      </c>
+      <c r="H219" s="4"/>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A220" s="2">
-        <v>6010000133</v>
+        <v>6010000135</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="C220" s="4">
+        <v>288</v>
+      </c>
+      <c r="C220" s="5">
         <v>46388</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E220" s="3" t="s">
         <v>87</v>
@@ -7049,214 +7038,214 @@
         <v>5</v>
       </c>
       <c r="G220" s="6">
-        <v>1100</v>
-      </c>
-      <c r="H220" s="5"/>
+        <v>1560</v>
+      </c>
+      <c r="H220" s="4"/>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221" s="2">
-        <v>6010000134</v>
+        <v>6010000136</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="C221" s="4">
-        <v>46488</v>
+        <v>290</v>
+      </c>
+      <c r="C221" s="5">
+        <v>46496</v>
       </c>
       <c r="D221" s="3" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E221" s="3" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="F221" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G221" s="6">
-        <v>1180</v>
-      </c>
-      <c r="H221" s="5"/>
+        <v>530</v>
+      </c>
+      <c r="H221" s="4"/>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A222" s="2">
-        <v>6010000135</v>
+        <v>6010000137</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="C222" s="4">
-        <v>46388</v>
+        <v>292</v>
+      </c>
+      <c r="C222" s="5">
+        <v>46496</v>
       </c>
       <c r="D222" s="3" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E222" s="3" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="F222" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G222" s="6">
-        <v>1560</v>
-      </c>
-      <c r="H222" s="5"/>
+        <v>370</v>
+      </c>
+      <c r="H222" s="4"/>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A223" s="2">
-        <v>6010000136</v>
+        <v>4010013269</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="C223" s="4">
-        <v>46496</v>
+        <v>20</v>
+      </c>
+      <c r="C223" s="5">
+        <v>46558</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>293</v>
+        <v>21</v>
       </c>
       <c r="E223" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F223" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G223" s="6">
-        <v>530</v>
-      </c>
-      <c r="H223" s="5"/>
+        <v>900</v>
+      </c>
+      <c r="H223" s="4"/>
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A224" s="2">
-        <v>6010000137</v>
+        <v>6010000177</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="C224" s="4">
-        <v>46496</v>
+        <v>360</v>
+      </c>
+      <c r="C224" s="5">
+        <v>46971</v>
       </c>
       <c r="D224" s="3" t="s">
-        <v>295</v>
+        <v>361</v>
       </c>
       <c r="E224" s="3" t="s">
-        <v>30</v>
+        <v>362</v>
       </c>
       <c r="F224" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G224" s="6">
-        <v>370</v>
-      </c>
-      <c r="H224" s="5"/>
+        <v>2880</v>
+      </c>
+      <c r="H224" s="4"/>
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A225" s="2">
-        <v>4010013269</v>
+        <v>6010000178</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C225" s="4">
-        <v>46558</v>
+        <v>363</v>
+      </c>
+      <c r="C225" s="5">
+        <v>47087</v>
       </c>
       <c r="D225" s="3" t="s">
-        <v>21</v>
+        <v>364</v>
       </c>
       <c r="E225" s="3" t="s">
-        <v>22</v>
+        <v>365</v>
       </c>
       <c r="F225" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G225" s="6">
-        <v>900</v>
-      </c>
-      <c r="H225" s="5"/>
+        <v>1140</v>
+      </c>
+      <c r="H225" s="4"/>
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226" s="2">
-        <v>6010000177</v>
+        <v>4010013597</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="C226" s="4">
-        <v>46971</v>
+        <v>113</v>
+      </c>
+      <c r="C226" s="5">
+        <v>46525</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>363</v>
+        <v>114</v>
       </c>
       <c r="E226" s="3" t="s">
-        <v>364</v>
+        <v>11</v>
       </c>
       <c r="F226" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G226" s="6">
-        <v>2880</v>
-      </c>
-      <c r="H226" s="5"/>
+        <v>620</v>
+      </c>
+      <c r="H226" s="4"/>
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A227" s="2">
-        <v>6010000178</v>
+        <v>4010013368</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="C227" s="4">
-        <v>47087</v>
+        <v>32</v>
+      </c>
+      <c r="C227" s="5">
+        <v>46533</v>
       </c>
       <c r="D227" s="3" t="s">
-        <v>366</v>
+        <v>33</v>
       </c>
       <c r="E227" s="3" t="s">
-        <v>367</v>
+        <v>4</v>
       </c>
       <c r="F227" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G227" s="6">
-        <v>1140</v>
-      </c>
-      <c r="H227" s="5"/>
+        <v>160</v>
+      </c>
+      <c r="H227" s="4"/>
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228" s="2">
-        <v>4010013597</v>
+        <v>4010013369</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C228" s="4">
-        <v>46525</v>
+        <v>34</v>
+      </c>
+      <c r="C228" s="5">
+        <v>46429</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>116</v>
+        <v>35</v>
       </c>
       <c r="E228" s="3" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F228" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G228" s="6">
-        <v>620</v>
-      </c>
-      <c r="H228" s="5"/>
+        <v>340</v>
+      </c>
+      <c r="H228" s="4"/>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A229" s="2">
-        <v>4010013368</v>
+        <v>4010013369</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C229" s="4">
+        <v>34</v>
+      </c>
+      <c r="C229" s="5">
         <v>46533</v>
       </c>
       <c r="D229" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E229" s="3" t="s">
         <v>4</v>
@@ -7265,282 +7254,282 @@
         <v>5</v>
       </c>
       <c r="G229" s="6">
-        <v>160</v>
-      </c>
-      <c r="H229" s="5"/>
+        <v>80</v>
+      </c>
+      <c r="H229" s="4"/>
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A230" s="2">
-        <v>4010013369</v>
+        <v>4010013399</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C230" s="4">
-        <v>46533</v>
+        <v>42</v>
+      </c>
+      <c r="C230" s="5">
+        <v>46532</v>
       </c>
       <c r="D230" s="3" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E230" s="3" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F230" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G230" s="6">
-        <v>80</v>
-      </c>
-      <c r="H230" s="5"/>
+        <v>1290</v>
+      </c>
+      <c r="H230" s="4"/>
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A231" s="2">
-        <v>4010013369</v>
+        <v>6010000203</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C231" s="4">
-        <v>46429</v>
+        <v>392</v>
+      </c>
+      <c r="C231" s="5">
+        <v>46606</v>
       </c>
       <c r="D231" s="3" t="s">
-        <v>36</v>
+        <v>393</v>
       </c>
       <c r="E231" s="3" t="s">
-        <v>4</v>
+        <v>389</v>
       </c>
       <c r="F231" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G231" s="6">
-        <v>340</v>
-      </c>
-      <c r="H231" s="5"/>
+        <v>460</v>
+      </c>
+      <c r="H231" s="4"/>
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A232" s="2">
-        <v>4010013399</v>
+        <v>4010013592</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C232" s="4">
-        <v>46532</v>
+        <v>102</v>
+      </c>
+      <c r="C232" s="5">
+        <v>46514</v>
       </c>
       <c r="D232" s="3" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="E232" s="3" t="s">
-        <v>22</v>
+        <v>104</v>
       </c>
       <c r="F232" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G232" s="6">
-        <v>1290</v>
-      </c>
-      <c r="H232" s="5"/>
+        <v>240</v>
+      </c>
+      <c r="H232" s="4"/>
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A233" s="2">
-        <v>6010000203</v>
+        <v>4010014926</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="C233" s="4">
-        <v>46606</v>
+        <v>157</v>
+      </c>
+      <c r="C233" s="5">
+        <v>46768</v>
       </c>
       <c r="D233" s="3" t="s">
-        <v>395</v>
+        <v>158</v>
       </c>
       <c r="E233" s="3" t="s">
-        <v>391</v>
+        <v>159</v>
       </c>
       <c r="F233" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G233" s="6">
-        <v>460</v>
-      </c>
-      <c r="H233" s="5"/>
+        <v>780</v>
+      </c>
+      <c r="H233" s="4"/>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A234" s="2">
-        <v>4010013592</v>
+        <v>7050000020</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="C234" s="4">
-        <v>46514</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="C234" s="5"/>
       <c r="D234" s="3" t="s">
-        <v>105</v>
+        <v>2</v>
       </c>
       <c r="E234" s="3" t="s">
-        <v>106</v>
+        <v>2</v>
       </c>
       <c r="F234" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G234" s="6">
-        <v>240</v>
-      </c>
-      <c r="H234" s="5"/>
+        <v>30</v>
+      </c>
+      <c r="H234" s="4"/>
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A235" s="2">
-        <v>4010014926</v>
+        <v>7050000020</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="C235" s="4">
-        <v>46768</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="C235" s="5"/>
       <c r="D235" s="3" t="s">
-        <v>160</v>
+        <v>2</v>
       </c>
       <c r="E235" s="3" t="s">
-        <v>161</v>
+        <v>2</v>
       </c>
       <c r="F235" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G235" s="6">
-        <v>780</v>
-      </c>
-      <c r="H235" s="5"/>
+        <v>70</v>
+      </c>
+      <c r="H235" s="4"/>
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A236" s="2">
-        <v>7050000020</v>
+        <v>4010013659</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="C236" s="4"/>
+        <v>124</v>
+      </c>
+      <c r="C236" s="5">
+        <v>46526</v>
+      </c>
       <c r="D236" s="3" t="s">
-        <v>2</v>
+        <v>125</v>
       </c>
       <c r="E236" s="3" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F236" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G236" s="6">
-        <v>30</v>
-      </c>
-      <c r="H236" s="5"/>
+        <v>1270</v>
+      </c>
+      <c r="H236" s="4"/>
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A237" s="2">
-        <v>7050000020</v>
+        <v>4010013273</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="C237" s="4"/>
+        <v>28</v>
+      </c>
+      <c r="C237" s="5">
+        <v>46444</v>
+      </c>
       <c r="D237" s="3" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="E237" s="3" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="F237" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G237" s="6">
-        <v>70</v>
-      </c>
-      <c r="H237" s="5"/>
+        <v>20</v>
+      </c>
+      <c r="H237" s="4"/>
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238" s="2">
-        <v>4010013659</v>
+        <v>4010013273</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C238" s="4">
-        <v>46526</v>
+        <v>28</v>
+      </c>
+      <c r="C238" s="5">
+        <v>46444</v>
       </c>
       <c r="D238" s="3" t="s">
-        <v>127</v>
+        <v>31</v>
       </c>
       <c r="E238" s="3" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F238" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G238" s="6">
-        <v>1270</v>
-      </c>
-      <c r="H238" s="5"/>
+        <v>710</v>
+      </c>
+      <c r="H238" s="4"/>
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A239" s="2">
-        <v>4010013273</v>
+        <v>4010013271</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C239" s="4">
-        <v>46444</v>
+        <v>23</v>
+      </c>
+      <c r="C239" s="5">
+        <v>46402</v>
       </c>
       <c r="D239" s="3" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E239" s="3" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F239" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G239" s="6">
-        <v>710</v>
-      </c>
-      <c r="H239" s="5"/>
+        <v>300</v>
+      </c>
+      <c r="H239" s="4"/>
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A240" s="2">
-        <v>4010013273</v>
+        <v>4010013272</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C240" s="4">
-        <v>46444</v>
+        <v>25</v>
+      </c>
+      <c r="C240" s="5">
+        <v>46523</v>
       </c>
       <c r="D240" s="3" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E240" s="3" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F240" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G240" s="6">
-        <v>20</v>
-      </c>
-      <c r="H240" s="5"/>
+        <v>1100</v>
+      </c>
+      <c r="H240" s="4"/>
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A241" s="2">
-        <v>4010013271</v>
+        <v>4010013272</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C241" s="4">
-        <v>46402</v>
+        <v>25</v>
+      </c>
+      <c r="C241" s="5">
+        <v>46594</v>
       </c>
       <c r="D241" s="3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E241" s="3" t="s">
         <v>8</v>
@@ -7549,22 +7538,22 @@
         <v>5</v>
       </c>
       <c r="G241" s="6">
-        <v>300</v>
-      </c>
-      <c r="H241" s="5"/>
+        <v>360</v>
+      </c>
+      <c r="H241" s="4"/>
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242" s="2">
-        <v>4010013272</v>
+        <v>4010013663</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C242" s="4">
-        <v>46523</v>
+        <v>131</v>
+      </c>
+      <c r="C242" s="5">
+        <v>46514</v>
       </c>
       <c r="D242" s="3" t="s">
-        <v>26</v>
+        <v>132</v>
       </c>
       <c r="E242" s="3" t="s">
         <v>8</v>
@@ -7573,22 +7562,22 @@
         <v>5</v>
       </c>
       <c r="G242" s="6">
-        <v>1100</v>
-      </c>
-      <c r="H242" s="5"/>
+        <v>100</v>
+      </c>
+      <c r="H242" s="4"/>
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A243" s="2">
-        <v>4010013272</v>
+        <v>4010013663</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C243" s="4">
-        <v>46594</v>
+        <v>131</v>
+      </c>
+      <c r="C243" s="5">
+        <v>46612</v>
       </c>
       <c r="D243" s="3" t="s">
-        <v>27</v>
+        <v>133</v>
       </c>
       <c r="E243" s="3" t="s">
         <v>8</v>
@@ -7597,158 +7586,110 @@
         <v>5</v>
       </c>
       <c r="G243" s="6">
-        <v>360</v>
-      </c>
-      <c r="H243" s="5"/>
+        <v>1200</v>
+      </c>
+      <c r="H243" s="4"/>
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A244" s="2">
-        <v>4010013663</v>
+        <v>6010000093</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="C244" s="4">
-        <v>46612</v>
+        <v>227</v>
+      </c>
+      <c r="C244" s="5">
+        <v>46484</v>
       </c>
       <c r="D244" s="3" t="s">
-        <v>134</v>
+        <v>228</v>
       </c>
       <c r="E244" s="3" t="s">
-        <v>8</v>
+        <v>229</v>
       </c>
       <c r="F244" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G244" s="6">
-        <v>1200</v>
-      </c>
-      <c r="H244" s="5"/>
+        <v>33000</v>
+      </c>
+      <c r="H244" s="4"/>
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A245" s="2">
-        <v>4010013663</v>
+        <v>6010000093</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="C245" s="4">
-        <v>46514</v>
+        <v>227</v>
+      </c>
+      <c r="C245" s="5">
+        <v>46504</v>
       </c>
       <c r="D245" s="3" t="s">
-        <v>135</v>
+        <v>230</v>
       </c>
       <c r="E245" s="3" t="s">
-        <v>8</v>
+        <v>229</v>
       </c>
       <c r="F245" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G245" s="6">
-        <v>100</v>
-      </c>
-      <c r="H245" s="5"/>
+        <v>15000</v>
+      </c>
+      <c r="H245" s="4"/>
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A246" s="2">
-        <v>6010000093</v>
+        <v>6010000161</v>
       </c>
       <c r="B246" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="C246" s="4">
-        <v>46484</v>
+        <v>338</v>
+      </c>
+      <c r="C246" s="5">
+        <v>47087</v>
       </c>
       <c r="D246" s="3" t="s">
-        <v>230</v>
+        <v>339</v>
       </c>
       <c r="E246" s="3" t="s">
-        <v>231</v>
+        <v>340</v>
       </c>
       <c r="F246" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G246" s="6">
-        <v>33000</v>
-      </c>
-      <c r="H246" s="5"/>
+        <v>630</v>
+      </c>
+      <c r="H246" s="4"/>
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A247" s="2">
-        <v>6010000093</v>
+        <v>6010000162</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="C247" s="4">
-        <v>46504</v>
+        <v>341</v>
+      </c>
+      <c r="C247" s="5">
+        <v>47087</v>
       </c>
       <c r="D247" s="3" t="s">
-        <v>232</v>
+        <v>342</v>
       </c>
       <c r="E247" s="3" t="s">
-        <v>231</v>
+        <v>343</v>
       </c>
       <c r="F247" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G247" s="6">
-        <v>15000</v>
-      </c>
-      <c r="H247" s="5"/>
-    </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A248" s="2">
-        <v>6010000161</v>
-      </c>
-      <c r="B248" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="C248" s="4">
-        <v>47087</v>
-      </c>
-      <c r="D248" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="E248" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="F248" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G248" s="6">
-        <v>666</v>
-      </c>
-      <c r="H248" s="5"/>
-    </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A249" s="2">
-        <v>6010000162</v>
-      </c>
-      <c r="B249" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="C249" s="4">
-        <v>47087</v>
-      </c>
-      <c r="D249" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="E249" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="F249" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G249" s="6">
         <v>1152</v>
       </c>
-      <c r="H249" s="5"/>
+      <c r="H247" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H249" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H249">
-      <sortCondition ref="B1:B249"/>
+  <autoFilter ref="A1:H247" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H247">
+      <sortCondition ref="B1:B247"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="0" type="noConversion"/>

--- a/KSTOCK.xlsx
+++ b/KSTOCK.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c2e6f8dd72a68295/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="53" documentId="11_BEF63D5DC4094E6A3107ECA5BE8046033DF61370" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BEA496B4-9D37-42F7-8418-02E41D7C721D}"/>
+  <xr:revisionPtr revIDLastSave="55" documentId="11_B0E21E57C4094E9AB632FCC5BE68F68731D2BFB0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7EF7475F-5E09-4EF5-B703-668D059BD81C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$242</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$241</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="973" uniqueCount="445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="969" uniqueCount="445">
   <si>
     <t>ROSUSEP-20</t>
   </si>
@@ -181,12 +181,12 @@
     <t>PROGISPHERE SR 200</t>
   </si>
   <si>
+    <t>25S2HTA612</t>
+  </si>
+  <si>
     <t>25S2HTA863</t>
   </si>
   <si>
-    <t>25S2HTA612</t>
-  </si>
-  <si>
     <t>PROGISPHERE SR 300</t>
   </si>
   <si>
@@ -217,12 +217,12 @@
     <t>25S3GCA034</t>
   </si>
   <si>
+    <t>25S3GCA105</t>
+  </si>
+  <si>
     <t>25S3GCA138</t>
   </si>
   <si>
-    <t>25S3GCA105</t>
-  </si>
-  <si>
     <t>SITAFREE-MET 1000 IR</t>
   </si>
   <si>
@@ -448,12 +448,12 @@
     <t>ATROLIA GOLD 20/75</t>
   </si>
   <si>
+    <t>25S3GCA129</t>
+  </si>
+  <si>
     <t>25S3GCA113</t>
   </si>
   <si>
-    <t>25S3GCA129</t>
-  </si>
-  <si>
     <t>Atrolia-ASP 75</t>
   </si>
   <si>
@@ -469,12 +469,12 @@
     <t>ROSUSEP-CV 10</t>
   </si>
   <si>
+    <t>25S3GCA099</t>
+  </si>
+  <si>
     <t>25S3GCA046</t>
   </si>
   <si>
-    <t>25S3GCA099</t>
-  </si>
-  <si>
     <t>ROSUSEP-CV 20</t>
   </si>
   <si>
@@ -538,21 +538,21 @@
     <t>CEFTAPACE-1G</t>
   </si>
   <si>
+    <t>NL2742601</t>
+  </si>
+  <si>
     <t>1X10ML</t>
   </si>
   <si>
-    <t>NL2742601</t>
-  </si>
-  <si>
     <t>CLAVMYCIN IV</t>
   </si>
   <si>
+    <t>NKCL12502</t>
+  </si>
+  <si>
     <t>10X1X1.2 G(SWFI)</t>
   </si>
   <si>
-    <t>NKCL12502</t>
-  </si>
-  <si>
     <t>DECAHIT INJECTION</t>
   </si>
   <si>
@@ -688,15 +688,15 @@
     <t>VOLOPAIN INJ</t>
   </si>
   <si>
+    <t>NL2702506</t>
+  </si>
+  <si>
+    <t>20X5X3ML</t>
+  </si>
+  <si>
     <t>NL2702507</t>
   </si>
   <si>
-    <t>20X5X3ML</t>
-  </si>
-  <si>
-    <t>NL2702506</t>
-  </si>
-  <si>
     <t>ACECLOPHARM-MR TABLET</t>
   </si>
   <si>
@@ -709,15 +709,15 @@
     <t>AMLINA-5 TABLET</t>
   </si>
   <si>
+    <t>T50499A</t>
+  </si>
+  <si>
+    <t>20X30</t>
+  </si>
+  <si>
     <t>T60096A</t>
   </si>
   <si>
-    <t>20X30</t>
-  </si>
-  <si>
-    <t>T50499A</t>
-  </si>
-  <si>
     <t>AMLINA-AT TABLET</t>
   </si>
   <si>
@@ -832,9 +832,6 @@
     <t>RIFIXIEM 550 TABLET</t>
   </si>
   <si>
-    <t>GE545002B</t>
-  </si>
-  <si>
     <t>GE545020</t>
   </si>
   <si>
@@ -847,6 +844,9 @@
     <t>SYNOBIT PLUS CAPSULE</t>
   </si>
   <si>
+    <t>MC2509095</t>
+  </si>
+  <si>
     <t>TELIKEM 20 TABLET</t>
   </si>
   <si>
@@ -937,12 +937,12 @@
     <t>SYNOCAINE GEL</t>
   </si>
   <si>
+    <t>L60067A</t>
+  </si>
+  <si>
     <t>1X200ML</t>
   </si>
   <si>
-    <t>L60067A</t>
-  </si>
-  <si>
     <t>POVIALL 10% 100 ML (Povidone Iodine IP</t>
   </si>
   <si>
@@ -1111,24 +1111,24 @@
     <t>Faropharm 200 Tablet</t>
   </si>
   <si>
+    <t>CBT26001B</t>
+  </si>
+  <si>
     <t>CBT25115D</t>
   </si>
   <si>
     <t>CBT26025B</t>
   </si>
   <si>
-    <t>CBT26001B</t>
-  </si>
-  <si>
     <t>EPODOX-200 DT Tablet</t>
   </si>
   <si>
+    <t>CT25507F</t>
+  </si>
+  <si>
     <t>CT26107C</t>
   </si>
   <si>
-    <t>CT25507F</t>
-  </si>
-  <si>
     <t>ATROLIA - F TABLET</t>
   </si>
   <si>
@@ -1180,12 +1180,12 @@
     <t>DANSOFT SHAMPOO 7.5ML SACHET</t>
   </si>
   <si>
+    <t>7.5ML</t>
+  </si>
+  <si>
     <t>N13250001</t>
   </si>
   <si>
-    <t>7.5ML</t>
-  </si>
-  <si>
     <t>POVIALL 7.5% SCRUB  500ML</t>
   </si>
   <si>
@@ -1195,12 +1195,12 @@
     <t>POVIALL OINTMENT 125GM</t>
   </si>
   <si>
+    <t>125GM</t>
+  </si>
+  <si>
     <t>GLN26004</t>
   </si>
   <si>
-    <t>125GM</t>
-  </si>
-  <si>
     <t>FAROPHARM 300 ER TABLET</t>
   </si>
   <si>
@@ -1261,12 +1261,12 @@
     <t>CEFIXLIA - 200 DT TABLET</t>
   </si>
   <si>
+    <t>CT26039A</t>
+  </si>
+  <si>
     <t>CT25427</t>
   </si>
   <si>
-    <t>CT26039A</t>
-  </si>
-  <si>
     <t>FERRIFINE XT TABLET</t>
   </si>
   <si>
@@ -1339,7 +1339,7 @@
     <t>Item Name</t>
   </si>
   <si>
-    <t>Unrestricted Qty</t>
+    <t>AR No.</t>
   </si>
   <si>
     <t>Blocked Qty</t>
@@ -1354,10 +1354,10 @@
     <t>Expiry</t>
   </si>
   <si>
-    <t xml:space="preserve"> Batch No.</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Transit Qty</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Unrestricted Qty</t>
   </si>
 </sst>
 </file>
@@ -1375,13 +1375,13 @@
     <font>
       <b/>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -1433,7 +1433,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -1455,28 +1455,10 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1492,6 +1474,21 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1839,69 +1836,76 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I242"/>
-  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I241"/>
+  <sheetFormatPr defaultColWidth="13.6640625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" style="1"/>
-    <col min="2" max="2" width="30.5546875" style="1" customWidth="1"/>
-    <col min="3" max="8" width="12.5546875" style="1"/>
-    <col min="9" max="9" width="10" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="12.5546875" style="1"/>
+    <col min="1" max="1" width="13.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="39.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9.77734375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.77734375" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="13.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:9" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
         <v>436</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="7" t="s">
         <v>437</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="7" t="s">
+        <v>438</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>442</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="E1" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>440</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>441</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="I1" s="8" t="s">
         <v>443</v>
       </c>
-      <c r="E1" s="13" t="s">
-        <v>439</v>
-      </c>
-      <c r="F1" s="13" t="s">
-        <v>440</v>
-      </c>
-      <c r="G1" s="13" t="s">
-        <v>441</v>
-      </c>
-      <c r="H1" s="14" t="s">
-        <v>438</v>
-      </c>
-      <c r="I1" s="14" t="s">
-        <v>444</v>
-      </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
+      <c r="A2" s="14">
         <v>6010000232</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="15" t="s">
         <v>408</v>
       </c>
-      <c r="C2" s="10">
+      <c r="C2" s="15" t="s">
+        <v>409</v>
+      </c>
+      <c r="D2" s="16">
         <v>46726</v>
       </c>
-      <c r="D2" s="9" t="s">
-        <v>409</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="E2" s="18">
         <v>28400</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
+      <c r="G2" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="18">
+        <v>0</v>
+      </c>
+      <c r="I2" s="17"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
@@ -1910,15 +1914,13 @@
       <c r="B3" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D3" s="5">
         <v>46559</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="E3" s="4">
-        <v>0</v>
-      </c>
+      <c r="E3" s="4"/>
       <c r="F3" s="3" t="s">
         <v>22</v>
       </c>
@@ -1926,7 +1928,7 @@
         <v>5</v>
       </c>
       <c r="H3" s="6">
-        <v>800</v>
+        <v>740</v>
       </c>
       <c r="I3" s="4"/>
     </row>
@@ -1937,15 +1939,13 @@
       <c r="B4" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="D4" s="5">
         <v>46568</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="E4" s="4">
-        <v>0</v>
-      </c>
+      <c r="E4" s="4"/>
       <c r="F4" s="3" t="s">
         <v>22</v>
       </c>
@@ -1958,27 +1958,25 @@
       <c r="I4" s="4"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="15">
+      <c r="A5" s="9">
         <v>6010000095</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="16" t="s">
+      <c r="C5" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="18">
-        <v>0</v>
-      </c>
-      <c r="F5" s="16" t="s">
+      <c r="D5" s="11"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="H5" s="18"/>
-      <c r="I5" s="19">
+      <c r="G5" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="H5" s="12"/>
+      <c r="I5" s="13">
         <v>3600</v>
       </c>
     </row>
@@ -1989,15 +1987,13 @@
       <c r="B6" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="D6" s="5">
         <v>46746</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="E6" s="4">
-        <v>0</v>
-      </c>
+      <c r="E6" s="4"/>
       <c r="F6" s="3" t="s">
         <v>286</v>
       </c>
@@ -2016,15 +2012,13 @@
       <c r="B7" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D7" s="5">
         <v>46752</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="E7" s="4">
-        <v>0</v>
-      </c>
+      <c r="E7" s="4"/>
       <c r="F7" s="3" t="s">
         <v>119</v>
       </c>
@@ -2043,15 +2037,13 @@
       <c r="B8" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" s="5">
         <v>46548</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E8" s="4">
-        <v>0</v>
-      </c>
+      <c r="E8" s="4"/>
       <c r="F8" s="3" t="s">
         <v>30</v>
       </c>
@@ -2070,15 +2062,13 @@
       <c r="B9" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="C9" s="5">
-        <v>46751</v>
-      </c>
-      <c r="D9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="E9" s="4">
-        <v>0</v>
-      </c>
+      <c r="D9" s="5">
+        <v>46556</v>
+      </c>
+      <c r="E9" s="4"/>
       <c r="F9" s="3" t="s">
         <v>229</v>
       </c>
@@ -2086,7 +2076,7 @@
         <v>5</v>
       </c>
       <c r="H9" s="6">
-        <v>160</v>
+        <v>300</v>
       </c>
       <c r="I9" s="4"/>
     </row>
@@ -2097,15 +2087,13 @@
       <c r="B10" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="C10" s="5">
-        <v>46556</v>
-      </c>
-      <c r="D10" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="E10" s="4">
-        <v>0</v>
-      </c>
+      <c r="D10" s="5">
+        <v>46751</v>
+      </c>
+      <c r="E10" s="4"/>
       <c r="F10" s="3" t="s">
         <v>229</v>
       </c>
@@ -2113,7 +2101,7 @@
         <v>5</v>
       </c>
       <c r="H10" s="6">
-        <v>300</v>
+        <v>160</v>
       </c>
       <c r="I10" s="4"/>
     </row>
@@ -2124,15 +2112,13 @@
       <c r="B11" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="D11" s="5">
         <v>46539</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="E11" s="4">
-        <v>0</v>
-      </c>
+      <c r="E11" s="4"/>
       <c r="F11" s="3" t="s">
         <v>87</v>
       </c>
@@ -2151,15 +2137,13 @@
       <c r="B12" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="D12" s="5">
         <v>46549</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="E12" s="4">
-        <v>0</v>
-      </c>
+      <c r="E12" s="4"/>
       <c r="F12" s="3" t="s">
         <v>22</v>
       </c>
@@ -2172,27 +2156,25 @@
       <c r="I12" s="4"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="15">
+      <c r="A13" s="9">
         <v>4010013259</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="17"/>
-      <c r="D13" s="16" t="s">
+      <c r="C13" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E13" s="18">
-        <v>0</v>
-      </c>
-      <c r="F13" s="16" t="s">
+      <c r="D13" s="11"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="G13" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="H13" s="18"/>
-      <c r="I13" s="19">
+      <c r="G13" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="H13" s="12"/>
+      <c r="I13" s="13">
         <v>240</v>
       </c>
     </row>
@@ -2203,15 +2185,13 @@
       <c r="B14" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="5">
         <v>46568</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="4">
-        <v>0</v>
-      </c>
+      <c r="E14" s="4"/>
       <c r="F14" s="3" t="s">
         <v>7</v>
       </c>
@@ -2224,27 +2204,25 @@
       <c r="I14" s="4"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="15">
+      <c r="A15" s="9">
         <v>4010013260</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="17"/>
-      <c r="D15" s="16" t="s">
+      <c r="C15" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E15" s="18">
-        <v>0</v>
-      </c>
-      <c r="F15" s="16" t="s">
+      <c r="D15" s="11"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G15" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="H15" s="18"/>
-      <c r="I15" s="19">
+      <c r="G15" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="H15" s="12"/>
+      <c r="I15" s="13">
         <v>20</v>
       </c>
     </row>
@@ -2255,15 +2233,13 @@
       <c r="B16" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C16" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" s="5">
         <v>46568</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="4">
-        <v>0</v>
-      </c>
+      <c r="E16" s="4"/>
       <c r="F16" s="3" t="s">
         <v>10</v>
       </c>
@@ -2282,15 +2258,13 @@
       <c r="B17" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="5">
+      <c r="C17" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="5">
         <v>46589</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E17" s="4">
-        <v>0</v>
-      </c>
+      <c r="E17" s="4"/>
       <c r="F17" s="3" t="s">
         <v>10</v>
       </c>
@@ -2309,15 +2283,13 @@
       <c r="B18" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="C18" s="5">
+      <c r="C18" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D18" s="5">
         <v>46549</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="E18" s="4">
-        <v>0</v>
-      </c>
+      <c r="E18" s="4"/>
       <c r="F18" s="3" t="s">
         <v>7</v>
       </c>
@@ -2336,15 +2308,13 @@
       <c r="B19" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="C19" s="5">
-        <v>46549</v>
-      </c>
-      <c r="D19" s="3" t="s">
+      <c r="C19" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="E19" s="4">
-        <v>0</v>
-      </c>
+      <c r="D19" s="5">
+        <v>46587</v>
+      </c>
+      <c r="E19" s="4"/>
       <c r="F19" s="3" t="s">
         <v>7</v>
       </c>
@@ -2352,7 +2322,7 @@
         <v>5</v>
       </c>
       <c r="H19" s="6">
-        <v>460</v>
+        <v>420</v>
       </c>
       <c r="I19" s="4"/>
     </row>
@@ -2363,15 +2333,13 @@
       <c r="B20" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="C20" s="5">
-        <v>46587</v>
-      </c>
-      <c r="D20" s="3" t="s">
+      <c r="C20" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="E20" s="4">
-        <v>0</v>
-      </c>
+      <c r="D20" s="5">
+        <v>46549</v>
+      </c>
+      <c r="E20" s="4"/>
       <c r="F20" s="3" t="s">
         <v>7</v>
       </c>
@@ -2379,7 +2347,7 @@
         <v>5</v>
       </c>
       <c r="H20" s="6">
-        <v>420</v>
+        <v>460</v>
       </c>
       <c r="I20" s="4"/>
     </row>
@@ -2390,15 +2358,13 @@
       <c r="B21" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C21" s="5">
+      <c r="C21" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D21" s="5">
         <v>46640</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="E21" s="4">
-        <v>0</v>
-      </c>
+      <c r="E21" s="4"/>
       <c r="F21" s="3" t="s">
         <v>22</v>
       </c>
@@ -2417,15 +2383,13 @@
       <c r="B22" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C22" s="5">
+      <c r="C22" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D22" s="5">
         <v>46666</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E22" s="4">
-        <v>0</v>
-      </c>
+      <c r="E22" s="4"/>
       <c r="F22" s="3" t="s">
         <v>87</v>
       </c>
@@ -2444,15 +2408,13 @@
       <c r="B23" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C23" s="5">
+      <c r="C23" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D23" s="5">
         <v>46598</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E23" s="4">
-        <v>0</v>
-      </c>
+      <c r="E23" s="4"/>
       <c r="F23" s="3" t="s">
         <v>22</v>
       </c>
@@ -2471,15 +2433,13 @@
       <c r="B24" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="C24" s="5">
+      <c r="C24" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D24" s="5">
         <v>46518</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="E24" s="4">
-        <v>0</v>
-      </c>
+      <c r="E24" s="4"/>
       <c r="F24" s="3" t="s">
         <v>22</v>
       </c>
@@ -2492,27 +2452,25 @@
       <c r="I24" s="4"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="15">
+      <c r="A25" s="9">
         <v>4010013694</v>
       </c>
-      <c r="B25" s="16" t="s">
+      <c r="B25" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="C25" s="17"/>
-      <c r="D25" s="16" t="s">
+      <c r="C25" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E25" s="18">
-        <v>0</v>
-      </c>
-      <c r="F25" s="16" t="s">
+      <c r="D25" s="11"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="G25" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="H25" s="18"/>
-      <c r="I25" s="19">
+      <c r="G25" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="H25" s="12"/>
+      <c r="I25" s="13">
         <v>240</v>
       </c>
     </row>
@@ -2523,15 +2481,13 @@
       <c r="B26" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="C26" s="5">
+      <c r="C26" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D26" s="5">
         <v>46536</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="E26" s="4">
-        <v>0</v>
-      </c>
+      <c r="E26" s="4"/>
       <c r="F26" s="3" t="s">
         <v>7</v>
       </c>
@@ -2539,7 +2495,7 @@
         <v>5</v>
       </c>
       <c r="H26" s="6">
-        <v>730</v>
+        <v>690</v>
       </c>
       <c r="I26" s="4"/>
     </row>
@@ -2550,15 +2506,13 @@
       <c r="B27" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="C27" s="5">
+      <c r="C27" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D27" s="5">
         <v>46447</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="E27" s="4">
-        <v>0</v>
-      </c>
+      <c r="E27" s="4"/>
       <c r="F27" s="3" t="s">
         <v>163</v>
       </c>
@@ -2577,15 +2531,13 @@
       <c r="B28" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C28" s="5">
+      <c r="C28" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D28" s="5">
         <v>46541</v>
       </c>
-      <c r="D28" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="E28" s="4">
-        <v>0</v>
-      </c>
+      <c r="E28" s="4"/>
       <c r="F28" s="3" t="s">
         <v>90</v>
       </c>
@@ -2593,7 +2545,7 @@
         <v>5</v>
       </c>
       <c r="H28" s="6">
-        <v>2880</v>
+        <v>2820</v>
       </c>
       <c r="I28" s="4"/>
     </row>
@@ -2604,13 +2556,11 @@
       <c r="B29" s="3" t="s">
         <v>433</v>
       </c>
-      <c r="C29" s="5"/>
-      <c r="D29" s="3" t="s">
+      <c r="C29" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E29" s="4">
-        <v>0</v>
-      </c>
+      <c r="D29" s="5"/>
+      <c r="E29" s="4"/>
       <c r="F29" s="3" t="s">
         <v>429</v>
       </c>
@@ -2629,13 +2579,11 @@
       <c r="B30" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="C30" s="5"/>
-      <c r="D30" s="3" t="s">
+      <c r="C30" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E30" s="4">
-        <v>0</v>
-      </c>
+      <c r="D30" s="5"/>
+      <c r="E30" s="4"/>
       <c r="F30" s="3" t="s">
         <v>429</v>
       </c>
@@ -2654,13 +2602,11 @@
       <c r="B31" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="C31" s="5"/>
-      <c r="D31" s="3" t="s">
+      <c r="C31" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E31" s="4">
-        <v>0</v>
-      </c>
+      <c r="D31" s="5"/>
+      <c r="E31" s="4"/>
       <c r="F31" s="3" t="s">
         <v>429</v>
       </c>
@@ -2679,13 +2625,11 @@
       <c r="B32" s="3" t="s">
         <v>428</v>
       </c>
-      <c r="C32" s="5"/>
-      <c r="D32" s="3" t="s">
+      <c r="C32" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E32" s="4">
-        <v>0</v>
-      </c>
+      <c r="D32" s="5"/>
+      <c r="E32" s="4"/>
       <c r="F32" s="3" t="s">
         <v>429</v>
       </c>
@@ -2704,13 +2648,11 @@
       <c r="B33" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="C33" s="5"/>
-      <c r="D33" s="3" t="s">
+      <c r="C33" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E33" s="4">
-        <v>0</v>
-      </c>
+      <c r="D33" s="5"/>
+      <c r="E33" s="4"/>
       <c r="F33" s="3" t="s">
         <v>429</v>
       </c>
@@ -2729,15 +2671,13 @@
       <c r="B34" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C34" s="5">
+      <c r="C34" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D34" s="5">
         <v>46568</v>
       </c>
-      <c r="D34" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E34" s="4">
-        <v>0</v>
-      </c>
+      <c r="E34" s="4"/>
       <c r="F34" s="3" t="s">
         <v>30</v>
       </c>
@@ -2756,15 +2696,13 @@
       <c r="B35" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C35" s="5">
+      <c r="C35" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D35" s="5">
         <v>46551</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E35" s="4">
-        <v>0</v>
-      </c>
+      <c r="E35" s="4"/>
       <c r="F35" s="3" t="s">
         <v>30</v>
       </c>
@@ -2783,15 +2721,13 @@
       <c r="B36" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="C36" s="5">
+      <c r="C36" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="D36" s="5">
         <v>47007</v>
       </c>
-      <c r="D36" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="E36" s="4">
-        <v>0</v>
-      </c>
+      <c r="E36" s="4"/>
       <c r="F36" s="3" t="s">
         <v>316</v>
       </c>
@@ -2799,7 +2735,7 @@
         <v>3</v>
       </c>
       <c r="H36" s="6">
-        <v>673</v>
+        <v>623</v>
       </c>
       <c r="I36" s="4"/>
     </row>
@@ -2810,15 +2746,13 @@
       <c r="B37" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="C37" s="5">
+      <c r="C37" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="D37" s="5">
         <v>46752</v>
       </c>
-      <c r="D37" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="E37" s="4">
-        <v>0</v>
-      </c>
+      <c r="E37" s="4"/>
       <c r="F37" s="3" t="s">
         <v>7</v>
       </c>
@@ -2837,15 +2771,13 @@
       <c r="B38" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="C38" s="5">
+      <c r="C38" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="D38" s="5">
         <v>46495</v>
       </c>
-      <c r="D38" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="E38" s="4">
-        <v>0</v>
-      </c>
+      <c r="E38" s="4"/>
       <c r="F38" s="3" t="s">
         <v>166</v>
       </c>
@@ -2864,15 +2796,13 @@
       <c r="B39" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="C39" s="5">
+      <c r="C39" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="D39" s="5">
         <v>46780</v>
       </c>
-      <c r="D39" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="E39" s="4">
-        <v>0</v>
-      </c>
+      <c r="E39" s="4"/>
       <c r="F39" s="3" t="s">
         <v>30</v>
       </c>
@@ -2891,15 +2821,13 @@
       <c r="B40" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="C40" s="5">
+      <c r="C40" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="D40" s="5">
         <v>46813</v>
       </c>
-      <c r="D40" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="E40" s="4">
-        <v>0</v>
-      </c>
+      <c r="E40" s="4"/>
       <c r="F40" s="3" t="s">
         <v>87</v>
       </c>
@@ -2907,32 +2835,30 @@
         <v>5</v>
       </c>
       <c r="H40" s="6">
-        <v>3560</v>
+        <v>3300</v>
       </c>
       <c r="I40" s="4"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="15">
+      <c r="A41" s="9">
         <v>6010000099</v>
       </c>
-      <c r="B41" s="16" t="s">
+      <c r="B41" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="C41" s="17"/>
-      <c r="D41" s="16" t="s">
+      <c r="C41" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E41" s="18">
-        <v>0</v>
-      </c>
-      <c r="F41" s="16" t="s">
+      <c r="D41" s="11"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="G41" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="H41" s="18"/>
-      <c r="I41" s="19">
+      <c r="G41" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="H41" s="12"/>
+      <c r="I41" s="13">
         <v>1200</v>
       </c>
     </row>
@@ -2943,15 +2869,13 @@
       <c r="B42" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="C42" s="5">
+      <c r="C42" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="D42" s="5">
         <v>46780</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="E42" s="4">
-        <v>0</v>
-      </c>
+      <c r="E42" s="4"/>
       <c r="F42" s="3" t="s">
         <v>327</v>
       </c>
@@ -2970,15 +2894,13 @@
       <c r="B43" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="C43" s="5">
-        <v>46661</v>
-      </c>
-      <c r="D43" s="3" t="s">
+      <c r="C43" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="E43" s="4">
-        <v>0</v>
-      </c>
+      <c r="D43" s="5">
+        <v>46726</v>
+      </c>
+      <c r="E43" s="4"/>
       <c r="F43" s="3" t="s">
         <v>22</v>
       </c>
@@ -2986,7 +2908,7 @@
         <v>5</v>
       </c>
       <c r="H43" s="6">
-        <v>280</v>
+        <v>7920</v>
       </c>
       <c r="I43" s="4"/>
     </row>
@@ -2997,15 +2919,13 @@
       <c r="B44" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="C44" s="5">
-        <v>46726</v>
-      </c>
-      <c r="D44" s="3" t="s">
+      <c r="C44" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="E44" s="4">
-        <v>0</v>
-      </c>
+      <c r="D44" s="5">
+        <v>46661</v>
+      </c>
+      <c r="E44" s="4"/>
       <c r="F44" s="3" t="s">
         <v>22</v>
       </c>
@@ -3013,32 +2933,30 @@
         <v>5</v>
       </c>
       <c r="H44" s="6">
-        <v>7920</v>
+        <v>280</v>
       </c>
       <c r="I44" s="4"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" s="15">
+      <c r="A45" s="9">
         <v>6010000239</v>
       </c>
-      <c r="B45" s="16" t="s">
+      <c r="B45" s="10" t="s">
         <v>416</v>
       </c>
-      <c r="C45" s="17"/>
-      <c r="D45" s="16" t="s">
+      <c r="C45" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E45" s="18">
-        <v>0</v>
-      </c>
-      <c r="F45" s="16" t="s">
+      <c r="D45" s="11"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="10" t="s">
         <v>360</v>
       </c>
-      <c r="G45" s="16" t="s">
+      <c r="G45" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="H45" s="18"/>
-      <c r="I45" s="19">
+      <c r="H45" s="12"/>
+      <c r="I45" s="13">
         <v>810</v>
       </c>
     </row>
@@ -3049,15 +2967,13 @@
       <c r="B46" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="C46" s="5">
+      <c r="C46" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="D46" s="5">
         <v>46507</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="E46" s="4">
-        <v>0</v>
-      </c>
+      <c r="E46" s="4"/>
       <c r="F46" s="3" t="s">
         <v>360</v>
       </c>
@@ -3065,7 +2981,7 @@
         <v>3</v>
       </c>
       <c r="H46" s="6">
-        <v>709</v>
+        <v>689</v>
       </c>
       <c r="I46" s="4"/>
     </row>
@@ -3076,15 +2992,13 @@
       <c r="B47" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="C47" s="5">
+      <c r="C47" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="D47" s="5">
         <v>46751</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="E47" s="4">
-        <v>0</v>
-      </c>
+      <c r="E47" s="4"/>
       <c r="F47" s="3" t="s">
         <v>30</v>
       </c>
@@ -3103,15 +3017,13 @@
       <c r="B48" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="C48" s="5">
+      <c r="C48" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="D48" s="5">
         <v>46721</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="E48" s="4">
-        <v>0</v>
-      </c>
+      <c r="E48" s="4"/>
       <c r="F48" s="3" t="s">
         <v>30</v>
       </c>
@@ -3130,15 +3042,13 @@
       <c r="B49" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="C49" s="5">
+      <c r="C49" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D49" s="5">
         <v>46721</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="E49" s="4">
-        <v>0</v>
-      </c>
+      <c r="E49" s="4"/>
       <c r="F49" s="3" t="s">
         <v>169</v>
       </c>
@@ -3151,56 +3061,52 @@
       <c r="I49" s="4"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" s="15">
+      <c r="A50" s="2">
         <v>6010000071</v>
       </c>
-      <c r="B50" s="16" t="s">
+      <c r="B50" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="C50" s="17"/>
-      <c r="D50" s="16" t="s">
+      <c r="C50" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D50" s="5">
+        <v>46797</v>
+      </c>
+      <c r="E50" s="4"/>
+      <c r="F50" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H50" s="6">
+        <v>2450</v>
+      </c>
+      <c r="I50" s="4"/>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" s="9">
+        <v>6010000071</v>
+      </c>
+      <c r="B51" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="C51" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E50" s="18">
-        <v>0</v>
-      </c>
-      <c r="F50" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="G50" s="16" t="s">
+      <c r="D51" s="11"/>
+      <c r="E51" s="12"/>
+      <c r="F51" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="G51" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="H50" s="18"/>
-      <c r="I50" s="19">
+      <c r="H51" s="12"/>
+      <c r="I51" s="13">
         <v>400</v>
       </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A51" s="2">
-        <v>6010000071</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="C51" s="5">
-        <v>46797</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="E51" s="4">
-        <v>0</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H51" s="6">
-        <v>2450</v>
-      </c>
-      <c r="I51" s="4"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
@@ -3209,15 +3115,13 @@
       <c r="B52" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C52" s="5">
+      <c r="C52" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D52" s="5">
         <v>46681</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E52" s="4">
-        <v>0</v>
-      </c>
+      <c r="E52" s="4"/>
       <c r="F52" s="3" t="s">
         <v>39</v>
       </c>
@@ -3225,7 +3129,7 @@
         <v>5</v>
       </c>
       <c r="H52" s="6">
-        <v>820</v>
+        <v>800</v>
       </c>
       <c r="I52" s="4"/>
     </row>
@@ -3236,15 +3140,13 @@
       <c r="B53" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C53" s="5">
+      <c r="C53" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D53" s="5">
         <v>46575</v>
       </c>
-      <c r="D53" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E53" s="4">
-        <v>0</v>
-      </c>
+      <c r="E53" s="4"/>
       <c r="F53" s="3" t="s">
         <v>7</v>
       </c>
@@ -3263,15 +3165,13 @@
       <c r="B54" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C54" s="5">
+      <c r="C54" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D54" s="5">
         <v>46598</v>
       </c>
-      <c r="D54" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E54" s="4">
-        <v>0</v>
-      </c>
+      <c r="E54" s="4"/>
       <c r="F54" s="3" t="s">
         <v>7</v>
       </c>
@@ -3290,15 +3190,13 @@
       <c r="B55" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C55" s="5">
+      <c r="C55" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D55" s="5">
         <v>46575</v>
       </c>
-      <c r="D55" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E55" s="4">
-        <v>0</v>
-      </c>
+      <c r="E55" s="4"/>
       <c r="F55" s="3" t="s">
         <v>7</v>
       </c>
@@ -3317,15 +3215,13 @@
       <c r="B56" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C56" s="5">
+      <c r="C56" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D56" s="5">
         <v>46545</v>
       </c>
-      <c r="D56" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E56" s="4">
-        <v>0</v>
-      </c>
+      <c r="E56" s="4"/>
       <c r="F56" s="3" t="s">
         <v>7</v>
       </c>
@@ -3333,7 +3229,7 @@
         <v>5</v>
       </c>
       <c r="H56" s="6">
-        <v>780</v>
+        <v>750</v>
       </c>
       <c r="I56" s="4"/>
     </row>
@@ -3344,15 +3240,13 @@
       <c r="B57" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="C57" s="5">
+      <c r="C57" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="D57" s="5">
         <v>46539</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="E57" s="4">
-        <v>0</v>
-      </c>
+      <c r="E57" s="4"/>
       <c r="F57" s="3" t="s">
         <v>30</v>
       </c>
@@ -3364,22 +3258,20 @@
       </c>
       <c r="I57" s="4"/>
     </row>
-    <row r="58" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>6010000224</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="C58" s="5">
+      <c r="C58" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="D58" s="5">
         <v>46711</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="E58" s="4">
-        <v>0</v>
-      </c>
+      <c r="E58" s="4"/>
       <c r="F58" s="3" t="s">
         <v>15</v>
       </c>
@@ -3387,86 +3279,80 @@
         <v>5</v>
       </c>
       <c r="H58" s="6">
-        <v>420</v>
+        <v>380</v>
       </c>
       <c r="I58" s="4"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" s="15">
+      <c r="A59" s="9">
         <v>6010000232</v>
       </c>
-      <c r="B59" s="16" t="s">
+      <c r="B59" s="10" t="s">
         <v>408</v>
       </c>
-      <c r="C59" s="17"/>
-      <c r="D59" s="16" t="s">
+      <c r="C59" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E59" s="18">
-        <v>0</v>
-      </c>
-      <c r="F59" s="16" t="s">
+      <c r="D59" s="11"/>
+      <c r="E59" s="12"/>
+      <c r="F59" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G59" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="H59" s="18"/>
-      <c r="I59" s="19">
+      <c r="G59" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="H59" s="12"/>
+      <c r="I59" s="13">
         <v>7200</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="15">
+      <c r="A60" s="2">
         <v>6010000073</v>
       </c>
-      <c r="B60" s="16" t="s">
+      <c r="B60" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="C60" s="17"/>
-      <c r="D60" s="16" t="s">
+      <c r="C60" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D60" s="5">
+        <v>46511</v>
+      </c>
+      <c r="E60" s="4"/>
+      <c r="F60" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H60" s="6">
+        <v>1150</v>
+      </c>
+      <c r="I60" s="4"/>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" s="9">
+        <v>6010000073</v>
+      </c>
+      <c r="B61" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="C61" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E60" s="18">
-        <v>0</v>
-      </c>
-      <c r="F60" s="16" t="s">
-        <v>174</v>
-      </c>
-      <c r="G60" s="16" t="s">
+      <c r="D61" s="11"/>
+      <c r="E61" s="12"/>
+      <c r="F61" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="G61" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="H60" s="18"/>
-      <c r="I60" s="19">
+      <c r="H61" s="12"/>
+      <c r="I61" s="13">
         <v>720</v>
       </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A61" s="2">
-        <v>6010000073</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C61" s="5">
-        <v>46511</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="E61" s="4">
-        <v>0</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="G61" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H61" s="6">
-        <v>1150</v>
-      </c>
-      <c r="I61" s="4"/>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
@@ -3475,15 +3361,13 @@
       <c r="B62" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="C62" s="5">
+      <c r="C62" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="D62" s="5">
         <v>46751</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="E62" s="4">
-        <v>0</v>
-      </c>
+      <c r="E62" s="4"/>
       <c r="F62" s="3" t="s">
         <v>104</v>
       </c>
@@ -3502,15 +3386,13 @@
       <c r="B63" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="C63" s="5">
+      <c r="C63" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="D63" s="5">
         <v>46721</v>
       </c>
-      <c r="D63" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="E63" s="4">
-        <v>0</v>
-      </c>
+      <c r="E63" s="4"/>
       <c r="F63" s="3" t="s">
         <v>104</v>
       </c>
@@ -3529,15 +3411,13 @@
       <c r="B64" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="C64" s="5">
+      <c r="C64" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="D64" s="5">
         <v>46711</v>
       </c>
-      <c r="D64" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="E64" s="4">
-        <v>0</v>
-      </c>
+      <c r="E64" s="4"/>
       <c r="F64" s="3" t="s">
         <v>289</v>
       </c>
@@ -3556,15 +3436,13 @@
       <c r="B65" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="C65" s="5">
+      <c r="C65" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="D65" s="5">
         <v>46813</v>
       </c>
-      <c r="D65" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="E65" s="4">
-        <v>0</v>
-      </c>
+      <c r="E65" s="4"/>
       <c r="F65" s="3" t="s">
         <v>427</v>
       </c>
@@ -3583,15 +3461,13 @@
       <c r="B66" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="C66" s="5">
+      <c r="C66" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="D66" s="5">
         <v>46746</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="E66" s="4">
-        <v>0</v>
-      </c>
+      <c r="E66" s="4"/>
       <c r="F66" s="3" t="s">
         <v>289</v>
       </c>
@@ -3604,56 +3480,52 @@
       <c r="I66" s="4"/>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A67" s="2">
+      <c r="A67" s="9">
         <v>6010000205</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="B67" s="10" t="s">
         <v>384</v>
       </c>
-      <c r="C67" s="5">
+      <c r="C67" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D67" s="11"/>
+      <c r="E67" s="12"/>
+      <c r="F67" s="10" t="s">
+        <v>385</v>
+      </c>
+      <c r="G67" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="H67" s="12"/>
+      <c r="I67" s="13">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A68" s="2">
+        <v>6010000205</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="D68" s="5">
         <v>46692</v>
       </c>
-      <c r="D67" s="3" t="s">
+      <c r="E68" s="4"/>
+      <c r="F68" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="E67" s="4">
-        <v>0</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="G67" s="3" t="s">
+      <c r="G68" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H67" s="6">
-        <v>9300</v>
-      </c>
-      <c r="I67" s="4"/>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A68" s="15">
-        <v>6010000205</v>
-      </c>
-      <c r="B68" s="16" t="s">
-        <v>384</v>
-      </c>
-      <c r="C68" s="17"/>
-      <c r="D68" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="E68" s="18">
-        <v>0</v>
-      </c>
-      <c r="F68" s="16" t="s">
-        <v>386</v>
-      </c>
-      <c r="G68" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="H68" s="18"/>
-      <c r="I68" s="19">
-        <v>7200</v>
-      </c>
+      <c r="H68" s="6">
+        <v>8850</v>
+      </c>
+      <c r="I68" s="4"/>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
@@ -3662,15 +3534,13 @@
       <c r="B69" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C69" s="5">
+      <c r="C69" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D69" s="5">
         <v>46504</v>
       </c>
-      <c r="D69" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E69" s="4">
-        <v>0</v>
-      </c>
+      <c r="E69" s="4"/>
       <c r="F69" s="3" t="s">
         <v>70</v>
       </c>
@@ -3689,15 +3559,13 @@
       <c r="B70" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="C70" s="5">
+      <c r="C70" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D70" s="5">
         <v>46721</v>
       </c>
-      <c r="D70" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E70" s="4">
-        <v>0</v>
-      </c>
+      <c r="E70" s="4"/>
       <c r="F70" s="3" t="s">
         <v>178</v>
       </c>
@@ -3710,81 +3578,75 @@
       <c r="I70" s="4"/>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A71" s="15">
+      <c r="A71" s="9">
         <v>6010000074</v>
       </c>
-      <c r="B71" s="16" t="s">
+      <c r="B71" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="C71" s="17"/>
-      <c r="D71" s="16" t="s">
+      <c r="C71" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E71" s="18">
-        <v>0</v>
-      </c>
-      <c r="F71" s="16" t="s">
+      <c r="D71" s="11"/>
+      <c r="E71" s="12"/>
+      <c r="F71" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="G71" s="16" t="s">
+      <c r="G71" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="H71" s="18"/>
-      <c r="I71" s="19">
+      <c r="H71" s="12"/>
+      <c r="I71" s="13">
         <v>5760</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A72" s="15">
+      <c r="A72" s="2">
         <v>6010000102</v>
       </c>
-      <c r="B72" s="16" t="s">
+      <c r="B72" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="C72" s="17"/>
-      <c r="D72" s="16" t="s">
+      <c r="C72" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="D72" s="5">
+        <v>46780</v>
+      </c>
+      <c r="E72" s="4"/>
+      <c r="F72" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H72" s="6">
+        <v>3520</v>
+      </c>
+      <c r="I72" s="4"/>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A73" s="9">
+        <v>6010000102</v>
+      </c>
+      <c r="B73" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="C73" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E72" s="18">
-        <v>0</v>
-      </c>
-      <c r="F72" s="16" t="s">
+      <c r="D73" s="11"/>
+      <c r="E73" s="12"/>
+      <c r="F73" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="G72" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="H72" s="18"/>
-      <c r="I72" s="19">
+      <c r="G73" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="H73" s="12"/>
+      <c r="I73" s="13">
         <v>1600</v>
       </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A73" s="2">
-        <v>6010000102</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="C73" s="5">
-        <v>46780</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="E73" s="4">
-        <v>0</v>
-      </c>
-      <c r="F73" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G73" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H73" s="6">
-        <v>3580</v>
-      </c>
-      <c r="I73" s="4"/>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
@@ -3793,15 +3655,13 @@
       <c r="B74" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="C74" s="5">
+      <c r="C74" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="D74" s="5">
         <v>46645</v>
       </c>
-      <c r="D74" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="E74" s="4">
-        <v>0</v>
-      </c>
+      <c r="E74" s="4"/>
       <c r="F74" s="3" t="s">
         <v>22</v>
       </c>
@@ -3820,15 +3680,13 @@
       <c r="B75" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="C75" s="5">
+      <c r="C75" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="D75" s="5">
         <v>46606</v>
       </c>
-      <c r="D75" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="E75" s="4">
-        <v>0</v>
-      </c>
+      <c r="E75" s="4"/>
       <c r="F75" s="3" t="s">
         <v>372</v>
       </c>
@@ -3847,15 +3705,13 @@
       <c r="B76" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C76" s="5">
+      <c r="C76" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D76" s="5">
         <v>46524</v>
       </c>
-      <c r="D76" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E76" s="4">
-        <v>0</v>
-      </c>
+      <c r="E76" s="4"/>
       <c r="F76" s="3" t="s">
         <v>30</v>
       </c>
@@ -3868,27 +3724,25 @@
       <c r="I76" s="4"/>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A77" s="15">
+      <c r="A77" s="9">
         <v>6010000150</v>
       </c>
-      <c r="B77" s="16" t="s">
+      <c r="B77" s="10" t="s">
         <v>310</v>
       </c>
-      <c r="C77" s="17"/>
-      <c r="D77" s="16" t="s">
+      <c r="C77" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E77" s="18">
-        <v>0</v>
-      </c>
-      <c r="F77" s="16" t="s">
+      <c r="D77" s="11"/>
+      <c r="E77" s="12"/>
+      <c r="F77" s="10" t="s">
         <v>311</v>
       </c>
-      <c r="G77" s="16" t="s">
+      <c r="G77" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="H77" s="18"/>
-      <c r="I77" s="19">
+      <c r="H77" s="12"/>
+      <c r="I77" s="13">
         <v>880</v>
       </c>
     </row>
@@ -3899,15 +3753,13 @@
       <c r="B78" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="C78" s="5">
+      <c r="C78" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="D78" s="5">
         <v>46692</v>
       </c>
-      <c r="D78" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="E78" s="4">
-        <v>0</v>
-      </c>
+      <c r="E78" s="4"/>
       <c r="F78" s="3" t="s">
         <v>311</v>
       </c>
@@ -3926,15 +3778,13 @@
       <c r="B79" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="C79" s="5">
+      <c r="C79" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="D79" s="5">
         <v>46596</v>
       </c>
-      <c r="D79" s="3" t="s">
-        <v>419</v>
-      </c>
-      <c r="E79" s="4">
-        <v>0</v>
-      </c>
+      <c r="E79" s="4"/>
       <c r="F79" s="3" t="s">
         <v>420</v>
       </c>
@@ -3953,15 +3803,13 @@
       <c r="B80" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="C80" s="5">
-        <v>46803</v>
-      </c>
-      <c r="D80" s="3" t="s">
+      <c r="C80" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="E80" s="4">
-        <v>0</v>
-      </c>
+      <c r="D80" s="5">
+        <v>46721</v>
+      </c>
+      <c r="E80" s="4"/>
       <c r="F80" s="3" t="s">
         <v>30</v>
       </c>
@@ -3969,7 +3817,7 @@
         <v>5</v>
       </c>
       <c r="H80" s="6">
-        <v>1470</v>
+        <v>4020</v>
       </c>
       <c r="I80" s="4"/>
     </row>
@@ -3980,15 +3828,13 @@
       <c r="B81" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="C81" s="5">
-        <v>46721</v>
-      </c>
-      <c r="D81" s="3" t="s">
+      <c r="C81" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="E81" s="4">
-        <v>0</v>
-      </c>
+      <c r="D81" s="5">
+        <v>46803</v>
+      </c>
+      <c r="E81" s="4"/>
       <c r="F81" s="3" t="s">
         <v>30</v>
       </c>
@@ -3996,7 +3842,7 @@
         <v>5</v>
       </c>
       <c r="H81" s="6">
-        <v>4020</v>
+        <v>1470</v>
       </c>
       <c r="I81" s="4"/>
     </row>
@@ -4007,15 +3853,13 @@
       <c r="B82" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="C82" s="5">
+      <c r="C82" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="D82" s="5">
         <v>46367</v>
       </c>
-      <c r="D82" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="E82" s="4">
-        <v>0</v>
-      </c>
+      <c r="E82" s="4"/>
       <c r="F82" s="3" t="s">
         <v>360</v>
       </c>
@@ -4023,7 +3867,7 @@
         <v>3</v>
       </c>
       <c r="H82" s="6">
-        <v>345</v>
+        <v>325</v>
       </c>
       <c r="I82" s="4"/>
     </row>
@@ -4034,15 +3878,13 @@
       <c r="B83" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="C83" s="5">
+      <c r="C83" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="D83" s="5">
         <v>46447</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="E83" s="4">
-        <v>0</v>
-      </c>
+      <c r="E83" s="4"/>
       <c r="F83" s="3" t="s">
         <v>30</v>
       </c>
@@ -4061,15 +3903,13 @@
       <c r="B84" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="C84" s="5">
+      <c r="C84" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="D84" s="5">
         <v>46574</v>
       </c>
-      <c r="D84" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="E84" s="4">
-        <v>0</v>
-      </c>
+      <c r="E84" s="4"/>
       <c r="F84" s="3" t="s">
         <v>15</v>
       </c>
@@ -4088,15 +3928,13 @@
       <c r="B85" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="C85" s="5">
-        <v>46711</v>
-      </c>
-      <c r="D85" s="3" t="s">
+      <c r="C85" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="E85" s="4">
-        <v>0</v>
-      </c>
+      <c r="D85" s="5">
+        <v>46726</v>
+      </c>
+      <c r="E85" s="4"/>
       <c r="F85" s="3" t="s">
         <v>30</v>
       </c>
@@ -4104,7 +3942,7 @@
         <v>5</v>
       </c>
       <c r="H85" s="6">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="I85" s="4"/>
     </row>
@@ -4115,15 +3953,13 @@
       <c r="B86" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="C86" s="5">
-        <v>46803</v>
-      </c>
-      <c r="D86" s="3" t="s">
+      <c r="C86" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="E86" s="4">
-        <v>0</v>
-      </c>
+      <c r="D86" s="5">
+        <v>46711</v>
+      </c>
+      <c r="E86" s="4"/>
       <c r="F86" s="3" t="s">
         <v>30</v>
       </c>
@@ -4131,7 +3967,7 @@
         <v>5</v>
       </c>
       <c r="H86" s="6">
-        <v>380</v>
+        <v>110</v>
       </c>
       <c r="I86" s="4"/>
     </row>
@@ -4142,15 +3978,13 @@
       <c r="B87" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="C87" s="5">
-        <v>46726</v>
-      </c>
-      <c r="D87" s="3" t="s">
+      <c r="C87" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="E87" s="4">
-        <v>0</v>
-      </c>
+      <c r="D87" s="5">
+        <v>46803</v>
+      </c>
+      <c r="E87" s="4"/>
       <c r="F87" s="3" t="s">
         <v>30</v>
       </c>
@@ -4158,7 +3992,7 @@
         <v>5</v>
       </c>
       <c r="H87" s="6">
-        <v>80</v>
+        <v>380</v>
       </c>
       <c r="I87" s="4"/>
     </row>
@@ -4169,15 +4003,13 @@
       <c r="B88" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="C88" s="5">
+      <c r="C88" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="D88" s="5">
         <v>46690</v>
       </c>
-      <c r="D88" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="E88" s="4">
-        <v>0</v>
-      </c>
+      <c r="E88" s="4"/>
       <c r="F88" s="3" t="s">
         <v>30</v>
       </c>
@@ -4196,15 +4028,13 @@
       <c r="B89" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="C89" s="5">
+      <c r="C89" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="D89" s="5">
         <v>46808</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="E89" s="4">
-        <v>0</v>
-      </c>
+      <c r="E89" s="4"/>
       <c r="F89" s="3" t="s">
         <v>15</v>
       </c>
@@ -4212,7 +4042,7 @@
         <v>5</v>
       </c>
       <c r="H89" s="6">
-        <v>1340</v>
+        <v>1240</v>
       </c>
       <c r="I89" s="4"/>
     </row>
@@ -4223,15 +4053,13 @@
       <c r="B90" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C90" s="5">
+      <c r="C90" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D90" s="5">
         <v>46546</v>
       </c>
-      <c r="D90" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="E90" s="4">
-        <v>0</v>
-      </c>
+      <c r="E90" s="4"/>
       <c r="F90" s="3" t="s">
         <v>30</v>
       </c>
@@ -4250,15 +4078,13 @@
       <c r="B91" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C91" s="5">
+      <c r="C91" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D91" s="5">
         <v>46537</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="E91" s="4">
-        <v>0</v>
-      </c>
+      <c r="E91" s="4"/>
       <c r="F91" s="3" t="s">
         <v>30</v>
       </c>
@@ -4277,15 +4103,13 @@
       <c r="B92" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C92" s="5">
+      <c r="C92" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D92" s="5">
         <v>46483</v>
       </c>
-      <c r="D92" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="E92" s="4">
-        <v>0</v>
-      </c>
+      <c r="E92" s="4"/>
       <c r="F92" s="3" t="s">
         <v>178</v>
       </c>
@@ -4304,15 +4128,13 @@
       <c r="B93" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="C93" s="5">
+      <c r="C93" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="D93" s="5">
         <v>46640</v>
       </c>
-      <c r="D93" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="E93" s="4">
-        <v>0</v>
-      </c>
+      <c r="E93" s="4"/>
       <c r="F93" s="3" t="s">
         <v>4</v>
       </c>
@@ -4331,15 +4153,13 @@
       <c r="B94" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="C94" s="5">
+      <c r="C94" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="D94" s="5">
         <v>46640</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="E94" s="4">
-        <v>0</v>
-      </c>
+      <c r="E94" s="4"/>
       <c r="F94" s="3" t="s">
         <v>4</v>
       </c>
@@ -4358,15 +4178,13 @@
       <c r="B95" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C95" s="5">
+      <c r="C95" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D95" s="5">
         <v>46532</v>
       </c>
-      <c r="D95" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="E95" s="4">
-        <v>0</v>
-      </c>
+      <c r="E95" s="4"/>
       <c r="F95" s="3" t="s">
         <v>87</v>
       </c>
@@ -4379,56 +4197,52 @@
       <c r="I95" s="4"/>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A96" s="2">
+      <c r="A96" s="9">
         <v>4010013584</v>
       </c>
-      <c r="B96" s="3" t="s">
+      <c r="B96" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="C96" s="5">
+      <c r="C96" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D96" s="11"/>
+      <c r="E96" s="12"/>
+      <c r="F96" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="G96" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="H96" s="12"/>
+      <c r="I96" s="13">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A97" s="2">
+        <v>4010013584</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D97" s="5">
         <v>46537</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="E96" s="4">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3" t="s">
+      <c r="E97" s="4"/>
+      <c r="F97" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H96" s="6">
+      <c r="G97" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H97" s="6">
         <v>380</v>
       </c>
-      <c r="I96" s="4"/>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A97" s="15">
-        <v>4010013584</v>
-      </c>
-      <c r="B97" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="C97" s="17"/>
-      <c r="D97" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="E97" s="18">
-        <v>0</v>
-      </c>
-      <c r="F97" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="G97" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="H97" s="18"/>
-      <c r="I97" s="19">
-        <v>900</v>
-      </c>
+      <c r="I97" s="4"/>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
@@ -4437,15 +4251,13 @@
       <c r="B98" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="C98" s="5">
+      <c r="C98" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="D98" s="5">
         <v>46579</v>
       </c>
-      <c r="D98" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="E98" s="4">
-        <v>0</v>
-      </c>
+      <c r="E98" s="4"/>
       <c r="F98" s="3" t="s">
         <v>87</v>
       </c>
@@ -4464,15 +4276,13 @@
       <c r="B99" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C99" s="5">
+      <c r="C99" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D99" s="5">
         <v>46568</v>
       </c>
-      <c r="D99" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="E99" s="4">
-        <v>0</v>
-      </c>
+      <c r="E99" s="4"/>
       <c r="F99" s="3" t="s">
         <v>87</v>
       </c>
@@ -4491,15 +4301,13 @@
       <c r="B100" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="C100" s="5">
+      <c r="C100" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="D100" s="5">
         <v>46579</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="E100" s="4">
-        <v>0</v>
-      </c>
+      <c r="E100" s="4"/>
       <c r="F100" s="3" t="s">
         <v>87</v>
       </c>
@@ -4518,15 +4326,13 @@
       <c r="B101" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="C101" s="5">
+      <c r="C101" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="D101" s="5">
         <v>46471</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="E101" s="4">
-        <v>0</v>
-      </c>
+      <c r="E101" s="4"/>
       <c r="F101" s="3" t="s">
         <v>183</v>
       </c>
@@ -4539,27 +4345,25 @@
       <c r="I101" s="4"/>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A102" s="15">
+      <c r="A102" s="9">
         <v>6010000078</v>
       </c>
-      <c r="B102" s="16" t="s">
+      <c r="B102" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="C102" s="17"/>
-      <c r="D102" s="16" t="s">
+      <c r="C102" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E102" s="18">
-        <v>0</v>
-      </c>
-      <c r="F102" s="16" t="s">
+      <c r="D102" s="11"/>
+      <c r="E102" s="12"/>
+      <c r="F102" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="G102" s="16" t="s">
+      <c r="G102" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="H102" s="18"/>
-      <c r="I102" s="19">
+      <c r="H102" s="12"/>
+      <c r="I102" s="13">
         <v>125</v>
       </c>
     </row>
@@ -4570,15 +4374,13 @@
       <c r="B103" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="C103" s="5">
+      <c r="C103" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="D103" s="5">
         <v>46780</v>
       </c>
-      <c r="D103" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="E103" s="4">
-        <v>0</v>
-      </c>
+      <c r="E103" s="4"/>
       <c r="F103" s="3" t="s">
         <v>185</v>
       </c>
@@ -4591,56 +4393,52 @@
       <c r="I103" s="4"/>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A104" s="2">
+      <c r="A104" s="9">
         <v>4010013593</v>
       </c>
-      <c r="B104" s="3" t="s">
+      <c r="B104" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="C104" s="5">
+      <c r="C104" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D104" s="11"/>
+      <c r="E104" s="12"/>
+      <c r="F104" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G104" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="H104" s="12"/>
+      <c r="I104" s="13">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A105" s="2">
+        <v>4010013593</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D105" s="5">
         <v>46758</v>
       </c>
-      <c r="D104" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="E104" s="4">
-        <v>0</v>
-      </c>
-      <c r="F104" s="3" t="s">
+      <c r="E105" s="4"/>
+      <c r="F105" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G104" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H104" s="6">
+      <c r="G105" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H105" s="6">
         <v>380</v>
       </c>
-      <c r="I104" s="4"/>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A105" s="15">
-        <v>4010013593</v>
-      </c>
-      <c r="B105" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="C105" s="17"/>
-      <c r="D105" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="E105" s="18">
-        <v>0</v>
-      </c>
-      <c r="F105" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="G105" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="H105" s="18"/>
-      <c r="I105" s="19">
-        <v>560</v>
-      </c>
+      <c r="I105" s="4"/>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
@@ -4649,15 +4447,13 @@
       <c r="B106" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C106" s="5">
+      <c r="C106" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D106" s="5">
         <v>46641</v>
       </c>
-      <c r="D106" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="E106" s="4">
-        <v>0</v>
-      </c>
+      <c r="E106" s="4"/>
       <c r="F106" s="3" t="s">
         <v>30</v>
       </c>
@@ -4670,27 +4466,25 @@
       <c r="I106" s="4"/>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A107" s="15">
+      <c r="A107" s="9">
         <v>4010013594</v>
       </c>
-      <c r="B107" s="16" t="s">
+      <c r="B107" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="C107" s="17"/>
-      <c r="D107" s="16" t="s">
+      <c r="C107" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E107" s="18">
-        <v>0</v>
-      </c>
-      <c r="F107" s="16" t="s">
+      <c r="D107" s="11"/>
+      <c r="E107" s="12"/>
+      <c r="F107" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="G107" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="H107" s="18"/>
-      <c r="I107" s="19">
+      <c r="G107" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="H107" s="12"/>
+      <c r="I107" s="13">
         <v>1120</v>
       </c>
     </row>
@@ -4701,15 +4495,13 @@
       <c r="B108" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C108" s="5">
+      <c r="C108" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D108" s="5">
         <v>46573</v>
       </c>
-      <c r="D108" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="E108" s="4">
-        <v>0</v>
-      </c>
+      <c r="E108" s="4"/>
       <c r="F108" s="3" t="s">
         <v>30</v>
       </c>
@@ -4728,15 +4520,13 @@
       <c r="B109" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="C109" s="5">
+      <c r="C109" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D109" s="5">
         <v>46610</v>
       </c>
-      <c r="D109" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="E109" s="4">
-        <v>0</v>
-      </c>
+      <c r="E109" s="4"/>
       <c r="F109" s="3" t="s">
         <v>30</v>
       </c>
@@ -4755,15 +4545,13 @@
       <c r="B110" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="C110" s="5">
+      <c r="C110" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="D110" s="5">
         <v>46447</v>
       </c>
-      <c r="D110" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="E110" s="4">
-        <v>0</v>
-      </c>
+      <c r="E110" s="4"/>
       <c r="F110" s="3" t="s">
         <v>30</v>
       </c>
@@ -4776,56 +4564,52 @@
       <c r="I110" s="4"/>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A111" s="15">
+      <c r="A111" s="2">
         <v>6010000233</v>
       </c>
-      <c r="B111" s="16" t="s">
+      <c r="B111" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="C111" s="17"/>
-      <c r="D111" s="16" t="s">
+      <c r="C111" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="D111" s="5">
+        <v>46721</v>
+      </c>
+      <c r="E111" s="4"/>
+      <c r="F111" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G111" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H111" s="6">
+        <v>90</v>
+      </c>
+      <c r="I111" s="4"/>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A112" s="9">
+        <v>6010000233</v>
+      </c>
+      <c r="B112" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="C112" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E111" s="18">
-        <v>0</v>
-      </c>
-      <c r="F111" s="16" t="s">
+      <c r="D112" s="11"/>
+      <c r="E112" s="12"/>
+      <c r="F112" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="G111" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="H111" s="18"/>
-      <c r="I111" s="19">
+      <c r="G112" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="H112" s="12"/>
+      <c r="I112" s="13">
         <v>1350</v>
       </c>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A112" s="2">
-        <v>6010000233</v>
-      </c>
-      <c r="B112" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="C112" s="5">
-        <v>46721</v>
-      </c>
-      <c r="D112" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="E112" s="4">
-        <v>0</v>
-      </c>
-      <c r="F112" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G112" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H112" s="6">
-        <v>90</v>
-      </c>
-      <c r="I112" s="4"/>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="2">
@@ -4834,15 +4618,13 @@
       <c r="B113" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="C113" s="5">
+      <c r="C113" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D113" s="5">
         <v>46423</v>
       </c>
-      <c r="D113" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E113" s="4">
-        <v>0</v>
-      </c>
+      <c r="E113" s="4"/>
       <c r="F113" s="3" t="s">
         <v>189</v>
       </c>
@@ -4861,15 +4643,13 @@
       <c r="B114" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="C114" s="5">
+      <c r="C114" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="D114" s="5">
         <v>46598</v>
       </c>
-      <c r="D114" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="E114" s="4">
-        <v>0</v>
-      </c>
+      <c r="E114" s="4"/>
       <c r="F114" s="3" t="s">
         <v>22</v>
       </c>
@@ -4888,15 +4668,13 @@
       <c r="B115" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C115" s="5">
+      <c r="C115" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D115" s="5">
         <v>46510</v>
       </c>
-      <c r="D115" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="E115" s="4">
-        <v>0</v>
-      </c>
+      <c r="E115" s="4"/>
       <c r="F115" s="3" t="s">
         <v>119</v>
       </c>
@@ -4904,7 +4682,7 @@
         <v>5</v>
       </c>
       <c r="H115" s="6">
-        <v>2280</v>
+        <v>2230</v>
       </c>
       <c r="I115" s="4"/>
     </row>
@@ -4915,15 +4693,13 @@
       <c r="B116" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="C116" s="5">
+      <c r="C116" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D116" s="5">
         <v>46623</v>
       </c>
-      <c r="D116" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="E116" s="4">
-        <v>0</v>
-      </c>
+      <c r="E116" s="4"/>
       <c r="F116" s="3" t="s">
         <v>30</v>
       </c>
@@ -4942,15 +4718,13 @@
       <c r="B117" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="C117" s="5">
+      <c r="C117" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="D117" s="5">
         <v>46586</v>
       </c>
-      <c r="D117" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="E117" s="4">
-        <v>0</v>
-      </c>
+      <c r="E117" s="4"/>
       <c r="F117" s="3" t="s">
         <v>344</v>
       </c>
@@ -4969,15 +4743,13 @@
       <c r="B118" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="C118" s="5">
+      <c r="C118" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D118" s="5">
         <v>46488</v>
       </c>
-      <c r="D118" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="E118" s="4">
-        <v>0</v>
-      </c>
+      <c r="E118" s="4"/>
       <c r="F118" s="3" t="s">
         <v>104</v>
       </c>
@@ -4996,15 +4768,13 @@
       <c r="B119" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="C119" s="5">
+      <c r="C119" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="D119" s="5">
         <v>46660</v>
       </c>
-      <c r="D119" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="E119" s="4">
-        <v>0</v>
-      </c>
+      <c r="E119" s="4"/>
       <c r="F119" s="3" t="s">
         <v>2</v>
       </c>
@@ -5023,15 +4793,13 @@
       <c r="B120" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="C120" s="5">
+      <c r="C120" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D120" s="5">
         <v>46505</v>
       </c>
-      <c r="D120" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="E120" s="4">
-        <v>0</v>
-      </c>
+      <c r="E120" s="4"/>
       <c r="F120" s="3" t="s">
         <v>194</v>
       </c>
@@ -5050,15 +4818,13 @@
       <c r="B121" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="C121" s="5">
+      <c r="C121" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="D121" s="5">
         <v>46556</v>
       </c>
-      <c r="D121" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="E121" s="4">
-        <v>0</v>
-      </c>
+      <c r="E121" s="4"/>
       <c r="F121" s="3" t="s">
         <v>347</v>
       </c>
@@ -5077,15 +4843,13 @@
       <c r="B122" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="C122" s="5">
+      <c r="C122" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="D122" s="5">
         <v>46586</v>
       </c>
-      <c r="D122" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="E122" s="4">
-        <v>0</v>
-      </c>
+      <c r="E122" s="4"/>
       <c r="F122" s="3" t="s">
         <v>347</v>
       </c>
@@ -5104,15 +4868,13 @@
       <c r="B123" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="C123" s="5">
+      <c r="C123" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="D123" s="5">
         <v>46624</v>
       </c>
-      <c r="D123" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="E123" s="4">
-        <v>0</v>
-      </c>
+      <c r="E123" s="4"/>
       <c r="F123" s="3" t="s">
         <v>379</v>
       </c>
@@ -5131,15 +4893,13 @@
       <c r="B124" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="C124" s="5">
+      <c r="C124" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="D124" s="5">
         <v>46685</v>
       </c>
-      <c r="D124" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="E124" s="4">
-        <v>0</v>
-      </c>
+      <c r="E124" s="4"/>
       <c r="F124" s="3" t="s">
         <v>379</v>
       </c>
@@ -5158,15 +4918,13 @@
       <c r="B125" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C125" s="5">
+      <c r="C125" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D125" s="5">
         <v>46549</v>
       </c>
-      <c r="D125" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E125" s="4">
-        <v>0</v>
-      </c>
+      <c r="E125" s="4"/>
       <c r="F125" s="3" t="s">
         <v>15</v>
       </c>
@@ -5185,15 +4943,13 @@
       <c r="B126" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C126" s="5">
+      <c r="C126" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D126" s="5">
         <v>46637</v>
       </c>
-      <c r="D126" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E126" s="4">
-        <v>0</v>
-      </c>
+      <c r="E126" s="4"/>
       <c r="F126" s="3" t="s">
         <v>15</v>
       </c>
@@ -5201,7 +4957,7 @@
         <v>5</v>
       </c>
       <c r="H126" s="6">
-        <v>980</v>
+        <v>1080</v>
       </c>
       <c r="I126" s="4"/>
     </row>
@@ -5212,15 +4968,13 @@
       <c r="B127" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C127" s="5">
+      <c r="C127" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D127" s="5">
         <v>46704</v>
       </c>
-      <c r="D127" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E127" s="4">
-        <v>0</v>
-      </c>
+      <c r="E127" s="4"/>
       <c r="F127" s="3" t="s">
         <v>48</v>
       </c>
@@ -5233,56 +4987,52 @@
       <c r="I127" s="4"/>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A128" s="2">
+      <c r="A128" s="9">
         <v>4010013671</v>
       </c>
-      <c r="B128" s="3" t="s">
+      <c r="B128" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="C128" s="5">
+      <c r="C128" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D128" s="11"/>
+      <c r="E128" s="12"/>
+      <c r="F128" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G128" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="H128" s="12"/>
+      <c r="I128" s="13">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A129" s="2">
+        <v>4010013671</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D129" s="5">
         <v>46566</v>
       </c>
-      <c r="D128" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="E128" s="4">
-        <v>0</v>
-      </c>
-      <c r="F128" s="3" t="s">
+      <c r="E129" s="4"/>
+      <c r="F129" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G128" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H128" s="6">
+      <c r="G129" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H129" s="6">
         <v>880</v>
       </c>
-      <c r="I128" s="4"/>
-    </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A129" s="15">
-        <v>4010013671</v>
-      </c>
-      <c r="B129" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="C129" s="17"/>
-      <c r="D129" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="E129" s="18">
-        <v>0</v>
-      </c>
-      <c r="F129" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="G129" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="H129" s="18"/>
-      <c r="I129" s="19">
-        <v>1440</v>
-      </c>
+      <c r="I129" s="4"/>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
@@ -5291,15 +5041,13 @@
       <c r="B130" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="C130" s="5">
+      <c r="C130" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="D130" s="5">
         <v>46780</v>
       </c>
-      <c r="D130" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="E130" s="4">
-        <v>0</v>
-      </c>
+      <c r="E130" s="4"/>
       <c r="F130" s="3" t="s">
         <v>423</v>
       </c>
@@ -5318,15 +5066,13 @@
       <c r="B131" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="C131" s="5">
+      <c r="C131" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="D131" s="5">
         <v>46661</v>
       </c>
-      <c r="D131" s="3" t="s">
-        <v>424</v>
-      </c>
-      <c r="E131" s="4">
-        <v>0</v>
-      </c>
+      <c r="E131" s="4"/>
       <c r="F131" s="3" t="s">
         <v>423</v>
       </c>
@@ -5345,15 +5091,13 @@
       <c r="B132" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="C132" s="5">
+      <c r="C132" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="D132" s="5">
         <v>46812</v>
       </c>
-      <c r="D132" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="E132" s="4">
-        <v>0</v>
-      </c>
+      <c r="E132" s="4"/>
       <c r="F132" s="3" t="s">
         <v>399</v>
       </c>
@@ -5372,15 +5116,13 @@
       <c r="B133" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="C133" s="5">
+      <c r="C133" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="D133" s="5">
         <v>46780</v>
       </c>
-      <c r="D133" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="E133" s="4">
-        <v>0</v>
-      </c>
+      <c r="E133" s="4"/>
       <c r="F133" s="3" t="s">
         <v>399</v>
       </c>
@@ -5393,27 +5135,25 @@
       <c r="I133" s="4"/>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A134" s="15">
+      <c r="A134" s="9">
         <v>6010000083</v>
       </c>
-      <c r="B134" s="16" t="s">
+      <c r="B134" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="C134" s="17"/>
-      <c r="D134" s="16" t="s">
+      <c r="C134" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E134" s="18">
-        <v>0</v>
-      </c>
-      <c r="F134" s="16" t="s">
+      <c r="D134" s="11"/>
+      <c r="E134" s="12"/>
+      <c r="F134" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="G134" s="16" t="s">
+      <c r="G134" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="H134" s="18"/>
-      <c r="I134" s="19">
+      <c r="H134" s="12"/>
+      <c r="I134" s="13">
         <v>300</v>
       </c>
     </row>
@@ -5424,15 +5164,13 @@
       <c r="B135" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="C135" s="5">
+      <c r="C135" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="D135" s="5">
         <v>46537</v>
       </c>
-      <c r="D135" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="E135" s="4">
-        <v>0</v>
-      </c>
+      <c r="E135" s="4"/>
       <c r="F135" s="3" t="s">
         <v>196</v>
       </c>
@@ -5440,7 +5178,7 @@
         <v>3</v>
       </c>
       <c r="H135" s="6">
-        <v>1270</v>
+        <v>1260</v>
       </c>
       <c r="I135" s="4"/>
     </row>
@@ -5451,15 +5189,13 @@
       <c r="B136" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="C136" s="5">
+      <c r="C136" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="D136" s="5">
         <v>46711</v>
       </c>
-      <c r="D136" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="E136" s="4">
-        <v>0</v>
-      </c>
+      <c r="E136" s="4"/>
       <c r="F136" s="3" t="s">
         <v>200</v>
       </c>
@@ -5478,15 +5214,13 @@
       <c r="B137" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="C137" s="5">
+      <c r="C137" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="D137" s="5">
         <v>46971</v>
       </c>
-      <c r="D137" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="E137" s="4">
-        <v>0</v>
-      </c>
+      <c r="E137" s="4"/>
       <c r="F137" s="3" t="s">
         <v>22</v>
       </c>
@@ -5499,56 +5233,52 @@
       <c r="I137" s="4"/>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A138" s="2">
+      <c r="A138" s="9">
         <v>6010000116</v>
       </c>
-      <c r="B138" s="3" t="s">
+      <c r="B138" s="10" t="s">
         <v>251</v>
       </c>
-      <c r="C138" s="5">
+      <c r="C138" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D138" s="11"/>
+      <c r="E138" s="12"/>
+      <c r="F138" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="G138" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="H138" s="12"/>
+      <c r="I138" s="13">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A139" s="2">
+        <v>6010000116</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="D139" s="5">
         <v>46971</v>
       </c>
-      <c r="D138" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="E138" s="4">
-        <v>0</v>
-      </c>
-      <c r="F138" s="3" t="s">
+      <c r="E139" s="4"/>
+      <c r="F139" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G138" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H138" s="6">
+      <c r="G139" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H139" s="6">
         <v>4780</v>
       </c>
-      <c r="I138" s="4"/>
-    </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A139" s="15">
-        <v>6010000116</v>
-      </c>
-      <c r="B139" s="16" t="s">
-        <v>251</v>
-      </c>
-      <c r="C139" s="17"/>
-      <c r="D139" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="E139" s="18">
-        <v>0</v>
-      </c>
-      <c r="F139" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="G139" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="H139" s="18"/>
-      <c r="I139" s="19">
-        <v>3600</v>
-      </c>
+      <c r="I139" s="4"/>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="2">
@@ -5557,13 +5287,11 @@
       <c r="B140" s="3" t="s">
         <v>434</v>
       </c>
-      <c r="C140" s="5"/>
-      <c r="D140" s="3" t="s">
+      <c r="C140" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E140" s="4">
-        <v>0</v>
-      </c>
+      <c r="D140" s="5"/>
+      <c r="E140" s="4"/>
       <c r="F140" s="3" t="s">
         <v>2</v>
       </c>
@@ -5582,15 +5310,13 @@
       <c r="B141" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="C141" s="5">
+      <c r="C141" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="D141" s="5">
         <v>46711</v>
       </c>
-      <c r="D141" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="E141" s="4">
-        <v>0</v>
-      </c>
+      <c r="E141" s="4"/>
       <c r="F141" s="3" t="s">
         <v>22</v>
       </c>
@@ -5609,15 +5335,13 @@
       <c r="B142" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="C142" s="5">
+      <c r="C142" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="D142" s="5">
         <v>46574</v>
       </c>
-      <c r="D142" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E142" s="4">
-        <v>0</v>
-      </c>
+      <c r="E142" s="4"/>
       <c r="F142" s="3" t="s">
         <v>22</v>
       </c>
@@ -5636,15 +5360,13 @@
       <c r="B143" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="C143" s="5">
+      <c r="C143" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="D143" s="5">
         <v>46751</v>
       </c>
-      <c r="D143" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="E143" s="4">
-        <v>0</v>
-      </c>
+      <c r="E143" s="4"/>
       <c r="F143" s="3" t="s">
         <v>22</v>
       </c>
@@ -5657,27 +5379,25 @@
       <c r="I143" s="4"/>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A144" s="15">
+      <c r="A144" s="9">
         <v>6010000148</v>
       </c>
-      <c r="B144" s="16" t="s">
+      <c r="B144" s="10" t="s">
         <v>308</v>
       </c>
-      <c r="C144" s="17"/>
-      <c r="D144" s="16" t="s">
+      <c r="C144" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E144" s="18">
-        <v>0</v>
-      </c>
-      <c r="F144" s="16" t="s">
+      <c r="D144" s="11"/>
+      <c r="E144" s="12"/>
+      <c r="F144" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="G144" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="H144" s="18"/>
-      <c r="I144" s="19">
+      <c r="G144" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="H144" s="12"/>
+      <c r="I144" s="13">
         <v>20</v>
       </c>
     </row>
@@ -5688,15 +5408,13 @@
       <c r="B145" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="C145" s="5">
+      <c r="C145" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="D145" s="5">
         <v>46598</v>
       </c>
-      <c r="D145" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="E145" s="4">
-        <v>0</v>
-      </c>
+      <c r="E145" s="4"/>
       <c r="F145" s="3" t="s">
         <v>259</v>
       </c>
@@ -5715,15 +5433,13 @@
       <c r="B146" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="C146" s="5">
+      <c r="C146" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="D146" s="5">
         <v>46388</v>
       </c>
-      <c r="D146" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="E146" s="4">
-        <v>0</v>
-      </c>
+      <c r="E146" s="4"/>
       <c r="F146" s="3" t="s">
         <v>203</v>
       </c>
@@ -5742,15 +5458,13 @@
       <c r="B147" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="C147" s="5">
+      <c r="C147" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D147" s="5">
         <v>46388</v>
       </c>
-      <c r="D147" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="E147" s="4">
-        <v>0</v>
-      </c>
+      <c r="E147" s="4"/>
       <c r="F147" s="3" t="s">
         <v>203</v>
       </c>
@@ -5769,15 +5483,13 @@
       <c r="B148" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="C148" s="5">
+      <c r="C148" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="D148" s="5">
         <v>46752</v>
       </c>
-      <c r="D148" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="E148" s="4">
-        <v>0</v>
-      </c>
+      <c r="E148" s="4"/>
       <c r="F148" s="3" t="s">
         <v>87</v>
       </c>
@@ -5785,7 +5497,7 @@
         <v>5</v>
       </c>
       <c r="H148" s="6">
-        <v>4860</v>
+        <v>4800</v>
       </c>
       <c r="I148" s="4"/>
     </row>
@@ -5796,15 +5508,13 @@
       <c r="B149" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="C149" s="5">
+      <c r="C149" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="D149" s="5">
         <v>46614</v>
       </c>
-      <c r="D149" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="E149" s="4">
-        <v>0</v>
-      </c>
+      <c r="E149" s="4"/>
       <c r="F149" s="3" t="s">
         <v>22</v>
       </c>
@@ -5823,15 +5533,13 @@
       <c r="B150" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="C150" s="5">
+      <c r="C150" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="D150" s="5">
         <v>46641</v>
       </c>
-      <c r="D150" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="E150" s="4">
-        <v>0</v>
-      </c>
+      <c r="E150" s="4"/>
       <c r="F150" s="3" t="s">
         <v>207</v>
       </c>
@@ -5839,109 +5547,101 @@
         <v>3</v>
       </c>
       <c r="H150" s="6">
-        <v>7000</v>
+        <v>6950</v>
       </c>
       <c r="I150" s="4"/>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A151" s="15">
+      <c r="A151" s="9">
         <v>6010000086</v>
       </c>
-      <c r="B151" s="16" t="s">
+      <c r="B151" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="C151" s="17"/>
-      <c r="D151" s="16" t="s">
+      <c r="C151" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E151" s="18">
-        <v>0</v>
-      </c>
-      <c r="F151" s="16" t="s">
+      <c r="D151" s="11"/>
+      <c r="E151" s="12"/>
+      <c r="F151" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="G151" s="16" t="s">
+      <c r="G151" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="H151" s="18"/>
-      <c r="I151" s="19">
+      <c r="H151" s="12"/>
+      <c r="I151" s="13">
         <v>2000</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A152" s="15">
+      <c r="A152" s="2">
         <v>6010000147</v>
       </c>
-      <c r="B152" s="16" t="s">
+      <c r="B152" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="C152" s="17"/>
-      <c r="D152" s="16" t="s">
+      <c r="C152" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="D152" s="5">
+        <v>46813</v>
+      </c>
+      <c r="E152" s="4"/>
+      <c r="F152" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="G152" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H152" s="6">
+        <v>670</v>
+      </c>
+      <c r="I152" s="4"/>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A153" s="9">
+        <v>6010000147</v>
+      </c>
+      <c r="B153" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="C153" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E152" s="18">
-        <v>0</v>
-      </c>
-      <c r="F152" s="16" t="s">
+      <c r="D153" s="11"/>
+      <c r="E153" s="12"/>
+      <c r="F153" s="10" t="s">
         <v>289</v>
       </c>
-      <c r="G152" s="16" t="s">
+      <c r="G153" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="H152" s="18"/>
-      <c r="I152" s="19">
+      <c r="H153" s="12"/>
+      <c r="I153" s="13">
         <v>500</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A153" s="2">
-        <v>6010000147</v>
-      </c>
-      <c r="B153" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="C153" s="5">
-        <v>46813</v>
-      </c>
-      <c r="D153" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="E153" s="4">
-        <v>0</v>
-      </c>
-      <c r="F153" s="3" t="s">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A154" s="9">
+        <v>6010000144</v>
+      </c>
+      <c r="B154" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="C154" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D154" s="11"/>
+      <c r="E154" s="12"/>
+      <c r="F154" s="10" t="s">
         <v>289</v>
       </c>
-      <c r="G153" s="3" t="s">
+      <c r="G154" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="H153" s="6">
-        <v>670</v>
-      </c>
-      <c r="I153" s="4"/>
-    </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A154" s="15">
-        <v>6010000144</v>
-      </c>
-      <c r="B154" s="16" t="s">
-        <v>298</v>
-      </c>
-      <c r="C154" s="17"/>
-      <c r="D154" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="E154" s="18">
-        <v>0</v>
-      </c>
-      <c r="F154" s="16" t="s">
-        <v>289</v>
-      </c>
-      <c r="G154" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="H154" s="18"/>
-      <c r="I154" s="19">
+      <c r="H154" s="12"/>
+      <c r="I154" s="13">
         <v>100</v>
       </c>
     </row>
@@ -5952,15 +5652,13 @@
       <c r="B155" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="C155" s="5">
+      <c r="C155" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="D155" s="5">
         <v>46605</v>
       </c>
-      <c r="D155" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="E155" s="4">
-        <v>0</v>
-      </c>
+      <c r="E155" s="4"/>
       <c r="F155" s="3" t="s">
         <v>289</v>
       </c>
@@ -5979,15 +5677,13 @@
       <c r="B156" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="C156" s="5">
+      <c r="C156" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="D156" s="5">
         <v>46692</v>
       </c>
-      <c r="D156" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="E156" s="4">
-        <v>0</v>
-      </c>
+      <c r="E156" s="4"/>
       <c r="F156" s="3" t="s">
         <v>302</v>
       </c>
@@ -6000,56 +5696,52 @@
       <c r="I156" s="4"/>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A157" s="2">
+      <c r="A157" s="9">
         <v>6010000215</v>
       </c>
-      <c r="B157" s="3" t="s">
+      <c r="B157" s="10" t="s">
         <v>389</v>
       </c>
-      <c r="C157" s="5">
+      <c r="C157" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D157" s="11"/>
+      <c r="E157" s="12"/>
+      <c r="F157" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="G157" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="H157" s="12"/>
+      <c r="I157" s="13">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A158" s="2">
+        <v>6010000215</v>
+      </c>
+      <c r="B158" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="C158" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="D158" s="5">
         <v>46726</v>
       </c>
-      <c r="D157" s="3" t="s">
+      <c r="E158" s="4"/>
+      <c r="F158" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="E157" s="4">
-        <v>0</v>
-      </c>
-      <c r="F157" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="G157" s="3" t="s">
+      <c r="G158" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H157" s="6">
+      <c r="H158" s="6">
         <v>494</v>
       </c>
-      <c r="I157" s="4"/>
-    </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A158" s="15">
-        <v>6010000215</v>
-      </c>
-      <c r="B158" s="16" t="s">
-        <v>389</v>
-      </c>
-      <c r="C158" s="17"/>
-      <c r="D158" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="E158" s="18">
-        <v>0</v>
-      </c>
-      <c r="F158" s="16" t="s">
-        <v>391</v>
-      </c>
-      <c r="G158" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="H158" s="18"/>
-      <c r="I158" s="19">
-        <v>1000</v>
-      </c>
+      <c r="I158" s="4"/>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" s="2">
@@ -6058,15 +5750,13 @@
       <c r="B159" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="C159" s="5">
+      <c r="C159" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="D159" s="5">
         <v>46610</v>
       </c>
-      <c r="D159" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="E159" s="4">
-        <v>0</v>
-      </c>
+      <c r="E159" s="4"/>
       <c r="F159" s="3" t="s">
         <v>294</v>
       </c>
@@ -6085,15 +5775,13 @@
       <c r="B160" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="C160" s="5">
+      <c r="C160" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="D160" s="5">
         <v>46425</v>
       </c>
-      <c r="D160" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="E160" s="4">
-        <v>0</v>
-      </c>
+      <c r="E160" s="4"/>
       <c r="F160" s="3" t="s">
         <v>297</v>
       </c>
@@ -6112,15 +5800,13 @@
       <c r="B161" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="C161" s="5">
+      <c r="C161" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="D161" s="5">
         <v>46556</v>
       </c>
-      <c r="D161" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="E161" s="4">
-        <v>0</v>
-      </c>
+      <c r="E161" s="4"/>
       <c r="F161" s="3" t="s">
         <v>302</v>
       </c>
@@ -6139,15 +5825,13 @@
       <c r="B162" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C162" s="5">
+      <c r="C162" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D162" s="5">
         <v>46446</v>
       </c>
-      <c r="D162" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="E162" s="4">
-        <v>0</v>
-      </c>
+      <c r="E162" s="4"/>
       <c r="F162" s="3" t="s">
         <v>30</v>
       </c>
@@ -6155,32 +5839,30 @@
         <v>5</v>
       </c>
       <c r="H162" s="6">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="I162" s="4"/>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A163" s="15">
+      <c r="A163" s="9">
         <v>4010013655</v>
       </c>
-      <c r="B163" s="16" t="s">
+      <c r="B163" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="C163" s="17"/>
-      <c r="D163" s="16" t="s">
+      <c r="C163" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E163" s="18">
-        <v>0</v>
-      </c>
-      <c r="F163" s="16" t="s">
+      <c r="D163" s="11"/>
+      <c r="E163" s="12"/>
+      <c r="F163" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="G163" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="H163" s="18"/>
-      <c r="I163" s="19">
+      <c r="G163" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="H163" s="12"/>
+      <c r="I163" s="13">
         <v>400</v>
       </c>
     </row>
@@ -6191,15 +5873,13 @@
       <c r="B164" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="C164" s="5">
+      <c r="C164" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D164" s="5">
         <v>46550</v>
       </c>
-      <c r="D164" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="E164" s="4">
-        <v>0</v>
-      </c>
+      <c r="E164" s="4"/>
       <c r="F164" s="3" t="s">
         <v>30</v>
       </c>
@@ -6207,7 +5887,7 @@
         <v>5</v>
       </c>
       <c r="H164" s="6">
-        <v>480</v>
+        <v>460</v>
       </c>
       <c r="I164" s="4"/>
     </row>
@@ -6218,15 +5898,13 @@
       <c r="B165" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C165" s="5">
-        <v>46579</v>
-      </c>
-      <c r="D165" s="3" t="s">
+      <c r="C165" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E165" s="4">
-        <v>0</v>
-      </c>
+      <c r="D165" s="5">
+        <v>46511</v>
+      </c>
+      <c r="E165" s="4"/>
       <c r="F165" s="3" t="s">
         <v>30</v>
       </c>
@@ -6234,7 +5912,7 @@
         <v>5</v>
       </c>
       <c r="H165" s="6">
-        <v>590</v>
+        <v>140</v>
       </c>
       <c r="I165" s="4"/>
     </row>
@@ -6245,15 +5923,13 @@
       <c r="B166" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C166" s="5">
-        <v>46511</v>
-      </c>
-      <c r="D166" s="3" t="s">
+      <c r="C166" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E166" s="4">
-        <v>0</v>
-      </c>
+      <c r="D166" s="5">
+        <v>46579</v>
+      </c>
+      <c r="E166" s="4"/>
       <c r="F166" s="3" t="s">
         <v>30</v>
       </c>
@@ -6261,7 +5937,7 @@
         <v>5</v>
       </c>
       <c r="H166" s="6">
-        <v>140</v>
+        <v>590</v>
       </c>
       <c r="I166" s="4"/>
     </row>
@@ -6272,15 +5948,13 @@
       <c r="B167" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C167" s="5">
+      <c r="C167" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D167" s="5">
         <v>46525</v>
       </c>
-      <c r="D167" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E167" s="4">
-        <v>0</v>
-      </c>
+      <c r="E167" s="4"/>
       <c r="F167" s="3" t="s">
         <v>30</v>
       </c>
@@ -6299,15 +5973,13 @@
       <c r="B168" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="C168" s="5">
+      <c r="C168" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="D168" s="5">
         <v>46484</v>
       </c>
-      <c r="D168" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="E168" s="4">
-        <v>0</v>
-      </c>
+      <c r="E168" s="4"/>
       <c r="F168" s="3" t="s">
         <v>194</v>
       </c>
@@ -6326,15 +5998,13 @@
       <c r="B169" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="C169" s="5">
+      <c r="C169" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D169" s="5">
         <v>46388</v>
       </c>
-      <c r="D169" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="E169" s="4">
-        <v>0</v>
-      </c>
+      <c r="E169" s="4"/>
       <c r="F169" s="3" t="s">
         <v>194</v>
       </c>
@@ -6347,108 +6017,100 @@
       <c r="I169" s="4"/>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A170" s="2">
+      <c r="A170" s="9">
         <v>6010000126</v>
       </c>
-      <c r="B170" s="3" t="s">
+      <c r="B170" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="C170" s="5">
+      <c r="C170" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D170" s="11"/>
+      <c r="E170" s="12"/>
+      <c r="F170" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="G170" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="H170" s="12"/>
+      <c r="I170" s="13">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A171" s="2">
+        <v>6010000126</v>
+      </c>
+      <c r="B171" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="C171" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="D171" s="5">
         <v>46780</v>
       </c>
-      <c r="D170" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="E170" s="4">
-        <v>0</v>
-      </c>
-      <c r="F170" s="3" t="s">
+      <c r="E171" s="4"/>
+      <c r="F171" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G170" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H170" s="6">
+      <c r="G171" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H171" s="6">
         <v>5100</v>
       </c>
-      <c r="I170" s="4"/>
-    </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A171" s="15">
-        <v>6010000126</v>
-      </c>
-      <c r="B171" s="16" t="s">
-        <v>262</v>
-      </c>
-      <c r="C171" s="17"/>
-      <c r="D171" s="16" t="s">
+      <c r="I171" s="4"/>
+    </row>
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A172" s="2">
+        <v>6010000227</v>
+      </c>
+      <c r="B172" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="C172" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="D172" s="5">
+        <v>46631</v>
+      </c>
+      <c r="E172" s="4"/>
+      <c r="F172" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G172" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H172" s="6">
+        <v>4340</v>
+      </c>
+      <c r="I172" s="4"/>
+    </row>
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A173" s="9">
+        <v>6010000227</v>
+      </c>
+      <c r="B173" s="10" t="s">
+        <v>403</v>
+      </c>
+      <c r="C173" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E171" s="18">
-        <v>0</v>
-      </c>
-      <c r="F171" s="16" t="s">
+      <c r="D173" s="11"/>
+      <c r="E173" s="12"/>
+      <c r="F173" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="G171" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="H171" s="18"/>
-      <c r="I171" s="19">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A172" s="15">
-        <v>6010000227</v>
-      </c>
-      <c r="B172" s="16" t="s">
-        <v>403</v>
-      </c>
-      <c r="C172" s="17"/>
-      <c r="D172" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="E172" s="18">
-        <v>0</v>
-      </c>
-      <c r="F172" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="G172" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="H172" s="18"/>
-      <c r="I172" s="19">
+      <c r="G173" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="H173" s="12"/>
+      <c r="I173" s="13">
         <v>1200</v>
       </c>
-    </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A173" s="2">
-        <v>6010000227</v>
-      </c>
-      <c r="B173" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="C173" s="5">
-        <v>46631</v>
-      </c>
-      <c r="D173" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="E173" s="4">
-        <v>0</v>
-      </c>
-      <c r="F173" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G173" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H173" s="6">
-        <v>4400</v>
-      </c>
-      <c r="I173" s="4"/>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" s="2">
@@ -6457,15 +6119,13 @@
       <c r="B174" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="C174" s="5">
+      <c r="C174" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="D174" s="5">
         <v>46645</v>
       </c>
-      <c r="D174" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="E174" s="4">
-        <v>0</v>
-      </c>
+      <c r="E174" s="4"/>
       <c r="F174" s="3" t="s">
         <v>22</v>
       </c>
@@ -6484,15 +6144,13 @@
       <c r="B175" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="C175" s="5">
+      <c r="C175" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D175" s="5">
         <v>46661</v>
       </c>
-      <c r="D175" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="E175" s="4">
-        <v>0</v>
-      </c>
+      <c r="E175" s="4"/>
       <c r="F175" s="3" t="s">
         <v>213</v>
       </c>
@@ -6511,15 +6169,13 @@
       <c r="B176" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C176" s="5">
+      <c r="C176" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D176" s="5">
         <v>46625</v>
       </c>
-      <c r="D176" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="E176" s="4">
-        <v>0</v>
-      </c>
+      <c r="E176" s="4"/>
       <c r="F176" s="3" t="s">
         <v>30</v>
       </c>
@@ -6532,108 +6188,100 @@
       <c r="I176" s="4"/>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A177" s="2">
+      <c r="A177" s="9">
         <v>4010013666</v>
       </c>
-      <c r="B177" s="3" t="s">
+      <c r="B177" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="C177" s="5">
+      <c r="C177" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D177" s="11"/>
+      <c r="E177" s="12"/>
+      <c r="F177" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G177" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="H177" s="12"/>
+      <c r="I177" s="13">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A178" s="2">
+        <v>4010013666</v>
+      </c>
+      <c r="B178" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C178" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D178" s="5">
         <v>46593</v>
       </c>
-      <c r="D177" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="E177" s="4">
-        <v>0</v>
-      </c>
-      <c r="F177" s="3" t="s">
+      <c r="E178" s="4"/>
+      <c r="F178" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G177" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H177" s="6">
+      <c r="G178" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H178" s="6">
         <v>100</v>
       </c>
-      <c r="I177" s="4"/>
-    </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A178" s="15">
-        <v>4010013666</v>
-      </c>
-      <c r="B178" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="C178" s="17"/>
-      <c r="D178" s="16" t="s">
+      <c r="I178" s="4"/>
+    </row>
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A179" s="9">
+        <v>6010000128</v>
+      </c>
+      <c r="B179" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="C179" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E178" s="18">
-        <v>0</v>
-      </c>
-      <c r="F178" s="16" t="s">
+      <c r="D179" s="11"/>
+      <c r="E179" s="12"/>
+      <c r="F179" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="G178" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="H178" s="18"/>
-      <c r="I178" s="19">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A179" s="2">
+      <c r="G179" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="H179" s="12"/>
+      <c r="I179" s="13">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A180" s="2">
         <v>6010000128</v>
       </c>
-      <c r="B179" s="3" t="s">
+      <c r="B180" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="C179" s="5">
+      <c r="C180" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D180" s="5">
         <v>46721</v>
       </c>
-      <c r="D179" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="E179" s="4">
-        <v>0</v>
-      </c>
-      <c r="F179" s="3" t="s">
+      <c r="E180" s="4"/>
+      <c r="F180" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G179" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H179" s="6">
-        <v>630</v>
-      </c>
-      <c r="I179" s="4"/>
-    </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A180" s="15">
-        <v>6010000128</v>
-      </c>
-      <c r="B180" s="16" t="s">
-        <v>264</v>
-      </c>
-      <c r="C180" s="17"/>
-      <c r="D180" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="E180" s="18">
-        <v>0</v>
-      </c>
-      <c r="F180" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="G180" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="H180" s="18"/>
-      <c r="I180" s="19">
-        <v>300</v>
-      </c>
+      <c r="G180" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H180" s="6">
+        <v>600</v>
+      </c>
+      <c r="I180" s="4"/>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" s="2">
@@ -6642,15 +6290,13 @@
       <c r="B181" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="C181" s="5">
+      <c r="C181" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D181" s="5">
         <v>46758</v>
       </c>
-      <c r="D181" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="E181" s="4">
-        <v>0</v>
-      </c>
+      <c r="E181" s="4"/>
       <c r="F181" s="3" t="s">
         <v>15</v>
       </c>
@@ -6658,211 +6304,195 @@
         <v>5</v>
       </c>
       <c r="H181" s="6">
-        <v>650</v>
+        <v>590</v>
       </c>
       <c r="I181" s="4"/>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A182" s="15">
+      <c r="A182" s="9">
         <v>6010000129</v>
       </c>
-      <c r="B182" s="16" t="s">
+      <c r="B182" s="10" t="s">
         <v>266</v>
       </c>
-      <c r="C182" s="17"/>
-      <c r="D182" s="16" t="s">
+      <c r="C182" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E182" s="18">
-        <v>0</v>
-      </c>
-      <c r="F182" s="16" t="s">
+      <c r="D182" s="11"/>
+      <c r="E182" s="12"/>
+      <c r="F182" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G182" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="H182" s="18"/>
-      <c r="I182" s="19">
+      <c r="G182" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="H182" s="12"/>
+      <c r="I182" s="13">
         <v>480</v>
       </c>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A183" s="15">
+      <c r="A183" s="2">
         <v>6010000130</v>
       </c>
-      <c r="B183" s="16" t="s">
+      <c r="B183" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="C183" s="17"/>
-      <c r="D183" s="16" t="s">
+      <c r="C183" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="D183" s="5">
+        <v>46753</v>
+      </c>
+      <c r="E183" s="4"/>
+      <c r="F183" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G183" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H183" s="6">
+        <v>630</v>
+      </c>
+      <c r="I183" s="4"/>
+    </row>
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A184" s="9">
+        <v>6010000130</v>
+      </c>
+      <c r="B184" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="C184" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E183" s="18">
-        <v>0</v>
-      </c>
-      <c r="F183" s="16" t="s">
+      <c r="D184" s="11"/>
+      <c r="E184" s="12"/>
+      <c r="F184" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="G183" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="H183" s="18"/>
-      <c r="I183" s="19">
+      <c r="G184" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="H184" s="12"/>
+      <c r="I184" s="13">
         <v>300</v>
       </c>
-    </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A184" s="2">
-        <v>6010000130</v>
-      </c>
-      <c r="B184" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="C184" s="5">
-        <v>46569</v>
-      </c>
-      <c r="D184" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="E184" s="4">
-        <v>0</v>
-      </c>
-      <c r="F184" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G184" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H184" s="6">
-        <v>10</v>
-      </c>
-      <c r="I184" s="4"/>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" s="2">
-        <v>6010000130</v>
+        <v>6010000198</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="C185" s="5">
-        <v>46753</v>
-      </c>
-      <c r="D185" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="E185" s="4">
-        <v>0</v>
-      </c>
+        <v>373</v>
+      </c>
+      <c r="C185" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="D185" s="5">
+        <v>46568</v>
+      </c>
+      <c r="E185" s="4"/>
       <c r="F185" s="3" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="G185" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H185" s="6">
-        <v>630</v>
+        <v>600</v>
       </c>
       <c r="I185" s="4"/>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" s="2">
-        <v>6010000198</v>
+        <v>4010013586</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="C186" s="5">
-        <v>46568</v>
-      </c>
-      <c r="D186" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="E186" s="4">
-        <v>0</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="C186" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D186" s="5">
+        <v>46537</v>
+      </c>
+      <c r="E186" s="4"/>
       <c r="F186" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G186" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H186" s="6">
-        <v>600</v>
+        <v>1250</v>
       </c>
       <c r="I186" s="4"/>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" s="2">
-        <v>4010013586</v>
+        <v>4010013549</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C187" s="5">
-        <v>46537</v>
-      </c>
-      <c r="D187" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="E187" s="4">
-        <v>0</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="C187" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D187" s="5">
+        <v>46525</v>
+      </c>
+      <c r="E187" s="4"/>
       <c r="F187" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G187" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H187" s="6">
-        <v>1250</v>
+        <v>940</v>
       </c>
       <c r="I187" s="4"/>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" s="2">
-        <v>4010013549</v>
+        <v>4010013249</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C188" s="5">
-        <v>46525</v>
-      </c>
-      <c r="D188" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E188" s="4">
         <v>0</v>
       </c>
+      <c r="C188" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D188" s="5">
+        <v>46442</v>
+      </c>
+      <c r="E188" s="4"/>
       <c r="F188" s="3" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G188" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H188" s="6">
-        <v>940</v>
+        <v>300</v>
       </c>
       <c r="I188" s="4"/>
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" s="2">
-        <v>4010013249</v>
+        <v>4010013573</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C189" s="5">
-        <v>46442</v>
-      </c>
-      <c r="D189" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E189" s="4">
-        <v>0</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="C189" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D189" s="5">
+        <v>46423</v>
+      </c>
+      <c r="E189" s="4"/>
       <c r="F189" s="3" t="s">
         <v>4</v>
       </c>
@@ -6870,80 +6500,74 @@
         <v>5</v>
       </c>
       <c r="H189" s="6">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="I189" s="4"/>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" s="2">
-        <v>4010013573</v>
+        <v>4010013574</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C190" s="5">
-        <v>46423</v>
-      </c>
-      <c r="D190" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="E190" s="4">
-        <v>0</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="C190" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D190" s="5">
+        <v>46545</v>
+      </c>
+      <c r="E190" s="4"/>
       <c r="F190" s="3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G190" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H190" s="6">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="I190" s="4"/>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" s="2">
-        <v>4010013574</v>
+        <v>4010013588</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C191" s="5">
-        <v>46545</v>
-      </c>
-      <c r="D191" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="E191" s="4">
-        <v>0</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="C191" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D191" s="5">
+        <v>46582</v>
+      </c>
+      <c r="E191" s="4"/>
       <c r="F191" s="3" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G191" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H191" s="6">
-        <v>580</v>
+        <v>2220</v>
       </c>
       <c r="I191" s="4"/>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" s="2">
-        <v>4010013588</v>
+        <v>4010013479</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C192" s="5">
-        <v>46582</v>
-      </c>
-      <c r="D192" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E192" s="4">
-        <v>0</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="C192" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D192" s="5">
+        <v>46419</v>
+      </c>
+      <c r="E192" s="4"/>
       <c r="F192" s="3" t="s">
         <v>4</v>
       </c>
@@ -6951,7 +6575,7 @@
         <v>5</v>
       </c>
       <c r="H192" s="6">
-        <v>2220</v>
+        <v>180</v>
       </c>
       <c r="I192" s="4"/>
     </row>
@@ -6962,15 +6586,13 @@
       <c r="B193" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C193" s="5">
-        <v>46419</v>
-      </c>
-      <c r="D193" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E193" s="4">
-        <v>0</v>
-      </c>
+      <c r="C193" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D193" s="5">
+        <v>46536</v>
+      </c>
+      <c r="E193" s="4"/>
       <c r="F193" s="3" t="s">
         <v>4</v>
       </c>
@@ -6978,7 +6600,7 @@
         <v>5</v>
       </c>
       <c r="H193" s="6">
-        <v>180</v>
+        <v>320</v>
       </c>
       <c r="I193" s="4"/>
     </row>
@@ -6989,15 +6611,13 @@
       <c r="B194" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C194" s="5">
+      <c r="C194" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D194" s="5">
         <v>46594</v>
       </c>
-      <c r="D194" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E194" s="4">
-        <v>0</v>
-      </c>
+      <c r="E194" s="4"/>
       <c r="F194" s="3" t="s">
         <v>4</v>
       </c>
@@ -7011,20 +6631,18 @@
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" s="2">
-        <v>4010013479</v>
+        <v>4010013700</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C195" s="5">
-        <v>46536</v>
-      </c>
-      <c r="D195" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E195" s="4">
-        <v>0</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="C195" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D195" s="5">
+        <v>46533</v>
+      </c>
+      <c r="E195" s="4"/>
       <c r="F195" s="3" t="s">
         <v>4</v>
       </c>
@@ -7032,7 +6650,7 @@
         <v>5</v>
       </c>
       <c r="H195" s="6">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="I195" s="4"/>
     </row>
@@ -7043,15 +6661,13 @@
       <c r="B196" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="C196" s="5">
+      <c r="C196" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D196" s="5">
         <v>46446</v>
       </c>
-      <c r="D196" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="E196" s="4">
-        <v>0</v>
-      </c>
+      <c r="E196" s="4"/>
       <c r="F196" s="3" t="s">
         <v>4</v>
       </c>
@@ -7065,20 +6681,18 @@
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" s="2">
-        <v>4010013700</v>
+        <v>4010013701</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="C197" s="5">
-        <v>46533</v>
-      </c>
-      <c r="D197" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="E197" s="4">
-        <v>0</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="C197" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D197" s="5">
+        <v>46589</v>
+      </c>
+      <c r="E197" s="4"/>
       <c r="F197" s="3" t="s">
         <v>4</v>
       </c>
@@ -7086,159 +6700,147 @@
         <v>5</v>
       </c>
       <c r="H197" s="6">
-        <v>300</v>
+        <v>1160</v>
       </c>
       <c r="I197" s="4"/>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" s="2">
-        <v>4010013701</v>
+        <v>4010013657</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C198" s="5">
-        <v>46589</v>
-      </c>
-      <c r="D198" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="E198" s="4">
-        <v>0</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="C198" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D198" s="5">
+        <v>46513</v>
+      </c>
+      <c r="E198" s="4"/>
       <c r="F198" s="3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G198" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H198" s="6">
-        <v>1160</v>
+        <v>540</v>
       </c>
       <c r="I198" s="4"/>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A199" s="2">
+      <c r="A199" s="9">
         <v>4010013657</v>
       </c>
-      <c r="B199" s="3" t="s">
+      <c r="B199" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="C199" s="5">
-        <v>46513</v>
-      </c>
-      <c r="D199" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="E199" s="4">
-        <v>0</v>
-      </c>
-      <c r="F199" s="3" t="s">
+      <c r="C199" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D199" s="11"/>
+      <c r="E199" s="12"/>
+      <c r="F199" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="G199" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H199" s="6">
-        <v>540</v>
-      </c>
-      <c r="I199" s="4"/>
+      <c r="G199" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="H199" s="12"/>
+      <c r="I199" s="13">
+        <v>160</v>
+      </c>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A200" s="15">
-        <v>4010013657</v>
-      </c>
-      <c r="B200" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="C200" s="17"/>
-      <c r="D200" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="E200" s="18">
-        <v>0</v>
-      </c>
-      <c r="F200" s="16" t="s">
+      <c r="A200" s="2">
+        <v>4010013658</v>
+      </c>
+      <c r="B200" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C200" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D200" s="5">
+        <v>46587</v>
+      </c>
+      <c r="E200" s="4"/>
+      <c r="F200" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G200" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="H200" s="18"/>
-      <c r="I200" s="19">
-        <v>160</v>
-      </c>
+      <c r="G200" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H200" s="6">
+        <v>1110</v>
+      </c>
+      <c r="I200" s="4"/>
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" s="2">
-        <v>4010013658</v>
+        <v>4010013548</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C201" s="5">
-        <v>46587</v>
-      </c>
-      <c r="D201" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E201" s="4">
-        <v>0</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="C201" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D201" s="5">
+        <v>46469</v>
+      </c>
+      <c r="E201" s="4"/>
       <c r="F201" s="3" t="s">
-        <v>7</v>
+        <v>70</v>
       </c>
       <c r="G201" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H201" s="6">
-        <v>1110</v>
+        <v>830</v>
       </c>
       <c r="I201" s="4"/>
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" s="2">
-        <v>4010013548</v>
+        <v>4010013480</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C202" s="5">
-        <v>46469</v>
-      </c>
-      <c r="D202" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E202" s="4">
-        <v>0</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="C202" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D202" s="5">
+        <v>46408</v>
+      </c>
+      <c r="E202" s="4"/>
       <c r="F202" s="3" t="s">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="G202" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H202" s="6">
-        <v>830</v>
+        <v>1210</v>
       </c>
       <c r="I202" s="4"/>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" s="2">
-        <v>4010013480</v>
+        <v>4010013477</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C203" s="5">
-        <v>46408</v>
-      </c>
-      <c r="D203" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E203" s="4">
-        <v>0</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="C203" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D203" s="5">
+        <v>46574</v>
+      </c>
+      <c r="E203" s="4"/>
       <c r="F203" s="3" t="s">
         <v>7</v>
       </c>
@@ -7246,88 +6848,82 @@
         <v>5</v>
       </c>
       <c r="H203" s="6">
-        <v>1210</v>
+        <v>500</v>
       </c>
       <c r="I203" s="4"/>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" s="2">
-        <v>4010013477</v>
+        <v>6010000131</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C204" s="5">
-        <v>46574</v>
-      </c>
-      <c r="D204" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E204" s="4">
-        <v>0</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="C204" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="D204" s="5">
+        <v>46784</v>
+      </c>
+      <c r="E204" s="4"/>
       <c r="F204" s="3" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="G204" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H204" s="6">
-        <v>580</v>
+        <v>1720</v>
       </c>
       <c r="I204" s="4"/>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" s="2">
-        <v>6010000131</v>
+        <v>4010013699</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="C205" s="5">
-        <v>46784</v>
-      </c>
-      <c r="D205" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="E205" s="4">
-        <v>0</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="C205" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D205" s="5">
+        <v>46438</v>
+      </c>
+      <c r="E205" s="4"/>
       <c r="F205" s="3" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="G205" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H205" s="6">
-        <v>1720</v>
+        <v>310</v>
       </c>
       <c r="I205" s="4"/>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" s="2">
-        <v>4010013699</v>
+        <v>6010000089</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C206" s="5">
-        <v>46438</v>
-      </c>
-      <c r="D206" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="E206" s="4">
-        <v>0</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="C206" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D206" s="5">
+        <v>46871</v>
+      </c>
+      <c r="E206" s="4"/>
       <c r="F206" s="3" t="s">
-        <v>30</v>
+        <v>216</v>
       </c>
       <c r="G206" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H206" s="6">
-        <v>310</v>
+        <v>2300</v>
       </c>
       <c r="I206" s="4"/>
     </row>
@@ -7338,15 +6934,13 @@
       <c r="B207" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="C207" s="5">
-        <v>46871</v>
-      </c>
-      <c r="D207" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="E207" s="4">
-        <v>0</v>
-      </c>
+      <c r="C207" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D207" s="5">
+        <v>46424</v>
+      </c>
+      <c r="E207" s="4"/>
       <c r="F207" s="3" t="s">
         <v>216</v>
       </c>
@@ -7354,186 +6948,172 @@
         <v>3</v>
       </c>
       <c r="H207" s="6">
-        <v>2300</v>
+        <v>2360</v>
       </c>
       <c r="I207" s="4"/>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" s="2">
-        <v>6010000089</v>
+        <v>6010000132</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="C208" s="5">
-        <v>46424</v>
-      </c>
-      <c r="D208" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="E208" s="4">
-        <v>0</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="C208" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="D208" s="5">
+        <v>46614</v>
+      </c>
+      <c r="E208" s="4"/>
       <c r="F208" s="3" t="s">
-        <v>216</v>
+        <v>30</v>
       </c>
       <c r="G208" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H208" s="6">
-        <v>2360</v>
+        <v>2450</v>
       </c>
       <c r="I208" s="4"/>
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" s="2">
-        <v>6010000132</v>
+        <v>6010000146</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="C209" s="5">
-        <v>46614</v>
-      </c>
-      <c r="D209" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="C209" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="D209" s="5">
+        <v>46746</v>
+      </c>
+      <c r="E209" s="4"/>
+      <c r="F209" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="G209" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H209" s="6">
+        <v>140</v>
+      </c>
+      <c r="I209" s="4"/>
+    </row>
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A210" s="9">
+        <v>6010000146</v>
+      </c>
+      <c r="B210" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="C210" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E209" s="4">
-        <v>0</v>
-      </c>
-      <c r="F209" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G209" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H209" s="6">
-        <v>2450</v>
-      </c>
-      <c r="I209" s="4"/>
-    </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A210" s="15">
-        <v>6010000146</v>
-      </c>
-      <c r="B210" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="C210" s="17"/>
-      <c r="D210" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="E210" s="18">
-        <v>0</v>
-      </c>
-      <c r="F210" s="16" t="s">
-        <v>304</v>
-      </c>
-      <c r="G210" s="16" t="s">
+      <c r="D210" s="11"/>
+      <c r="E210" s="12"/>
+      <c r="F210" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="G210" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="H210" s="18"/>
-      <c r="I210" s="19">
+      <c r="H210" s="12"/>
+      <c r="I210" s="13">
         <v>480</v>
       </c>
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" s="2">
-        <v>6010000146</v>
+        <v>6010000090</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="C211" s="5">
-        <v>46746</v>
-      </c>
-      <c r="D211" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="E211" s="4">
-        <v>0</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="C211" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D211" s="5">
+        <v>46482</v>
+      </c>
+      <c r="E211" s="4"/>
       <c r="F211" s="3" t="s">
-        <v>304</v>
+        <v>169</v>
       </c>
       <c r="G211" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H211" s="6">
-        <v>140</v>
+        <v>4400</v>
       </c>
       <c r="I211" s="4"/>
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" s="2">
-        <v>6010000090</v>
+        <v>6010000199</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="C212" s="5">
-        <v>46482</v>
-      </c>
-      <c r="D212" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="E212" s="4">
-        <v>0</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="C212" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="D212" s="5">
+        <v>46556</v>
+      </c>
+      <c r="E212" s="4"/>
       <c r="F212" s="3" t="s">
-        <v>169</v>
+        <v>22</v>
       </c>
       <c r="G212" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H212" s="6">
-        <v>4420</v>
+        <v>1640</v>
       </c>
       <c r="I212" s="4"/>
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" s="2">
-        <v>6010000199</v>
+        <v>6010000133</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="C213" s="5">
-        <v>46556</v>
-      </c>
-      <c r="D213" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="E213" s="4">
-        <v>0</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="C213" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="D213" s="5">
+        <v>46388</v>
+      </c>
+      <c r="E213" s="4"/>
       <c r="F213" s="3" t="s">
-        <v>22</v>
+        <v>87</v>
       </c>
       <c r="G213" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H213" s="6">
-        <v>1640</v>
+        <v>1080</v>
       </c>
       <c r="I213" s="4"/>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" s="2">
-        <v>6010000133</v>
+        <v>6010000134</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="C214" s="5">
-        <v>46388</v>
-      </c>
-      <c r="D214" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="E214" s="4">
-        <v>0</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="C214" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="D214" s="5">
+        <v>46488</v>
+      </c>
+      <c r="E214" s="4"/>
       <c r="F214" s="3" t="s">
         <v>87</v>
       </c>
@@ -7541,26 +7121,24 @@
         <v>5</v>
       </c>
       <c r="H214" s="6">
-        <v>1080</v>
+        <v>1160</v>
       </c>
       <c r="I214" s="4"/>
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" s="2">
-        <v>6010000134</v>
+        <v>6010000135</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="C215" s="5">
-        <v>46488</v>
-      </c>
-      <c r="D215" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="E215" s="4">
-        <v>0</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="C215" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="D215" s="5">
+        <v>46388</v>
+      </c>
+      <c r="E215" s="4"/>
       <c r="F215" s="3" t="s">
         <v>87</v>
       </c>
@@ -7568,53 +7146,49 @@
         <v>5</v>
       </c>
       <c r="H215" s="6">
-        <v>1160</v>
+        <v>1560</v>
       </c>
       <c r="I215" s="4"/>
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" s="2">
-        <v>6010000135</v>
+        <v>6010000136</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="C216" s="5">
-        <v>46388</v>
-      </c>
-      <c r="D216" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="E216" s="4">
-        <v>0</v>
-      </c>
+        <v>280</v>
+      </c>
+      <c r="C216" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="D216" s="5">
+        <v>46496</v>
+      </c>
+      <c r="E216" s="4"/>
       <c r="F216" s="3" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="G216" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H216" s="6">
-        <v>1560</v>
+        <v>490</v>
       </c>
       <c r="I216" s="4"/>
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" s="2">
-        <v>6010000136</v>
+        <v>6010000137</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="C217" s="5">
+        <v>282</v>
+      </c>
+      <c r="C217" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D217" s="5">
         <v>46496</v>
       </c>
-      <c r="D217" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="E217" s="4">
-        <v>0</v>
-      </c>
+      <c r="E217" s="4"/>
       <c r="F217" s="3" t="s">
         <v>30</v>
       </c>
@@ -7622,161 +7196,149 @@
         <v>5</v>
       </c>
       <c r="H217" s="6">
-        <v>490</v>
+        <v>330</v>
       </c>
       <c r="I217" s="4"/>
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" s="2">
-        <v>6010000137</v>
+        <v>4010013269</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="C218" s="5">
-        <v>46496</v>
-      </c>
-      <c r="D218" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="E218" s="4">
-        <v>0</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="C218" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D218" s="5">
+        <v>46558</v>
+      </c>
+      <c r="E218" s="4"/>
       <c r="F218" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="G218" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H218" s="6">
-        <v>330</v>
+        <v>900</v>
       </c>
       <c r="I218" s="4"/>
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" s="2">
-        <v>4010013269</v>
+        <v>6010000177</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C219" s="5">
-        <v>46558</v>
-      </c>
-      <c r="D219" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E219" s="4">
-        <v>0</v>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="C219" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="D219" s="5">
+        <v>46971</v>
+      </c>
+      <c r="E219" s="4"/>
       <c r="F219" s="3" t="s">
-        <v>22</v>
+        <v>352</v>
       </c>
       <c r="G219" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H219" s="6">
-        <v>900</v>
+        <v>2880</v>
       </c>
       <c r="I219" s="4"/>
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" s="2">
-        <v>6010000177</v>
+        <v>6010000178</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="C220" s="5">
-        <v>46971</v>
-      </c>
-      <c r="D220" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="E220" s="4">
-        <v>0</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="C220" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="D220" s="5">
+        <v>47087</v>
+      </c>
+      <c r="E220" s="4"/>
       <c r="F220" s="3" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="G220" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H220" s="6">
-        <v>2880</v>
+        <v>990</v>
       </c>
       <c r="I220" s="4"/>
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" s="2">
-        <v>6010000178</v>
+        <v>4010013597</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="C221" s="5">
-        <v>47087</v>
-      </c>
-      <c r="D221" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="E221" s="4">
-        <v>0</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="C221" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D221" s="5">
+        <v>46525</v>
+      </c>
+      <c r="E221" s="4"/>
       <c r="F221" s="3" t="s">
-        <v>355</v>
+        <v>10</v>
       </c>
       <c r="G221" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H221" s="6">
-        <v>990</v>
+        <v>620</v>
       </c>
       <c r="I221" s="4"/>
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" s="2">
-        <v>4010013597</v>
+        <v>4010013368</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C222" s="5">
-        <v>46525</v>
-      </c>
-      <c r="D222" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E222" s="4">
-        <v>0</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="C222" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D222" s="5">
+        <v>46533</v>
+      </c>
+      <c r="E222" s="4"/>
       <c r="F222" s="3" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G222" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H222" s="6">
-        <v>620</v>
+        <v>160</v>
       </c>
       <c r="I222" s="4"/>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" s="2">
-        <v>4010013368</v>
+        <v>4010013369</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C223" s="5">
-        <v>46533</v>
-      </c>
-      <c r="D223" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E223" s="4">
-        <v>0</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="C223" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D223" s="5">
+        <v>46429</v>
+      </c>
+      <c r="E223" s="4"/>
       <c r="F223" s="3" t="s">
         <v>4</v>
       </c>
@@ -7784,7 +7346,7 @@
         <v>5</v>
       </c>
       <c r="H223" s="6">
-        <v>160</v>
+        <v>320</v>
       </c>
       <c r="I223" s="4"/>
     </row>
@@ -7795,15 +7357,13 @@
       <c r="B224" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C224" s="5">
-        <v>46429</v>
-      </c>
-      <c r="D224" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E224" s="4">
-        <v>0</v>
-      </c>
+      <c r="C224" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D224" s="5">
+        <v>46533</v>
+      </c>
+      <c r="E224" s="4"/>
       <c r="F224" s="3" t="s">
         <v>4</v>
       </c>
@@ -7811,142 +7371,130 @@
         <v>5</v>
       </c>
       <c r="H224" s="6">
-        <v>320</v>
+        <v>80</v>
       </c>
       <c r="I224" s="4"/>
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" s="2">
-        <v>4010013369</v>
+        <v>4010013399</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C225" s="5">
-        <v>46533</v>
-      </c>
-      <c r="D225" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E225" s="4">
-        <v>0</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="C225" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D225" s="5">
+        <v>46532</v>
+      </c>
+      <c r="E225" s="4"/>
       <c r="F225" s="3" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="G225" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H225" s="6">
-        <v>80</v>
+        <v>1070</v>
       </c>
       <c r="I225" s="4"/>
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" s="2">
-        <v>4010013399</v>
+        <v>6010000203</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C226" s="5">
-        <v>46532</v>
-      </c>
-      <c r="D226" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E226" s="4">
-        <v>0</v>
-      </c>
+        <v>382</v>
+      </c>
+      <c r="C226" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="D226" s="5">
+        <v>46606</v>
+      </c>
+      <c r="E226" s="4"/>
       <c r="F226" s="3" t="s">
-        <v>22</v>
+        <v>379</v>
       </c>
       <c r="G226" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H226" s="6">
-        <v>1070</v>
+        <v>430</v>
       </c>
       <c r="I226" s="4"/>
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" s="2">
-        <v>6010000203</v>
+        <v>4010013592</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="C227" s="5">
-        <v>46606</v>
-      </c>
-      <c r="D227" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="E227" s="4">
-        <v>0</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="C227" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D227" s="5">
+        <v>46514</v>
+      </c>
+      <c r="E227" s="4"/>
       <c r="F227" s="3" t="s">
-        <v>379</v>
+        <v>104</v>
       </c>
       <c r="G227" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H227" s="6">
-        <v>430</v>
+        <v>230</v>
       </c>
       <c r="I227" s="4"/>
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" s="2">
-        <v>4010013592</v>
+        <v>4010014926</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C228" s="5">
-        <v>46514</v>
-      </c>
-      <c r="D228" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E228" s="4">
-        <v>0</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="C228" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D228" s="5">
+        <v>46768</v>
+      </c>
+      <c r="E228" s="4"/>
       <c r="F228" s="3" t="s">
-        <v>104</v>
+        <v>158</v>
       </c>
       <c r="G228" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H228" s="6">
-        <v>230</v>
+        <v>780</v>
       </c>
       <c r="I228" s="4"/>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" s="2">
-        <v>4010014926</v>
+        <v>7050000020</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="C229" s="5">
-        <v>46768</v>
-      </c>
-      <c r="D229" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="E229" s="4">
-        <v>0</v>
-      </c>
+        <v>435</v>
+      </c>
+      <c r="C229" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D229" s="5"/>
+      <c r="E229" s="4"/>
       <c r="F229" s="3" t="s">
-        <v>158</v>
+        <v>2</v>
       </c>
       <c r="G229" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H229" s="6">
-        <v>780</v>
+        <v>30</v>
       </c>
       <c r="I229" s="4"/>
     </row>
@@ -7957,13 +7505,11 @@
       <c r="B230" s="3" t="s">
         <v>435</v>
       </c>
-      <c r="C230" s="5"/>
-      <c r="D230" s="3" t="s">
+      <c r="C230" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E230" s="4">
-        <v>0</v>
-      </c>
+      <c r="D230" s="5"/>
+      <c r="E230" s="4"/>
       <c r="F230" s="3" t="s">
         <v>2</v>
       </c>
@@ -7971,59 +7517,57 @@
         <v>3</v>
       </c>
       <c r="H230" s="6">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="I230" s="4"/>
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" s="2">
-        <v>7050000020</v>
+        <v>4010013659</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>435</v>
-      </c>
-      <c r="C231" s="5"/>
-      <c r="D231" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E231" s="4">
-        <v>0</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="C231" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D231" s="5">
+        <v>46526</v>
+      </c>
+      <c r="E231" s="4"/>
       <c r="F231" s="3" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G231" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H231" s="6">
-        <v>70</v>
+        <v>1270</v>
       </c>
       <c r="I231" s="4"/>
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" s="2">
-        <v>4010013659</v>
+        <v>4010013273</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="C232" s="5">
-        <v>46526</v>
-      </c>
-      <c r="D232" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="E232" s="4">
-        <v>0</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="C232" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D232" s="5">
+        <v>46444</v>
+      </c>
+      <c r="E232" s="4"/>
       <c r="F232" s="3" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="G232" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H232" s="6">
-        <v>1270</v>
+        <v>20</v>
       </c>
       <c r="I232" s="4"/>
     </row>
@@ -8034,15 +7578,13 @@
       <c r="B233" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C233" s="5">
+      <c r="C233" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D233" s="5">
         <v>46444</v>
       </c>
-      <c r="D233" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E233" s="4">
-        <v>0</v>
-      </c>
+      <c r="E233" s="4"/>
       <c r="F233" s="3" t="s">
         <v>30</v>
       </c>
@@ -8050,53 +7592,49 @@
         <v>5</v>
       </c>
       <c r="H233" s="6">
-        <v>20</v>
+        <v>710</v>
       </c>
       <c r="I233" s="4"/>
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" s="2">
-        <v>4010013273</v>
+        <v>4010013271</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C234" s="5">
-        <v>46444</v>
-      </c>
-      <c r="D234" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E234" s="4">
-        <v>0</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="C234" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D234" s="5">
+        <v>46402</v>
+      </c>
+      <c r="E234" s="4"/>
       <c r="F234" s="3" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="G234" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H234" s="6">
-        <v>710</v>
+        <v>280</v>
       </c>
       <c r="I234" s="4"/>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" s="2">
-        <v>4010013271</v>
+        <v>4010013272</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C235" s="5">
-        <v>46402</v>
-      </c>
-      <c r="D235" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E235" s="4">
-        <v>0</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="C235" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D235" s="5">
+        <v>46594</v>
+      </c>
+      <c r="E235" s="4"/>
       <c r="F235" s="3" t="s">
         <v>7</v>
       </c>
@@ -8104,7 +7642,7 @@
         <v>5</v>
       </c>
       <c r="H235" s="6">
-        <v>280</v>
+        <v>360</v>
       </c>
       <c r="I235" s="4"/>
     </row>
@@ -8115,15 +7653,13 @@
       <c r="B236" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C236" s="5">
-        <v>46594</v>
-      </c>
-      <c r="D236" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E236" s="4">
-        <v>0</v>
-      </c>
+      <c r="C236" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D236" s="5">
+        <v>46523</v>
+      </c>
+      <c r="E236" s="4"/>
       <c r="F236" s="3" t="s">
         <v>7</v>
       </c>
@@ -8131,26 +7667,24 @@
         <v>5</v>
       </c>
       <c r="H236" s="6">
-        <v>360</v>
+        <v>1100</v>
       </c>
       <c r="I236" s="4"/>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" s="2">
-        <v>4010013272</v>
+        <v>4010013663</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C237" s="5">
-        <v>46523</v>
-      </c>
-      <c r="D237" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E237" s="4">
-        <v>0</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="C237" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D237" s="5">
+        <v>46612</v>
+      </c>
+      <c r="E237" s="4"/>
       <c r="F237" s="3" t="s">
         <v>7</v>
       </c>
@@ -8158,34 +7692,32 @@
         <v>5</v>
       </c>
       <c r="H237" s="6">
-        <v>1100</v>
+        <v>1160</v>
       </c>
       <c r="I237" s="4"/>
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" s="2">
-        <v>4010013663</v>
+        <v>6010000093</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="C238" s="5">
-        <v>46612</v>
-      </c>
-      <c r="D238" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="E238" s="4">
-        <v>0</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="C238" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="D238" s="5">
+        <v>46504</v>
+      </c>
+      <c r="E238" s="4"/>
       <c r="F238" s="3" t="s">
-        <v>7</v>
+        <v>222</v>
       </c>
       <c r="G238" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H238" s="6">
-        <v>1160</v>
+        <v>15000</v>
       </c>
       <c r="I238" s="4"/>
     </row>
@@ -8196,15 +7728,13 @@
       <c r="B239" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C239" s="5">
+      <c r="C239" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="D239" s="5">
         <v>46484</v>
       </c>
-      <c r="D239" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="E239" s="4">
-        <v>0</v>
-      </c>
+      <c r="E239" s="4"/>
       <c r="F239" s="3" t="s">
         <v>222</v>
       </c>
@@ -8218,89 +7748,58 @@
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" s="2">
-        <v>6010000093</v>
+        <v>6010000161</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="C240" s="5">
-        <v>46504</v>
-      </c>
-      <c r="D240" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="E240" s="4">
-        <v>0</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="C240" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="D240" s="5">
+        <v>47087</v>
+      </c>
+      <c r="E240" s="4"/>
       <c r="F240" s="3" t="s">
-        <v>222</v>
+        <v>330</v>
       </c>
       <c r="G240" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H240" s="6">
-        <v>15000</v>
+        <v>558</v>
       </c>
       <c r="I240" s="4"/>
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" s="2">
-        <v>6010000161</v>
+        <v>6010000162</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="C241" s="5">
+        <v>331</v>
+      </c>
+      <c r="C241" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="D241" s="5">
         <v>47087</v>
       </c>
-      <c r="D241" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="E241" s="4">
-        <v>0</v>
-      </c>
+      <c r="E241" s="4"/>
       <c r="F241" s="3" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="G241" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H241" s="6">
-        <v>558</v>
+        <v>1092</v>
       </c>
       <c r="I241" s="4"/>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A242" s="2">
-        <v>6010000162</v>
-      </c>
-      <c r="B242" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="C242" s="5">
-        <v>47087</v>
-      </c>
-      <c r="D242" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="E242" s="4">
-        <v>0</v>
-      </c>
-      <c r="F242" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="G242" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H242" s="6">
-        <v>1092</v>
-      </c>
-      <c r="I242" s="4"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I242" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I242">
-      <sortCondition sortBy="fontColor" ref="B1:B242" dxfId="1"/>
+  <autoFilter ref="A1:I241" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I241">
+      <sortCondition sortBy="fontColor" ref="B1:B241" dxfId="1"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="0" type="noConversion"/>

--- a/KSTOCK.xlsx
+++ b/KSTOCK.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c2e6f8dd72a68295/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="55" documentId="11_B0E21E57C4094E9AB632FCC5BE68F68731D2BFB0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7EF7475F-5E09-4EF5-B703-668D059BD81C}"/>
+  <xr:revisionPtr revIDLastSave="69" documentId="11_E57ABE4AC4094E9AB632FCC5BE90968107E0BFB6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3245FD2F-61BC-4D31-84B3-5D849F2F4797}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -643,12 +643,12 @@
     <t>PANTAHIT IV</t>
   </si>
   <si>
+    <t>1X10ML(SWFI)</t>
+  </si>
+  <si>
     <t>NL3905003</t>
   </si>
   <si>
-    <t>1X10ML(SWFI)</t>
-  </si>
-  <si>
     <t>RANINIT INJ</t>
   </si>
   <si>
@@ -1339,9 +1339,6 @@
     <t>Item Name</t>
   </si>
   <si>
-    <t>AR No.</t>
-  </si>
-  <si>
     <t>Blocked Qty</t>
   </si>
   <si>
@@ -1354,10 +1351,13 @@
     <t>Expiry</t>
   </si>
   <si>
+    <t>Batch No.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Unrestricted Qty</t>
+  </si>
+  <si>
     <t xml:space="preserve"> Transit Qty</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Unrestricted Qty</t>
   </si>
 </sst>
 </file>
@@ -1386,7 +1386,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1402,6 +1402,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1433,17 +1439,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1461,6 +1467,21 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1476,19 +1497,19 @@
     <xf numFmtId="3" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1837,21 +1858,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I241"/>
-  <sheetFormatPr defaultColWidth="13.6640625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="39.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12" style="1" customWidth="1"/>
-    <col min="5" max="5" width="9.77734375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.77734375" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="13.6640625" style="1"/>
+    <col min="1" max="1" width="13.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="37.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.33203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10.77734375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.21875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>436</v>
       </c>
@@ -1859,72 +1880,70 @@
         <v>437</v>
       </c>
       <c r="C1" s="7" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>441</v>
+      </c>
+      <c r="E1" s="8" t="s">
         <v>438</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>442</v>
-      </c>
-      <c r="E1" s="8" t="s">
+      <c r="F1" s="8" t="s">
         <v>439</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="G1" s="8" t="s">
         <v>440</v>
       </c>
-      <c r="G1" s="7" t="s">
-        <v>441</v>
-      </c>
       <c r="H1" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="I1" s="8" t="s">
         <v>444</v>
       </c>
-      <c r="I1" s="8" t="s">
-        <v>443</v>
-      </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="14">
+      <c r="A2" s="9">
         <v>6010000232</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="10" t="s">
         <v>408</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="10" t="s">
         <v>409</v>
       </c>
-      <c r="D2" s="16">
+      <c r="D2" s="11">
         <v>46726</v>
       </c>
-      <c r="E2" s="18">
+      <c r="E2" s="13">
         <v>28400</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="H2" s="18">
-        <v>0</v>
-      </c>
-      <c r="I2" s="17"/>
+      <c r="G2" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
+      <c r="A3" s="3">
         <v>6010000095</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>225</v>
       </c>
       <c r="D3" s="5">
         <v>46559</v>
       </c>
       <c r="E3" s="4"/>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H3" s="6">
@@ -1933,23 +1952,23 @@
       <c r="I3" s="4"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
+      <c r="A4" s="3">
         <v>6010000095</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>226</v>
       </c>
       <c r="D4" s="5">
         <v>46568</v>
       </c>
       <c r="E4" s="4"/>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H4" s="6">
@@ -1958,46 +1977,46 @@
       <c r="I4" s="4"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="9">
+      <c r="A5" s="14">
         <v>6010000095</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="15" t="s">
         <v>224</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="11"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="10" t="s">
+      <c r="D5" s="16"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="H5" s="12"/>
-      <c r="I5" s="13">
+      <c r="G5" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="H5" s="17"/>
+      <c r="I5" s="18">
         <v>3600</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
+      <c r="A6" s="3">
         <v>6010000138</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>285</v>
       </c>
       <c r="D6" s="5">
         <v>46746</v>
       </c>
       <c r="E6" s="4"/>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H6" s="6">
@@ -2006,23 +2025,23 @@
       <c r="I6" s="4"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
+      <c r="A7" s="3">
         <v>4010015107</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>160</v>
       </c>
       <c r="D7" s="5">
         <v>46752</v>
       </c>
       <c r="E7" s="4"/>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H7" s="6">
@@ -2031,23 +2050,23 @@
       <c r="I7" s="4"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
+      <c r="A8" s="3">
         <v>4010013476</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>57</v>
       </c>
       <c r="D8" s="5">
         <v>46548</v>
       </c>
       <c r="E8" s="4"/>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H8" s="6">
@@ -2056,23 +2075,23 @@
       <c r="I8" s="4"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
+      <c r="A9" s="3">
         <v>6010000097</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>228</v>
       </c>
       <c r="D9" s="5">
         <v>46556</v>
       </c>
       <c r="E9" s="4"/>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H9" s="6">
@@ -2081,23 +2100,23 @@
       <c r="I9" s="4"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
+      <c r="A10" s="3">
         <v>6010000097</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="2" t="s">
         <v>230</v>
       </c>
       <c r="D10" s="5">
         <v>46751</v>
       </c>
       <c r="E10" s="4"/>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H10" s="6">
@@ -2106,23 +2125,23 @@
       <c r="I10" s="4"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
+      <c r="A11" s="3">
         <v>6010000098</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="2" t="s">
         <v>232</v>
       </c>
       <c r="D11" s="5">
         <v>46539</v>
       </c>
       <c r="E11" s="4"/>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H11" s="6">
@@ -2131,23 +2150,23 @@
       <c r="I11" s="4"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
+      <c r="A12" s="3">
         <v>6010000195</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="2" t="s">
         <v>369</v>
       </c>
       <c r="D12" s="5">
         <v>46549</v>
       </c>
       <c r="E12" s="4"/>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="G12" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H12" s="6">
@@ -2156,46 +2175,46 @@
       <c r="I12" s="4"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="9">
+      <c r="A13" s="14">
         <v>4010013259</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D13" s="11"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="10" t="s">
+      <c r="D13" s="16"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="G13" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="H13" s="12"/>
-      <c r="I13" s="13">
+      <c r="G13" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="H13" s="17"/>
+      <c r="I13" s="18">
         <v>240</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
+      <c r="A14" s="3">
         <v>4010013259</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D14" s="5">
         <v>46568</v>
       </c>
       <c r="E14" s="4"/>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="G14" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H14" s="6">
@@ -2204,46 +2223,46 @@
       <c r="I14" s="4"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="9">
+      <c r="A15" s="14">
         <v>4010013260</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D15" s="11"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="10" t="s">
+      <c r="D15" s="16"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="G15" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="H15" s="12"/>
-      <c r="I15" s="13">
+      <c r="G15" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="H15" s="17"/>
+      <c r="I15" s="18">
         <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
+      <c r="A16" s="3">
         <v>4010013260</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D16" s="5">
         <v>46568</v>
       </c>
       <c r="E16" s="4"/>
-      <c r="F16" s="3" t="s">
+      <c r="F16" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="G16" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H16" s="6">
@@ -2252,23 +2271,23 @@
       <c r="I16" s="4"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
+      <c r="A17" s="3">
         <v>4010013260</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="5">
         <v>46589</v>
       </c>
       <c r="E17" s="4"/>
-      <c r="F17" s="3" t="s">
+      <c r="F17" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="G17" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H17" s="6">
@@ -2277,23 +2296,23 @@
       <c r="I17" s="4"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
+      <c r="A18" s="3">
         <v>4010013692</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="2" t="s">
         <v>139</v>
       </c>
       <c r="D18" s="5">
         <v>46549</v>
       </c>
       <c r="E18" s="4"/>
-      <c r="F18" s="3" t="s">
+      <c r="F18" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="G18" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H18" s="6">
@@ -2302,23 +2321,23 @@
       <c r="I18" s="4"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
+      <c r="A19" s="3">
         <v>4010013693</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="2" t="s">
         <v>141</v>
       </c>
       <c r="D19" s="5">
         <v>46587</v>
       </c>
       <c r="E19" s="4"/>
-      <c r="F19" s="3" t="s">
+      <c r="F19" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="G19" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H19" s="6">
@@ -2327,23 +2346,23 @@
       <c r="I19" s="4"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
+      <c r="A20" s="3">
         <v>4010013693</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="2" t="s">
         <v>142</v>
       </c>
       <c r="D20" s="5">
         <v>46549</v>
       </c>
       <c r="E20" s="4"/>
-      <c r="F20" s="3" t="s">
+      <c r="F20" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="G20" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H20" s="6">
@@ -2352,23 +2371,23 @@
       <c r="I20" s="4"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
+      <c r="A21" s="3">
         <v>4010013578</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="2" t="s">
         <v>84</v>
       </c>
       <c r="D21" s="5">
         <v>46640</v>
       </c>
       <c r="E21" s="4"/>
-      <c r="F21" s="3" t="s">
+      <c r="F21" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="G21" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H21" s="6">
@@ -2377,23 +2396,23 @@
       <c r="I21" s="4"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
+      <c r="A22" s="3">
         <v>4010013580</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="2" t="s">
         <v>86</v>
       </c>
       <c r="D22" s="5">
         <v>46666</v>
       </c>
       <c r="E22" s="4"/>
-      <c r="F22" s="3" t="s">
+      <c r="F22" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="G22" s="3" t="s">
+      <c r="G22" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H22" s="6">
@@ -2402,23 +2421,23 @@
       <c r="I22" s="4"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
+      <c r="A23" s="3">
         <v>4010013551</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="2" t="s">
         <v>76</v>
       </c>
       <c r="D23" s="5">
         <v>46598</v>
       </c>
       <c r="E23" s="4"/>
-      <c r="F23" s="3" t="s">
+      <c r="F23" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="G23" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H23" s="6">
@@ -2427,23 +2446,23 @@
       <c r="I23" s="4"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="2">
+      <c r="A24" s="3">
         <v>4010013660</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="2" t="s">
         <v>127</v>
       </c>
       <c r="D24" s="5">
         <v>46518</v>
       </c>
       <c r="E24" s="4"/>
-      <c r="F24" s="3" t="s">
+      <c r="F24" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="G24" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H24" s="6">
@@ -2452,46 +2471,46 @@
       <c r="I24" s="4"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="9">
+      <c r="A25" s="14">
         <v>4010013694</v>
       </c>
-      <c r="B25" s="10" t="s">
+      <c r="B25" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D25" s="11"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="10" t="s">
+      <c r="D25" s="16"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="G25" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="H25" s="12"/>
-      <c r="I25" s="13">
+      <c r="G25" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="H25" s="17"/>
+      <c r="I25" s="18">
         <v>240</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="2">
+      <c r="A26" s="3">
         <v>4010013694</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="2" t="s">
         <v>144</v>
       </c>
       <c r="D26" s="5">
         <v>46536</v>
       </c>
       <c r="E26" s="4"/>
-      <c r="F26" s="3" t="s">
+      <c r="F26" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="G26" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H26" s="6">
@@ -2500,23 +2519,23 @@
       <c r="I26" s="4"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="2">
+      <c r="A27" s="3">
         <v>6010000065</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="2" t="s">
         <v>162</v>
       </c>
       <c r="D27" s="5">
         <v>46447</v>
       </c>
       <c r="E27" s="4"/>
-      <c r="F27" s="3" t="s">
+      <c r="F27" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="G27" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H27" s="6">
@@ -2525,23 +2544,23 @@
       <c r="I27" s="4"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="2">
+      <c r="A28" s="3">
         <v>4010013581</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="2" t="s">
         <v>89</v>
       </c>
       <c r="D28" s="5">
         <v>46541</v>
       </c>
       <c r="E28" s="4"/>
-      <c r="F28" s="3" t="s">
+      <c r="F28" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="G28" s="3" t="s">
+      <c r="G28" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H28" s="6">
@@ -2550,21 +2569,21 @@
       <c r="I28" s="4"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="2">
+      <c r="A29" s="3">
         <v>7050000018</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D29" s="5"/>
       <c r="E29" s="4"/>
-      <c r="F29" s="3" t="s">
+      <c r="F29" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="G29" s="3" t="s">
+      <c r="G29" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H29" s="6">
@@ -2573,21 +2592,21 @@
       <c r="I29" s="4"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
+      <c r="A30" s="3">
         <v>7050000016</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D30" s="5"/>
       <c r="E30" s="4"/>
-      <c r="F30" s="3" t="s">
+      <c r="F30" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="G30" s="3" t="s">
+      <c r="G30" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H30" s="6">
@@ -2596,21 +2615,21 @@
       <c r="I30" s="4"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
+      <c r="A31" s="3">
         <v>7050000015</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D31" s="5"/>
       <c r="E31" s="4"/>
-      <c r="F31" s="3" t="s">
+      <c r="F31" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="G31" s="3" t="s">
+      <c r="G31" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H31" s="6">
@@ -2619,21 +2638,21 @@
       <c r="I31" s="4"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="2">
+      <c r="A32" s="3">
         <v>7050000014</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D32" s="5"/>
       <c r="E32" s="4"/>
-      <c r="F32" s="3" t="s">
+      <c r="F32" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="G32" s="3" t="s">
+      <c r="G32" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H32" s="6">
@@ -2642,21 +2661,21 @@
       <c r="I32" s="4"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="2">
+      <c r="A33" s="3">
         <v>7050000017</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D33" s="5"/>
       <c r="E33" s="4"/>
-      <c r="F33" s="3" t="s">
+      <c r="F33" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="G33" s="3" t="s">
+      <c r="G33" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H33" s="6">
@@ -2665,23 +2684,23 @@
       <c r="I33" s="4"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="2">
+      <c r="A34" s="3">
         <v>4010013550</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D34" s="5">
         <v>46568</v>
       </c>
       <c r="E34" s="4"/>
-      <c r="F34" s="3" t="s">
+      <c r="F34" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G34" s="3" t="s">
+      <c r="G34" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H34" s="6">
@@ -2690,23 +2709,23 @@
       <c r="I34" s="4"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="2">
+      <c r="A35" s="3">
         <v>4010013478</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" s="2" t="s">
         <v>61</v>
       </c>
       <c r="D35" s="5">
         <v>46551</v>
       </c>
       <c r="E35" s="4"/>
-      <c r="F35" s="3" t="s">
+      <c r="F35" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G35" s="3" t="s">
+      <c r="G35" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H35" s="6">
@@ -2715,23 +2734,23 @@
       <c r="I35" s="4"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="2">
+      <c r="A36" s="3">
         <v>6010000154</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" s="2" t="s">
         <v>315</v>
       </c>
       <c r="D36" s="5">
         <v>47007</v>
       </c>
       <c r="E36" s="4"/>
-      <c r="F36" s="3" t="s">
+      <c r="F36" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="G36" s="3" t="s">
+      <c r="G36" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H36" s="6">
@@ -2740,23 +2759,23 @@
       <c r="I36" s="4"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="2">
+      <c r="A37" s="3">
         <v>6010000158</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C37" s="2" t="s">
         <v>322</v>
       </c>
       <c r="D37" s="5">
         <v>46752</v>
       </c>
       <c r="E37" s="4"/>
-      <c r="F37" s="3" t="s">
+      <c r="F37" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G37" s="3" t="s">
+      <c r="G37" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H37" s="6">
@@ -2765,23 +2784,23 @@
       <c r="I37" s="4"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="2">
+      <c r="A38" s="3">
         <v>6010000068</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" s="2" t="s">
         <v>165</v>
       </c>
       <c r="D38" s="5">
         <v>46495</v>
       </c>
       <c r="E38" s="4"/>
-      <c r="F38" s="3" t="s">
+      <c r="F38" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="G38" s="3" t="s">
+      <c r="G38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H38" s="6">
@@ -2790,23 +2809,23 @@
       <c r="I38" s="4"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="2">
+      <c r="A39" s="3">
         <v>6010000159</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C39" s="2" t="s">
         <v>324</v>
       </c>
       <c r="D39" s="5">
         <v>46780</v>
       </c>
       <c r="E39" s="4"/>
-      <c r="F39" s="3" t="s">
+      <c r="F39" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G39" s="3" t="s">
+      <c r="G39" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H39" s="6">
@@ -2815,23 +2834,23 @@
       <c r="I39" s="4"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="2">
+      <c r="A40" s="3">
         <v>6010000099</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B40" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C40" s="2" t="s">
         <v>234</v>
       </c>
       <c r="D40" s="5">
         <v>46813</v>
       </c>
       <c r="E40" s="4"/>
-      <c r="F40" s="3" t="s">
+      <c r="F40" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="G40" s="3" t="s">
+      <c r="G40" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H40" s="6">
@@ -2840,46 +2859,46 @@
       <c r="I40" s="4"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="9">
+      <c r="A41" s="14">
         <v>6010000099</v>
       </c>
-      <c r="B41" s="10" t="s">
+      <c r="B41" s="15" t="s">
         <v>233</v>
       </c>
-      <c r="C41" s="10" t="s">
+      <c r="C41" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D41" s="11"/>
-      <c r="E41" s="12"/>
-      <c r="F41" s="10" t="s">
+      <c r="D41" s="16"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="G41" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="H41" s="12"/>
-      <c r="I41" s="13">
+      <c r="G41" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="H41" s="17"/>
+      <c r="I41" s="18">
         <v>1200</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="2">
+      <c r="A42" s="3">
         <v>6010000160</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B42" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C42" s="2" t="s">
         <v>326</v>
       </c>
       <c r="D42" s="5">
         <v>46780</v>
       </c>
       <c r="E42" s="4"/>
-      <c r="F42" s="3" t="s">
+      <c r="F42" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="G42" s="3" t="s">
+      <c r="G42" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H42" s="6">
@@ -2888,23 +2907,23 @@
       <c r="I42" s="4"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" s="2">
+      <c r="A43" s="3">
         <v>6010000234</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B43" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C43" s="2" t="s">
         <v>412</v>
       </c>
       <c r="D43" s="5">
         <v>46726</v>
       </c>
       <c r="E43" s="4"/>
-      <c r="F43" s="3" t="s">
+      <c r="F43" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G43" s="3" t="s">
+      <c r="G43" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H43" s="6">
@@ -2913,23 +2932,23 @@
       <c r="I43" s="4"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="2">
+      <c r="A44" s="3">
         <v>6010000234</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B44" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C44" s="2" t="s">
         <v>413</v>
       </c>
       <c r="D44" s="5">
         <v>46661</v>
       </c>
       <c r="E44" s="4"/>
-      <c r="F44" s="3" t="s">
+      <c r="F44" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G44" s="3" t="s">
+      <c r="G44" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H44" s="6">
@@ -2938,46 +2957,46 @@
       <c r="I44" s="4"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" s="9">
+      <c r="A45" s="14">
         <v>6010000239</v>
       </c>
-      <c r="B45" s="10" t="s">
+      <c r="B45" s="15" t="s">
         <v>416</v>
       </c>
-      <c r="C45" s="10" t="s">
+      <c r="C45" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D45" s="11"/>
-      <c r="E45" s="12"/>
-      <c r="F45" s="10" t="s">
+      <c r="D45" s="16"/>
+      <c r="E45" s="17"/>
+      <c r="F45" s="15" t="s">
         <v>360</v>
       </c>
-      <c r="G45" s="10" t="s">
+      <c r="G45" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="H45" s="12"/>
-      <c r="I45" s="13">
+      <c r="H45" s="17"/>
+      <c r="I45" s="18">
         <v>810</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" s="2">
+      <c r="A46" s="3">
         <v>6010000239</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="C46" s="2" t="s">
         <v>417</v>
       </c>
       <c r="D46" s="5">
         <v>46507</v>
       </c>
       <c r="E46" s="4"/>
-      <c r="F46" s="3" t="s">
+      <c r="F46" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="G46" s="3" t="s">
+      <c r="G46" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H46" s="6">
@@ -2986,23 +3005,23 @@
       <c r="I46" s="4"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="2">
+      <c r="A47" s="3">
         <v>6010000217</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B47" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C47" s="2" t="s">
         <v>395</v>
       </c>
       <c r="D47" s="5">
         <v>46751</v>
       </c>
       <c r="E47" s="4"/>
-      <c r="F47" s="3" t="s">
+      <c r="F47" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G47" s="3" t="s">
+      <c r="G47" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H47" s="6">
@@ -3011,23 +3030,23 @@
       <c r="I47" s="4"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48" s="2">
+      <c r="A48" s="3">
         <v>6010000217</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B48" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="C48" s="2" t="s">
         <v>396</v>
       </c>
       <c r="D48" s="5">
         <v>46721</v>
       </c>
       <c r="E48" s="4"/>
-      <c r="F48" s="3" t="s">
+      <c r="F48" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G48" s="3" t="s">
+      <c r="G48" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H48" s="6">
@@ -3036,23 +3055,23 @@
       <c r="I48" s="4"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" s="2">
+      <c r="A49" s="3">
         <v>6010000070</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="B49" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C49" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D49" s="5">
         <v>46721</v>
       </c>
       <c r="E49" s="4"/>
-      <c r="F49" s="3" t="s">
+      <c r="F49" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="G49" s="3" t="s">
+      <c r="G49" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H49" s="6">
@@ -3061,23 +3080,23 @@
       <c r="I49" s="4"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" s="2">
+      <c r="A50" s="3">
         <v>6010000071</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="B50" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="C50" s="2" t="s">
         <v>171</v>
       </c>
       <c r="D50" s="5">
         <v>46797</v>
       </c>
       <c r="E50" s="4"/>
-      <c r="F50" s="3" t="s">
+      <c r="F50" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="G50" s="3" t="s">
+      <c r="G50" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H50" s="6">
@@ -3086,46 +3105,46 @@
       <c r="I50" s="4"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A51" s="9">
+      <c r="A51" s="14">
         <v>6010000071</v>
       </c>
-      <c r="B51" s="10" t="s">
+      <c r="B51" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="C51" s="10" t="s">
+      <c r="C51" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D51" s="11"/>
-      <c r="E51" s="12"/>
-      <c r="F51" s="10" t="s">
+      <c r="D51" s="16"/>
+      <c r="E51" s="17"/>
+      <c r="F51" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="G51" s="10" t="s">
+      <c r="G51" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="H51" s="12"/>
-      <c r="I51" s="13">
+      <c r="H51" s="17"/>
+      <c r="I51" s="18">
         <v>400</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A52" s="2">
+      <c r="A52" s="3">
         <v>4010013389</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="B52" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C52" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D52" s="5">
         <v>46681</v>
       </c>
       <c r="E52" s="4"/>
-      <c r="F52" s="3" t="s">
+      <c r="F52" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G52" s="3" t="s">
+      <c r="G52" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H52" s="6">
@@ -3134,48 +3153,48 @@
       <c r="I52" s="4"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A53" s="2">
+      <c r="A53" s="3">
         <v>4010013266</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="B53" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="C53" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D53" s="5">
         <v>46575</v>
       </c>
       <c r="E53" s="4"/>
-      <c r="F53" s="3" t="s">
+      <c r="F53" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G53" s="3" t="s">
+      <c r="G53" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H53" s="6">
-        <v>240</v>
+        <v>140</v>
       </c>
       <c r="I53" s="4"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A54" s="2">
+      <c r="A54" s="3">
         <v>4010013267</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="B54" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="C54" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D54" s="5">
         <v>46598</v>
       </c>
       <c r="E54" s="4"/>
-      <c r="F54" s="3" t="s">
+      <c r="F54" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G54" s="3" t="s">
+      <c r="G54" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H54" s="6">
@@ -3184,48 +3203,48 @@
       <c r="I54" s="4"/>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A55" s="2">
+      <c r="A55" s="3">
         <v>4010013553</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="B55" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="C55" s="2" t="s">
         <v>78</v>
       </c>
       <c r="D55" s="5">
         <v>46575</v>
       </c>
       <c r="E55" s="4"/>
-      <c r="F55" s="3" t="s">
+      <c r="F55" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G55" s="3" t="s">
+      <c r="G55" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H55" s="6">
-        <v>840</v>
+        <v>740</v>
       </c>
       <c r="I55" s="4"/>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A56" s="2">
+      <c r="A56" s="3">
         <v>4010013397</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="B56" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="C56" s="2" t="s">
         <v>41</v>
       </c>
       <c r="D56" s="5">
         <v>46545</v>
       </c>
       <c r="E56" s="4"/>
-      <c r="F56" s="3" t="s">
+      <c r="F56" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G56" s="3" t="s">
+      <c r="G56" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H56" s="6">
@@ -3234,23 +3253,23 @@
       <c r="I56" s="4"/>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A57" s="2">
+      <c r="A57" s="3">
         <v>6010000189</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="B57" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="C57" s="2" t="s">
         <v>357</v>
       </c>
       <c r="D57" s="5">
         <v>46539</v>
       </c>
       <c r="E57" s="4"/>
-      <c r="F57" s="3" t="s">
+      <c r="F57" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G57" s="3" t="s">
+      <c r="G57" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H57" s="6">
@@ -3259,23 +3278,23 @@
       <c r="I57" s="4"/>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A58" s="2">
+      <c r="A58" s="3">
         <v>6010000224</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="B58" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="C58" s="2" t="s">
         <v>402</v>
       </c>
       <c r="D58" s="5">
         <v>46711</v>
       </c>
       <c r="E58" s="4"/>
-      <c r="F58" s="3" t="s">
+      <c r="F58" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G58" s="3" t="s">
+      <c r="G58" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H58" s="6">
@@ -3284,46 +3303,46 @@
       <c r="I58" s="4"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" s="9">
+      <c r="A59" s="14">
         <v>6010000232</v>
       </c>
-      <c r="B59" s="10" t="s">
+      <c r="B59" s="15" t="s">
         <v>408</v>
       </c>
-      <c r="C59" s="10" t="s">
+      <c r="C59" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D59" s="11"/>
-      <c r="E59" s="12"/>
-      <c r="F59" s="10" t="s">
+      <c r="D59" s="16"/>
+      <c r="E59" s="17"/>
+      <c r="F59" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="G59" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="H59" s="12"/>
-      <c r="I59" s="13">
+      <c r="G59" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="H59" s="17"/>
+      <c r="I59" s="18">
         <v>7200</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="2">
+      <c r="A60" s="3">
         <v>6010000073</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="B60" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="C60" s="2" t="s">
         <v>174</v>
       </c>
       <c r="D60" s="5">
         <v>46511</v>
       </c>
       <c r="E60" s="4"/>
-      <c r="F60" s="3" t="s">
+      <c r="F60" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="G60" s="3" t="s">
+      <c r="G60" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H60" s="6">
@@ -3332,46 +3351,46 @@
       <c r="I60" s="4"/>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A61" s="9">
+      <c r="A61" s="14">
         <v>6010000073</v>
       </c>
-      <c r="B61" s="10" t="s">
+      <c r="B61" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="C61" s="10" t="s">
+      <c r="C61" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D61" s="11"/>
-      <c r="E61" s="12"/>
-      <c r="F61" s="10" t="s">
+      <c r="D61" s="16"/>
+      <c r="E61" s="17"/>
+      <c r="F61" s="15" t="s">
         <v>175</v>
       </c>
-      <c r="G61" s="10" t="s">
+      <c r="G61" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="H61" s="12"/>
-      <c r="I61" s="13">
+      <c r="H61" s="17"/>
+      <c r="I61" s="18">
         <v>720</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A62" s="2">
+      <c r="A62" s="3">
         <v>6010000169</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="B62" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="C62" s="3" t="s">
+      <c r="C62" s="2" t="s">
         <v>335</v>
       </c>
       <c r="D62" s="5">
         <v>46751</v>
       </c>
       <c r="E62" s="4"/>
-      <c r="F62" s="3" t="s">
+      <c r="F62" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="G62" s="3" t="s">
+      <c r="G62" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H62" s="6">
@@ -3380,23 +3399,23 @@
       <c r="I62" s="4"/>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A63" s="2">
+      <c r="A63" s="3">
         <v>6010000170</v>
       </c>
-      <c r="B63" s="3" t="s">
+      <c r="B63" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="C63" s="3" t="s">
+      <c r="C63" s="2" t="s">
         <v>337</v>
       </c>
       <c r="D63" s="5">
         <v>46721</v>
       </c>
       <c r="E63" s="4"/>
-      <c r="F63" s="3" t="s">
+      <c r="F63" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="G63" s="3" t="s">
+      <c r="G63" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H63" s="6">
@@ -3405,23 +3424,23 @@
       <c r="I63" s="4"/>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A64" s="2">
+      <c r="A64" s="3">
         <v>6010000139</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="B64" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="C64" s="2" t="s">
         <v>288</v>
       </c>
       <c r="D64" s="5">
         <v>46711</v>
       </c>
       <c r="E64" s="4"/>
-      <c r="F64" s="3" t="s">
+      <c r="F64" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="G64" s="3" t="s">
+      <c r="G64" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H64" s="6">
@@ -3430,23 +3449,23 @@
       <c r="I64" s="4"/>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A65" s="2">
+      <c r="A65" s="3">
         <v>6010000267</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="B65" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="C65" s="3" t="s">
+      <c r="C65" s="2" t="s">
         <v>426</v>
       </c>
       <c r="D65" s="5">
         <v>46813</v>
       </c>
       <c r="E65" s="4"/>
-      <c r="F65" s="3" t="s">
+      <c r="F65" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="G65" s="3" t="s">
+      <c r="G65" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H65" s="6">
@@ -3455,23 +3474,23 @@
       <c r="I65" s="4"/>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A66" s="2">
+      <c r="A66" s="3">
         <v>6010000141</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="B66" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="C66" s="3" t="s">
+      <c r="C66" s="2" t="s">
         <v>291</v>
       </c>
       <c r="D66" s="5">
         <v>46746</v>
       </c>
       <c r="E66" s="4"/>
-      <c r="F66" s="3" t="s">
+      <c r="F66" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="G66" s="3" t="s">
+      <c r="G66" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H66" s="6">
@@ -3480,46 +3499,46 @@
       <c r="I66" s="4"/>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A67" s="9">
+      <c r="A67" s="14">
         <v>6010000205</v>
       </c>
-      <c r="B67" s="10" t="s">
+      <c r="B67" s="15" t="s">
         <v>384</v>
       </c>
-      <c r="C67" s="10" t="s">
+      <c r="C67" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D67" s="11"/>
-      <c r="E67" s="12"/>
-      <c r="F67" s="10" t="s">
+      <c r="D67" s="16"/>
+      <c r="E67" s="17"/>
+      <c r="F67" s="15" t="s">
         <v>385</v>
       </c>
-      <c r="G67" s="10" t="s">
+      <c r="G67" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="H67" s="12"/>
-      <c r="I67" s="13">
+      <c r="H67" s="17"/>
+      <c r="I67" s="18">
         <v>7200</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A68" s="2">
+      <c r="A68" s="3">
         <v>6010000205</v>
       </c>
-      <c r="B68" s="3" t="s">
+      <c r="B68" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="C68" s="3" t="s">
+      <c r="C68" s="2" t="s">
         <v>386</v>
       </c>
       <c r="D68" s="5">
         <v>46692</v>
       </c>
       <c r="E68" s="4"/>
-      <c r="F68" s="3" t="s">
+      <c r="F68" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="G68" s="3" t="s">
+      <c r="G68" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H68" s="6">
@@ -3528,23 +3547,23 @@
       <c r="I68" s="4"/>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A69" s="2">
+      <c r="A69" s="3">
         <v>4010013583</v>
       </c>
-      <c r="B69" s="3" t="s">
+      <c r="B69" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="C69" s="2" t="s">
         <v>92</v>
       </c>
       <c r="D69" s="5">
         <v>46504</v>
       </c>
       <c r="E69" s="4"/>
-      <c r="F69" s="3" t="s">
+      <c r="F69" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="G69" s="3" t="s">
+      <c r="G69" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H69" s="6">
@@ -3553,23 +3572,23 @@
       <c r="I69" s="4"/>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A70" s="2">
+      <c r="A70" s="3">
         <v>6010000074</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="B70" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="C70" s="2" t="s">
         <v>177</v>
       </c>
       <c r="D70" s="5">
         <v>46721</v>
       </c>
       <c r="E70" s="4"/>
-      <c r="F70" s="3" t="s">
+      <c r="F70" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="G70" s="3" t="s">
+      <c r="G70" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H70" s="6">
@@ -3578,46 +3597,46 @@
       <c r="I70" s="4"/>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A71" s="9">
+      <c r="A71" s="14">
         <v>6010000074</v>
       </c>
-      <c r="B71" s="10" t="s">
+      <c r="B71" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="C71" s="10" t="s">
+      <c r="C71" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D71" s="11"/>
-      <c r="E71" s="12"/>
-      <c r="F71" s="10" t="s">
+      <c r="D71" s="16"/>
+      <c r="E71" s="17"/>
+      <c r="F71" s="15" t="s">
         <v>178</v>
       </c>
-      <c r="G71" s="10" t="s">
+      <c r="G71" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="H71" s="12"/>
-      <c r="I71" s="13">
+      <c r="H71" s="17"/>
+      <c r="I71" s="18">
         <v>5760</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A72" s="2">
+      <c r="A72" s="3">
         <v>6010000102</v>
       </c>
-      <c r="B72" s="3" t="s">
+      <c r="B72" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="C72" s="3" t="s">
+      <c r="C72" s="2" t="s">
         <v>236</v>
       </c>
       <c r="D72" s="5">
         <v>46780</v>
       </c>
       <c r="E72" s="4"/>
-      <c r="F72" s="3" t="s">
+      <c r="F72" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G72" s="3" t="s">
+      <c r="G72" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H72" s="6">
@@ -3626,46 +3645,46 @@
       <c r="I72" s="4"/>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A73" s="9">
+      <c r="A73" s="14">
         <v>6010000102</v>
       </c>
-      <c r="B73" s="10" t="s">
+      <c r="B73" s="15" t="s">
         <v>235</v>
       </c>
-      <c r="C73" s="10" t="s">
+      <c r="C73" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D73" s="11"/>
-      <c r="E73" s="12"/>
-      <c r="F73" s="10" t="s">
+      <c r="D73" s="16"/>
+      <c r="E73" s="17"/>
+      <c r="F73" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="G73" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="H73" s="12"/>
-      <c r="I73" s="13">
+      <c r="G73" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="H73" s="17"/>
+      <c r="I73" s="18">
         <v>1600</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A74" s="2">
+      <c r="A74" s="3">
         <v>6010000103</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="B74" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="C74" s="3" t="s">
+      <c r="C74" s="2" t="s">
         <v>238</v>
       </c>
       <c r="D74" s="5">
         <v>46645</v>
       </c>
       <c r="E74" s="4"/>
-      <c r="F74" s="3" t="s">
+      <c r="F74" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G74" s="3" t="s">
+      <c r="G74" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H74" s="6">
@@ -3674,23 +3693,23 @@
       <c r="I74" s="4"/>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A75" s="2">
+      <c r="A75" s="3">
         <v>6010000196</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="B75" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="C75" s="3" t="s">
+      <c r="C75" s="2" t="s">
         <v>371</v>
       </c>
       <c r="D75" s="5">
         <v>46606</v>
       </c>
       <c r="E75" s="4"/>
-      <c r="F75" s="3" t="s">
+      <c r="F75" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="G75" s="3" t="s">
+      <c r="G75" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H75" s="6">
@@ -3699,23 +3718,23 @@
       <c r="I75" s="4"/>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A76" s="2">
+      <c r="A76" s="3">
         <v>4010013473</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="B76" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="C76" s="2" t="s">
         <v>50</v>
       </c>
       <c r="D76" s="5">
         <v>46524</v>
       </c>
       <c r="E76" s="4"/>
-      <c r="F76" s="3" t="s">
+      <c r="F76" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G76" s="3" t="s">
+      <c r="G76" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H76" s="6">
@@ -3724,46 +3743,46 @@
       <c r="I76" s="4"/>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A77" s="9">
+      <c r="A77" s="14">
         <v>6010000150</v>
       </c>
-      <c r="B77" s="10" t="s">
+      <c r="B77" s="15" t="s">
         <v>310</v>
       </c>
-      <c r="C77" s="10" t="s">
+      <c r="C77" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D77" s="11"/>
-      <c r="E77" s="12"/>
-      <c r="F77" s="10" t="s">
+      <c r="D77" s="16"/>
+      <c r="E77" s="17"/>
+      <c r="F77" s="15" t="s">
         <v>311</v>
       </c>
-      <c r="G77" s="10" t="s">
+      <c r="G77" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="H77" s="12"/>
-      <c r="I77" s="13">
+      <c r="H77" s="17"/>
+      <c r="I77" s="18">
         <v>880</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A78" s="2">
+      <c r="A78" s="3">
         <v>6010000151</v>
       </c>
-      <c r="B78" s="3" t="s">
+      <c r="B78" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="C78" s="3" t="s">
+      <c r="C78" s="2" t="s">
         <v>313</v>
       </c>
       <c r="D78" s="5">
         <v>46692</v>
       </c>
       <c r="E78" s="4"/>
-      <c r="F78" s="3" t="s">
+      <c r="F78" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="G78" s="3" t="s">
+      <c r="G78" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H78" s="6">
@@ -3772,23 +3791,23 @@
       <c r="I78" s="4"/>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A79" s="2">
+      <c r="A79" s="3">
         <v>6010000241</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="B79" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="C79" s="2" t="s">
         <v>419</v>
       </c>
       <c r="D79" s="5">
         <v>46596</v>
       </c>
       <c r="E79" s="4"/>
-      <c r="F79" s="3" t="s">
+      <c r="F79" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="G79" s="3" t="s">
+      <c r="G79" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H79" s="6">
@@ -3797,23 +3816,23 @@
       <c r="I79" s="4"/>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A80" s="2">
+      <c r="A80" s="3">
         <v>6010000194</v>
       </c>
-      <c r="B80" s="3" t="s">
+      <c r="B80" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="C80" s="3" t="s">
+      <c r="C80" s="2" t="s">
         <v>366</v>
       </c>
       <c r="D80" s="5">
         <v>46721</v>
       </c>
       <c r="E80" s="4"/>
-      <c r="F80" s="3" t="s">
+      <c r="F80" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G80" s="3" t="s">
+      <c r="G80" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H80" s="6">
@@ -3822,23 +3841,23 @@
       <c r="I80" s="4"/>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A81" s="2">
+      <c r="A81" s="3">
         <v>6010000194</v>
       </c>
-      <c r="B81" s="3" t="s">
+      <c r="B81" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="C81" s="3" t="s">
+      <c r="C81" s="2" t="s">
         <v>367</v>
       </c>
       <c r="D81" s="5">
         <v>46803</v>
       </c>
       <c r="E81" s="4"/>
-      <c r="F81" s="3" t="s">
+      <c r="F81" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G81" s="3" t="s">
+      <c r="G81" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H81" s="6">
@@ -3847,23 +3866,23 @@
       <c r="I81" s="4"/>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A82" s="2">
+      <c r="A82" s="3">
         <v>6010000192</v>
       </c>
-      <c r="B82" s="3" t="s">
+      <c r="B82" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="C82" s="3" t="s">
+      <c r="C82" s="2" t="s">
         <v>359</v>
       </c>
       <c r="D82" s="5">
         <v>46367</v>
       </c>
       <c r="E82" s="4"/>
-      <c r="F82" s="3" t="s">
+      <c r="F82" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="G82" s="3" t="s">
+      <c r="G82" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H82" s="6">
@@ -3872,23 +3891,23 @@
       <c r="I82" s="4"/>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A83" s="2">
+      <c r="A83" s="3">
         <v>6010000155</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="B83" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="C83" s="3" t="s">
+      <c r="C83" s="2" t="s">
         <v>318</v>
       </c>
       <c r="D83" s="5">
         <v>46447</v>
       </c>
       <c r="E83" s="4"/>
-      <c r="F83" s="3" t="s">
+      <c r="F83" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G83" s="3" t="s">
+      <c r="G83" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H83" s="6">
@@ -3897,23 +3916,23 @@
       <c r="I83" s="4"/>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A84" s="2">
+      <c r="A84" s="3">
         <v>6010000108</v>
       </c>
-      <c r="B84" s="3" t="s">
+      <c r="B84" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="C84" s="3" t="s">
+      <c r="C84" s="2" t="s">
         <v>240</v>
       </c>
       <c r="D84" s="5">
         <v>46574</v>
       </c>
       <c r="E84" s="4"/>
-      <c r="F84" s="3" t="s">
+      <c r="F84" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G84" s="3" t="s">
+      <c r="G84" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H84" s="6">
@@ -3922,23 +3941,23 @@
       <c r="I84" s="4"/>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A85" s="2">
+      <c r="A85" s="3">
         <v>6010000193</v>
       </c>
-      <c r="B85" s="3" t="s">
+      <c r="B85" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="C85" s="3" t="s">
+      <c r="C85" s="2" t="s">
         <v>362</v>
       </c>
       <c r="D85" s="5">
         <v>46726</v>
       </c>
       <c r="E85" s="4"/>
-      <c r="F85" s="3" t="s">
+      <c r="F85" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G85" s="3" t="s">
+      <c r="G85" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H85" s="6">
@@ -3947,23 +3966,23 @@
       <c r="I85" s="4"/>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A86" s="2">
+      <c r="A86" s="3">
         <v>6010000193</v>
       </c>
-      <c r="B86" s="3" t="s">
+      <c r="B86" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="C86" s="3" t="s">
+      <c r="C86" s="2" t="s">
         <v>363</v>
       </c>
       <c r="D86" s="5">
         <v>46711</v>
       </c>
       <c r="E86" s="4"/>
-      <c r="F86" s="3" t="s">
+      <c r="F86" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G86" s="3" t="s">
+      <c r="G86" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H86" s="6">
@@ -3972,23 +3991,23 @@
       <c r="I86" s="4"/>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A87" s="2">
+      <c r="A87" s="3">
         <v>6010000193</v>
       </c>
-      <c r="B87" s="3" t="s">
+      <c r="B87" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="C87" s="3" t="s">
+      <c r="C87" s="2" t="s">
         <v>364</v>
       </c>
       <c r="D87" s="5">
         <v>46803</v>
       </c>
       <c r="E87" s="4"/>
-      <c r="F87" s="3" t="s">
+      <c r="F87" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G87" s="3" t="s">
+      <c r="G87" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H87" s="6">
@@ -3997,23 +4016,23 @@
       <c r="I87" s="4"/>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A88" s="2">
+      <c r="A88" s="3">
         <v>6010000216</v>
       </c>
-      <c r="B88" s="3" t="s">
+      <c r="B88" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="C88" s="3" t="s">
+      <c r="C88" s="2" t="s">
         <v>393</v>
       </c>
       <c r="D88" s="5">
         <v>46690</v>
       </c>
       <c r="E88" s="4"/>
-      <c r="F88" s="3" t="s">
+      <c r="F88" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G88" s="3" t="s">
+      <c r="G88" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H88" s="6">
@@ -4022,23 +4041,23 @@
       <c r="I88" s="4"/>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A89" s="2">
+      <c r="A89" s="3">
         <v>6010000235</v>
       </c>
-      <c r="B89" s="3" t="s">
+      <c r="B89" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="C89" s="3" t="s">
+      <c r="C89" s="2" t="s">
         <v>415</v>
       </c>
       <c r="D89" s="5">
         <v>46808</v>
       </c>
       <c r="E89" s="4"/>
-      <c r="F89" s="3" t="s">
+      <c r="F89" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G89" s="3" t="s">
+      <c r="G89" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H89" s="6">
@@ -4047,23 +4066,23 @@
       <c r="I89" s="4"/>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A90" s="2">
+      <c r="A90" s="3">
         <v>4010013662</v>
       </c>
-      <c r="B90" s="3" t="s">
+      <c r="B90" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C90" s="3" t="s">
+      <c r="C90" s="2" t="s">
         <v>129</v>
       </c>
       <c r="D90" s="5">
         <v>46546</v>
       </c>
       <c r="E90" s="4"/>
-      <c r="F90" s="3" t="s">
+      <c r="F90" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G90" s="3" t="s">
+      <c r="G90" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H90" s="6">
@@ -4072,23 +4091,23 @@
       <c r="I90" s="4"/>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A91" s="2">
+      <c r="A91" s="3">
         <v>4010013662</v>
       </c>
-      <c r="B91" s="3" t="s">
+      <c r="B91" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C91" s="3" t="s">
+      <c r="C91" s="2" t="s">
         <v>130</v>
       </c>
       <c r="D91" s="5">
         <v>46537</v>
       </c>
       <c r="E91" s="4"/>
-      <c r="F91" s="3" t="s">
+      <c r="F91" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G91" s="3" t="s">
+      <c r="G91" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H91" s="6">
@@ -4097,23 +4116,23 @@
       <c r="I91" s="4"/>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A92" s="2">
+      <c r="A92" s="3">
         <v>6010000076</v>
       </c>
-      <c r="B92" s="3" t="s">
+      <c r="B92" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C92" s="3" t="s">
+      <c r="C92" s="2" t="s">
         <v>180</v>
       </c>
       <c r="D92" s="5">
         <v>46483</v>
       </c>
       <c r="E92" s="4"/>
-      <c r="F92" s="3" t="s">
+      <c r="F92" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="G92" s="3" t="s">
+      <c r="G92" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H92" s="6">
@@ -4122,23 +4141,23 @@
       <c r="I92" s="4"/>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A93" s="2">
+      <c r="A93" s="3">
         <v>6010000110</v>
       </c>
-      <c r="B93" s="3" t="s">
+      <c r="B93" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="C93" s="3" t="s">
+      <c r="C93" s="2" t="s">
         <v>242</v>
       </c>
       <c r="D93" s="5">
         <v>46640</v>
       </c>
       <c r="E93" s="4"/>
-      <c r="F93" s="3" t="s">
+      <c r="F93" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G93" s="3" t="s">
+      <c r="G93" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H93" s="6">
@@ -4147,23 +4166,23 @@
       <c r="I93" s="4"/>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A94" s="2">
+      <c r="A94" s="3">
         <v>6010000111</v>
       </c>
-      <c r="B94" s="3" t="s">
+      <c r="B94" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="C94" s="3" t="s">
+      <c r="C94" s="2" t="s">
         <v>244</v>
       </c>
       <c r="D94" s="5">
         <v>46640</v>
       </c>
       <c r="E94" s="4"/>
-      <c r="F94" s="3" t="s">
+      <c r="F94" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G94" s="3" t="s">
+      <c r="G94" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H94" s="6">
@@ -4172,23 +4191,23 @@
       <c r="I94" s="4"/>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A95" s="2">
+      <c r="A95" s="3">
         <v>4010013584</v>
       </c>
-      <c r="B95" s="3" t="s">
+      <c r="B95" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C95" s="3" t="s">
+      <c r="C95" s="2" t="s">
         <v>94</v>
       </c>
       <c r="D95" s="5">
         <v>46532</v>
       </c>
       <c r="E95" s="4"/>
-      <c r="F95" s="3" t="s">
+      <c r="F95" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="G95" s="3" t="s">
+      <c r="G95" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H95" s="6">
@@ -4197,46 +4216,46 @@
       <c r="I95" s="4"/>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A96" s="9">
+      <c r="A96" s="14">
         <v>4010013584</v>
       </c>
-      <c r="B96" s="10" t="s">
+      <c r="B96" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="C96" s="10" t="s">
+      <c r="C96" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D96" s="11"/>
-      <c r="E96" s="12"/>
-      <c r="F96" s="10" t="s">
+      <c r="D96" s="16"/>
+      <c r="E96" s="17"/>
+      <c r="F96" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="G96" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="H96" s="12"/>
-      <c r="I96" s="13">
+      <c r="G96" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="H96" s="17"/>
+      <c r="I96" s="18">
         <v>900</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A97" s="2">
+      <c r="A97" s="3">
         <v>4010013584</v>
       </c>
-      <c r="B97" s="3" t="s">
+      <c r="B97" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C97" s="3" t="s">
+      <c r="C97" s="2" t="s">
         <v>95</v>
       </c>
       <c r="D97" s="5">
         <v>46537</v>
       </c>
       <c r="E97" s="4"/>
-      <c r="F97" s="3" t="s">
+      <c r="F97" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="G97" s="3" t="s">
+      <c r="G97" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H97" s="6">
@@ -4245,23 +4264,23 @@
       <c r="I97" s="4"/>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A98" s="2">
+      <c r="A98" s="3">
         <v>6010000171</v>
       </c>
-      <c r="B98" s="3" t="s">
+      <c r="B98" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="C98" s="3" t="s">
+      <c r="C98" s="2" t="s">
         <v>339</v>
       </c>
       <c r="D98" s="5">
         <v>46579</v>
       </c>
       <c r="E98" s="4"/>
-      <c r="F98" s="3" t="s">
+      <c r="F98" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="G98" s="3" t="s">
+      <c r="G98" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H98" s="6">
@@ -4270,23 +4289,23 @@
       <c r="I98" s="4"/>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A99" s="2">
+      <c r="A99" s="3">
         <v>4010013585</v>
       </c>
-      <c r="B99" s="3" t="s">
+      <c r="B99" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C99" s="3" t="s">
+      <c r="C99" s="2" t="s">
         <v>97</v>
       </c>
       <c r="D99" s="5">
         <v>46568</v>
       </c>
       <c r="E99" s="4"/>
-      <c r="F99" s="3" t="s">
+      <c r="F99" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="G99" s="3" t="s">
+      <c r="G99" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H99" s="6">
@@ -4295,23 +4314,23 @@
       <c r="I99" s="4"/>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A100" s="2">
+      <c r="A100" s="3">
         <v>6010000172</v>
       </c>
-      <c r="B100" s="3" t="s">
+      <c r="B100" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="C100" s="3" t="s">
+      <c r="C100" s="2" t="s">
         <v>341</v>
       </c>
       <c r="D100" s="5">
         <v>46579</v>
       </c>
       <c r="E100" s="4"/>
-      <c r="F100" s="3" t="s">
+      <c r="F100" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="G100" s="3" t="s">
+      <c r="G100" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H100" s="6">
@@ -4320,23 +4339,23 @@
       <c r="I100" s="4"/>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A101" s="2">
+      <c r="A101" s="3">
         <v>6010000077</v>
       </c>
-      <c r="B101" s="3" t="s">
+      <c r="B101" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="C101" s="3" t="s">
+      <c r="C101" s="2" t="s">
         <v>182</v>
       </c>
       <c r="D101" s="5">
         <v>46471</v>
       </c>
       <c r="E101" s="4"/>
-      <c r="F101" s="3" t="s">
+      <c r="F101" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="G101" s="3" t="s">
+      <c r="G101" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H101" s="6">
@@ -4345,46 +4364,46 @@
       <c r="I101" s="4"/>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A102" s="9">
+      <c r="A102" s="14">
         <v>6010000078</v>
       </c>
-      <c r="B102" s="10" t="s">
+      <c r="B102" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="C102" s="10" t="s">
+      <c r="C102" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D102" s="11"/>
-      <c r="E102" s="12"/>
-      <c r="F102" s="10" t="s">
+      <c r="D102" s="16"/>
+      <c r="E102" s="17"/>
+      <c r="F102" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="G102" s="10" t="s">
+      <c r="G102" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="H102" s="12"/>
-      <c r="I102" s="13">
+      <c r="H102" s="17"/>
+      <c r="I102" s="18">
         <v>125</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A103" s="2">
+      <c r="A103" s="3">
         <v>6010000078</v>
       </c>
-      <c r="B103" s="3" t="s">
+      <c r="B103" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C103" s="3" t="s">
+      <c r="C103" s="2" t="s">
         <v>186</v>
       </c>
       <c r="D103" s="5">
         <v>46780</v>
       </c>
       <c r="E103" s="4"/>
-      <c r="F103" s="3" t="s">
+      <c r="F103" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="G103" s="3" t="s">
+      <c r="G103" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H103" s="6">
@@ -4393,46 +4412,46 @@
       <c r="I103" s="4"/>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A104" s="9">
+      <c r="A104" s="14">
         <v>4010013593</v>
       </c>
-      <c r="B104" s="10" t="s">
+      <c r="B104" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="C104" s="10" t="s">
+      <c r="C104" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D104" s="11"/>
-      <c r="E104" s="12"/>
-      <c r="F104" s="10" t="s">
+      <c r="D104" s="16"/>
+      <c r="E104" s="17"/>
+      <c r="F104" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="G104" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="H104" s="12"/>
-      <c r="I104" s="13">
+      <c r="G104" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="H104" s="17"/>
+      <c r="I104" s="18">
         <v>560</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A105" s="2">
+      <c r="A105" s="3">
         <v>4010013593</v>
       </c>
-      <c r="B105" s="3" t="s">
+      <c r="B105" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C105" s="3" t="s">
+      <c r="C105" s="2" t="s">
         <v>106</v>
       </c>
       <c r="D105" s="5">
         <v>46758</v>
       </c>
       <c r="E105" s="4"/>
-      <c r="F105" s="3" t="s">
+      <c r="F105" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G105" s="3" t="s">
+      <c r="G105" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H105" s="6">
@@ -4441,23 +4460,23 @@
       <c r="I105" s="4"/>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A106" s="2">
+      <c r="A106" s="3">
         <v>4010014329</v>
       </c>
-      <c r="B106" s="3" t="s">
+      <c r="B106" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C106" s="3" t="s">
+      <c r="C106" s="2" t="s">
         <v>153</v>
       </c>
       <c r="D106" s="5">
         <v>46641</v>
       </c>
       <c r="E106" s="4"/>
-      <c r="F106" s="3" t="s">
+      <c r="F106" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G106" s="3" t="s">
+      <c r="G106" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H106" s="6">
@@ -4466,46 +4485,46 @@
       <c r="I106" s="4"/>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A107" s="9">
+      <c r="A107" s="14">
         <v>4010013594</v>
       </c>
-      <c r="B107" s="10" t="s">
+      <c r="B107" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="C107" s="10" t="s">
+      <c r="C107" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D107" s="11"/>
-      <c r="E107" s="12"/>
-      <c r="F107" s="10" t="s">
+      <c r="D107" s="16"/>
+      <c r="E107" s="17"/>
+      <c r="F107" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="G107" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="H107" s="12"/>
-      <c r="I107" s="13">
+      <c r="G107" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="H107" s="17"/>
+      <c r="I107" s="18">
         <v>1120</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A108" s="2">
+      <c r="A108" s="3">
         <v>4010013594</v>
       </c>
-      <c r="B108" s="3" t="s">
+      <c r="B108" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C108" s="3" t="s">
+      <c r="C108" s="2" t="s">
         <v>108</v>
       </c>
       <c r="D108" s="5">
         <v>46573</v>
       </c>
       <c r="E108" s="4"/>
-      <c r="F108" s="3" t="s">
+      <c r="F108" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G108" s="3" t="s">
+      <c r="G108" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H108" s="6">
@@ -4514,23 +4533,23 @@
       <c r="I108" s="4"/>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A109" s="2">
+      <c r="A109" s="3">
         <v>4010014330</v>
       </c>
-      <c r="B109" s="3" t="s">
+      <c r="B109" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="C109" s="3" t="s">
+      <c r="C109" s="2" t="s">
         <v>155</v>
       </c>
       <c r="D109" s="5">
         <v>46610</v>
       </c>
       <c r="E109" s="4"/>
-      <c r="F109" s="3" t="s">
+      <c r="F109" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G109" s="3" t="s">
+      <c r="G109" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H109" s="6">
@@ -4539,23 +4558,23 @@
       <c r="I109" s="4"/>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A110" s="2">
+      <c r="A110" s="3">
         <v>6010000156</v>
       </c>
-      <c r="B110" s="3" t="s">
+      <c r="B110" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="C110" s="3" t="s">
+      <c r="C110" s="2" t="s">
         <v>320</v>
       </c>
       <c r="D110" s="5">
         <v>46447</v>
       </c>
       <c r="E110" s="4"/>
-      <c r="F110" s="3" t="s">
+      <c r="F110" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G110" s="3" t="s">
+      <c r="G110" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H110" s="6">
@@ -4564,23 +4583,23 @@
       <c r="I110" s="4"/>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A111" s="2">
+      <c r="A111" s="3">
         <v>6010000233</v>
       </c>
-      <c r="B111" s="3" t="s">
+      <c r="B111" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="C111" s="3" t="s">
+      <c r="C111" s="2" t="s">
         <v>410</v>
       </c>
       <c r="D111" s="5">
         <v>46721</v>
       </c>
       <c r="E111" s="4"/>
-      <c r="F111" s="3" t="s">
+      <c r="F111" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G111" s="3" t="s">
+      <c r="G111" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H111" s="6">
@@ -4589,46 +4608,46 @@
       <c r="I111" s="4"/>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A112" s="9">
+      <c r="A112" s="14">
         <v>6010000233</v>
       </c>
-      <c r="B112" s="10" t="s">
+      <c r="B112" s="15" t="s">
         <v>319</v>
       </c>
-      <c r="C112" s="10" t="s">
+      <c r="C112" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D112" s="11"/>
-      <c r="E112" s="12"/>
-      <c r="F112" s="10" t="s">
+      <c r="D112" s="16"/>
+      <c r="E112" s="17"/>
+      <c r="F112" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="G112" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="H112" s="12"/>
-      <c r="I112" s="13">
+      <c r="G112" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="H112" s="17"/>
+      <c r="I112" s="18">
         <v>1350</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A113" s="2">
+      <c r="A113" s="3">
         <v>6010000080</v>
       </c>
-      <c r="B113" s="3" t="s">
+      <c r="B113" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="C113" s="3" t="s">
+      <c r="C113" s="2" t="s">
         <v>188</v>
       </c>
       <c r="D113" s="5">
         <v>46423</v>
       </c>
       <c r="E113" s="4"/>
-      <c r="F113" s="3" t="s">
+      <c r="F113" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="G113" s="3" t="s">
+      <c r="G113" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H113" s="6">
@@ -4637,23 +4656,23 @@
       <c r="I113" s="4"/>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A114" s="2">
+      <c r="A114" s="3">
         <v>6010000113</v>
       </c>
-      <c r="B114" s="3" t="s">
+      <c r="B114" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="C114" s="3" t="s">
+      <c r="C114" s="2" t="s">
         <v>246</v>
       </c>
       <c r="D114" s="5">
         <v>46598</v>
       </c>
       <c r="E114" s="4"/>
-      <c r="F114" s="3" t="s">
+      <c r="F114" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G114" s="3" t="s">
+      <c r="G114" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H114" s="6">
@@ -4662,23 +4681,23 @@
       <c r="I114" s="4"/>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A115" s="2">
+      <c r="A115" s="3">
         <v>4010013656</v>
       </c>
-      <c r="B115" s="3" t="s">
+      <c r="B115" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="C115" s="3" t="s">
+      <c r="C115" s="2" t="s">
         <v>118</v>
       </c>
       <c r="D115" s="5">
         <v>46510</v>
       </c>
       <c r="E115" s="4"/>
-      <c r="F115" s="3" t="s">
+      <c r="F115" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="G115" s="3" t="s">
+      <c r="G115" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H115" s="6">
@@ -4687,23 +4706,23 @@
       <c r="I115" s="4"/>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A116" s="2">
+      <c r="A116" s="3">
         <v>4010013595</v>
       </c>
-      <c r="B116" s="3" t="s">
+      <c r="B116" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C116" s="3" t="s">
+      <c r="C116" s="2" t="s">
         <v>110</v>
       </c>
       <c r="D116" s="5">
         <v>46623</v>
       </c>
       <c r="E116" s="4"/>
-      <c r="F116" s="3" t="s">
+      <c r="F116" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G116" s="3" t="s">
+      <c r="G116" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H116" s="6">
@@ -4712,23 +4731,23 @@
       <c r="I116" s="4"/>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A117" s="2">
+      <c r="A117" s="3">
         <v>6010000174</v>
       </c>
-      <c r="B117" s="3" t="s">
+      <c r="B117" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="C117" s="3" t="s">
+      <c r="C117" s="2" t="s">
         <v>343</v>
       </c>
       <c r="D117" s="5">
         <v>46586</v>
       </c>
       <c r="E117" s="4"/>
-      <c r="F117" s="3" t="s">
+      <c r="F117" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="G117" s="3" t="s">
+      <c r="G117" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H117" s="6">
@@ -4737,23 +4756,23 @@
       <c r="I117" s="4"/>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A118" s="2">
+      <c r="A118" s="3">
         <v>6010000114</v>
       </c>
-      <c r="B118" s="3" t="s">
+      <c r="B118" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="C118" s="3" t="s">
+      <c r="C118" s="2" t="s">
         <v>248</v>
       </c>
       <c r="D118" s="5">
         <v>46488</v>
       </c>
       <c r="E118" s="4"/>
-      <c r="F118" s="3" t="s">
+      <c r="F118" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="G118" s="3" t="s">
+      <c r="G118" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H118" s="6">
@@ -4762,23 +4781,23 @@
       <c r="I118" s="4"/>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A119" s="2">
+      <c r="A119" s="3">
         <v>6010000081</v>
       </c>
-      <c r="B119" s="3" t="s">
+      <c r="B119" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="C119" s="3" t="s">
+      <c r="C119" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D119" s="5">
         <v>46660</v>
       </c>
       <c r="E119" s="4"/>
-      <c r="F119" s="3" t="s">
+      <c r="F119" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G119" s="3" t="s">
+      <c r="G119" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H119" s="6">
@@ -4787,48 +4806,48 @@
       <c r="I119" s="4"/>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A120" s="2">
+      <c r="A120" s="3">
         <v>6010000082</v>
       </c>
-      <c r="B120" s="3" t="s">
+      <c r="B120" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="C120" s="3" t="s">
+      <c r="C120" s="2" t="s">
         <v>193</v>
       </c>
       <c r="D120" s="5">
         <v>46505</v>
       </c>
       <c r="E120" s="4"/>
-      <c r="F120" s="3" t="s">
+      <c r="F120" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="G120" s="3" t="s">
+      <c r="G120" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H120" s="6">
-        <v>11100</v>
+        <v>10600</v>
       </c>
       <c r="I120" s="4"/>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A121" s="2">
+      <c r="A121" s="3">
         <v>6010000175</v>
       </c>
-      <c r="B121" s="3" t="s">
+      <c r="B121" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="C121" s="3" t="s">
+      <c r="C121" s="2" t="s">
         <v>346</v>
       </c>
       <c r="D121" s="5">
         <v>46556</v>
       </c>
       <c r="E121" s="4"/>
-      <c r="F121" s="3" t="s">
+      <c r="F121" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="G121" s="3" t="s">
+      <c r="G121" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H121" s="6">
@@ -4837,23 +4856,23 @@
       <c r="I121" s="4"/>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A122" s="2">
+      <c r="A122" s="3">
         <v>6010000176</v>
       </c>
-      <c r="B122" s="3" t="s">
+      <c r="B122" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="C122" s="3" t="s">
+      <c r="C122" s="2" t="s">
         <v>349</v>
       </c>
       <c r="D122" s="5">
         <v>46586</v>
       </c>
       <c r="E122" s="4"/>
-      <c r="F122" s="3" t="s">
+      <c r="F122" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="G122" s="3" t="s">
+      <c r="G122" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H122" s="6">
@@ -4862,23 +4881,23 @@
       <c r="I122" s="4"/>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A123" s="2">
+      <c r="A123" s="3">
         <v>6010000201</v>
       </c>
-      <c r="B123" s="3" t="s">
+      <c r="B123" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C123" s="3" t="s">
+      <c r="C123" s="2" t="s">
         <v>378</v>
       </c>
       <c r="D123" s="5">
         <v>46624</v>
       </c>
       <c r="E123" s="4"/>
-      <c r="F123" s="3" t="s">
+      <c r="F123" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="G123" s="3" t="s">
+      <c r="G123" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H123" s="6">
@@ -4887,23 +4906,23 @@
       <c r="I123" s="4"/>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A124" s="2">
+      <c r="A124" s="3">
         <v>6010000202</v>
       </c>
-      <c r="B124" s="3" t="s">
+      <c r="B124" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="C124" s="3" t="s">
+      <c r="C124" s="2" t="s">
         <v>381</v>
       </c>
       <c r="D124" s="5">
         <v>46685</v>
       </c>
       <c r="E124" s="4"/>
-      <c r="F124" s="3" t="s">
+      <c r="F124" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="G124" s="3" t="s">
+      <c r="G124" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H124" s="6">
@@ -4912,23 +4931,23 @@
       <c r="I124" s="4"/>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A125" s="2">
+      <c r="A125" s="3">
         <v>4010013262</v>
       </c>
-      <c r="B125" s="3" t="s">
+      <c r="B125" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C125" s="3" t="s">
+      <c r="C125" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D125" s="5">
         <v>46549</v>
       </c>
       <c r="E125" s="4"/>
-      <c r="F125" s="3" t="s">
+      <c r="F125" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G125" s="3" t="s">
+      <c r="G125" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H125" s="6">
@@ -4937,96 +4956,96 @@
       <c r="I125" s="4"/>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A126" s="2">
+      <c r="A126" s="19">
         <v>4010013465</v>
       </c>
-      <c r="B126" s="3" t="s">
+      <c r="B126" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="C126" s="3" t="s">
+      <c r="C126" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="D126" s="5">
+      <c r="D126" s="21">
         <v>46637</v>
       </c>
-      <c r="E126" s="4"/>
-      <c r="F126" s="3" t="s">
+      <c r="E126" s="22"/>
+      <c r="F126" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="G126" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H126" s="6">
+      <c r="G126" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="H126" s="23">
         <v>1080</v>
       </c>
       <c r="I126" s="4"/>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A127" s="2">
+      <c r="A127" s="19">
         <v>4010013466</v>
       </c>
-      <c r="B127" s="3" t="s">
+      <c r="B127" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="C127" s="3" t="s">
+      <c r="C127" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="D127" s="5">
+      <c r="D127" s="21">
         <v>46704</v>
       </c>
-      <c r="E127" s="4"/>
-      <c r="F127" s="3" t="s">
+      <c r="E127" s="22"/>
+      <c r="F127" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="G127" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H127" s="6">
+      <c r="G127" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="H127" s="23">
         <v>80</v>
       </c>
       <c r="I127" s="4"/>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A128" s="9">
+      <c r="A128" s="14">
         <v>4010013671</v>
       </c>
-      <c r="B128" s="10" t="s">
+      <c r="B128" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="C128" s="10" t="s">
+      <c r="C128" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D128" s="11"/>
-      <c r="E128" s="12"/>
-      <c r="F128" s="10" t="s">
+      <c r="D128" s="16"/>
+      <c r="E128" s="17"/>
+      <c r="F128" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="G128" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="H128" s="12"/>
-      <c r="I128" s="13">
+      <c r="G128" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="H128" s="17"/>
+      <c r="I128" s="18">
         <v>1440</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A129" s="2">
+      <c r="A129" s="3">
         <v>4010013671</v>
       </c>
-      <c r="B129" s="3" t="s">
+      <c r="B129" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C129" s="3" t="s">
+      <c r="C129" s="2" t="s">
         <v>137</v>
       </c>
       <c r="D129" s="5">
         <v>46566</v>
       </c>
       <c r="E129" s="4"/>
-      <c r="F129" s="3" t="s">
+      <c r="F129" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G129" s="3" t="s">
+      <c r="G129" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H129" s="6">
@@ -5035,23 +5054,23 @@
       <c r="I129" s="4"/>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A130" s="2">
+      <c r="A130" s="3">
         <v>6010000252</v>
       </c>
-      <c r="B130" s="3" t="s">
+      <c r="B130" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="C130" s="3" t="s">
+      <c r="C130" s="2" t="s">
         <v>422</v>
       </c>
       <c r="D130" s="5">
         <v>46780</v>
       </c>
       <c r="E130" s="4"/>
-      <c r="F130" s="3" t="s">
+      <c r="F130" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="G130" s="3" t="s">
+      <c r="G130" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H130" s="6">
@@ -5060,23 +5079,23 @@
       <c r="I130" s="4"/>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A131" s="2">
+      <c r="A131" s="3">
         <v>6010000252</v>
       </c>
-      <c r="B131" s="3" t="s">
+      <c r="B131" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="C131" s="3" t="s">
+      <c r="C131" s="2" t="s">
         <v>424</v>
       </c>
       <c r="D131" s="5">
         <v>46661</v>
       </c>
       <c r="E131" s="4"/>
-      <c r="F131" s="3" t="s">
+      <c r="F131" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="G131" s="3" t="s">
+      <c r="G131" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H131" s="6">
@@ -5085,23 +5104,23 @@
       <c r="I131" s="4"/>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A132" s="2">
+      <c r="A132" s="3">
         <v>6010000218</v>
       </c>
-      <c r="B132" s="3" t="s">
+      <c r="B132" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="C132" s="3" t="s">
+      <c r="C132" s="2" t="s">
         <v>398</v>
       </c>
       <c r="D132" s="5">
         <v>46812</v>
       </c>
       <c r="E132" s="4"/>
-      <c r="F132" s="3" t="s">
+      <c r="F132" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="G132" s="3" t="s">
+      <c r="G132" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H132" s="6">
@@ -5110,23 +5129,23 @@
       <c r="I132" s="4"/>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A133" s="2">
+      <c r="A133" s="3">
         <v>6010000218</v>
       </c>
-      <c r="B133" s="3" t="s">
+      <c r="B133" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="C133" s="3" t="s">
+      <c r="C133" s="2" t="s">
         <v>400</v>
       </c>
       <c r="D133" s="5">
         <v>46780</v>
       </c>
       <c r="E133" s="4"/>
-      <c r="F133" s="3" t="s">
+      <c r="F133" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="G133" s="3" t="s">
+      <c r="G133" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H133" s="6">
@@ -5135,46 +5154,46 @@
       <c r="I133" s="4"/>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A134" s="9">
+      <c r="A134" s="14">
         <v>6010000083</v>
       </c>
-      <c r="B134" s="10" t="s">
+      <c r="B134" s="15" t="s">
         <v>195</v>
       </c>
-      <c r="C134" s="10" t="s">
+      <c r="C134" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D134" s="11"/>
-      <c r="E134" s="12"/>
-      <c r="F134" s="10" t="s">
+      <c r="D134" s="16"/>
+      <c r="E134" s="17"/>
+      <c r="F134" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="G134" s="10" t="s">
+      <c r="G134" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="H134" s="12"/>
-      <c r="I134" s="13">
+      <c r="H134" s="17"/>
+      <c r="I134" s="18">
         <v>300</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A135" s="2">
+      <c r="A135" s="3">
         <v>6010000083</v>
       </c>
-      <c r="B135" s="3" t="s">
+      <c r="B135" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="C135" s="3" t="s">
+      <c r="C135" s="2" t="s">
         <v>197</v>
       </c>
       <c r="D135" s="5">
         <v>46537</v>
       </c>
       <c r="E135" s="4"/>
-      <c r="F135" s="3" t="s">
+      <c r="F135" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="G135" s="3" t="s">
+      <c r="G135" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H135" s="6">
@@ -5183,23 +5202,23 @@
       <c r="I135" s="4"/>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A136" s="2">
+      <c r="A136" s="3">
         <v>6010000084</v>
       </c>
-      <c r="B136" s="3" t="s">
+      <c r="B136" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="C136" s="3" t="s">
+      <c r="C136" s="2" t="s">
         <v>199</v>
       </c>
       <c r="D136" s="5">
         <v>46711</v>
       </c>
       <c r="E136" s="4"/>
-      <c r="F136" s="3" t="s">
+      <c r="F136" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="G136" s="3" t="s">
+      <c r="G136" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H136" s="6">
@@ -5208,23 +5227,23 @@
       <c r="I136" s="4"/>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A137" s="2">
+      <c r="A137" s="3">
         <v>6010000115</v>
       </c>
-      <c r="B137" s="3" t="s">
+      <c r="B137" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="C137" s="3" t="s">
+      <c r="C137" s="2" t="s">
         <v>250</v>
       </c>
       <c r="D137" s="5">
         <v>46971</v>
       </c>
       <c r="E137" s="4"/>
-      <c r="F137" s="3" t="s">
+      <c r="F137" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G137" s="3" t="s">
+      <c r="G137" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H137" s="6">
@@ -5233,46 +5252,46 @@
       <c r="I137" s="4"/>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A138" s="9">
+      <c r="A138" s="14">
         <v>6010000116</v>
       </c>
-      <c r="B138" s="10" t="s">
+      <c r="B138" s="15" t="s">
         <v>251</v>
       </c>
-      <c r="C138" s="10" t="s">
+      <c r="C138" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D138" s="11"/>
-      <c r="E138" s="12"/>
-      <c r="F138" s="10" t="s">
+      <c r="D138" s="16"/>
+      <c r="E138" s="17"/>
+      <c r="F138" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="G138" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="H138" s="12"/>
-      <c r="I138" s="13">
+      <c r="G138" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="H138" s="17"/>
+      <c r="I138" s="18">
         <v>3600</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A139" s="2">
+      <c r="A139" s="3">
         <v>6010000116</v>
       </c>
-      <c r="B139" s="3" t="s">
+      <c r="B139" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="C139" s="3" t="s">
+      <c r="C139" s="2" t="s">
         <v>252</v>
       </c>
       <c r="D139" s="5">
         <v>46971</v>
       </c>
       <c r="E139" s="4"/>
-      <c r="F139" s="3" t="s">
+      <c r="F139" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G139" s="3" t="s">
+      <c r="G139" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H139" s="6">
@@ -5281,21 +5300,21 @@
       <c r="I139" s="4"/>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A140" s="2">
+      <c r="A140" s="3">
         <v>7050000019</v>
       </c>
-      <c r="B140" s="3" t="s">
+      <c r="B140" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="C140" s="3" t="s">
+      <c r="C140" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D140" s="5"/>
       <c r="E140" s="4"/>
-      <c r="F140" s="3" t="s">
+      <c r="F140" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G140" s="3" t="s">
+      <c r="G140" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H140" s="6">
@@ -5304,23 +5323,23 @@
       <c r="I140" s="4"/>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A141" s="2">
+      <c r="A141" s="3">
         <v>6010000117</v>
       </c>
-      <c r="B141" s="3" t="s">
+      <c r="B141" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C141" s="3" t="s">
+      <c r="C141" s="2" t="s">
         <v>254</v>
       </c>
       <c r="D141" s="5">
         <v>46711</v>
       </c>
       <c r="E141" s="4"/>
-      <c r="F141" s="3" t="s">
+      <c r="F141" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G141" s="3" t="s">
+      <c r="G141" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H141" s="6">
@@ -5329,23 +5348,23 @@
       <c r="I141" s="4"/>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A142" s="2">
+      <c r="A142" s="3">
         <v>6010000118</v>
       </c>
-      <c r="B142" s="3" t="s">
+      <c r="B142" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="C142" s="3" t="s">
+      <c r="C142" s="2" t="s">
         <v>256</v>
       </c>
       <c r="D142" s="5">
         <v>46574</v>
       </c>
       <c r="E142" s="4"/>
-      <c r="F142" s="3" t="s">
+      <c r="F142" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G142" s="3" t="s">
+      <c r="G142" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H142" s="6">
@@ -5354,23 +5373,23 @@
       <c r="I142" s="4"/>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A143" s="2">
+      <c r="A143" s="3">
         <v>6010000148</v>
       </c>
-      <c r="B143" s="3" t="s">
+      <c r="B143" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="C143" s="3" t="s">
+      <c r="C143" s="2" t="s">
         <v>309</v>
       </c>
       <c r="D143" s="5">
         <v>46751</v>
       </c>
       <c r="E143" s="4"/>
-      <c r="F143" s="3" t="s">
+      <c r="F143" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G143" s="3" t="s">
+      <c r="G143" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H143" s="6">
@@ -5379,46 +5398,46 @@
       <c r="I143" s="4"/>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A144" s="9">
+      <c r="A144" s="14">
         <v>6010000148</v>
       </c>
-      <c r="B144" s="10" t="s">
+      <c r="B144" s="15" t="s">
         <v>308</v>
       </c>
-      <c r="C144" s="10" t="s">
+      <c r="C144" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D144" s="11"/>
-      <c r="E144" s="12"/>
-      <c r="F144" s="10" t="s">
+      <c r="D144" s="16"/>
+      <c r="E144" s="17"/>
+      <c r="F144" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="G144" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="H144" s="12"/>
-      <c r="I144" s="13">
+      <c r="G144" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="H144" s="17"/>
+      <c r="I144" s="18">
         <v>20</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A145" s="2">
+      <c r="A145" s="3">
         <v>6010000119</v>
       </c>
-      <c r="B145" s="3" t="s">
+      <c r="B145" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="C145" s="3" t="s">
+      <c r="C145" s="2" t="s">
         <v>258</v>
       </c>
       <c r="D145" s="5">
         <v>46598</v>
       </c>
       <c r="E145" s="4"/>
-      <c r="F145" s="3" t="s">
+      <c r="F145" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="G145" s="3" t="s">
+      <c r="G145" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H145" s="6">
@@ -5427,23 +5446,23 @@
       <c r="I145" s="4"/>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A146" s="2">
+      <c r="A146" s="3">
         <v>6010000085</v>
       </c>
-      <c r="B146" s="3" t="s">
+      <c r="B146" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C146" s="3" t="s">
+      <c r="C146" s="2" t="s">
         <v>202</v>
       </c>
       <c r="D146" s="5">
         <v>46388</v>
       </c>
       <c r="E146" s="4"/>
-      <c r="F146" s="3" t="s">
+      <c r="F146" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="G146" s="3" t="s">
+      <c r="G146" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H146" s="6">
@@ -5452,23 +5471,23 @@
       <c r="I146" s="4"/>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A147" s="2">
+      <c r="A147" s="3">
         <v>6010000085</v>
       </c>
-      <c r="B147" s="3" t="s">
+      <c r="B147" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C147" s="3" t="s">
+      <c r="C147" s="2" t="s">
         <v>204</v>
       </c>
       <c r="D147" s="5">
         <v>46388</v>
       </c>
       <c r="E147" s="4"/>
-      <c r="F147" s="3" t="s">
+      <c r="F147" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="G147" s="3" t="s">
+      <c r="G147" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H147" s="6">
@@ -5477,23 +5496,23 @@
       <c r="I147" s="4"/>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A148" s="2">
+      <c r="A148" s="3">
         <v>6010000123</v>
       </c>
-      <c r="B148" s="3" t="s">
+      <c r="B148" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="C148" s="3" t="s">
+      <c r="C148" s="2" t="s">
         <v>261</v>
       </c>
       <c r="D148" s="5">
         <v>46752</v>
       </c>
       <c r="E148" s="4"/>
-      <c r="F148" s="3" t="s">
+      <c r="F148" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="G148" s="3" t="s">
+      <c r="G148" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H148" s="6">
@@ -5502,167 +5521,167 @@
       <c r="I148" s="4"/>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A149" s="2">
+      <c r="A149" s="19">
         <v>6010000230</v>
       </c>
-      <c r="B149" s="3" t="s">
+      <c r="B149" s="20" t="s">
         <v>406</v>
       </c>
-      <c r="C149" s="3" t="s">
+      <c r="C149" s="20" t="s">
         <v>407</v>
       </c>
-      <c r="D149" s="5">
+      <c r="D149" s="21">
         <v>46614</v>
       </c>
-      <c r="E149" s="4"/>
-      <c r="F149" s="3" t="s">
+      <c r="E149" s="22"/>
+      <c r="F149" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="G149" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H149" s="6">
+      <c r="G149" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="H149" s="23">
         <v>460</v>
       </c>
-      <c r="I149" s="4"/>
+      <c r="I149" s="22"/>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A150" s="2">
+      <c r="A150" s="14">
         <v>6010000086</v>
       </c>
-      <c r="B150" s="3" t="s">
+      <c r="B150" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="C150" s="3" t="s">
+      <c r="C150" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D150" s="16"/>
+      <c r="E150" s="17"/>
+      <c r="F150" s="15" t="s">
         <v>206</v>
       </c>
-      <c r="D150" s="5">
+      <c r="G150" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="H150" s="17"/>
+      <c r="I150" s="18">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A151" s="3">
+        <v>6010000086</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="D151" s="5">
         <v>46641</v>
       </c>
-      <c r="E150" s="4"/>
-      <c r="F150" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="G150" s="3" t="s">
+      <c r="E151" s="4"/>
+      <c r="F151" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="G151" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H150" s="6">
+      <c r="H151" s="6">
         <v>6950</v>
       </c>
-      <c r="I150" s="4"/>
-    </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A151" s="9">
-        <v>6010000086</v>
-      </c>
-      <c r="B151" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="C151" s="10" t="s">
+      <c r="I151" s="4"/>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A152" s="14">
+        <v>6010000147</v>
+      </c>
+      <c r="B152" s="15" t="s">
+        <v>306</v>
+      </c>
+      <c r="C152" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D151" s="11"/>
-      <c r="E151" s="12"/>
-      <c r="F151" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="G151" s="10" t="s">
+      <c r="D152" s="16"/>
+      <c r="E152" s="17"/>
+      <c r="F152" s="15" t="s">
+        <v>289</v>
+      </c>
+      <c r="G152" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="H151" s="12"/>
-      <c r="I151" s="13">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A152" s="2">
+      <c r="H152" s="17"/>
+      <c r="I152" s="18">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A153" s="3">
         <v>6010000147</v>
       </c>
-      <c r="B152" s="3" t="s">
+      <c r="B153" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="C152" s="3" t="s">
+      <c r="C153" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="D152" s="5">
+      <c r="D153" s="5">
         <v>46813</v>
       </c>
-      <c r="E152" s="4"/>
-      <c r="F152" s="3" t="s">
+      <c r="E153" s="4"/>
+      <c r="F153" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="G152" s="3" t="s">
+      <c r="G153" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H152" s="6">
+      <c r="H153" s="6">
         <v>670</v>
       </c>
-      <c r="I152" s="4"/>
-    </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A153" s="9">
-        <v>6010000147</v>
-      </c>
-      <c r="B153" s="10" t="s">
-        <v>306</v>
-      </c>
-      <c r="C153" s="10" t="s">
+      <c r="I153" s="4"/>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A154" s="14">
+        <v>6010000144</v>
+      </c>
+      <c r="B154" s="15" t="s">
+        <v>298</v>
+      </c>
+      <c r="C154" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D153" s="11"/>
-      <c r="E153" s="12"/>
-      <c r="F153" s="10" t="s">
+      <c r="D154" s="16"/>
+      <c r="E154" s="17"/>
+      <c r="F154" s="15" t="s">
         <v>289</v>
       </c>
-      <c r="G153" s="10" t="s">
+      <c r="G154" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="H153" s="12"/>
-      <c r="I153" s="13">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A154" s="9">
+      <c r="H154" s="17"/>
+      <c r="I154" s="18">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A155" s="3">
         <v>6010000144</v>
       </c>
-      <c r="B154" s="10" t="s">
+      <c r="B155" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="C154" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="D154" s="11"/>
-      <c r="E154" s="12"/>
-      <c r="F154" s="10" t="s">
-        <v>289</v>
-      </c>
-      <c r="G154" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="H154" s="12"/>
-      <c r="I154" s="13">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A155" s="2">
-        <v>6010000144</v>
-      </c>
-      <c r="B155" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="C155" s="3" t="s">
+      <c r="C155" s="2" t="s">
         <v>299</v>
       </c>
       <c r="D155" s="5">
         <v>46605</v>
       </c>
       <c r="E155" s="4"/>
-      <c r="F155" s="3" t="s">
+      <c r="F155" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="G155" s="3" t="s">
+      <c r="G155" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H155" s="6">
@@ -5671,23 +5690,23 @@
       <c r="I155" s="4"/>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A156" s="2">
+      <c r="A156" s="3">
         <v>6010000214</v>
       </c>
-      <c r="B156" s="3" t="s">
+      <c r="B156" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="C156" s="3" t="s">
+      <c r="C156" s="2" t="s">
         <v>388</v>
       </c>
       <c r="D156" s="5">
         <v>46692</v>
       </c>
       <c r="E156" s="4"/>
-      <c r="F156" s="3" t="s">
+      <c r="F156" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="G156" s="3" t="s">
+      <c r="G156" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H156" s="6">
@@ -5696,71 +5715,71 @@
       <c r="I156" s="4"/>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A157" s="9">
+      <c r="A157" s="14">
         <v>6010000215</v>
       </c>
-      <c r="B157" s="10" t="s">
+      <c r="B157" s="15" t="s">
         <v>389</v>
       </c>
-      <c r="C157" s="10" t="s">
+      <c r="C157" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D157" s="11"/>
-      <c r="E157" s="12"/>
-      <c r="F157" s="10" t="s">
+      <c r="D157" s="16"/>
+      <c r="E157" s="17"/>
+      <c r="F157" s="15" t="s">
         <v>390</v>
       </c>
-      <c r="G157" s="10" t="s">
+      <c r="G157" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="H157" s="12"/>
-      <c r="I157" s="13">
+      <c r="H157" s="17"/>
+      <c r="I157" s="18">
         <v>1000</v>
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A158" s="2">
+      <c r="A158" s="3">
         <v>6010000215</v>
       </c>
-      <c r="B158" s="3" t="s">
+      <c r="B158" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="C158" s="3" t="s">
+      <c r="C158" s="2" t="s">
         <v>391</v>
       </c>
       <c r="D158" s="5">
         <v>46726</v>
       </c>
       <c r="E158" s="4"/>
-      <c r="F158" s="3" t="s">
+      <c r="F158" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="G158" s="3" t="s">
+      <c r="G158" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H158" s="6">
-        <v>494</v>
+        <v>394</v>
       </c>
       <c r="I158" s="4"/>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A159" s="2">
+      <c r="A159" s="3">
         <v>6010000142</v>
       </c>
-      <c r="B159" s="3" t="s">
+      <c r="B159" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="C159" s="3" t="s">
+      <c r="C159" s="2" t="s">
         <v>293</v>
       </c>
       <c r="D159" s="5">
         <v>46610</v>
       </c>
       <c r="E159" s="4"/>
-      <c r="F159" s="3" t="s">
+      <c r="F159" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="G159" s="3" t="s">
+      <c r="G159" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H159" s="6">
@@ -5769,23 +5788,23 @@
       <c r="I159" s="4"/>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A160" s="2">
+      <c r="A160" s="3">
         <v>6010000143</v>
       </c>
-      <c r="B160" s="3" t="s">
+      <c r="B160" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="C160" s="3" t="s">
+      <c r="C160" s="2" t="s">
         <v>296</v>
       </c>
       <c r="D160" s="5">
         <v>46425</v>
       </c>
       <c r="E160" s="4"/>
-      <c r="F160" s="3" t="s">
+      <c r="F160" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="G160" s="3" t="s">
+      <c r="G160" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H160" s="6">
@@ -5794,23 +5813,23 @@
       <c r="I160" s="4"/>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A161" s="2">
+      <c r="A161" s="3">
         <v>6010000145</v>
       </c>
-      <c r="B161" s="3" t="s">
+      <c r="B161" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="C161" s="3" t="s">
+      <c r="C161" s="2" t="s">
         <v>301</v>
       </c>
       <c r="D161" s="5">
         <v>46556</v>
       </c>
       <c r="E161" s="4"/>
-      <c r="F161" s="3" t="s">
+      <c r="F161" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="G161" s="3" t="s">
+      <c r="G161" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H161" s="6">
@@ -5819,23 +5838,23 @@
       <c r="I161" s="4"/>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A162" s="2">
+      <c r="A162" s="3">
         <v>4010013596</v>
       </c>
-      <c r="B162" s="3" t="s">
+      <c r="B162" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C162" s="3" t="s">
+      <c r="C162" s="2" t="s">
         <v>112</v>
       </c>
       <c r="D162" s="5">
         <v>46446</v>
       </c>
       <c r="E162" s="4"/>
-      <c r="F162" s="3" t="s">
+      <c r="F162" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G162" s="3" t="s">
+      <c r="G162" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H162" s="6">
@@ -5844,71 +5863,71 @@
       <c r="I162" s="4"/>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A163" s="9">
+      <c r="A163" s="14">
         <v>4010013655</v>
       </c>
-      <c r="B163" s="10" t="s">
+      <c r="B163" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="C163" s="10" t="s">
+      <c r="C163" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D163" s="11"/>
-      <c r="E163" s="12"/>
-      <c r="F163" s="10" t="s">
+      <c r="D163" s="16"/>
+      <c r="E163" s="17"/>
+      <c r="F163" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="G163" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="H163" s="12"/>
-      <c r="I163" s="13">
+      <c r="G163" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="H163" s="17"/>
+      <c r="I163" s="18">
         <v>400</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A164" s="2">
+      <c r="A164" s="3">
         <v>4010013655</v>
       </c>
-      <c r="B164" s="3" t="s">
+      <c r="B164" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C164" s="3" t="s">
+      <c r="C164" s="2" t="s">
         <v>116</v>
       </c>
       <c r="D164" s="5">
         <v>46550</v>
       </c>
       <c r="E164" s="4"/>
-      <c r="F164" s="3" t="s">
+      <c r="F164" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G164" s="3" t="s">
+      <c r="G164" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H164" s="6">
-        <v>460</v>
+        <v>430</v>
       </c>
       <c r="I164" s="4"/>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A165" s="2">
+      <c r="A165" s="3">
         <v>4010013474</v>
       </c>
-      <c r="B165" s="3" t="s">
+      <c r="B165" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C165" s="3" t="s">
+      <c r="C165" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D165" s="5">
         <v>46511</v>
       </c>
       <c r="E165" s="4"/>
-      <c r="F165" s="3" t="s">
+      <c r="F165" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G165" s="3" t="s">
+      <c r="G165" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H165" s="6">
@@ -5917,23 +5936,23 @@
       <c r="I165" s="4"/>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A166" s="2">
+      <c r="A166" s="3">
         <v>4010013474</v>
       </c>
-      <c r="B166" s="3" t="s">
+      <c r="B166" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C166" s="3" t="s">
+      <c r="C166" s="2" t="s">
         <v>53</v>
       </c>
       <c r="D166" s="5">
         <v>46579</v>
       </c>
       <c r="E166" s="4"/>
-      <c r="F166" s="3" t="s">
+      <c r="F166" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G166" s="3" t="s">
+      <c r="G166" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H166" s="6">
@@ -5942,23 +5961,23 @@
       <c r="I166" s="4"/>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A167" s="2">
+      <c r="A167" s="3">
         <v>4010013475</v>
       </c>
-      <c r="B167" s="3" t="s">
+      <c r="B167" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C167" s="3" t="s">
+      <c r="C167" s="2" t="s">
         <v>55</v>
       </c>
       <c r="D167" s="5">
         <v>46525</v>
       </c>
       <c r="E167" s="4"/>
-      <c r="F167" s="3" t="s">
+      <c r="F167" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G167" s="3" t="s">
+      <c r="G167" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H167" s="6">
@@ -5967,23 +5986,23 @@
       <c r="I167" s="4"/>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A168" s="2">
+      <c r="A168" s="3">
         <v>6010000087</v>
       </c>
-      <c r="B168" s="3" t="s">
+      <c r="B168" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="C168" s="3" t="s">
+      <c r="C168" s="2" t="s">
         <v>209</v>
       </c>
       <c r="D168" s="5">
         <v>46484</v>
       </c>
       <c r="E168" s="4"/>
-      <c r="F168" s="3" t="s">
+      <c r="F168" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="G168" s="3" t="s">
+      <c r="G168" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H168" s="6">
@@ -5992,23 +6011,23 @@
       <c r="I168" s="4"/>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A169" s="2">
+      <c r="A169" s="3">
         <v>6010000087</v>
       </c>
-      <c r="B169" s="3" t="s">
+      <c r="B169" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="C169" s="3" t="s">
+      <c r="C169" s="2" t="s">
         <v>210</v>
       </c>
       <c r="D169" s="5">
         <v>46388</v>
       </c>
       <c r="E169" s="4"/>
-      <c r="F169" s="3" t="s">
+      <c r="F169" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="G169" s="3" t="s">
+      <c r="G169" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H169" s="6">
@@ -6017,46 +6036,46 @@
       <c r="I169" s="4"/>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A170" s="9">
+      <c r="A170" s="14">
         <v>6010000126</v>
       </c>
-      <c r="B170" s="10" t="s">
+      <c r="B170" s="15" t="s">
         <v>262</v>
       </c>
-      <c r="C170" s="10" t="s">
+      <c r="C170" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D170" s="11"/>
-      <c r="E170" s="12"/>
-      <c r="F170" s="10" t="s">
+      <c r="D170" s="16"/>
+      <c r="E170" s="17"/>
+      <c r="F170" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="G170" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="H170" s="12"/>
-      <c r="I170" s="13">
+      <c r="G170" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="H170" s="17"/>
+      <c r="I170" s="18">
         <v>2000</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A171" s="2">
+      <c r="A171" s="3">
         <v>6010000126</v>
       </c>
-      <c r="B171" s="3" t="s">
+      <c r="B171" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="C171" s="3" t="s">
+      <c r="C171" s="2" t="s">
         <v>263</v>
       </c>
       <c r="D171" s="5">
         <v>46780</v>
       </c>
       <c r="E171" s="4"/>
-      <c r="F171" s="3" t="s">
+      <c r="F171" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G171" s="3" t="s">
+      <c r="G171" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H171" s="6">
@@ -6065,23 +6084,23 @@
       <c r="I171" s="4"/>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A172" s="2">
+      <c r="A172" s="3">
         <v>6010000227</v>
       </c>
-      <c r="B172" s="3" t="s">
+      <c r="B172" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="C172" s="3" t="s">
+      <c r="C172" s="2" t="s">
         <v>404</v>
       </c>
       <c r="D172" s="5">
         <v>46631</v>
       </c>
       <c r="E172" s="4"/>
-      <c r="F172" s="3" t="s">
+      <c r="F172" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G172" s="3" t="s">
+      <c r="G172" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H172" s="6">
@@ -6090,46 +6109,46 @@
       <c r="I172" s="4"/>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A173" s="9">
+      <c r="A173" s="14">
         <v>6010000227</v>
       </c>
-      <c r="B173" s="10" t="s">
+      <c r="B173" s="15" t="s">
         <v>403</v>
       </c>
-      <c r="C173" s="10" t="s">
+      <c r="C173" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D173" s="11"/>
-      <c r="E173" s="12"/>
-      <c r="F173" s="10" t="s">
+      <c r="D173" s="16"/>
+      <c r="E173" s="17"/>
+      <c r="F173" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="G173" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="H173" s="12"/>
-      <c r="I173" s="13">
+      <c r="G173" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="H173" s="17"/>
+      <c r="I173" s="18">
         <v>1200</v>
       </c>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A174" s="2">
+      <c r="A174" s="3">
         <v>6010000227</v>
       </c>
-      <c r="B174" s="3" t="s">
+      <c r="B174" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="C174" s="3" t="s">
+      <c r="C174" s="2" t="s">
         <v>405</v>
       </c>
       <c r="D174" s="5">
         <v>46645</v>
       </c>
       <c r="E174" s="4"/>
-      <c r="F174" s="3" t="s">
+      <c r="F174" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G174" s="3" t="s">
+      <c r="G174" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H174" s="6">
@@ -6138,23 +6157,23 @@
       <c r="I174" s="4"/>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A175" s="2">
+      <c r="A175" s="3">
         <v>6010000088</v>
       </c>
-      <c r="B175" s="3" t="s">
+      <c r="B175" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="C175" s="3" t="s">
+      <c r="C175" s="2" t="s">
         <v>212</v>
       </c>
       <c r="D175" s="5">
         <v>46661</v>
       </c>
       <c r="E175" s="4"/>
-      <c r="F175" s="3" t="s">
+      <c r="F175" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="G175" s="3" t="s">
+      <c r="G175" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H175" s="6">
@@ -6163,23 +6182,23 @@
       <c r="I175" s="4"/>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A176" s="2">
+      <c r="A176" s="3">
         <v>4010013666</v>
       </c>
-      <c r="B176" s="3" t="s">
+      <c r="B176" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C176" s="3" t="s">
+      <c r="C176" s="2" t="s">
         <v>134</v>
       </c>
       <c r="D176" s="5">
         <v>46625</v>
       </c>
       <c r="E176" s="4"/>
-      <c r="F176" s="3" t="s">
+      <c r="F176" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G176" s="3" t="s">
+      <c r="G176" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H176" s="6">
@@ -6188,94 +6207,94 @@
       <c r="I176" s="4"/>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A177" s="9">
+      <c r="A177" s="14">
         <v>4010013666</v>
       </c>
-      <c r="B177" s="10" t="s">
+      <c r="B177" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="C177" s="10" t="s">
+      <c r="C177" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D177" s="11"/>
-      <c r="E177" s="12"/>
-      <c r="F177" s="10" t="s">
+      <c r="D177" s="16"/>
+      <c r="E177" s="17"/>
+      <c r="F177" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="G177" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="H177" s="12"/>
-      <c r="I177" s="13">
+      <c r="G177" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="H177" s="17"/>
+      <c r="I177" s="18">
         <v>200</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A178" s="2">
+      <c r="A178" s="3">
         <v>4010013666</v>
       </c>
-      <c r="B178" s="3" t="s">
+      <c r="B178" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C178" s="3" t="s">
+      <c r="C178" s="2" t="s">
         <v>135</v>
       </c>
       <c r="D178" s="5">
         <v>46593</v>
       </c>
       <c r="E178" s="4"/>
-      <c r="F178" s="3" t="s">
+      <c r="F178" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G178" s="3" t="s">
+      <c r="G178" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H178" s="6">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I178" s="4"/>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A179" s="9">
+      <c r="A179" s="14">
         <v>6010000128</v>
       </c>
-      <c r="B179" s="10" t="s">
+      <c r="B179" s="15" t="s">
         <v>264</v>
       </c>
-      <c r="C179" s="10" t="s">
+      <c r="C179" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D179" s="11"/>
-      <c r="E179" s="12"/>
-      <c r="F179" s="10" t="s">
+      <c r="D179" s="16"/>
+      <c r="E179" s="17"/>
+      <c r="F179" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="G179" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="H179" s="12"/>
-      <c r="I179" s="13">
+      <c r="G179" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="H179" s="17"/>
+      <c r="I179" s="18">
         <v>300</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A180" s="2">
+      <c r="A180" s="3">
         <v>6010000128</v>
       </c>
-      <c r="B180" s="3" t="s">
+      <c r="B180" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="C180" s="3" t="s">
+      <c r="C180" s="2" t="s">
         <v>265</v>
       </c>
       <c r="D180" s="5">
         <v>46721</v>
       </c>
       <c r="E180" s="4"/>
-      <c r="F180" s="3" t="s">
+      <c r="F180" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G180" s="3" t="s">
+      <c r="G180" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H180" s="6">
@@ -6284,119 +6303,119 @@
       <c r="I180" s="4"/>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A181" s="2">
+      <c r="A181" s="14">
         <v>6010000129</v>
       </c>
-      <c r="B181" s="3" t="s">
+      <c r="B181" s="15" t="s">
         <v>266</v>
       </c>
-      <c r="C181" s="3" t="s">
+      <c r="C181" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D181" s="16"/>
+      <c r="E181" s="17"/>
+      <c r="F181" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G181" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="H181" s="17"/>
+      <c r="I181" s="18">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A182" s="3">
+        <v>6010000129</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="C182" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="D181" s="5">
+      <c r="D182" s="5">
         <v>46758</v>
       </c>
-      <c r="E181" s="4"/>
-      <c r="F181" s="3" t="s">
+      <c r="E182" s="4"/>
+      <c r="F182" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G181" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H181" s="6">
+      <c r="G182" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H182" s="6">
         <v>590</v>
       </c>
-      <c r="I181" s="4"/>
-    </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A182" s="9">
-        <v>6010000129</v>
-      </c>
-      <c r="B182" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="C182" s="10" t="s">
+      <c r="I182" s="4"/>
+    </row>
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A183" s="14">
+        <v>6010000130</v>
+      </c>
+      <c r="B183" s="15" t="s">
+        <v>268</v>
+      </c>
+      <c r="C183" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D182" s="11"/>
-      <c r="E182" s="12"/>
-      <c r="F182" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G182" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="H182" s="12"/>
-      <c r="I182" s="13">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A183" s="2">
+      <c r="D183" s="16"/>
+      <c r="E183" s="17"/>
+      <c r="F183" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G183" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="H183" s="17"/>
+      <c r="I183" s="18">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A184" s="3">
         <v>6010000130</v>
       </c>
-      <c r="B183" s="3" t="s">
+      <c r="B184" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="C183" s="3" t="s">
+      <c r="C184" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="D183" s="5">
+      <c r="D184" s="5">
         <v>46753</v>
       </c>
-      <c r="E183" s="4"/>
-      <c r="F183" s="3" t="s">
+      <c r="E184" s="4"/>
+      <c r="F184" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G183" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H183" s="6">
+      <c r="G184" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H184" s="6">
         <v>630</v>
       </c>
-      <c r="I183" s="4"/>
-    </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A184" s="9">
-        <v>6010000130</v>
-      </c>
-      <c r="B184" s="10" t="s">
-        <v>268</v>
-      </c>
-      <c r="C184" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="D184" s="11"/>
-      <c r="E184" s="12"/>
-      <c r="F184" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="G184" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="H184" s="12"/>
-      <c r="I184" s="13">
-        <v>300</v>
-      </c>
+      <c r="I184" s="4"/>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A185" s="2">
+      <c r="A185" s="3">
         <v>6010000198</v>
       </c>
-      <c r="B185" s="3" t="s">
+      <c r="B185" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="C185" s="3" t="s">
+      <c r="C185" s="2" t="s">
         <v>374</v>
       </c>
       <c r="D185" s="5">
         <v>46568</v>
       </c>
       <c r="E185" s="4"/>
-      <c r="F185" s="3" t="s">
+      <c r="F185" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G185" s="3" t="s">
+      <c r="G185" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H185" s="6">
@@ -6405,23 +6424,23 @@
       <c r="I185" s="4"/>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A186" s="2">
+      <c r="A186" s="3">
         <v>4010013586</v>
       </c>
-      <c r="B186" s="3" t="s">
+      <c r="B186" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C186" s="3" t="s">
+      <c r="C186" s="2" t="s">
         <v>99</v>
       </c>
       <c r="D186" s="5">
         <v>46537</v>
       </c>
       <c r="E186" s="4"/>
-      <c r="F186" s="3" t="s">
+      <c r="F186" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G186" s="3" t="s">
+      <c r="G186" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H186" s="6">
@@ -6430,23 +6449,23 @@
       <c r="I186" s="4"/>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A187" s="2">
+      <c r="A187" s="3">
         <v>4010013549</v>
       </c>
-      <c r="B187" s="3" t="s">
+      <c r="B187" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C187" s="3" t="s">
+      <c r="C187" s="2" t="s">
         <v>72</v>
       </c>
       <c r="D187" s="5">
         <v>46525</v>
       </c>
       <c r="E187" s="4"/>
-      <c r="F187" s="3" t="s">
+      <c r="F187" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G187" s="3" t="s">
+      <c r="G187" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H187" s="6">
@@ -6455,23 +6474,23 @@
       <c r="I187" s="4"/>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A188" s="2">
+      <c r="A188" s="3">
         <v>4010013249</v>
       </c>
-      <c r="B188" s="3" t="s">
+      <c r="B188" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C188" s="3" t="s">
+      <c r="C188" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D188" s="5">
         <v>46442</v>
       </c>
       <c r="E188" s="4"/>
-      <c r="F188" s="3" t="s">
+      <c r="F188" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G188" s="3" t="s">
+      <c r="G188" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H188" s="6">
@@ -6480,23 +6499,23 @@
       <c r="I188" s="4"/>
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A189" s="2">
+      <c r="A189" s="3">
         <v>4010013573</v>
       </c>
-      <c r="B189" s="3" t="s">
+      <c r="B189" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C189" s="3" t="s">
+      <c r="C189" s="2" t="s">
         <v>80</v>
       </c>
       <c r="D189" s="5">
         <v>46423</v>
       </c>
       <c r="E189" s="4"/>
-      <c r="F189" s="3" t="s">
+      <c r="F189" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G189" s="3" t="s">
+      <c r="G189" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H189" s="6">
@@ -6505,23 +6524,23 @@
       <c r="I189" s="4"/>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A190" s="2">
+      <c r="A190" s="3">
         <v>4010013574</v>
       </c>
-      <c r="B190" s="3" t="s">
+      <c r="B190" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C190" s="3" t="s">
+      <c r="C190" s="2" t="s">
         <v>82</v>
       </c>
       <c r="D190" s="5">
         <v>46545</v>
       </c>
       <c r="E190" s="4"/>
-      <c r="F190" s="3" t="s">
+      <c r="F190" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G190" s="3" t="s">
+      <c r="G190" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H190" s="6">
@@ -6530,48 +6549,48 @@
       <c r="I190" s="4"/>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A191" s="2">
+      <c r="A191" s="3">
         <v>4010013588</v>
       </c>
-      <c r="B191" s="3" t="s">
+      <c r="B191" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C191" s="3" t="s">
+      <c r="C191" s="2" t="s">
         <v>101</v>
       </c>
       <c r="D191" s="5">
         <v>46582</v>
       </c>
       <c r="E191" s="4"/>
-      <c r="F191" s="3" t="s">
+      <c r="F191" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G191" s="3" t="s">
+      <c r="G191" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H191" s="6">
-        <v>2220</v>
+        <v>2020</v>
       </c>
       <c r="I191" s="4"/>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A192" s="2">
+      <c r="A192" s="3">
         <v>4010013479</v>
       </c>
-      <c r="B192" s="3" t="s">
+      <c r="B192" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C192" s="3" t="s">
+      <c r="C192" s="2" t="s">
         <v>63</v>
       </c>
       <c r="D192" s="5">
         <v>46419</v>
       </c>
       <c r="E192" s="4"/>
-      <c r="F192" s="3" t="s">
+      <c r="F192" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G192" s="3" t="s">
+      <c r="G192" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H192" s="6">
@@ -6580,23 +6599,23 @@
       <c r="I192" s="4"/>
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A193" s="2">
+      <c r="A193" s="3">
         <v>4010013479</v>
       </c>
-      <c r="B193" s="3" t="s">
+      <c r="B193" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C193" s="3" t="s">
+      <c r="C193" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D193" s="5">
         <v>46536</v>
       </c>
       <c r="E193" s="4"/>
-      <c r="F193" s="3" t="s">
+      <c r="F193" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G193" s="3" t="s">
+      <c r="G193" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H193" s="6">
@@ -6605,23 +6624,23 @@
       <c r="I193" s="4"/>
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A194" s="2">
+      <c r="A194" s="3">
         <v>4010013479</v>
       </c>
-      <c r="B194" s="3" t="s">
+      <c r="B194" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C194" s="3" t="s">
+      <c r="C194" s="2" t="s">
         <v>65</v>
       </c>
       <c r="D194" s="5">
         <v>46594</v>
       </c>
       <c r="E194" s="4"/>
-      <c r="F194" s="3" t="s">
+      <c r="F194" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G194" s="3" t="s">
+      <c r="G194" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H194" s="6">
@@ -6630,23 +6649,23 @@
       <c r="I194" s="4"/>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A195" s="2">
+      <c r="A195" s="3">
         <v>4010013700</v>
       </c>
-      <c r="B195" s="3" t="s">
+      <c r="B195" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="C195" s="3" t="s">
+      <c r="C195" s="2" t="s">
         <v>148</v>
       </c>
       <c r="D195" s="5">
         <v>46533</v>
       </c>
       <c r="E195" s="4"/>
-      <c r="F195" s="3" t="s">
+      <c r="F195" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G195" s="3" t="s">
+      <c r="G195" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H195" s="6">
@@ -6655,23 +6674,23 @@
       <c r="I195" s="4"/>
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A196" s="2">
+      <c r="A196" s="3">
         <v>4010013700</v>
       </c>
-      <c r="B196" s="3" t="s">
+      <c r="B196" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="C196" s="3" t="s">
+      <c r="C196" s="2" t="s">
         <v>149</v>
       </c>
       <c r="D196" s="5">
         <v>46446</v>
       </c>
       <c r="E196" s="4"/>
-      <c r="F196" s="3" t="s">
+      <c r="F196" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G196" s="3" t="s">
+      <c r="G196" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H196" s="6">
@@ -6680,23 +6699,23 @@
       <c r="I196" s="4"/>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A197" s="2">
+      <c r="A197" s="3">
         <v>4010013701</v>
       </c>
-      <c r="B197" s="3" t="s">
+      <c r="B197" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C197" s="3" t="s">
+      <c r="C197" s="2" t="s">
         <v>151</v>
       </c>
       <c r="D197" s="5">
         <v>46589</v>
       </c>
       <c r="E197" s="4"/>
-      <c r="F197" s="3" t="s">
+      <c r="F197" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G197" s="3" t="s">
+      <c r="G197" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H197" s="6">
@@ -6705,23 +6724,23 @@
       <c r="I197" s="4"/>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A198" s="2">
+      <c r="A198" s="3">
         <v>4010013657</v>
       </c>
-      <c r="B198" s="3" t="s">
+      <c r="B198" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C198" s="3" t="s">
+      <c r="C198" s="2" t="s">
         <v>121</v>
       </c>
       <c r="D198" s="5">
         <v>46513</v>
       </c>
       <c r="E198" s="4"/>
-      <c r="F198" s="3" t="s">
+      <c r="F198" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G198" s="3" t="s">
+      <c r="G198" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H198" s="6">
@@ -6730,46 +6749,46 @@
       <c r="I198" s="4"/>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A199" s="9">
+      <c r="A199" s="14">
         <v>4010013657</v>
       </c>
-      <c r="B199" s="10" t="s">
+      <c r="B199" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C199" s="10" t="s">
+      <c r="C199" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D199" s="11"/>
-      <c r="E199" s="12"/>
-      <c r="F199" s="10" t="s">
+      <c r="D199" s="16"/>
+      <c r="E199" s="17"/>
+      <c r="F199" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="G199" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="H199" s="12"/>
-      <c r="I199" s="13">
+      <c r="G199" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="H199" s="17"/>
+      <c r="I199" s="18">
         <v>160</v>
       </c>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A200" s="2">
+      <c r="A200" s="3">
         <v>4010013658</v>
       </c>
-      <c r="B200" s="3" t="s">
+      <c r="B200" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C200" s="3" t="s">
+      <c r="C200" s="2" t="s">
         <v>123</v>
       </c>
       <c r="D200" s="5">
         <v>46587</v>
       </c>
       <c r="E200" s="4"/>
-      <c r="F200" s="3" t="s">
+      <c r="F200" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G200" s="3" t="s">
+      <c r="G200" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H200" s="6">
@@ -6778,23 +6797,23 @@
       <c r="I200" s="4"/>
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A201" s="2">
+      <c r="A201" s="3">
         <v>4010013548</v>
       </c>
-      <c r="B201" s="3" t="s">
+      <c r="B201" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C201" s="3" t="s">
+      <c r="C201" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D201" s="5">
         <v>46469</v>
       </c>
       <c r="E201" s="4"/>
-      <c r="F201" s="3" t="s">
+      <c r="F201" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="G201" s="3" t="s">
+      <c r="G201" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H201" s="6">
@@ -6803,23 +6822,23 @@
       <c r="I201" s="4"/>
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A202" s="2">
+      <c r="A202" s="3">
         <v>4010013480</v>
       </c>
-      <c r="B202" s="3" t="s">
+      <c r="B202" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C202" s="3" t="s">
+      <c r="C202" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D202" s="5">
         <v>46408</v>
       </c>
       <c r="E202" s="4"/>
-      <c r="F202" s="3" t="s">
+      <c r="F202" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G202" s="3" t="s">
+      <c r="G202" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H202" s="6">
@@ -6828,23 +6847,23 @@
       <c r="I202" s="4"/>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A203" s="2">
+      <c r="A203" s="3">
         <v>4010013477</v>
       </c>
-      <c r="B203" s="3" t="s">
+      <c r="B203" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C203" s="3" t="s">
+      <c r="C203" s="2" t="s">
         <v>59</v>
       </c>
       <c r="D203" s="5">
         <v>46574</v>
       </c>
       <c r="E203" s="4"/>
-      <c r="F203" s="3" t="s">
+      <c r="F203" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G203" s="3" t="s">
+      <c r="G203" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H203" s="6">
@@ -6853,23 +6872,23 @@
       <c r="I203" s="4"/>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A204" s="2">
+      <c r="A204" s="3">
         <v>6010000131</v>
       </c>
-      <c r="B204" s="3" t="s">
+      <c r="B204" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="C204" s="3" t="s">
+      <c r="C204" s="2" t="s">
         <v>271</v>
       </c>
       <c r="D204" s="5">
         <v>46784</v>
       </c>
       <c r="E204" s="4"/>
-      <c r="F204" s="3" t="s">
+      <c r="F204" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G204" s="3" t="s">
+      <c r="G204" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H204" s="6">
@@ -6878,23 +6897,23 @@
       <c r="I204" s="4"/>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A205" s="2">
+      <c r="A205" s="3">
         <v>4010013699</v>
       </c>
-      <c r="B205" s="3" t="s">
+      <c r="B205" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="C205" s="3" t="s">
+      <c r="C205" s="2" t="s">
         <v>146</v>
       </c>
       <c r="D205" s="5">
         <v>46438</v>
       </c>
       <c r="E205" s="4"/>
-      <c r="F205" s="3" t="s">
+      <c r="F205" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G205" s="3" t="s">
+      <c r="G205" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H205" s="6">
@@ -6903,23 +6922,23 @@
       <c r="I205" s="4"/>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A206" s="2">
+      <c r="A206" s="3">
         <v>6010000089</v>
       </c>
-      <c r="B206" s="3" t="s">
+      <c r="B206" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="C206" s="3" t="s">
+      <c r="C206" s="2" t="s">
         <v>215</v>
       </c>
       <c r="D206" s="5">
         <v>46871</v>
       </c>
       <c r="E206" s="4"/>
-      <c r="F206" s="3" t="s">
+      <c r="F206" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="G206" s="3" t="s">
+      <c r="G206" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H206" s="6">
@@ -6928,23 +6947,23 @@
       <c r="I206" s="4"/>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A207" s="2">
+      <c r="A207" s="3">
         <v>6010000089</v>
       </c>
-      <c r="B207" s="3" t="s">
+      <c r="B207" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="C207" s="3" t="s">
+      <c r="C207" s="2" t="s">
         <v>217</v>
       </c>
       <c r="D207" s="5">
         <v>46424</v>
       </c>
       <c r="E207" s="4"/>
-      <c r="F207" s="3" t="s">
+      <c r="F207" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="G207" s="3" t="s">
+      <c r="G207" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H207" s="6">
@@ -6953,23 +6972,23 @@
       <c r="I207" s="4"/>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A208" s="2">
+      <c r="A208" s="3">
         <v>6010000132</v>
       </c>
-      <c r="B208" s="3" t="s">
+      <c r="B208" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="C208" s="3" t="s">
+      <c r="C208" s="2" t="s">
         <v>273</v>
       </c>
       <c r="D208" s="5">
         <v>46614</v>
       </c>
       <c r="E208" s="4"/>
-      <c r="F208" s="3" t="s">
+      <c r="F208" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G208" s="3" t="s">
+      <c r="G208" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H208" s="6">
@@ -6978,23 +6997,23 @@
       <c r="I208" s="4"/>
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A209" s="2">
+      <c r="A209" s="3">
         <v>6010000146</v>
       </c>
-      <c r="B209" s="3" t="s">
+      <c r="B209" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="C209" s="3" t="s">
+      <c r="C209" s="2" t="s">
         <v>304</v>
       </c>
       <c r="D209" s="5">
         <v>46746</v>
       </c>
       <c r="E209" s="4"/>
-      <c r="F209" s="3" t="s">
+      <c r="F209" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="G209" s="3" t="s">
+      <c r="G209" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H209" s="6">
@@ -7003,46 +7022,46 @@
       <c r="I209" s="4"/>
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A210" s="9">
+      <c r="A210" s="14">
         <v>6010000146</v>
       </c>
-      <c r="B210" s="10" t="s">
+      <c r="B210" s="15" t="s">
         <v>303</v>
       </c>
-      <c r="C210" s="10" t="s">
+      <c r="C210" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D210" s="11"/>
-      <c r="E210" s="12"/>
-      <c r="F210" s="10" t="s">
+      <c r="D210" s="16"/>
+      <c r="E210" s="17"/>
+      <c r="F210" s="15" t="s">
         <v>305</v>
       </c>
-      <c r="G210" s="10" t="s">
+      <c r="G210" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="H210" s="12"/>
-      <c r="I210" s="13">
+      <c r="H210" s="17"/>
+      <c r="I210" s="18">
         <v>480</v>
       </c>
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A211" s="2">
+      <c r="A211" s="3">
         <v>6010000090</v>
       </c>
-      <c r="B211" s="3" t="s">
+      <c r="B211" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="C211" s="3" t="s">
+      <c r="C211" s="2" t="s">
         <v>219</v>
       </c>
       <c r="D211" s="5">
         <v>46482</v>
       </c>
       <c r="E211" s="4"/>
-      <c r="F211" s="3" t="s">
+      <c r="F211" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="G211" s="3" t="s">
+      <c r="G211" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H211" s="6">
@@ -7051,23 +7070,23 @@
       <c r="I211" s="4"/>
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A212" s="2">
+      <c r="A212" s="3">
         <v>6010000199</v>
       </c>
-      <c r="B212" s="3" t="s">
+      <c r="B212" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="C212" s="3" t="s">
+      <c r="C212" s="2" t="s">
         <v>376</v>
       </c>
       <c r="D212" s="5">
         <v>46556</v>
       </c>
       <c r="E212" s="4"/>
-      <c r="F212" s="3" t="s">
+      <c r="F212" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G212" s="3" t="s">
+      <c r="G212" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H212" s="6">
@@ -7076,23 +7095,23 @@
       <c r="I212" s="4"/>
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A213" s="2">
+      <c r="A213" s="3">
         <v>6010000133</v>
       </c>
-      <c r="B213" s="3" t="s">
+      <c r="B213" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="C213" s="3" t="s">
+      <c r="C213" s="2" t="s">
         <v>275</v>
       </c>
       <c r="D213" s="5">
         <v>46388</v>
       </c>
       <c r="E213" s="4"/>
-      <c r="F213" s="3" t="s">
+      <c r="F213" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="G213" s="3" t="s">
+      <c r="G213" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H213" s="6">
@@ -7101,23 +7120,23 @@
       <c r="I213" s="4"/>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A214" s="2">
+      <c r="A214" s="3">
         <v>6010000134</v>
       </c>
-      <c r="B214" s="3" t="s">
+      <c r="B214" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="C214" s="3" t="s">
+      <c r="C214" s="2" t="s">
         <v>277</v>
       </c>
       <c r="D214" s="5">
         <v>46488</v>
       </c>
       <c r="E214" s="4"/>
-      <c r="F214" s="3" t="s">
+      <c r="F214" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="G214" s="3" t="s">
+      <c r="G214" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H214" s="6">
@@ -7126,23 +7145,23 @@
       <c r="I214" s="4"/>
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A215" s="2">
+      <c r="A215" s="3">
         <v>6010000135</v>
       </c>
-      <c r="B215" s="3" t="s">
+      <c r="B215" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="C215" s="3" t="s">
+      <c r="C215" s="2" t="s">
         <v>279</v>
       </c>
       <c r="D215" s="5">
         <v>46388</v>
       </c>
       <c r="E215" s="4"/>
-      <c r="F215" s="3" t="s">
+      <c r="F215" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="G215" s="3" t="s">
+      <c r="G215" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H215" s="6">
@@ -7151,23 +7170,23 @@
       <c r="I215" s="4"/>
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A216" s="2">
+      <c r="A216" s="3">
         <v>6010000136</v>
       </c>
-      <c r="B216" s="3" t="s">
+      <c r="B216" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="C216" s="3" t="s">
+      <c r="C216" s="2" t="s">
         <v>281</v>
       </c>
       <c r="D216" s="5">
         <v>46496</v>
       </c>
       <c r="E216" s="4"/>
-      <c r="F216" s="3" t="s">
+      <c r="F216" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G216" s="3" t="s">
+      <c r="G216" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H216" s="6">
@@ -7176,23 +7195,23 @@
       <c r="I216" s="4"/>
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A217" s="2">
+      <c r="A217" s="3">
         <v>6010000137</v>
       </c>
-      <c r="B217" s="3" t="s">
+      <c r="B217" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="C217" s="3" t="s">
+      <c r="C217" s="2" t="s">
         <v>283</v>
       </c>
       <c r="D217" s="5">
         <v>46496</v>
       </c>
       <c r="E217" s="4"/>
-      <c r="F217" s="3" t="s">
+      <c r="F217" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G217" s="3" t="s">
+      <c r="G217" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H217" s="6">
@@ -7201,23 +7220,23 @@
       <c r="I217" s="4"/>
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A218" s="2">
+      <c r="A218" s="3">
         <v>4010013269</v>
       </c>
-      <c r="B218" s="3" t="s">
+      <c r="B218" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C218" s="3" t="s">
+      <c r="C218" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D218" s="5">
         <v>46558</v>
       </c>
       <c r="E218" s="4"/>
-      <c r="F218" s="3" t="s">
+      <c r="F218" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G218" s="3" t="s">
+      <c r="G218" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H218" s="6">
@@ -7226,23 +7245,23 @@
       <c r="I218" s="4"/>
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A219" s="2">
+      <c r="A219" s="3">
         <v>6010000177</v>
       </c>
-      <c r="B219" s="3" t="s">
+      <c r="B219" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="C219" s="3" t="s">
+      <c r="C219" s="2" t="s">
         <v>351</v>
       </c>
       <c r="D219" s="5">
         <v>46971</v>
       </c>
       <c r="E219" s="4"/>
-      <c r="F219" s="3" t="s">
+      <c r="F219" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="G219" s="3" t="s">
+      <c r="G219" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H219" s="6">
@@ -7251,23 +7270,23 @@
       <c r="I219" s="4"/>
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A220" s="2">
+      <c r="A220" s="3">
         <v>6010000178</v>
       </c>
-      <c r="B220" s="3" t="s">
+      <c r="B220" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="C220" s="3" t="s">
+      <c r="C220" s="2" t="s">
         <v>354</v>
       </c>
       <c r="D220" s="5">
         <v>47087</v>
       </c>
       <c r="E220" s="4"/>
-      <c r="F220" s="3" t="s">
+      <c r="F220" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="G220" s="3" t="s">
+      <c r="G220" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H220" s="6">
@@ -7276,23 +7295,23 @@
       <c r="I220" s="4"/>
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A221" s="2">
+      <c r="A221" s="3">
         <v>4010013597</v>
       </c>
-      <c r="B221" s="3" t="s">
+      <c r="B221" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C221" s="3" t="s">
+      <c r="C221" s="2" t="s">
         <v>114</v>
       </c>
       <c r="D221" s="5">
         <v>46525</v>
       </c>
       <c r="E221" s="4"/>
-      <c r="F221" s="3" t="s">
+      <c r="F221" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G221" s="3" t="s">
+      <c r="G221" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H221" s="6">
@@ -7301,23 +7320,23 @@
       <c r="I221" s="4"/>
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A222" s="2">
+      <c r="A222" s="3">
         <v>4010013368</v>
       </c>
-      <c r="B222" s="3" t="s">
+      <c r="B222" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C222" s="3" t="s">
+      <c r="C222" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D222" s="5">
         <v>46533</v>
       </c>
       <c r="E222" s="4"/>
-      <c r="F222" s="3" t="s">
+      <c r="F222" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G222" s="3" t="s">
+      <c r="G222" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H222" s="6">
@@ -7326,23 +7345,23 @@
       <c r="I222" s="4"/>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A223" s="2">
+      <c r="A223" s="3">
         <v>4010013369</v>
       </c>
-      <c r="B223" s="3" t="s">
+      <c r="B223" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C223" s="3" t="s">
+      <c r="C223" s="2" t="s">
         <v>35</v>
       </c>
       <c r="D223" s="5">
         <v>46429</v>
       </c>
       <c r="E223" s="4"/>
-      <c r="F223" s="3" t="s">
+      <c r="F223" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G223" s="3" t="s">
+      <c r="G223" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H223" s="6">
@@ -7351,23 +7370,23 @@
       <c r="I223" s="4"/>
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A224" s="2">
+      <c r="A224" s="3">
         <v>4010013369</v>
       </c>
-      <c r="B224" s="3" t="s">
+      <c r="B224" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C224" s="3" t="s">
+      <c r="C224" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D224" s="5">
         <v>46533</v>
       </c>
       <c r="E224" s="4"/>
-      <c r="F224" s="3" t="s">
+      <c r="F224" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G224" s="3" t="s">
+      <c r="G224" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H224" s="6">
@@ -7376,23 +7395,23 @@
       <c r="I224" s="4"/>
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A225" s="2">
+      <c r="A225" s="3">
         <v>4010013399</v>
       </c>
-      <c r="B225" s="3" t="s">
+      <c r="B225" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C225" s="3" t="s">
+      <c r="C225" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D225" s="5">
         <v>46532</v>
       </c>
       <c r="E225" s="4"/>
-      <c r="F225" s="3" t="s">
+      <c r="F225" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G225" s="3" t="s">
+      <c r="G225" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H225" s="6">
@@ -7401,23 +7420,23 @@
       <c r="I225" s="4"/>
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A226" s="2">
+      <c r="A226" s="3">
         <v>6010000203</v>
       </c>
-      <c r="B226" s="3" t="s">
+      <c r="B226" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="C226" s="3" t="s">
+      <c r="C226" s="2" t="s">
         <v>383</v>
       </c>
       <c r="D226" s="5">
         <v>46606</v>
       </c>
       <c r="E226" s="4"/>
-      <c r="F226" s="3" t="s">
+      <c r="F226" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="G226" s="3" t="s">
+      <c r="G226" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H226" s="6">
@@ -7426,23 +7445,23 @@
       <c r="I226" s="4"/>
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A227" s="2">
+      <c r="A227" s="3">
         <v>4010013592</v>
       </c>
-      <c r="B227" s="3" t="s">
+      <c r="B227" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C227" s="3" t="s">
+      <c r="C227" s="2" t="s">
         <v>103</v>
       </c>
       <c r="D227" s="5">
         <v>46514</v>
       </c>
       <c r="E227" s="4"/>
-      <c r="F227" s="3" t="s">
+      <c r="F227" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="G227" s="3" t="s">
+      <c r="G227" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H227" s="6">
@@ -7451,23 +7470,23 @@
       <c r="I227" s="4"/>
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A228" s="2">
+      <c r="A228" s="3">
         <v>4010014926</v>
       </c>
-      <c r="B228" s="3" t="s">
+      <c r="B228" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="C228" s="3" t="s">
+      <c r="C228" s="2" t="s">
         <v>157</v>
       </c>
       <c r="D228" s="5">
         <v>46768</v>
       </c>
       <c r="E228" s="4"/>
-      <c r="F228" s="3" t="s">
+      <c r="F228" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="G228" s="3" t="s">
+      <c r="G228" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H228" s="6">
@@ -7476,21 +7495,21 @@
       <c r="I228" s="4"/>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A229" s="2">
+      <c r="A229" s="3">
         <v>7050000020</v>
       </c>
-      <c r="B229" s="3" t="s">
+      <c r="B229" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="C229" s="3" t="s">
+      <c r="C229" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D229" s="5"/>
       <c r="E229" s="4"/>
-      <c r="F229" s="3" t="s">
+      <c r="F229" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G229" s="3" t="s">
+      <c r="G229" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H229" s="6">
@@ -7499,21 +7518,21 @@
       <c r="I229" s="4"/>
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A230" s="2">
+      <c r="A230" s="3">
         <v>7050000020</v>
       </c>
-      <c r="B230" s="3" t="s">
+      <c r="B230" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="C230" s="3" t="s">
+      <c r="C230" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D230" s="5"/>
       <c r="E230" s="4"/>
-      <c r="F230" s="3" t="s">
+      <c r="F230" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G230" s="3" t="s">
+      <c r="G230" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H230" s="6">
@@ -7522,23 +7541,23 @@
       <c r="I230" s="4"/>
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A231" s="2">
+      <c r="A231" s="3">
         <v>4010013659</v>
       </c>
-      <c r="B231" s="3" t="s">
+      <c r="B231" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C231" s="3" t="s">
+      <c r="C231" s="2" t="s">
         <v>125</v>
       </c>
       <c r="D231" s="5">
         <v>46526</v>
       </c>
       <c r="E231" s="4"/>
-      <c r="F231" s="3" t="s">
+      <c r="F231" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G231" s="3" t="s">
+      <c r="G231" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H231" s="6">
@@ -7547,23 +7566,23 @@
       <c r="I231" s="4"/>
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A232" s="2">
+      <c r="A232" s="3">
         <v>4010013273</v>
       </c>
-      <c r="B232" s="3" t="s">
+      <c r="B232" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C232" s="3" t="s">
+      <c r="C232" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D232" s="5">
         <v>46444</v>
       </c>
       <c r="E232" s="4"/>
-      <c r="F232" s="3" t="s">
+      <c r="F232" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G232" s="3" t="s">
+      <c r="G232" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H232" s="6">
@@ -7572,23 +7591,23 @@
       <c r="I232" s="4"/>
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A233" s="2">
+      <c r="A233" s="3">
         <v>4010013273</v>
       </c>
-      <c r="B233" s="3" t="s">
+      <c r="B233" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C233" s="3" t="s">
+      <c r="C233" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D233" s="5">
         <v>46444</v>
       </c>
       <c r="E233" s="4"/>
-      <c r="F233" s="3" t="s">
+      <c r="F233" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G233" s="3" t="s">
+      <c r="G233" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H233" s="6">
@@ -7597,23 +7616,23 @@
       <c r="I233" s="4"/>
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A234" s="2">
+      <c r="A234" s="3">
         <v>4010013271</v>
       </c>
-      <c r="B234" s="3" t="s">
+      <c r="B234" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C234" s="3" t="s">
+      <c r="C234" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D234" s="5">
         <v>46402</v>
       </c>
       <c r="E234" s="4"/>
-      <c r="F234" s="3" t="s">
+      <c r="F234" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G234" s="3" t="s">
+      <c r="G234" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H234" s="6">
@@ -7622,23 +7641,23 @@
       <c r="I234" s="4"/>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A235" s="2">
+      <c r="A235" s="3">
         <v>4010013272</v>
       </c>
-      <c r="B235" s="3" t="s">
+      <c r="B235" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C235" s="3" t="s">
+      <c r="C235" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D235" s="5">
         <v>46594</v>
       </c>
       <c r="E235" s="4"/>
-      <c r="F235" s="3" t="s">
+      <c r="F235" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G235" s="3" t="s">
+      <c r="G235" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H235" s="6">
@@ -7647,23 +7666,23 @@
       <c r="I235" s="4"/>
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A236" s="2">
+      <c r="A236" s="3">
         <v>4010013272</v>
       </c>
-      <c r="B236" s="3" t="s">
+      <c r="B236" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C236" s="3" t="s">
+      <c r="C236" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D236" s="5">
         <v>46523</v>
       </c>
       <c r="E236" s="4"/>
-      <c r="F236" s="3" t="s">
+      <c r="F236" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G236" s="3" t="s">
+      <c r="G236" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H236" s="6">
@@ -7672,23 +7691,23 @@
       <c r="I236" s="4"/>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A237" s="2">
+      <c r="A237" s="3">
         <v>4010013663</v>
       </c>
-      <c r="B237" s="3" t="s">
+      <c r="B237" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C237" s="3" t="s">
+      <c r="C237" s="2" t="s">
         <v>132</v>
       </c>
       <c r="D237" s="5">
         <v>46612</v>
       </c>
       <c r="E237" s="4"/>
-      <c r="F237" s="3" t="s">
+      <c r="F237" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G237" s="3" t="s">
+      <c r="G237" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H237" s="6">
@@ -7697,23 +7716,23 @@
       <c r="I237" s="4"/>
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A238" s="2">
+      <c r="A238" s="3">
         <v>6010000093</v>
       </c>
-      <c r="B238" s="3" t="s">
+      <c r="B238" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="C238" s="3" t="s">
+      <c r="C238" s="2" t="s">
         <v>221</v>
       </c>
       <c r="D238" s="5">
         <v>46504</v>
       </c>
       <c r="E238" s="4"/>
-      <c r="F238" s="3" t="s">
+      <c r="F238" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="G238" s="3" t="s">
+      <c r="G238" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H238" s="6">
@@ -7722,23 +7741,23 @@
       <c r="I238" s="4"/>
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A239" s="2">
+      <c r="A239" s="3">
         <v>6010000093</v>
       </c>
-      <c r="B239" s="3" t="s">
+      <c r="B239" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="C239" s="3" t="s">
+      <c r="C239" s="2" t="s">
         <v>223</v>
       </c>
       <c r="D239" s="5">
         <v>46484</v>
       </c>
       <c r="E239" s="4"/>
-      <c r="F239" s="3" t="s">
+      <c r="F239" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="G239" s="3" t="s">
+      <c r="G239" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H239" s="6">
@@ -7747,23 +7766,23 @@
       <c r="I239" s="4"/>
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A240" s="2">
+      <c r="A240" s="3">
         <v>6010000161</v>
       </c>
-      <c r="B240" s="3" t="s">
+      <c r="B240" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="C240" s="3" t="s">
+      <c r="C240" s="2" t="s">
         <v>329</v>
       </c>
       <c r="D240" s="5">
         <v>47087</v>
       </c>
       <c r="E240" s="4"/>
-      <c r="F240" s="3" t="s">
+      <c r="F240" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="G240" s="3" t="s">
+      <c r="G240" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H240" s="6">
@@ -7772,23 +7791,23 @@
       <c r="I240" s="4"/>
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A241" s="2">
+      <c r="A241" s="3">
         <v>6010000162</v>
       </c>
-      <c r="B241" s="3" t="s">
+      <c r="B241" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="C241" s="3" t="s">
+      <c r="C241" s="2" t="s">
         <v>332</v>
       </c>
       <c r="D241" s="5">
         <v>47087</v>
       </c>
       <c r="E241" s="4"/>
-      <c r="F241" s="3" t="s">
+      <c r="F241" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="G241" s="3" t="s">
+      <c r="G241" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H241" s="6">

--- a/KSTOCK.xlsx
+++ b/KSTOCK.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c2e6f8dd72a68295/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="11_ADD69E4EC4094E9AB632FCC5BE58E68737F706B9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11D8BE91-E835-49AF-BC1E-34FEC8A6F176}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="11_B6725C47C4094E9AB632FCC5BE58E68737F746BC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{817DDC40-D19A-4EDE-A66D-AE3604E0AB94}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1288,9 +1288,6 @@
     <t>Item Name</t>
   </si>
   <si>
-    <t>Unrestricted Qty</t>
-  </si>
-  <si>
     <t>PACK STYLE</t>
   </si>
   <si>
@@ -1301,6 +1298,9 @@
   </si>
   <si>
     <t>Batch No.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Unrestricted Qty</t>
   </si>
   <si>
     <t xml:space="preserve"> Transit Qty</t>
@@ -1310,9 +1310,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.000"/>
-  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -1334,13 +1331,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1372,7 +1369,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -1385,31 +1382,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1420,7 +1414,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF7C7AC"/>
+          <fgColor rgb="FFFBE2D5"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -1428,7 +1422,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF7C7AC"/>
+          <fgColor rgb="FFFBE2D5"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -1764,86 +1758,86 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H200"/>
-  <sheetFormatPr defaultColWidth="13.5546875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="13.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="39.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.21875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.5546875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="13.5546875" style="1"/>
+    <col min="4" max="4" width="19.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.77734375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12.109375" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="13.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:8" ht="28.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
         <v>419</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>420</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="G1" s="7" t="s">
         <v>425</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>424</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>422</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>423</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="6" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="9">
+      <c r="A2" s="8">
         <v>4010013595</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="11"/>
-      <c r="E2" s="10" t="s">
+      <c r="D2" s="10"/>
+      <c r="E2" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12">
+      <c r="F2" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11">
         <v>1400</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="9">
+      <c r="A3" s="8">
         <v>6010000122</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="9" t="s">
         <v>247</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="10" t="s">
+      <c r="D3" s="10"/>
+      <c r="E3" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12">
+      <c r="F3" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11">
         <v>1440</v>
       </c>
     </row>
@@ -1857,7 +1851,7 @@
       <c r="C4" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="4">
         <v>46568</v>
       </c>
       <c r="E4" s="3" t="s">
@@ -1866,10 +1860,10 @@
       <c r="F4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="6">
-        <v>4300</v>
-      </c>
-      <c r="H4" s="4"/>
+      <c r="G4" s="5">
+        <v>4200</v>
+      </c>
+      <c r="H4" s="5"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
@@ -1881,7 +1875,7 @@
       <c r="C5" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="4">
         <v>46746</v>
       </c>
       <c r="E5" s="3" t="s">
@@ -1890,10 +1884,10 @@
       <c r="F5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="5">
         <v>313</v>
       </c>
-      <c r="H5" s="4"/>
+      <c r="H5" s="5"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
@@ -1905,7 +1899,7 @@
       <c r="C6" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="4">
         <v>46752</v>
       </c>
       <c r="E6" s="3" t="s">
@@ -1914,10 +1908,10 @@
       <c r="F6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="5">
         <v>1040</v>
       </c>
-      <c r="H6" s="4"/>
+      <c r="H6" s="5"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
@@ -1929,7 +1923,7 @@
       <c r="C7" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="4">
         <v>46548</v>
       </c>
       <c r="E7" s="3" t="s">
@@ -1938,10 +1932,10 @@
       <c r="F7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="5">
         <v>170</v>
       </c>
-      <c r="H7" s="4"/>
+      <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
@@ -1953,7 +1947,7 @@
       <c r="C8" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="4">
         <v>46751</v>
       </c>
       <c r="E8" s="3" t="s">
@@ -1962,10 +1956,10 @@
       <c r="F8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="5">
         <v>160</v>
       </c>
-      <c r="H8" s="4"/>
+      <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
@@ -1977,7 +1971,7 @@
       <c r="C9" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="4">
         <v>46556</v>
       </c>
       <c r="E9" s="3" t="s">
@@ -1986,10 +1980,10 @@
       <c r="F9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="5">
         <v>100</v>
       </c>
-      <c r="H9" s="4"/>
+      <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
@@ -2001,7 +1995,7 @@
       <c r="C10" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="4">
         <v>46539</v>
       </c>
       <c r="E10" s="3" t="s">
@@ -2010,10 +2004,10 @@
       <c r="F10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="5">
         <v>1140</v>
       </c>
-      <c r="H10" s="4"/>
+      <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
@@ -2025,7 +2019,7 @@
       <c r="C11" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="4">
         <v>46549</v>
       </c>
       <c r="E11" s="3" t="s">
@@ -2034,10 +2028,10 @@
       <c r="F11" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G11" s="5">
         <v>400</v>
       </c>
-      <c r="H11" s="4"/>
+      <c r="H11" s="5"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
@@ -2049,7 +2043,7 @@
       <c r="C12" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="4">
         <v>46568</v>
       </c>
       <c r="E12" s="3" t="s">
@@ -2058,10 +2052,10 @@
       <c r="F12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="5">
         <v>260</v>
       </c>
-      <c r="H12" s="4"/>
+      <c r="H12" s="5"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
@@ -2073,7 +2067,7 @@
       <c r="C13" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="4">
         <v>46435</v>
       </c>
       <c r="E13" s="3" t="s">
@@ -2082,10 +2076,10 @@
       <c r="F13" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G13" s="6">
+      <c r="G13" s="5">
         <v>10</v>
       </c>
-      <c r="H13" s="4"/>
+      <c r="H13" s="5"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
@@ -2097,7 +2091,7 @@
       <c r="C14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="4">
         <v>46568</v>
       </c>
       <c r="E14" s="3" t="s">
@@ -2106,10 +2100,10 @@
       <c r="F14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G14" s="6">
+      <c r="G14" s="5">
         <v>480</v>
       </c>
-      <c r="H14" s="4"/>
+      <c r="H14" s="5"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
@@ -2121,7 +2115,7 @@
       <c r="C15" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="4">
         <v>46589</v>
       </c>
       <c r="E15" s="3" t="s">
@@ -2130,10 +2124,10 @@
       <c r="F15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G15" s="6">
+      <c r="G15" s="5">
         <v>1200</v>
       </c>
-      <c r="H15" s="4"/>
+      <c r="H15" s="5"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
@@ -2145,7 +2139,7 @@
       <c r="C16" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D16" s="4">
         <v>46549</v>
       </c>
       <c r="E16" s="3" t="s">
@@ -2154,10 +2148,10 @@
       <c r="F16" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G16" s="6">
+      <c r="G16" s="5">
         <v>640</v>
       </c>
-      <c r="H16" s="4"/>
+      <c r="H16" s="5"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
@@ -2169,7 +2163,7 @@
       <c r="C17" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="4">
         <v>46587</v>
       </c>
       <c r="E17" s="3" t="s">
@@ -2178,10 +2172,10 @@
       <c r="F17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G17" s="6">
+      <c r="G17" s="5">
         <v>420</v>
       </c>
-      <c r="H17" s="4"/>
+      <c r="H17" s="5"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
@@ -2193,7 +2187,7 @@
       <c r="C18" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="D18" s="5">
+      <c r="D18" s="4">
         <v>46549</v>
       </c>
       <c r="E18" s="3" t="s">
@@ -2202,10 +2196,10 @@
       <c r="F18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G18" s="6">
+      <c r="G18" s="5">
         <v>460</v>
       </c>
-      <c r="H18" s="4"/>
+      <c r="H18" s="5"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
@@ -2217,7 +2211,7 @@
       <c r="C19" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D19" s="5">
+      <c r="D19" s="4">
         <v>46640</v>
       </c>
       <c r="E19" s="3" t="s">
@@ -2226,10 +2220,10 @@
       <c r="F19" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G19" s="6">
+      <c r="G19" s="5">
         <v>670</v>
       </c>
-      <c r="H19" s="4"/>
+      <c r="H19" s="5"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
@@ -2241,7 +2235,7 @@
       <c r="C20" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D20" s="5">
+      <c r="D20" s="4">
         <v>46666</v>
       </c>
       <c r="E20" s="3" t="s">
@@ -2250,10 +2244,10 @@
       <c r="F20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G20" s="6">
+      <c r="G20" s="5">
         <v>400</v>
       </c>
-      <c r="H20" s="4"/>
+      <c r="H20" s="5"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
@@ -2265,7 +2259,7 @@
       <c r="C21" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D21" s="5">
+      <c r="D21" s="4">
         <v>46598</v>
       </c>
       <c r="E21" s="3" t="s">
@@ -2274,10 +2268,10 @@
       <c r="F21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G21" s="6">
+      <c r="G21" s="5">
         <v>600</v>
       </c>
-      <c r="H21" s="4"/>
+      <c r="H21" s="5"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
@@ -2289,7 +2283,7 @@
       <c r="C22" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D22" s="5">
+      <c r="D22" s="4">
         <v>46518</v>
       </c>
       <c r="E22" s="3" t="s">
@@ -2298,10 +2292,10 @@
       <c r="F22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G22" s="6">
+      <c r="G22" s="5">
         <v>320</v>
       </c>
-      <c r="H22" s="4"/>
+      <c r="H22" s="5"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
@@ -2313,7 +2307,7 @@
       <c r="C23" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="D23" s="5">
+      <c r="D23" s="4">
         <v>46536</v>
       </c>
       <c r="E23" s="3" t="s">
@@ -2322,10 +2316,10 @@
       <c r="F23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G23" s="6">
+      <c r="G23" s="5">
         <v>930</v>
       </c>
-      <c r="H23" s="4"/>
+      <c r="H23" s="5"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
@@ -2337,7 +2331,7 @@
       <c r="C24" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D24" s="5">
+      <c r="D24" s="4">
         <v>46447</v>
       </c>
       <c r="E24" s="3" t="s">
@@ -2346,10 +2340,10 @@
       <c r="F24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G24" s="6">
+      <c r="G24" s="5">
         <v>1800</v>
       </c>
-      <c r="H24" s="4"/>
+      <c r="H24" s="5"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
@@ -2361,17 +2355,17 @@
       <c r="C25" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D25" s="5"/>
+      <c r="D25" s="4"/>
       <c r="E25" s="3" t="s">
         <v>412</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G25" s="6">
+      <c r="G25" s="5">
         <v>100</v>
       </c>
-      <c r="H25" s="4"/>
+      <c r="H25" s="5"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
@@ -2383,17 +2377,17 @@
       <c r="C26" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D26" s="5"/>
+      <c r="D26" s="4"/>
       <c r="E26" s="3" t="s">
         <v>412</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G26" s="6">
+      <c r="G26" s="5">
         <v>100</v>
       </c>
-      <c r="H26" s="4"/>
+      <c r="H26" s="5"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
@@ -2405,17 +2399,17 @@
       <c r="C27" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D27" s="5"/>
+      <c r="D27" s="4"/>
       <c r="E27" s="3" t="s">
         <v>412</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G27" s="6">
+      <c r="G27" s="5">
         <v>100</v>
       </c>
-      <c r="H27" s="4"/>
+      <c r="H27" s="5"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
@@ -2427,17 +2421,17 @@
       <c r="C28" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D28" s="5"/>
+      <c r="D28" s="4"/>
       <c r="E28" s="3" t="s">
         <v>412</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G28" s="6">
+      <c r="G28" s="5">
         <v>100</v>
       </c>
-      <c r="H28" s="4"/>
+      <c r="H28" s="5"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
@@ -2449,17 +2443,17 @@
       <c r="C29" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D29" s="5"/>
+      <c r="D29" s="4"/>
       <c r="E29" s="3" t="s">
         <v>412</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G29" s="6">
+      <c r="G29" s="5">
         <v>100</v>
       </c>
-      <c r="H29" s="4"/>
+      <c r="H29" s="5"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
@@ -2471,7 +2465,7 @@
       <c r="C30" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D30" s="5">
+      <c r="D30" s="4">
         <v>46568</v>
       </c>
       <c r="E30" s="3" t="s">
@@ -2480,10 +2474,10 @@
       <c r="F30" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G30" s="6">
+      <c r="G30" s="5">
         <v>1130</v>
       </c>
-      <c r="H30" s="4"/>
+      <c r="H30" s="5"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
@@ -2495,7 +2489,7 @@
       <c r="C31" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D31" s="5">
+      <c r="D31" s="4">
         <v>46551</v>
       </c>
       <c r="E31" s="3" t="s">
@@ -2504,10 +2498,10 @@
       <c r="F31" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G31" s="6">
+      <c r="G31" s="5">
         <v>110</v>
       </c>
-      <c r="H31" s="4"/>
+      <c r="H31" s="5"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
@@ -2519,7 +2513,7 @@
       <c r="C32" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="D32" s="5">
+      <c r="D32" s="4">
         <v>47007</v>
       </c>
       <c r="E32" s="3" t="s">
@@ -2528,10 +2522,10 @@
       <c r="F32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G32" s="6">
+      <c r="G32" s="5">
         <v>443</v>
       </c>
-      <c r="H32" s="4"/>
+      <c r="H32" s="5"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
@@ -2543,7 +2537,7 @@
       <c r="C33" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="D33" s="5">
+      <c r="D33" s="4">
         <v>46752</v>
       </c>
       <c r="E33" s="3" t="s">
@@ -2552,10 +2546,10 @@
       <c r="F33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G33" s="6">
+      <c r="G33" s="5">
         <v>340</v>
       </c>
-      <c r="H33" s="4"/>
+      <c r="H33" s="5"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
@@ -2567,7 +2561,7 @@
       <c r="C34" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="D34" s="5">
+      <c r="D34" s="4">
         <v>46495</v>
       </c>
       <c r="E34" s="3" t="s">
@@ -2576,10 +2570,10 @@
       <c r="F34" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G34" s="6">
+      <c r="G34" s="5">
         <v>1100</v>
       </c>
-      <c r="H34" s="4"/>
+      <c r="H34" s="5"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
@@ -2591,7 +2585,7 @@
       <c r="C35" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="D35" s="5">
+      <c r="D35" s="4">
         <v>46780</v>
       </c>
       <c r="E35" s="3" t="s">
@@ -2600,10 +2594,10 @@
       <c r="F35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G35" s="6">
+      <c r="G35" s="5">
         <v>70</v>
       </c>
-      <c r="H35" s="4"/>
+      <c r="H35" s="5"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
@@ -2615,7 +2609,7 @@
       <c r="C36" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="D36" s="5">
+      <c r="D36" s="4">
         <v>46813</v>
       </c>
       <c r="E36" s="3" t="s">
@@ -2624,10 +2618,10 @@
       <c r="F36" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G36" s="6">
+      <c r="G36" s="5">
         <v>3300</v>
       </c>
-      <c r="H36" s="4"/>
+      <c r="H36" s="5"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
@@ -2639,7 +2633,7 @@
       <c r="C37" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="D37" s="5">
+      <c r="D37" s="4">
         <v>46780</v>
       </c>
       <c r="E37" s="3" t="s">
@@ -2648,10 +2642,10 @@
       <c r="F37" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G37" s="6">
+      <c r="G37" s="5">
         <v>760</v>
       </c>
-      <c r="H37" s="4"/>
+      <c r="H37" s="5"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
@@ -2663,7 +2657,7 @@
       <c r="C38" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="D38" s="5">
+      <c r="D38" s="4">
         <v>46726</v>
       </c>
       <c r="E38" s="3" t="s">
@@ -2672,10 +2666,10 @@
       <c r="F38" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G38" s="6">
+      <c r="G38" s="5">
         <v>3900</v>
       </c>
-      <c r="H38" s="4"/>
+      <c r="H38" s="5"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
@@ -2687,7 +2681,7 @@
       <c r="C39" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="D39" s="5">
+      <c r="D39" s="4">
         <v>46538</v>
       </c>
       <c r="E39" s="3" t="s">
@@ -2696,10 +2690,10 @@
       <c r="F39" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G39" s="6">
+      <c r="G39" s="5">
         <v>810</v>
       </c>
-      <c r="H39" s="4"/>
+      <c r="H39" s="5"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
@@ -2711,7 +2705,7 @@
       <c r="C40" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="D40" s="5">
+      <c r="D40" s="4">
         <v>46507</v>
       </c>
       <c r="E40" s="3" t="s">
@@ -2720,10 +2714,10 @@
       <c r="F40" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G40" s="6">
-        <v>289</v>
-      </c>
-      <c r="H40" s="4"/>
+      <c r="G40" s="5">
+        <v>239</v>
+      </c>
+      <c r="H40" s="5"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
@@ -2735,7 +2729,7 @@
       <c r="C41" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="D41" s="5">
+      <c r="D41" s="4">
         <v>46751</v>
       </c>
       <c r="E41" s="3" t="s">
@@ -2744,10 +2738,10 @@
       <c r="F41" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G41" s="6">
+      <c r="G41" s="5">
         <v>60</v>
       </c>
-      <c r="H41" s="4"/>
+      <c r="H41" s="5"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
@@ -2759,7 +2753,7 @@
       <c r="C42" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="D42" s="5">
+      <c r="D42" s="4">
         <v>46797</v>
       </c>
       <c r="E42" s="3" t="s">
@@ -2768,10 +2762,10 @@
       <c r="F42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G42" s="6">
+      <c r="G42" s="5">
         <v>2800</v>
       </c>
-      <c r="H42" s="4"/>
+      <c r="H42" s="5"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
@@ -2783,7 +2777,7 @@
       <c r="C43" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D43" s="5">
+      <c r="D43" s="4">
         <v>46681</v>
       </c>
       <c r="E43" s="3" t="s">
@@ -2792,10 +2786,10 @@
       <c r="F43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G43" s="6">
+      <c r="G43" s="5">
         <v>300</v>
       </c>
-      <c r="H43" s="4"/>
+      <c r="H43" s="5"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
@@ -2807,7 +2801,7 @@
       <c r="C44" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D44" s="5">
+      <c r="D44" s="4">
         <v>46575</v>
       </c>
       <c r="E44" s="3" t="s">
@@ -2816,10 +2810,10 @@
       <c r="F44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G44" s="6">
+      <c r="G44" s="5">
         <v>140</v>
       </c>
-      <c r="H44" s="4"/>
+      <c r="H44" s="5"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
@@ -2831,7 +2825,7 @@
       <c r="C45" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D45" s="5">
+      <c r="D45" s="4">
         <v>46598</v>
       </c>
       <c r="E45" s="3" t="s">
@@ -2840,10 +2834,10 @@
       <c r="F45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G45" s="6">
+      <c r="G45" s="5">
         <v>540</v>
       </c>
-      <c r="H45" s="4"/>
+      <c r="H45" s="5"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
@@ -2855,7 +2849,7 @@
       <c r="C46" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D46" s="5">
+      <c r="D46" s="4">
         <v>46575</v>
       </c>
       <c r="E46" s="3" t="s">
@@ -2864,10 +2858,10 @@
       <c r="F46" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G46" s="6">
+      <c r="G46" s="5">
         <v>740</v>
       </c>
-      <c r="H46" s="4"/>
+      <c r="H46" s="5"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
@@ -2879,7 +2873,7 @@
       <c r="C47" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D47" s="5">
+      <c r="D47" s="4">
         <v>46545</v>
       </c>
       <c r="E47" s="3" t="s">
@@ -2888,10 +2882,10 @@
       <c r="F47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G47" s="6">
+      <c r="G47" s="5">
         <v>330</v>
       </c>
-      <c r="H47" s="4"/>
+      <c r="H47" s="5"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
@@ -2903,7 +2897,7 @@
       <c r="C48" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="D48" s="5">
+      <c r="D48" s="4">
         <v>46539</v>
       </c>
       <c r="E48" s="3" t="s">
@@ -2912,10 +2906,10 @@
       <c r="F48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G48" s="6">
+      <c r="G48" s="5">
         <v>110</v>
       </c>
-      <c r="H48" s="4"/>
+      <c r="H48" s="5"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
@@ -2927,7 +2921,7 @@
       <c r="C49" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="D49" s="5">
+      <c r="D49" s="4">
         <v>46711</v>
       </c>
       <c r="E49" s="3" t="s">
@@ -2936,10 +2930,10 @@
       <c r="F49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G49" s="6">
+      <c r="G49" s="5">
         <v>380</v>
       </c>
-      <c r="H49" s="4"/>
+      <c r="H49" s="5"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
@@ -2951,7 +2945,7 @@
       <c r="C50" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="D50" s="5">
+      <c r="D50" s="4">
         <v>46726</v>
       </c>
       <c r="E50" s="3" t="s">
@@ -2960,10 +2954,10 @@
       <c r="F50" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G50" s="6">
+      <c r="G50" s="5">
         <v>2840</v>
       </c>
-      <c r="H50" s="4"/>
+      <c r="H50" s="5"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
@@ -2975,7 +2969,7 @@
       <c r="C51" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="D51" s="5">
+      <c r="D51" s="4">
         <v>46726</v>
       </c>
       <c r="E51" s="3" t="s">
@@ -2984,10 +2978,10 @@
       <c r="F51" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G51" s="6">
+      <c r="G51" s="5">
         <v>7200</v>
       </c>
-      <c r="H51" s="4"/>
+      <c r="H51" s="5"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
@@ -2999,7 +2993,7 @@
       <c r="C52" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="D52" s="5">
+      <c r="D52" s="4">
         <v>46511</v>
       </c>
       <c r="E52" s="3" t="s">
@@ -3008,10 +3002,10 @@
       <c r="F52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G52" s="6">
+      <c r="G52" s="5">
         <v>720</v>
       </c>
-      <c r="H52" s="4"/>
+      <c r="H52" s="5"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
@@ -3023,7 +3017,7 @@
       <c r="C53" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="D53" s="5">
+      <c r="D53" s="4">
         <v>46751</v>
       </c>
       <c r="E53" s="3" t="s">
@@ -3032,10 +3026,10 @@
       <c r="F53" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G53" s="6">
+      <c r="G53" s="5">
         <v>2000</v>
       </c>
-      <c r="H53" s="4"/>
+      <c r="H53" s="5"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
@@ -3047,7 +3041,7 @@
       <c r="C54" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="D54" s="5">
+      <c r="D54" s="4">
         <v>46721</v>
       </c>
       <c r="E54" s="3" t="s">
@@ -3056,10 +3050,10 @@
       <c r="F54" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G54" s="6">
+      <c r="G54" s="5">
         <v>2490</v>
       </c>
-      <c r="H54" s="4"/>
+      <c r="H54" s="5"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
@@ -3071,7 +3065,7 @@
       <c r="C55" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="D55" s="5">
+      <c r="D55" s="4">
         <v>46711</v>
       </c>
       <c r="E55" s="3" t="s">
@@ -3080,10 +3074,10 @@
       <c r="F55" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G55" s="6">
+      <c r="G55" s="5">
         <v>1438</v>
       </c>
-      <c r="H55" s="4"/>
+      <c r="H55" s="5"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
@@ -3095,7 +3089,7 @@
       <c r="C56" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="D56" s="5">
+      <c r="D56" s="4">
         <v>46813</v>
       </c>
       <c r="E56" s="3" t="s">
@@ -3104,10 +3098,10 @@
       <c r="F56" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G56" s="6">
-        <v>270</v>
-      </c>
-      <c r="H56" s="4"/>
+      <c r="G56" s="5">
+        <v>220</v>
+      </c>
+      <c r="H56" s="5"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
@@ -3119,7 +3113,7 @@
       <c r="C57" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="D57" s="5">
+      <c r="D57" s="4">
         <v>46746</v>
       </c>
       <c r="E57" s="3" t="s">
@@ -3128,10 +3122,10 @@
       <c r="F57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G57" s="6">
-        <v>2235</v>
-      </c>
-      <c r="H57" s="4"/>
+      <c r="G57" s="5">
+        <v>2185</v>
+      </c>
+      <c r="H57" s="5"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
@@ -3143,7 +3137,7 @@
       <c r="C58" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="D58" s="5">
+      <c r="D58" s="4">
         <v>46692</v>
       </c>
       <c r="E58" s="3" t="s">
@@ -3152,10 +3146,10 @@
       <c r="F58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G58" s="6">
-        <v>16050</v>
-      </c>
-      <c r="H58" s="4"/>
+      <c r="G58" s="5">
+        <v>15900</v>
+      </c>
+      <c r="H58" s="5"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
@@ -3167,7 +3161,7 @@
       <c r="C59" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D59" s="5">
+      <c r="D59" s="4">
         <v>46504</v>
       </c>
       <c r="E59" s="3" t="s">
@@ -3176,10 +3170,10 @@
       <c r="F59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G59" s="6">
+      <c r="G59" s="5">
         <v>510</v>
       </c>
-      <c r="H59" s="4"/>
+      <c r="H59" s="5"/>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
@@ -3191,7 +3185,7 @@
       <c r="C60" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="D60" s="5">
+      <c r="D60" s="4">
         <v>46721</v>
       </c>
       <c r="E60" s="3" t="s">
@@ -3200,10 +3194,10 @@
       <c r="F60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G60" s="6">
+      <c r="G60" s="5">
         <v>5760</v>
       </c>
-      <c r="H60" s="4"/>
+      <c r="H60" s="5"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
@@ -3215,7 +3209,7 @@
       <c r="C61" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="D61" s="5">
+      <c r="D61" s="4">
         <v>46780</v>
       </c>
       <c r="E61" s="3" t="s">
@@ -3224,10 +3218,10 @@
       <c r="F61" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G61" s="6">
+      <c r="G61" s="5">
         <v>2120</v>
       </c>
-      <c r="H61" s="4"/>
+      <c r="H61" s="5"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
@@ -3239,7 +3233,7 @@
       <c r="C62" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="D62" s="5">
+      <c r="D62" s="4">
         <v>46645</v>
       </c>
       <c r="E62" s="3" t="s">
@@ -3248,10 +3242,10 @@
       <c r="F62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G62" s="6">
+      <c r="G62" s="5">
         <v>2400</v>
       </c>
-      <c r="H62" s="4"/>
+      <c r="H62" s="5"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
@@ -3263,7 +3257,7 @@
       <c r="C63" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="D63" s="5">
+      <c r="D63" s="4">
         <v>46606</v>
       </c>
       <c r="E63" s="3" t="s">
@@ -3272,10 +3266,10 @@
       <c r="F63" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G63" s="6">
+      <c r="G63" s="5">
         <v>1090</v>
       </c>
-      <c r="H63" s="4"/>
+      <c r="H63" s="5"/>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
@@ -3287,7 +3281,7 @@
       <c r="C64" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D64" s="5">
+      <c r="D64" s="4">
         <v>46524</v>
       </c>
       <c r="E64" s="3" t="s">
@@ -3296,10 +3290,10 @@
       <c r="F64" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G64" s="6">
+      <c r="G64" s="5">
         <v>390</v>
       </c>
-      <c r="H64" s="4"/>
+      <c r="H64" s="5"/>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
@@ -3311,7 +3305,7 @@
       <c r="C65" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="D65" s="5">
+      <c r="D65" s="4">
         <v>46812</v>
       </c>
       <c r="E65" s="3" t="s">
@@ -3320,10 +3314,10 @@
       <c r="F65" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G65" s="6">
+      <c r="G65" s="5">
         <v>880</v>
       </c>
-      <c r="H65" s="4"/>
+      <c r="H65" s="5"/>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
@@ -3335,7 +3329,7 @@
       <c r="C66" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="D66" s="5">
+      <c r="D66" s="4">
         <v>46692</v>
       </c>
       <c r="E66" s="3" t="s">
@@ -3344,10 +3338,10 @@
       <c r="F66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G66" s="6">
+      <c r="G66" s="5">
         <v>430</v>
       </c>
-      <c r="H66" s="4"/>
+      <c r="H66" s="5"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
@@ -3359,7 +3353,7 @@
       <c r="C67" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="D67" s="5">
+      <c r="D67" s="4">
         <v>46596</v>
       </c>
       <c r="E67" s="3" t="s">
@@ -3368,10 +3362,10 @@
       <c r="F67" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G67" s="6">
+      <c r="G67" s="5">
         <v>466</v>
       </c>
-      <c r="H67" s="4"/>
+      <c r="H67" s="5"/>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
@@ -3383,7 +3377,7 @@
       <c r="C68" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="D68" s="5">
+      <c r="D68" s="4">
         <v>46803</v>
       </c>
       <c r="E68" s="3" t="s">
@@ -3392,10 +3386,10 @@
       <c r="F68" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G68" s="6">
+      <c r="G68" s="5">
         <v>490</v>
       </c>
-      <c r="H68" s="4"/>
+      <c r="H68" s="5"/>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
@@ -3407,7 +3401,7 @@
       <c r="C69" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="D69" s="5">
+      <c r="D69" s="4">
         <v>46367</v>
       </c>
       <c r="E69" s="3" t="s">
@@ -3416,10 +3410,10 @@
       <c r="F69" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G69" s="6">
+      <c r="G69" s="5">
         <v>325</v>
       </c>
-      <c r="H69" s="4"/>
+      <c r="H69" s="5"/>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
@@ -3431,7 +3425,7 @@
       <c r="C70" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="D70" s="5">
+      <c r="D70" s="4">
         <v>46447</v>
       </c>
       <c r="E70" s="3" t="s">
@@ -3440,10 +3434,10 @@
       <c r="F70" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G70" s="6">
+      <c r="G70" s="5">
         <v>380</v>
       </c>
-      <c r="H70" s="4"/>
+      <c r="H70" s="5"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
@@ -3455,7 +3449,7 @@
       <c r="C71" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="D71" s="5">
+      <c r="D71" s="4">
         <v>46574</v>
       </c>
       <c r="E71" s="3" t="s">
@@ -3464,10 +3458,10 @@
       <c r="F71" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G71" s="6">
+      <c r="G71" s="5">
         <v>560</v>
       </c>
-      <c r="H71" s="4"/>
+      <c r="H71" s="5"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
@@ -3479,7 +3473,7 @@
       <c r="C72" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="D72" s="5">
+      <c r="D72" s="4">
         <v>46726</v>
       </c>
       <c r="E72" s="3" t="s">
@@ -3488,10 +3482,10 @@
       <c r="F72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G72" s="6">
+      <c r="G72" s="5">
         <v>80</v>
       </c>
-      <c r="H72" s="4"/>
+      <c r="H72" s="5"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
@@ -3503,7 +3497,7 @@
       <c r="C73" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="D73" s="5">
+      <c r="D73" s="4">
         <v>46803</v>
       </c>
       <c r="E73" s="3" t="s">
@@ -3512,10 +3506,10 @@
       <c r="F73" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G73" s="6">
+      <c r="G73" s="5">
         <v>380</v>
       </c>
-      <c r="H73" s="4"/>
+      <c r="H73" s="5"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
@@ -3527,7 +3521,7 @@
       <c r="C74" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="D74" s="5">
+      <c r="D74" s="4">
         <v>46711</v>
       </c>
       <c r="E74" s="3" t="s">
@@ -3536,10 +3530,10 @@
       <c r="F74" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G74" s="6">
+      <c r="G74" s="5">
         <v>110</v>
       </c>
-      <c r="H74" s="4"/>
+      <c r="H74" s="5"/>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
@@ -3551,7 +3545,7 @@
       <c r="C75" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="D75" s="5">
+      <c r="D75" s="4">
         <v>46690</v>
       </c>
       <c r="E75" s="3" t="s">
@@ -3560,10 +3554,10 @@
       <c r="F75" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G75" s="6">
+      <c r="G75" s="5">
         <v>80</v>
       </c>
-      <c r="H75" s="4"/>
+      <c r="H75" s="5"/>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
@@ -3575,7 +3569,7 @@
       <c r="C76" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="D76" s="5">
+      <c r="D76" s="4">
         <v>46808</v>
       </c>
       <c r="E76" s="3" t="s">
@@ -3584,10 +3578,10 @@
       <c r="F76" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G76" s="6">
+      <c r="G76" s="5">
         <v>420</v>
       </c>
-      <c r="H76" s="4"/>
+      <c r="H76" s="5"/>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
@@ -3599,7 +3593,7 @@
       <c r="C77" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="D77" s="5">
+      <c r="D77" s="4">
         <v>46537</v>
       </c>
       <c r="E77" s="3" t="s">
@@ -3608,10 +3602,10 @@
       <c r="F77" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G77" s="6">
+      <c r="G77" s="5">
         <v>30</v>
       </c>
-      <c r="H77" s="4"/>
+      <c r="H77" s="5"/>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
@@ -3623,7 +3617,7 @@
       <c r="C78" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D78" s="5">
+      <c r="D78" s="4">
         <v>46546</v>
       </c>
       <c r="E78" s="3" t="s">
@@ -3632,10 +3626,10 @@
       <c r="F78" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G78" s="6">
+      <c r="G78" s="5">
         <v>420</v>
       </c>
-      <c r="H78" s="4"/>
+      <c r="H78" s="5"/>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
@@ -3647,7 +3641,7 @@
       <c r="C79" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="D79" s="5">
+      <c r="D79" s="4">
         <v>46640</v>
       </c>
       <c r="E79" s="3" t="s">
@@ -3656,10 +3650,10 @@
       <c r="F79" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G79" s="6">
+      <c r="G79" s="5">
         <v>1000</v>
       </c>
-      <c r="H79" s="4"/>
+      <c r="H79" s="5"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
@@ -3671,7 +3665,7 @@
       <c r="C80" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="D80" s="5">
+      <c r="D80" s="4">
         <v>46640</v>
       </c>
       <c r="E80" s="3" t="s">
@@ -3680,10 +3674,10 @@
       <c r="F80" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G80" s="6">
+      <c r="G80" s="5">
         <v>2640</v>
       </c>
-      <c r="H80" s="4"/>
+      <c r="H80" s="5"/>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
@@ -3695,7 +3689,7 @@
       <c r="C81" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D81" s="5">
+      <c r="D81" s="4">
         <v>46537</v>
       </c>
       <c r="E81" s="3" t="s">
@@ -3704,10 +3698,10 @@
       <c r="F81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G81" s="6">
+      <c r="G81" s="5">
         <v>220</v>
       </c>
-      <c r="H81" s="4"/>
+      <c r="H81" s="5"/>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
@@ -3719,7 +3713,7 @@
       <c r="C82" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="D82" s="5">
+      <c r="D82" s="4">
         <v>46532</v>
       </c>
       <c r="E82" s="3" t="s">
@@ -3728,10 +3722,10 @@
       <c r="F82" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G82" s="6">
+      <c r="G82" s="5">
         <v>900</v>
       </c>
-      <c r="H82" s="4"/>
+      <c r="H82" s="5"/>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
@@ -3743,7 +3737,7 @@
       <c r="C83" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="D83" s="5">
+      <c r="D83" s="4">
         <v>46579</v>
       </c>
       <c r="E83" s="3" t="s">
@@ -3752,10 +3746,10 @@
       <c r="F83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G83" s="6">
+      <c r="G83" s="5">
         <v>1500</v>
       </c>
-      <c r="H83" s="4"/>
+      <c r="H83" s="5"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
@@ -3767,7 +3761,7 @@
       <c r="C84" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D84" s="5">
+      <c r="D84" s="4">
         <v>46568</v>
       </c>
       <c r="E84" s="3" t="s">
@@ -3776,10 +3770,10 @@
       <c r="F84" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G84" s="6">
+      <c r="G84" s="5">
         <v>1140</v>
       </c>
-      <c r="H84" s="4"/>
+      <c r="H84" s="5"/>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
@@ -3791,7 +3785,7 @@
       <c r="C85" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="D85" s="5">
+      <c r="D85" s="4">
         <v>46579</v>
       </c>
       <c r="E85" s="3" t="s">
@@ -3800,10 +3794,10 @@
       <c r="F85" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G85" s="6">
+      <c r="G85" s="5">
         <v>1620</v>
       </c>
-      <c r="H85" s="4"/>
+      <c r="H85" s="5"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
@@ -3815,7 +3809,7 @@
       <c r="C86" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="D86" s="5">
+      <c r="D86" s="4">
         <v>46471</v>
       </c>
       <c r="E86" s="3" t="s">
@@ -3824,10 +3818,10 @@
       <c r="F86" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G86" s="6">
-        <v>4870</v>
-      </c>
-      <c r="H86" s="4"/>
+      <c r="G86" s="5">
+        <v>4670</v>
+      </c>
+      <c r="H86" s="5"/>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
@@ -3839,7 +3833,7 @@
       <c r="C87" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="D87" s="5">
+      <c r="D87" s="4">
         <v>46780</v>
       </c>
       <c r="E87" s="3" t="s">
@@ -3848,10 +3842,10 @@
       <c r="F87" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G87" s="6">
+      <c r="G87" s="5">
         <v>5650</v>
       </c>
-      <c r="H87" s="4"/>
+      <c r="H87" s="5"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
@@ -3863,7 +3857,7 @@
       <c r="C88" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="D88" s="5">
+      <c r="D88" s="4">
         <v>46758</v>
       </c>
       <c r="E88" s="3" t="s">
@@ -3872,10 +3866,10 @@
       <c r="F88" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G88" s="6">
+      <c r="G88" s="5">
         <v>840</v>
       </c>
-      <c r="H88" s="4"/>
+      <c r="H88" s="5"/>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
@@ -3887,7 +3881,7 @@
       <c r="C89" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="D89" s="5">
+      <c r="D89" s="4">
         <v>46641</v>
       </c>
       <c r="E89" s="3" t="s">
@@ -3896,10 +3890,10 @@
       <c r="F89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G89" s="6">
+      <c r="G89" s="5">
         <v>230</v>
       </c>
-      <c r="H89" s="4"/>
+      <c r="H89" s="5"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
@@ -3911,7 +3905,7 @@
       <c r="C90" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D90" s="5">
+      <c r="D90" s="4">
         <v>46573</v>
       </c>
       <c r="E90" s="3" t="s">
@@ -3920,10 +3914,10 @@
       <c r="F90" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G90" s="6">
+      <c r="G90" s="5">
         <v>1880</v>
       </c>
-      <c r="H90" s="4"/>
+      <c r="H90" s="5"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
@@ -3935,7 +3929,7 @@
       <c r="C91" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D91" s="5">
+      <c r="D91" s="4">
         <v>46610</v>
       </c>
       <c r="E91" s="3" t="s">
@@ -3944,10 +3938,10 @@
       <c r="F91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G91" s="6">
+      <c r="G91" s="5">
         <v>230</v>
       </c>
-      <c r="H91" s="4"/>
+      <c r="H91" s="5"/>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
@@ -3959,7 +3953,7 @@
       <c r="C92" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="D92" s="5">
+      <c r="D92" s="4">
         <v>46447</v>
       </c>
       <c r="E92" s="3" t="s">
@@ -3968,10 +3962,10 @@
       <c r="F92" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G92" s="6">
+      <c r="G92" s="5">
         <v>270</v>
       </c>
-      <c r="H92" s="4"/>
+      <c r="H92" s="5"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
@@ -3983,7 +3977,7 @@
       <c r="C93" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="D93" s="5">
+      <c r="D93" s="4">
         <v>46721</v>
       </c>
       <c r="E93" s="3" t="s">
@@ -3992,10 +3986,10 @@
       <c r="F93" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G93" s="6">
+      <c r="G93" s="5">
         <v>1440</v>
       </c>
-      <c r="H93" s="4"/>
+      <c r="H93" s="5"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
@@ -4007,7 +4001,7 @@
       <c r="C94" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="D94" s="5">
+      <c r="D94" s="4">
         <v>46423</v>
       </c>
       <c r="E94" s="3" t="s">
@@ -4016,10 +4010,10 @@
       <c r="F94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G94" s="6">
+      <c r="G94" s="5">
         <v>500</v>
       </c>
-      <c r="H94" s="4"/>
+      <c r="H94" s="5"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
@@ -4031,7 +4025,7 @@
       <c r="C95" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="D95" s="5">
+      <c r="D95" s="4">
         <v>46598</v>
       </c>
       <c r="E95" s="3" t="s">
@@ -4040,10 +4034,10 @@
       <c r="F95" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G95" s="6">
+      <c r="G95" s="5">
         <v>7540</v>
       </c>
-      <c r="H95" s="4"/>
+      <c r="H95" s="5"/>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
@@ -4055,7 +4049,7 @@
       <c r="C96" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="D96" s="5">
+      <c r="D96" s="4">
         <v>46510</v>
       </c>
       <c r="E96" s="3" t="s">
@@ -4064,10 +4058,10 @@
       <c r="F96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G96" s="6">
+      <c r="G96" s="5">
         <v>2230</v>
       </c>
-      <c r="H96" s="4"/>
+      <c r="H96" s="5"/>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
@@ -4079,7 +4073,7 @@
       <c r="C97" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="D97" s="5">
+      <c r="D97" s="4">
         <v>46586</v>
       </c>
       <c r="E97" s="3" t="s">
@@ -4088,10 +4082,10 @@
       <c r="F97" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G97" s="6">
+      <c r="G97" s="5">
         <v>1120</v>
       </c>
-      <c r="H97" s="4"/>
+      <c r="H97" s="5"/>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
@@ -4103,7 +4097,7 @@
       <c r="C98" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="D98" s="5">
+      <c r="D98" s="4">
         <v>46488</v>
       </c>
       <c r="E98" s="3" t="s">
@@ -4112,10 +4106,10 @@
       <c r="F98" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G98" s="6">
+      <c r="G98" s="5">
         <v>2000</v>
       </c>
-      <c r="H98" s="4"/>
+      <c r="H98" s="5"/>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
@@ -4127,7 +4121,7 @@
       <c r="C99" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="D99" s="5">
+      <c r="D99" s="4">
         <v>46660</v>
       </c>
       <c r="E99" s="3" t="s">
@@ -4136,10 +4130,10 @@
       <c r="F99" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G99" s="6">
+      <c r="G99" s="5">
         <v>750</v>
       </c>
-      <c r="H99" s="4"/>
+      <c r="H99" s="5"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
@@ -4151,7 +4145,7 @@
       <c r="C100" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="D100" s="5">
+      <c r="D100" s="4">
         <v>46505</v>
       </c>
       <c r="E100" s="3" t="s">
@@ -4160,10 +4154,10 @@
       <c r="F100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G100" s="6">
+      <c r="G100" s="5">
         <v>9500</v>
       </c>
-      <c r="H100" s="4"/>
+      <c r="H100" s="5"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
@@ -4175,7 +4169,7 @@
       <c r="C101" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="D101" s="5">
+      <c r="D101" s="4">
         <v>46556</v>
       </c>
       <c r="E101" s="3" t="s">
@@ -4184,10 +4178,10 @@
       <c r="F101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G101" s="6">
+      <c r="G101" s="5">
         <v>1780</v>
       </c>
-      <c r="H101" s="4"/>
+      <c r="H101" s="5"/>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
@@ -4199,7 +4193,7 @@
       <c r="C102" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="D102" s="5">
+      <c r="D102" s="4">
         <v>46586</v>
       </c>
       <c r="E102" s="3" t="s">
@@ -4208,10 +4202,10 @@
       <c r="F102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G102" s="6">
+      <c r="G102" s="5">
         <v>1920</v>
       </c>
-      <c r="H102" s="4"/>
+      <c r="H102" s="5"/>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
@@ -4223,7 +4217,7 @@
       <c r="C103" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="D103" s="5">
+      <c r="D103" s="4">
         <v>46624</v>
       </c>
       <c r="E103" s="3" t="s">
@@ -4232,10 +4226,10 @@
       <c r="F103" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G103" s="6">
-        <v>900</v>
-      </c>
-      <c r="H103" s="4"/>
+      <c r="G103" s="5">
+        <v>860</v>
+      </c>
+      <c r="H103" s="5"/>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
@@ -4247,7 +4241,7 @@
       <c r="C104" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="D104" s="5">
+      <c r="D104" s="4">
         <v>46685</v>
       </c>
       <c r="E104" s="3" t="s">
@@ -4256,10 +4250,10 @@
       <c r="F104" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G104" s="6">
-        <v>820</v>
-      </c>
-      <c r="H104" s="4"/>
+      <c r="G104" s="5">
+        <v>780</v>
+      </c>
+      <c r="H104" s="5"/>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
@@ -4271,7 +4265,7 @@
       <c r="C105" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D105" s="5">
+      <c r="D105" s="4">
         <v>46549</v>
       </c>
       <c r="E105" s="3" t="s">
@@ -4280,10 +4274,10 @@
       <c r="F105" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G105" s="6">
+      <c r="G105" s="5">
         <v>340</v>
       </c>
-      <c r="H105" s="4"/>
+      <c r="H105" s="5"/>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
@@ -4295,7 +4289,7 @@
       <c r="C106" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="D106" s="5">
+      <c r="D106" s="4">
         <v>46566</v>
       </c>
       <c r="E106" s="3" t="s">
@@ -4304,10 +4298,10 @@
       <c r="F106" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G106" s="6">
+      <c r="G106" s="5">
         <v>1920</v>
       </c>
-      <c r="H106" s="4"/>
+      <c r="H106" s="5"/>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
@@ -4319,7 +4313,7 @@
       <c r="C107" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="D107" s="5">
+      <c r="D107" s="4">
         <v>46780</v>
       </c>
       <c r="E107" s="3" t="s">
@@ -4328,10 +4322,10 @@
       <c r="F107" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G107" s="6">
+      <c r="G107" s="5">
         <v>1500</v>
       </c>
-      <c r="H107" s="4"/>
+      <c r="H107" s="5"/>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
@@ -4343,7 +4337,7 @@
       <c r="C108" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="D108" s="5">
+      <c r="D108" s="4">
         <v>46661</v>
       </c>
       <c r="E108" s="3" t="s">
@@ -4352,10 +4346,10 @@
       <c r="F108" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G108" s="6">
-        <v>90</v>
-      </c>
-      <c r="H108" s="4"/>
+      <c r="G108" s="5">
+        <v>40</v>
+      </c>
+      <c r="H108" s="5"/>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
@@ -4367,7 +4361,7 @@
       <c r="C109" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="D109" s="5">
+      <c r="D109" s="4">
         <v>46780</v>
       </c>
       <c r="E109" s="3" t="s">
@@ -4376,10 +4370,10 @@
       <c r="F109" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G109" s="6">
-        <v>2130</v>
-      </c>
-      <c r="H109" s="4"/>
+      <c r="G109" s="5">
+        <v>2080</v>
+      </c>
+      <c r="H109" s="5"/>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
@@ -4391,7 +4385,7 @@
       <c r="C110" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="D110" s="5">
+      <c r="D110" s="4">
         <v>46812</v>
       </c>
       <c r="E110" s="3" t="s">
@@ -4400,10 +4394,10 @@
       <c r="F110" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G110" s="6">
+      <c r="G110" s="5">
         <v>500</v>
       </c>
-      <c r="H110" s="4"/>
+      <c r="H110" s="5"/>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
@@ -4415,7 +4409,7 @@
       <c r="C111" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="D111" s="5">
+      <c r="D111" s="4">
         <v>46537</v>
       </c>
       <c r="E111" s="3" t="s">
@@ -4424,10 +4418,10 @@
       <c r="F111" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G111" s="6">
+      <c r="G111" s="5">
         <v>1560</v>
       </c>
-      <c r="H111" s="4"/>
+      <c r="H111" s="5"/>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
@@ -4439,7 +4433,7 @@
       <c r="C112" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="D112" s="5">
+      <c r="D112" s="4">
         <v>46711</v>
       </c>
       <c r="E112" s="3" t="s">
@@ -4448,10 +4442,10 @@
       <c r="F112" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G112" s="6">
+      <c r="G112" s="5">
         <v>1940</v>
       </c>
-      <c r="H112" s="4"/>
+      <c r="H112" s="5"/>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="2">
@@ -4463,7 +4457,7 @@
       <c r="C113" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="D113" s="5">
+      <c r="D113" s="4">
         <v>46971</v>
       </c>
       <c r="E113" s="3" t="s">
@@ -4472,10 +4466,10 @@
       <c r="F113" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G113" s="6">
+      <c r="G113" s="5">
         <v>7100</v>
       </c>
-      <c r="H113" s="4"/>
+      <c r="H113" s="5"/>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
@@ -4487,7 +4481,7 @@
       <c r="C114" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="D114" s="5">
+      <c r="D114" s="4">
         <v>46971</v>
       </c>
       <c r="E114" s="3" t="s">
@@ -4496,10 +4490,10 @@
       <c r="F114" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G114" s="6">
+      <c r="G114" s="5">
         <v>5980</v>
       </c>
-      <c r="H114" s="4"/>
+      <c r="H114" s="5"/>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
@@ -4511,17 +4505,17 @@
       <c r="C115" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D115" s="5"/>
+      <c r="D115" s="4"/>
       <c r="E115" s="3" t="s">
         <v>2</v>
       </c>
       <c r="F115" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G115" s="6">
+      <c r="G115" s="5">
         <v>530</v>
       </c>
-      <c r="H115" s="4"/>
+      <c r="H115" s="5"/>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
@@ -4533,7 +4527,7 @@
       <c r="C116" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="D116" s="5">
+      <c r="D116" s="4">
         <v>46711</v>
       </c>
       <c r="E116" s="3" t="s">
@@ -4542,10 +4536,10 @@
       <c r="F116" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G116" s="6">
+      <c r="G116" s="5">
         <v>5860</v>
       </c>
-      <c r="H116" s="4"/>
+      <c r="H116" s="5"/>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
@@ -4557,7 +4551,7 @@
       <c r="C117" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="D117" s="5">
+      <c r="D117" s="4">
         <v>46574</v>
       </c>
       <c r="E117" s="3" t="s">
@@ -4566,10 +4560,10 @@
       <c r="F117" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G117" s="6">
+      <c r="G117" s="5">
         <v>6640</v>
       </c>
-      <c r="H117" s="4"/>
+      <c r="H117" s="5"/>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
@@ -4581,7 +4575,7 @@
       <c r="C118" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="D118" s="5">
+      <c r="D118" s="4">
         <v>46751</v>
       </c>
       <c r="E118" s="3" t="s">
@@ -4590,10 +4584,10 @@
       <c r="F118" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G118" s="6">
+      <c r="G118" s="5">
         <v>20</v>
       </c>
-      <c r="H118" s="4"/>
+      <c r="H118" s="5"/>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
@@ -4605,7 +4599,7 @@
       <c r="C119" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="D119" s="5">
+      <c r="D119" s="4">
         <v>46598</v>
       </c>
       <c r="E119" s="3" t="s">
@@ -4614,10 +4608,10 @@
       <c r="F119" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G119" s="6">
+      <c r="G119" s="5">
         <v>240</v>
       </c>
-      <c r="H119" s="4"/>
+      <c r="H119" s="5"/>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" s="2">
@@ -4629,7 +4623,7 @@
       <c r="C120" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="D120" s="5">
+      <c r="D120" s="4">
         <v>46388</v>
       </c>
       <c r="E120" s="3" t="s">
@@ -4638,10 +4632,10 @@
       <c r="F120" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G120" s="6">
+      <c r="G120" s="5">
         <v>41100</v>
       </c>
-      <c r="H120" s="4"/>
+      <c r="H120" s="5"/>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
@@ -4653,7 +4647,7 @@
       <c r="C121" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="D121" s="5">
+      <c r="D121" s="4">
         <v>46388</v>
       </c>
       <c r="E121" s="3" t="s">
@@ -4662,10 +4656,10 @@
       <c r="F121" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G121" s="6">
+      <c r="G121" s="5">
         <v>11700</v>
       </c>
-      <c r="H121" s="4"/>
+      <c r="H121" s="5"/>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
@@ -4677,7 +4671,7 @@
       <c r="C122" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="D122" s="5">
+      <c r="D122" s="4">
         <v>46752</v>
       </c>
       <c r="E122" s="3" t="s">
@@ -4686,10 +4680,10 @@
       <c r="F122" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G122" s="6">
+      <c r="G122" s="5">
         <v>3900</v>
       </c>
-      <c r="H122" s="4"/>
+      <c r="H122" s="5"/>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
@@ -4701,7 +4695,7 @@
       <c r="C123" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="D123" s="5">
+      <c r="D123" s="4">
         <v>46641</v>
       </c>
       <c r="E123" s="3" t="s">
@@ -4710,10 +4704,10 @@
       <c r="F123" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G123" s="6">
+      <c r="G123" s="5">
         <v>6850</v>
       </c>
-      <c r="H123" s="4"/>
+      <c r="H123" s="5"/>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" s="2">
@@ -4725,7 +4719,7 @@
       <c r="C124" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="D124" s="5">
+      <c r="D124" s="4">
         <v>46721</v>
       </c>
       <c r="E124" s="3" t="s">
@@ -4734,10 +4728,10 @@
       <c r="F124" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G124" s="6">
+      <c r="G124" s="5">
         <v>2000</v>
       </c>
-      <c r="H124" s="4"/>
+      <c r="H124" s="5"/>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" s="2">
@@ -4749,7 +4743,7 @@
       <c r="C125" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="D125" s="5">
+      <c r="D125" s="4">
         <v>46813</v>
       </c>
       <c r="E125" s="3" t="s">
@@ -4758,10 +4752,10 @@
       <c r="F125" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G125" s="6">
+      <c r="G125" s="5">
         <v>500</v>
       </c>
-      <c r="H125" s="4"/>
+      <c r="H125" s="5"/>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" s="2">
@@ -4773,7 +4767,7 @@
       <c r="C126" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="D126" s="5">
+      <c r="D126" s="4">
         <v>46605</v>
       </c>
       <c r="E126" s="3" t="s">
@@ -4782,10 +4776,10 @@
       <c r="F126" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G126" s="6">
+      <c r="G126" s="5">
         <v>100</v>
       </c>
-      <c r="H126" s="4"/>
+      <c r="H126" s="5"/>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" s="2">
@@ -4797,7 +4791,7 @@
       <c r="C127" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="D127" s="5">
+      <c r="D127" s="4">
         <v>46692</v>
       </c>
       <c r="E127" s="3" t="s">
@@ -4806,10 +4800,10 @@
       <c r="F127" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G127" s="6">
+      <c r="G127" s="5">
         <v>300</v>
       </c>
-      <c r="H127" s="4"/>
+      <c r="H127" s="5"/>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" s="2">
@@ -4821,7 +4815,7 @@
       <c r="C128" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="D128" s="5">
+      <c r="D128" s="4">
         <v>46726</v>
       </c>
       <c r="E128" s="3" t="s">
@@ -4830,10 +4824,10 @@
       <c r="F128" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G128" s="6">
+      <c r="G128" s="5">
         <v>1000</v>
       </c>
-      <c r="H128" s="4"/>
+      <c r="H128" s="5"/>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
@@ -4845,7 +4839,7 @@
       <c r="C129" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="D129" s="5">
+      <c r="D129" s="4">
         <v>46425</v>
       </c>
       <c r="E129" s="3" t="s">
@@ -4854,10 +4848,10 @@
       <c r="F129" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G129" s="6">
+      <c r="G129" s="5">
         <v>103</v>
       </c>
-      <c r="H129" s="4"/>
+      <c r="H129" s="5"/>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
@@ -4869,7 +4863,7 @@
       <c r="C130" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="D130" s="5">
+      <c r="D130" s="4">
         <v>46556</v>
       </c>
       <c r="E130" s="3" t="s">
@@ -4878,10 +4872,10 @@
       <c r="F130" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G130" s="6">
+      <c r="G130" s="5">
         <v>175</v>
       </c>
-      <c r="H130" s="4"/>
+      <c r="H130" s="5"/>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" s="2">
@@ -4893,7 +4887,7 @@
       <c r="C131" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="D131" s="5">
+      <c r="D131" s="4">
         <v>46446</v>
       </c>
       <c r="E131" s="3" t="s">
@@ -4902,10 +4896,10 @@
       <c r="F131" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G131" s="6">
+      <c r="G131" s="5">
         <v>260</v>
       </c>
-      <c r="H131" s="4"/>
+      <c r="H131" s="5"/>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" s="2">
@@ -4917,7 +4911,7 @@
       <c r="C132" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D132" s="5">
+      <c r="D132" s="4">
         <v>46550</v>
       </c>
       <c r="E132" s="3" t="s">
@@ -4926,10 +4920,10 @@
       <c r="F132" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G132" s="6">
+      <c r="G132" s="5">
         <v>390</v>
       </c>
-      <c r="H132" s="4"/>
+      <c r="H132" s="5"/>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" s="2">
@@ -4941,7 +4935,7 @@
       <c r="C133" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D133" s="5">
+      <c r="D133" s="4">
         <v>46579</v>
       </c>
       <c r="E133" s="3" t="s">
@@ -4950,10 +4944,10 @@
       <c r="F133" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G133" s="6">
+      <c r="G133" s="5">
         <v>590</v>
       </c>
-      <c r="H133" s="4"/>
+      <c r="H133" s="5"/>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
@@ -4965,7 +4959,7 @@
       <c r="C134" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D134" s="5">
+      <c r="D134" s="4">
         <v>46511</v>
       </c>
       <c r="E134" s="3" t="s">
@@ -4974,10 +4968,10 @@
       <c r="F134" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G134" s="6">
+      <c r="G134" s="5">
         <v>40</v>
       </c>
-      <c r="H134" s="4"/>
+      <c r="H134" s="5"/>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" s="2">
@@ -4989,7 +4983,7 @@
       <c r="C135" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D135" s="5">
+      <c r="D135" s="4">
         <v>46525</v>
       </c>
       <c r="E135" s="3" t="s">
@@ -4998,10 +4992,10 @@
       <c r="F135" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G135" s="6">
+      <c r="G135" s="5">
         <v>1330</v>
       </c>
-      <c r="H135" s="4"/>
+      <c r="H135" s="5"/>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" s="2">
@@ -5013,7 +5007,7 @@
       <c r="C136" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="D136" s="5">
+      <c r="D136" s="4">
         <v>46484</v>
       </c>
       <c r="E136" s="3" t="s">
@@ -5022,10 +5016,10 @@
       <c r="F136" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G136" s="6">
+      <c r="G136" s="5">
         <v>10000</v>
       </c>
-      <c r="H136" s="4"/>
+      <c r="H136" s="5"/>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" s="2">
@@ -5037,7 +5031,7 @@
       <c r="C137" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="D137" s="5">
+      <c r="D137" s="4">
         <v>46388</v>
       </c>
       <c r="E137" s="3" t="s">
@@ -5046,10 +5040,10 @@
       <c r="F137" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G137" s="6">
+      <c r="G137" s="5">
         <v>900</v>
       </c>
-      <c r="H137" s="4"/>
+      <c r="H137" s="5"/>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" s="2">
@@ -5061,7 +5055,7 @@
       <c r="C138" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="D138" s="5">
+      <c r="D138" s="4">
         <v>46780</v>
       </c>
       <c r="E138" s="3" t="s">
@@ -5070,10 +5064,10 @@
       <c r="F138" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G138" s="6">
+      <c r="G138" s="5">
         <v>2900</v>
       </c>
-      <c r="H138" s="4"/>
+      <c r="H138" s="5"/>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" s="2">
@@ -5085,7 +5079,7 @@
       <c r="C139" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="D139" s="5">
+      <c r="D139" s="4">
         <v>46631</v>
       </c>
       <c r="E139" s="3" t="s">
@@ -5094,10 +5088,10 @@
       <c r="F139" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G139" s="6">
+      <c r="G139" s="5">
         <v>5140</v>
       </c>
-      <c r="H139" s="4"/>
+      <c r="H139" s="5"/>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" s="2">
@@ -5109,7 +5103,7 @@
       <c r="C140" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="D140" s="5">
+      <c r="D140" s="4">
         <v>46645</v>
       </c>
       <c r="E140" s="3" t="s">
@@ -5118,10 +5112,10 @@
       <c r="F140" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G140" s="6">
+      <c r="G140" s="5">
         <v>2240</v>
       </c>
-      <c r="H140" s="4"/>
+      <c r="H140" s="5"/>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" s="2">
@@ -5133,7 +5127,7 @@
       <c r="C141" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="D141" s="5">
+      <c r="D141" s="4">
         <v>46661</v>
       </c>
       <c r="E141" s="3" t="s">
@@ -5142,10 +5136,10 @@
       <c r="F141" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G141" s="6">
+      <c r="G141" s="5">
         <v>2660</v>
       </c>
-      <c r="H141" s="4"/>
+      <c r="H141" s="5"/>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" s="2">
@@ -5157,7 +5151,7 @@
       <c r="C142" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="D142" s="5">
+      <c r="D142" s="4">
         <v>46625</v>
       </c>
       <c r="E142" s="3" t="s">
@@ -5166,10 +5160,10 @@
       <c r="F142" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G142" s="6">
+      <c r="G142" s="5">
         <v>300</v>
       </c>
-      <c r="H142" s="4"/>
+      <c r="H142" s="5"/>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" s="2">
@@ -5181,7 +5175,7 @@
       <c r="C143" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D143" s="5">
+      <c r="D143" s="4">
         <v>46593</v>
       </c>
       <c r="E143" s="3" t="s">
@@ -5190,10 +5184,10 @@
       <c r="F143" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G143" s="6">
+      <c r="G143" s="5">
         <v>50</v>
       </c>
-      <c r="H143" s="4"/>
+      <c r="H143" s="5"/>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" s="2">
@@ -5205,7 +5199,7 @@
       <c r="C144" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="D144" s="5">
+      <c r="D144" s="4">
         <v>46721</v>
       </c>
       <c r="E144" s="3" t="s">
@@ -5214,10 +5208,10 @@
       <c r="F144" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G144" s="6">
+      <c r="G144" s="5">
         <v>800</v>
       </c>
-      <c r="H144" s="4"/>
+      <c r="H144" s="5"/>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" s="2">
@@ -5229,7 +5223,7 @@
       <c r="C145" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="D145" s="5">
+      <c r="D145" s="4">
         <v>46758</v>
       </c>
       <c r="E145" s="3" t="s">
@@ -5238,10 +5232,10 @@
       <c r="F145" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G145" s="6">
+      <c r="G145" s="5">
         <v>950</v>
       </c>
-      <c r="H145" s="4"/>
+      <c r="H145" s="5"/>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" s="2">
@@ -5253,7 +5247,7 @@
       <c r="C146" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="D146" s="5">
+      <c r="D146" s="4">
         <v>46753</v>
       </c>
       <c r="E146" s="3" t="s">
@@ -5262,10 +5256,10 @@
       <c r="F146" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G146" s="6">
+      <c r="G146" s="5">
         <v>920</v>
       </c>
-      <c r="H146" s="4"/>
+      <c r="H146" s="5"/>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" s="2">
@@ -5277,7 +5271,7 @@
       <c r="C147" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="D147" s="5">
+      <c r="D147" s="4">
         <v>46568</v>
       </c>
       <c r="E147" s="3" t="s">
@@ -5286,10 +5280,10 @@
       <c r="F147" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G147" s="6">
+      <c r="G147" s="5">
         <v>580</v>
       </c>
-      <c r="H147" s="4"/>
+      <c r="H147" s="5"/>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" s="2">
@@ -5301,7 +5295,7 @@
       <c r="C148" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D148" s="5">
+      <c r="D148" s="4">
         <v>46537</v>
       </c>
       <c r="E148" s="3" t="s">
@@ -5310,10 +5304,10 @@
       <c r="F148" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G148" s="6">
+      <c r="G148" s="5">
         <v>1250</v>
       </c>
-      <c r="H148" s="4"/>
+      <c r="H148" s="5"/>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" s="2">
@@ -5325,7 +5319,7 @@
       <c r="C149" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D149" s="5">
+      <c r="D149" s="4">
         <v>46525</v>
       </c>
       <c r="E149" s="3" t="s">
@@ -5334,10 +5328,10 @@
       <c r="F149" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G149" s="6">
+      <c r="G149" s="5">
         <v>920</v>
       </c>
-      <c r="H149" s="4"/>
+      <c r="H149" s="5"/>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" s="2">
@@ -5349,7 +5343,7 @@
       <c r="C150" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D150" s="5">
+      <c r="D150" s="4">
         <v>46442</v>
       </c>
       <c r="E150" s="3" t="s">
@@ -5358,10 +5352,10 @@
       <c r="F150" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G150" s="6">
+      <c r="G150" s="5">
         <v>280</v>
       </c>
-      <c r="H150" s="4"/>
+      <c r="H150" s="5"/>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" s="2">
@@ -5373,7 +5367,7 @@
       <c r="C151" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D151" s="5">
+      <c r="D151" s="4">
         <v>46423</v>
       </c>
       <c r="E151" s="3" t="s">
@@ -5382,10 +5376,10 @@
       <c r="F151" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G151" s="6">
+      <c r="G151" s="5">
         <v>480</v>
       </c>
-      <c r="H151" s="4"/>
+      <c r="H151" s="5"/>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" s="2">
@@ -5397,7 +5391,7 @@
       <c r="C152" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D152" s="5">
+      <c r="D152" s="4">
         <v>46545</v>
       </c>
       <c r="E152" s="3" t="s">
@@ -5406,10 +5400,10 @@
       <c r="F152" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G152" s="6">
+      <c r="G152" s="5">
         <v>560</v>
       </c>
-      <c r="H152" s="4"/>
+      <c r="H152" s="5"/>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" s="2">
@@ -5421,7 +5415,7 @@
       <c r="C153" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D153" s="5">
+      <c r="D153" s="4">
         <v>46582</v>
       </c>
       <c r="E153" s="3" t="s">
@@ -5430,10 +5424,10 @@
       <c r="F153" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G153" s="6">
+      <c r="G153" s="5">
         <v>2020</v>
       </c>
-      <c r="H153" s="4"/>
+      <c r="H153" s="5"/>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" s="2">
@@ -5445,7 +5439,7 @@
       <c r="C154" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D154" s="5">
+      <c r="D154" s="4">
         <v>46536</v>
       </c>
       <c r="E154" s="3" t="s">
@@ -5454,10 +5448,10 @@
       <c r="F154" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G154" s="6">
+      <c r="G154" s="5">
         <v>320</v>
       </c>
-      <c r="H154" s="4"/>
+      <c r="H154" s="5"/>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" s="2">
@@ -5469,7 +5463,7 @@
       <c r="C155" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D155" s="5">
+      <c r="D155" s="4">
         <v>46594</v>
       </c>
       <c r="E155" s="3" t="s">
@@ -5478,10 +5472,10 @@
       <c r="F155" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G155" s="6">
+      <c r="G155" s="5">
         <v>400</v>
       </c>
-      <c r="H155" s="4"/>
+      <c r="H155" s="5"/>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" s="2">
@@ -5493,7 +5487,7 @@
       <c r="C156" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D156" s="5">
+      <c r="D156" s="4">
         <v>46419</v>
       </c>
       <c r="E156" s="3" t="s">
@@ -5502,10 +5496,10 @@
       <c r="F156" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G156" s="6">
+      <c r="G156" s="5">
         <v>180</v>
       </c>
-      <c r="H156" s="4"/>
+      <c r="H156" s="5"/>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" s="2">
@@ -5517,7 +5511,7 @@
       <c r="C157" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="D157" s="5">
+      <c r="D157" s="4">
         <v>46446</v>
       </c>
       <c r="E157" s="3" t="s">
@@ -5526,10 +5520,10 @@
       <c r="F157" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G157" s="6">
+      <c r="G157" s="5">
         <v>520</v>
       </c>
-      <c r="H157" s="4"/>
+      <c r="H157" s="5"/>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" s="2">
@@ -5541,7 +5535,7 @@
       <c r="C158" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="D158" s="5">
+      <c r="D158" s="4">
         <v>46533</v>
       </c>
       <c r="E158" s="3" t="s">
@@ -5550,10 +5544,10 @@
       <c r="F158" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G158" s="6">
+      <c r="G158" s="5">
         <v>300</v>
       </c>
-      <c r="H158" s="4"/>
+      <c r="H158" s="5"/>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" s="2">
@@ -5565,7 +5559,7 @@
       <c r="C159" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="D159" s="5">
+      <c r="D159" s="4">
         <v>46589</v>
       </c>
       <c r="E159" s="3" t="s">
@@ -5574,10 +5568,10 @@
       <c r="F159" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G159" s="6">
+      <c r="G159" s="5">
         <v>1160</v>
       </c>
-      <c r="H159" s="4"/>
+      <c r="H159" s="5"/>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" s="2">
@@ -5589,7 +5583,7 @@
       <c r="C160" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D160" s="5">
+      <c r="D160" s="4">
         <v>46513</v>
       </c>
       <c r="E160" s="3" t="s">
@@ -5598,10 +5592,10 @@
       <c r="F160" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G160" s="6">
+      <c r="G160" s="5">
         <v>700</v>
       </c>
-      <c r="H160" s="4"/>
+      <c r="H160" s="5"/>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" s="2">
@@ -5613,7 +5607,7 @@
       <c r="C161" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D161" s="5">
+      <c r="D161" s="4">
         <v>46587</v>
       </c>
       <c r="E161" s="3" t="s">
@@ -5622,10 +5616,10 @@
       <c r="F161" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G161" s="6">
+      <c r="G161" s="5">
         <v>1110</v>
       </c>
-      <c r="H161" s="4"/>
+      <c r="H161" s="5"/>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" s="2">
@@ -5637,7 +5631,7 @@
       <c r="C162" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D162" s="5">
+      <c r="D162" s="4">
         <v>46469</v>
       </c>
       <c r="E162" s="3" t="s">
@@ -5646,10 +5640,10 @@
       <c r="F162" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G162" s="6">
+      <c r="G162" s="5">
         <v>830</v>
       </c>
-      <c r="H162" s="4"/>
+      <c r="H162" s="5"/>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" s="2">
@@ -5661,7 +5655,7 @@
       <c r="C163" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D163" s="5">
+      <c r="D163" s="4">
         <v>46408</v>
       </c>
       <c r="E163" s="3" t="s">
@@ -5670,10 +5664,10 @@
       <c r="F163" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G163" s="6">
+      <c r="G163" s="5">
         <v>1210</v>
       </c>
-      <c r="H163" s="4"/>
+      <c r="H163" s="5"/>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" s="2">
@@ -5685,7 +5679,7 @@
       <c r="C164" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D164" s="5">
+      <c r="D164" s="4">
         <v>46574</v>
       </c>
       <c r="E164" s="3" t="s">
@@ -5694,10 +5688,10 @@
       <c r="F164" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G164" s="6">
+      <c r="G164" s="5">
         <v>500</v>
       </c>
-      <c r="H164" s="4"/>
+      <c r="H164" s="5"/>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" s="2">
@@ -5709,7 +5703,7 @@
       <c r="C165" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="D165" s="5">
+      <c r="D165" s="4">
         <v>46784</v>
       </c>
       <c r="E165" s="3" t="s">
@@ -5718,10 +5712,10 @@
       <c r="F165" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G165" s="6">
+      <c r="G165" s="5">
         <v>1520</v>
       </c>
-      <c r="H165" s="4"/>
+      <c r="H165" s="5"/>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" s="2">
@@ -5733,7 +5727,7 @@
       <c r="C166" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="D166" s="5">
+      <c r="D166" s="4">
         <v>46438</v>
       </c>
       <c r="E166" s="3" t="s">
@@ -5742,10 +5736,10 @@
       <c r="F166" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G166" s="6">
+      <c r="G166" s="5">
         <v>310</v>
       </c>
-      <c r="H166" s="4"/>
+      <c r="H166" s="5"/>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" s="2">
@@ -5757,7 +5751,7 @@
       <c r="C167" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="D167" s="5">
+      <c r="D167" s="4">
         <v>46871</v>
       </c>
       <c r="E167" s="3" t="s">
@@ -5766,10 +5760,10 @@
       <c r="F167" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G167" s="6">
+      <c r="G167" s="5">
         <v>2300</v>
       </c>
-      <c r="H167" s="4"/>
+      <c r="H167" s="5"/>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" s="2">
@@ -5781,7 +5775,7 @@
       <c r="C168" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="D168" s="5">
+      <c r="D168" s="4">
         <v>46424</v>
       </c>
       <c r="E168" s="3" t="s">
@@ -5790,10 +5784,10 @@
       <c r="F168" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G168" s="6">
+      <c r="G168" s="5">
         <v>2360</v>
       </c>
-      <c r="H168" s="4"/>
+      <c r="H168" s="5"/>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" s="2">
@@ -5805,7 +5799,7 @@
       <c r="C169" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="D169" s="5">
+      <c r="D169" s="4">
         <v>46614</v>
       </c>
       <c r="E169" s="3" t="s">
@@ -5814,10 +5808,10 @@
       <c r="F169" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G169" s="6">
+      <c r="G169" s="5">
         <v>2450</v>
       </c>
-      <c r="H169" s="4"/>
+      <c r="H169" s="5"/>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" s="2">
@@ -5829,7 +5823,7 @@
       <c r="C170" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="D170" s="5">
+      <c r="D170" s="4">
         <v>46746</v>
       </c>
       <c r="E170" s="3" t="s">
@@ -5838,10 +5832,10 @@
       <c r="F170" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G170" s="6">
+      <c r="G170" s="5">
         <v>480</v>
       </c>
-      <c r="H170" s="4"/>
+      <c r="H170" s="5"/>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" s="2">
@@ -5853,7 +5847,7 @@
       <c r="C171" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="D171" s="5">
+      <c r="D171" s="4">
         <v>46482</v>
       </c>
       <c r="E171" s="3" t="s">
@@ -5862,10 +5856,10 @@
       <c r="F171" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G171" s="6">
+      <c r="G171" s="5">
         <v>4400</v>
       </c>
-      <c r="H171" s="4"/>
+      <c r="H171" s="5"/>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" s="2">
@@ -5877,7 +5871,7 @@
       <c r="C172" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="D172" s="5">
+      <c r="D172" s="4">
         <v>46556</v>
       </c>
       <c r="E172" s="3" t="s">
@@ -5886,10 +5880,10 @@
       <c r="F172" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G172" s="6">
+      <c r="G172" s="5">
         <v>1640</v>
       </c>
-      <c r="H172" s="4"/>
+      <c r="H172" s="5"/>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" s="2">
@@ -5901,7 +5895,7 @@
       <c r="C173" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="D173" s="5">
+      <c r="D173" s="4">
         <v>46388</v>
       </c>
       <c r="E173" s="3" t="s">
@@ -5910,10 +5904,10 @@
       <c r="F173" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G173" s="6">
+      <c r="G173" s="5">
         <v>980</v>
       </c>
-      <c r="H173" s="4"/>
+      <c r="H173" s="5"/>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" s="2">
@@ -5925,7 +5919,7 @@
       <c r="C174" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="D174" s="5">
+      <c r="D174" s="4">
         <v>46488</v>
       </c>
       <c r="E174" s="3" t="s">
@@ -5934,10 +5928,10 @@
       <c r="F174" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G174" s="6">
+      <c r="G174" s="5">
         <v>160</v>
       </c>
-      <c r="H174" s="4"/>
+      <c r="H174" s="5"/>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" s="2">
@@ -5949,7 +5943,7 @@
       <c r="C175" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="D175" s="5">
+      <c r="D175" s="4">
         <v>46388</v>
       </c>
       <c r="E175" s="3" t="s">
@@ -5958,10 +5952,10 @@
       <c r="F175" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G175" s="6">
+      <c r="G175" s="5">
         <v>1460</v>
       </c>
-      <c r="H175" s="4"/>
+      <c r="H175" s="5"/>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" s="2">
@@ -5973,7 +5967,7 @@
       <c r="C176" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="D176" s="5">
+      <c r="D176" s="4">
         <v>46496</v>
       </c>
       <c r="E176" s="3" t="s">
@@ -5982,10 +5976,10 @@
       <c r="F176" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G176" s="6">
+      <c r="G176" s="5">
         <v>290</v>
       </c>
-      <c r="H176" s="4"/>
+      <c r="H176" s="5"/>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" s="2">
@@ -5997,7 +5991,7 @@
       <c r="C177" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="D177" s="5">
+      <c r="D177" s="4">
         <v>46496</v>
       </c>
       <c r="E177" s="3" t="s">
@@ -6006,10 +6000,10 @@
       <c r="F177" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G177" s="6">
+      <c r="G177" s="5">
         <v>130</v>
       </c>
-      <c r="H177" s="4"/>
+      <c r="H177" s="5"/>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" s="2">
@@ -6021,7 +6015,7 @@
       <c r="C178" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D178" s="5">
+      <c r="D178" s="4">
         <v>46558</v>
       </c>
       <c r="E178" s="3" t="s">
@@ -6030,10 +6024,10 @@
       <c r="F178" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G178" s="6">
+      <c r="G178" s="5">
         <v>880</v>
       </c>
-      <c r="H178" s="4"/>
+      <c r="H178" s="5"/>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" s="2">
@@ -6045,7 +6039,7 @@
       <c r="C179" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="D179" s="5">
+      <c r="D179" s="4">
         <v>46971</v>
       </c>
       <c r="E179" s="3" t="s">
@@ -6054,10 +6048,10 @@
       <c r="F179" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G179" s="6">
+      <c r="G179" s="5">
         <v>1680</v>
       </c>
-      <c r="H179" s="4"/>
+      <c r="H179" s="5"/>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" s="2">
@@ -6069,7 +6063,7 @@
       <c r="C180" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="D180" s="5">
+      <c r="D180" s="4">
         <v>47087</v>
       </c>
       <c r="E180" s="3" t="s">
@@ -6078,10 +6072,10 @@
       <c r="F180" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G180" s="6">
+      <c r="G180" s="5">
         <v>990</v>
       </c>
-      <c r="H180" s="4"/>
+      <c r="H180" s="5"/>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" s="2">
@@ -6093,7 +6087,7 @@
       <c r="C181" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D181" s="5">
+      <c r="D181" s="4">
         <v>46525</v>
       </c>
       <c r="E181" s="3" t="s">
@@ -6102,10 +6096,10 @@
       <c r="F181" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G181" s="6">
+      <c r="G181" s="5">
         <v>620</v>
       </c>
-      <c r="H181" s="4"/>
+      <c r="H181" s="5"/>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" s="2">
@@ -6117,7 +6111,7 @@
       <c r="C182" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D182" s="5">
+      <c r="D182" s="4">
         <v>46533</v>
       </c>
       <c r="E182" s="3" t="s">
@@ -6126,10 +6120,10 @@
       <c r="F182" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G182" s="6">
+      <c r="G182" s="5">
         <v>160</v>
       </c>
-      <c r="H182" s="4"/>
+      <c r="H182" s="5"/>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" s="2">
@@ -6141,7 +6135,7 @@
       <c r="C183" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D183" s="5">
+      <c r="D183" s="4">
         <v>46533</v>
       </c>
       <c r="E183" s="3" t="s">
@@ -6150,10 +6144,10 @@
       <c r="F183" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G183" s="6">
+      <c r="G183" s="5">
         <v>80</v>
       </c>
-      <c r="H183" s="4"/>
+      <c r="H183" s="5"/>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" s="2">
@@ -6165,7 +6159,7 @@
       <c r="C184" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D184" s="5">
+      <c r="D184" s="4">
         <v>46532</v>
       </c>
       <c r="E184" s="3" t="s">
@@ -6174,10 +6168,10 @@
       <c r="F184" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G184" s="6">
+      <c r="G184" s="5">
         <v>1070</v>
       </c>
-      <c r="H184" s="4"/>
+      <c r="H184" s="5"/>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" s="2">
@@ -6189,7 +6183,7 @@
       <c r="C185" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="D185" s="5">
+      <c r="D185" s="4">
         <v>46606</v>
       </c>
       <c r="E185" s="3" t="s">
@@ -6198,10 +6192,10 @@
       <c r="F185" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G185" s="6">
-        <v>410</v>
-      </c>
-      <c r="H185" s="4"/>
+      <c r="G185" s="5">
+        <v>370</v>
+      </c>
+      <c r="H185" s="5"/>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" s="2">
@@ -6213,7 +6207,7 @@
       <c r="C186" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D186" s="5">
+      <c r="D186" s="4">
         <v>46514</v>
       </c>
       <c r="E186" s="3" t="s">
@@ -6222,10 +6216,10 @@
       <c r="F186" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G186" s="6">
+      <c r="G186" s="5">
         <v>230</v>
       </c>
-      <c r="H186" s="4"/>
+      <c r="H186" s="5"/>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187" s="2">
@@ -6237,7 +6231,7 @@
       <c r="C187" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="D187" s="5">
+      <c r="D187" s="4">
         <v>46768</v>
       </c>
       <c r="E187" s="3" t="s">
@@ -6246,10 +6240,10 @@
       <c r="F187" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G187" s="6">
+      <c r="G187" s="5">
         <v>780</v>
       </c>
-      <c r="H187" s="4"/>
+      <c r="H187" s="5"/>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" s="2">
@@ -6261,17 +6255,17 @@
       <c r="C188" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D188" s="5"/>
+      <c r="D188" s="4"/>
       <c r="E188" s="3" t="s">
         <v>2</v>
       </c>
       <c r="F188" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G188" s="6">
+      <c r="G188" s="5">
         <v>30</v>
       </c>
-      <c r="H188" s="4"/>
+      <c r="H188" s="5"/>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" s="2">
@@ -6283,17 +6277,17 @@
       <c r="C189" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D189" s="5"/>
+      <c r="D189" s="4"/>
       <c r="E189" s="3" t="s">
         <v>2</v>
       </c>
       <c r="F189" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G189" s="6">
+      <c r="G189" s="5">
         <v>70</v>
       </c>
-      <c r="H189" s="4"/>
+      <c r="H189" s="5"/>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190" s="2">
@@ -6305,7 +6299,7 @@
       <c r="C190" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D190" s="5">
+      <c r="D190" s="4">
         <v>46526</v>
       </c>
       <c r="E190" s="3" t="s">
@@ -6314,10 +6308,10 @@
       <c r="F190" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G190" s="6">
+      <c r="G190" s="5">
         <v>1250</v>
       </c>
-      <c r="H190" s="4"/>
+      <c r="H190" s="5"/>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" s="2">
@@ -6329,7 +6323,7 @@
       <c r="C191" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D191" s="5">
+      <c r="D191" s="4">
         <v>46444</v>
       </c>
       <c r="E191" s="3" t="s">
@@ -6338,10 +6332,10 @@
       <c r="F191" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G191" s="6">
+      <c r="G191" s="5">
         <v>710</v>
       </c>
-      <c r="H191" s="4"/>
+      <c r="H191" s="5"/>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192" s="2">
@@ -6353,7 +6347,7 @@
       <c r="C192" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D192" s="5">
+      <c r="D192" s="4">
         <v>46444</v>
       </c>
       <c r="E192" s="3" t="s">
@@ -6362,10 +6356,10 @@
       <c r="F192" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G192" s="6">
+      <c r="G192" s="5">
         <v>20</v>
       </c>
-      <c r="H192" s="4"/>
+      <c r="H192" s="5"/>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" s="2">
@@ -6377,7 +6371,7 @@
       <c r="C193" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D193" s="5">
+      <c r="D193" s="4">
         <v>46402</v>
       </c>
       <c r="E193" s="3" t="s">
@@ -6386,10 +6380,10 @@
       <c r="F193" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G193" s="6">
+      <c r="G193" s="5">
         <v>280</v>
       </c>
-      <c r="H193" s="4"/>
+      <c r="H193" s="5"/>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" s="2">
@@ -6401,7 +6395,7 @@
       <c r="C194" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D194" s="5">
+      <c r="D194" s="4">
         <v>46594</v>
       </c>
       <c r="E194" s="3" t="s">
@@ -6410,10 +6404,10 @@
       <c r="F194" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G194" s="6">
+      <c r="G194" s="5">
         <v>360</v>
       </c>
-      <c r="H194" s="4"/>
+      <c r="H194" s="5"/>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" s="2">
@@ -6425,7 +6419,7 @@
       <c r="C195" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D195" s="5">
+      <c r="D195" s="4">
         <v>46523</v>
       </c>
       <c r="E195" s="3" t="s">
@@ -6434,10 +6428,10 @@
       <c r="F195" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G195" s="6">
+      <c r="G195" s="5">
         <v>880</v>
       </c>
-      <c r="H195" s="4"/>
+      <c r="H195" s="5"/>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" s="2">
@@ -6449,7 +6443,7 @@
       <c r="C196" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="D196" s="5">
+      <c r="D196" s="4">
         <v>46612</v>
       </c>
       <c r="E196" s="3" t="s">
@@ -6458,10 +6452,10 @@
       <c r="F196" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G196" s="6">
+      <c r="G196" s="5">
         <v>1160</v>
       </c>
-      <c r="H196" s="4"/>
+      <c r="H196" s="5"/>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" s="2">
@@ -6473,7 +6467,7 @@
       <c r="C197" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="D197" s="5">
+      <c r="D197" s="4">
         <v>46484</v>
       </c>
       <c r="E197" s="3" t="s">
@@ -6482,10 +6476,10 @@
       <c r="F197" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G197" s="6">
+      <c r="G197" s="5">
         <v>26500</v>
       </c>
-      <c r="H197" s="4"/>
+      <c r="H197" s="5"/>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" s="2">
@@ -6497,7 +6491,7 @@
       <c r="C198" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="D198" s="5">
+      <c r="D198" s="4">
         <v>46504</v>
       </c>
       <c r="E198" s="3" t="s">
@@ -6506,10 +6500,10 @@
       <c r="F198" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G198" s="6">
+      <c r="G198" s="5">
         <v>15000</v>
       </c>
-      <c r="H198" s="4"/>
+      <c r="H198" s="5"/>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" s="2">
@@ -6521,7 +6515,7 @@
       <c r="C199" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="D199" s="5">
+      <c r="D199" s="4">
         <v>47087</v>
       </c>
       <c r="E199" s="3" t="s">
@@ -6530,10 +6524,10 @@
       <c r="F199" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G199" s="6">
+      <c r="G199" s="5">
         <v>498</v>
       </c>
-      <c r="H199" s="4"/>
+      <c r="H199" s="5"/>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" s="2">
@@ -6545,7 +6539,7 @@
       <c r="C200" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="D200" s="5">
+      <c r="D200" s="4">
         <v>47087</v>
       </c>
       <c r="E200" s="3" t="s">
@@ -6554,10 +6548,10 @@
       <c r="F200" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G200" s="6">
+      <c r="G200" s="5">
         <v>1020</v>
       </c>
-      <c r="H200" s="4"/>
+      <c r="H200" s="5"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H200" xr:uid="{00000000-0001-0000-0000-000000000000}">

--- a/KSTOCK.xlsx
+++ b/KSTOCK.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c2e6f8dd72a68295/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="44" documentId="11_AFBA3D4BC4094E9AB632FCC5BECF5645043394C5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0CAAFB11-4DBD-440E-B5ED-F70452470AF6}"/>
+  <xr:revisionPtr revIDLastSave="52" documentId="11_A43A9C41C4094E9AB632FCC5BE28A68627F55F60" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D1574BC-1171-40A7-9222-ACDEB238D07A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$200</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$218</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="429">
   <si>
     <t>ROSUSEP-20</t>
   </si>
@@ -46,12 +46,12 @@
     <t>ATROLIA CV 10/75</t>
   </si>
   <si>
+    <t>10X2X15</t>
+  </si>
+  <si>
     <t>25S3GCA109</t>
   </si>
   <si>
-    <t>10X2X15</t>
-  </si>
-  <si>
     <t>ATROLIA CV 20/75</t>
   </si>
   <si>
@@ -106,12 +106,12 @@
     <t>Vildapharm-Met 500</t>
   </si>
   <si>
+    <t>25S3GTA610</t>
+  </si>
+  <si>
     <t>25S3GTA972</t>
   </si>
   <si>
-    <t>25S3GTA610</t>
-  </si>
-  <si>
     <t>VILDAPHARM-DP</t>
   </si>
   <si>
@@ -166,12 +166,12 @@
     <t>PROGISPHERE SR 200</t>
   </si>
   <si>
+    <t>25S2HTA612</t>
+  </si>
+  <si>
     <t>25S2HTA863</t>
   </si>
   <si>
-    <t>25S2HTA612</t>
-  </si>
-  <si>
     <t>PROGISPHERE SR 300</t>
   </si>
   <si>
@@ -199,12 +199,12 @@
     <t>ROSUSEP-ASP 20</t>
   </si>
   <si>
+    <t>25S3GCA034</t>
+  </si>
+  <si>
     <t>25S3GCA138</t>
   </si>
   <si>
-    <t>25S3GCA034</t>
-  </si>
-  <si>
     <t>25S3GCA105</t>
   </si>
   <si>
@@ -283,12 +283,12 @@
     <t>GLIMKAT-MET 1 (PR)</t>
   </si>
   <si>
+    <t>25S3GTA626</t>
+  </si>
+  <si>
     <t>25S3GTA625</t>
   </si>
   <si>
-    <t>25S3GTA626</t>
-  </si>
-  <si>
     <t>GLIMKAT-MET 2 (PR)</t>
   </si>
   <si>
@@ -400,12 +400,12 @@
     <t>REBEHIT-LS</t>
   </si>
   <si>
+    <t>25S2GCA762</t>
+  </si>
+  <si>
     <t>25S2GCA829</t>
   </si>
   <si>
-    <t>25S2GCA762</t>
-  </si>
-  <si>
     <t>MONTALIA-FX</t>
   </si>
   <si>
@@ -421,12 +421,12 @@
     <t>ATROLIA GOLD 20/75</t>
   </si>
   <si>
+    <t>25S3GCA113</t>
+  </si>
+  <si>
     <t>25S3GCA129</t>
   </si>
   <si>
-    <t>25S3GCA113</t>
-  </si>
-  <si>
     <t>Atrolia-ASP 75</t>
   </si>
   <si>
@@ -442,12 +442,12 @@
     <t>ROSUSEP-CV 10</t>
   </si>
   <si>
+    <t>25S3GCA046</t>
+  </si>
+  <si>
     <t>25S3GCA099</t>
   </si>
   <si>
-    <t>25S3GCA046</t>
-  </si>
-  <si>
     <t>ROSUSEP-CV 20</t>
   </si>
   <si>
@@ -613,12 +613,12 @@
     <t>RANINIT INJ</t>
   </si>
   <si>
+    <t>NL1442502</t>
+  </si>
+  <si>
     <t>NL1442501</t>
   </si>
   <si>
-    <t>NL1442502</t>
-  </si>
-  <si>
     <t>REBEHIT IV</t>
   </si>
   <si>
@@ -631,15 +631,15 @@
     <t>SYNACORT</t>
   </si>
   <si>
+    <t>NL2682502</t>
+  </si>
+  <si>
+    <t>10X8X1ML</t>
+  </si>
+  <si>
     <t>NL2682501</t>
   </si>
   <si>
-    <t>10X8X1ML</t>
-  </si>
-  <si>
-    <t>NL2682502</t>
-  </si>
-  <si>
     <t>TAZCILLIN-P 4.5 INJ</t>
   </si>
   <si>
@@ -1069,12 +1069,12 @@
     <t>Faropharm 200 Tablet</t>
   </si>
   <si>
+    <t>CBT26001B</t>
+  </si>
+  <si>
     <t>CBT26025B</t>
   </si>
   <si>
-    <t>CBT26001B</t>
-  </si>
-  <si>
     <t>CBT25115D</t>
   </si>
   <si>
@@ -1171,15 +1171,15 @@
     <t>MONTALIA-LC 60ML SYRUP</t>
   </si>
   <si>
+    <t>DL603008</t>
+  </si>
+  <si>
+    <t>60 ML</t>
+  </si>
+  <si>
     <t>DL602011A</t>
   </si>
   <si>
-    <t>60 ML</t>
-  </si>
-  <si>
-    <t>DL603008</t>
-  </si>
-  <si>
     <t>CLAVMYCIN 375 DUO TABLET (20x1x10)</t>
   </si>
   <si>
@@ -1198,12 +1198,12 @@
     <t>CLAVMYCIN 625 DUO TABLET (20x1x10)</t>
   </si>
   <si>
+    <t>50046010</t>
+  </si>
+  <si>
     <t>50046012</t>
   </si>
   <si>
-    <t>50046010</t>
-  </si>
-  <si>
     <t>CT25512H</t>
   </si>
   <si>
@@ -1222,10 +1222,16 @@
     <t>CEFIXLIA-50 ORAL SUSPENSION (Glass Bottl</t>
   </si>
   <si>
+    <t>CD25583C</t>
+  </si>
+  <si>
     <t>CD25654B</t>
   </si>
   <si>
-    <t>CD25583C</t>
+    <t>CLAVMYCIN DS SUSPENSION (Glass Bottle)</t>
+  </si>
+  <si>
+    <t>30ML + SWFI</t>
   </si>
   <si>
     <t>EPODOX 50 DRY SYRUP (Glass Bottle)</t>
@@ -1234,9 +1240,6 @@
     <t>CD26083B</t>
   </si>
   <si>
-    <t>30ML + SWFI</t>
-  </si>
-  <si>
     <t>VOLOPAIN AQ INJECTION</t>
   </si>
   <si>
@@ -1300,13 +1303,13 @@
     <t>Expiry</t>
   </si>
   <si>
-    <t xml:space="preserve"> Batch No.</t>
+    <t>Batch No.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Unrestricted Qty</t>
   </si>
   <si>
     <t xml:space="preserve"> Transit Qty</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Unrestricted Qty</t>
   </si>
 </sst>
 </file>
@@ -1337,13 +1340,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1423,7 +1426,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF7C7AC"/>
+          <fgColor rgb="FFFBE2D5"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -1431,7 +1434,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF7C7AC"/>
+          <fgColor rgb="FFFBE2D5"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -1766,504 +1769,512 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H200"/>
-  <sheetFormatPr defaultColWidth="12.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H218"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.88671875" style="1"/>
+    <col min="1" max="1" width="11" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="39.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="12.88671875" style="1"/>
-    <col min="6" max="6" width="8.33203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.88671875" style="1"/>
-    <col min="8" max="8" width="9.33203125" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="12.88671875" style="1"/>
+    <col min="3" max="3" width="12.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.77734375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.77734375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9.88671875" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C1" s="11" t="s">
+        <v>426</v>
+      </c>
+      <c r="D1" s="11" t="s">
         <v>425</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="E1" s="12" t="s">
+        <v>423</v>
+      </c>
+      <c r="F1" s="12" t="s">
         <v>424</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>422</v>
-      </c>
-      <c r="F1" s="12" t="s">
-        <v>423</v>
       </c>
       <c r="G1" s="12" t="s">
         <v>427</v>
       </c>
       <c r="H1" s="12" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
-        <v>4010013595</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="9"/>
-      <c r="E2" s="8" t="s">
+      <c r="A2" s="2">
+        <v>6010000095</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="D2" s="4">
+        <v>46568</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="6">
+        <v>3800</v>
+      </c>
+      <c r="H2" s="5"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>6010000138</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="D3" s="4">
+        <v>46746</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="6">
+        <v>253</v>
+      </c>
+      <c r="H3" s="5"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>4010015107</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D4" s="4">
+        <v>46752</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="6">
+        <v>1040</v>
+      </c>
+      <c r="H4" s="5"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>4010013476</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" s="4">
+        <v>46548</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10">
-        <v>1400</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
-        <v>6010000122</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10">
-        <v>1440</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
-        <v>6010000142</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>280</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="8" t="s">
-        <v>281</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
-        <v>6010000245</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>404</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="9"/>
-      <c r="E5" s="8" t="s">
-        <v>405</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10">
-        <v>20000</v>
-      </c>
+      <c r="F5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G5" s="6">
+        <v>170</v>
+      </c>
+      <c r="H5" s="5"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>6010000095</v>
+        <v>6010000097</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D6" s="4">
-        <v>46568</v>
+        <v>46556</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>23</v>
+        <v>216</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G6" s="6">
-        <v>3800</v>
+        <v>100</v>
       </c>
       <c r="H6" s="5"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>6010000138</v>
+        <v>6010000097</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>272</v>
+        <v>214</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>273</v>
+        <v>217</v>
       </c>
       <c r="D7" s="4">
-        <v>46746</v>
+        <v>46751</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>274</v>
+        <v>216</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G7" s="6">
-        <v>253</v>
+        <v>160</v>
       </c>
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>4010015107</v>
+        <v>6010000098</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>150</v>
+        <v>218</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>151</v>
+        <v>219</v>
       </c>
       <c r="D8" s="4">
-        <v>46752</v>
+        <v>46539</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G8" s="6">
-        <v>1040</v>
+        <v>1140</v>
       </c>
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>4010013476</v>
+        <v>6010000195</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>51</v>
+        <v>353</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>52</v>
+        <v>354</v>
       </c>
       <c r="D9" s="4">
-        <v>46548</v>
+        <v>46549</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G9" s="6">
-        <v>170</v>
+        <v>400</v>
       </c>
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
-        <v>6010000097</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D10" s="4">
-        <v>46556</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="6">
-        <v>100</v>
-      </c>
-      <c r="H10" s="5"/>
+      <c r="A10" s="7">
+        <v>4010013259</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="9"/>
+      <c r="E10" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10">
+        <v>480</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
-        <v>6010000097</v>
+        <v>4010013259</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>214</v>
+        <v>6</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>217</v>
+        <v>8</v>
       </c>
       <c r="D11" s="4">
-        <v>46751</v>
+        <v>46568</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>216</v>
+        <v>7</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G11" s="6">
-        <v>160</v>
+        <v>260</v>
       </c>
       <c r="H11" s="5"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
-        <v>6010000098</v>
+        <v>4010013260</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>218</v>
+        <v>9</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>219</v>
+        <v>10</v>
       </c>
       <c r="D12" s="4">
-        <v>46539</v>
+        <v>46589</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>82</v>
+        <v>11</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G12" s="6">
-        <v>1140</v>
+        <v>1200</v>
       </c>
       <c r="H12" s="5"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
-        <v>6010000195</v>
+        <v>4010013260</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>353</v>
+        <v>9</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>354</v>
+        <v>12</v>
       </c>
       <c r="D13" s="4">
-        <v>46549</v>
+        <v>46568</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G13" s="6">
-        <v>400</v>
+        <v>480</v>
       </c>
       <c r="H13" s="5"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <v>4010013259</v>
+        <v>4010013260</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D14" s="4">
-        <v>46568</v>
+        <v>46435</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G14" s="6">
-        <v>260</v>
+        <v>10</v>
       </c>
       <c r="H14" s="5"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
-        <v>4010013260</v>
+        <v>4010013692</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>9</v>
+        <v>129</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>10</v>
+        <v>130</v>
       </c>
       <c r="D15" s="4">
-        <v>46589</v>
+        <v>46549</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G15" s="6">
-        <v>1200</v>
+        <v>640</v>
       </c>
       <c r="H15" s="5"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
-        <v>4010013260</v>
+        <v>4010013693</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>9</v>
+        <v>131</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>12</v>
+        <v>132</v>
       </c>
       <c r="D16" s="4">
-        <v>46568</v>
+        <v>46549</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G16" s="6">
-        <v>480</v>
+        <v>460</v>
       </c>
       <c r="H16" s="5"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
-        <v>4010013260</v>
+        <v>4010013693</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>9</v>
+        <v>131</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>13</v>
+        <v>133</v>
       </c>
       <c r="D17" s="4">
-        <v>46435</v>
+        <v>46587</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G17" s="6">
-        <v>10</v>
+        <v>420</v>
       </c>
       <c r="H17" s="5"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <v>4010013692</v>
+        <v>4010013578</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>129</v>
+        <v>78</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>130</v>
+        <v>79</v>
       </c>
       <c r="D18" s="4">
-        <v>46549</v>
+        <v>46640</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G18" s="6">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="H18" s="5"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
-        <v>4010013693</v>
+        <v>4010013580</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>131</v>
+        <v>80</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>132</v>
+        <v>81</v>
       </c>
       <c r="D19" s="4">
-        <v>46587</v>
+        <v>46666</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G19" s="6">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="H19" s="5"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
-        <v>4010013693</v>
+        <v>4010013551</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>131</v>
+        <v>70</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>133</v>
+        <v>71</v>
       </c>
       <c r="D20" s="4">
-        <v>46549</v>
+        <v>46598</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G20" s="6">
-        <v>460</v>
+        <v>580</v>
       </c>
       <c r="H20" s="5"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
-        <v>4010013578</v>
+        <v>4010013660</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="D21" s="4">
-        <v>46640</v>
+        <v>46518</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>23</v>
@@ -2272,143 +2283,137 @@
         <v>5</v>
       </c>
       <c r="G21" s="6">
-        <v>670</v>
+        <v>320</v>
       </c>
       <c r="H21" s="5"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
-        <v>4010013580</v>
+        <v>4010013694</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>81</v>
+        <v>135</v>
       </c>
       <c r="D22" s="4">
-        <v>46666</v>
+        <v>46536</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>82</v>
+        <v>7</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G22" s="6">
-        <v>400</v>
+        <v>930</v>
       </c>
       <c r="H22" s="5"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
-        <v>4010013551</v>
+        <v>6010000065</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>70</v>
+        <v>152</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>71</v>
+        <v>153</v>
       </c>
       <c r="D23" s="4">
-        <v>46598</v>
+        <v>46447</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>23</v>
+        <v>154</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G23" s="6">
-        <v>580</v>
+        <v>1800</v>
       </c>
       <c r="H23" s="5"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
-        <v>4010013660</v>
+        <v>7050000018</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>117</v>
+        <v>418</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="D24" s="4">
-        <v>46518</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D24" s="4"/>
       <c r="E24" s="3" t="s">
-        <v>23</v>
+        <v>414</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G24" s="6">
-        <v>320</v>
+        <v>100</v>
       </c>
       <c r="H24" s="5"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
-        <v>4010013694</v>
+        <v>7050000016</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>134</v>
+        <v>416</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="D25" s="4">
-        <v>46536</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D25" s="4"/>
       <c r="E25" s="3" t="s">
-        <v>8</v>
+        <v>414</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G25" s="6">
-        <v>930</v>
+        <v>100</v>
       </c>
       <c r="H25" s="5"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
-        <v>6010000065</v>
+        <v>7050000015</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>152</v>
+        <v>415</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="D26" s="4">
-        <v>46447</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D26" s="4"/>
       <c r="E26" s="3" t="s">
-        <v>154</v>
+        <v>414</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G26" s="6">
-        <v>1800</v>
+        <v>100</v>
       </c>
       <c r="H26" s="5"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
-        <v>7050000018</v>
+        <v>7050000014</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="3" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>3</v>
@@ -2420,17 +2425,17 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
-        <v>7050000016</v>
+        <v>7050000017</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="3" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>3</v>
@@ -2442,477 +2447,477 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
-        <v>7050000015</v>
+        <v>4010013550</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>414</v>
+        <v>68</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D29" s="4"/>
+        <v>69</v>
+      </c>
+      <c r="D29" s="4">
+        <v>46568</v>
+      </c>
       <c r="E29" s="3" t="s">
-        <v>413</v>
+        <v>31</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G29" s="6">
-        <v>100</v>
+        <v>1130</v>
       </c>
       <c r="H29" s="5"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
-        <v>7050000014</v>
+        <v>4010013478</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>412</v>
+        <v>55</v>
       </c>
       <c r="C30" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D30" s="4">
+        <v>46551</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G30" s="6">
+        <v>110</v>
+      </c>
+      <c r="H30" s="5"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="7">
+        <v>6010000154</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="C31" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D30" s="4"/>
-      <c r="E30" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="F30" s="3" t="s">
+      <c r="D31" s="9"/>
+      <c r="E31" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="F31" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G30" s="6">
-        <v>100</v>
-      </c>
-      <c r="H30" s="5"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
-        <v>7050000017</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D31" s="4"/>
-      <c r="E31" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G31" s="6">
-        <v>100</v>
-      </c>
-      <c r="H31" s="5"/>
+      <c r="G31" s="10"/>
+      <c r="H31" s="10">
+        <v>95</v>
+      </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
-        <v>4010013550</v>
+        <v>6010000154</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>68</v>
+        <v>300</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>69</v>
+        <v>301</v>
       </c>
       <c r="D32" s="4">
-        <v>46568</v>
+        <v>47007</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>31</v>
+        <v>302</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G32" s="6">
-        <v>1130</v>
+        <v>351</v>
       </c>
       <c r="H32" s="5"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
-        <v>4010013478</v>
+        <v>6010000158</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>55</v>
+        <v>307</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>56</v>
+        <v>308</v>
       </c>
       <c r="D33" s="4">
-        <v>46551</v>
+        <v>46752</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G33" s="6">
-        <v>110</v>
+        <v>340</v>
       </c>
       <c r="H33" s="5"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
-        <v>6010000154</v>
+        <v>6010000068</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>300</v>
+        <v>155</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>301</v>
+        <v>156</v>
       </c>
       <c r="D34" s="4">
-        <v>47007</v>
+        <v>46495</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>302</v>
+        <v>157</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G34" s="6">
-        <v>363</v>
+        <v>800</v>
       </c>
       <c r="H34" s="5"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
-        <v>6010000158</v>
+        <v>6010000159</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D35" s="4">
-        <v>46752</v>
+        <v>46780</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G35" s="6">
-        <v>340</v>
+        <v>70</v>
       </c>
       <c r="H35" s="5"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
-        <v>6010000068</v>
+        <v>6010000099</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>155</v>
+        <v>220</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>156</v>
+        <v>221</v>
       </c>
       <c r="D36" s="4">
-        <v>46495</v>
+        <v>46813</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G36" s="6">
-        <v>800</v>
+        <v>3200</v>
       </c>
       <c r="H36" s="5"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
-        <v>6010000159</v>
+        <v>6010000160</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D37" s="4">
         <v>46780</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>31</v>
+        <v>313</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G37" s="6">
-        <v>70</v>
+        <v>760</v>
       </c>
       <c r="H37" s="5"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
-        <v>6010000099</v>
+        <v>6010000234</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>220</v>
+        <v>394</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>221</v>
+        <v>395</v>
       </c>
       <c r="D38" s="4">
-        <v>46813</v>
+        <v>46726</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>82</v>
+        <v>23</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G38" s="6">
-        <v>3200</v>
+        <v>3500</v>
       </c>
       <c r="H38" s="5"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
-        <v>6010000160</v>
+        <v>6010000239</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>311</v>
+        <v>398</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>312</v>
+        <v>399</v>
       </c>
       <c r="D39" s="4">
-        <v>46780</v>
+        <v>46507</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>313</v>
+        <v>346</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G39" s="6">
-        <v>760</v>
+        <v>209</v>
       </c>
       <c r="H39" s="5"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
-        <v>6010000234</v>
+        <v>6010000239</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="D40" s="4">
-        <v>46726</v>
+        <v>46538</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>23</v>
+        <v>346</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G40" s="6">
-        <v>3500</v>
+        <v>810</v>
       </c>
       <c r="H40" s="5"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="2">
-        <v>6010000239</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="D41" s="4">
-        <v>46538</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G41" s="6">
-        <v>810</v>
-      </c>
-      <c r="H41" s="5"/>
+      <c r="A41" s="7">
+        <v>6010000217</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D41" s="9"/>
+      <c r="E41" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G41" s="10"/>
+      <c r="H41" s="10">
+        <v>600</v>
+      </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
-        <v>6010000239</v>
+        <v>6010000217</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>398</v>
+        <v>379</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="D42" s="4">
-        <v>46507</v>
+        <v>46751</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>346</v>
+        <v>31</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G42" s="6">
-        <v>209</v>
+        <v>60</v>
       </c>
       <c r="H42" s="5"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
-        <v>6010000217</v>
+        <v>6010000071</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>379</v>
+        <v>158</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>380</v>
+        <v>159</v>
       </c>
       <c r="D43" s="4">
-        <v>46751</v>
+        <v>46797</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>31</v>
+        <v>160</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G43" s="6">
-        <v>60</v>
+        <v>2800</v>
       </c>
       <c r="H43" s="5"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
-        <v>6010000071</v>
+        <v>4010013389</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>158</v>
+        <v>37</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
       <c r="D44" s="4">
-        <v>46797</v>
+        <v>46681</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>160</v>
+        <v>39</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G44" s="6">
-        <v>2800</v>
+        <v>220</v>
       </c>
       <c r="H44" s="5"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
-        <v>4010013389</v>
+        <v>4010013266</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="D45" s="4">
-        <v>46681</v>
+        <v>46575</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G45" s="6">
-        <v>220</v>
+        <v>40</v>
       </c>
       <c r="H45" s="5"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
-        <v>4010013266</v>
+        <v>4010013267</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D46" s="4">
-        <v>46575</v>
+        <v>46598</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G46" s="6">
-        <v>40</v>
+        <v>540</v>
       </c>
       <c r="H46" s="5"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
-        <v>4010013267</v>
+        <v>4010013553</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>20</v>
+        <v>73</v>
       </c>
       <c r="D47" s="4">
-        <v>46598</v>
+        <v>46575</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G47" s="6">
-        <v>540</v>
+        <v>700</v>
       </c>
       <c r="H47" s="5"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="2">
-        <v>4010013553</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D48" s="4">
-        <v>46575</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G48" s="6">
-        <v>700</v>
-      </c>
-      <c r="H48" s="5"/>
+      <c r="A48" s="7">
+        <v>4010013397</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D48" s="9"/>
+      <c r="E48" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G48" s="10"/>
+      <c r="H48" s="10">
+        <v>220</v>
+      </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
@@ -2928,7 +2933,7 @@
         <v>46545</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>5</v>
@@ -2987,28 +2992,26 @@
       <c r="H51" s="5"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="2">
+      <c r="A52" s="7">
         <v>6010000232</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="B52" s="8" t="s">
         <v>390</v>
       </c>
-      <c r="C52" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="D52" s="4">
-        <v>46726</v>
-      </c>
-      <c r="E52" s="3" t="s">
+      <c r="C52" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D52" s="9"/>
+      <c r="E52" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G52" s="6">
-        <v>7200</v>
-      </c>
-      <c r="H52" s="5"/>
+      <c r="F52" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G52" s="10"/>
+      <c r="H52" s="10">
+        <v>4320</v>
+      </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
@@ -3018,7 +3021,7 @@
         <v>390</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D53" s="4">
         <v>46726</v>
@@ -3036,136 +3039,134 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
-        <v>6010000073</v>
+        <v>6010000232</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>161</v>
+        <v>390</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>162</v>
+        <v>392</v>
       </c>
       <c r="D54" s="4">
-        <v>46511</v>
+        <v>46726</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>163</v>
+        <v>16</v>
       </c>
       <c r="F54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G54" s="6">
+        <v>7200</v>
+      </c>
+      <c r="H54" s="5"/>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="7">
+        <v>6010000240</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>401</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D55" s="9"/>
+      <c r="E55" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="F55" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G54" s="6">
-        <v>720</v>
-      </c>
-      <c r="H54" s="5"/>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="2">
-        <v>6010000169</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="D55" s="4">
-        <v>46751</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G55" s="6">
-        <v>2000</v>
-      </c>
-      <c r="H55" s="5"/>
+      <c r="G55" s="10"/>
+      <c r="H55" s="10">
+        <v>1620</v>
+      </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
-        <v>6010000170</v>
+        <v>6010000073</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>322</v>
+        <v>161</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>323</v>
+        <v>162</v>
       </c>
       <c r="D56" s="4">
-        <v>46721</v>
+        <v>46511</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>96</v>
+        <v>163</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G56" s="6">
-        <v>2490</v>
+        <v>720</v>
       </c>
       <c r="H56" s="5"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
-        <v>6010000139</v>
+        <v>6010000169</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>275</v>
+        <v>320</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>276</v>
+        <v>321</v>
       </c>
       <c r="D57" s="4">
-        <v>46711</v>
+        <v>46751</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>277</v>
+        <v>96</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G57" s="6">
-        <v>1438</v>
+        <v>2000</v>
       </c>
       <c r="H57" s="5"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
-        <v>6010000267</v>
+        <v>6010000170</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>409</v>
+        <v>322</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>410</v>
+        <v>323</v>
       </c>
       <c r="D58" s="4">
-        <v>46813</v>
+        <v>46721</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>411</v>
+        <v>96</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G58" s="6">
-        <v>220</v>
+        <v>2490</v>
       </c>
       <c r="H58" s="5"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
-        <v>6010000141</v>
+        <v>6010000139</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="D59" s="4">
-        <v>46746</v>
+        <v>46711</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>277</v>
@@ -3174,382 +3175,380 @@
         <v>3</v>
       </c>
       <c r="G59" s="6">
-        <v>2185</v>
+        <v>1438</v>
       </c>
       <c r="H59" s="5"/>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="2">
-        <v>6010000205</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="D60" s="4">
-        <v>46692</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="F60" s="3" t="s">
+      <c r="A60" s="7">
+        <v>6010000267</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D60" s="9"/>
+      <c r="E60" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="F60" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G60" s="6">
-        <v>15750</v>
-      </c>
-      <c r="H60" s="5"/>
+      <c r="G60" s="10"/>
+      <c r="H60" s="10">
+        <v>1600</v>
+      </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
-        <v>4010013583</v>
+        <v>6010000267</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>83</v>
+        <v>410</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>84</v>
+        <v>411</v>
       </c>
       <c r="D61" s="4">
-        <v>46504</v>
+        <v>46813</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>65</v>
+        <v>412</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G61" s="6">
-        <v>510</v>
+        <v>220</v>
       </c>
       <c r="H61" s="5"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
-        <v>6010000074</v>
+        <v>6010000141</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>164</v>
+        <v>278</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>165</v>
+        <v>279</v>
       </c>
       <c r="D62" s="4">
-        <v>46721</v>
+        <v>46746</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>166</v>
+        <v>277</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G62" s="6">
-        <v>5760</v>
+        <v>2185</v>
       </c>
       <c r="H62" s="5"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
-        <v>6010000102</v>
+        <v>6010000205</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>222</v>
+        <v>369</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>223</v>
+        <v>370</v>
       </c>
       <c r="D63" s="4">
-        <v>46780</v>
+        <v>46692</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>23</v>
+        <v>371</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G63" s="6">
-        <v>1880</v>
+        <v>15750</v>
       </c>
       <c r="H63" s="5"/>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
-        <v>6010000103</v>
+        <v>4010013583</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>224</v>
+        <v>83</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>225</v>
+        <v>84</v>
       </c>
       <c r="D64" s="4">
-        <v>46645</v>
+        <v>46504</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G64" s="6">
-        <v>2400</v>
+        <v>510</v>
       </c>
       <c r="H64" s="5"/>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
-        <v>6010000196</v>
+        <v>6010000074</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>355</v>
+        <v>164</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>356</v>
+        <v>165</v>
       </c>
       <c r="D65" s="4">
-        <v>46606</v>
+        <v>46721</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>357</v>
+        <v>166</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G65" s="6">
-        <v>1040</v>
+        <v>5760</v>
       </c>
       <c r="H65" s="5"/>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
-        <v>4010013473</v>
+        <v>6010000102</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>44</v>
+        <v>222</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>45</v>
+        <v>223</v>
       </c>
       <c r="D66" s="4">
-        <v>46524</v>
+        <v>46780</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G66" s="6">
-        <v>390</v>
+        <v>1880</v>
       </c>
       <c r="H66" s="5"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
-        <v>6010000150</v>
+        <v>6010000103</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>295</v>
+        <v>224</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>296</v>
+        <v>225</v>
       </c>
       <c r="D67" s="4">
-        <v>46812</v>
+        <v>46645</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>297</v>
+        <v>23</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G67" s="6">
-        <v>880</v>
+        <v>2400</v>
       </c>
       <c r="H67" s="5"/>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
-        <v>6010000151</v>
+        <v>6010000196</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>298</v>
+        <v>355</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>299</v>
+        <v>356</v>
       </c>
       <c r="D68" s="4">
-        <v>46692</v>
+        <v>46606</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>297</v>
+        <v>357</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G68" s="6">
-        <v>430</v>
+        <v>1040</v>
       </c>
       <c r="H68" s="5"/>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
-        <v>6010000241</v>
+        <v>4010013473</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>401</v>
+        <v>44</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>402</v>
+        <v>45</v>
       </c>
       <c r="D69" s="4">
-        <v>46596</v>
+        <v>46524</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>403</v>
+        <v>31</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G69" s="6">
-        <v>436</v>
+        <v>390</v>
       </c>
       <c r="H69" s="5"/>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
-        <v>6010000194</v>
+        <v>6010000150</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>351</v>
+        <v>295</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>352</v>
+        <v>296</v>
       </c>
       <c r="D70" s="4">
-        <v>46803</v>
+        <v>46812</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>31</v>
+        <v>297</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G70" s="6">
-        <v>390</v>
+        <v>880</v>
       </c>
       <c r="H70" s="5"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
-        <v>6010000192</v>
+        <v>6010000151</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>344</v>
+        <v>298</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>345</v>
+        <v>299</v>
       </c>
       <c r="D71" s="4">
-        <v>46367</v>
+        <v>46692</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="F71" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G71" s="6">
-        <v>325</v>
+        <v>430</v>
       </c>
       <c r="H71" s="5"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
-        <v>6010000155</v>
+        <v>6010000241</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>303</v>
+        <v>403</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>304</v>
+        <v>404</v>
       </c>
       <c r="D72" s="4">
-        <v>46447</v>
+        <v>46596</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>31</v>
+        <v>402</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G72" s="6">
-        <v>380</v>
+        <v>436</v>
       </c>
       <c r="H72" s="5"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
-        <v>6010000108</v>
+        <v>6010000194</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>226</v>
+        <v>351</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>227</v>
+        <v>352</v>
       </c>
       <c r="D73" s="4">
-        <v>46574</v>
+        <v>46803</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F73" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G73" s="6">
-        <v>560</v>
+        <v>390</v>
       </c>
       <c r="H73" s="5"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
-        <v>6010000193</v>
+        <v>6010000192</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="D74" s="4">
-        <v>46803</v>
+        <v>46367</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>31</v>
+        <v>346</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G74" s="6">
-        <v>380</v>
+        <v>325</v>
       </c>
       <c r="H74" s="5"/>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
-        <v>6010000193</v>
+        <v>6010000155</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>347</v>
+        <v>303</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>349</v>
+        <v>304</v>
       </c>
       <c r="D75" s="4">
-        <v>46726</v>
+        <v>46447</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>31</v>
@@ -3558,46 +3557,46 @@
         <v>5</v>
       </c>
       <c r="G75" s="6">
-        <v>80</v>
+        <v>380</v>
       </c>
       <c r="H75" s="5"/>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
-        <v>6010000193</v>
+        <v>6010000108</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>347</v>
+        <v>226</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>350</v>
+        <v>227</v>
       </c>
       <c r="D76" s="4">
-        <v>46711</v>
+        <v>46574</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G76" s="6">
-        <v>110</v>
+        <v>560</v>
       </c>
       <c r="H76" s="5"/>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
-        <v>6010000216</v>
+        <v>6010000193</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>377</v>
+        <v>347</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>378</v>
+        <v>348</v>
       </c>
       <c r="D77" s="4">
-        <v>46690</v>
+        <v>46726</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>31</v>
@@ -3612,40 +3611,40 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
-        <v>6010000235</v>
+        <v>6010000193</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>396</v>
+        <v>347</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>397</v>
+        <v>349</v>
       </c>
       <c r="D78" s="4">
-        <v>46808</v>
+        <v>46803</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G78" s="6">
-        <v>300</v>
+        <v>380</v>
       </c>
       <c r="H78" s="5"/>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
-        <v>4010013662</v>
+        <v>6010000193</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>119</v>
+        <v>347</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>120</v>
+        <v>350</v>
       </c>
       <c r="D79" s="4">
-        <v>46537</v>
+        <v>46711</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>31</v>
@@ -3654,22 +3653,22 @@
         <v>5</v>
       </c>
       <c r="G79" s="6">
-        <v>30</v>
+        <v>110</v>
       </c>
       <c r="H79" s="5"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
-        <v>4010013662</v>
+        <v>6010000216</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>119</v>
+        <v>377</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>121</v>
+        <v>378</v>
       </c>
       <c r="D80" s="4">
-        <v>46546</v>
+        <v>46690</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>31</v>
@@ -3678,142 +3677,142 @@
         <v>5</v>
       </c>
       <c r="G80" s="6">
-        <v>420</v>
+        <v>80</v>
       </c>
       <c r="H80" s="5"/>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
-        <v>6010000110</v>
+        <v>6010000235</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>228</v>
+        <v>396</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>229</v>
+        <v>397</v>
       </c>
       <c r="D81" s="4">
-        <v>46640</v>
+        <v>46808</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G81" s="6">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="H81" s="5"/>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
-        <v>6010000111</v>
+        <v>4010013662</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>230</v>
+        <v>119</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>231</v>
+        <v>120</v>
       </c>
       <c r="D82" s="4">
-        <v>46640</v>
+        <v>46537</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="F82" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G82" s="6">
-        <v>2640</v>
+        <v>30</v>
       </c>
       <c r="H82" s="5"/>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
-        <v>4010013584</v>
+        <v>4010013662</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>85</v>
+        <v>119</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>86</v>
+        <v>121</v>
       </c>
       <c r="D83" s="4">
-        <v>46537</v>
+        <v>46546</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>82</v>
+        <v>31</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G83" s="6">
-        <v>220</v>
+        <v>420</v>
       </c>
       <c r="H83" s="5"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
-        <v>4010013584</v>
+        <v>6010000110</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>85</v>
+        <v>228</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>87</v>
+        <v>229</v>
       </c>
       <c r="D84" s="4">
-        <v>46532</v>
+        <v>46640</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>82</v>
+        <v>4</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G84" s="6">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="H84" s="5"/>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
-        <v>6010000171</v>
+        <v>6010000111</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>324</v>
+        <v>230</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>325</v>
+        <v>231</v>
       </c>
       <c r="D85" s="4">
-        <v>46579</v>
+        <v>46640</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>82</v>
+        <v>4</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G85" s="6">
-        <v>1500</v>
+        <v>2640</v>
       </c>
       <c r="H85" s="5"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
-        <v>4010013585</v>
+        <v>4010013584</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D86" s="4">
-        <v>46568</v>
+        <v>46532</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>82</v>
@@ -3822,22 +3821,22 @@
         <v>5</v>
       </c>
       <c r="G86" s="6">
-        <v>1100</v>
+        <v>900</v>
       </c>
       <c r="H86" s="5"/>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
-        <v>6010000172</v>
+        <v>4010013584</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>326</v>
+        <v>85</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>327</v>
+        <v>87</v>
       </c>
       <c r="D87" s="4">
-        <v>46579</v>
+        <v>46537</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>82</v>
@@ -3846,142 +3845,142 @@
         <v>5</v>
       </c>
       <c r="G87" s="6">
-        <v>1620</v>
+        <v>220</v>
       </c>
       <c r="H87" s="5"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
-        <v>6010000077</v>
+        <v>6010000171</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>167</v>
+        <v>324</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>168</v>
+        <v>325</v>
       </c>
       <c r="D88" s="4">
-        <v>46471</v>
+        <v>46579</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G88" s="6">
-        <v>4620</v>
+        <v>1500</v>
       </c>
       <c r="H88" s="5"/>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
-        <v>6010000078</v>
+        <v>4010013585</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>170</v>
+        <v>88</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>171</v>
+        <v>89</v>
       </c>
       <c r="D89" s="4">
-        <v>46780</v>
+        <v>46568</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>172</v>
+        <v>82</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G89" s="6">
-        <v>5650</v>
+        <v>1000</v>
       </c>
       <c r="H89" s="5"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
-        <v>4010013593</v>
+        <v>6010000172</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>97</v>
+        <v>326</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>98</v>
+        <v>327</v>
       </c>
       <c r="D90" s="4">
-        <v>46758</v>
+        <v>46579</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>31</v>
+        <v>82</v>
       </c>
       <c r="F90" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G90" s="6">
-        <v>840</v>
+        <v>1620</v>
       </c>
       <c r="H90" s="5"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
-        <v>4010014329</v>
+        <v>6010000077</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>143</v>
+        <v>167</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="D91" s="4">
-        <v>46641</v>
+        <v>46471</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>31</v>
+        <v>169</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G91" s="6">
-        <v>230</v>
+        <v>4620</v>
       </c>
       <c r="H91" s="5"/>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
-        <v>4010013594</v>
+        <v>6010000078</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>99</v>
+        <v>170</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>100</v>
+        <v>171</v>
       </c>
       <c r="D92" s="4">
-        <v>46573</v>
+        <v>46780</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>31</v>
+        <v>172</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G92" s="6">
-        <v>1850</v>
+        <v>5650</v>
       </c>
       <c r="H92" s="5"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
-        <v>4010014330</v>
+        <v>4010013593</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>145</v>
+        <v>97</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>146</v>
+        <v>98</v>
       </c>
       <c r="D93" s="4">
-        <v>46610</v>
+        <v>46758</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>31</v>
@@ -3990,22 +3989,22 @@
         <v>5</v>
       </c>
       <c r="G93" s="6">
-        <v>230</v>
+        <v>840</v>
       </c>
       <c r="H93" s="5"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
-        <v>6010000156</v>
+        <v>4010014329</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>305</v>
+        <v>143</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>306</v>
+        <v>144</v>
       </c>
       <c r="D94" s="4">
-        <v>46447</v>
+        <v>46641</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>31</v>
@@ -4014,22 +4013,22 @@
         <v>5</v>
       </c>
       <c r="G94" s="6">
-        <v>270</v>
+        <v>230</v>
       </c>
       <c r="H94" s="5"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
-        <v>6010000233</v>
+        <v>4010013594</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>305</v>
+        <v>99</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>393</v>
+        <v>100</v>
       </c>
       <c r="D95" s="4">
-        <v>46721</v>
+        <v>46573</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>31</v>
@@ -4038,313 +4037,311 @@
         <v>5</v>
       </c>
       <c r="G95" s="6">
-        <v>1440</v>
+        <v>1850</v>
       </c>
       <c r="H95" s="5"/>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
-        <v>6010000080</v>
+        <v>4010014330</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>173</v>
+        <v>145</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>174</v>
+        <v>146</v>
       </c>
       <c r="D96" s="4">
-        <v>46423</v>
+        <v>46610</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>175</v>
+        <v>31</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G96" s="6">
-        <v>500</v>
+        <v>230</v>
       </c>
       <c r="H96" s="5"/>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
-        <v>6010000113</v>
+        <v>6010000156</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>232</v>
+        <v>305</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>233</v>
+        <v>306</v>
       </c>
       <c r="D97" s="4">
-        <v>46598</v>
+        <v>46447</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F97" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G97" s="6">
-        <v>7440</v>
+        <v>270</v>
       </c>
       <c r="H97" s="5"/>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
-        <v>4010013656</v>
+        <v>6010000233</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>108</v>
+        <v>305</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>109</v>
+        <v>393</v>
       </c>
       <c r="D98" s="4">
-        <v>46510</v>
+        <v>46721</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>110</v>
+        <v>31</v>
       </c>
       <c r="F98" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G98" s="6">
-        <v>2220</v>
+        <v>1440</v>
       </c>
       <c r="H98" s="5"/>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
-        <v>6010000174</v>
+        <v>6010000080</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>328</v>
+        <v>173</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>329</v>
+        <v>174</v>
       </c>
       <c r="D99" s="4">
-        <v>46586</v>
+        <v>46423</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>330</v>
+        <v>175</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G99" s="6">
-        <v>1120</v>
+        <v>500</v>
       </c>
       <c r="H99" s="5"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
-        <v>6010000114</v>
+        <v>6010000113</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D100" s="4">
-        <v>46488</v>
+        <v>46598</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>96</v>
+        <v>23</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G100" s="6">
-        <v>2000</v>
+        <v>7440</v>
       </c>
       <c r="H100" s="5"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
-        <v>6010000081</v>
+        <v>4010013656</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>176</v>
+        <v>108</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>177</v>
+        <v>109</v>
       </c>
       <c r="D101" s="4">
-        <v>46660</v>
+        <v>46510</v>
       </c>
       <c r="E101" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G101" s="6">
+        <v>2220</v>
+      </c>
+      <c r="H101" s="5"/>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" s="7">
+        <v>4010013595</v>
+      </c>
+      <c r="B102" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C102" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="F101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G101" s="6">
-        <v>700</v>
-      </c>
-      <c r="H101" s="5"/>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A102" s="2">
-        <v>6010000082</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C102" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D102" s="4">
-        <v>46505</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G102" s="6">
-        <v>9440</v>
-      </c>
-      <c r="H102" s="5"/>
+      <c r="D102" s="9"/>
+      <c r="E102" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F102" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G102" s="10"/>
+      <c r="H102" s="10">
+        <v>1400</v>
+      </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
-        <v>6010000175</v>
+        <v>6010000174</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D103" s="4">
-        <v>46556</v>
+        <v>46586</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="F103" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G103" s="6">
-        <v>1780</v>
+        <v>1120</v>
       </c>
       <c r="H103" s="5"/>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
-        <v>6010000176</v>
+        <v>6010000114</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>334</v>
+        <v>234</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>335</v>
+        <v>235</v>
       </c>
       <c r="D104" s="4">
-        <v>46586</v>
+        <v>46488</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>333</v>
+        <v>96</v>
       </c>
       <c r="F104" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G104" s="6">
-        <v>1920</v>
+        <v>2000</v>
       </c>
       <c r="H104" s="5"/>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
-        <v>6010000201</v>
+        <v>6010000081</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>362</v>
+        <v>176</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>363</v>
+        <v>177</v>
       </c>
       <c r="D105" s="4">
-        <v>46624</v>
+        <v>46660</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>364</v>
+        <v>2</v>
       </c>
       <c r="F105" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G105" s="6">
-        <v>860</v>
+        <v>700</v>
       </c>
       <c r="H105" s="5"/>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
-        <v>6010000202</v>
+        <v>6010000082</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>365</v>
+        <v>178</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>366</v>
+        <v>179</v>
       </c>
       <c r="D106" s="4">
-        <v>46685</v>
+        <v>46505</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>364</v>
+        <v>180</v>
       </c>
       <c r="F106" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G106" s="6">
-        <v>780</v>
+        <v>9440</v>
       </c>
       <c r="H106" s="5"/>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
-        <v>4010013262</v>
+        <v>6010000175</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>14</v>
+        <v>331</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>15</v>
+        <v>332</v>
       </c>
       <c r="D107" s="4">
-        <v>46549</v>
+        <v>46556</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>16</v>
+        <v>333</v>
       </c>
       <c r="F107" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G107" s="6">
-        <v>340</v>
+        <v>1780</v>
       </c>
       <c r="H107" s="5"/>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
-        <v>4010013671</v>
+        <v>6010000176</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>127</v>
+        <v>334</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>128</v>
+        <v>335</v>
       </c>
       <c r="D108" s="4">
-        <v>46566</v>
+        <v>46586</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>16</v>
+        <v>333</v>
       </c>
       <c r="F108" s="3" t="s">
         <v>5</v>
@@ -4356,230 +4353,232 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
-        <v>6010000252</v>
+        <v>6010000201</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>406</v>
+        <v>362</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>407</v>
+        <v>363</v>
       </c>
       <c r="D109" s="4">
-        <v>46780</v>
+        <v>46624</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>408</v>
+        <v>364</v>
       </c>
       <c r="F109" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G109" s="6">
-        <v>1490</v>
+        <v>860</v>
       </c>
       <c r="H109" s="5"/>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
-        <v>6010000218</v>
+        <v>6010000202</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>381</v>
+        <v>365</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="D110" s="4">
-        <v>46780</v>
+        <v>46685</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>383</v>
+        <v>364</v>
       </c>
       <c r="F110" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G110" s="6">
-        <v>2055</v>
+        <v>780</v>
       </c>
       <c r="H110" s="5"/>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
-        <v>6010000218</v>
+        <v>4010013262</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>381</v>
+        <v>14</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>384</v>
+        <v>15</v>
       </c>
       <c r="D111" s="4">
-        <v>46812</v>
+        <v>46549</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>383</v>
+        <v>16</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G111" s="6">
-        <v>500</v>
+        <v>340</v>
       </c>
       <c r="H111" s="5"/>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
-        <v>6010000083</v>
+        <v>4010013671</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>181</v>
+        <v>127</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>182</v>
+        <v>128</v>
       </c>
       <c r="D112" s="4">
-        <v>46537</v>
+        <v>46566</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>183</v>
+        <v>16</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G112" s="6">
-        <v>1510</v>
+        <v>1920</v>
       </c>
       <c r="H112" s="5"/>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="2">
-        <v>6010000084</v>
+        <v>6010000252</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>184</v>
+        <v>407</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>185</v>
+        <v>408</v>
       </c>
       <c r="D113" s="4">
-        <v>46711</v>
+        <v>46780</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>186</v>
+        <v>409</v>
       </c>
       <c r="F113" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G113" s="6">
-        <v>1940</v>
+        <v>1490</v>
       </c>
       <c r="H113" s="5"/>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
-        <v>6010000115</v>
+        <v>6010000218</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>236</v>
+        <v>381</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>237</v>
+        <v>382</v>
       </c>
       <c r="D114" s="4">
-        <v>46971</v>
+        <v>46812</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>23</v>
+        <v>383</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G114" s="6">
-        <v>7100</v>
+        <v>500</v>
       </c>
       <c r="H114" s="5"/>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
-        <v>6010000116</v>
+        <v>6010000218</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>238</v>
+        <v>381</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>239</v>
+        <v>384</v>
       </c>
       <c r="D115" s="4">
-        <v>46971</v>
+        <v>46780</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>4</v>
+        <v>383</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G115" s="6">
-        <v>5680</v>
+        <v>2025</v>
       </c>
       <c r="H115" s="5"/>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
-        <v>7050000019</v>
+        <v>6010000083</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>418</v>
+        <v>181</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D116" s="4"/>
+        <v>182</v>
+      </c>
+      <c r="D116" s="4">
+        <v>46537</v>
+      </c>
       <c r="E116" s="3" t="s">
-        <v>2</v>
+        <v>183</v>
       </c>
       <c r="F116" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G116" s="6">
-        <v>530</v>
+        <v>1510</v>
       </c>
       <c r="H116" s="5"/>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
-        <v>6010000117</v>
+        <v>6010000084</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>240</v>
+        <v>184</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>241</v>
+        <v>185</v>
       </c>
       <c r="D117" s="4">
         <v>46711</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>23</v>
+        <v>186</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G117" s="6">
-        <v>5800</v>
+        <v>1940</v>
       </c>
       <c r="H117" s="5"/>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
-        <v>6010000118</v>
+        <v>6010000115</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="D118" s="4">
-        <v>46574</v>
+        <v>46971</v>
       </c>
       <c r="E118" s="3" t="s">
         <v>23</v>
@@ -4588,574 +4587,562 @@
         <v>5</v>
       </c>
       <c r="G118" s="6">
-        <v>6640</v>
+        <v>7100</v>
       </c>
       <c r="H118" s="5"/>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
-        <v>6010000119</v>
+        <v>6010000116</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="D119" s="4">
-        <v>46598</v>
+        <v>46971</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>246</v>
+        <v>4</v>
       </c>
       <c r="F119" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G119" s="6">
-        <v>160</v>
+        <v>5680</v>
       </c>
       <c r="H119" s="5"/>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" s="2">
-        <v>6010000085</v>
+        <v>7050000019</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>187</v>
+        <v>419</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="D120" s="4">
-        <v>46388</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D120" s="4"/>
       <c r="E120" s="3" t="s">
-        <v>189</v>
+        <v>2</v>
       </c>
       <c r="F120" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G120" s="6">
-        <v>41100</v>
+        <v>530</v>
       </c>
       <c r="H120" s="5"/>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
-        <v>6010000085</v>
+        <v>6010000117</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>187</v>
+        <v>240</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>190</v>
+        <v>241</v>
       </c>
       <c r="D121" s="4">
-        <v>46388</v>
+        <v>46711</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>189</v>
+        <v>23</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G121" s="6">
-        <v>8400</v>
+        <v>5800</v>
       </c>
       <c r="H121" s="5"/>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
-        <v>6010000123</v>
+        <v>6010000118</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D122" s="4">
-        <v>46752</v>
+        <v>46574</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>82</v>
+        <v>23</v>
       </c>
       <c r="F122" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G122" s="6">
-        <v>3700</v>
+        <v>6640</v>
       </c>
       <c r="H122" s="5"/>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
-        <v>6010000086</v>
+        <v>6010000119</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>191</v>
+        <v>244</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>192</v>
+        <v>245</v>
       </c>
       <c r="D123" s="4">
-        <v>46721</v>
+        <v>46598</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>193</v>
+        <v>246</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G123" s="6">
-        <v>2000</v>
+        <v>160</v>
       </c>
       <c r="H123" s="5"/>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" s="2">
-        <v>6010000086</v>
+        <v>6010000085</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="D124" s="4">
-        <v>46641</v>
+        <v>46388</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="F124" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G124" s="6">
-        <v>6550</v>
+        <v>41100</v>
       </c>
       <c r="H124" s="5"/>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" s="2">
-        <v>6010000147</v>
+        <v>6010000085</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>293</v>
+        <v>187</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>294</v>
+        <v>190</v>
       </c>
       <c r="D125" s="4">
-        <v>46813</v>
+        <v>46388</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>277</v>
+        <v>189</v>
       </c>
       <c r="F125" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G125" s="6">
-        <v>480</v>
+        <v>8400</v>
       </c>
       <c r="H125" s="5"/>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A126" s="2">
-        <v>6010000144</v>
-      </c>
-      <c r="B126" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="C126" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="D126" s="4">
-        <v>46605</v>
-      </c>
-      <c r="E126" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="F126" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G126" s="6">
-        <v>100</v>
-      </c>
-      <c r="H126" s="5"/>
+      <c r="A126" s="7">
+        <v>6010000122</v>
+      </c>
+      <c r="B126" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="C126" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D126" s="9"/>
+      <c r="E126" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F126" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G126" s="10"/>
+      <c r="H126" s="10">
+        <v>1440</v>
+      </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" s="2">
-        <v>6010000214</v>
+        <v>6010000123</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>372</v>
+        <v>248</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>373</v>
+        <v>249</v>
       </c>
       <c r="D127" s="4">
-        <v>46692</v>
+        <v>46752</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>289</v>
+        <v>82</v>
       </c>
       <c r="F127" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G127" s="6">
-        <v>290</v>
+        <v>3700</v>
       </c>
       <c r="H127" s="5"/>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" s="2">
-        <v>6010000215</v>
+        <v>6010000086</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>374</v>
+        <v>191</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>375</v>
+        <v>192</v>
       </c>
       <c r="D128" s="4">
-        <v>46726</v>
+        <v>46721</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>376</v>
+        <v>193</v>
       </c>
       <c r="F128" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G128" s="6">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="H128" s="5"/>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
-        <v>6010000143</v>
+        <v>6010000086</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>282</v>
+        <v>191</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>283</v>
+        <v>194</v>
       </c>
       <c r="D129" s="4">
-        <v>46425</v>
+        <v>46641</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>284</v>
+        <v>193</v>
       </c>
       <c r="F129" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G129" s="6">
-        <v>103</v>
+        <v>6550</v>
       </c>
       <c r="H129" s="5"/>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A130" s="2">
-        <v>6010000145</v>
-      </c>
-      <c r="B130" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="C130" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="D130" s="4">
-        <v>46556</v>
-      </c>
-      <c r="E130" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="F130" s="3" t="s">
+      <c r="A130" s="7">
+        <v>6010000147</v>
+      </c>
+      <c r="B130" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="C130" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D130" s="9"/>
+      <c r="E130" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="F130" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G130" s="6">
-        <v>175</v>
-      </c>
-      <c r="H130" s="5"/>
+      <c r="G130" s="10"/>
+      <c r="H130" s="10">
+        <v>1000</v>
+      </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" s="2">
-        <v>4010013596</v>
+        <v>6010000147</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>102</v>
+        <v>293</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>103</v>
+        <v>294</v>
       </c>
       <c r="D131" s="4">
-        <v>46446</v>
+        <v>46813</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>31</v>
+        <v>277</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G131" s="6">
-        <v>260</v>
+        <v>480</v>
       </c>
       <c r="H131" s="5"/>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" s="2">
-        <v>4010013655</v>
+        <v>6010000144</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>106</v>
+        <v>285</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>107</v>
+        <v>286</v>
       </c>
       <c r="D132" s="4">
-        <v>46550</v>
+        <v>46605</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>31</v>
+        <v>277</v>
       </c>
       <c r="F132" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G132" s="6">
-        <v>370</v>
+        <v>100</v>
       </c>
       <c r="H132" s="5"/>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" s="2">
-        <v>4010013474</v>
+        <v>6010000214</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>46</v>
+        <v>372</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>47</v>
+        <v>373</v>
       </c>
       <c r="D133" s="4">
-        <v>46579</v>
+        <v>46692</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>31</v>
+        <v>289</v>
       </c>
       <c r="F133" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G133" s="6">
-        <v>590</v>
+        <v>290</v>
       </c>
       <c r="H133" s="5"/>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
-        <v>4010013474</v>
+        <v>6010000215</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>46</v>
+        <v>374</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>48</v>
+        <v>375</v>
       </c>
       <c r="D134" s="4">
-        <v>46511</v>
+        <v>46726</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>31</v>
+        <v>376</v>
       </c>
       <c r="F134" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G134" s="6">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="H134" s="5"/>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A135" s="2">
-        <v>4010013475</v>
-      </c>
-      <c r="B135" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C135" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D135" s="4">
-        <v>46525</v>
-      </c>
-      <c r="E135" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F135" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G135" s="6">
-        <v>1330</v>
-      </c>
-      <c r="H135" s="5"/>
+      <c r="A135" s="7">
+        <v>6010000142</v>
+      </c>
+      <c r="B135" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="C135" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D135" s="9"/>
+      <c r="E135" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="F135" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="G135" s="10"/>
+      <c r="H135" s="10">
+        <v>3000</v>
+      </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" s="2">
-        <v>6010000087</v>
+        <v>6010000143</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>195</v>
+        <v>282</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>196</v>
+        <v>283</v>
       </c>
       <c r="D136" s="4">
-        <v>46388</v>
+        <v>46425</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>180</v>
+        <v>284</v>
       </c>
       <c r="F136" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G136" s="6">
-        <v>600</v>
+        <v>101</v>
       </c>
       <c r="H136" s="5"/>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A137" s="2">
-        <v>6010000087</v>
-      </c>
-      <c r="B137" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="C137" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="D137" s="4">
-        <v>46484</v>
-      </c>
-      <c r="E137" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="F137" s="3" t="s">
+      <c r="A137" s="7">
+        <v>6010000145</v>
+      </c>
+      <c r="B137" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="C137" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D137" s="9"/>
+      <c r="E137" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="F137" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G137" s="6">
-        <v>10000</v>
-      </c>
-      <c r="H137" s="5"/>
+      <c r="G137" s="10"/>
+      <c r="H137" s="10">
+        <v>300</v>
+      </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" s="2">
-        <v>6010000126</v>
+        <v>6010000145</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>250</v>
+        <v>287</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>251</v>
+        <v>288</v>
       </c>
       <c r="D138" s="4">
-        <v>46780</v>
+        <v>46556</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>23</v>
+        <v>289</v>
       </c>
       <c r="F138" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G138" s="6">
-        <v>2800</v>
+        <v>175</v>
       </c>
       <c r="H138" s="5"/>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" s="2">
-        <v>6010000227</v>
+        <v>4010013596</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>387</v>
+        <v>102</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>388</v>
+        <v>103</v>
       </c>
       <c r="D139" s="4">
-        <v>46645</v>
+        <v>46446</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F139" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G139" s="6">
-        <v>2240</v>
+        <v>210</v>
       </c>
       <c r="H139" s="5"/>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A140" s="2">
-        <v>6010000227</v>
-      </c>
-      <c r="B140" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="C140" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="D140" s="4">
-        <v>46631</v>
-      </c>
-      <c r="E140" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F140" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G140" s="6">
-        <v>4840</v>
-      </c>
-      <c r="H140" s="5"/>
+      <c r="A140" s="7">
+        <v>4010013655</v>
+      </c>
+      <c r="B140" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="C140" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D140" s="9"/>
+      <c r="E140" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F140" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G140" s="10"/>
+      <c r="H140" s="10">
+        <v>400</v>
+      </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" s="2">
-        <v>6010000088</v>
+        <v>4010013655</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>198</v>
+        <v>106</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>199</v>
+        <v>107</v>
       </c>
       <c r="D141" s="4">
-        <v>46661</v>
+        <v>46550</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>200</v>
+        <v>31</v>
       </c>
       <c r="F141" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G141" s="6">
-        <v>2660</v>
+        <v>360</v>
       </c>
       <c r="H141" s="5"/>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" s="2">
-        <v>4010013666</v>
+        <v>4010013474</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>124</v>
+        <v>46</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>125</v>
+        <v>47</v>
       </c>
       <c r="D142" s="4">
-        <v>46625</v>
+        <v>46511</v>
       </c>
       <c r="E142" s="3" t="s">
         <v>31</v>
@@ -5164,22 +5151,22 @@
         <v>5</v>
       </c>
       <c r="G142" s="6">
-        <v>300</v>
+        <v>40</v>
       </c>
       <c r="H142" s="5"/>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" s="2">
-        <v>4010013666</v>
+        <v>4010013474</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>124</v>
+        <v>46</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>126</v>
+        <v>48</v>
       </c>
       <c r="D143" s="4">
-        <v>46593</v>
+        <v>46579</v>
       </c>
       <c r="E143" s="3" t="s">
         <v>31</v>
@@ -5188,22 +5175,22 @@
         <v>5</v>
       </c>
       <c r="G143" s="6">
-        <v>50</v>
+        <v>590</v>
       </c>
       <c r="H143" s="5"/>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" s="2">
-        <v>6010000128</v>
+        <v>4010013475</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>252</v>
+        <v>49</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>253</v>
+        <v>50</v>
       </c>
       <c r="D144" s="4">
-        <v>46721</v>
+        <v>46525</v>
       </c>
       <c r="E144" s="3" t="s">
         <v>31</v>
@@ -5212,790 +5199,786 @@
         <v>5</v>
       </c>
       <c r="G144" s="6">
-        <v>760</v>
+        <v>1330</v>
       </c>
       <c r="H144" s="5"/>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" s="2">
-        <v>6010000129</v>
+        <v>6010000087</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>254</v>
+        <v>195</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>255</v>
+        <v>196</v>
       </c>
       <c r="D145" s="4">
-        <v>46758</v>
+        <v>46484</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>16</v>
+        <v>180</v>
       </c>
       <c r="F145" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G145" s="6">
-        <v>950</v>
+        <v>10000</v>
       </c>
       <c r="H145" s="5"/>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" s="2">
-        <v>6010000130</v>
+        <v>6010000087</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>256</v>
+        <v>195</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>257</v>
+        <v>197</v>
       </c>
       <c r="D146" s="4">
-        <v>46753</v>
+        <v>46388</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>31</v>
+        <v>180</v>
       </c>
       <c r="F146" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G146" s="6">
-        <v>920</v>
+        <v>600</v>
       </c>
       <c r="H146" s="5"/>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A147" s="2">
-        <v>6010000198</v>
-      </c>
-      <c r="B147" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="C147" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="D147" s="4">
-        <v>46568</v>
-      </c>
-      <c r="E147" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F147" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G147" s="6">
-        <v>560</v>
-      </c>
-      <c r="H147" s="5"/>
+      <c r="A147" s="7">
+        <v>6010000126</v>
+      </c>
+      <c r="B147" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="C147" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D147" s="9"/>
+      <c r="E147" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F147" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G147" s="10"/>
+      <c r="H147" s="10">
+        <v>2000</v>
+      </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" s="2">
-        <v>4010013586</v>
+        <v>6010000126</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>90</v>
+        <v>250</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>91</v>
+        <v>251</v>
       </c>
       <c r="D148" s="4">
-        <v>46537</v>
+        <v>46780</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F148" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G148" s="6">
-        <v>1250</v>
+        <v>2800</v>
       </c>
       <c r="H148" s="5"/>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" s="2">
-        <v>4010013549</v>
+        <v>6010000227</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>66</v>
+        <v>387</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>67</v>
+        <v>388</v>
       </c>
       <c r="D149" s="4">
-        <v>46525</v>
+        <v>46645</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F149" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G149" s="6">
-        <v>920</v>
+        <v>2240</v>
       </c>
       <c r="H149" s="5"/>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" s="2">
-        <v>4010013249</v>
+        <v>6010000227</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>0</v>
+        <v>387</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>1</v>
+        <v>389</v>
       </c>
       <c r="D150" s="4">
-        <v>46442</v>
+        <v>46631</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F150" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G150" s="6">
-        <v>280</v>
+        <v>4840</v>
       </c>
       <c r="H150" s="5"/>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" s="2">
-        <v>4010013573</v>
+        <v>6010000088</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>74</v>
+        <v>198</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>75</v>
+        <v>199</v>
       </c>
       <c r="D151" s="4">
-        <v>46423</v>
+        <v>46661</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>4</v>
+        <v>200</v>
       </c>
       <c r="F151" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G151" s="6">
-        <v>480</v>
+        <v>2660</v>
       </c>
       <c r="H151" s="5"/>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" s="2">
-        <v>4010013574</v>
+        <v>4010013666</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>76</v>
+        <v>124</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>77</v>
+        <v>125</v>
       </c>
       <c r="D152" s="4">
-        <v>46545</v>
+        <v>46593</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="F152" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G152" s="6">
-        <v>560</v>
+        <v>50</v>
       </c>
       <c r="H152" s="5"/>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" s="2">
-        <v>4010013588</v>
+        <v>4010013666</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>93</v>
+        <v>126</v>
       </c>
       <c r="D153" s="4">
-        <v>46582</v>
+        <v>46625</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="F153" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G153" s="6">
-        <v>2020</v>
+        <v>300</v>
       </c>
       <c r="H153" s="5"/>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" s="2">
-        <v>4010013479</v>
+        <v>6010000128</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>57</v>
+        <v>252</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>58</v>
+        <v>253</v>
       </c>
       <c r="D154" s="4">
-        <v>46594</v>
+        <v>46721</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="F154" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G154" s="6">
-        <v>400</v>
+        <v>760</v>
       </c>
       <c r="H154" s="5"/>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" s="2">
-        <v>4010013479</v>
+        <v>6010000129</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>57</v>
+        <v>254</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>59</v>
+        <v>255</v>
       </c>
       <c r="D155" s="4">
-        <v>46419</v>
+        <v>46758</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F155" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G155" s="6">
-        <v>180</v>
+        <v>950</v>
       </c>
       <c r="H155" s="5"/>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" s="2">
-        <v>4010013479</v>
+        <v>6010000130</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>57</v>
+        <v>256</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>60</v>
+        <v>257</v>
       </c>
       <c r="D156" s="4">
-        <v>46536</v>
+        <v>46753</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="F156" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G156" s="6">
-        <v>320</v>
+        <v>920</v>
       </c>
       <c r="H156" s="5"/>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" s="2">
-        <v>4010013700</v>
+        <v>6010000198</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>138</v>
+        <v>358</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>139</v>
+        <v>359</v>
       </c>
       <c r="D157" s="4">
-        <v>46533</v>
+        <v>46568</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F157" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G157" s="6">
-        <v>300</v>
+        <v>560</v>
       </c>
       <c r="H157" s="5"/>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" s="2">
-        <v>4010013700</v>
+        <v>4010013586</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>138</v>
+        <v>90</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>140</v>
+        <v>91</v>
       </c>
       <c r="D158" s="4">
-        <v>46446</v>
+        <v>46537</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F158" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G158" s="6">
-        <v>520</v>
+        <v>1250</v>
       </c>
       <c r="H158" s="5"/>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" s="2">
-        <v>4010013701</v>
+        <v>4010013549</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>141</v>
+        <v>66</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>142</v>
+        <v>67</v>
       </c>
       <c r="D159" s="4">
-        <v>46589</v>
+        <v>46525</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F159" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G159" s="6">
-        <v>1160</v>
+        <v>920</v>
       </c>
       <c r="H159" s="5"/>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" s="2">
-        <v>4010013657</v>
+        <v>4010013249</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>112</v>
+        <v>1</v>
       </c>
       <c r="D160" s="4">
-        <v>46513</v>
+        <v>46442</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F160" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G160" s="6">
-        <v>700</v>
+        <v>280</v>
       </c>
       <c r="H160" s="5"/>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" s="2">
-        <v>4010013658</v>
+        <v>4010013573</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>113</v>
+        <v>74</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="D161" s="4">
-        <v>46587</v>
+        <v>46423</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F161" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G161" s="6">
-        <v>1090</v>
+        <v>480</v>
       </c>
       <c r="H161" s="5"/>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" s="2">
-        <v>4010013548</v>
+        <v>4010013574</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="D162" s="4">
-        <v>46469</v>
+        <v>46545</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>65</v>
+        <v>7</v>
       </c>
       <c r="F162" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G162" s="6">
-        <v>730</v>
+        <v>560</v>
       </c>
       <c r="H162" s="5"/>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" s="2">
-        <v>4010013480</v>
+        <v>4010013588</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="D163" s="4">
-        <v>46408</v>
+        <v>46582</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F163" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G163" s="6">
-        <v>1210</v>
+        <v>1820</v>
       </c>
       <c r="H163" s="5"/>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" s="2">
-        <v>4010013477</v>
+        <v>4010013479</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D164" s="4">
-        <v>46574</v>
+        <v>46419</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F164" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G164" s="6">
-        <v>500</v>
+        <v>180</v>
       </c>
       <c r="H164" s="5"/>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" s="2">
-        <v>6010000131</v>
+        <v>4010013479</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>258</v>
+        <v>57</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>259</v>
+        <v>59</v>
       </c>
       <c r="D165" s="4">
-        <v>46784</v>
+        <v>46594</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F165" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G165" s="6">
-        <v>1520</v>
+        <v>400</v>
       </c>
       <c r="H165" s="5"/>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" s="2">
-        <v>4010013699</v>
+        <v>4010013479</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>136</v>
+        <v>57</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>137</v>
+        <v>60</v>
       </c>
       <c r="D166" s="4">
-        <v>46438</v>
+        <v>46536</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="F166" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G166" s="6">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="H166" s="5"/>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" s="2">
-        <v>6010000089</v>
+        <v>4010013700</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>201</v>
+        <v>138</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>202</v>
+        <v>139</v>
       </c>
       <c r="D167" s="4">
-        <v>46789</v>
+        <v>46446</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>203</v>
+        <v>4</v>
       </c>
       <c r="F167" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G167" s="6">
-        <v>2360</v>
+        <v>520</v>
       </c>
       <c r="H167" s="5"/>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" s="2">
-        <v>6010000089</v>
+        <v>4010013700</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>201</v>
+        <v>138</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>204</v>
+        <v>140</v>
       </c>
       <c r="D168" s="4">
-        <v>46871</v>
+        <v>46533</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>203</v>
+        <v>4</v>
       </c>
       <c r="F168" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G168" s="6">
-        <v>2300</v>
+        <v>300</v>
       </c>
       <c r="H168" s="5"/>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" s="2">
-        <v>6010000132</v>
+        <v>4010013701</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>260</v>
+        <v>141</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>261</v>
+        <v>142</v>
       </c>
       <c r="D169" s="4">
-        <v>46614</v>
+        <v>46589</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="F169" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G169" s="6">
-        <v>2450</v>
+        <v>1160</v>
       </c>
       <c r="H169" s="5"/>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" s="2">
-        <v>6010000146</v>
+        <v>4010013657</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>290</v>
+        <v>111</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>291</v>
+        <v>112</v>
       </c>
       <c r="D170" s="4">
-        <v>46746</v>
+        <v>46513</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>292</v>
+        <v>7</v>
       </c>
       <c r="F170" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G170" s="6">
-        <v>480</v>
+        <v>700</v>
       </c>
       <c r="H170" s="5"/>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" s="2">
-        <v>6010000090</v>
+        <v>4010013658</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>205</v>
+        <v>113</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>206</v>
+        <v>114</v>
       </c>
       <c r="D171" s="4">
-        <v>46482</v>
+        <v>46587</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>207</v>
+        <v>7</v>
       </c>
       <c r="F171" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G171" s="6">
-        <v>4400</v>
+        <v>1090</v>
       </c>
       <c r="H171" s="5"/>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" s="2">
-        <v>6010000199</v>
+        <v>4010013548</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>360</v>
+        <v>63</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>361</v>
+        <v>64</v>
       </c>
       <c r="D172" s="4">
-        <v>46556</v>
+        <v>46469</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="F172" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G172" s="6">
-        <v>1640</v>
+        <v>720</v>
       </c>
       <c r="H172" s="5"/>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" s="2">
-        <v>6010000133</v>
+        <v>4010013480</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>262</v>
+        <v>61</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>263</v>
+        <v>62</v>
       </c>
       <c r="D173" s="4">
-        <v>46388</v>
+        <v>46408</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>82</v>
+        <v>7</v>
       </c>
       <c r="F173" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G173" s="6">
-        <v>980</v>
+        <v>1210</v>
       </c>
       <c r="H173" s="5"/>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A174" s="2">
-        <v>6010000134</v>
-      </c>
-      <c r="B174" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="C174" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="D174" s="4">
-        <v>46488</v>
-      </c>
-      <c r="E174" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="F174" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G174" s="6">
-        <v>160</v>
-      </c>
-      <c r="H174" s="5"/>
+      <c r="A174" s="7">
+        <v>4010013477</v>
+      </c>
+      <c r="B174" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C174" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D174" s="9"/>
+      <c r="E174" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F174" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G174" s="10"/>
+      <c r="H174" s="10">
+        <v>960</v>
+      </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" s="2">
-        <v>6010000135</v>
+        <v>4010013477</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>266</v>
+        <v>53</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>267</v>
+        <v>54</v>
       </c>
       <c r="D175" s="4">
-        <v>46388</v>
+        <v>46574</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>82</v>
+        <v>7</v>
       </c>
       <c r="F175" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G175" s="6">
-        <v>1460</v>
+        <v>500</v>
       </c>
       <c r="H175" s="5"/>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" s="2">
-        <v>6010000136</v>
+        <v>6010000131</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="D176" s="4">
-        <v>46496</v>
+        <v>46784</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F176" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G176" s="6">
-        <v>290</v>
+        <v>1500</v>
       </c>
       <c r="H176" s="5"/>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" s="2">
-        <v>6010000137</v>
+        <v>4010013699</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>270</v>
+        <v>136</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>271</v>
+        <v>137</v>
       </c>
       <c r="D177" s="4">
-        <v>46496</v>
+        <v>46438</v>
       </c>
       <c r="E177" s="3" t="s">
         <v>31</v>
@@ -6004,562 +5987,980 @@
         <v>5</v>
       </c>
       <c r="G177" s="6">
-        <v>130</v>
+        <v>310</v>
       </c>
       <c r="H177" s="5"/>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" s="2">
-        <v>4010013269</v>
+        <v>6010000089</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>21</v>
+        <v>201</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>22</v>
+        <v>202</v>
       </c>
       <c r="D178" s="4">
-        <v>46558</v>
+        <v>46871</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>23</v>
+        <v>203</v>
       </c>
       <c r="F178" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G178" s="6">
-        <v>820</v>
+        <v>2300</v>
       </c>
       <c r="H178" s="5"/>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" s="2">
-        <v>6010000177</v>
+        <v>6010000089</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>336</v>
+        <v>201</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>337</v>
+        <v>204</v>
       </c>
       <c r="D179" s="4">
-        <v>46971</v>
+        <v>46789</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>338</v>
+        <v>203</v>
       </c>
       <c r="F179" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G179" s="6">
-        <v>1680</v>
+        <v>2360</v>
       </c>
       <c r="H179" s="5"/>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" s="2">
-        <v>6010000178</v>
+        <v>6010000132</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>339</v>
+        <v>260</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>340</v>
+        <v>261</v>
       </c>
       <c r="D180" s="4">
-        <v>47087</v>
+        <v>46614</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>341</v>
+        <v>31</v>
       </c>
       <c r="F180" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G180" s="6">
-        <v>990</v>
+        <v>2450</v>
       </c>
       <c r="H180" s="5"/>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" s="2">
-        <v>4010013597</v>
+        <v>6010000146</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>104</v>
+        <v>290</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>105</v>
+        <v>291</v>
       </c>
       <c r="D181" s="4">
-        <v>46525</v>
+        <v>46746</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>11</v>
+        <v>292</v>
       </c>
       <c r="F181" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G181" s="6">
-        <v>620</v>
+        <v>450</v>
       </c>
       <c r="H181" s="5"/>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" s="2">
-        <v>4010013368</v>
+        <v>6010000090</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>33</v>
+        <v>205</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>34</v>
+        <v>206</v>
       </c>
       <c r="D182" s="4">
-        <v>46533</v>
+        <v>46482</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>4</v>
+        <v>207</v>
       </c>
       <c r="F182" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G182" s="6">
-        <v>160</v>
+        <v>4400</v>
       </c>
       <c r="H182" s="5"/>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" s="2">
-        <v>4010013369</v>
+        <v>6010000199</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>35</v>
+        <v>360</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>36</v>
+        <v>361</v>
       </c>
       <c r="D183" s="4">
-        <v>46533</v>
+        <v>46556</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F183" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G183" s="6">
-        <v>40</v>
+        <v>1640</v>
       </c>
       <c r="H183" s="5"/>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" s="2">
-        <v>4010013399</v>
+        <v>6010000133</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>42</v>
+        <v>262</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>43</v>
+        <v>263</v>
       </c>
       <c r="D184" s="4">
-        <v>46532</v>
+        <v>46388</v>
       </c>
       <c r="E184" s="3" t="s">
-        <v>23</v>
+        <v>82</v>
       </c>
       <c r="F184" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G184" s="6">
-        <v>1070</v>
+        <v>980</v>
       </c>
       <c r="H184" s="5"/>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" s="2">
-        <v>6010000203</v>
+        <v>6010000134</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>367</v>
+        <v>264</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>368</v>
+        <v>265</v>
       </c>
       <c r="D185" s="4">
-        <v>46606</v>
+        <v>46488</v>
       </c>
       <c r="E185" s="3" t="s">
-        <v>364</v>
+        <v>82</v>
       </c>
       <c r="F185" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G185" s="6">
-        <v>370</v>
+        <v>160</v>
       </c>
       <c r="H185" s="5"/>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" s="2">
-        <v>4010013592</v>
+        <v>6010000135</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>94</v>
+        <v>266</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>95</v>
+        <v>267</v>
       </c>
       <c r="D186" s="4">
-        <v>46514</v>
+        <v>46388</v>
       </c>
       <c r="E186" s="3" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="F186" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G186" s="6">
-        <v>230</v>
+        <v>1460</v>
       </c>
       <c r="H186" s="5"/>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A187" s="2">
-        <v>4010014926</v>
-      </c>
-      <c r="B187" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="C187" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D187" s="4">
-        <v>46768</v>
-      </c>
-      <c r="E187" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="F187" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G187" s="6">
-        <v>750</v>
-      </c>
-      <c r="H187" s="5"/>
+      <c r="A187" s="7">
+        <v>6010000136</v>
+      </c>
+      <c r="B187" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="C187" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D187" s="9"/>
+      <c r="E187" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F187" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G187" s="10"/>
+      <c r="H187" s="10">
+        <v>400</v>
+      </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" s="2">
-        <v>7050000020</v>
+        <v>6010000136</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>419</v>
+        <v>268</v>
       </c>
       <c r="C188" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="D188" s="4">
+        <v>46496</v>
+      </c>
+      <c r="E188" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F188" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G188" s="6">
+        <v>290</v>
+      </c>
+      <c r="H188" s="5"/>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A189" s="7">
+        <v>6010000137</v>
+      </c>
+      <c r="B189" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="C189" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D188" s="4"/>
-      <c r="E188" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F188" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G188" s="6">
-        <v>30</v>
-      </c>
-      <c r="H188" s="5"/>
-    </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A189" s="2">
-        <v>7050000020</v>
-      </c>
-      <c r="B189" s="3" t="s">
-        <v>419</v>
-      </c>
-      <c r="C189" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D189" s="4"/>
-      <c r="E189" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F189" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G189" s="6">
-        <v>70</v>
-      </c>
-      <c r="H189" s="5"/>
+      <c r="D189" s="9"/>
+      <c r="E189" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F189" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G189" s="10"/>
+      <c r="H189" s="10">
+        <v>400</v>
+      </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190" s="2">
-        <v>4010013659</v>
+        <v>6010000137</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>115</v>
+        <v>270</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>116</v>
+        <v>271</v>
       </c>
       <c r="D190" s="4">
-        <v>46526</v>
+        <v>46496</v>
       </c>
       <c r="E190" s="3" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="F190" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G190" s="6">
-        <v>1250</v>
+        <v>130</v>
       </c>
       <c r="H190" s="5"/>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" s="2">
-        <v>4010013273</v>
+        <v>4010013269</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D191" s="4">
-        <v>46444</v>
+        <v>46558</v>
       </c>
       <c r="E191" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F191" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G191" s="6">
-        <v>710</v>
+        <v>820</v>
       </c>
       <c r="H191" s="5"/>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192" s="2">
-        <v>4010013273</v>
+        <v>6010000177</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>29</v>
+        <v>336</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>32</v>
+        <v>337</v>
       </c>
       <c r="D192" s="4">
-        <v>46444</v>
+        <v>46971</v>
       </c>
       <c r="E192" s="3" t="s">
-        <v>31</v>
+        <v>338</v>
       </c>
       <c r="F192" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G192" s="6">
-        <v>20</v>
+        <v>1680</v>
       </c>
       <c r="H192" s="5"/>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" s="2">
-        <v>4010013271</v>
+        <v>6010000178</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>24</v>
+        <v>339</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>25</v>
+        <v>340</v>
       </c>
       <c r="D193" s="4">
-        <v>46402</v>
+        <v>47087</v>
       </c>
       <c r="E193" s="3" t="s">
-        <v>8</v>
+        <v>341</v>
       </c>
       <c r="F193" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G193" s="6">
-        <v>280</v>
+        <v>990</v>
       </c>
       <c r="H193" s="5"/>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" s="2">
-        <v>4010013272</v>
+        <v>4010013597</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>26</v>
+        <v>104</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>27</v>
+        <v>105</v>
       </c>
       <c r="D194" s="4">
-        <v>46594</v>
+        <v>46525</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F194" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G194" s="6">
-        <v>360</v>
+        <v>620</v>
       </c>
       <c r="H194" s="5"/>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" s="2">
-        <v>4010013272</v>
+        <v>4010013368</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D195" s="4">
-        <v>46523</v>
+        <v>46533</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F195" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G195" s="6">
-        <v>880</v>
+        <v>160</v>
       </c>
       <c r="H195" s="5"/>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A196" s="2">
-        <v>4010013663</v>
-      </c>
-      <c r="B196" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C196" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D196" s="4">
-        <v>46612</v>
-      </c>
-      <c r="E196" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F196" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G196" s="6">
-        <v>1100</v>
-      </c>
-      <c r="H196" s="5"/>
+      <c r="A196" s="7">
+        <v>4010013369</v>
+      </c>
+      <c r="B196" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C196" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D196" s="9"/>
+      <c r="E196" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F196" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G196" s="10"/>
+      <c r="H196" s="10">
+        <v>360</v>
+      </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" s="2">
-        <v>6010000093</v>
+        <v>4010013369</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>208</v>
+        <v>35</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>209</v>
+        <v>36</v>
       </c>
       <c r="D197" s="4">
-        <v>46484</v>
+        <v>46533</v>
       </c>
       <c r="E197" s="3" t="s">
-        <v>210</v>
+        <v>4</v>
       </c>
       <c r="F197" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G197" s="6">
-        <v>25175</v>
+        <v>40</v>
       </c>
       <c r="H197" s="5"/>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" s="2">
-        <v>6010000093</v>
+        <v>4010013399</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>208</v>
+        <v>42</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>211</v>
+        <v>43</v>
       </c>
       <c r="D198" s="4">
-        <v>46504</v>
+        <v>46532</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>210</v>
+        <v>23</v>
       </c>
       <c r="F198" s="3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G198" s="6">
-        <v>15000</v>
+        <v>1070</v>
       </c>
       <c r="H198" s="5"/>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" s="2">
-        <v>6010000161</v>
+        <v>6010000203</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>314</v>
+        <v>367</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>315</v>
+        <v>368</v>
       </c>
       <c r="D199" s="4">
-        <v>47087</v>
+        <v>46606</v>
       </c>
       <c r="E199" s="3" t="s">
-        <v>316</v>
+        <v>364</v>
       </c>
       <c r="F199" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G199" s="6">
-        <v>474</v>
+        <v>370</v>
       </c>
       <c r="H199" s="5"/>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" s="2">
+        <v>4010013592</v>
+      </c>
+      <c r="B200" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C200" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D200" s="4">
+        <v>46514</v>
+      </c>
+      <c r="E200" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F200" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G200" s="6">
+        <v>230</v>
+      </c>
+      <c r="H200" s="5"/>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A201" s="2">
+        <v>4010014926</v>
+      </c>
+      <c r="B201" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C201" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D201" s="4">
+        <v>46768</v>
+      </c>
+      <c r="E201" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="F201" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G201" s="6">
+        <v>750</v>
+      </c>
+      <c r="H201" s="5"/>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A202" s="2">
+        <v>7050000020</v>
+      </c>
+      <c r="B202" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="C202" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D202" s="4"/>
+      <c r="E202" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F202" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G202" s="6">
+        <v>70</v>
+      </c>
+      <c r="H202" s="5"/>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A203" s="2">
+        <v>7050000020</v>
+      </c>
+      <c r="B203" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="C203" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D203" s="4"/>
+      <c r="E203" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F203" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G203" s="6">
+        <v>30</v>
+      </c>
+      <c r="H203" s="5"/>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A204" s="7">
+        <v>4010013659</v>
+      </c>
+      <c r="B204" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="C204" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D204" s="9"/>
+      <c r="E204" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F204" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G204" s="10"/>
+      <c r="H204" s="10">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A205" s="2">
+        <v>4010013659</v>
+      </c>
+      <c r="B205" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C205" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D205" s="4">
+        <v>46526</v>
+      </c>
+      <c r="E205" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F205" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G205" s="6">
+        <v>1250</v>
+      </c>
+      <c r="H205" s="5"/>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A206" s="2">
+        <v>4010013273</v>
+      </c>
+      <c r="B206" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C206" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D206" s="4">
+        <v>46444</v>
+      </c>
+      <c r="E206" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F206" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G206" s="6">
+        <v>710</v>
+      </c>
+      <c r="H206" s="5"/>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A207" s="2">
+        <v>4010013273</v>
+      </c>
+      <c r="B207" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C207" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D207" s="4">
+        <v>46444</v>
+      </c>
+      <c r="E207" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F207" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G207" s="6">
+        <v>20</v>
+      </c>
+      <c r="H207" s="5"/>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A208" s="7">
+        <v>4010013271</v>
+      </c>
+      <c r="B208" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C208" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D208" s="9"/>
+      <c r="E208" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F208" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G208" s="10"/>
+      <c r="H208" s="10">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A209" s="2">
+        <v>4010013271</v>
+      </c>
+      <c r="B209" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C209" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D209" s="4">
+        <v>46402</v>
+      </c>
+      <c r="E209" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F209" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G209" s="6">
+        <v>280</v>
+      </c>
+      <c r="H209" s="5"/>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A210" s="7">
+        <v>4010013272</v>
+      </c>
+      <c r="B210" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C210" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D210" s="9"/>
+      <c r="E210" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F210" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G210" s="10"/>
+      <c r="H210" s="10">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A211" s="2">
+        <v>4010013272</v>
+      </c>
+      <c r="B211" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C211" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D211" s="4">
+        <v>46523</v>
+      </c>
+      <c r="E211" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F211" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G211" s="6">
+        <v>860</v>
+      </c>
+      <c r="H211" s="5"/>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A212" s="2">
+        <v>4010013272</v>
+      </c>
+      <c r="B212" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C212" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D212" s="4">
+        <v>46594</v>
+      </c>
+      <c r="E212" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F212" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G212" s="6">
+        <v>360</v>
+      </c>
+      <c r="H212" s="5"/>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A213" s="2">
+        <v>4010013663</v>
+      </c>
+      <c r="B213" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C213" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D213" s="4">
+        <v>46612</v>
+      </c>
+      <c r="E213" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F213" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G213" s="6">
+        <v>1100</v>
+      </c>
+      <c r="H213" s="5"/>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A214" s="7">
+        <v>6010000245</v>
+      </c>
+      <c r="B214" s="8" t="s">
+        <v>405</v>
+      </c>
+      <c r="C214" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D214" s="9"/>
+      <c r="E214" s="8" t="s">
+        <v>406</v>
+      </c>
+      <c r="F214" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="G214" s="10"/>
+      <c r="H214" s="10">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A215" s="2">
+        <v>6010000093</v>
+      </c>
+      <c r="B215" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C215" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="D215" s="4">
+        <v>46484</v>
+      </c>
+      <c r="E215" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="F215" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G215" s="6">
+        <v>25175</v>
+      </c>
+      <c r="H215" s="5"/>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A216" s="2">
+        <v>6010000093</v>
+      </c>
+      <c r="B216" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C216" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="D216" s="4">
+        <v>46504</v>
+      </c>
+      <c r="E216" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="F216" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G216" s="6">
+        <v>15000</v>
+      </c>
+      <c r="H216" s="5"/>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A217" s="2">
+        <v>6010000161</v>
+      </c>
+      <c r="B217" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="C217" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="D217" s="4">
+        <v>47087</v>
+      </c>
+      <c r="E217" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="F217" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G217" s="6">
+        <v>450</v>
+      </c>
+      <c r="H217" s="5"/>
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A218" s="2">
         <v>6010000162</v>
       </c>
-      <c r="B200" s="3" t="s">
+      <c r="B218" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="C200" s="3" t="s">
+      <c r="C218" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="D200" s="4">
+      <c r="D218" s="4">
         <v>47087</v>
       </c>
-      <c r="E200" s="3" t="s">
+      <c r="E218" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="F200" s="3" t="s">
+      <c r="F218" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G200" s="6">
+      <c r="G218" s="6">
         <v>1020</v>
       </c>
-      <c r="H200" s="5"/>
+      <c r="H218" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H200" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H200">
-      <sortCondition sortBy="cellColor" ref="B1:B200" dxfId="1"/>
+  <autoFilter ref="A1:H218" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H218">
+      <sortCondition ref="B1:B218"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="0" type="noConversion"/>

--- a/KSTOCK.xlsx
+++ b/KSTOCK.xlsx
@@ -1,29 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c2e6f8dd72a68295/Desktop/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="52" documentId="11_A43A9C41C4094E9AB632FCC5BE28A68627F55F60" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D1574BC-1171-40A7-9222-ACDEB238D07A}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$218</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$218</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="428">
   <si>
     <t>ROSUSEP-20</t>
   </si>
@@ -1307,18 +1301,12 @@
   </si>
   <si>
     <t xml:space="preserve"> Unrestricted Qty</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Transit Qty</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.000"/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -1378,7 +1366,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -1392,9 +1380,6 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1422,24 +1407,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFBE2D5"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFBE2D5"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1495,7 +1463,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1547,7 +1515,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1761,66 +1729,62 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H218"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G218"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="39.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.77734375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.77734375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.77734375" style="1" customWidth="1"/>
     <col min="6" max="6" width="9.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.44140625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9.88671875" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="1"/>
+    <col min="8" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
         <v>421</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>422</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
+        <v>425</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>426</v>
       </c>
-      <c r="D1" s="11" t="s">
-        <v>425</v>
-      </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="11" t="s">
         <v>423</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="11" t="s">
         <v>424</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="11" t="s">
         <v>427</v>
       </c>
-      <c r="H1" s="12" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>6010000095</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4">
+        <v>46568</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>213</v>
-      </c>
-      <c r="D2" s="4">
-        <v>46568</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>23</v>
@@ -1828,23 +1792,22 @@
       <c r="F2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="6">
+      <c r="G2" s="5">
         <v>3800</v>
       </c>
-      <c r="H2" s="5"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>6010000138</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4">
+        <v>46746</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>273</v>
-      </c>
-      <c r="D3" s="4">
-        <v>46746</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>274</v>
@@ -1852,23 +1815,22 @@
       <c r="F3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="5">
         <v>253</v>
       </c>
-      <c r="H3" s="5"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>4010015107</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4">
+        <v>46752</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="D4" s="4">
-        <v>46752</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>110</v>
@@ -1876,23 +1838,22 @@
       <c r="F4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="5">
         <v>1040</v>
       </c>
-      <c r="H4" s="5"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4010013476</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4">
+        <v>46548</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="D5" s="4">
-        <v>46548</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>31</v>
@@ -1900,23 +1861,22 @@
       <c r="F5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="5">
         <v>170</v>
       </c>
-      <c r="H5" s="5"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>6010000097</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4">
+        <v>46556</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>215</v>
-      </c>
-      <c r="D6" s="4">
-        <v>46556</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>216</v>
@@ -1924,23 +1884,22 @@
       <c r="F6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="5">
         <v>100</v>
       </c>
-      <c r="H6" s="5"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6010000097</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4">
+        <v>46751</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>217</v>
-      </c>
-      <c r="D7" s="4">
-        <v>46751</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>216</v>
@@ -1948,23 +1907,22 @@
       <c r="F7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="5">
         <v>160</v>
       </c>
-      <c r="H7" s="5"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>6010000098</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4">
+        <v>46539</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>219</v>
-      </c>
-      <c r="D8" s="4">
-        <v>46539</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>82</v>
@@ -1972,23 +1930,22 @@
       <c r="F8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="5">
         <v>1140</v>
       </c>
-      <c r="H8" s="5"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>6010000195</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4">
+        <v>46549</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>354</v>
-      </c>
-      <c r="D9" s="4">
-        <v>46549</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>23</v>
@@ -1996,45 +1953,41 @@
       <c r="F9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="5">
         <v>400</v>
       </c>
-      <c r="H9" s="5"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="7">
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="6">
         <v>4010013259</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="8"/>
+      <c r="D10" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="F10" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F10" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G10" s="9"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>4010013259</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4">
+        <v>46568</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="D11" s="4">
-        <v>46568</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>7</v>
@@ -2042,23 +1995,22 @@
       <c r="F11" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G11" s="5">
         <v>260</v>
       </c>
-      <c r="H11" s="5"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>4010013260</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="4">
+        <v>46589</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="D12" s="4">
-        <v>46589</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>11</v>
@@ -2066,23 +2018,22 @@
       <c r="F12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="5">
         <v>1200</v>
       </c>
-      <c r="H12" s="5"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>4010013260</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="4">
+        <v>46568</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="D13" s="4">
-        <v>46568</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>11</v>
@@ -2090,23 +2041,22 @@
       <c r="F13" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G13" s="6">
+      <c r="G13" s="5">
         <v>480</v>
       </c>
-      <c r="H13" s="5"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>4010013260</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="4">
+        <v>46435</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>13</v>
-      </c>
-      <c r="D14" s="4">
-        <v>46435</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>11</v>
@@ -2114,23 +2064,22 @@
       <c r="F14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G14" s="6">
+      <c r="G14" s="5">
         <v>10</v>
       </c>
-      <c r="H14" s="5"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>4010013692</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="4">
+        <v>46549</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>130</v>
-      </c>
-      <c r="D15" s="4">
-        <v>46549</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>7</v>
@@ -2138,23 +2087,22 @@
       <c r="F15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G15" s="6">
+      <c r="G15" s="5">
         <v>640</v>
       </c>
-      <c r="H15" s="5"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>4010013693</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="4">
+        <v>46549</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>132</v>
-      </c>
-      <c r="D16" s="4">
-        <v>46549</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>7</v>
@@ -2162,23 +2110,22 @@
       <c r="F16" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G16" s="6">
+      <c r="G16" s="5">
         <v>460</v>
       </c>
-      <c r="H16" s="5"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>4010013693</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="4">
+        <v>46587</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>133</v>
-      </c>
-      <c r="D17" s="4">
-        <v>46587</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>7</v>
@@ -2186,23 +2133,22 @@
       <c r="F17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G17" s="6">
+      <c r="G17" s="5">
         <v>420</v>
       </c>
-      <c r="H17" s="5"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>4010013578</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="4">
+        <v>46640</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="D18" s="4">
-        <v>46640</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>23</v>
@@ -2210,23 +2156,22 @@
       <c r="F18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G18" s="6">
+      <c r="G18" s="5">
         <v>670</v>
       </c>
-      <c r="H18" s="5"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>4010013580</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="4">
+        <v>46666</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="D19" s="4">
-        <v>46666</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>82</v>
@@ -2234,23 +2179,22 @@
       <c r="F19" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G19" s="6">
+      <c r="G19" s="5">
         <v>400</v>
       </c>
-      <c r="H19" s="5"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>4010013551</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="4">
+        <v>46598</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="D20" s="4">
-        <v>46598</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>23</v>
@@ -2258,23 +2202,22 @@
       <c r="F20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G20" s="6">
+      <c r="G20" s="5">
         <v>580</v>
       </c>
-      <c r="H20" s="5"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>4010013660</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="4">
+        <v>46518</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>118</v>
-      </c>
-      <c r="D21" s="4">
-        <v>46518</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>23</v>
@@ -2282,23 +2225,22 @@
       <c r="F21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G21" s="6">
+      <c r="G21" s="5">
         <v>320</v>
       </c>
-      <c r="H21" s="5"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>4010013694</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="4">
+        <v>46536</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>135</v>
-      </c>
-      <c r="D22" s="4">
-        <v>46536</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>7</v>
@@ -2306,23 +2248,22 @@
       <c r="F22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G22" s="6">
+      <c r="G22" s="5">
         <v>930</v>
       </c>
-      <c r="H22" s="5"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>6010000065</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="4">
+        <v>46447</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>153</v>
-      </c>
-      <c r="D23" s="4">
-        <v>46447</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>154</v>
@@ -2330,133 +2271,127 @@
       <c r="F23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G23" s="6">
+      <c r="G23" s="5">
         <v>1800</v>
       </c>
-      <c r="H23" s="5"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>7050000018</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="4"/>
+      <c r="D24" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D24" s="4"/>
       <c r="E24" s="3" t="s">
         <v>414</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G24" s="6">
+      <c r="G24" s="5">
         <v>100</v>
       </c>
-      <c r="H24" s="5"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>7050000016</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="4"/>
+      <c r="D25" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D25" s="4"/>
       <c r="E25" s="3" t="s">
         <v>414</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G25" s="6">
+      <c r="G25" s="5">
         <v>100</v>
       </c>
-      <c r="H25" s="5"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>7050000015</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="4"/>
+      <c r="D26" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D26" s="4"/>
       <c r="E26" s="3" t="s">
         <v>414</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G26" s="6">
+      <c r="G26" s="5">
         <v>100</v>
       </c>
-      <c r="H26" s="5"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>7050000014</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="4"/>
+      <c r="D27" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D27" s="4"/>
       <c r="E27" s="3" t="s">
         <v>414</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G27" s="6">
+      <c r="G27" s="5">
         <v>100</v>
       </c>
-      <c r="H27" s="5"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>7050000017</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="4"/>
+      <c r="D28" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D28" s="4"/>
       <c r="E28" s="3" t="s">
         <v>414</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G28" s="6">
+      <c r="G28" s="5">
         <v>100</v>
       </c>
-      <c r="H28" s="5"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>4010013550</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" s="4">
+        <v>46568</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>69</v>
-      </c>
-      <c r="D29" s="4">
-        <v>46568</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>31</v>
@@ -2464,23 +2399,22 @@
       <c r="F29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G29" s="6">
+      <c r="G29" s="5">
         <v>1130</v>
       </c>
-      <c r="H29" s="5"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>4010013478</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="4">
+        <v>46551</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="D30" s="4">
-        <v>46551</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>31</v>
@@ -2488,45 +2422,41 @@
       <c r="F30" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G30" s="6">
+      <c r="G30" s="5">
         <v>110</v>
       </c>
-      <c r="H30" s="5"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="7">
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="6">
         <v>6010000154</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="7" t="s">
         <v>300</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="C31" s="8"/>
+      <c r="D31" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D31" s="9"/>
-      <c r="E31" s="8" t="s">
+      <c r="E31" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="F31" s="8" t="s">
+      <c r="F31" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G31" s="10"/>
-      <c r="H31" s="10">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G31" s="9"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>6010000154</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="4">
+        <v>47007</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>301</v>
-      </c>
-      <c r="D32" s="4">
-        <v>47007</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>302</v>
@@ -2534,23 +2464,22 @@
       <c r="F32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G32" s="6">
+      <c r="G32" s="5">
         <v>351</v>
       </c>
-      <c r="H32" s="5"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>6010000158</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" s="4">
+        <v>46752</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>308</v>
-      </c>
-      <c r="D33" s="4">
-        <v>46752</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>7</v>
@@ -2558,23 +2487,22 @@
       <c r="F33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G33" s="6">
+      <c r="G33" s="5">
         <v>340</v>
       </c>
-      <c r="H33" s="5"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>6010000068</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" s="4">
+        <v>46495</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="D34" s="4">
-        <v>46495</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>157</v>
@@ -2582,23 +2510,22 @@
       <c r="F34" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G34" s="6">
+      <c r="G34" s="5">
         <v>800</v>
       </c>
-      <c r="H34" s="5"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>6010000159</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" s="4">
+        <v>46780</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>310</v>
-      </c>
-      <c r="D35" s="4">
-        <v>46780</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>31</v>
@@ -2606,23 +2533,22 @@
       <c r="F35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G35" s="6">
+      <c r="G35" s="5">
         <v>70</v>
       </c>
-      <c r="H35" s="5"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>6010000099</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" s="4">
+        <v>46813</v>
+      </c>
+      <c r="D36" s="3" t="s">
         <v>221</v>
-      </c>
-      <c r="D36" s="4">
-        <v>46813</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>82</v>
@@ -2630,23 +2556,22 @@
       <c r="F36" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G36" s="6">
+      <c r="G36" s="5">
         <v>3200</v>
       </c>
-      <c r="H36" s="5"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>6010000160</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C37" s="4">
+        <v>46780</v>
+      </c>
+      <c r="D37" s="3" t="s">
         <v>312</v>
-      </c>
-      <c r="D37" s="4">
-        <v>46780</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>313</v>
@@ -2654,23 +2579,22 @@
       <c r="F37" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G37" s="6">
+      <c r="G37" s="5">
         <v>760</v>
       </c>
-      <c r="H37" s="5"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>6010000234</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" s="4">
+        <v>46726</v>
+      </c>
+      <c r="D38" s="3" t="s">
     